--- a/04-Bieu-Mau/07-FRM-700/FRM-715_Vacuum_Compatible_Clean_Build_and_Bagging_Record.xlsx
+++ b/04-Bieu-Mau/07-FRM-700/FRM-715_Vacuum_Compatible_Clean_Build_and_Bagging_Record.xlsx
@@ -25,7 +25,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="79">
+  <fonts count="81">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -475,6 +475,16 @@
       <color rgb="00334155"/>
       <sz val="8"/>
     </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color theme="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color theme="1"/>
+      <sz val="8"/>
+    </font>
   </fonts>
   <fills count="47">
     <fill>
@@ -709,7 +719,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="271">
+  <borders count="293">
     <border>
       <left/>
       <right/>
@@ -3628,11 +3638,227 @@
       </bottom>
       <diagonal/>
     </border>
+    <border/>
+    <border>
+      <left style="thin">
+        <color rgb="00C5D9E8"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00C5D9E8"/>
+      </left>
+      <right style="thin">
+        <color rgb="00C5D9E8"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00C5D9E8"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00C5D9E8"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00C5D9E8"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00C5D9E8"/>
+      </left>
+      <right style="thin">
+        <color rgb="00C5D9E8"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00C5D9E8"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00C5D9E8"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00C5D9E8"/>
+      </right>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00C5D9E8"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00C5D9E8"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00C5D9E8"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00C5D9E8"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00C5D9E8"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00C5D9E8"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="79" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="340">
+  <cellXfs count="428">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -4415,6 +4641,249 @@
     <xf numFmtId="0" fontId="53" fillId="3" borderId="130" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="79" fillId="4" borderId="272" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="79" fillId="0" borderId="273" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="272" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="274" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="79" fillId="0" borderId="275" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="79" fillId="0" borderId="276" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="276" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="79" fillId="0" borderId="277" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="79" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="79" fillId="0" borderId="278" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="79" fillId="0" borderId="279" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="277" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="278" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="79" fillId="0" borderId="271" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="274" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="274" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="0" borderId="275" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="0" borderId="276" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="276" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="0" borderId="275" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="0" borderId="276" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="276" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="79" fillId="0" borderId="275" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="79" fillId="0" borderId="276" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="274" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="276" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="280" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="0" borderId="279" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="0" borderId="281" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="281" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="0" borderId="279" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="0" borderId="281" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="281" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="281" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="281" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="271" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="271" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="271" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="271" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="271" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="271" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="274" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="275" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="276" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="274" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="79" fillId="0" borderId="273" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="79" fillId="0" borderId="282" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="0" borderId="277" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="0" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="0" borderId="283" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="0" borderId="278" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="271" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="4" borderId="281" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="7" borderId="274" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="3" borderId="274" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="274" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="274" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="274" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="274" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="79" fillId="0" borderId="287" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="79" fillId="0" borderId="289" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="79" fillId="0" borderId="290" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="79" fillId="0" borderId="291" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="79" fillId="0" borderId="292" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="79" fillId="0" borderId="285" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="80" fillId="0" borderId="289" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="0" borderId="290" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="0" borderId="289" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="0" borderId="290" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="79" fillId="0" borderId="289" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="79" fillId="0" borderId="290" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="0" borderId="285" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="0" borderId="286" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="0" borderId="285" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="0" borderId="286" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="79" fillId="0" borderId="287" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="79" fillId="0" borderId="288" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="0" borderId="291" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="0" borderId="284" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="0" borderId="292" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="271" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="287" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="289" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="290" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="291" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="292" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="285" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -4489,39 +4958,6 @@
     </indexedColors>
   </colors>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>219075</colOff>
-      <row>0</row>
-      <rowOff>257175</rowOff>
-    </from>
-    <ext cx="1552575" cy="438150"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="1" name="Image 1" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-</wsDr>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -4909,1871 +5345,2128 @@
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1">
-      <c r="A1" s="267" t="n"/>
-      <c r="B1" s="268" t="n"/>
-      <c r="C1" s="268" t="n"/>
-      <c r="D1" s="268" t="n"/>
-      <c r="E1" s="268" t="n"/>
-      <c r="F1" s="268" t="n"/>
-      <c r="G1" s="268" t="n"/>
-      <c r="H1" s="268" t="n"/>
-      <c r="I1" s="268" t="n"/>
-      <c r="J1" s="268" t="n"/>
-      <c r="K1" s="268" t="n"/>
-      <c r="L1" s="269" t="inlineStr">
+      <c r="A1" s="340" t="n"/>
+      <c r="B1" s="422" t="n"/>
+      <c r="C1" s="422" t="n"/>
+      <c r="D1" s="422" t="n"/>
+      <c r="E1" s="422" t="n"/>
+      <c r="F1" s="422" t="n"/>
+      <c r="G1" s="422" t="n"/>
+      <c r="H1" s="422" t="n"/>
+      <c r="I1" s="422" t="n"/>
+      <c r="J1" s="422" t="n"/>
+      <c r="K1" s="422" t="n"/>
+      <c r="L1" s="342" t="inlineStr">
         <is>
           <t>Vacuum-Compatible Clean Build and Bagging Record</t>
         </is>
       </c>
-      <c r="M1" s="268" t="n"/>
-      <c r="N1" s="268" t="n"/>
-      <c r="O1" s="268" t="n"/>
-      <c r="P1" s="268" t="n"/>
-      <c r="Q1" s="268" t="n"/>
-      <c r="R1" s="268" t="n"/>
-      <c r="S1" s="268" t="n"/>
-      <c r="T1" s="268" t="n"/>
-      <c r="U1" s="268" t="n"/>
-      <c r="V1" s="268" t="n"/>
-      <c r="W1" s="268" t="n"/>
-      <c r="X1" s="268" t="n"/>
-      <c r="Y1" s="268" t="n"/>
-      <c r="Z1" s="268" t="n"/>
-      <c r="AA1" s="268" t="n"/>
-      <c r="AB1" s="268" t="n"/>
-      <c r="AC1" s="268" t="n"/>
-      <c r="AD1" s="268" t="n"/>
-      <c r="AE1" s="268" t="n"/>
-      <c r="AF1" s="268" t="n"/>
-      <c r="AG1" s="268" t="n"/>
-      <c r="AH1" s="268" t="n"/>
-      <c r="AI1" s="268" t="n"/>
-      <c r="AJ1" s="268" t="n"/>
-      <c r="AK1" s="268" t="n"/>
-      <c r="AL1" s="268" t="n"/>
-      <c r="AM1" s="268" t="n"/>
-      <c r="AN1" s="268" t="n"/>
-      <c r="AO1" s="268" t="n"/>
-      <c r="AP1" s="268" t="n"/>
-      <c r="AQ1" s="270" t="n"/>
-      <c r="AR1" s="271" t="n"/>
-      <c r="AS1" s="271" t="n"/>
-      <c r="AT1" s="271" t="n"/>
-      <c r="AU1" s="271" t="n"/>
-      <c r="AV1" s="272" t="n"/>
-      <c r="AW1" s="273" t="inlineStr">
+      <c r="M1" s="422" t="n"/>
+      <c r="N1" s="422" t="n"/>
+      <c r="O1" s="422" t="n"/>
+      <c r="P1" s="422" t="n"/>
+      <c r="Q1" s="422" t="n"/>
+      <c r="R1" s="422" t="n"/>
+      <c r="S1" s="422" t="n"/>
+      <c r="T1" s="422" t="n"/>
+      <c r="U1" s="422" t="n"/>
+      <c r="V1" s="422" t="n"/>
+      <c r="W1" s="422" t="n"/>
+      <c r="X1" s="422" t="n"/>
+      <c r="Y1" s="422" t="n"/>
+      <c r="Z1" s="422" t="n"/>
+      <c r="AA1" s="422" t="n"/>
+      <c r="AB1" s="422" t="n"/>
+      <c r="AC1" s="422" t="n"/>
+      <c r="AD1" s="422" t="n"/>
+      <c r="AE1" s="422" t="n"/>
+      <c r="AF1" s="422" t="n"/>
+      <c r="AG1" s="422" t="n"/>
+      <c r="AH1" s="422" t="n"/>
+      <c r="AI1" s="422" t="n"/>
+      <c r="AJ1" s="422" t="n"/>
+      <c r="AK1" s="422" t="n"/>
+      <c r="AL1" s="422" t="n"/>
+      <c r="AM1" s="422" t="n"/>
+      <c r="AN1" s="422" t="n"/>
+      <c r="AO1" s="422" t="n"/>
+      <c r="AP1" s="422" t="n"/>
+      <c r="AQ1" s="343" t="n"/>
+      <c r="AR1" s="423" t="n"/>
+      <c r="AS1" s="423" t="n"/>
+      <c r="AT1" s="423" t="n"/>
+      <c r="AU1" s="423" t="n"/>
+      <c r="AV1" s="424" t="n"/>
+      <c r="AW1" s="346" t="inlineStr">
         <is>
           <t>FRM-715</t>
         </is>
       </c>
-      <c r="AX1" s="271" t="n"/>
-      <c r="AY1" s="271" t="n"/>
-      <c r="AZ1" s="271" t="n"/>
-      <c r="BA1" s="271" t="n"/>
-      <c r="BB1" s="271" t="n"/>
-      <c r="BC1" s="271" t="n"/>
-      <c r="BD1" s="274" t="n"/>
+      <c r="AX1" s="423" t="n"/>
+      <c r="AY1" s="423" t="n"/>
+      <c r="AZ1" s="423" t="n"/>
+      <c r="BA1" s="423" t="n"/>
+      <c r="BB1" s="423" t="n"/>
+      <c r="BC1" s="423" t="n"/>
+      <c r="BD1" s="424" t="n"/>
     </row>
     <row r="2" ht="15" customHeight="1">
-      <c r="A2" s="275" t="n"/>
-      <c r="L2" s="275" t="n"/>
-      <c r="AQ2" s="270" t="n"/>
-      <c r="AR2" s="271" t="n"/>
-      <c r="AS2" s="271" t="n"/>
-      <c r="AT2" s="271" t="n"/>
-      <c r="AU2" s="271" t="n"/>
-      <c r="AV2" s="272" t="n"/>
-      <c r="AW2" s="273" t="inlineStr">
+      <c r="A2" s="425" t="n"/>
+      <c r="L2" s="425" t="n"/>
+      <c r="AQ2" s="343" t="n"/>
+      <c r="AR2" s="423" t="n"/>
+      <c r="AS2" s="423" t="n"/>
+      <c r="AT2" s="423" t="n"/>
+      <c r="AU2" s="423" t="n"/>
+      <c r="AV2" s="424" t="n"/>
+      <c r="AW2" s="346" t="inlineStr">
         <is>
           <t>V0</t>
         </is>
       </c>
-      <c r="AX2" s="271" t="n"/>
-      <c r="AY2" s="271" t="n"/>
-      <c r="AZ2" s="271" t="n"/>
-      <c r="BA2" s="271" t="n"/>
-      <c r="BB2" s="271" t="n"/>
-      <c r="BC2" s="271" t="n"/>
-      <c r="BD2" s="274" t="n"/>
+      <c r="AX2" s="423" t="n"/>
+      <c r="AY2" s="423" t="n"/>
+      <c r="AZ2" s="423" t="n"/>
+      <c r="BA2" s="423" t="n"/>
+      <c r="BB2" s="423" t="n"/>
+      <c r="BC2" s="423" t="n"/>
+      <c r="BD2" s="424" t="n"/>
     </row>
     <row r="3" ht="15" customHeight="1">
-      <c r="A3" s="275" t="n"/>
-      <c r="L3" s="279" t="n"/>
-      <c r="M3" s="276" t="n"/>
-      <c r="N3" s="276" t="n"/>
-      <c r="O3" s="276" t="n"/>
-      <c r="P3" s="276" t="n"/>
-      <c r="Q3" s="276" t="n"/>
-      <c r="R3" s="276" t="n"/>
-      <c r="S3" s="276" t="n"/>
-      <c r="T3" s="276" t="n"/>
-      <c r="U3" s="276" t="n"/>
-      <c r="V3" s="276" t="n"/>
-      <c r="W3" s="276" t="n"/>
-      <c r="X3" s="276" t="n"/>
-      <c r="Y3" s="276" t="n"/>
-      <c r="Z3" s="276" t="n"/>
-      <c r="AA3" s="276" t="n"/>
-      <c r="AB3" s="276" t="n"/>
-      <c r="AC3" s="276" t="n"/>
-      <c r="AD3" s="276" t="n"/>
-      <c r="AE3" s="276" t="n"/>
-      <c r="AF3" s="276" t="n"/>
-      <c r="AG3" s="276" t="n"/>
-      <c r="AH3" s="276" t="n"/>
-      <c r="AI3" s="276" t="n"/>
-      <c r="AJ3" s="276" t="n"/>
-      <c r="AK3" s="276" t="n"/>
-      <c r="AL3" s="276" t="n"/>
-      <c r="AM3" s="276" t="n"/>
-      <c r="AN3" s="276" t="n"/>
-      <c r="AO3" s="276" t="n"/>
-      <c r="AP3" s="276" t="n"/>
-      <c r="AQ3" s="270" t="n"/>
-      <c r="AR3" s="271" t="n"/>
-      <c r="AS3" s="271" t="n"/>
-      <c r="AT3" s="271" t="n"/>
-      <c r="AU3" s="271" t="n"/>
-      <c r="AV3" s="272" t="n"/>
-      <c r="AW3" s="273" t="inlineStr">
+      <c r="A3" s="425" t="n"/>
+      <c r="L3" s="426" t="n"/>
+      <c r="M3" s="427" t="n"/>
+      <c r="N3" s="427" t="n"/>
+      <c r="O3" s="427" t="n"/>
+      <c r="P3" s="427" t="n"/>
+      <c r="Q3" s="427" t="n"/>
+      <c r="R3" s="427" t="n"/>
+      <c r="S3" s="427" t="n"/>
+      <c r="T3" s="427" t="n"/>
+      <c r="U3" s="427" t="n"/>
+      <c r="V3" s="427" t="n"/>
+      <c r="W3" s="427" t="n"/>
+      <c r="X3" s="427" t="n"/>
+      <c r="Y3" s="427" t="n"/>
+      <c r="Z3" s="427" t="n"/>
+      <c r="AA3" s="427" t="n"/>
+      <c r="AB3" s="427" t="n"/>
+      <c r="AC3" s="427" t="n"/>
+      <c r="AD3" s="427" t="n"/>
+      <c r="AE3" s="427" t="n"/>
+      <c r="AF3" s="427" t="n"/>
+      <c r="AG3" s="427" t="n"/>
+      <c r="AH3" s="427" t="n"/>
+      <c r="AI3" s="427" t="n"/>
+      <c r="AJ3" s="427" t="n"/>
+      <c r="AK3" s="427" t="n"/>
+      <c r="AL3" s="427" t="n"/>
+      <c r="AM3" s="427" t="n"/>
+      <c r="AN3" s="427" t="n"/>
+      <c r="AO3" s="427" t="n"/>
+      <c r="AP3" s="427" t="n"/>
+      <c r="AQ3" s="343" t="n"/>
+      <c r="AR3" s="423" t="n"/>
+      <c r="AS3" s="423" t="n"/>
+      <c r="AT3" s="423" t="n"/>
+      <c r="AU3" s="423" t="n"/>
+      <c r="AV3" s="424" t="n"/>
+      <c r="AW3" s="346" t="inlineStr">
         <is>
           <t>YYYY-MM-DD</t>
         </is>
       </c>
-      <c r="AX3" s="271" t="n"/>
-      <c r="AY3" s="271" t="n"/>
-      <c r="AZ3" s="271" t="n"/>
-      <c r="BA3" s="271" t="n"/>
-      <c r="BB3" s="271" t="n"/>
-      <c r="BC3" s="271" t="n"/>
-      <c r="BD3" s="274" t="n"/>
+      <c r="AX3" s="423" t="n"/>
+      <c r="AY3" s="423" t="n"/>
+      <c r="AZ3" s="423" t="n"/>
+      <c r="BA3" s="423" t="n"/>
+      <c r="BB3" s="423" t="n"/>
+      <c r="BC3" s="423" t="n"/>
+      <c r="BD3" s="424" t="n"/>
     </row>
     <row r="4" ht="15" customHeight="1">
-      <c r="A4" s="275" t="n"/>
-      <c r="L4" s="17" t="inlineStr">
+      <c r="A4" s="425" t="n"/>
+      <c r="L4" s="351" t="inlineStr">
         <is>
           <t>Quality Management System · Controlled Document</t>
         </is>
       </c>
-      <c r="AQ4" s="270" t="n"/>
-      <c r="AR4" s="271" t="n"/>
-      <c r="AS4" s="271" t="n"/>
-      <c r="AT4" s="271" t="n"/>
-      <c r="AU4" s="271" t="n"/>
-      <c r="AV4" s="272" t="n"/>
-      <c r="AW4" s="273" t="inlineStr">
+      <c r="AQ4" s="343" t="n"/>
+      <c r="AR4" s="423" t="n"/>
+      <c r="AS4" s="423" t="n"/>
+      <c r="AT4" s="423" t="n"/>
+      <c r="AU4" s="423" t="n"/>
+      <c r="AV4" s="424" t="n"/>
+      <c r="AW4" s="346" t="inlineStr">
         <is>
           <t>Warehouse + QA</t>
         </is>
       </c>
-      <c r="AX4" s="271" t="n"/>
-      <c r="AY4" s="271" t="n"/>
-      <c r="AZ4" s="271" t="n"/>
-      <c r="BA4" s="271" t="n"/>
-      <c r="BB4" s="271" t="n"/>
-      <c r="BC4" s="271" t="n"/>
-      <c r="BD4" s="274" t="n"/>
+      <c r="AX4" s="423" t="n"/>
+      <c r="AY4" s="423" t="n"/>
+      <c r="AZ4" s="423" t="n"/>
+      <c r="BA4" s="423" t="n"/>
+      <c r="BB4" s="423" t="n"/>
+      <c r="BC4" s="423" t="n"/>
+      <c r="BD4" s="424" t="n"/>
     </row>
     <row r="5" ht="15" customHeight="1">
-      <c r="A5" s="280" t="n"/>
-      <c r="B5" s="281" t="n"/>
-      <c r="C5" s="281" t="n"/>
-      <c r="D5" s="281" t="n"/>
-      <c r="E5" s="281" t="n"/>
-      <c r="F5" s="281" t="n"/>
-      <c r="G5" s="281" t="n"/>
-      <c r="H5" s="281" t="n"/>
-      <c r="I5" s="281" t="n"/>
-      <c r="J5" s="281" t="n"/>
-      <c r="K5" s="281" t="n"/>
-      <c r="L5" s="20" t="inlineStr">
+      <c r="A5" s="426" t="n"/>
+      <c r="B5" s="427" t="n"/>
+      <c r="C5" s="427" t="n"/>
+      <c r="D5" s="427" t="n"/>
+      <c r="E5" s="427" t="n"/>
+      <c r="F5" s="427" t="n"/>
+      <c r="G5" s="427" t="n"/>
+      <c r="H5" s="427" t="n"/>
+      <c r="I5" s="427" t="n"/>
+      <c r="J5" s="427" t="n"/>
+      <c r="K5" s="427" t="n"/>
+      <c r="L5" s="352" t="inlineStr">
         <is>
           <t>HESEM Engineering · ISO 9001 / AS9100 · Semiconductor Equipment Parts</t>
         </is>
       </c>
-      <c r="M5" s="281" t="n"/>
-      <c r="N5" s="281" t="n"/>
-      <c r="O5" s="281" t="n"/>
-      <c r="P5" s="281" t="n"/>
-      <c r="Q5" s="281" t="n"/>
-      <c r="R5" s="281" t="n"/>
-      <c r="S5" s="281" t="n"/>
-      <c r="T5" s="281" t="n"/>
-      <c r="U5" s="281" t="n"/>
-      <c r="V5" s="281" t="n"/>
-      <c r="W5" s="281" t="n"/>
-      <c r="X5" s="281" t="n"/>
-      <c r="Y5" s="281" t="n"/>
-      <c r="Z5" s="281" t="n"/>
-      <c r="AA5" s="281" t="n"/>
-      <c r="AB5" s="281" t="n"/>
-      <c r="AC5" s="281" t="n"/>
-      <c r="AD5" s="281" t="n"/>
-      <c r="AE5" s="281" t="n"/>
-      <c r="AF5" s="281" t="n"/>
-      <c r="AG5" s="281" t="n"/>
-      <c r="AH5" s="281" t="n"/>
-      <c r="AI5" s="281" t="n"/>
-      <c r="AJ5" s="281" t="n"/>
-      <c r="AK5" s="281" t="n"/>
-      <c r="AL5" s="281" t="n"/>
-      <c r="AM5" s="281" t="n"/>
-      <c r="AN5" s="281" t="n"/>
-      <c r="AO5" s="281" t="n"/>
-      <c r="AP5" s="281" t="n"/>
-      <c r="AQ5" s="270" t="n"/>
-      <c r="AR5" s="271" t="n"/>
-      <c r="AS5" s="271" t="n"/>
-      <c r="AT5" s="271" t="n"/>
-      <c r="AU5" s="271" t="n"/>
-      <c r="AV5" s="272" t="n"/>
-      <c r="AW5" s="273" t="inlineStr">
+      <c r="M5" s="427" t="n"/>
+      <c r="N5" s="427" t="n"/>
+      <c r="O5" s="427" t="n"/>
+      <c r="P5" s="427" t="n"/>
+      <c r="Q5" s="427" t="n"/>
+      <c r="R5" s="427" t="n"/>
+      <c r="S5" s="427" t="n"/>
+      <c r="T5" s="427" t="n"/>
+      <c r="U5" s="427" t="n"/>
+      <c r="V5" s="427" t="n"/>
+      <c r="W5" s="427" t="n"/>
+      <c r="X5" s="427" t="n"/>
+      <c r="Y5" s="427" t="n"/>
+      <c r="Z5" s="427" t="n"/>
+      <c r="AA5" s="427" t="n"/>
+      <c r="AB5" s="427" t="n"/>
+      <c r="AC5" s="427" t="n"/>
+      <c r="AD5" s="427" t="n"/>
+      <c r="AE5" s="427" t="n"/>
+      <c r="AF5" s="427" t="n"/>
+      <c r="AG5" s="427" t="n"/>
+      <c r="AH5" s="427" t="n"/>
+      <c r="AI5" s="427" t="n"/>
+      <c r="AJ5" s="427" t="n"/>
+      <c r="AK5" s="427" t="n"/>
+      <c r="AL5" s="427" t="n"/>
+      <c r="AM5" s="427" t="n"/>
+      <c r="AN5" s="427" t="n"/>
+      <c r="AO5" s="427" t="n"/>
+      <c r="AP5" s="427" t="n"/>
+      <c r="AQ5" s="343" t="n"/>
+      <c r="AR5" s="423" t="n"/>
+      <c r="AS5" s="423" t="n"/>
+      <c r="AT5" s="423" t="n"/>
+      <c r="AU5" s="423" t="n"/>
+      <c r="AV5" s="424" t="n"/>
+      <c r="AW5" s="346" t="inlineStr">
         <is>
           <t>General Manager</t>
         </is>
       </c>
-      <c r="AX5" s="271" t="n"/>
-      <c r="AY5" s="271" t="n"/>
-      <c r="AZ5" s="271" t="n"/>
-      <c r="BA5" s="271" t="n"/>
-      <c r="BB5" s="271" t="n"/>
-      <c r="BC5" s="271" t="n"/>
-      <c r="BD5" s="274" t="n"/>
+      <c r="AX5" s="423" t="n"/>
+      <c r="AY5" s="423" t="n"/>
+      <c r="AZ5" s="423" t="n"/>
+      <c r="BA5" s="423" t="n"/>
+      <c r="BB5" s="423" t="n"/>
+      <c r="BC5" s="423" t="n"/>
+      <c r="BD5" s="424" t="n"/>
     </row>
     <row r="6" ht="4" customHeight="1">
-      <c r="A6" s="25" t="n"/>
+      <c r="A6" s="353" t="n"/>
+      <c r="B6" s="421" t="n"/>
+      <c r="C6" s="421" t="n"/>
+      <c r="D6" s="421" t="n"/>
+      <c r="E6" s="421" t="n"/>
+      <c r="F6" s="421" t="n"/>
+      <c r="G6" s="421" t="n"/>
+      <c r="H6" s="421" t="n"/>
+      <c r="I6" s="421" t="n"/>
+      <c r="J6" s="421" t="n"/>
+      <c r="K6" s="421" t="n"/>
+      <c r="L6" s="421" t="n"/>
+      <c r="M6" s="421" t="n"/>
+      <c r="N6" s="421" t="n"/>
+      <c r="O6" s="421" t="n"/>
+      <c r="P6" s="421" t="n"/>
+      <c r="Q6" s="421" t="n"/>
+      <c r="R6" s="421" t="n"/>
+      <c r="S6" s="421" t="n"/>
+      <c r="T6" s="421" t="n"/>
+      <c r="U6" s="421" t="n"/>
+      <c r="V6" s="421" t="n"/>
+      <c r="W6" s="421" t="n"/>
+      <c r="X6" s="421" t="n"/>
+      <c r="Y6" s="421" t="n"/>
+      <c r="Z6" s="421" t="n"/>
+      <c r="AA6" s="421" t="n"/>
+      <c r="AB6" s="421" t="n"/>
+      <c r="AC6" s="421" t="n"/>
+      <c r="AD6" s="421" t="n"/>
+      <c r="AE6" s="421" t="n"/>
+      <c r="AF6" s="421" t="n"/>
+      <c r="AG6" s="421" t="n"/>
+      <c r="AH6" s="421" t="n"/>
+      <c r="AI6" s="421" t="n"/>
+      <c r="AJ6" s="421" t="n"/>
+      <c r="AK6" s="421" t="n"/>
+      <c r="AL6" s="421" t="n"/>
+      <c r="AM6" s="421" t="n"/>
+      <c r="AN6" s="421" t="n"/>
+      <c r="AO6" s="421" t="n"/>
+      <c r="AP6" s="421" t="n"/>
+      <c r="AQ6" s="421" t="n"/>
+      <c r="AR6" s="421" t="n"/>
+      <c r="AS6" s="421" t="n"/>
+      <c r="AT6" s="421" t="n"/>
+      <c r="AU6" s="421" t="n"/>
+      <c r="AV6" s="421" t="n"/>
+      <c r="AW6" s="421" t="n"/>
+      <c r="AX6" s="421" t="n"/>
+      <c r="AY6" s="421" t="n"/>
+      <c r="AZ6" s="421" t="n"/>
+      <c r="BA6" s="421" t="n"/>
+      <c r="BB6" s="421" t="n"/>
+      <c r="BC6" s="421" t="n"/>
+      <c r="BD6" s="421" t="n"/>
     </row>
     <row r="7" ht="17" customHeight="1">
-      <c r="A7" s="284" t="inlineStr">
+      <c r="A7" s="354" t="inlineStr">
         <is>
           <t xml:space="preserve">  1. REFERENCE INFORMATION</t>
         </is>
       </c>
-      <c r="B7" s="285" t="n"/>
-      <c r="C7" s="285" t="n"/>
-      <c r="D7" s="285" t="n"/>
-      <c r="E7" s="285" t="n"/>
-      <c r="F7" s="285" t="n"/>
-      <c r="G7" s="285" t="n"/>
-      <c r="H7" s="285" t="n"/>
-      <c r="I7" s="285" t="n"/>
-      <c r="J7" s="285" t="n"/>
-      <c r="K7" s="285" t="n"/>
-      <c r="L7" s="285" t="n"/>
-      <c r="M7" s="285" t="n"/>
-      <c r="N7" s="285" t="n"/>
-      <c r="O7" s="285" t="n"/>
-      <c r="P7" s="285" t="n"/>
-      <c r="Q7" s="285" t="n"/>
-      <c r="R7" s="285" t="n"/>
-      <c r="S7" s="285" t="n"/>
-      <c r="T7" s="285" t="n"/>
-      <c r="U7" s="285" t="n"/>
-      <c r="V7" s="285" t="n"/>
-      <c r="W7" s="285" t="n"/>
-      <c r="X7" s="285" t="n"/>
-      <c r="Y7" s="285" t="n"/>
-      <c r="Z7" s="285" t="n"/>
-      <c r="AA7" s="285" t="n"/>
-      <c r="AB7" s="285" t="n"/>
-      <c r="AC7" s="285" t="n"/>
-      <c r="AD7" s="285" t="n"/>
-      <c r="AE7" s="285" t="n"/>
-      <c r="AF7" s="285" t="n"/>
-      <c r="AG7" s="285" t="n"/>
-      <c r="AH7" s="285" t="n"/>
-      <c r="AI7" s="285" t="n"/>
-      <c r="AJ7" s="285" t="n"/>
-      <c r="AK7" s="285" t="n"/>
-      <c r="AL7" s="285" t="n"/>
-      <c r="AM7" s="285" t="n"/>
-      <c r="AN7" s="285" t="n"/>
-      <c r="AO7" s="285" t="n"/>
-      <c r="AP7" s="285" t="n"/>
-      <c r="AQ7" s="285" t="n"/>
-      <c r="AR7" s="285" t="n"/>
-      <c r="AS7" s="285" t="n"/>
-      <c r="AT7" s="285" t="n"/>
-      <c r="AU7" s="285" t="n"/>
-      <c r="AV7" s="285" t="n"/>
-      <c r="AW7" s="285" t="n"/>
-      <c r="AX7" s="285" t="n"/>
-      <c r="AY7" s="285" t="n"/>
-      <c r="AZ7" s="285" t="n"/>
-      <c r="BA7" s="285" t="n"/>
-      <c r="BB7" s="285" t="n"/>
-      <c r="BC7" s="285" t="n"/>
-      <c r="BD7" s="286" t="n"/>
+      <c r="B7" s="423" t="n"/>
+      <c r="C7" s="423" t="n"/>
+      <c r="D7" s="423" t="n"/>
+      <c r="E7" s="423" t="n"/>
+      <c r="F7" s="423" t="n"/>
+      <c r="G7" s="423" t="n"/>
+      <c r="H7" s="423" t="n"/>
+      <c r="I7" s="423" t="n"/>
+      <c r="J7" s="423" t="n"/>
+      <c r="K7" s="423" t="n"/>
+      <c r="L7" s="423" t="n"/>
+      <c r="M7" s="423" t="n"/>
+      <c r="N7" s="423" t="n"/>
+      <c r="O7" s="423" t="n"/>
+      <c r="P7" s="423" t="n"/>
+      <c r="Q7" s="423" t="n"/>
+      <c r="R7" s="423" t="n"/>
+      <c r="S7" s="423" t="n"/>
+      <c r="T7" s="423" t="n"/>
+      <c r="U7" s="423" t="n"/>
+      <c r="V7" s="423" t="n"/>
+      <c r="W7" s="423" t="n"/>
+      <c r="X7" s="423" t="n"/>
+      <c r="Y7" s="423" t="n"/>
+      <c r="Z7" s="423" t="n"/>
+      <c r="AA7" s="423" t="n"/>
+      <c r="AB7" s="423" t="n"/>
+      <c r="AC7" s="423" t="n"/>
+      <c r="AD7" s="423" t="n"/>
+      <c r="AE7" s="423" t="n"/>
+      <c r="AF7" s="423" t="n"/>
+      <c r="AG7" s="423" t="n"/>
+      <c r="AH7" s="423" t="n"/>
+      <c r="AI7" s="423" t="n"/>
+      <c r="AJ7" s="423" t="n"/>
+      <c r="AK7" s="423" t="n"/>
+      <c r="AL7" s="423" t="n"/>
+      <c r="AM7" s="423" t="n"/>
+      <c r="AN7" s="423" t="n"/>
+      <c r="AO7" s="423" t="n"/>
+      <c r="AP7" s="423" t="n"/>
+      <c r="AQ7" s="423" t="n"/>
+      <c r="AR7" s="423" t="n"/>
+      <c r="AS7" s="423" t="n"/>
+      <c r="AT7" s="423" t="n"/>
+      <c r="AU7" s="423" t="n"/>
+      <c r="AV7" s="423" t="n"/>
+      <c r="AW7" s="423" t="n"/>
+      <c r="AX7" s="423" t="n"/>
+      <c r="AY7" s="423" t="n"/>
+      <c r="AZ7" s="423" t="n"/>
+      <c r="BA7" s="423" t="n"/>
+      <c r="BB7" s="423" t="n"/>
+      <c r="BC7" s="423" t="n"/>
+      <c r="BD7" s="424" t="n"/>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="287" t="inlineStr">
+      <c r="A8" s="355" t="inlineStr">
         <is>
           <t>Clean Build Record ID</t>
         </is>
       </c>
-      <c r="B8" s="271" t="n"/>
-      <c r="C8" s="271" t="n"/>
-      <c r="D8" s="271" t="n"/>
-      <c r="E8" s="271" t="n"/>
-      <c r="F8" s="271" t="n"/>
-      <c r="G8" s="271" t="n"/>
-      <c r="H8" s="271" t="n"/>
-      <c r="I8" s="271" t="n"/>
-      <c r="J8" s="272" t="n"/>
-      <c r="K8" s="288" t="n"/>
-      <c r="L8" s="320" t="n"/>
-      <c r="M8" s="320" t="n"/>
-      <c r="N8" s="320" t="n"/>
-      <c r="O8" s="320" t="n"/>
-      <c r="P8" s="320" t="n"/>
-      <c r="Q8" s="320" t="n"/>
-      <c r="R8" s="320" t="n"/>
-      <c r="S8" s="320" t="n"/>
-      <c r="T8" s="320" t="n"/>
-      <c r="U8" s="320" t="n"/>
-      <c r="V8" s="320" t="n"/>
-      <c r="W8" s="320" t="n"/>
-      <c r="X8" s="320" t="n"/>
-      <c r="Y8" s="320" t="n"/>
-      <c r="Z8" s="320" t="n"/>
-      <c r="AA8" s="320" t="n"/>
-      <c r="AB8" s="321" t="n"/>
-      <c r="AC8" s="289" t="inlineStr">
+      <c r="B8" s="406" t="n"/>
+      <c r="C8" s="406" t="n"/>
+      <c r="D8" s="406" t="n"/>
+      <c r="E8" s="406" t="n"/>
+      <c r="F8" s="406" t="n"/>
+      <c r="G8" s="406" t="n"/>
+      <c r="H8" s="406" t="n"/>
+      <c r="I8" s="406" t="n"/>
+      <c r="J8" s="407" t="n"/>
+      <c r="K8" s="358" t="n"/>
+      <c r="L8" s="408" t="n"/>
+      <c r="M8" s="408" t="n"/>
+      <c r="N8" s="408" t="n"/>
+      <c r="O8" s="408" t="n"/>
+      <c r="P8" s="408" t="n"/>
+      <c r="Q8" s="408" t="n"/>
+      <c r="R8" s="408" t="n"/>
+      <c r="S8" s="408" t="n"/>
+      <c r="T8" s="408" t="n"/>
+      <c r="U8" s="408" t="n"/>
+      <c r="V8" s="408" t="n"/>
+      <c r="W8" s="408" t="n"/>
+      <c r="X8" s="408" t="n"/>
+      <c r="Y8" s="408" t="n"/>
+      <c r="Z8" s="408" t="n"/>
+      <c r="AA8" s="408" t="n"/>
+      <c r="AB8" s="409" t="n"/>
+      <c r="AC8" s="361" t="inlineStr">
         <is>
           <t>Release Status</t>
         </is>
       </c>
-      <c r="AD8" s="271" t="n"/>
-      <c r="AE8" s="271" t="n"/>
-      <c r="AF8" s="271" t="n"/>
-      <c r="AG8" s="271" t="n"/>
-      <c r="AH8" s="271" t="n"/>
-      <c r="AI8" s="271" t="n"/>
-      <c r="AJ8" s="271" t="n"/>
-      <c r="AK8" s="271" t="n"/>
-      <c r="AL8" s="272" t="n"/>
-      <c r="AM8" s="290" t="n"/>
-      <c r="AN8" s="320" t="n"/>
-      <c r="AO8" s="320" t="n"/>
-      <c r="AP8" s="320" t="n"/>
-      <c r="AQ8" s="320" t="n"/>
-      <c r="AR8" s="320" t="n"/>
-      <c r="AS8" s="320" t="n"/>
-      <c r="AT8" s="320" t="n"/>
-      <c r="AU8" s="320" t="n"/>
-      <c r="AV8" s="320" t="n"/>
-      <c r="AW8" s="320" t="n"/>
-      <c r="AX8" s="320" t="n"/>
-      <c r="AY8" s="320" t="n"/>
-      <c r="AZ8" s="320" t="n"/>
-      <c r="BA8" s="320" t="n"/>
-      <c r="BB8" s="320" t="n"/>
-      <c r="BC8" s="320" t="n"/>
-      <c r="BD8" s="322" t="n"/>
+      <c r="AD8" s="406" t="n"/>
+      <c r="AE8" s="406" t="n"/>
+      <c r="AF8" s="406" t="n"/>
+      <c r="AG8" s="406" t="n"/>
+      <c r="AH8" s="406" t="n"/>
+      <c r="AI8" s="406" t="n"/>
+      <c r="AJ8" s="406" t="n"/>
+      <c r="AK8" s="406" t="n"/>
+      <c r="AL8" s="407" t="n"/>
+      <c r="AM8" s="358" t="n"/>
+      <c r="AN8" s="408" t="n"/>
+      <c r="AO8" s="408" t="n"/>
+      <c r="AP8" s="408" t="n"/>
+      <c r="AQ8" s="408" t="n"/>
+      <c r="AR8" s="408" t="n"/>
+      <c r="AS8" s="408" t="n"/>
+      <c r="AT8" s="408" t="n"/>
+      <c r="AU8" s="408" t="n"/>
+      <c r="AV8" s="408" t="n"/>
+      <c r="AW8" s="408" t="n"/>
+      <c r="AX8" s="408" t="n"/>
+      <c r="AY8" s="408" t="n"/>
+      <c r="AZ8" s="408" t="n"/>
+      <c r="BA8" s="408" t="n"/>
+      <c r="BB8" s="408" t="n"/>
+      <c r="BC8" s="408" t="n"/>
+      <c r="BD8" s="409" t="n"/>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="287" t="inlineStr">
+      <c r="A9" s="355" t="inlineStr">
         <is>
           <t>Job / Part / Package Class</t>
         </is>
       </c>
-      <c r="B9" s="271" t="n"/>
-      <c r="C9" s="271" t="n"/>
-      <c r="D9" s="271" t="n"/>
-      <c r="E9" s="271" t="n"/>
-      <c r="F9" s="271" t="n"/>
-      <c r="G9" s="271" t="n"/>
-      <c r="H9" s="271" t="n"/>
-      <c r="I9" s="271" t="n"/>
-      <c r="J9" s="272" t="n"/>
-      <c r="K9" s="288" t="n"/>
-      <c r="L9" s="320" t="n"/>
-      <c r="M9" s="320" t="n"/>
-      <c r="N9" s="320" t="n"/>
-      <c r="O9" s="320" t="n"/>
-      <c r="P9" s="320" t="n"/>
-      <c r="Q9" s="320" t="n"/>
-      <c r="R9" s="320" t="n"/>
-      <c r="S9" s="320" t="n"/>
-      <c r="T9" s="320" t="n"/>
-      <c r="U9" s="320" t="n"/>
-      <c r="V9" s="320" t="n"/>
-      <c r="W9" s="320" t="n"/>
-      <c r="X9" s="320" t="n"/>
-      <c r="Y9" s="320" t="n"/>
-      <c r="Z9" s="320" t="n"/>
-      <c r="AA9" s="320" t="n"/>
-      <c r="AB9" s="321" t="n"/>
-      <c r="AC9" s="289" t="inlineStr">
+      <c r="B9" s="406" t="n"/>
+      <c r="C9" s="406" t="n"/>
+      <c r="D9" s="406" t="n"/>
+      <c r="E9" s="406" t="n"/>
+      <c r="F9" s="406" t="n"/>
+      <c r="G9" s="406" t="n"/>
+      <c r="H9" s="406" t="n"/>
+      <c r="I9" s="406" t="n"/>
+      <c r="J9" s="407" t="n"/>
+      <c r="K9" s="358" t="n"/>
+      <c r="L9" s="408" t="n"/>
+      <c r="M9" s="408" t="n"/>
+      <c r="N9" s="408" t="n"/>
+      <c r="O9" s="408" t="n"/>
+      <c r="P9" s="408" t="n"/>
+      <c r="Q9" s="408" t="n"/>
+      <c r="R9" s="408" t="n"/>
+      <c r="S9" s="408" t="n"/>
+      <c r="T9" s="408" t="n"/>
+      <c r="U9" s="408" t="n"/>
+      <c r="V9" s="408" t="n"/>
+      <c r="W9" s="408" t="n"/>
+      <c r="X9" s="408" t="n"/>
+      <c r="Y9" s="408" t="n"/>
+      <c r="Z9" s="408" t="n"/>
+      <c r="AA9" s="408" t="n"/>
+      <c r="AB9" s="409" t="n"/>
+      <c r="AC9" s="361" t="inlineStr">
         <is>
           <t>Clean Class</t>
         </is>
       </c>
-      <c r="AD9" s="271" t="n"/>
-      <c r="AE9" s="271" t="n"/>
-      <c r="AF9" s="271" t="n"/>
-      <c r="AG9" s="271" t="n"/>
-      <c r="AH9" s="271" t="n"/>
-      <c r="AI9" s="271" t="n"/>
-      <c r="AJ9" s="271" t="n"/>
-      <c r="AK9" s="271" t="n"/>
-      <c r="AL9" s="272" t="n"/>
-      <c r="AM9" s="290" t="n"/>
-      <c r="AN9" s="320" t="n"/>
-      <c r="AO9" s="320" t="n"/>
-      <c r="AP9" s="320" t="n"/>
-      <c r="AQ9" s="320" t="n"/>
-      <c r="AR9" s="320" t="n"/>
-      <c r="AS9" s="320" t="n"/>
-      <c r="AT9" s="320" t="n"/>
-      <c r="AU9" s="320" t="n"/>
-      <c r="AV9" s="320" t="n"/>
-      <c r="AW9" s="320" t="n"/>
-      <c r="AX9" s="320" t="n"/>
-      <c r="AY9" s="320" t="n"/>
-      <c r="AZ9" s="320" t="n"/>
-      <c r="BA9" s="320" t="n"/>
-      <c r="BB9" s="320" t="n"/>
-      <c r="BC9" s="320" t="n"/>
-      <c r="BD9" s="322" t="n"/>
+      <c r="AD9" s="406" t="n"/>
+      <c r="AE9" s="406" t="n"/>
+      <c r="AF9" s="406" t="n"/>
+      <c r="AG9" s="406" t="n"/>
+      <c r="AH9" s="406" t="n"/>
+      <c r="AI9" s="406" t="n"/>
+      <c r="AJ9" s="406" t="n"/>
+      <c r="AK9" s="406" t="n"/>
+      <c r="AL9" s="407" t="n"/>
+      <c r="AM9" s="358" t="n"/>
+      <c r="AN9" s="408" t="n"/>
+      <c r="AO9" s="408" t="n"/>
+      <c r="AP9" s="408" t="n"/>
+      <c r="AQ9" s="408" t="n"/>
+      <c r="AR9" s="408" t="n"/>
+      <c r="AS9" s="408" t="n"/>
+      <c r="AT9" s="408" t="n"/>
+      <c r="AU9" s="408" t="n"/>
+      <c r="AV9" s="408" t="n"/>
+      <c r="AW9" s="408" t="n"/>
+      <c r="AX9" s="408" t="n"/>
+      <c r="AY9" s="408" t="n"/>
+      <c r="AZ9" s="408" t="n"/>
+      <c r="BA9" s="408" t="n"/>
+      <c r="BB9" s="408" t="n"/>
+      <c r="BC9" s="408" t="n"/>
+      <c r="BD9" s="409" t="n"/>
     </row>
     <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="287" t="inlineStr">
+      <c r="A10" s="355" t="inlineStr">
         <is>
           <t>Bagging Configuration</t>
         </is>
       </c>
-      <c r="B10" s="271" t="n"/>
-      <c r="C10" s="271" t="n"/>
-      <c r="D10" s="271" t="n"/>
-      <c r="E10" s="271" t="n"/>
-      <c r="F10" s="271" t="n"/>
-      <c r="G10" s="271" t="n"/>
-      <c r="H10" s="271" t="n"/>
-      <c r="I10" s="271" t="n"/>
-      <c r="J10" s="272" t="n"/>
-      <c r="K10" s="288" t="n"/>
-      <c r="L10" s="320" t="n"/>
-      <c r="M10" s="320" t="n"/>
-      <c r="N10" s="320" t="n"/>
-      <c r="O10" s="320" t="n"/>
-      <c r="P10" s="320" t="n"/>
-      <c r="Q10" s="320" t="n"/>
-      <c r="R10" s="320" t="n"/>
-      <c r="S10" s="320" t="n"/>
-      <c r="T10" s="320" t="n"/>
-      <c r="U10" s="320" t="n"/>
-      <c r="V10" s="320" t="n"/>
-      <c r="W10" s="320" t="n"/>
-      <c r="X10" s="320" t="n"/>
-      <c r="Y10" s="320" t="n"/>
-      <c r="Z10" s="320" t="n"/>
-      <c r="AA10" s="320" t="n"/>
-      <c r="AB10" s="321" t="n"/>
-      <c r="AC10" s="289" t="inlineStr">
+      <c r="B10" s="406" t="n"/>
+      <c r="C10" s="406" t="n"/>
+      <c r="D10" s="406" t="n"/>
+      <c r="E10" s="406" t="n"/>
+      <c r="F10" s="406" t="n"/>
+      <c r="G10" s="406" t="n"/>
+      <c r="H10" s="406" t="n"/>
+      <c r="I10" s="406" t="n"/>
+      <c r="J10" s="407" t="n"/>
+      <c r="K10" s="358" t="n"/>
+      <c r="L10" s="408" t="n"/>
+      <c r="M10" s="408" t="n"/>
+      <c r="N10" s="408" t="n"/>
+      <c r="O10" s="408" t="n"/>
+      <c r="P10" s="408" t="n"/>
+      <c r="Q10" s="408" t="n"/>
+      <c r="R10" s="408" t="n"/>
+      <c r="S10" s="408" t="n"/>
+      <c r="T10" s="408" t="n"/>
+      <c r="U10" s="408" t="n"/>
+      <c r="V10" s="408" t="n"/>
+      <c r="W10" s="408" t="n"/>
+      <c r="X10" s="408" t="n"/>
+      <c r="Y10" s="408" t="n"/>
+      <c r="Z10" s="408" t="n"/>
+      <c r="AA10" s="408" t="n"/>
+      <c r="AB10" s="409" t="n"/>
+      <c r="AC10" s="361" t="inlineStr">
         <is>
           <t>Line Clearance / Gowning</t>
         </is>
       </c>
-      <c r="AD10" s="271" t="n"/>
-      <c r="AE10" s="271" t="n"/>
-      <c r="AF10" s="271" t="n"/>
-      <c r="AG10" s="271" t="n"/>
-      <c r="AH10" s="271" t="n"/>
-      <c r="AI10" s="271" t="n"/>
-      <c r="AJ10" s="271" t="n"/>
-      <c r="AK10" s="271" t="n"/>
-      <c r="AL10" s="272" t="n"/>
-      <c r="AM10" s="290" t="n"/>
-      <c r="AN10" s="320" t="n"/>
-      <c r="AO10" s="320" t="n"/>
-      <c r="AP10" s="320" t="n"/>
-      <c r="AQ10" s="320" t="n"/>
-      <c r="AR10" s="320" t="n"/>
-      <c r="AS10" s="320" t="n"/>
-      <c r="AT10" s="320" t="n"/>
-      <c r="AU10" s="320" t="n"/>
-      <c r="AV10" s="320" t="n"/>
-      <c r="AW10" s="320" t="n"/>
-      <c r="AX10" s="320" t="n"/>
-      <c r="AY10" s="320" t="n"/>
-      <c r="AZ10" s="320" t="n"/>
-      <c r="BA10" s="320" t="n"/>
-      <c r="BB10" s="320" t="n"/>
-      <c r="BC10" s="320" t="n"/>
-      <c r="BD10" s="322" t="n"/>
+      <c r="AD10" s="406" t="n"/>
+      <c r="AE10" s="406" t="n"/>
+      <c r="AF10" s="406" t="n"/>
+      <c r="AG10" s="406" t="n"/>
+      <c r="AH10" s="406" t="n"/>
+      <c r="AI10" s="406" t="n"/>
+      <c r="AJ10" s="406" t="n"/>
+      <c r="AK10" s="406" t="n"/>
+      <c r="AL10" s="407" t="n"/>
+      <c r="AM10" s="358" t="n"/>
+      <c r="AN10" s="408" t="n"/>
+      <c r="AO10" s="408" t="n"/>
+      <c r="AP10" s="408" t="n"/>
+      <c r="AQ10" s="408" t="n"/>
+      <c r="AR10" s="408" t="n"/>
+      <c r="AS10" s="408" t="n"/>
+      <c r="AT10" s="408" t="n"/>
+      <c r="AU10" s="408" t="n"/>
+      <c r="AV10" s="408" t="n"/>
+      <c r="AW10" s="408" t="n"/>
+      <c r="AX10" s="408" t="n"/>
+      <c r="AY10" s="408" t="n"/>
+      <c r="AZ10" s="408" t="n"/>
+      <c r="BA10" s="408" t="n"/>
+      <c r="BB10" s="408" t="n"/>
+      <c r="BC10" s="408" t="n"/>
+      <c r="BD10" s="409" t="n"/>
     </row>
     <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="287" t="inlineStr">
+      <c r="A11" s="355" t="inlineStr">
         <is>
           <t>Prepared by / Date-Time</t>
         </is>
       </c>
-      <c r="B11" s="271" t="n"/>
-      <c r="C11" s="271" t="n"/>
-      <c r="D11" s="271" t="n"/>
-      <c r="E11" s="271" t="n"/>
-      <c r="F11" s="271" t="n"/>
-      <c r="G11" s="271" t="n"/>
-      <c r="H11" s="271" t="n"/>
-      <c r="I11" s="271" t="n"/>
-      <c r="J11" s="272" t="n"/>
-      <c r="K11" s="288" t="n"/>
-      <c r="L11" s="320" t="n"/>
-      <c r="M11" s="320" t="n"/>
-      <c r="N11" s="320" t="n"/>
-      <c r="O11" s="320" t="n"/>
-      <c r="P11" s="320" t="n"/>
-      <c r="Q11" s="320" t="n"/>
-      <c r="R11" s="320" t="n"/>
-      <c r="S11" s="320" t="n"/>
-      <c r="T11" s="320" t="n"/>
-      <c r="U11" s="320" t="n"/>
-      <c r="V11" s="320" t="n"/>
-      <c r="W11" s="320" t="n"/>
-      <c r="X11" s="320" t="n"/>
-      <c r="Y11" s="320" t="n"/>
-      <c r="Z11" s="320" t="n"/>
-      <c r="AA11" s="320" t="n"/>
-      <c r="AB11" s="321" t="n"/>
-      <c r="AC11" s="289" t="inlineStr">
+      <c r="B11" s="401" t="n"/>
+      <c r="C11" s="401" t="n"/>
+      <c r="D11" s="401" t="n"/>
+      <c r="E11" s="401" t="n"/>
+      <c r="F11" s="401" t="n"/>
+      <c r="G11" s="401" t="n"/>
+      <c r="H11" s="401" t="n"/>
+      <c r="I11" s="401" t="n"/>
+      <c r="J11" s="402" t="n"/>
+      <c r="K11" s="358" t="n"/>
+      <c r="L11" s="410" t="n"/>
+      <c r="M11" s="410" t="n"/>
+      <c r="N11" s="410" t="n"/>
+      <c r="O11" s="410" t="n"/>
+      <c r="P11" s="410" t="n"/>
+      <c r="Q11" s="410" t="n"/>
+      <c r="R11" s="410" t="n"/>
+      <c r="S11" s="410" t="n"/>
+      <c r="T11" s="410" t="n"/>
+      <c r="U11" s="410" t="n"/>
+      <c r="V11" s="410" t="n"/>
+      <c r="W11" s="410" t="n"/>
+      <c r="X11" s="410" t="n"/>
+      <c r="Y11" s="410" t="n"/>
+      <c r="Z11" s="410" t="n"/>
+      <c r="AA11" s="410" t="n"/>
+      <c r="AB11" s="411" t="n"/>
+      <c r="AC11" s="361" t="inlineStr">
         <is>
           <t>Warehouse Owner</t>
         </is>
       </c>
-      <c r="AD11" s="271" t="n"/>
-      <c r="AE11" s="271" t="n"/>
-      <c r="AF11" s="271" t="n"/>
-      <c r="AG11" s="271" t="n"/>
-      <c r="AH11" s="271" t="n"/>
-      <c r="AI11" s="271" t="n"/>
-      <c r="AJ11" s="271" t="n"/>
-      <c r="AK11" s="271" t="n"/>
-      <c r="AL11" s="272" t="n"/>
-      <c r="AM11" s="290" t="n"/>
-      <c r="AN11" s="320" t="n"/>
-      <c r="AO11" s="320" t="n"/>
-      <c r="AP11" s="320" t="n"/>
-      <c r="AQ11" s="320" t="n"/>
-      <c r="AR11" s="320" t="n"/>
-      <c r="AS11" s="320" t="n"/>
-      <c r="AT11" s="320" t="n"/>
-      <c r="AU11" s="320" t="n"/>
-      <c r="AV11" s="320" t="n"/>
-      <c r="AW11" s="320" t="n"/>
-      <c r="AX11" s="320" t="n"/>
-      <c r="AY11" s="320" t="n"/>
-      <c r="AZ11" s="320" t="n"/>
-      <c r="BA11" s="320" t="n"/>
-      <c r="BB11" s="320" t="n"/>
-      <c r="BC11" s="320" t="n"/>
-      <c r="BD11" s="322" t="n"/>
+      <c r="AD11" s="401" t="n"/>
+      <c r="AE11" s="401" t="n"/>
+      <c r="AF11" s="401" t="n"/>
+      <c r="AG11" s="401" t="n"/>
+      <c r="AH11" s="401" t="n"/>
+      <c r="AI11" s="401" t="n"/>
+      <c r="AJ11" s="401" t="n"/>
+      <c r="AK11" s="401" t="n"/>
+      <c r="AL11" s="402" t="n"/>
+      <c r="AM11" s="358" t="n"/>
+      <c r="AN11" s="410" t="n"/>
+      <c r="AO11" s="410" t="n"/>
+      <c r="AP11" s="410" t="n"/>
+      <c r="AQ11" s="410" t="n"/>
+      <c r="AR11" s="410" t="n"/>
+      <c r="AS11" s="410" t="n"/>
+      <c r="AT11" s="410" t="n"/>
+      <c r="AU11" s="410" t="n"/>
+      <c r="AV11" s="410" t="n"/>
+      <c r="AW11" s="410" t="n"/>
+      <c r="AX11" s="410" t="n"/>
+      <c r="AY11" s="410" t="n"/>
+      <c r="AZ11" s="410" t="n"/>
+      <c r="BA11" s="410" t="n"/>
+      <c r="BB11" s="410" t="n"/>
+      <c r="BC11" s="410" t="n"/>
+      <c r="BD11" s="411" t="n"/>
     </row>
     <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="287" t="inlineStr">
+      <c r="A12" s="355" t="inlineStr">
         <is>
           <t>Evidence Package Ref</t>
         </is>
       </c>
-      <c r="B12" s="271" t="n"/>
-      <c r="C12" s="271" t="n"/>
-      <c r="D12" s="271" t="n"/>
-      <c r="E12" s="271" t="n"/>
-      <c r="F12" s="271" t="n"/>
-      <c r="G12" s="271" t="n"/>
-      <c r="H12" s="271" t="n"/>
-      <c r="I12" s="271" t="n"/>
-      <c r="J12" s="272" t="n"/>
-      <c r="K12" s="288" t="n"/>
-      <c r="L12" s="320" t="n"/>
-      <c r="M12" s="320" t="n"/>
-      <c r="N12" s="320" t="n"/>
-      <c r="O12" s="320" t="n"/>
-      <c r="P12" s="320" t="n"/>
-      <c r="Q12" s="320" t="n"/>
-      <c r="R12" s="320" t="n"/>
-      <c r="S12" s="320" t="n"/>
-      <c r="T12" s="320" t="n"/>
-      <c r="U12" s="320" t="n"/>
-      <c r="V12" s="320" t="n"/>
-      <c r="W12" s="320" t="n"/>
-      <c r="X12" s="320" t="n"/>
-      <c r="Y12" s="320" t="n"/>
-      <c r="Z12" s="320" t="n"/>
-      <c r="AA12" s="320" t="n"/>
-      <c r="AB12" s="321" t="n"/>
-      <c r="AC12" s="289" t="inlineStr">
+      <c r="B12" s="406" t="n"/>
+      <c r="C12" s="406" t="n"/>
+      <c r="D12" s="406" t="n"/>
+      <c r="E12" s="406" t="n"/>
+      <c r="F12" s="406" t="n"/>
+      <c r="G12" s="406" t="n"/>
+      <c r="H12" s="406" t="n"/>
+      <c r="I12" s="406" t="n"/>
+      <c r="J12" s="407" t="n"/>
+      <c r="K12" s="358" t="n"/>
+      <c r="L12" s="408" t="n"/>
+      <c r="M12" s="408" t="n"/>
+      <c r="N12" s="408" t="n"/>
+      <c r="O12" s="408" t="n"/>
+      <c r="P12" s="408" t="n"/>
+      <c r="Q12" s="408" t="n"/>
+      <c r="R12" s="408" t="n"/>
+      <c r="S12" s="408" t="n"/>
+      <c r="T12" s="408" t="n"/>
+      <c r="U12" s="408" t="n"/>
+      <c r="V12" s="408" t="n"/>
+      <c r="W12" s="408" t="n"/>
+      <c r="X12" s="408" t="n"/>
+      <c r="Y12" s="408" t="n"/>
+      <c r="Z12" s="408" t="n"/>
+      <c r="AA12" s="408" t="n"/>
+      <c r="AB12" s="409" t="n"/>
+      <c r="AC12" s="361" t="inlineStr">
         <is>
           <t>Record Status</t>
         </is>
       </c>
-      <c r="AD12" s="271" t="n"/>
-      <c r="AE12" s="271" t="n"/>
-      <c r="AF12" s="271" t="n"/>
-      <c r="AG12" s="271" t="n"/>
-      <c r="AH12" s="271" t="n"/>
-      <c r="AI12" s="271" t="n"/>
-      <c r="AJ12" s="271" t="n"/>
-      <c r="AK12" s="271" t="n"/>
-      <c r="AL12" s="272" t="n"/>
-      <c r="AM12" s="290" t="n"/>
-      <c r="AN12" s="320" t="n"/>
-      <c r="AO12" s="320" t="n"/>
-      <c r="AP12" s="320" t="n"/>
-      <c r="AQ12" s="320" t="n"/>
-      <c r="AR12" s="320" t="n"/>
-      <c r="AS12" s="320" t="n"/>
-      <c r="AT12" s="320" t="n"/>
-      <c r="AU12" s="320" t="n"/>
-      <c r="AV12" s="320" t="n"/>
-      <c r="AW12" s="320" t="n"/>
-      <c r="AX12" s="320" t="n"/>
-      <c r="AY12" s="320" t="n"/>
-      <c r="AZ12" s="320" t="n"/>
-      <c r="BA12" s="320" t="n"/>
-      <c r="BB12" s="320" t="n"/>
-      <c r="BC12" s="320" t="n"/>
-      <c r="BD12" s="322" t="n"/>
+      <c r="AD12" s="406" t="n"/>
+      <c r="AE12" s="406" t="n"/>
+      <c r="AF12" s="406" t="n"/>
+      <c r="AG12" s="406" t="n"/>
+      <c r="AH12" s="406" t="n"/>
+      <c r="AI12" s="406" t="n"/>
+      <c r="AJ12" s="406" t="n"/>
+      <c r="AK12" s="406" t="n"/>
+      <c r="AL12" s="407" t="n"/>
+      <c r="AM12" s="358" t="n"/>
+      <c r="AN12" s="408" t="n"/>
+      <c r="AO12" s="408" t="n"/>
+      <c r="AP12" s="408" t="n"/>
+      <c r="AQ12" s="408" t="n"/>
+      <c r="AR12" s="408" t="n"/>
+      <c r="AS12" s="408" t="n"/>
+      <c r="AT12" s="408" t="n"/>
+      <c r="AU12" s="408" t="n"/>
+      <c r="AV12" s="408" t="n"/>
+      <c r="AW12" s="408" t="n"/>
+      <c r="AX12" s="408" t="n"/>
+      <c r="AY12" s="408" t="n"/>
+      <c r="AZ12" s="408" t="n"/>
+      <c r="BA12" s="408" t="n"/>
+      <c r="BB12" s="408" t="n"/>
+      <c r="BC12" s="408" t="n"/>
+      <c r="BD12" s="409" t="n"/>
     </row>
     <row r="13" ht="4" customHeight="1">
-      <c r="A13" s="25" t="n"/>
+      <c r="A13" s="353" t="n"/>
+      <c r="B13" s="353" t="n"/>
+      <c r="C13" s="353" t="n"/>
+      <c r="D13" s="353" t="n"/>
+      <c r="E13" s="353" t="n"/>
+      <c r="F13" s="353" t="n"/>
+      <c r="G13" s="353" t="n"/>
+      <c r="H13" s="353" t="n"/>
+      <c r="I13" s="353" t="n"/>
+      <c r="J13" s="353" t="n"/>
+      <c r="K13" s="353" t="n"/>
+      <c r="L13" s="353" t="n"/>
+      <c r="M13" s="353" t="n"/>
+      <c r="N13" s="353" t="n"/>
+      <c r="O13" s="353" t="n"/>
+      <c r="P13" s="353" t="n"/>
+      <c r="Q13" s="353" t="n"/>
+      <c r="R13" s="353" t="n"/>
+      <c r="S13" s="353" t="n"/>
+      <c r="T13" s="353" t="n"/>
+      <c r="U13" s="353" t="n"/>
+      <c r="V13" s="353" t="n"/>
+      <c r="W13" s="353" t="n"/>
+      <c r="X13" s="353" t="n"/>
+      <c r="Y13" s="353" t="n"/>
+      <c r="Z13" s="353" t="n"/>
+      <c r="AA13" s="353" t="n"/>
+      <c r="AB13" s="353" t="n"/>
+      <c r="AC13" s="353" t="n"/>
+      <c r="AD13" s="353" t="n"/>
+      <c r="AE13" s="353" t="n"/>
+      <c r="AF13" s="353" t="n"/>
+      <c r="AG13" s="353" t="n"/>
+      <c r="AH13" s="353" t="n"/>
+      <c r="AI13" s="353" t="n"/>
+      <c r="AJ13" s="353" t="n"/>
+      <c r="AK13" s="353" t="n"/>
+      <c r="AL13" s="353" t="n"/>
+      <c r="AM13" s="353" t="n"/>
+      <c r="AN13" s="353" t="n"/>
+      <c r="AO13" s="353" t="n"/>
+      <c r="AP13" s="353" t="n"/>
+      <c r="AQ13" s="353" t="n"/>
+      <c r="AR13" s="353" t="n"/>
+      <c r="AS13" s="353" t="n"/>
+      <c r="AT13" s="353" t="n"/>
+      <c r="AU13" s="353" t="n"/>
+      <c r="AV13" s="353" t="n"/>
+      <c r="AW13" s="353" t="n"/>
+      <c r="AX13" s="353" t="n"/>
+      <c r="AY13" s="353" t="n"/>
+      <c r="AZ13" s="353" t="n"/>
+      <c r="BA13" s="353" t="n"/>
+      <c r="BB13" s="353" t="n"/>
+      <c r="BC13" s="353" t="n"/>
+      <c r="BD13" s="353" t="n"/>
     </row>
-    <row r="14" ht="17" customHeight="1">
-      <c r="A14" s="284" t="inlineStr">
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="354" t="inlineStr">
         <is>
           <t xml:space="preserve">  2. CLEAN BUILD / BAGGING VERIFICATION</t>
         </is>
       </c>
-      <c r="B14" s="285" t="n"/>
-      <c r="C14" s="285" t="n"/>
-      <c r="D14" s="285" t="n"/>
-      <c r="E14" s="285" t="n"/>
-      <c r="F14" s="285" t="n"/>
-      <c r="G14" s="285" t="n"/>
-      <c r="H14" s="285" t="n"/>
-      <c r="I14" s="285" t="n"/>
-      <c r="J14" s="285" t="n"/>
-      <c r="K14" s="285" t="n"/>
-      <c r="L14" s="285" t="n"/>
-      <c r="M14" s="285" t="n"/>
-      <c r="N14" s="285" t="n"/>
-      <c r="O14" s="285" t="n"/>
-      <c r="P14" s="285" t="n"/>
-      <c r="Q14" s="285" t="n"/>
-      <c r="R14" s="285" t="n"/>
-      <c r="S14" s="285" t="n"/>
-      <c r="T14" s="285" t="n"/>
-      <c r="U14" s="285" t="n"/>
-      <c r="V14" s="285" t="n"/>
-      <c r="W14" s="285" t="n"/>
-      <c r="X14" s="285" t="n"/>
-      <c r="Y14" s="285" t="n"/>
-      <c r="Z14" s="285" t="n"/>
-      <c r="AA14" s="285" t="n"/>
-      <c r="AB14" s="285" t="n"/>
-      <c r="AC14" s="285" t="n"/>
-      <c r="AD14" s="285" t="n"/>
-      <c r="AE14" s="285" t="n"/>
-      <c r="AF14" s="285" t="n"/>
-      <c r="AG14" s="285" t="n"/>
-      <c r="AH14" s="285" t="n"/>
-      <c r="AI14" s="285" t="n"/>
-      <c r="AJ14" s="285" t="n"/>
-      <c r="AK14" s="285" t="n"/>
-      <c r="AL14" s="285" t="n"/>
-      <c r="AM14" s="285" t="n"/>
-      <c r="AN14" s="285" t="n"/>
-      <c r="AO14" s="285" t="n"/>
-      <c r="AP14" s="285" t="n"/>
-      <c r="AQ14" s="285" t="n"/>
-      <c r="AR14" s="285" t="n"/>
-      <c r="AS14" s="285" t="n"/>
-      <c r="AT14" s="285" t="n"/>
-      <c r="AU14" s="285" t="n"/>
-      <c r="AV14" s="285" t="n"/>
-      <c r="AW14" s="285" t="n"/>
-      <c r="AX14" s="285" t="n"/>
-      <c r="AY14" s="285" t="n"/>
-      <c r="AZ14" s="285" t="n"/>
-      <c r="BA14" s="285" t="n"/>
-      <c r="BB14" s="285" t="n"/>
-      <c r="BC14" s="285" t="n"/>
-      <c r="BD14" s="286" t="n"/>
+      <c r="B14" s="406" t="n"/>
+      <c r="C14" s="406" t="n"/>
+      <c r="D14" s="406" t="n"/>
+      <c r="E14" s="406" t="n"/>
+      <c r="F14" s="406" t="n"/>
+      <c r="G14" s="406" t="n"/>
+      <c r="H14" s="406" t="n"/>
+      <c r="I14" s="406" t="n"/>
+      <c r="J14" s="406" t="n"/>
+      <c r="K14" s="406" t="n"/>
+      <c r="L14" s="406" t="n"/>
+      <c r="M14" s="406" t="n"/>
+      <c r="N14" s="406" t="n"/>
+      <c r="O14" s="406" t="n"/>
+      <c r="P14" s="406" t="n"/>
+      <c r="Q14" s="406" t="n"/>
+      <c r="R14" s="406" t="n"/>
+      <c r="S14" s="406" t="n"/>
+      <c r="T14" s="406" t="n"/>
+      <c r="U14" s="406" t="n"/>
+      <c r="V14" s="406" t="n"/>
+      <c r="W14" s="406" t="n"/>
+      <c r="X14" s="406" t="n"/>
+      <c r="Y14" s="406" t="n"/>
+      <c r="Z14" s="406" t="n"/>
+      <c r="AA14" s="406" t="n"/>
+      <c r="AB14" s="406" t="n"/>
+      <c r="AC14" s="406" t="n"/>
+      <c r="AD14" s="406" t="n"/>
+      <c r="AE14" s="406" t="n"/>
+      <c r="AF14" s="406" t="n"/>
+      <c r="AG14" s="406" t="n"/>
+      <c r="AH14" s="406" t="n"/>
+      <c r="AI14" s="406" t="n"/>
+      <c r="AJ14" s="406" t="n"/>
+      <c r="AK14" s="406" t="n"/>
+      <c r="AL14" s="406" t="n"/>
+      <c r="AM14" s="406" t="n"/>
+      <c r="AN14" s="406" t="n"/>
+      <c r="AO14" s="406" t="n"/>
+      <c r="AP14" s="406" t="n"/>
+      <c r="AQ14" s="406" t="n"/>
+      <c r="AR14" s="406" t="n"/>
+      <c r="AS14" s="406" t="n"/>
+      <c r="AT14" s="406" t="n"/>
+      <c r="AU14" s="406" t="n"/>
+      <c r="AV14" s="406" t="n"/>
+      <c r="AW14" s="406" t="n"/>
+      <c r="AX14" s="406" t="n"/>
+      <c r="AY14" s="406" t="n"/>
+      <c r="AZ14" s="406" t="n"/>
+      <c r="BA14" s="406" t="n"/>
+      <c r="BB14" s="406" t="n"/>
+      <c r="BC14" s="406" t="n"/>
+      <c r="BD14" s="407" t="n"/>
     </row>
-    <row r="15" ht="17" customHeight="1">
-      <c r="A15" s="291" t="inlineStr">
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="364" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B15" s="271" t="n"/>
-      <c r="C15" s="272" t="n"/>
-      <c r="D15" s="292" t="inlineStr">
+      <c r="B15" s="406" t="n"/>
+      <c r="C15" s="407" t="n"/>
+      <c r="D15" s="365" t="inlineStr">
         <is>
           <t>Cat.</t>
         </is>
       </c>
-      <c r="E15" s="271" t="n"/>
-      <c r="F15" s="271" t="n"/>
-      <c r="G15" s="272" t="n"/>
-      <c r="H15" s="292" t="inlineStr">
+      <c r="E15" s="406" t="n"/>
+      <c r="F15" s="406" t="n"/>
+      <c r="G15" s="407" t="n"/>
+      <c r="H15" s="365" t="inlineStr">
         <is>
           <t>Clean Build / Bagging Requirement</t>
         </is>
       </c>
-      <c r="I15" s="271" t="n"/>
-      <c r="J15" s="271" t="n"/>
-      <c r="K15" s="271" t="n"/>
-      <c r="L15" s="271" t="n"/>
-      <c r="M15" s="271" t="n"/>
-      <c r="N15" s="271" t="n"/>
-      <c r="O15" s="271" t="n"/>
-      <c r="P15" s="271" t="n"/>
-      <c r="Q15" s="271" t="n"/>
-      <c r="R15" s="271" t="n"/>
-      <c r="S15" s="271" t="n"/>
-      <c r="T15" s="271" t="n"/>
-      <c r="U15" s="271" t="n"/>
-      <c r="V15" s="271" t="n"/>
-      <c r="W15" s="271" t="n"/>
-      <c r="X15" s="271" t="n"/>
-      <c r="Y15" s="271" t="n"/>
-      <c r="Z15" s="272" t="n"/>
-      <c r="AA15" s="292" t="inlineStr">
+      <c r="I15" s="406" t="n"/>
+      <c r="J15" s="406" t="n"/>
+      <c r="K15" s="406" t="n"/>
+      <c r="L15" s="406" t="n"/>
+      <c r="M15" s="406" t="n"/>
+      <c r="N15" s="406" t="n"/>
+      <c r="O15" s="406" t="n"/>
+      <c r="P15" s="406" t="n"/>
+      <c r="Q15" s="406" t="n"/>
+      <c r="R15" s="406" t="n"/>
+      <c r="S15" s="406" t="n"/>
+      <c r="T15" s="406" t="n"/>
+      <c r="U15" s="406" t="n"/>
+      <c r="V15" s="406" t="n"/>
+      <c r="W15" s="406" t="n"/>
+      <c r="X15" s="406" t="n"/>
+      <c r="Y15" s="406" t="n"/>
+      <c r="Z15" s="407" t="n"/>
+      <c r="AA15" s="365" t="inlineStr">
         <is>
           <t>Evidence / Method</t>
         </is>
       </c>
-      <c r="AB15" s="271" t="n"/>
-      <c r="AC15" s="271" t="n"/>
-      <c r="AD15" s="271" t="n"/>
-      <c r="AE15" s="271" t="n"/>
-      <c r="AF15" s="271" t="n"/>
-      <c r="AG15" s="271" t="n"/>
-      <c r="AH15" s="271" t="n"/>
-      <c r="AI15" s="271" t="n"/>
-      <c r="AJ15" s="271" t="n"/>
-      <c r="AK15" s="271" t="n"/>
-      <c r="AL15" s="271" t="n"/>
-      <c r="AM15" s="271" t="n"/>
-      <c r="AN15" s="271" t="n"/>
-      <c r="AO15" s="271" t="n"/>
-      <c r="AP15" s="271" t="n"/>
-      <c r="AQ15" s="272" t="n"/>
-      <c r="AR15" s="292" t="inlineStr">
+      <c r="AB15" s="406" t="n"/>
+      <c r="AC15" s="406" t="n"/>
+      <c r="AD15" s="406" t="n"/>
+      <c r="AE15" s="406" t="n"/>
+      <c r="AF15" s="406" t="n"/>
+      <c r="AG15" s="406" t="n"/>
+      <c r="AH15" s="406" t="n"/>
+      <c r="AI15" s="406" t="n"/>
+      <c r="AJ15" s="406" t="n"/>
+      <c r="AK15" s="406" t="n"/>
+      <c r="AL15" s="406" t="n"/>
+      <c r="AM15" s="406" t="n"/>
+      <c r="AN15" s="406" t="n"/>
+      <c r="AO15" s="406" t="n"/>
+      <c r="AP15" s="406" t="n"/>
+      <c r="AQ15" s="407" t="n"/>
+      <c r="AR15" s="365" t="inlineStr">
         <is>
           <t>Result</t>
         </is>
       </c>
-      <c r="AS15" s="271" t="n"/>
-      <c r="AT15" s="271" t="n"/>
-      <c r="AU15" s="271" t="n"/>
-      <c r="AV15" s="271" t="n"/>
-      <c r="AW15" s="272" t="n"/>
-      <c r="AX15" s="292" t="inlineStr">
+      <c r="AS15" s="406" t="n"/>
+      <c r="AT15" s="406" t="n"/>
+      <c r="AU15" s="406" t="n"/>
+      <c r="AV15" s="406" t="n"/>
+      <c r="AW15" s="407" t="n"/>
+      <c r="AX15" s="365" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="AY15" s="271" t="n"/>
-      <c r="AZ15" s="271" t="n"/>
-      <c r="BA15" s="272" t="n"/>
-      <c r="BB15" s="293" t="inlineStr">
+      <c r="AY15" s="406" t="n"/>
+      <c r="AZ15" s="406" t="n"/>
+      <c r="BA15" s="407" t="n"/>
+      <c r="BB15" s="365" t="inlineStr">
         <is>
           <t>Ref.</t>
         </is>
       </c>
-      <c r="BC15" s="271" t="n"/>
-      <c r="BD15" s="274" t="n"/>
+      <c r="BC15" s="406" t="n"/>
+      <c r="BD15" s="407" t="n"/>
     </row>
     <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="294">
+      <c r="A16" s="366">
         <f>ROW()-ROW($A$16)+1</f>
         <v/>
       </c>
-      <c r="B16" s="276" t="n"/>
-      <c r="C16" s="277" t="n"/>
-      <c r="D16" s="295" t="n"/>
-      <c r="E16" s="323" t="n"/>
-      <c r="F16" s="323" t="n"/>
-      <c r="G16" s="324" t="n"/>
-      <c r="H16" s="296" t="n"/>
-      <c r="I16" s="323" t="n"/>
-      <c r="J16" s="323" t="n"/>
-      <c r="K16" s="323" t="n"/>
-      <c r="L16" s="323" t="n"/>
-      <c r="M16" s="323" t="n"/>
-      <c r="N16" s="323" t="n"/>
-      <c r="O16" s="323" t="n"/>
-      <c r="P16" s="323" t="n"/>
-      <c r="Q16" s="323" t="n"/>
-      <c r="R16" s="323" t="n"/>
-      <c r="S16" s="323" t="n"/>
-      <c r="T16" s="323" t="n"/>
-      <c r="U16" s="323" t="n"/>
-      <c r="V16" s="323" t="n"/>
-      <c r="W16" s="323" t="n"/>
-      <c r="X16" s="323" t="n"/>
-      <c r="Y16" s="323" t="n"/>
-      <c r="Z16" s="324" t="n"/>
-      <c r="AA16" s="297" t="n"/>
-      <c r="AB16" s="323" t="n"/>
-      <c r="AC16" s="323" t="n"/>
-      <c r="AD16" s="323" t="n"/>
-      <c r="AE16" s="323" t="n"/>
-      <c r="AF16" s="323" t="n"/>
-      <c r="AG16" s="323" t="n"/>
-      <c r="AH16" s="323" t="n"/>
-      <c r="AI16" s="323" t="n"/>
-      <c r="AJ16" s="323" t="n"/>
-      <c r="AK16" s="323" t="n"/>
-      <c r="AL16" s="323" t="n"/>
-      <c r="AM16" s="323" t="n"/>
-      <c r="AN16" s="323" t="n"/>
-      <c r="AO16" s="323" t="n"/>
-      <c r="AP16" s="323" t="n"/>
-      <c r="AQ16" s="324" t="n"/>
-      <c r="AR16" s="296" t="n"/>
-      <c r="AS16" s="323" t="n"/>
-      <c r="AT16" s="323" t="n"/>
-      <c r="AU16" s="323" t="n"/>
-      <c r="AV16" s="323" t="n"/>
-      <c r="AW16" s="324" t="n"/>
-      <c r="AX16" s="296" t="n"/>
-      <c r="AY16" s="323" t="n"/>
-      <c r="AZ16" s="323" t="n"/>
-      <c r="BA16" s="324" t="n"/>
-      <c r="BB16" s="298" t="n"/>
-      <c r="BC16" s="323" t="n"/>
-      <c r="BD16" s="325" t="n"/>
+      <c r="B16" s="412" t="n"/>
+      <c r="C16" s="413" t="n"/>
+      <c r="D16" s="369" t="n"/>
+      <c r="E16" s="414" t="n"/>
+      <c r="F16" s="414" t="n"/>
+      <c r="G16" s="415" t="n"/>
+      <c r="H16" s="372" t="n"/>
+      <c r="I16" s="414" t="n"/>
+      <c r="J16" s="414" t="n"/>
+      <c r="K16" s="414" t="n"/>
+      <c r="L16" s="414" t="n"/>
+      <c r="M16" s="414" t="n"/>
+      <c r="N16" s="414" t="n"/>
+      <c r="O16" s="414" t="n"/>
+      <c r="P16" s="414" t="n"/>
+      <c r="Q16" s="414" t="n"/>
+      <c r="R16" s="414" t="n"/>
+      <c r="S16" s="414" t="n"/>
+      <c r="T16" s="414" t="n"/>
+      <c r="U16" s="414" t="n"/>
+      <c r="V16" s="414" t="n"/>
+      <c r="W16" s="414" t="n"/>
+      <c r="X16" s="414" t="n"/>
+      <c r="Y16" s="414" t="n"/>
+      <c r="Z16" s="415" t="n"/>
+      <c r="AA16" s="373" t="n"/>
+      <c r="AB16" s="414" t="n"/>
+      <c r="AC16" s="414" t="n"/>
+      <c r="AD16" s="414" t="n"/>
+      <c r="AE16" s="414" t="n"/>
+      <c r="AF16" s="414" t="n"/>
+      <c r="AG16" s="414" t="n"/>
+      <c r="AH16" s="414" t="n"/>
+      <c r="AI16" s="414" t="n"/>
+      <c r="AJ16" s="414" t="n"/>
+      <c r="AK16" s="414" t="n"/>
+      <c r="AL16" s="414" t="n"/>
+      <c r="AM16" s="414" t="n"/>
+      <c r="AN16" s="414" t="n"/>
+      <c r="AO16" s="414" t="n"/>
+      <c r="AP16" s="414" t="n"/>
+      <c r="AQ16" s="415" t="n"/>
+      <c r="AR16" s="372" t="n"/>
+      <c r="AS16" s="414" t="n"/>
+      <c r="AT16" s="414" t="n"/>
+      <c r="AU16" s="414" t="n"/>
+      <c r="AV16" s="414" t="n"/>
+      <c r="AW16" s="415" t="n"/>
+      <c r="AX16" s="372" t="n"/>
+      <c r="AY16" s="414" t="n"/>
+      <c r="AZ16" s="414" t="n"/>
+      <c r="BA16" s="415" t="n"/>
+      <c r="BB16" s="374" t="n"/>
+      <c r="BC16" s="414" t="n"/>
+      <c r="BD16" s="415" t="n"/>
     </row>
     <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="294">
+      <c r="A17" s="366">
         <f>ROW()-ROW($A$16)+1</f>
         <v/>
       </c>
-      <c r="B17" s="276" t="n"/>
-      <c r="C17" s="277" t="n"/>
-      <c r="D17" s="295" t="n"/>
-      <c r="E17" s="323" t="n"/>
-      <c r="F17" s="323" t="n"/>
-      <c r="G17" s="324" t="n"/>
-      <c r="H17" s="296" t="n"/>
-      <c r="I17" s="323" t="n"/>
-      <c r="J17" s="323" t="n"/>
-      <c r="K17" s="323" t="n"/>
-      <c r="L17" s="323" t="n"/>
-      <c r="M17" s="323" t="n"/>
-      <c r="N17" s="323" t="n"/>
-      <c r="O17" s="323" t="n"/>
-      <c r="P17" s="323" t="n"/>
-      <c r="Q17" s="323" t="n"/>
-      <c r="R17" s="323" t="n"/>
-      <c r="S17" s="323" t="n"/>
-      <c r="T17" s="323" t="n"/>
-      <c r="U17" s="323" t="n"/>
-      <c r="V17" s="323" t="n"/>
-      <c r="W17" s="323" t="n"/>
-      <c r="X17" s="323" t="n"/>
-      <c r="Y17" s="323" t="n"/>
-      <c r="Z17" s="324" t="n"/>
-      <c r="AA17" s="297" t="n"/>
-      <c r="AB17" s="323" t="n"/>
-      <c r="AC17" s="323" t="n"/>
-      <c r="AD17" s="323" t="n"/>
-      <c r="AE17" s="323" t="n"/>
-      <c r="AF17" s="323" t="n"/>
-      <c r="AG17" s="323" t="n"/>
-      <c r="AH17" s="323" t="n"/>
-      <c r="AI17" s="323" t="n"/>
-      <c r="AJ17" s="323" t="n"/>
-      <c r="AK17" s="323" t="n"/>
-      <c r="AL17" s="323" t="n"/>
-      <c r="AM17" s="323" t="n"/>
-      <c r="AN17" s="323" t="n"/>
-      <c r="AO17" s="323" t="n"/>
-      <c r="AP17" s="323" t="n"/>
-      <c r="AQ17" s="324" t="n"/>
-      <c r="AR17" s="296" t="n"/>
-      <c r="AS17" s="323" t="n"/>
-      <c r="AT17" s="323" t="n"/>
-      <c r="AU17" s="323" t="n"/>
-      <c r="AV17" s="323" t="n"/>
-      <c r="AW17" s="324" t="n"/>
-      <c r="AX17" s="296" t="n"/>
-      <c r="AY17" s="323" t="n"/>
-      <c r="AZ17" s="323" t="n"/>
-      <c r="BA17" s="324" t="n"/>
-      <c r="BB17" s="298" t="n"/>
-      <c r="BC17" s="323" t="n"/>
-      <c r="BD17" s="325" t="n"/>
+      <c r="B17" s="412" t="n"/>
+      <c r="C17" s="413" t="n"/>
+      <c r="D17" s="369" t="n"/>
+      <c r="E17" s="414" t="n"/>
+      <c r="F17" s="414" t="n"/>
+      <c r="G17" s="415" t="n"/>
+      <c r="H17" s="372" t="n"/>
+      <c r="I17" s="414" t="n"/>
+      <c r="J17" s="414" t="n"/>
+      <c r="K17" s="414" t="n"/>
+      <c r="L17" s="414" t="n"/>
+      <c r="M17" s="414" t="n"/>
+      <c r="N17" s="414" t="n"/>
+      <c r="O17" s="414" t="n"/>
+      <c r="P17" s="414" t="n"/>
+      <c r="Q17" s="414" t="n"/>
+      <c r="R17" s="414" t="n"/>
+      <c r="S17" s="414" t="n"/>
+      <c r="T17" s="414" t="n"/>
+      <c r="U17" s="414" t="n"/>
+      <c r="V17" s="414" t="n"/>
+      <c r="W17" s="414" t="n"/>
+      <c r="X17" s="414" t="n"/>
+      <c r="Y17" s="414" t="n"/>
+      <c r="Z17" s="415" t="n"/>
+      <c r="AA17" s="373" t="n"/>
+      <c r="AB17" s="414" t="n"/>
+      <c r="AC17" s="414" t="n"/>
+      <c r="AD17" s="414" t="n"/>
+      <c r="AE17" s="414" t="n"/>
+      <c r="AF17" s="414" t="n"/>
+      <c r="AG17" s="414" t="n"/>
+      <c r="AH17" s="414" t="n"/>
+      <c r="AI17" s="414" t="n"/>
+      <c r="AJ17" s="414" t="n"/>
+      <c r="AK17" s="414" t="n"/>
+      <c r="AL17" s="414" t="n"/>
+      <c r="AM17" s="414" t="n"/>
+      <c r="AN17" s="414" t="n"/>
+      <c r="AO17" s="414" t="n"/>
+      <c r="AP17" s="414" t="n"/>
+      <c r="AQ17" s="415" t="n"/>
+      <c r="AR17" s="372" t="n"/>
+      <c r="AS17" s="414" t="n"/>
+      <c r="AT17" s="414" t="n"/>
+      <c r="AU17" s="414" t="n"/>
+      <c r="AV17" s="414" t="n"/>
+      <c r="AW17" s="415" t="n"/>
+      <c r="AX17" s="372" t="n"/>
+      <c r="AY17" s="414" t="n"/>
+      <c r="AZ17" s="414" t="n"/>
+      <c r="BA17" s="415" t="n"/>
+      <c r="BB17" s="374" t="n"/>
+      <c r="BC17" s="414" t="n"/>
+      <c r="BD17" s="415" t="n"/>
     </row>
     <row r="18" ht="20" customHeight="1">
-      <c r="A18" s="294">
+      <c r="A18" s="366">
         <f>ROW()-ROW($A$16)+1</f>
         <v/>
       </c>
-      <c r="B18" s="276" t="n"/>
-      <c r="C18" s="277" t="n"/>
-      <c r="D18" s="295" t="n"/>
-      <c r="E18" s="323" t="n"/>
-      <c r="F18" s="323" t="n"/>
-      <c r="G18" s="324" t="n"/>
-      <c r="H18" s="296" t="n"/>
-      <c r="I18" s="323" t="n"/>
-      <c r="J18" s="323" t="n"/>
-      <c r="K18" s="323" t="n"/>
-      <c r="L18" s="323" t="n"/>
-      <c r="M18" s="323" t="n"/>
-      <c r="N18" s="323" t="n"/>
-      <c r="O18" s="323" t="n"/>
-      <c r="P18" s="323" t="n"/>
-      <c r="Q18" s="323" t="n"/>
-      <c r="R18" s="323" t="n"/>
-      <c r="S18" s="323" t="n"/>
-      <c r="T18" s="323" t="n"/>
-      <c r="U18" s="323" t="n"/>
-      <c r="V18" s="323" t="n"/>
-      <c r="W18" s="323" t="n"/>
-      <c r="X18" s="323" t="n"/>
-      <c r="Y18" s="323" t="n"/>
-      <c r="Z18" s="324" t="n"/>
-      <c r="AA18" s="297" t="n"/>
-      <c r="AB18" s="323" t="n"/>
-      <c r="AC18" s="323" t="n"/>
-      <c r="AD18" s="323" t="n"/>
-      <c r="AE18" s="323" t="n"/>
-      <c r="AF18" s="323" t="n"/>
-      <c r="AG18" s="323" t="n"/>
-      <c r="AH18" s="323" t="n"/>
-      <c r="AI18" s="323" t="n"/>
-      <c r="AJ18" s="323" t="n"/>
-      <c r="AK18" s="323" t="n"/>
-      <c r="AL18" s="323" t="n"/>
-      <c r="AM18" s="323" t="n"/>
-      <c r="AN18" s="323" t="n"/>
-      <c r="AO18" s="323" t="n"/>
-      <c r="AP18" s="323" t="n"/>
-      <c r="AQ18" s="324" t="n"/>
-      <c r="AR18" s="296" t="n"/>
-      <c r="AS18" s="323" t="n"/>
-      <c r="AT18" s="323" t="n"/>
-      <c r="AU18" s="323" t="n"/>
-      <c r="AV18" s="323" t="n"/>
-      <c r="AW18" s="324" t="n"/>
-      <c r="AX18" s="296" t="n"/>
-      <c r="AY18" s="323" t="n"/>
-      <c r="AZ18" s="323" t="n"/>
-      <c r="BA18" s="324" t="n"/>
-      <c r="BB18" s="298" t="n"/>
-      <c r="BC18" s="323" t="n"/>
-      <c r="BD18" s="325" t="n"/>
+      <c r="B18" s="412" t="n"/>
+      <c r="C18" s="413" t="n"/>
+      <c r="D18" s="369" t="n"/>
+      <c r="E18" s="414" t="n"/>
+      <c r="F18" s="414" t="n"/>
+      <c r="G18" s="415" t="n"/>
+      <c r="H18" s="372" t="n"/>
+      <c r="I18" s="414" t="n"/>
+      <c r="J18" s="414" t="n"/>
+      <c r="K18" s="414" t="n"/>
+      <c r="L18" s="414" t="n"/>
+      <c r="M18" s="414" t="n"/>
+      <c r="N18" s="414" t="n"/>
+      <c r="O18" s="414" t="n"/>
+      <c r="P18" s="414" t="n"/>
+      <c r="Q18" s="414" t="n"/>
+      <c r="R18" s="414" t="n"/>
+      <c r="S18" s="414" t="n"/>
+      <c r="T18" s="414" t="n"/>
+      <c r="U18" s="414" t="n"/>
+      <c r="V18" s="414" t="n"/>
+      <c r="W18" s="414" t="n"/>
+      <c r="X18" s="414" t="n"/>
+      <c r="Y18" s="414" t="n"/>
+      <c r="Z18" s="415" t="n"/>
+      <c r="AA18" s="373" t="n"/>
+      <c r="AB18" s="414" t="n"/>
+      <c r="AC18" s="414" t="n"/>
+      <c r="AD18" s="414" t="n"/>
+      <c r="AE18" s="414" t="n"/>
+      <c r="AF18" s="414" t="n"/>
+      <c r="AG18" s="414" t="n"/>
+      <c r="AH18" s="414" t="n"/>
+      <c r="AI18" s="414" t="n"/>
+      <c r="AJ18" s="414" t="n"/>
+      <c r="AK18" s="414" t="n"/>
+      <c r="AL18" s="414" t="n"/>
+      <c r="AM18" s="414" t="n"/>
+      <c r="AN18" s="414" t="n"/>
+      <c r="AO18" s="414" t="n"/>
+      <c r="AP18" s="414" t="n"/>
+      <c r="AQ18" s="415" t="n"/>
+      <c r="AR18" s="372" t="n"/>
+      <c r="AS18" s="414" t="n"/>
+      <c r="AT18" s="414" t="n"/>
+      <c r="AU18" s="414" t="n"/>
+      <c r="AV18" s="414" t="n"/>
+      <c r="AW18" s="415" t="n"/>
+      <c r="AX18" s="372" t="n"/>
+      <c r="AY18" s="414" t="n"/>
+      <c r="AZ18" s="414" t="n"/>
+      <c r="BA18" s="415" t="n"/>
+      <c r="BB18" s="374" t="n"/>
+      <c r="BC18" s="414" t="n"/>
+      <c r="BD18" s="415" t="n"/>
     </row>
     <row r="19" ht="20" customHeight="1">
-      <c r="A19" s="294">
+      <c r="A19" s="366">
         <f>ROW()-ROW($A$16)+1</f>
         <v/>
       </c>
-      <c r="B19" s="276" t="n"/>
-      <c r="C19" s="277" t="n"/>
-      <c r="D19" s="295" t="n"/>
-      <c r="E19" s="323" t="n"/>
-      <c r="F19" s="323" t="n"/>
-      <c r="G19" s="324" t="n"/>
-      <c r="H19" s="296" t="n"/>
-      <c r="I19" s="323" t="n"/>
-      <c r="J19" s="323" t="n"/>
-      <c r="K19" s="323" t="n"/>
-      <c r="L19" s="323" t="n"/>
-      <c r="M19" s="323" t="n"/>
-      <c r="N19" s="323" t="n"/>
-      <c r="O19" s="323" t="n"/>
-      <c r="P19" s="323" t="n"/>
-      <c r="Q19" s="323" t="n"/>
-      <c r="R19" s="323" t="n"/>
-      <c r="S19" s="323" t="n"/>
-      <c r="T19" s="323" t="n"/>
-      <c r="U19" s="323" t="n"/>
-      <c r="V19" s="323" t="n"/>
-      <c r="W19" s="323" t="n"/>
-      <c r="X19" s="323" t="n"/>
-      <c r="Y19" s="323" t="n"/>
-      <c r="Z19" s="324" t="n"/>
-      <c r="AA19" s="297" t="n"/>
-      <c r="AB19" s="323" t="n"/>
-      <c r="AC19" s="323" t="n"/>
-      <c r="AD19" s="323" t="n"/>
-      <c r="AE19" s="323" t="n"/>
-      <c r="AF19" s="323" t="n"/>
-      <c r="AG19" s="323" t="n"/>
-      <c r="AH19" s="323" t="n"/>
-      <c r="AI19" s="323" t="n"/>
-      <c r="AJ19" s="323" t="n"/>
-      <c r="AK19" s="323" t="n"/>
-      <c r="AL19" s="323" t="n"/>
-      <c r="AM19" s="323" t="n"/>
-      <c r="AN19" s="323" t="n"/>
-      <c r="AO19" s="323" t="n"/>
-      <c r="AP19" s="323" t="n"/>
-      <c r="AQ19" s="324" t="n"/>
-      <c r="AR19" s="296" t="n"/>
-      <c r="AS19" s="323" t="n"/>
-      <c r="AT19" s="323" t="n"/>
-      <c r="AU19" s="323" t="n"/>
-      <c r="AV19" s="323" t="n"/>
-      <c r="AW19" s="324" t="n"/>
-      <c r="AX19" s="296" t="n"/>
-      <c r="AY19" s="323" t="n"/>
-      <c r="AZ19" s="323" t="n"/>
-      <c r="BA19" s="324" t="n"/>
-      <c r="BB19" s="298" t="n"/>
-      <c r="BC19" s="323" t="n"/>
-      <c r="BD19" s="325" t="n"/>
+      <c r="B19" s="412" t="n"/>
+      <c r="C19" s="413" t="n"/>
+      <c r="D19" s="369" t="n"/>
+      <c r="E19" s="414" t="n"/>
+      <c r="F19" s="414" t="n"/>
+      <c r="G19" s="415" t="n"/>
+      <c r="H19" s="372" t="n"/>
+      <c r="I19" s="414" t="n"/>
+      <c r="J19" s="414" t="n"/>
+      <c r="K19" s="414" t="n"/>
+      <c r="L19" s="414" t="n"/>
+      <c r="M19" s="414" t="n"/>
+      <c r="N19" s="414" t="n"/>
+      <c r="O19" s="414" t="n"/>
+      <c r="P19" s="414" t="n"/>
+      <c r="Q19" s="414" t="n"/>
+      <c r="R19" s="414" t="n"/>
+      <c r="S19" s="414" t="n"/>
+      <c r="T19" s="414" t="n"/>
+      <c r="U19" s="414" t="n"/>
+      <c r="V19" s="414" t="n"/>
+      <c r="W19" s="414" t="n"/>
+      <c r="X19" s="414" t="n"/>
+      <c r="Y19" s="414" t="n"/>
+      <c r="Z19" s="415" t="n"/>
+      <c r="AA19" s="373" t="n"/>
+      <c r="AB19" s="414" t="n"/>
+      <c r="AC19" s="414" t="n"/>
+      <c r="AD19" s="414" t="n"/>
+      <c r="AE19" s="414" t="n"/>
+      <c r="AF19" s="414" t="n"/>
+      <c r="AG19" s="414" t="n"/>
+      <c r="AH19" s="414" t="n"/>
+      <c r="AI19" s="414" t="n"/>
+      <c r="AJ19" s="414" t="n"/>
+      <c r="AK19" s="414" t="n"/>
+      <c r="AL19" s="414" t="n"/>
+      <c r="AM19" s="414" t="n"/>
+      <c r="AN19" s="414" t="n"/>
+      <c r="AO19" s="414" t="n"/>
+      <c r="AP19" s="414" t="n"/>
+      <c r="AQ19" s="415" t="n"/>
+      <c r="AR19" s="372" t="n"/>
+      <c r="AS19" s="414" t="n"/>
+      <c r="AT19" s="414" t="n"/>
+      <c r="AU19" s="414" t="n"/>
+      <c r="AV19" s="414" t="n"/>
+      <c r="AW19" s="415" t="n"/>
+      <c r="AX19" s="372" t="n"/>
+      <c r="AY19" s="414" t="n"/>
+      <c r="AZ19" s="414" t="n"/>
+      <c r="BA19" s="415" t="n"/>
+      <c r="BB19" s="374" t="n"/>
+      <c r="BC19" s="414" t="n"/>
+      <c r="BD19" s="415" t="n"/>
     </row>
     <row r="20" ht="20" customHeight="1">
-      <c r="A20" s="294">
+      <c r="A20" s="366">
         <f>ROW()-ROW($A$16)+1</f>
         <v/>
       </c>
-      <c r="B20" s="276" t="n"/>
-      <c r="C20" s="277" t="n"/>
-      <c r="D20" s="295" t="n"/>
-      <c r="E20" s="323" t="n"/>
-      <c r="F20" s="323" t="n"/>
-      <c r="G20" s="324" t="n"/>
-      <c r="H20" s="296" t="n"/>
-      <c r="I20" s="323" t="n"/>
-      <c r="J20" s="323" t="n"/>
-      <c r="K20" s="323" t="n"/>
-      <c r="L20" s="323" t="n"/>
-      <c r="M20" s="323" t="n"/>
-      <c r="N20" s="323" t="n"/>
-      <c r="O20" s="323" t="n"/>
-      <c r="P20" s="323" t="n"/>
-      <c r="Q20" s="323" t="n"/>
-      <c r="R20" s="323" t="n"/>
-      <c r="S20" s="323" t="n"/>
-      <c r="T20" s="323" t="n"/>
-      <c r="U20" s="323" t="n"/>
-      <c r="V20" s="323" t="n"/>
-      <c r="W20" s="323" t="n"/>
-      <c r="X20" s="323" t="n"/>
-      <c r="Y20" s="323" t="n"/>
-      <c r="Z20" s="324" t="n"/>
-      <c r="AA20" s="297" t="n"/>
-      <c r="AB20" s="323" t="n"/>
-      <c r="AC20" s="323" t="n"/>
-      <c r="AD20" s="323" t="n"/>
-      <c r="AE20" s="323" t="n"/>
-      <c r="AF20" s="323" t="n"/>
-      <c r="AG20" s="323" t="n"/>
-      <c r="AH20" s="323" t="n"/>
-      <c r="AI20" s="323" t="n"/>
-      <c r="AJ20" s="323" t="n"/>
-      <c r="AK20" s="323" t="n"/>
-      <c r="AL20" s="323" t="n"/>
-      <c r="AM20" s="323" t="n"/>
-      <c r="AN20" s="323" t="n"/>
-      <c r="AO20" s="323" t="n"/>
-      <c r="AP20" s="323" t="n"/>
-      <c r="AQ20" s="324" t="n"/>
-      <c r="AR20" s="296" t="n"/>
-      <c r="AS20" s="323" t="n"/>
-      <c r="AT20" s="323" t="n"/>
-      <c r="AU20" s="323" t="n"/>
-      <c r="AV20" s="323" t="n"/>
-      <c r="AW20" s="324" t="n"/>
-      <c r="AX20" s="296" t="n"/>
-      <c r="AY20" s="323" t="n"/>
-      <c r="AZ20" s="323" t="n"/>
-      <c r="BA20" s="324" t="n"/>
-      <c r="BB20" s="298" t="n"/>
-      <c r="BC20" s="323" t="n"/>
-      <c r="BD20" s="325" t="n"/>
+      <c r="B20" s="412" t="n"/>
+      <c r="C20" s="413" t="n"/>
+      <c r="D20" s="369" t="n"/>
+      <c r="E20" s="414" t="n"/>
+      <c r="F20" s="414" t="n"/>
+      <c r="G20" s="415" t="n"/>
+      <c r="H20" s="372" t="n"/>
+      <c r="I20" s="414" t="n"/>
+      <c r="J20" s="414" t="n"/>
+      <c r="K20" s="414" t="n"/>
+      <c r="L20" s="414" t="n"/>
+      <c r="M20" s="414" t="n"/>
+      <c r="N20" s="414" t="n"/>
+      <c r="O20" s="414" t="n"/>
+      <c r="P20" s="414" t="n"/>
+      <c r="Q20" s="414" t="n"/>
+      <c r="R20" s="414" t="n"/>
+      <c r="S20" s="414" t="n"/>
+      <c r="T20" s="414" t="n"/>
+      <c r="U20" s="414" t="n"/>
+      <c r="V20" s="414" t="n"/>
+      <c r="W20" s="414" t="n"/>
+      <c r="X20" s="414" t="n"/>
+      <c r="Y20" s="414" t="n"/>
+      <c r="Z20" s="415" t="n"/>
+      <c r="AA20" s="373" t="n"/>
+      <c r="AB20" s="414" t="n"/>
+      <c r="AC20" s="414" t="n"/>
+      <c r="AD20" s="414" t="n"/>
+      <c r="AE20" s="414" t="n"/>
+      <c r="AF20" s="414" t="n"/>
+      <c r="AG20" s="414" t="n"/>
+      <c r="AH20" s="414" t="n"/>
+      <c r="AI20" s="414" t="n"/>
+      <c r="AJ20" s="414" t="n"/>
+      <c r="AK20" s="414" t="n"/>
+      <c r="AL20" s="414" t="n"/>
+      <c r="AM20" s="414" t="n"/>
+      <c r="AN20" s="414" t="n"/>
+      <c r="AO20" s="414" t="n"/>
+      <c r="AP20" s="414" t="n"/>
+      <c r="AQ20" s="415" t="n"/>
+      <c r="AR20" s="372" t="n"/>
+      <c r="AS20" s="414" t="n"/>
+      <c r="AT20" s="414" t="n"/>
+      <c r="AU20" s="414" t="n"/>
+      <c r="AV20" s="414" t="n"/>
+      <c r="AW20" s="415" t="n"/>
+      <c r="AX20" s="372" t="n"/>
+      <c r="AY20" s="414" t="n"/>
+      <c r="AZ20" s="414" t="n"/>
+      <c r="BA20" s="415" t="n"/>
+      <c r="BB20" s="374" t="n"/>
+      <c r="BC20" s="414" t="n"/>
+      <c r="BD20" s="415" t="n"/>
     </row>
     <row r="21" ht="20" customHeight="1">
-      <c r="A21" s="294">
+      <c r="A21" s="366">
         <f>ROW()-ROW($A$16)+1</f>
         <v/>
       </c>
-      <c r="B21" s="276" t="n"/>
-      <c r="C21" s="277" t="n"/>
-      <c r="D21" s="295" t="n"/>
-      <c r="E21" s="323" t="n"/>
-      <c r="F21" s="323" t="n"/>
-      <c r="G21" s="324" t="n"/>
-      <c r="H21" s="296" t="n"/>
-      <c r="I21" s="323" t="n"/>
-      <c r="J21" s="323" t="n"/>
-      <c r="K21" s="323" t="n"/>
-      <c r="L21" s="323" t="n"/>
-      <c r="M21" s="323" t="n"/>
-      <c r="N21" s="323" t="n"/>
-      <c r="O21" s="323" t="n"/>
-      <c r="P21" s="323" t="n"/>
-      <c r="Q21" s="323" t="n"/>
-      <c r="R21" s="323" t="n"/>
-      <c r="S21" s="323" t="n"/>
-      <c r="T21" s="323" t="n"/>
-      <c r="U21" s="323" t="n"/>
-      <c r="V21" s="323" t="n"/>
-      <c r="W21" s="323" t="n"/>
-      <c r="X21" s="323" t="n"/>
-      <c r="Y21" s="323" t="n"/>
-      <c r="Z21" s="324" t="n"/>
-      <c r="AA21" s="297" t="n"/>
-      <c r="AB21" s="323" t="n"/>
-      <c r="AC21" s="323" t="n"/>
-      <c r="AD21" s="323" t="n"/>
-      <c r="AE21" s="323" t="n"/>
-      <c r="AF21" s="323" t="n"/>
-      <c r="AG21" s="323" t="n"/>
-      <c r="AH21" s="323" t="n"/>
-      <c r="AI21" s="323" t="n"/>
-      <c r="AJ21" s="323" t="n"/>
-      <c r="AK21" s="323" t="n"/>
-      <c r="AL21" s="323" t="n"/>
-      <c r="AM21" s="323" t="n"/>
-      <c r="AN21" s="323" t="n"/>
-      <c r="AO21" s="323" t="n"/>
-      <c r="AP21" s="323" t="n"/>
-      <c r="AQ21" s="324" t="n"/>
-      <c r="AR21" s="296" t="n"/>
-      <c r="AS21" s="323" t="n"/>
-      <c r="AT21" s="323" t="n"/>
-      <c r="AU21" s="323" t="n"/>
-      <c r="AV21" s="323" t="n"/>
-      <c r="AW21" s="324" t="n"/>
-      <c r="AX21" s="296" t="n"/>
-      <c r="AY21" s="323" t="n"/>
-      <c r="AZ21" s="323" t="n"/>
-      <c r="BA21" s="324" t="n"/>
-      <c r="BB21" s="298" t="n"/>
-      <c r="BC21" s="323" t="n"/>
-      <c r="BD21" s="325" t="n"/>
+      <c r="B21" s="412" t="n"/>
+      <c r="C21" s="413" t="n"/>
+      <c r="D21" s="369" t="n"/>
+      <c r="E21" s="414" t="n"/>
+      <c r="F21" s="414" t="n"/>
+      <c r="G21" s="415" t="n"/>
+      <c r="H21" s="372" t="n"/>
+      <c r="I21" s="414" t="n"/>
+      <c r="J21" s="414" t="n"/>
+      <c r="K21" s="414" t="n"/>
+      <c r="L21" s="414" t="n"/>
+      <c r="M21" s="414" t="n"/>
+      <c r="N21" s="414" t="n"/>
+      <c r="O21" s="414" t="n"/>
+      <c r="P21" s="414" t="n"/>
+      <c r="Q21" s="414" t="n"/>
+      <c r="R21" s="414" t="n"/>
+      <c r="S21" s="414" t="n"/>
+      <c r="T21" s="414" t="n"/>
+      <c r="U21" s="414" t="n"/>
+      <c r="V21" s="414" t="n"/>
+      <c r="W21" s="414" t="n"/>
+      <c r="X21" s="414" t="n"/>
+      <c r="Y21" s="414" t="n"/>
+      <c r="Z21" s="415" t="n"/>
+      <c r="AA21" s="373" t="n"/>
+      <c r="AB21" s="414" t="n"/>
+      <c r="AC21" s="414" t="n"/>
+      <c r="AD21" s="414" t="n"/>
+      <c r="AE21" s="414" t="n"/>
+      <c r="AF21" s="414" t="n"/>
+      <c r="AG21" s="414" t="n"/>
+      <c r="AH21" s="414" t="n"/>
+      <c r="AI21" s="414" t="n"/>
+      <c r="AJ21" s="414" t="n"/>
+      <c r="AK21" s="414" t="n"/>
+      <c r="AL21" s="414" t="n"/>
+      <c r="AM21" s="414" t="n"/>
+      <c r="AN21" s="414" t="n"/>
+      <c r="AO21" s="414" t="n"/>
+      <c r="AP21" s="414" t="n"/>
+      <c r="AQ21" s="415" t="n"/>
+      <c r="AR21" s="372" t="n"/>
+      <c r="AS21" s="414" t="n"/>
+      <c r="AT21" s="414" t="n"/>
+      <c r="AU21" s="414" t="n"/>
+      <c r="AV21" s="414" t="n"/>
+      <c r="AW21" s="415" t="n"/>
+      <c r="AX21" s="372" t="n"/>
+      <c r="AY21" s="414" t="n"/>
+      <c r="AZ21" s="414" t="n"/>
+      <c r="BA21" s="415" t="n"/>
+      <c r="BB21" s="374" t="n"/>
+      <c r="BC21" s="414" t="n"/>
+      <c r="BD21" s="415" t="n"/>
     </row>
     <row r="22" ht="20" customHeight="1">
-      <c r="A22" s="294">
+      <c r="A22" s="366">
         <f>ROW()-ROW($A$16)+1</f>
         <v/>
       </c>
-      <c r="B22" s="276" t="n"/>
-      <c r="C22" s="277" t="n"/>
-      <c r="D22" s="295" t="n"/>
-      <c r="E22" s="323" t="n"/>
-      <c r="F22" s="323" t="n"/>
-      <c r="G22" s="324" t="n"/>
-      <c r="H22" s="296" t="n"/>
-      <c r="I22" s="323" t="n"/>
-      <c r="J22" s="323" t="n"/>
-      <c r="K22" s="323" t="n"/>
-      <c r="L22" s="323" t="n"/>
-      <c r="M22" s="323" t="n"/>
-      <c r="N22" s="323" t="n"/>
-      <c r="O22" s="323" t="n"/>
-      <c r="P22" s="323" t="n"/>
-      <c r="Q22" s="323" t="n"/>
-      <c r="R22" s="323" t="n"/>
-      <c r="S22" s="323" t="n"/>
-      <c r="T22" s="323" t="n"/>
-      <c r="U22" s="323" t="n"/>
-      <c r="V22" s="323" t="n"/>
-      <c r="W22" s="323" t="n"/>
-      <c r="X22" s="323" t="n"/>
-      <c r="Y22" s="323" t="n"/>
-      <c r="Z22" s="324" t="n"/>
-      <c r="AA22" s="297" t="n"/>
-      <c r="AB22" s="323" t="n"/>
-      <c r="AC22" s="323" t="n"/>
-      <c r="AD22" s="323" t="n"/>
-      <c r="AE22" s="323" t="n"/>
-      <c r="AF22" s="323" t="n"/>
-      <c r="AG22" s="323" t="n"/>
-      <c r="AH22" s="323" t="n"/>
-      <c r="AI22" s="323" t="n"/>
-      <c r="AJ22" s="323" t="n"/>
-      <c r="AK22" s="323" t="n"/>
-      <c r="AL22" s="323" t="n"/>
-      <c r="AM22" s="323" t="n"/>
-      <c r="AN22" s="323" t="n"/>
-      <c r="AO22" s="323" t="n"/>
-      <c r="AP22" s="323" t="n"/>
-      <c r="AQ22" s="324" t="n"/>
-      <c r="AR22" s="296" t="n"/>
-      <c r="AS22" s="323" t="n"/>
-      <c r="AT22" s="323" t="n"/>
-      <c r="AU22" s="323" t="n"/>
-      <c r="AV22" s="323" t="n"/>
-      <c r="AW22" s="324" t="n"/>
-      <c r="AX22" s="296" t="n"/>
-      <c r="AY22" s="323" t="n"/>
-      <c r="AZ22" s="323" t="n"/>
-      <c r="BA22" s="324" t="n"/>
-      <c r="BB22" s="298" t="n"/>
-      <c r="BC22" s="323" t="n"/>
-      <c r="BD22" s="325" t="n"/>
+      <c r="B22" s="412" t="n"/>
+      <c r="C22" s="413" t="n"/>
+      <c r="D22" s="369" t="n"/>
+      <c r="E22" s="414" t="n"/>
+      <c r="F22" s="414" t="n"/>
+      <c r="G22" s="415" t="n"/>
+      <c r="H22" s="372" t="n"/>
+      <c r="I22" s="414" t="n"/>
+      <c r="J22" s="414" t="n"/>
+      <c r="K22" s="414" t="n"/>
+      <c r="L22" s="414" t="n"/>
+      <c r="M22" s="414" t="n"/>
+      <c r="N22" s="414" t="n"/>
+      <c r="O22" s="414" t="n"/>
+      <c r="P22" s="414" t="n"/>
+      <c r="Q22" s="414" t="n"/>
+      <c r="R22" s="414" t="n"/>
+      <c r="S22" s="414" t="n"/>
+      <c r="T22" s="414" t="n"/>
+      <c r="U22" s="414" t="n"/>
+      <c r="V22" s="414" t="n"/>
+      <c r="W22" s="414" t="n"/>
+      <c r="X22" s="414" t="n"/>
+      <c r="Y22" s="414" t="n"/>
+      <c r="Z22" s="415" t="n"/>
+      <c r="AA22" s="373" t="n"/>
+      <c r="AB22" s="414" t="n"/>
+      <c r="AC22" s="414" t="n"/>
+      <c r="AD22" s="414" t="n"/>
+      <c r="AE22" s="414" t="n"/>
+      <c r="AF22" s="414" t="n"/>
+      <c r="AG22" s="414" t="n"/>
+      <c r="AH22" s="414" t="n"/>
+      <c r="AI22" s="414" t="n"/>
+      <c r="AJ22" s="414" t="n"/>
+      <c r="AK22" s="414" t="n"/>
+      <c r="AL22" s="414" t="n"/>
+      <c r="AM22" s="414" t="n"/>
+      <c r="AN22" s="414" t="n"/>
+      <c r="AO22" s="414" t="n"/>
+      <c r="AP22" s="414" t="n"/>
+      <c r="AQ22" s="415" t="n"/>
+      <c r="AR22" s="372" t="n"/>
+      <c r="AS22" s="414" t="n"/>
+      <c r="AT22" s="414" t="n"/>
+      <c r="AU22" s="414" t="n"/>
+      <c r="AV22" s="414" t="n"/>
+      <c r="AW22" s="415" t="n"/>
+      <c r="AX22" s="372" t="n"/>
+      <c r="AY22" s="414" t="n"/>
+      <c r="AZ22" s="414" t="n"/>
+      <c r="BA22" s="415" t="n"/>
+      <c r="BB22" s="374" t="n"/>
+      <c r="BC22" s="414" t="n"/>
+      <c r="BD22" s="415" t="n"/>
     </row>
     <row r="23" ht="20" customHeight="1">
-      <c r="A23" s="294">
+      <c r="A23" s="366">
         <f>ROW()-ROW($A$16)+1</f>
         <v/>
       </c>
-      <c r="B23" s="276" t="n"/>
-      <c r="C23" s="277" t="n"/>
-      <c r="D23" s="295" t="n"/>
-      <c r="E23" s="323" t="n"/>
-      <c r="F23" s="323" t="n"/>
-      <c r="G23" s="324" t="n"/>
-      <c r="H23" s="296" t="n"/>
-      <c r="I23" s="323" t="n"/>
-      <c r="J23" s="323" t="n"/>
-      <c r="K23" s="323" t="n"/>
-      <c r="L23" s="323" t="n"/>
-      <c r="M23" s="323" t="n"/>
-      <c r="N23" s="323" t="n"/>
-      <c r="O23" s="323" t="n"/>
-      <c r="P23" s="323" t="n"/>
-      <c r="Q23" s="323" t="n"/>
-      <c r="R23" s="323" t="n"/>
-      <c r="S23" s="323" t="n"/>
-      <c r="T23" s="323" t="n"/>
-      <c r="U23" s="323" t="n"/>
-      <c r="V23" s="323" t="n"/>
-      <c r="W23" s="323" t="n"/>
-      <c r="X23" s="323" t="n"/>
-      <c r="Y23" s="323" t="n"/>
-      <c r="Z23" s="324" t="n"/>
-      <c r="AA23" s="297" t="n"/>
-      <c r="AB23" s="323" t="n"/>
-      <c r="AC23" s="323" t="n"/>
-      <c r="AD23" s="323" t="n"/>
-      <c r="AE23" s="323" t="n"/>
-      <c r="AF23" s="323" t="n"/>
-      <c r="AG23" s="323" t="n"/>
-      <c r="AH23" s="323" t="n"/>
-      <c r="AI23" s="323" t="n"/>
-      <c r="AJ23" s="323" t="n"/>
-      <c r="AK23" s="323" t="n"/>
-      <c r="AL23" s="323" t="n"/>
-      <c r="AM23" s="323" t="n"/>
-      <c r="AN23" s="323" t="n"/>
-      <c r="AO23" s="323" t="n"/>
-      <c r="AP23" s="323" t="n"/>
-      <c r="AQ23" s="324" t="n"/>
-      <c r="AR23" s="296" t="n"/>
-      <c r="AS23" s="323" t="n"/>
-      <c r="AT23" s="323" t="n"/>
-      <c r="AU23" s="323" t="n"/>
-      <c r="AV23" s="323" t="n"/>
-      <c r="AW23" s="324" t="n"/>
-      <c r="AX23" s="296" t="n"/>
-      <c r="AY23" s="323" t="n"/>
-      <c r="AZ23" s="323" t="n"/>
-      <c r="BA23" s="324" t="n"/>
-      <c r="BB23" s="298" t="n"/>
-      <c r="BC23" s="323" t="n"/>
-      <c r="BD23" s="325" t="n"/>
+      <c r="B23" s="412" t="n"/>
+      <c r="C23" s="413" t="n"/>
+      <c r="D23" s="369" t="n"/>
+      <c r="E23" s="414" t="n"/>
+      <c r="F23" s="414" t="n"/>
+      <c r="G23" s="415" t="n"/>
+      <c r="H23" s="372" t="n"/>
+      <c r="I23" s="414" t="n"/>
+      <c r="J23" s="414" t="n"/>
+      <c r="K23" s="414" t="n"/>
+      <c r="L23" s="414" t="n"/>
+      <c r="M23" s="414" t="n"/>
+      <c r="N23" s="414" t="n"/>
+      <c r="O23" s="414" t="n"/>
+      <c r="P23" s="414" t="n"/>
+      <c r="Q23" s="414" t="n"/>
+      <c r="R23" s="414" t="n"/>
+      <c r="S23" s="414" t="n"/>
+      <c r="T23" s="414" t="n"/>
+      <c r="U23" s="414" t="n"/>
+      <c r="V23" s="414" t="n"/>
+      <c r="W23" s="414" t="n"/>
+      <c r="X23" s="414" t="n"/>
+      <c r="Y23" s="414" t="n"/>
+      <c r="Z23" s="415" t="n"/>
+      <c r="AA23" s="373" t="n"/>
+      <c r="AB23" s="414" t="n"/>
+      <c r="AC23" s="414" t="n"/>
+      <c r="AD23" s="414" t="n"/>
+      <c r="AE23" s="414" t="n"/>
+      <c r="AF23" s="414" t="n"/>
+      <c r="AG23" s="414" t="n"/>
+      <c r="AH23" s="414" t="n"/>
+      <c r="AI23" s="414" t="n"/>
+      <c r="AJ23" s="414" t="n"/>
+      <c r="AK23" s="414" t="n"/>
+      <c r="AL23" s="414" t="n"/>
+      <c r="AM23" s="414" t="n"/>
+      <c r="AN23" s="414" t="n"/>
+      <c r="AO23" s="414" t="n"/>
+      <c r="AP23" s="414" t="n"/>
+      <c r="AQ23" s="415" t="n"/>
+      <c r="AR23" s="372" t="n"/>
+      <c r="AS23" s="414" t="n"/>
+      <c r="AT23" s="414" t="n"/>
+      <c r="AU23" s="414" t="n"/>
+      <c r="AV23" s="414" t="n"/>
+      <c r="AW23" s="415" t="n"/>
+      <c r="AX23" s="372" t="n"/>
+      <c r="AY23" s="414" t="n"/>
+      <c r="AZ23" s="414" t="n"/>
+      <c r="BA23" s="415" t="n"/>
+      <c r="BB23" s="374" t="n"/>
+      <c r="BC23" s="414" t="n"/>
+      <c r="BD23" s="415" t="n"/>
     </row>
     <row r="24" ht="4" customHeight="1">
-      <c r="A24" s="294" t="n"/>
-      <c r="D24" s="299" t="n"/>
-      <c r="H24" s="300" t="n"/>
-      <c r="AA24" s="301" t="n"/>
-      <c r="AR24" s="302" t="n"/>
-      <c r="AX24" s="302" t="n"/>
-      <c r="BB24" s="303" t="n"/>
+      <c r="A24" s="375" t="n"/>
+      <c r="B24" s="353" t="n"/>
+      <c r="C24" s="353" t="n"/>
+      <c r="D24" s="376" t="n"/>
+      <c r="E24" s="353" t="n"/>
+      <c r="F24" s="353" t="n"/>
+      <c r="G24" s="353" t="n"/>
+      <c r="H24" s="377" t="n"/>
+      <c r="I24" s="353" t="n"/>
+      <c r="J24" s="353" t="n"/>
+      <c r="K24" s="353" t="n"/>
+      <c r="L24" s="353" t="n"/>
+      <c r="M24" s="353" t="n"/>
+      <c r="N24" s="353" t="n"/>
+      <c r="O24" s="353" t="n"/>
+      <c r="P24" s="353" t="n"/>
+      <c r="Q24" s="353" t="n"/>
+      <c r="R24" s="353" t="n"/>
+      <c r="S24" s="353" t="n"/>
+      <c r="T24" s="353" t="n"/>
+      <c r="U24" s="353" t="n"/>
+      <c r="V24" s="353" t="n"/>
+      <c r="W24" s="353" t="n"/>
+      <c r="X24" s="353" t="n"/>
+      <c r="Y24" s="353" t="n"/>
+      <c r="Z24" s="353" t="n"/>
+      <c r="AA24" s="378" t="n"/>
+      <c r="AB24" s="353" t="n"/>
+      <c r="AC24" s="353" t="n"/>
+      <c r="AD24" s="353" t="n"/>
+      <c r="AE24" s="353" t="n"/>
+      <c r="AF24" s="353" t="n"/>
+      <c r="AG24" s="353" t="n"/>
+      <c r="AH24" s="353" t="n"/>
+      <c r="AI24" s="353" t="n"/>
+      <c r="AJ24" s="353" t="n"/>
+      <c r="AK24" s="353" t="n"/>
+      <c r="AL24" s="353" t="n"/>
+      <c r="AM24" s="353" t="n"/>
+      <c r="AN24" s="353" t="n"/>
+      <c r="AO24" s="353" t="n"/>
+      <c r="AP24" s="353" t="n"/>
+      <c r="AQ24" s="353" t="n"/>
+      <c r="AR24" s="379" t="n"/>
+      <c r="AS24" s="353" t="n"/>
+      <c r="AT24" s="353" t="n"/>
+      <c r="AU24" s="353" t="n"/>
+      <c r="AV24" s="353" t="n"/>
+      <c r="AW24" s="353" t="n"/>
+      <c r="AX24" s="379" t="n"/>
+      <c r="AY24" s="353" t="n"/>
+      <c r="AZ24" s="353" t="n"/>
+      <c r="BA24" s="353" t="n"/>
+      <c r="BB24" s="380" t="n"/>
+      <c r="BC24" s="353" t="n"/>
+      <c r="BD24" s="353" t="n"/>
     </row>
-    <row r="25" ht="17" customHeight="1">
-      <c r="A25" s="284" t="inlineStr">
+    <row r="25" ht="20" customHeight="1">
+      <c r="A25" s="354" t="inlineStr">
         <is>
           <t xml:space="preserve">  3. CONDITIONS / ACTIONS / RELEASE</t>
         </is>
       </c>
-      <c r="B25" s="285" t="n"/>
-      <c r="C25" s="285" t="n"/>
-      <c r="D25" s="285" t="n"/>
-      <c r="E25" s="285" t="n"/>
-      <c r="F25" s="285" t="n"/>
-      <c r="G25" s="285" t="n"/>
-      <c r="H25" s="285" t="n"/>
-      <c r="I25" s="285" t="n"/>
-      <c r="J25" s="285" t="n"/>
-      <c r="K25" s="285" t="n"/>
-      <c r="L25" s="285" t="n"/>
-      <c r="M25" s="285" t="n"/>
-      <c r="N25" s="285" t="n"/>
-      <c r="O25" s="285" t="n"/>
-      <c r="P25" s="285" t="n"/>
-      <c r="Q25" s="285" t="n"/>
-      <c r="R25" s="285" t="n"/>
-      <c r="S25" s="285" t="n"/>
-      <c r="T25" s="285" t="n"/>
-      <c r="U25" s="285" t="n"/>
-      <c r="V25" s="285" t="n"/>
-      <c r="W25" s="285" t="n"/>
-      <c r="X25" s="285" t="n"/>
-      <c r="Y25" s="285" t="n"/>
-      <c r="Z25" s="285" t="n"/>
-      <c r="AA25" s="285" t="n"/>
-      <c r="AB25" s="285" t="n"/>
-      <c r="AC25" s="285" t="n"/>
-      <c r="AD25" s="285" t="n"/>
-      <c r="AE25" s="285" t="n"/>
-      <c r="AF25" s="285" t="n"/>
-      <c r="AG25" s="285" t="n"/>
-      <c r="AH25" s="285" t="n"/>
-      <c r="AI25" s="285" t="n"/>
-      <c r="AJ25" s="285" t="n"/>
-      <c r="AK25" s="285" t="n"/>
-      <c r="AL25" s="285" t="n"/>
-      <c r="AM25" s="285" t="n"/>
-      <c r="AN25" s="285" t="n"/>
-      <c r="AO25" s="285" t="n"/>
-      <c r="AP25" s="285" t="n"/>
-      <c r="AQ25" s="285" t="n"/>
-      <c r="AR25" s="285" t="n"/>
-      <c r="AS25" s="285" t="n"/>
-      <c r="AT25" s="285" t="n"/>
-      <c r="AU25" s="285" t="n"/>
-      <c r="AV25" s="285" t="n"/>
-      <c r="AW25" s="285" t="n"/>
-      <c r="AX25" s="285" t="n"/>
-      <c r="AY25" s="285" t="n"/>
-      <c r="AZ25" s="285" t="n"/>
-      <c r="BA25" s="285" t="n"/>
-      <c r="BB25" s="285" t="n"/>
-      <c r="BC25" s="285" t="n"/>
-      <c r="BD25" s="286" t="n"/>
+      <c r="B25" s="406" t="n"/>
+      <c r="C25" s="406" t="n"/>
+      <c r="D25" s="406" t="n"/>
+      <c r="E25" s="406" t="n"/>
+      <c r="F25" s="406" t="n"/>
+      <c r="G25" s="406" t="n"/>
+      <c r="H25" s="406" t="n"/>
+      <c r="I25" s="406" t="n"/>
+      <c r="J25" s="406" t="n"/>
+      <c r="K25" s="406" t="n"/>
+      <c r="L25" s="406" t="n"/>
+      <c r="M25" s="406" t="n"/>
+      <c r="N25" s="406" t="n"/>
+      <c r="O25" s="406" t="n"/>
+      <c r="P25" s="406" t="n"/>
+      <c r="Q25" s="406" t="n"/>
+      <c r="R25" s="406" t="n"/>
+      <c r="S25" s="406" t="n"/>
+      <c r="T25" s="406" t="n"/>
+      <c r="U25" s="406" t="n"/>
+      <c r="V25" s="406" t="n"/>
+      <c r="W25" s="406" t="n"/>
+      <c r="X25" s="406" t="n"/>
+      <c r="Y25" s="406" t="n"/>
+      <c r="Z25" s="406" t="n"/>
+      <c r="AA25" s="406" t="n"/>
+      <c r="AB25" s="406" t="n"/>
+      <c r="AC25" s="406" t="n"/>
+      <c r="AD25" s="406" t="n"/>
+      <c r="AE25" s="406" t="n"/>
+      <c r="AF25" s="406" t="n"/>
+      <c r="AG25" s="406" t="n"/>
+      <c r="AH25" s="406" t="n"/>
+      <c r="AI25" s="406" t="n"/>
+      <c r="AJ25" s="406" t="n"/>
+      <c r="AK25" s="406" t="n"/>
+      <c r="AL25" s="406" t="n"/>
+      <c r="AM25" s="406" t="n"/>
+      <c r="AN25" s="406" t="n"/>
+      <c r="AO25" s="406" t="n"/>
+      <c r="AP25" s="406" t="n"/>
+      <c r="AQ25" s="406" t="n"/>
+      <c r="AR25" s="406" t="n"/>
+      <c r="AS25" s="406" t="n"/>
+      <c r="AT25" s="406" t="n"/>
+      <c r="AU25" s="406" t="n"/>
+      <c r="AV25" s="406" t="n"/>
+      <c r="AW25" s="406" t="n"/>
+      <c r="AX25" s="406" t="n"/>
+      <c r="AY25" s="406" t="n"/>
+      <c r="AZ25" s="406" t="n"/>
+      <c r="BA25" s="406" t="n"/>
+      <c r="BB25" s="406" t="n"/>
+      <c r="BC25" s="406" t="n"/>
+      <c r="BD25" s="407" t="n"/>
     </row>
     <row r="26" ht="20" customHeight="1">
-      <c r="A26" s="287" t="inlineStr">
+      <c r="A26" s="355" t="inlineStr">
         <is>
           <t>Conditional Action Required (YES/NO)</t>
         </is>
       </c>
-      <c r="B26" s="271" t="n"/>
-      <c r="C26" s="271" t="n"/>
-      <c r="D26" s="271" t="n"/>
-      <c r="E26" s="271" t="n"/>
-      <c r="F26" s="271" t="n"/>
-      <c r="G26" s="271" t="n"/>
-      <c r="H26" s="271" t="n"/>
-      <c r="I26" s="271" t="n"/>
-      <c r="J26" s="272" t="n"/>
-      <c r="K26" s="288" t="n"/>
-      <c r="L26" s="320" t="n"/>
-      <c r="M26" s="320" t="n"/>
-      <c r="N26" s="320" t="n"/>
-      <c r="O26" s="320" t="n"/>
-      <c r="P26" s="320" t="n"/>
-      <c r="Q26" s="320" t="n"/>
-      <c r="R26" s="320" t="n"/>
-      <c r="S26" s="320" t="n"/>
-      <c r="T26" s="320" t="n"/>
-      <c r="U26" s="320" t="n"/>
-      <c r="V26" s="320" t="n"/>
-      <c r="W26" s="320" t="n"/>
-      <c r="X26" s="320" t="n"/>
-      <c r="Y26" s="320" t="n"/>
-      <c r="Z26" s="320" t="n"/>
-      <c r="AA26" s="320" t="n"/>
-      <c r="AB26" s="321" t="n"/>
-      <c r="AC26" s="289" t="inlineStr">
+      <c r="B26" s="406" t="n"/>
+      <c r="C26" s="406" t="n"/>
+      <c r="D26" s="406" t="n"/>
+      <c r="E26" s="406" t="n"/>
+      <c r="F26" s="406" t="n"/>
+      <c r="G26" s="406" t="n"/>
+      <c r="H26" s="406" t="n"/>
+      <c r="I26" s="406" t="n"/>
+      <c r="J26" s="407" t="n"/>
+      <c r="K26" s="358" t="n"/>
+      <c r="L26" s="408" t="n"/>
+      <c r="M26" s="408" t="n"/>
+      <c r="N26" s="408" t="n"/>
+      <c r="O26" s="408" t="n"/>
+      <c r="P26" s="408" t="n"/>
+      <c r="Q26" s="408" t="n"/>
+      <c r="R26" s="408" t="n"/>
+      <c r="S26" s="408" t="n"/>
+      <c r="T26" s="408" t="n"/>
+      <c r="U26" s="408" t="n"/>
+      <c r="V26" s="408" t="n"/>
+      <c r="W26" s="408" t="n"/>
+      <c r="X26" s="408" t="n"/>
+      <c r="Y26" s="408" t="n"/>
+      <c r="Z26" s="408" t="n"/>
+      <c r="AA26" s="408" t="n"/>
+      <c r="AB26" s="409" t="n"/>
+      <c r="AC26" s="361" t="inlineStr">
         <is>
           <t>Bagging / Seal Ref</t>
         </is>
       </c>
-      <c r="AD26" s="271" t="n"/>
-      <c r="AE26" s="271" t="n"/>
-      <c r="AF26" s="271" t="n"/>
-      <c r="AG26" s="271" t="n"/>
-      <c r="AH26" s="271" t="n"/>
-      <c r="AI26" s="271" t="n"/>
-      <c r="AJ26" s="271" t="n"/>
-      <c r="AK26" s="271" t="n"/>
-      <c r="AL26" s="272" t="n"/>
-      <c r="AM26" s="290" t="n"/>
-      <c r="AN26" s="320" t="n"/>
-      <c r="AO26" s="320" t="n"/>
-      <c r="AP26" s="320" t="n"/>
-      <c r="AQ26" s="320" t="n"/>
-      <c r="AR26" s="320" t="n"/>
-      <c r="AS26" s="320" t="n"/>
-      <c r="AT26" s="320" t="n"/>
-      <c r="AU26" s="320" t="n"/>
-      <c r="AV26" s="320" t="n"/>
-      <c r="AW26" s="320" t="n"/>
-      <c r="AX26" s="320" t="n"/>
-      <c r="AY26" s="320" t="n"/>
-      <c r="AZ26" s="320" t="n"/>
-      <c r="BA26" s="320" t="n"/>
-      <c r="BB26" s="320" t="n"/>
-      <c r="BC26" s="320" t="n"/>
-      <c r="BD26" s="322" t="n"/>
+      <c r="AD26" s="406" t="n"/>
+      <c r="AE26" s="406" t="n"/>
+      <c r="AF26" s="406" t="n"/>
+      <c r="AG26" s="406" t="n"/>
+      <c r="AH26" s="406" t="n"/>
+      <c r="AI26" s="406" t="n"/>
+      <c r="AJ26" s="406" t="n"/>
+      <c r="AK26" s="406" t="n"/>
+      <c r="AL26" s="407" t="n"/>
+      <c r="AM26" s="358" t="n"/>
+      <c r="AN26" s="408" t="n"/>
+      <c r="AO26" s="408" t="n"/>
+      <c r="AP26" s="408" t="n"/>
+      <c r="AQ26" s="408" t="n"/>
+      <c r="AR26" s="408" t="n"/>
+      <c r="AS26" s="408" t="n"/>
+      <c r="AT26" s="408" t="n"/>
+      <c r="AU26" s="408" t="n"/>
+      <c r="AV26" s="408" t="n"/>
+      <c r="AW26" s="408" t="n"/>
+      <c r="AX26" s="408" t="n"/>
+      <c r="AY26" s="408" t="n"/>
+      <c r="AZ26" s="408" t="n"/>
+      <c r="BA26" s="408" t="n"/>
+      <c r="BB26" s="408" t="n"/>
+      <c r="BC26" s="408" t="n"/>
+      <c r="BD26" s="409" t="n"/>
     </row>
     <row r="27" ht="20" customHeight="1">
-      <c r="A27" s="287" t="inlineStr">
+      <c r="A27" s="355" t="inlineStr">
         <is>
           <t>Final Release Decision</t>
         </is>
       </c>
-      <c r="B27" s="271" t="n"/>
-      <c r="C27" s="271" t="n"/>
-      <c r="D27" s="271" t="n"/>
-      <c r="E27" s="271" t="n"/>
-      <c r="F27" s="271" t="n"/>
-      <c r="G27" s="271" t="n"/>
-      <c r="H27" s="271" t="n"/>
-      <c r="I27" s="271" t="n"/>
-      <c r="J27" s="272" t="n"/>
-      <c r="K27" s="288" t="n"/>
-      <c r="L27" s="320" t="n"/>
-      <c r="M27" s="320" t="n"/>
-      <c r="N27" s="320" t="n"/>
-      <c r="O27" s="320" t="n"/>
-      <c r="P27" s="320" t="n"/>
-      <c r="Q27" s="320" t="n"/>
-      <c r="R27" s="320" t="n"/>
-      <c r="S27" s="320" t="n"/>
-      <c r="T27" s="320" t="n"/>
-      <c r="U27" s="320" t="n"/>
-      <c r="V27" s="320" t="n"/>
-      <c r="W27" s="320" t="n"/>
-      <c r="X27" s="320" t="n"/>
-      <c r="Y27" s="320" t="n"/>
-      <c r="Z27" s="320" t="n"/>
-      <c r="AA27" s="320" t="n"/>
-      <c r="AB27" s="321" t="n"/>
-      <c r="AC27" s="289" t="inlineStr">
+      <c r="B27" s="406" t="n"/>
+      <c r="C27" s="406" t="n"/>
+      <c r="D27" s="406" t="n"/>
+      <c r="E27" s="406" t="n"/>
+      <c r="F27" s="406" t="n"/>
+      <c r="G27" s="406" t="n"/>
+      <c r="H27" s="406" t="n"/>
+      <c r="I27" s="406" t="n"/>
+      <c r="J27" s="407" t="n"/>
+      <c r="K27" s="358" t="n"/>
+      <c r="L27" s="408" t="n"/>
+      <c r="M27" s="408" t="n"/>
+      <c r="N27" s="408" t="n"/>
+      <c r="O27" s="408" t="n"/>
+      <c r="P27" s="408" t="n"/>
+      <c r="Q27" s="408" t="n"/>
+      <c r="R27" s="408" t="n"/>
+      <c r="S27" s="408" t="n"/>
+      <c r="T27" s="408" t="n"/>
+      <c r="U27" s="408" t="n"/>
+      <c r="V27" s="408" t="n"/>
+      <c r="W27" s="408" t="n"/>
+      <c r="X27" s="408" t="n"/>
+      <c r="Y27" s="408" t="n"/>
+      <c r="Z27" s="408" t="n"/>
+      <c r="AA27" s="408" t="n"/>
+      <c r="AB27" s="409" t="n"/>
+      <c r="AC27" s="361" t="inlineStr">
         <is>
           <t>Approved by</t>
         </is>
       </c>
-      <c r="AD27" s="271" t="n"/>
-      <c r="AE27" s="271" t="n"/>
-      <c r="AF27" s="271" t="n"/>
-      <c r="AG27" s="271" t="n"/>
-      <c r="AH27" s="271" t="n"/>
-      <c r="AI27" s="271" t="n"/>
-      <c r="AJ27" s="271" t="n"/>
-      <c r="AK27" s="271" t="n"/>
-      <c r="AL27" s="272" t="n"/>
-      <c r="AM27" s="290" t="n"/>
-      <c r="AN27" s="320" t="n"/>
-      <c r="AO27" s="320" t="n"/>
-      <c r="AP27" s="320" t="n"/>
-      <c r="AQ27" s="320" t="n"/>
-      <c r="AR27" s="320" t="n"/>
-      <c r="AS27" s="320" t="n"/>
-      <c r="AT27" s="320" t="n"/>
-      <c r="AU27" s="320" t="n"/>
-      <c r="AV27" s="320" t="n"/>
-      <c r="AW27" s="320" t="n"/>
-      <c r="AX27" s="320" t="n"/>
-      <c r="AY27" s="320" t="n"/>
-      <c r="AZ27" s="320" t="n"/>
-      <c r="BA27" s="320" t="n"/>
-      <c r="BB27" s="320" t="n"/>
-      <c r="BC27" s="320" t="n"/>
-      <c r="BD27" s="322" t="n"/>
+      <c r="AD27" s="406" t="n"/>
+      <c r="AE27" s="406" t="n"/>
+      <c r="AF27" s="406" t="n"/>
+      <c r="AG27" s="406" t="n"/>
+      <c r="AH27" s="406" t="n"/>
+      <c r="AI27" s="406" t="n"/>
+      <c r="AJ27" s="406" t="n"/>
+      <c r="AK27" s="406" t="n"/>
+      <c r="AL27" s="407" t="n"/>
+      <c r="AM27" s="358" t="n"/>
+      <c r="AN27" s="408" t="n"/>
+      <c r="AO27" s="408" t="n"/>
+      <c r="AP27" s="408" t="n"/>
+      <c r="AQ27" s="408" t="n"/>
+      <c r="AR27" s="408" t="n"/>
+      <c r="AS27" s="408" t="n"/>
+      <c r="AT27" s="408" t="n"/>
+      <c r="AU27" s="408" t="n"/>
+      <c r="AV27" s="408" t="n"/>
+      <c r="AW27" s="408" t="n"/>
+      <c r="AX27" s="408" t="n"/>
+      <c r="AY27" s="408" t="n"/>
+      <c r="AZ27" s="408" t="n"/>
+      <c r="BA27" s="408" t="n"/>
+      <c r="BB27" s="408" t="n"/>
+      <c r="BC27" s="408" t="n"/>
+      <c r="BD27" s="409" t="n"/>
     </row>
     <row r="28" ht="4" customHeight="1">
-      <c r="A28" s="294" t="n"/>
-      <c r="D28" s="299" t="n"/>
-      <c r="H28" s="300" t="n"/>
-      <c r="AA28" s="301" t="n"/>
-      <c r="AR28" s="302" t="n"/>
-      <c r="AX28" s="302" t="n"/>
-      <c r="BB28" s="303" t="n"/>
+      <c r="A28" s="375" t="n"/>
+      <c r="B28" s="353" t="n"/>
+      <c r="C28" s="353" t="n"/>
+      <c r="D28" s="376" t="n"/>
+      <c r="E28" s="353" t="n"/>
+      <c r="F28" s="353" t="n"/>
+      <c r="G28" s="353" t="n"/>
+      <c r="H28" s="377" t="n"/>
+      <c r="I28" s="353" t="n"/>
+      <c r="J28" s="353" t="n"/>
+      <c r="K28" s="353" t="n"/>
+      <c r="L28" s="353" t="n"/>
+      <c r="M28" s="353" t="n"/>
+      <c r="N28" s="353" t="n"/>
+      <c r="O28" s="353" t="n"/>
+      <c r="P28" s="353" t="n"/>
+      <c r="Q28" s="353" t="n"/>
+      <c r="R28" s="353" t="n"/>
+      <c r="S28" s="353" t="n"/>
+      <c r="T28" s="353" t="n"/>
+      <c r="U28" s="353" t="n"/>
+      <c r="V28" s="353" t="n"/>
+      <c r="W28" s="353" t="n"/>
+      <c r="X28" s="353" t="n"/>
+      <c r="Y28" s="353" t="n"/>
+      <c r="Z28" s="353" t="n"/>
+      <c r="AA28" s="378" t="n"/>
+      <c r="AB28" s="353" t="n"/>
+      <c r="AC28" s="353" t="n"/>
+      <c r="AD28" s="353" t="n"/>
+      <c r="AE28" s="353" t="n"/>
+      <c r="AF28" s="353" t="n"/>
+      <c r="AG28" s="353" t="n"/>
+      <c r="AH28" s="353" t="n"/>
+      <c r="AI28" s="353" t="n"/>
+      <c r="AJ28" s="353" t="n"/>
+      <c r="AK28" s="353" t="n"/>
+      <c r="AL28" s="353" t="n"/>
+      <c r="AM28" s="353" t="n"/>
+      <c r="AN28" s="353" t="n"/>
+      <c r="AO28" s="353" t="n"/>
+      <c r="AP28" s="353" t="n"/>
+      <c r="AQ28" s="353" t="n"/>
+      <c r="AR28" s="379" t="n"/>
+      <c r="AS28" s="353" t="n"/>
+      <c r="AT28" s="353" t="n"/>
+      <c r="AU28" s="353" t="n"/>
+      <c r="AV28" s="353" t="n"/>
+      <c r="AW28" s="353" t="n"/>
+      <c r="AX28" s="379" t="n"/>
+      <c r="AY28" s="353" t="n"/>
+      <c r="AZ28" s="353" t="n"/>
+      <c r="BA28" s="353" t="n"/>
+      <c r="BB28" s="380" t="n"/>
+      <c r="BC28" s="353" t="n"/>
+      <c r="BD28" s="353" t="n"/>
     </row>
-    <row r="29" ht="17" customHeight="1">
-      <c r="A29" s="284" t="inlineStr">
+    <row r="29" ht="20" customHeight="1">
+      <c r="A29" s="354" t="inlineStr">
         <is>
           <t xml:space="preserve">  4. APPROVAL / SIGN-OFF</t>
         </is>
       </c>
-      <c r="B29" s="285" t="n"/>
-      <c r="C29" s="285" t="n"/>
-      <c r="D29" s="285" t="n"/>
-      <c r="E29" s="285" t="n"/>
-      <c r="F29" s="285" t="n"/>
-      <c r="G29" s="285" t="n"/>
-      <c r="H29" s="285" t="n"/>
-      <c r="I29" s="285" t="n"/>
-      <c r="J29" s="285" t="n"/>
-      <c r="K29" s="285" t="n"/>
-      <c r="L29" s="285" t="n"/>
-      <c r="M29" s="285" t="n"/>
-      <c r="N29" s="285" t="n"/>
-      <c r="O29" s="285" t="n"/>
-      <c r="P29" s="285" t="n"/>
-      <c r="Q29" s="285" t="n"/>
-      <c r="R29" s="285" t="n"/>
-      <c r="S29" s="285" t="n"/>
-      <c r="T29" s="285" t="n"/>
-      <c r="U29" s="285" t="n"/>
-      <c r="V29" s="285" t="n"/>
-      <c r="W29" s="285" t="n"/>
-      <c r="X29" s="285" t="n"/>
-      <c r="Y29" s="285" t="n"/>
-      <c r="Z29" s="285" t="n"/>
-      <c r="AA29" s="285" t="n"/>
-      <c r="AB29" s="285" t="n"/>
-      <c r="AC29" s="285" t="n"/>
-      <c r="AD29" s="285" t="n"/>
-      <c r="AE29" s="285" t="n"/>
-      <c r="AF29" s="285" t="n"/>
-      <c r="AG29" s="285" t="n"/>
-      <c r="AH29" s="285" t="n"/>
-      <c r="AI29" s="285" t="n"/>
-      <c r="AJ29" s="285" t="n"/>
-      <c r="AK29" s="285" t="n"/>
-      <c r="AL29" s="285" t="n"/>
-      <c r="AM29" s="285" t="n"/>
-      <c r="AN29" s="285" t="n"/>
-      <c r="AO29" s="285" t="n"/>
-      <c r="AP29" s="285" t="n"/>
-      <c r="AQ29" s="285" t="n"/>
-      <c r="AR29" s="285" t="n"/>
-      <c r="AS29" s="285" t="n"/>
-      <c r="AT29" s="285" t="n"/>
-      <c r="AU29" s="285" t="n"/>
-      <c r="AV29" s="285" t="n"/>
-      <c r="AW29" s="285" t="n"/>
-      <c r="AX29" s="285" t="n"/>
-      <c r="AY29" s="285" t="n"/>
-      <c r="AZ29" s="285" t="n"/>
-      <c r="BA29" s="285" t="n"/>
-      <c r="BB29" s="285" t="n"/>
-      <c r="BC29" s="285" t="n"/>
-      <c r="BD29" s="286" t="n"/>
+      <c r="B29" s="406" t="n"/>
+      <c r="C29" s="406" t="n"/>
+      <c r="D29" s="406" t="n"/>
+      <c r="E29" s="406" t="n"/>
+      <c r="F29" s="406" t="n"/>
+      <c r="G29" s="406" t="n"/>
+      <c r="H29" s="406" t="n"/>
+      <c r="I29" s="406" t="n"/>
+      <c r="J29" s="406" t="n"/>
+      <c r="K29" s="406" t="n"/>
+      <c r="L29" s="406" t="n"/>
+      <c r="M29" s="406" t="n"/>
+      <c r="N29" s="406" t="n"/>
+      <c r="O29" s="406" t="n"/>
+      <c r="P29" s="406" t="n"/>
+      <c r="Q29" s="406" t="n"/>
+      <c r="R29" s="406" t="n"/>
+      <c r="S29" s="406" t="n"/>
+      <c r="T29" s="406" t="n"/>
+      <c r="U29" s="406" t="n"/>
+      <c r="V29" s="406" t="n"/>
+      <c r="W29" s="406" t="n"/>
+      <c r="X29" s="406" t="n"/>
+      <c r="Y29" s="406" t="n"/>
+      <c r="Z29" s="406" t="n"/>
+      <c r="AA29" s="406" t="n"/>
+      <c r="AB29" s="406" t="n"/>
+      <c r="AC29" s="406" t="n"/>
+      <c r="AD29" s="406" t="n"/>
+      <c r="AE29" s="406" t="n"/>
+      <c r="AF29" s="406" t="n"/>
+      <c r="AG29" s="406" t="n"/>
+      <c r="AH29" s="406" t="n"/>
+      <c r="AI29" s="406" t="n"/>
+      <c r="AJ29" s="406" t="n"/>
+      <c r="AK29" s="406" t="n"/>
+      <c r="AL29" s="406" t="n"/>
+      <c r="AM29" s="406" t="n"/>
+      <c r="AN29" s="406" t="n"/>
+      <c r="AO29" s="406" t="n"/>
+      <c r="AP29" s="406" t="n"/>
+      <c r="AQ29" s="406" t="n"/>
+      <c r="AR29" s="406" t="n"/>
+      <c r="AS29" s="406" t="n"/>
+      <c r="AT29" s="406" t="n"/>
+      <c r="AU29" s="406" t="n"/>
+      <c r="AV29" s="406" t="n"/>
+      <c r="AW29" s="406" t="n"/>
+      <c r="AX29" s="406" t="n"/>
+      <c r="AY29" s="406" t="n"/>
+      <c r="AZ29" s="406" t="n"/>
+      <c r="BA29" s="406" t="n"/>
+      <c r="BB29" s="406" t="n"/>
+      <c r="BC29" s="406" t="n"/>
+      <c r="BD29" s="407" t="n"/>
     </row>
-    <row r="30" ht="17" customHeight="1">
-      <c r="A30" s="326" t="inlineStr">
+    <row r="30" ht="20" customHeight="1">
+      <c r="A30" s="381" t="inlineStr">
         <is>
           <t>Prepared by</t>
         </is>
       </c>
-      <c r="B30" s="285" t="n"/>
-      <c r="C30" s="285" t="n"/>
-      <c r="D30" s="285" t="n"/>
-      <c r="E30" s="285" t="n"/>
-      <c r="F30" s="285" t="n"/>
-      <c r="G30" s="285" t="n"/>
-      <c r="H30" s="285" t="n"/>
-      <c r="I30" s="285" t="n"/>
-      <c r="J30" s="285" t="n"/>
-      <c r="K30" s="285" t="n"/>
-      <c r="L30" s="285" t="n"/>
-      <c r="M30" s="285" t="n"/>
-      <c r="N30" s="285" t="n"/>
-      <c r="O30" s="285" t="n"/>
-      <c r="P30" s="285" t="n"/>
-      <c r="Q30" s="285" t="n"/>
-      <c r="R30" s="327" t="n"/>
-      <c r="S30" s="51" t="inlineStr">
+      <c r="B30" s="401" t="n"/>
+      <c r="C30" s="401" t="n"/>
+      <c r="D30" s="401" t="n"/>
+      <c r="E30" s="401" t="n"/>
+      <c r="F30" s="401" t="n"/>
+      <c r="G30" s="401" t="n"/>
+      <c r="H30" s="401" t="n"/>
+      <c r="I30" s="401" t="n"/>
+      <c r="J30" s="401" t="n"/>
+      <c r="K30" s="401" t="n"/>
+      <c r="L30" s="401" t="n"/>
+      <c r="M30" s="401" t="n"/>
+      <c r="N30" s="401" t="n"/>
+      <c r="O30" s="401" t="n"/>
+      <c r="P30" s="401" t="n"/>
+      <c r="Q30" s="401" t="n"/>
+      <c r="R30" s="402" t="n"/>
+      <c r="S30" s="382" t="inlineStr">
         <is>
           <t>Reviewed by</t>
         </is>
       </c>
-      <c r="T30" s="285" t="n"/>
-      <c r="U30" s="285" t="n"/>
-      <c r="V30" s="285" t="n"/>
-      <c r="W30" s="285" t="n"/>
-      <c r="X30" s="285" t="n"/>
-      <c r="Y30" s="285" t="n"/>
-      <c r="Z30" s="285" t="n"/>
-      <c r="AA30" s="285" t="n"/>
-      <c r="AB30" s="285" t="n"/>
-      <c r="AC30" s="285" t="n"/>
-      <c r="AD30" s="285" t="n"/>
-      <c r="AE30" s="285" t="n"/>
-      <c r="AF30" s="285" t="n"/>
-      <c r="AG30" s="285" t="n"/>
-      <c r="AH30" s="285" t="n"/>
-      <c r="AI30" s="285" t="n"/>
-      <c r="AJ30" s="285" t="n"/>
-      <c r="AK30" s="304" t="inlineStr">
+      <c r="T30" s="401" t="n"/>
+      <c r="U30" s="401" t="n"/>
+      <c r="V30" s="401" t="n"/>
+      <c r="W30" s="401" t="n"/>
+      <c r="X30" s="401" t="n"/>
+      <c r="Y30" s="401" t="n"/>
+      <c r="Z30" s="401" t="n"/>
+      <c r="AA30" s="401" t="n"/>
+      <c r="AB30" s="401" t="n"/>
+      <c r="AC30" s="401" t="n"/>
+      <c r="AD30" s="401" t="n"/>
+      <c r="AE30" s="401" t="n"/>
+      <c r="AF30" s="401" t="n"/>
+      <c r="AG30" s="401" t="n"/>
+      <c r="AH30" s="401" t="n"/>
+      <c r="AI30" s="401" t="n"/>
+      <c r="AJ30" s="401" t="n"/>
+      <c r="AK30" s="383" t="inlineStr">
         <is>
           <t>Approved by</t>
         </is>
       </c>
-      <c r="AL30" s="285" t="n"/>
-      <c r="AM30" s="285" t="n"/>
-      <c r="AN30" s="285" t="n"/>
-      <c r="AO30" s="285" t="n"/>
-      <c r="AP30" s="285" t="n"/>
-      <c r="AQ30" s="285" t="n"/>
-      <c r="AR30" s="285" t="n"/>
-      <c r="AS30" s="285" t="n"/>
-      <c r="AT30" s="285" t="n"/>
-      <c r="AU30" s="285" t="n"/>
-      <c r="AV30" s="285" t="n"/>
-      <c r="AW30" s="285" t="n"/>
-      <c r="AX30" s="285" t="n"/>
-      <c r="AY30" s="285" t="n"/>
-      <c r="AZ30" s="285" t="n"/>
-      <c r="BA30" s="285" t="n"/>
-      <c r="BB30" s="285" t="n"/>
-      <c r="BC30" s="285" t="n"/>
-      <c r="BD30" s="286" t="n"/>
+      <c r="AL30" s="401" t="n"/>
+      <c r="AM30" s="401" t="n"/>
+      <c r="AN30" s="401" t="n"/>
+      <c r="AO30" s="401" t="n"/>
+      <c r="AP30" s="401" t="n"/>
+      <c r="AQ30" s="401" t="n"/>
+      <c r="AR30" s="401" t="n"/>
+      <c r="AS30" s="401" t="n"/>
+      <c r="AT30" s="401" t="n"/>
+      <c r="AU30" s="401" t="n"/>
+      <c r="AV30" s="401" t="n"/>
+      <c r="AW30" s="401" t="n"/>
+      <c r="AX30" s="401" t="n"/>
+      <c r="AY30" s="401" t="n"/>
+      <c r="AZ30" s="401" t="n"/>
+      <c r="BA30" s="401" t="n"/>
+      <c r="BB30" s="401" t="n"/>
+      <c r="BC30" s="401" t="n"/>
+      <c r="BD30" s="402" t="n"/>
     </row>
-    <row r="31" ht="26" customHeight="1">
-      <c r="A31" s="305" t="inlineStr">
+    <row r="31" ht="20" customHeight="1">
+      <c r="A31" s="384" t="inlineStr">
         <is>
           <t>Name / Signature / Date</t>
         </is>
       </c>
-      <c r="B31" s="328" t="n"/>
-      <c r="C31" s="328" t="n"/>
-      <c r="D31" s="328" t="n"/>
-      <c r="E31" s="328" t="n"/>
-      <c r="F31" s="328" t="n"/>
-      <c r="G31" s="328" t="n"/>
-      <c r="H31" s="328" t="n"/>
-      <c r="I31" s="328" t="n"/>
-      <c r="J31" s="328" t="n"/>
-      <c r="K31" s="328" t="n"/>
-      <c r="L31" s="328" t="n"/>
-      <c r="M31" s="328" t="n"/>
-      <c r="N31" s="328" t="n"/>
-      <c r="O31" s="328" t="n"/>
-      <c r="P31" s="328" t="n"/>
-      <c r="Q31" s="328" t="n"/>
-      <c r="R31" s="329" t="n"/>
-      <c r="S31" s="305" t="inlineStr">
+      <c r="B31" s="416" t="n"/>
+      <c r="C31" s="416" t="n"/>
+      <c r="D31" s="416" t="n"/>
+      <c r="E31" s="416" t="n"/>
+      <c r="F31" s="416" t="n"/>
+      <c r="G31" s="416" t="n"/>
+      <c r="H31" s="416" t="n"/>
+      <c r="I31" s="416" t="n"/>
+      <c r="J31" s="416" t="n"/>
+      <c r="K31" s="416" t="n"/>
+      <c r="L31" s="416" t="n"/>
+      <c r="M31" s="416" t="n"/>
+      <c r="N31" s="416" t="n"/>
+      <c r="O31" s="416" t="n"/>
+      <c r="P31" s="416" t="n"/>
+      <c r="Q31" s="416" t="n"/>
+      <c r="R31" s="417" t="n"/>
+      <c r="S31" s="384" t="inlineStr">
         <is>
           <t>Name / Signature / Date</t>
         </is>
       </c>
-      <c r="T31" s="328" t="n"/>
-      <c r="U31" s="328" t="n"/>
-      <c r="V31" s="328" t="n"/>
-      <c r="W31" s="328" t="n"/>
-      <c r="X31" s="328" t="n"/>
-      <c r="Y31" s="328" t="n"/>
-      <c r="Z31" s="328" t="n"/>
-      <c r="AA31" s="328" t="n"/>
-      <c r="AB31" s="328" t="n"/>
-      <c r="AC31" s="328" t="n"/>
-      <c r="AD31" s="328" t="n"/>
-      <c r="AE31" s="328" t="n"/>
-      <c r="AF31" s="328" t="n"/>
-      <c r="AG31" s="328" t="n"/>
-      <c r="AH31" s="328" t="n"/>
-      <c r="AI31" s="328" t="n"/>
-      <c r="AJ31" s="329" t="n"/>
-      <c r="AK31" s="305" t="inlineStr">
+      <c r="T31" s="416" t="n"/>
+      <c r="U31" s="416" t="n"/>
+      <c r="V31" s="416" t="n"/>
+      <c r="W31" s="416" t="n"/>
+      <c r="X31" s="416" t="n"/>
+      <c r="Y31" s="416" t="n"/>
+      <c r="Z31" s="416" t="n"/>
+      <c r="AA31" s="416" t="n"/>
+      <c r="AB31" s="416" t="n"/>
+      <c r="AC31" s="416" t="n"/>
+      <c r="AD31" s="416" t="n"/>
+      <c r="AE31" s="416" t="n"/>
+      <c r="AF31" s="416" t="n"/>
+      <c r="AG31" s="416" t="n"/>
+      <c r="AH31" s="416" t="n"/>
+      <c r="AI31" s="416" t="n"/>
+      <c r="AJ31" s="417" t="n"/>
+      <c r="AK31" s="384" t="inlineStr">
         <is>
           <t>Name / Signature / Date</t>
         </is>
       </c>
-      <c r="AL31" s="328" t="n"/>
-      <c r="AM31" s="328" t="n"/>
-      <c r="AN31" s="328" t="n"/>
-      <c r="AO31" s="328" t="n"/>
-      <c r="AP31" s="328" t="n"/>
-      <c r="AQ31" s="328" t="n"/>
-      <c r="AR31" s="328" t="n"/>
-      <c r="AS31" s="328" t="n"/>
-      <c r="AT31" s="328" t="n"/>
-      <c r="AU31" s="328" t="n"/>
-      <c r="AV31" s="328" t="n"/>
-      <c r="AW31" s="328" t="n"/>
-      <c r="AX31" s="328" t="n"/>
-      <c r="AY31" s="328" t="n"/>
-      <c r="AZ31" s="328" t="n"/>
-      <c r="BA31" s="328" t="n"/>
-      <c r="BB31" s="328" t="n"/>
-      <c r="BC31" s="328" t="n"/>
-      <c r="BD31" s="329" t="n"/>
+      <c r="AL31" s="416" t="n"/>
+      <c r="AM31" s="416" t="n"/>
+      <c r="AN31" s="416" t="n"/>
+      <c r="AO31" s="416" t="n"/>
+      <c r="AP31" s="416" t="n"/>
+      <c r="AQ31" s="416" t="n"/>
+      <c r="AR31" s="416" t="n"/>
+      <c r="AS31" s="416" t="n"/>
+      <c r="AT31" s="416" t="n"/>
+      <c r="AU31" s="416" t="n"/>
+      <c r="AV31" s="416" t="n"/>
+      <c r="AW31" s="416" t="n"/>
+      <c r="AX31" s="416" t="n"/>
+      <c r="AY31" s="416" t="n"/>
+      <c r="AZ31" s="416" t="n"/>
+      <c r="BA31" s="416" t="n"/>
+      <c r="BB31" s="416" t="n"/>
+      <c r="BC31" s="416" t="n"/>
+      <c r="BD31" s="417" t="n"/>
     </row>
-    <row r="32" ht="26" customHeight="1">
-      <c r="A32" s="330" t="n"/>
-      <c r="B32" s="331" t="n"/>
-      <c r="C32" s="331" t="n"/>
-      <c r="D32" s="331" t="n"/>
-      <c r="E32" s="331" t="n"/>
-      <c r="F32" s="331" t="n"/>
-      <c r="G32" s="331" t="n"/>
-      <c r="H32" s="331" t="n"/>
-      <c r="I32" s="331" t="n"/>
-      <c r="J32" s="331" t="n"/>
-      <c r="K32" s="331" t="n"/>
-      <c r="L32" s="331" t="n"/>
-      <c r="M32" s="331" t="n"/>
-      <c r="N32" s="331" t="n"/>
-      <c r="O32" s="331" t="n"/>
-      <c r="P32" s="331" t="n"/>
-      <c r="Q32" s="331" t="n"/>
-      <c r="R32" s="332" t="n"/>
-      <c r="S32" s="330" t="n"/>
-      <c r="T32" s="331" t="n"/>
-      <c r="U32" s="331" t="n"/>
-      <c r="V32" s="331" t="n"/>
-      <c r="W32" s="331" t="n"/>
-      <c r="X32" s="331" t="n"/>
-      <c r="Y32" s="331" t="n"/>
-      <c r="Z32" s="331" t="n"/>
-      <c r="AA32" s="331" t="n"/>
-      <c r="AB32" s="331" t="n"/>
-      <c r="AC32" s="331" t="n"/>
-      <c r="AD32" s="331" t="n"/>
-      <c r="AE32" s="331" t="n"/>
-      <c r="AF32" s="331" t="n"/>
-      <c r="AG32" s="331" t="n"/>
-      <c r="AH32" s="331" t="n"/>
-      <c r="AI32" s="331" t="n"/>
-      <c r="AJ32" s="332" t="n"/>
-      <c r="AK32" s="330" t="n"/>
-      <c r="AL32" s="331" t="n"/>
-      <c r="AM32" s="331" t="n"/>
-      <c r="AN32" s="331" t="n"/>
-      <c r="AO32" s="331" t="n"/>
-      <c r="AP32" s="331" t="n"/>
-      <c r="AQ32" s="331" t="n"/>
-      <c r="AR32" s="331" t="n"/>
-      <c r="AS32" s="331" t="n"/>
-      <c r="AT32" s="331" t="n"/>
-      <c r="AU32" s="331" t="n"/>
-      <c r="AV32" s="331" t="n"/>
-      <c r="AW32" s="331" t="n"/>
-      <c r="AX32" s="331" t="n"/>
-      <c r="AY32" s="331" t="n"/>
-      <c r="AZ32" s="331" t="n"/>
-      <c r="BA32" s="331" t="n"/>
-      <c r="BB32" s="331" t="n"/>
-      <c r="BC32" s="331" t="n"/>
-      <c r="BD32" s="332" t="n"/>
+    <row r="32" ht="20" customHeight="1">
+      <c r="A32" s="418" t="n"/>
+      <c r="B32" s="388" t="n"/>
+      <c r="C32" s="388" t="n"/>
+      <c r="D32" s="388" t="n"/>
+      <c r="E32" s="388" t="n"/>
+      <c r="F32" s="388" t="n"/>
+      <c r="G32" s="388" t="n"/>
+      <c r="H32" s="388" t="n"/>
+      <c r="I32" s="388" t="n"/>
+      <c r="J32" s="388" t="n"/>
+      <c r="K32" s="388" t="n"/>
+      <c r="L32" s="388" t="n"/>
+      <c r="M32" s="388" t="n"/>
+      <c r="N32" s="388" t="n"/>
+      <c r="O32" s="388" t="n"/>
+      <c r="P32" s="388" t="n"/>
+      <c r="Q32" s="388" t="n"/>
+      <c r="R32" s="419" t="n"/>
+      <c r="S32" s="418" t="n"/>
+      <c r="T32" s="388" t="n"/>
+      <c r="U32" s="388" t="n"/>
+      <c r="V32" s="388" t="n"/>
+      <c r="W32" s="388" t="n"/>
+      <c r="X32" s="388" t="n"/>
+      <c r="Y32" s="388" t="n"/>
+      <c r="Z32" s="388" t="n"/>
+      <c r="AA32" s="388" t="n"/>
+      <c r="AB32" s="388" t="n"/>
+      <c r="AC32" s="388" t="n"/>
+      <c r="AD32" s="388" t="n"/>
+      <c r="AE32" s="388" t="n"/>
+      <c r="AF32" s="388" t="n"/>
+      <c r="AG32" s="388" t="n"/>
+      <c r="AH32" s="388" t="n"/>
+      <c r="AI32" s="388" t="n"/>
+      <c r="AJ32" s="419" t="n"/>
+      <c r="AK32" s="418" t="n"/>
+      <c r="AL32" s="388" t="n"/>
+      <c r="AM32" s="388" t="n"/>
+      <c r="AN32" s="388" t="n"/>
+      <c r="AO32" s="388" t="n"/>
+      <c r="AP32" s="388" t="n"/>
+      <c r="AQ32" s="388" t="n"/>
+      <c r="AR32" s="388" t="n"/>
+      <c r="AS32" s="388" t="n"/>
+      <c r="AT32" s="388" t="n"/>
+      <c r="AU32" s="388" t="n"/>
+      <c r="AV32" s="388" t="n"/>
+      <c r="AW32" s="388" t="n"/>
+      <c r="AX32" s="388" t="n"/>
+      <c r="AY32" s="388" t="n"/>
+      <c r="AZ32" s="388" t="n"/>
+      <c r="BA32" s="388" t="n"/>
+      <c r="BB32" s="388" t="n"/>
+      <c r="BC32" s="388" t="n"/>
+      <c r="BD32" s="419" t="n"/>
     </row>
-    <row r="33" ht="26" customHeight="1">
-      <c r="A33" s="333" t="n"/>
-      <c r="B33" s="334" t="n"/>
-      <c r="C33" s="334" t="n"/>
-      <c r="D33" s="334" t="n"/>
-      <c r="E33" s="334" t="n"/>
-      <c r="F33" s="334" t="n"/>
-      <c r="G33" s="334" t="n"/>
-      <c r="H33" s="334" t="n"/>
-      <c r="I33" s="334" t="n"/>
-      <c r="J33" s="334" t="n"/>
-      <c r="K33" s="334" t="n"/>
-      <c r="L33" s="334" t="n"/>
-      <c r="M33" s="334" t="n"/>
-      <c r="N33" s="334" t="n"/>
-      <c r="O33" s="334" t="n"/>
-      <c r="P33" s="334" t="n"/>
-      <c r="Q33" s="334" t="n"/>
-      <c r="R33" s="335" t="n"/>
-      <c r="S33" s="333" t="n"/>
-      <c r="T33" s="334" t="n"/>
-      <c r="U33" s="334" t="n"/>
-      <c r="V33" s="334" t="n"/>
-      <c r="W33" s="334" t="n"/>
-      <c r="X33" s="334" t="n"/>
-      <c r="Y33" s="334" t="n"/>
-      <c r="Z33" s="334" t="n"/>
-      <c r="AA33" s="334" t="n"/>
-      <c r="AB33" s="334" t="n"/>
-      <c r="AC33" s="334" t="n"/>
-      <c r="AD33" s="334" t="n"/>
-      <c r="AE33" s="334" t="n"/>
-      <c r="AF33" s="334" t="n"/>
-      <c r="AG33" s="334" t="n"/>
-      <c r="AH33" s="334" t="n"/>
-      <c r="AI33" s="334" t="n"/>
-      <c r="AJ33" s="335" t="n"/>
-      <c r="AK33" s="333" t="n"/>
-      <c r="AL33" s="334" t="n"/>
-      <c r="AM33" s="334" t="n"/>
-      <c r="AN33" s="334" t="n"/>
-      <c r="AO33" s="334" t="n"/>
-      <c r="AP33" s="334" t="n"/>
-      <c r="AQ33" s="334" t="n"/>
-      <c r="AR33" s="334" t="n"/>
-      <c r="AS33" s="334" t="n"/>
-      <c r="AT33" s="334" t="n"/>
-      <c r="AU33" s="334" t="n"/>
-      <c r="AV33" s="334" t="n"/>
-      <c r="AW33" s="334" t="n"/>
-      <c r="AX33" s="334" t="n"/>
-      <c r="AY33" s="334" t="n"/>
-      <c r="AZ33" s="334" t="n"/>
-      <c r="BA33" s="334" t="n"/>
-      <c r="BB33" s="334" t="n"/>
-      <c r="BC33" s="334" t="n"/>
-      <c r="BD33" s="335" t="n"/>
+    <row r="33" ht="20" customHeight="1">
+      <c r="A33" s="420" t="n"/>
+      <c r="B33" s="414" t="n"/>
+      <c r="C33" s="414" t="n"/>
+      <c r="D33" s="414" t="n"/>
+      <c r="E33" s="414" t="n"/>
+      <c r="F33" s="414" t="n"/>
+      <c r="G33" s="414" t="n"/>
+      <c r="H33" s="414" t="n"/>
+      <c r="I33" s="414" t="n"/>
+      <c r="J33" s="414" t="n"/>
+      <c r="K33" s="414" t="n"/>
+      <c r="L33" s="414" t="n"/>
+      <c r="M33" s="414" t="n"/>
+      <c r="N33" s="414" t="n"/>
+      <c r="O33" s="414" t="n"/>
+      <c r="P33" s="414" t="n"/>
+      <c r="Q33" s="414" t="n"/>
+      <c r="R33" s="415" t="n"/>
+      <c r="S33" s="420" t="n"/>
+      <c r="T33" s="414" t="n"/>
+      <c r="U33" s="414" t="n"/>
+      <c r="V33" s="414" t="n"/>
+      <c r="W33" s="414" t="n"/>
+      <c r="X33" s="414" t="n"/>
+      <c r="Y33" s="414" t="n"/>
+      <c r="Z33" s="414" t="n"/>
+      <c r="AA33" s="414" t="n"/>
+      <c r="AB33" s="414" t="n"/>
+      <c r="AC33" s="414" t="n"/>
+      <c r="AD33" s="414" t="n"/>
+      <c r="AE33" s="414" t="n"/>
+      <c r="AF33" s="414" t="n"/>
+      <c r="AG33" s="414" t="n"/>
+      <c r="AH33" s="414" t="n"/>
+      <c r="AI33" s="414" t="n"/>
+      <c r="AJ33" s="415" t="n"/>
+      <c r="AK33" s="420" t="n"/>
+      <c r="AL33" s="414" t="n"/>
+      <c r="AM33" s="414" t="n"/>
+      <c r="AN33" s="414" t="n"/>
+      <c r="AO33" s="414" t="n"/>
+      <c r="AP33" s="414" t="n"/>
+      <c r="AQ33" s="414" t="n"/>
+      <c r="AR33" s="414" t="n"/>
+      <c r="AS33" s="414" t="n"/>
+      <c r="AT33" s="414" t="n"/>
+      <c r="AU33" s="414" t="n"/>
+      <c r="AV33" s="414" t="n"/>
+      <c r="AW33" s="414" t="n"/>
+      <c r="AX33" s="414" t="n"/>
+      <c r="AY33" s="414" t="n"/>
+      <c r="AZ33" s="414" t="n"/>
+      <c r="BA33" s="414" t="n"/>
+      <c r="BB33" s="414" t="n"/>
+      <c r="BC33" s="414" t="n"/>
+      <c r="BD33" s="415" t="n"/>
     </row>
     <row r="34" ht="4" customHeight="1">
-      <c r="A34" s="291" t="n"/>
-      <c r="D34" s="292" t="n"/>
-      <c r="R34" s="292" t="n"/>
-      <c r="AI34" s="292" t="n"/>
-      <c r="AP34" s="292" t="n"/>
-      <c r="AW34" s="292" t="n"/>
-      <c r="BA34" s="293" t="n"/>
+      <c r="A34" s="391" t="n"/>
+      <c r="B34" s="353" t="n"/>
+      <c r="C34" s="353" t="n"/>
+      <c r="D34" s="391" t="n"/>
+      <c r="E34" s="353" t="n"/>
+      <c r="F34" s="353" t="n"/>
+      <c r="G34" s="353" t="n"/>
+      <c r="H34" s="353" t="n"/>
+      <c r="I34" s="353" t="n"/>
+      <c r="J34" s="353" t="n"/>
+      <c r="K34" s="353" t="n"/>
+      <c r="L34" s="353" t="n"/>
+      <c r="M34" s="353" t="n"/>
+      <c r="N34" s="353" t="n"/>
+      <c r="O34" s="353" t="n"/>
+      <c r="P34" s="353" t="n"/>
+      <c r="Q34" s="353" t="n"/>
+      <c r="R34" s="391" t="n"/>
+      <c r="S34" s="353" t="n"/>
+      <c r="T34" s="353" t="n"/>
+      <c r="U34" s="353" t="n"/>
+      <c r="V34" s="353" t="n"/>
+      <c r="W34" s="353" t="n"/>
+      <c r="X34" s="353" t="n"/>
+      <c r="Y34" s="353" t="n"/>
+      <c r="Z34" s="353" t="n"/>
+      <c r="AA34" s="353" t="n"/>
+      <c r="AB34" s="353" t="n"/>
+      <c r="AC34" s="353" t="n"/>
+      <c r="AD34" s="353" t="n"/>
+      <c r="AE34" s="353" t="n"/>
+      <c r="AF34" s="353" t="n"/>
+      <c r="AG34" s="353" t="n"/>
+      <c r="AH34" s="353" t="n"/>
+      <c r="AI34" s="391" t="n"/>
+      <c r="AJ34" s="353" t="n"/>
+      <c r="AK34" s="353" t="n"/>
+      <c r="AL34" s="353" t="n"/>
+      <c r="AM34" s="353" t="n"/>
+      <c r="AN34" s="353" t="n"/>
+      <c r="AO34" s="353" t="n"/>
+      <c r="AP34" s="391" t="n"/>
+      <c r="AQ34" s="353" t="n"/>
+      <c r="AR34" s="353" t="n"/>
+      <c r="AS34" s="353" t="n"/>
+      <c r="AT34" s="353" t="n"/>
+      <c r="AU34" s="353" t="n"/>
+      <c r="AV34" s="353" t="n"/>
+      <c r="AW34" s="391" t="n"/>
+      <c r="AX34" s="353" t="n"/>
+      <c r="AY34" s="353" t="n"/>
+      <c r="AZ34" s="353" t="n"/>
+      <c r="BA34" s="391" t="n"/>
+      <c r="BB34" s="353" t="n"/>
+      <c r="BC34" s="353" t="n"/>
+      <c r="BD34" s="353" t="n"/>
     </row>
-    <row r="35" ht="24" customHeight="1">
-      <c r="A35" s="336" t="inlineStr">
+    <row r="35" ht="20" customHeight="1">
+      <c r="A35" s="392" t="inlineStr">
         <is>
           <t>NOTICE: Confirm cleanliness, approved materials, line clearance, bagging sequence and seal integrity before release. This is a controlled gap form.</t>
         </is>
       </c>
-      <c r="B35" s="276" t="n"/>
-      <c r="C35" s="276" t="n"/>
-      <c r="D35" s="276" t="n"/>
-      <c r="E35" s="276" t="n"/>
-      <c r="F35" s="276" t="n"/>
-      <c r="G35" s="276" t="n"/>
-      <c r="H35" s="276" t="n"/>
-      <c r="I35" s="276" t="n"/>
-      <c r="J35" s="276" t="n"/>
-      <c r="K35" s="276" t="n"/>
-      <c r="L35" s="276" t="n"/>
-      <c r="M35" s="276" t="n"/>
-      <c r="N35" s="276" t="n"/>
-      <c r="O35" s="276" t="n"/>
-      <c r="P35" s="276" t="n"/>
-      <c r="Q35" s="276" t="n"/>
-      <c r="R35" s="276" t="n"/>
-      <c r="S35" s="276" t="n"/>
-      <c r="T35" s="276" t="n"/>
-      <c r="U35" s="276" t="n"/>
-      <c r="V35" s="276" t="n"/>
-      <c r="W35" s="276" t="n"/>
-      <c r="X35" s="276" t="n"/>
-      <c r="Y35" s="276" t="n"/>
-      <c r="Z35" s="276" t="n"/>
-      <c r="AA35" s="276" t="n"/>
-      <c r="AB35" s="276" t="n"/>
-      <c r="AC35" s="276" t="n"/>
-      <c r="AD35" s="276" t="n"/>
-      <c r="AE35" s="276" t="n"/>
-      <c r="AF35" s="276" t="n"/>
-      <c r="AG35" s="276" t="n"/>
-      <c r="AH35" s="276" t="n"/>
-      <c r="AI35" s="276" t="n"/>
-      <c r="AJ35" s="276" t="n"/>
-      <c r="AK35" s="276" t="n"/>
-      <c r="AL35" s="276" t="n"/>
-      <c r="AM35" s="276" t="n"/>
-      <c r="AN35" s="276" t="n"/>
-      <c r="AO35" s="276" t="n"/>
-      <c r="AP35" s="276" t="n"/>
-      <c r="AQ35" s="276" t="n"/>
-      <c r="AR35" s="276" t="n"/>
-      <c r="AS35" s="276" t="n"/>
-      <c r="AT35" s="276" t="n"/>
-      <c r="AU35" s="276" t="n"/>
-      <c r="AV35" s="276" t="n"/>
-      <c r="AW35" s="276" t="n"/>
-      <c r="AX35" s="276" t="n"/>
-      <c r="AY35" s="276" t="n"/>
-      <c r="AZ35" s="276" t="n"/>
-      <c r="BA35" s="276" t="n"/>
-      <c r="BB35" s="276" t="n"/>
-      <c r="BC35" s="276" t="n"/>
-      <c r="BD35" s="277" t="n"/>
+      <c r="B35" s="412" t="n"/>
+      <c r="C35" s="412" t="n"/>
+      <c r="D35" s="412" t="n"/>
+      <c r="E35" s="412" t="n"/>
+      <c r="F35" s="412" t="n"/>
+      <c r="G35" s="412" t="n"/>
+      <c r="H35" s="412" t="n"/>
+      <c r="I35" s="412" t="n"/>
+      <c r="J35" s="412" t="n"/>
+      <c r="K35" s="412" t="n"/>
+      <c r="L35" s="412" t="n"/>
+      <c r="M35" s="412" t="n"/>
+      <c r="N35" s="412" t="n"/>
+      <c r="O35" s="412" t="n"/>
+      <c r="P35" s="412" t="n"/>
+      <c r="Q35" s="412" t="n"/>
+      <c r="R35" s="412" t="n"/>
+      <c r="S35" s="412" t="n"/>
+      <c r="T35" s="412" t="n"/>
+      <c r="U35" s="412" t="n"/>
+      <c r="V35" s="412" t="n"/>
+      <c r="W35" s="412" t="n"/>
+      <c r="X35" s="412" t="n"/>
+      <c r="Y35" s="412" t="n"/>
+      <c r="Z35" s="412" t="n"/>
+      <c r="AA35" s="412" t="n"/>
+      <c r="AB35" s="412" t="n"/>
+      <c r="AC35" s="412" t="n"/>
+      <c r="AD35" s="412" t="n"/>
+      <c r="AE35" s="412" t="n"/>
+      <c r="AF35" s="412" t="n"/>
+      <c r="AG35" s="412" t="n"/>
+      <c r="AH35" s="412" t="n"/>
+      <c r="AI35" s="412" t="n"/>
+      <c r="AJ35" s="412" t="n"/>
+      <c r="AK35" s="412" t="n"/>
+      <c r="AL35" s="412" t="n"/>
+      <c r="AM35" s="412" t="n"/>
+      <c r="AN35" s="412" t="n"/>
+      <c r="AO35" s="412" t="n"/>
+      <c r="AP35" s="412" t="n"/>
+      <c r="AQ35" s="412" t="n"/>
+      <c r="AR35" s="412" t="n"/>
+      <c r="AS35" s="412" t="n"/>
+      <c r="AT35" s="412" t="n"/>
+      <c r="AU35" s="412" t="n"/>
+      <c r="AV35" s="412" t="n"/>
+      <c r="AW35" s="412" t="n"/>
+      <c r="AX35" s="412" t="n"/>
+      <c r="AY35" s="412" t="n"/>
+      <c r="AZ35" s="412" t="n"/>
+      <c r="BA35" s="412" t="n"/>
+      <c r="BB35" s="412" t="n"/>
+      <c r="BC35" s="412" t="n"/>
+      <c r="BD35" s="413" t="n"/>
     </row>
     <row r="36" ht="20" customHeight="1"/>
     <row r="37" ht="20" customHeight="1"/>
@@ -6926,7 +7619,6 @@
     <firstHeader/>
     <firstFooter/>
   </headerFooter>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -7193,31 +7885,96 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:AN14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="24" customWidth="1" min="8" max="8"/>
+    <col width="2.33" customWidth="1" min="1" max="1"/>
+    <col width="2.33" customWidth="1" min="2" max="2"/>
+    <col width="2.33" customWidth="1" min="3" max="3"/>
+    <col width="2.33" customWidth="1" min="4" max="4"/>
+    <col width="2.33" customWidth="1" min="5" max="5"/>
+    <col width="2.33" customWidth="1" min="6" max="6"/>
+    <col width="2.33" customWidth="1" min="7" max="7"/>
+    <col width="2.33" customWidth="1" min="8" max="8"/>
+    <col width="2.33" customWidth="1" min="9" max="9"/>
+    <col width="2.33" customWidth="1" min="10" max="10"/>
+    <col width="2.33" customWidth="1" min="11" max="11"/>
+    <col width="2.33" customWidth="1" min="12" max="12"/>
+    <col width="2.33" customWidth="1" min="13" max="13"/>
+    <col width="2.33" customWidth="1" min="14" max="14"/>
+    <col width="2.33" customWidth="1" min="15" max="15"/>
+    <col width="2.33" customWidth="1" min="16" max="16"/>
+    <col width="2.33" customWidth="1" min="17" max="17"/>
+    <col width="2.33" customWidth="1" min="18" max="18"/>
+    <col width="2.33" customWidth="1" min="19" max="19"/>
+    <col width="2.33" customWidth="1" min="20" max="20"/>
+    <col width="2.33" customWidth="1" min="21" max="21"/>
+    <col width="2.33" customWidth="1" min="22" max="22"/>
+    <col width="2.33" customWidth="1" min="23" max="23"/>
+    <col width="2.33" customWidth="1" min="24" max="24"/>
+    <col width="2.33" customWidth="1" min="25" max="25"/>
+    <col width="2.33" customWidth="1" min="26" max="26"/>
+    <col width="2.33" customWidth="1" min="27" max="27"/>
+    <col width="2.33" customWidth="1" min="28" max="28"/>
+    <col width="2.33" customWidth="1" min="29" max="29"/>
+    <col width="2.33" customWidth="1" min="30" max="30"/>
+    <col width="2.33" customWidth="1" min="31" max="31"/>
+    <col width="2.33" customWidth="1" min="32" max="32"/>
+    <col width="2.33" customWidth="1" min="33" max="33"/>
+    <col width="2.33" customWidth="1" min="34" max="34"/>
+    <col width="2.33" customWidth="1" min="35" max="35"/>
+    <col width="2.33" customWidth="1" min="36" max="36"/>
+    <col width="2.33" customWidth="1" min="37" max="37"/>
+    <col width="2.33" customWidth="1" min="38" max="38"/>
+    <col width="2.33" customWidth="1" min="39" max="39"/>
+    <col width="2.33" customWidth="1" min="40" max="40"/>
   </cols>
   <sheetData>
     <row r="1" ht="18" customHeight="1">
-      <c r="A1" s="337" t="inlineStr">
+      <c r="A1" s="393" t="inlineStr">
         <is>
           <t>Conditions / Exceptions / Actions</t>
         </is>
       </c>
-      <c r="B1" s="285" t="n"/>
-      <c r="C1" s="285" t="n"/>
-      <c r="D1" s="285" t="n"/>
-      <c r="E1" s="285" t="n"/>
-      <c r="F1" s="285" t="n"/>
-      <c r="G1" s="286" t="n"/>
+      <c r="B1" s="423" t="n"/>
+      <c r="C1" s="423" t="n"/>
+      <c r="D1" s="423" t="n"/>
+      <c r="E1" s="423" t="n"/>
+      <c r="F1" s="423" t="n"/>
+      <c r="G1" s="424" t="n"/>
+      <c r="H1" s="348" t="n"/>
+      <c r="I1" s="348" t="n"/>
+      <c r="J1" s="348" t="n"/>
+      <c r="K1" s="348" t="n"/>
+      <c r="L1" s="348" t="n"/>
+      <c r="M1" s="348" t="n"/>
+      <c r="N1" s="348" t="n"/>
+      <c r="O1" s="348" t="n"/>
+      <c r="P1" s="348" t="n"/>
+      <c r="Q1" s="348" t="n"/>
+      <c r="R1" s="348" t="n"/>
+      <c r="S1" s="348" t="n"/>
+      <c r="T1" s="348" t="n"/>
+      <c r="U1" s="348" t="n"/>
+      <c r="V1" s="348" t="n"/>
+      <c r="W1" s="348" t="n"/>
+      <c r="X1" s="348" t="n"/>
+      <c r="Y1" s="348" t="n"/>
+      <c r="Z1" s="348" t="n"/>
+      <c r="AA1" s="348" t="n"/>
+      <c r="AB1" s="348" t="n"/>
+      <c r="AC1" s="348" t="n"/>
+      <c r="AD1" s="348" t="n"/>
+      <c r="AE1" s="348" t="n"/>
+      <c r="AF1" s="348" t="n"/>
+      <c r="AG1" s="348" t="n"/>
+      <c r="AH1" s="348" t="n"/>
+      <c r="AI1" s="348" t="n"/>
+      <c r="AJ1" s="348" t="n"/>
+      <c r="AK1" s="348" t="n"/>
+      <c r="AL1" s="348" t="n"/>
+      <c r="AM1" s="348" t="n"/>
+      <c r="AN1" s="348" t="n"/>
     </row>
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="338" t="inlineStr">
@@ -7225,179 +7982,605 @@
           <t>Vacuum-compatible clean build and bagging gate for controlled preservation and packaging release.</t>
         </is>
       </c>
+      <c r="H2" s="348" t="n"/>
+      <c r="I2" s="348" t="n"/>
+      <c r="J2" s="348" t="n"/>
+      <c r="K2" s="348" t="n"/>
+      <c r="L2" s="348" t="n"/>
+      <c r="M2" s="348" t="n"/>
+      <c r="N2" s="348" t="n"/>
+      <c r="O2" s="348" t="n"/>
+      <c r="P2" s="348" t="n"/>
+      <c r="Q2" s="348" t="n"/>
+      <c r="R2" s="348" t="n"/>
+      <c r="S2" s="348" t="n"/>
+      <c r="T2" s="348" t="n"/>
+      <c r="U2" s="348" t="n"/>
+      <c r="V2" s="348" t="n"/>
+      <c r="W2" s="348" t="n"/>
+      <c r="X2" s="348" t="n"/>
+      <c r="Y2" s="348" t="n"/>
+      <c r="Z2" s="348" t="n"/>
+      <c r="AA2" s="348" t="n"/>
+      <c r="AB2" s="348" t="n"/>
+      <c r="AC2" s="348" t="n"/>
+      <c r="AD2" s="348" t="n"/>
+      <c r="AE2" s="348" t="n"/>
+      <c r="AF2" s="348" t="n"/>
+      <c r="AG2" s="348" t="n"/>
+      <c r="AH2" s="348" t="n"/>
+      <c r="AI2" s="348" t="n"/>
+      <c r="AJ2" s="348" t="n"/>
+      <c r="AK2" s="348" t="n"/>
+      <c r="AL2" s="348" t="n"/>
+      <c r="AM2" s="348" t="n"/>
+      <c r="AN2" s="348" t="n"/>
     </row>
-    <row r="3" ht="18" customHeight="1"/>
+    <row r="3" ht="18" customHeight="1">
+      <c r="A3" s="348" t="n"/>
+      <c r="B3" s="348" t="n"/>
+      <c r="C3" s="348" t="n"/>
+      <c r="D3" s="348" t="n"/>
+      <c r="E3" s="348" t="n"/>
+      <c r="F3" s="348" t="n"/>
+      <c r="G3" s="348" t="n"/>
+      <c r="H3" s="348" t="n"/>
+      <c r="I3" s="348" t="n"/>
+      <c r="J3" s="348" t="n"/>
+      <c r="K3" s="348" t="n"/>
+      <c r="L3" s="348" t="n"/>
+      <c r="M3" s="348" t="n"/>
+      <c r="N3" s="348" t="n"/>
+      <c r="O3" s="348" t="n"/>
+      <c r="P3" s="348" t="n"/>
+      <c r="Q3" s="348" t="n"/>
+      <c r="R3" s="348" t="n"/>
+      <c r="S3" s="348" t="n"/>
+      <c r="T3" s="348" t="n"/>
+      <c r="U3" s="348" t="n"/>
+      <c r="V3" s="348" t="n"/>
+      <c r="W3" s="348" t="n"/>
+      <c r="X3" s="348" t="n"/>
+      <c r="Y3" s="348" t="n"/>
+      <c r="Z3" s="348" t="n"/>
+      <c r="AA3" s="348" t="n"/>
+      <c r="AB3" s="348" t="n"/>
+      <c r="AC3" s="348" t="n"/>
+      <c r="AD3" s="348" t="n"/>
+      <c r="AE3" s="348" t="n"/>
+      <c r="AF3" s="348" t="n"/>
+      <c r="AG3" s="348" t="n"/>
+      <c r="AH3" s="348" t="n"/>
+      <c r="AI3" s="348" t="n"/>
+      <c r="AJ3" s="348" t="n"/>
+      <c r="AK3" s="348" t="n"/>
+      <c r="AL3" s="348" t="n"/>
+      <c r="AM3" s="348" t="n"/>
+      <c r="AN3" s="348" t="n"/>
+    </row>
     <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="339" t="inlineStr">
+      <c r="A4" s="394" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B4" s="339" t="inlineStr">
+      <c r="B4" s="394" t="inlineStr">
         <is>
           <t>Condition / Exception</t>
         </is>
       </c>
-      <c r="C4" s="339" t="inlineStr">
+      <c r="C4" s="394" t="inlineStr">
         <is>
           <t>Required Action</t>
         </is>
       </c>
-      <c r="D4" s="339" t="inlineStr">
+      <c r="D4" s="394" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="E4" s="339" t="inlineStr">
+      <c r="E4" s="394" t="inlineStr">
         <is>
           <t>Due Date</t>
         </is>
       </c>
-      <c r="F4" s="339" t="inlineStr">
+      <c r="F4" s="394" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="G4" s="339" t="inlineStr">
+      <c r="G4" s="394" t="inlineStr">
         <is>
           <t>Evidence Ref</t>
         </is>
       </c>
-      <c r="H4" s="339" t="inlineStr">
+      <c r="H4" s="394" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
+      <c r="I4" s="348" t="n"/>
+      <c r="J4" s="348" t="n"/>
+      <c r="K4" s="348" t="n"/>
+      <c r="L4" s="348" t="n"/>
+      <c r="M4" s="348" t="n"/>
+      <c r="N4" s="348" t="n"/>
+      <c r="O4" s="348" t="n"/>
+      <c r="P4" s="348" t="n"/>
+      <c r="Q4" s="348" t="n"/>
+      <c r="R4" s="348" t="n"/>
+      <c r="S4" s="348" t="n"/>
+      <c r="T4" s="348" t="n"/>
+      <c r="U4" s="348" t="n"/>
+      <c r="V4" s="348" t="n"/>
+      <c r="W4" s="348" t="n"/>
+      <c r="X4" s="348" t="n"/>
+      <c r="Y4" s="348" t="n"/>
+      <c r="Z4" s="348" t="n"/>
+      <c r="AA4" s="348" t="n"/>
+      <c r="AB4" s="348" t="n"/>
+      <c r="AC4" s="348" t="n"/>
+      <c r="AD4" s="348" t="n"/>
+      <c r="AE4" s="348" t="n"/>
+      <c r="AF4" s="348" t="n"/>
+      <c r="AG4" s="348" t="n"/>
+      <c r="AH4" s="348" t="n"/>
+      <c r="AI4" s="348" t="n"/>
+      <c r="AJ4" s="348" t="n"/>
+      <c r="AK4" s="348" t="n"/>
+      <c r="AL4" s="348" t="n"/>
+      <c r="AM4" s="348" t="n"/>
+      <c r="AN4" s="348" t="n"/>
     </row>
     <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="318">
+      <c r="A5" s="395">
         <f>ROW()-ROW($A$5)+1</f>
         <v/>
       </c>
-      <c r="B5" s="319" t="n"/>
-      <c r="C5" s="319" t="n"/>
-      <c r="D5" s="319" t="n"/>
-      <c r="E5" s="319" t="n"/>
-      <c r="F5" s="319" t="n"/>
-      <c r="G5" s="319" t="n"/>
-      <c r="H5" s="319" t="n"/>
+      <c r="B5" s="396" t="n"/>
+      <c r="C5" s="396" t="n"/>
+      <c r="D5" s="396" t="n"/>
+      <c r="E5" s="396" t="n"/>
+      <c r="F5" s="396" t="n"/>
+      <c r="G5" s="396" t="n"/>
+      <c r="H5" s="396" t="n"/>
+      <c r="I5" s="348" t="n"/>
+      <c r="J5" s="348" t="n"/>
+      <c r="K5" s="348" t="n"/>
+      <c r="L5" s="348" t="n"/>
+      <c r="M5" s="348" t="n"/>
+      <c r="N5" s="348" t="n"/>
+      <c r="O5" s="348" t="n"/>
+      <c r="P5" s="348" t="n"/>
+      <c r="Q5" s="348" t="n"/>
+      <c r="R5" s="348" t="n"/>
+      <c r="S5" s="348" t="n"/>
+      <c r="T5" s="348" t="n"/>
+      <c r="U5" s="348" t="n"/>
+      <c r="V5" s="348" t="n"/>
+      <c r="W5" s="348" t="n"/>
+      <c r="X5" s="348" t="n"/>
+      <c r="Y5" s="348" t="n"/>
+      <c r="Z5" s="348" t="n"/>
+      <c r="AA5" s="348" t="n"/>
+      <c r="AB5" s="348" t="n"/>
+      <c r="AC5" s="348" t="n"/>
+      <c r="AD5" s="348" t="n"/>
+      <c r="AE5" s="348" t="n"/>
+      <c r="AF5" s="348" t="n"/>
+      <c r="AG5" s="348" t="n"/>
+      <c r="AH5" s="348" t="n"/>
+      <c r="AI5" s="348" t="n"/>
+      <c r="AJ5" s="348" t="n"/>
+      <c r="AK5" s="348" t="n"/>
+      <c r="AL5" s="348" t="n"/>
+      <c r="AM5" s="348" t="n"/>
+      <c r="AN5" s="348" t="n"/>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="318">
+      <c r="A6" s="395">
         <f>ROW()-ROW($A$5)+1</f>
         <v/>
       </c>
-      <c r="B6" s="319" t="n"/>
-      <c r="C6" s="319" t="n"/>
-      <c r="D6" s="319" t="n"/>
-      <c r="E6" s="319" t="n"/>
-      <c r="F6" s="319" t="n"/>
-      <c r="G6" s="319" t="n"/>
-      <c r="H6" s="319" t="n"/>
+      <c r="B6" s="396" t="n"/>
+      <c r="C6" s="396" t="n"/>
+      <c r="D6" s="396" t="n"/>
+      <c r="E6" s="396" t="n"/>
+      <c r="F6" s="396" t="n"/>
+      <c r="G6" s="396" t="n"/>
+      <c r="H6" s="396" t="n"/>
+      <c r="I6" s="348" t="n"/>
+      <c r="J6" s="348" t="n"/>
+      <c r="K6" s="348" t="n"/>
+      <c r="L6" s="348" t="n"/>
+      <c r="M6" s="348" t="n"/>
+      <c r="N6" s="348" t="n"/>
+      <c r="O6" s="348" t="n"/>
+      <c r="P6" s="348" t="n"/>
+      <c r="Q6" s="348" t="n"/>
+      <c r="R6" s="348" t="n"/>
+      <c r="S6" s="348" t="n"/>
+      <c r="T6" s="348" t="n"/>
+      <c r="U6" s="348" t="n"/>
+      <c r="V6" s="348" t="n"/>
+      <c r="W6" s="348" t="n"/>
+      <c r="X6" s="348" t="n"/>
+      <c r="Y6" s="348" t="n"/>
+      <c r="Z6" s="348" t="n"/>
+      <c r="AA6" s="348" t="n"/>
+      <c r="AB6" s="348" t="n"/>
+      <c r="AC6" s="348" t="n"/>
+      <c r="AD6" s="348" t="n"/>
+      <c r="AE6" s="348" t="n"/>
+      <c r="AF6" s="348" t="n"/>
+      <c r="AG6" s="348" t="n"/>
+      <c r="AH6" s="348" t="n"/>
+      <c r="AI6" s="348" t="n"/>
+      <c r="AJ6" s="348" t="n"/>
+      <c r="AK6" s="348" t="n"/>
+      <c r="AL6" s="348" t="n"/>
+      <c r="AM6" s="348" t="n"/>
+      <c r="AN6" s="348" t="n"/>
     </row>
     <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="318">
+      <c r="A7" s="395">
         <f>ROW()-ROW($A$5)+1</f>
         <v/>
       </c>
-      <c r="B7" s="319" t="n"/>
-      <c r="C7" s="319" t="n"/>
-      <c r="D7" s="319" t="n"/>
-      <c r="E7" s="319" t="n"/>
-      <c r="F7" s="319" t="n"/>
-      <c r="G7" s="319" t="n"/>
-      <c r="H7" s="319" t="n"/>
+      <c r="B7" s="396" t="n"/>
+      <c r="C7" s="396" t="n"/>
+      <c r="D7" s="396" t="n"/>
+      <c r="E7" s="396" t="n"/>
+      <c r="F7" s="396" t="n"/>
+      <c r="G7" s="396" t="n"/>
+      <c r="H7" s="396" t="n"/>
+      <c r="I7" s="348" t="n"/>
+      <c r="J7" s="348" t="n"/>
+      <c r="K7" s="348" t="n"/>
+      <c r="L7" s="348" t="n"/>
+      <c r="M7" s="348" t="n"/>
+      <c r="N7" s="348" t="n"/>
+      <c r="O7" s="348" t="n"/>
+      <c r="P7" s="348" t="n"/>
+      <c r="Q7" s="348" t="n"/>
+      <c r="R7" s="348" t="n"/>
+      <c r="S7" s="348" t="n"/>
+      <c r="T7" s="348" t="n"/>
+      <c r="U7" s="348" t="n"/>
+      <c r="V7" s="348" t="n"/>
+      <c r="W7" s="348" t="n"/>
+      <c r="X7" s="348" t="n"/>
+      <c r="Y7" s="348" t="n"/>
+      <c r="Z7" s="348" t="n"/>
+      <c r="AA7" s="348" t="n"/>
+      <c r="AB7" s="348" t="n"/>
+      <c r="AC7" s="348" t="n"/>
+      <c r="AD7" s="348" t="n"/>
+      <c r="AE7" s="348" t="n"/>
+      <c r="AF7" s="348" t="n"/>
+      <c r="AG7" s="348" t="n"/>
+      <c r="AH7" s="348" t="n"/>
+      <c r="AI7" s="348" t="n"/>
+      <c r="AJ7" s="348" t="n"/>
+      <c r="AK7" s="348" t="n"/>
+      <c r="AL7" s="348" t="n"/>
+      <c r="AM7" s="348" t="n"/>
+      <c r="AN7" s="348" t="n"/>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="318">
+      <c r="A8" s="397">
         <f>ROW()-ROW($A$5)+1</f>
         <v/>
       </c>
-      <c r="B8" s="319" t="n"/>
-      <c r="C8" s="319" t="n"/>
-      <c r="D8" s="319" t="n"/>
-      <c r="E8" s="319" t="n"/>
-      <c r="F8" s="319" t="n"/>
-      <c r="G8" s="319" t="n"/>
-      <c r="H8" s="319" t="n"/>
+      <c r="B8" s="398" t="n"/>
+      <c r="C8" s="398" t="n"/>
+      <c r="D8" s="398" t="n"/>
+      <c r="E8" s="398" t="n"/>
+      <c r="F8" s="398" t="n"/>
+      <c r="G8" s="398" t="n"/>
+      <c r="H8" s="398" t="n"/>
+      <c r="I8" s="399" t="n"/>
+      <c r="J8" s="399" t="n"/>
+      <c r="K8" s="399" t="n"/>
+      <c r="L8" s="399" t="n"/>
+      <c r="M8" s="399" t="n"/>
+      <c r="N8" s="399" t="n"/>
+      <c r="O8" s="399" t="n"/>
+      <c r="P8" s="399" t="n"/>
+      <c r="Q8" s="399" t="n"/>
+      <c r="R8" s="399" t="n"/>
+      <c r="S8" s="399" t="n"/>
+      <c r="T8" s="399" t="n"/>
+      <c r="U8" s="399" t="n"/>
+      <c r="V8" s="399" t="n"/>
+      <c r="W8" s="399" t="n"/>
+      <c r="X8" s="399" t="n"/>
+      <c r="Y8" s="399" t="n"/>
+      <c r="Z8" s="399" t="n"/>
+      <c r="AA8" s="399" t="n"/>
+      <c r="AB8" s="399" t="n"/>
+      <c r="AC8" s="399" t="n"/>
+      <c r="AD8" s="399" t="n"/>
+      <c r="AE8" s="399" t="n"/>
+      <c r="AF8" s="399" t="n"/>
+      <c r="AG8" s="399" t="n"/>
+      <c r="AH8" s="399" t="n"/>
+      <c r="AI8" s="399" t="n"/>
+      <c r="AJ8" s="399" t="n"/>
+      <c r="AK8" s="399" t="n"/>
+      <c r="AL8" s="399" t="n"/>
+      <c r="AM8" s="399" t="n"/>
+      <c r="AN8" s="399" t="n"/>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="318">
+      <c r="A9" s="397">
         <f>ROW()-ROW($A$5)+1</f>
         <v/>
       </c>
-      <c r="B9" s="319" t="n"/>
-      <c r="C9" s="319" t="n"/>
-      <c r="D9" s="319" t="n"/>
-      <c r="E9" s="319" t="n"/>
-      <c r="F9" s="319" t="n"/>
-      <c r="G9" s="319" t="n"/>
-      <c r="H9" s="319" t="n"/>
+      <c r="B9" s="398" t="n"/>
+      <c r="C9" s="398" t="n"/>
+      <c r="D9" s="398" t="n"/>
+      <c r="E9" s="398" t="n"/>
+      <c r="F9" s="398" t="n"/>
+      <c r="G9" s="398" t="n"/>
+      <c r="H9" s="398" t="n"/>
+      <c r="I9" s="399" t="n"/>
+      <c r="J9" s="399" t="n"/>
+      <c r="K9" s="399" t="n"/>
+      <c r="L9" s="399" t="n"/>
+      <c r="M9" s="399" t="n"/>
+      <c r="N9" s="399" t="n"/>
+      <c r="O9" s="399" t="n"/>
+      <c r="P9" s="399" t="n"/>
+      <c r="Q9" s="399" t="n"/>
+      <c r="R9" s="399" t="n"/>
+      <c r="S9" s="399" t="n"/>
+      <c r="T9" s="399" t="n"/>
+      <c r="U9" s="399" t="n"/>
+      <c r="V9" s="399" t="n"/>
+      <c r="W9" s="399" t="n"/>
+      <c r="X9" s="399" t="n"/>
+      <c r="Y9" s="399" t="n"/>
+      <c r="Z9" s="399" t="n"/>
+      <c r="AA9" s="399" t="n"/>
+      <c r="AB9" s="399" t="n"/>
+      <c r="AC9" s="399" t="n"/>
+      <c r="AD9" s="399" t="n"/>
+      <c r="AE9" s="399" t="n"/>
+      <c r="AF9" s="399" t="n"/>
+      <c r="AG9" s="399" t="n"/>
+      <c r="AH9" s="399" t="n"/>
+      <c r="AI9" s="399" t="n"/>
+      <c r="AJ9" s="399" t="n"/>
+      <c r="AK9" s="399" t="n"/>
+      <c r="AL9" s="399" t="n"/>
+      <c r="AM9" s="399" t="n"/>
+      <c r="AN9" s="399" t="n"/>
     </row>
     <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="318">
+      <c r="A10" s="397">
         <f>ROW()-ROW($A$5)+1</f>
         <v/>
       </c>
-      <c r="B10" s="319" t="n"/>
-      <c r="C10" s="319" t="n"/>
-      <c r="D10" s="319" t="n"/>
-      <c r="E10" s="319" t="n"/>
-      <c r="F10" s="319" t="n"/>
-      <c r="G10" s="319" t="n"/>
-      <c r="H10" s="319" t="n"/>
+      <c r="B10" s="398" t="n"/>
+      <c r="C10" s="398" t="n"/>
+      <c r="D10" s="398" t="n"/>
+      <c r="E10" s="398" t="n"/>
+      <c r="F10" s="398" t="n"/>
+      <c r="G10" s="398" t="n"/>
+      <c r="H10" s="398" t="n"/>
+      <c r="I10" s="399" t="n"/>
+      <c r="J10" s="399" t="n"/>
+      <c r="K10" s="399" t="n"/>
+      <c r="L10" s="399" t="n"/>
+      <c r="M10" s="399" t="n"/>
+      <c r="N10" s="399" t="n"/>
+      <c r="O10" s="399" t="n"/>
+      <c r="P10" s="399" t="n"/>
+      <c r="Q10" s="399" t="n"/>
+      <c r="R10" s="399" t="n"/>
+      <c r="S10" s="399" t="n"/>
+      <c r="T10" s="399" t="n"/>
+      <c r="U10" s="399" t="n"/>
+      <c r="V10" s="399" t="n"/>
+      <c r="W10" s="399" t="n"/>
+      <c r="X10" s="399" t="n"/>
+      <c r="Y10" s="399" t="n"/>
+      <c r="Z10" s="399" t="n"/>
+      <c r="AA10" s="399" t="n"/>
+      <c r="AB10" s="399" t="n"/>
+      <c r="AC10" s="399" t="n"/>
+      <c r="AD10" s="399" t="n"/>
+      <c r="AE10" s="399" t="n"/>
+      <c r="AF10" s="399" t="n"/>
+      <c r="AG10" s="399" t="n"/>
+      <c r="AH10" s="399" t="n"/>
+      <c r="AI10" s="399" t="n"/>
+      <c r="AJ10" s="399" t="n"/>
+      <c r="AK10" s="399" t="n"/>
+      <c r="AL10" s="399" t="n"/>
+      <c r="AM10" s="399" t="n"/>
+      <c r="AN10" s="399" t="n"/>
     </row>
     <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="318">
+      <c r="A11" s="397">
         <f>ROW()-ROW($A$5)+1</f>
         <v/>
       </c>
-      <c r="B11" s="319" t="n"/>
-      <c r="C11" s="319" t="n"/>
-      <c r="D11" s="319" t="n"/>
-      <c r="E11" s="319" t="n"/>
-      <c r="F11" s="319" t="n"/>
-      <c r="G11" s="319" t="n"/>
-      <c r="H11" s="319" t="n"/>
+      <c r="B11" s="398" t="n"/>
+      <c r="C11" s="398" t="n"/>
+      <c r="D11" s="398" t="n"/>
+      <c r="E11" s="398" t="n"/>
+      <c r="F11" s="398" t="n"/>
+      <c r="G11" s="398" t="n"/>
+      <c r="H11" s="398" t="n"/>
+      <c r="I11" s="399" t="n"/>
+      <c r="J11" s="399" t="n"/>
+      <c r="K11" s="399" t="n"/>
+      <c r="L11" s="399" t="n"/>
+      <c r="M11" s="399" t="n"/>
+      <c r="N11" s="399" t="n"/>
+      <c r="O11" s="399" t="n"/>
+      <c r="P11" s="399" t="n"/>
+      <c r="Q11" s="399" t="n"/>
+      <c r="R11" s="399" t="n"/>
+      <c r="S11" s="399" t="n"/>
+      <c r="T11" s="399" t="n"/>
+      <c r="U11" s="399" t="n"/>
+      <c r="V11" s="399" t="n"/>
+      <c r="W11" s="399" t="n"/>
+      <c r="X11" s="399" t="n"/>
+      <c r="Y11" s="399" t="n"/>
+      <c r="Z11" s="399" t="n"/>
+      <c r="AA11" s="399" t="n"/>
+      <c r="AB11" s="399" t="n"/>
+      <c r="AC11" s="399" t="n"/>
+      <c r="AD11" s="399" t="n"/>
+      <c r="AE11" s="399" t="n"/>
+      <c r="AF11" s="399" t="n"/>
+      <c r="AG11" s="399" t="n"/>
+      <c r="AH11" s="399" t="n"/>
+      <c r="AI11" s="399" t="n"/>
+      <c r="AJ11" s="399" t="n"/>
+      <c r="AK11" s="399" t="n"/>
+      <c r="AL11" s="399" t="n"/>
+      <c r="AM11" s="399" t="n"/>
+      <c r="AN11" s="399" t="n"/>
     </row>
     <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="318">
+      <c r="A12" s="397">
         <f>ROW()-ROW($A$5)+1</f>
         <v/>
       </c>
-      <c r="B12" s="319" t="n"/>
-      <c r="C12" s="319" t="n"/>
-      <c r="D12" s="319" t="n"/>
-      <c r="E12" s="319" t="n"/>
-      <c r="F12" s="319" t="n"/>
-      <c r="G12" s="319" t="n"/>
-      <c r="H12" s="319" t="n"/>
+      <c r="B12" s="398" t="n"/>
+      <c r="C12" s="398" t="n"/>
+      <c r="D12" s="398" t="n"/>
+      <c r="E12" s="398" t="n"/>
+      <c r="F12" s="398" t="n"/>
+      <c r="G12" s="398" t="n"/>
+      <c r="H12" s="398" t="n"/>
+      <c r="I12" s="399" t="n"/>
+      <c r="J12" s="399" t="n"/>
+      <c r="K12" s="399" t="n"/>
+      <c r="L12" s="399" t="n"/>
+      <c r="M12" s="399" t="n"/>
+      <c r="N12" s="399" t="n"/>
+      <c r="O12" s="399" t="n"/>
+      <c r="P12" s="399" t="n"/>
+      <c r="Q12" s="399" t="n"/>
+      <c r="R12" s="399" t="n"/>
+      <c r="S12" s="399" t="n"/>
+      <c r="T12" s="399" t="n"/>
+      <c r="U12" s="399" t="n"/>
+      <c r="V12" s="399" t="n"/>
+      <c r="W12" s="399" t="n"/>
+      <c r="X12" s="399" t="n"/>
+      <c r="Y12" s="399" t="n"/>
+      <c r="Z12" s="399" t="n"/>
+      <c r="AA12" s="399" t="n"/>
+      <c r="AB12" s="399" t="n"/>
+      <c r="AC12" s="399" t="n"/>
+      <c r="AD12" s="399" t="n"/>
+      <c r="AE12" s="399" t="n"/>
+      <c r="AF12" s="399" t="n"/>
+      <c r="AG12" s="399" t="n"/>
+      <c r="AH12" s="399" t="n"/>
+      <c r="AI12" s="399" t="n"/>
+      <c r="AJ12" s="399" t="n"/>
+      <c r="AK12" s="399" t="n"/>
+      <c r="AL12" s="399" t="n"/>
+      <c r="AM12" s="399" t="n"/>
+      <c r="AN12" s="399" t="n"/>
     </row>
     <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="318">
+      <c r="A13" s="397">
         <f>ROW()-ROW($A$5)+1</f>
         <v/>
       </c>
-      <c r="B13" s="319" t="n"/>
-      <c r="C13" s="319" t="n"/>
-      <c r="D13" s="319" t="n"/>
-      <c r="E13" s="319" t="n"/>
-      <c r="F13" s="319" t="n"/>
-      <c r="G13" s="319" t="n"/>
-      <c r="H13" s="319" t="n"/>
+      <c r="B13" s="398" t="n"/>
+      <c r="C13" s="398" t="n"/>
+      <c r="D13" s="398" t="n"/>
+      <c r="E13" s="398" t="n"/>
+      <c r="F13" s="398" t="n"/>
+      <c r="G13" s="398" t="n"/>
+      <c r="H13" s="398" t="n"/>
+      <c r="I13" s="399" t="n"/>
+      <c r="J13" s="399" t="n"/>
+      <c r="K13" s="399" t="n"/>
+      <c r="L13" s="399" t="n"/>
+      <c r="M13" s="399" t="n"/>
+      <c r="N13" s="399" t="n"/>
+      <c r="O13" s="399" t="n"/>
+      <c r="P13" s="399" t="n"/>
+      <c r="Q13" s="399" t="n"/>
+      <c r="R13" s="399" t="n"/>
+      <c r="S13" s="399" t="n"/>
+      <c r="T13" s="399" t="n"/>
+      <c r="U13" s="399" t="n"/>
+      <c r="V13" s="399" t="n"/>
+      <c r="W13" s="399" t="n"/>
+      <c r="X13" s="399" t="n"/>
+      <c r="Y13" s="399" t="n"/>
+      <c r="Z13" s="399" t="n"/>
+      <c r="AA13" s="399" t="n"/>
+      <c r="AB13" s="399" t="n"/>
+      <c r="AC13" s="399" t="n"/>
+      <c r="AD13" s="399" t="n"/>
+      <c r="AE13" s="399" t="n"/>
+      <c r="AF13" s="399" t="n"/>
+      <c r="AG13" s="399" t="n"/>
+      <c r="AH13" s="399" t="n"/>
+      <c r="AI13" s="399" t="n"/>
+      <c r="AJ13" s="399" t="n"/>
+      <c r="AK13" s="399" t="n"/>
+      <c r="AL13" s="399" t="n"/>
+      <c r="AM13" s="399" t="n"/>
+      <c r="AN13" s="399" t="n"/>
     </row>
     <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="318">
+      <c r="A14" s="397">
         <f>ROW()-ROW($A$5)+1</f>
         <v/>
       </c>
-      <c r="B14" s="319" t="n"/>
-      <c r="C14" s="319" t="n"/>
-      <c r="D14" s="319" t="n"/>
-      <c r="E14" s="319" t="n"/>
-      <c r="F14" s="319" t="n"/>
-      <c r="G14" s="319" t="n"/>
-      <c r="H14" s="319" t="n"/>
+      <c r="B14" s="398" t="n"/>
+      <c r="C14" s="398" t="n"/>
+      <c r="D14" s="398" t="n"/>
+      <c r="E14" s="398" t="n"/>
+      <c r="F14" s="398" t="n"/>
+      <c r="G14" s="398" t="n"/>
+      <c r="H14" s="398" t="n"/>
+      <c r="I14" s="399" t="n"/>
+      <c r="J14" s="399" t="n"/>
+      <c r="K14" s="399" t="n"/>
+      <c r="L14" s="399" t="n"/>
+      <c r="M14" s="399" t="n"/>
+      <c r="N14" s="399" t="n"/>
+      <c r="O14" s="399" t="n"/>
+      <c r="P14" s="399" t="n"/>
+      <c r="Q14" s="399" t="n"/>
+      <c r="R14" s="399" t="n"/>
+      <c r="S14" s="399" t="n"/>
+      <c r="T14" s="399" t="n"/>
+      <c r="U14" s="399" t="n"/>
+      <c r="V14" s="399" t="n"/>
+      <c r="W14" s="399" t="n"/>
+      <c r="X14" s="399" t="n"/>
+      <c r="Y14" s="399" t="n"/>
+      <c r="Z14" s="399" t="n"/>
+      <c r="AA14" s="399" t="n"/>
+      <c r="AB14" s="399" t="n"/>
+      <c r="AC14" s="399" t="n"/>
+      <c r="AD14" s="399" t="n"/>
+      <c r="AE14" s="399" t="n"/>
+      <c r="AF14" s="399" t="n"/>
+      <c r="AG14" s="399" t="n"/>
+      <c r="AH14" s="399" t="n"/>
+      <c r="AI14" s="399" t="n"/>
+      <c r="AJ14" s="399" t="n"/>
+      <c r="AK14" s="399" t="n"/>
+      <c r="AL14" s="399" t="n"/>
+      <c r="AM14" s="399" t="n"/>
+      <c r="AN14" s="399" t="n"/>
     </row>
     <row r="15" ht="20" customHeight="1"/>
     <row r="16" ht="20" customHeight="1"/>
@@ -7442,7 +8625,8 @@
       <formula1>=LISTS!$F$2:$F$11</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.197" right="0.197" top="0.197" bottom="0.197" header="0.1" footer="0.1"/>
+  <pageSetup paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <tableParts count="2">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
@@ -7456,30 +8640,96 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:AN14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="52" customWidth="1" min="2" max="2"/>
-    <col width="65" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="24" customWidth="1" min="7" max="7"/>
+    <col width="2.33" customWidth="1" min="1" max="1"/>
+    <col width="2.33" customWidth="1" min="2" max="2"/>
+    <col width="2.33" customWidth="1" min="3" max="3"/>
+    <col width="2.33" customWidth="1" min="4" max="4"/>
+    <col width="2.33" customWidth="1" min="5" max="5"/>
+    <col width="2.33" customWidth="1" min="6" max="6"/>
+    <col width="2.33" customWidth="1" min="7" max="7"/>
+    <col width="2.33" customWidth="1" min="8" max="8"/>
+    <col width="2.33" customWidth="1" min="9" max="9"/>
+    <col width="2.33" customWidth="1" min="10" max="10"/>
+    <col width="2.33" customWidth="1" min="11" max="11"/>
+    <col width="2.33" customWidth="1" min="12" max="12"/>
+    <col width="2.33" customWidth="1" min="13" max="13"/>
+    <col width="2.33" customWidth="1" min="14" max="14"/>
+    <col width="2.33" customWidth="1" min="15" max="15"/>
+    <col width="2.33" customWidth="1" min="16" max="16"/>
+    <col width="2.33" customWidth="1" min="17" max="17"/>
+    <col width="2.33" customWidth="1" min="18" max="18"/>
+    <col width="2.33" customWidth="1" min="19" max="19"/>
+    <col width="2.33" customWidth="1" min="20" max="20"/>
+    <col width="2.33" customWidth="1" min="21" max="21"/>
+    <col width="2.33" customWidth="1" min="22" max="22"/>
+    <col width="2.33" customWidth="1" min="23" max="23"/>
+    <col width="2.33" customWidth="1" min="24" max="24"/>
+    <col width="2.33" customWidth="1" min="25" max="25"/>
+    <col width="2.33" customWidth="1" min="26" max="26"/>
+    <col width="2.33" customWidth="1" min="27" max="27"/>
+    <col width="2.33" customWidth="1" min="28" max="28"/>
+    <col width="2.33" customWidth="1" min="29" max="29"/>
+    <col width="2.33" customWidth="1" min="30" max="30"/>
+    <col width="2.33" customWidth="1" min="31" max="31"/>
+    <col width="2.33" customWidth="1" min="32" max="32"/>
+    <col width="2.33" customWidth="1" min="33" max="33"/>
+    <col width="2.33" customWidth="1" min="34" max="34"/>
+    <col width="2.33" customWidth="1" min="35" max="35"/>
+    <col width="2.33" customWidth="1" min="36" max="36"/>
+    <col width="2.33" customWidth="1" min="37" max="37"/>
+    <col width="2.33" customWidth="1" min="38" max="38"/>
+    <col width="2.33" customWidth="1" min="39" max="39"/>
+    <col width="2.33" customWidth="1" min="40" max="40"/>
   </cols>
   <sheetData>
     <row r="1" ht="18" customHeight="1">
-      <c r="A1" s="337" t="inlineStr">
+      <c r="A1" s="393" t="inlineStr">
         <is>
           <t>Upstream References / Import Guidance</t>
         </is>
       </c>
-      <c r="B1" s="285" t="n"/>
-      <c r="C1" s="285" t="n"/>
-      <c r="D1" s="285" t="n"/>
-      <c r="E1" s="285" t="n"/>
-      <c r="F1" s="285" t="n"/>
-      <c r="G1" s="286" t="n"/>
+      <c r="B1" s="423" t="n"/>
+      <c r="C1" s="423" t="n"/>
+      <c r="D1" s="423" t="n"/>
+      <c r="E1" s="423" t="n"/>
+      <c r="F1" s="423" t="n"/>
+      <c r="G1" s="424" t="n"/>
+      <c r="H1" s="348" t="n"/>
+      <c r="I1" s="348" t="n"/>
+      <c r="J1" s="348" t="n"/>
+      <c r="K1" s="348" t="n"/>
+      <c r="L1" s="348" t="n"/>
+      <c r="M1" s="348" t="n"/>
+      <c r="N1" s="348" t="n"/>
+      <c r="O1" s="348" t="n"/>
+      <c r="P1" s="348" t="n"/>
+      <c r="Q1" s="348" t="n"/>
+      <c r="R1" s="348" t="n"/>
+      <c r="S1" s="348" t="n"/>
+      <c r="T1" s="348" t="n"/>
+      <c r="U1" s="348" t="n"/>
+      <c r="V1" s="348" t="n"/>
+      <c r="W1" s="348" t="n"/>
+      <c r="X1" s="348" t="n"/>
+      <c r="Y1" s="348" t="n"/>
+      <c r="Z1" s="348" t="n"/>
+      <c r="AA1" s="348" t="n"/>
+      <c r="AB1" s="348" t="n"/>
+      <c r="AC1" s="348" t="n"/>
+      <c r="AD1" s="348" t="n"/>
+      <c r="AE1" s="348" t="n"/>
+      <c r="AF1" s="348" t="n"/>
+      <c r="AG1" s="348" t="n"/>
+      <c r="AH1" s="348" t="n"/>
+      <c r="AI1" s="348" t="n"/>
+      <c r="AJ1" s="348" t="n"/>
+      <c r="AK1" s="348" t="n"/>
+      <c r="AL1" s="348" t="n"/>
+      <c r="AM1" s="348" t="n"/>
+      <c r="AN1" s="348" t="n"/>
     </row>
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="338" t="inlineStr">
@@ -7487,49 +8737,197 @@
           <t>Vacuum-compatible clean build and bagging gate for controlled preservation and packaging release.</t>
         </is>
       </c>
+      <c r="H2" s="348" t="n"/>
+      <c r="I2" s="348" t="n"/>
+      <c r="J2" s="348" t="n"/>
+      <c r="K2" s="348" t="n"/>
+      <c r="L2" s="348" t="n"/>
+      <c r="M2" s="348" t="n"/>
+      <c r="N2" s="348" t="n"/>
+      <c r="O2" s="348" t="n"/>
+      <c r="P2" s="348" t="n"/>
+      <c r="Q2" s="348" t="n"/>
+      <c r="R2" s="348" t="n"/>
+      <c r="S2" s="348" t="n"/>
+      <c r="T2" s="348" t="n"/>
+      <c r="U2" s="348" t="n"/>
+      <c r="V2" s="348" t="n"/>
+      <c r="W2" s="348" t="n"/>
+      <c r="X2" s="348" t="n"/>
+      <c r="Y2" s="348" t="n"/>
+      <c r="Z2" s="348" t="n"/>
+      <c r="AA2" s="348" t="n"/>
+      <c r="AB2" s="348" t="n"/>
+      <c r="AC2" s="348" t="n"/>
+      <c r="AD2" s="348" t="n"/>
+      <c r="AE2" s="348" t="n"/>
+      <c r="AF2" s="348" t="n"/>
+      <c r="AG2" s="348" t="n"/>
+      <c r="AH2" s="348" t="n"/>
+      <c r="AI2" s="348" t="n"/>
+      <c r="AJ2" s="348" t="n"/>
+      <c r="AK2" s="348" t="n"/>
+      <c r="AL2" s="348" t="n"/>
+      <c r="AM2" s="348" t="n"/>
+      <c r="AN2" s="348" t="n"/>
     </row>
-    <row r="3" ht="18" customHeight="1"/>
+    <row r="3" ht="18" customHeight="1">
+      <c r="A3" s="348" t="n"/>
+      <c r="B3" s="348" t="n"/>
+      <c r="C3" s="348" t="n"/>
+      <c r="D3" s="348" t="n"/>
+      <c r="E3" s="348" t="n"/>
+      <c r="F3" s="348" t="n"/>
+      <c r="G3" s="348" t="n"/>
+      <c r="H3" s="348" t="n"/>
+      <c r="I3" s="348" t="n"/>
+      <c r="J3" s="348" t="n"/>
+      <c r="K3" s="348" t="n"/>
+      <c r="L3" s="348" t="n"/>
+      <c r="M3" s="348" t="n"/>
+      <c r="N3" s="348" t="n"/>
+      <c r="O3" s="348" t="n"/>
+      <c r="P3" s="348" t="n"/>
+      <c r="Q3" s="348" t="n"/>
+      <c r="R3" s="348" t="n"/>
+      <c r="S3" s="348" t="n"/>
+      <c r="T3" s="348" t="n"/>
+      <c r="U3" s="348" t="n"/>
+      <c r="V3" s="348" t="n"/>
+      <c r="W3" s="348" t="n"/>
+      <c r="X3" s="348" t="n"/>
+      <c r="Y3" s="348" t="n"/>
+      <c r="Z3" s="348" t="n"/>
+      <c r="AA3" s="348" t="n"/>
+      <c r="AB3" s="348" t="n"/>
+      <c r="AC3" s="348" t="n"/>
+      <c r="AD3" s="348" t="n"/>
+      <c r="AE3" s="348" t="n"/>
+      <c r="AF3" s="348" t="n"/>
+      <c r="AG3" s="348" t="n"/>
+      <c r="AH3" s="348" t="n"/>
+      <c r="AI3" s="348" t="n"/>
+      <c r="AJ3" s="348" t="n"/>
+      <c r="AK3" s="348" t="n"/>
+      <c r="AL3" s="348" t="n"/>
+      <c r="AM3" s="348" t="n"/>
+      <c r="AN3" s="348" t="n"/>
+    </row>
     <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="339" t="inlineStr">
+      <c r="A4" s="394" t="inlineStr">
         <is>
           <t>Field</t>
         </is>
       </c>
-      <c r="B4" s="339" t="inlineStr">
+      <c r="B4" s="394" t="inlineStr">
         <is>
           <t>Value / Reference</t>
         </is>
       </c>
-      <c r="C4" s="339" t="inlineStr">
+      <c r="C4" s="394" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
+      <c r="D4" s="348" t="n"/>
+      <c r="E4" s="348" t="n"/>
+      <c r="F4" s="348" t="n"/>
+      <c r="G4" s="348" t="n"/>
+      <c r="H4" s="348" t="n"/>
+      <c r="I4" s="348" t="n"/>
+      <c r="J4" s="348" t="n"/>
+      <c r="K4" s="348" t="n"/>
+      <c r="L4" s="348" t="n"/>
+      <c r="M4" s="348" t="n"/>
+      <c r="N4" s="348" t="n"/>
+      <c r="O4" s="348" t="n"/>
+      <c r="P4" s="348" t="n"/>
+      <c r="Q4" s="348" t="n"/>
+      <c r="R4" s="348" t="n"/>
+      <c r="S4" s="348" t="n"/>
+      <c r="T4" s="348" t="n"/>
+      <c r="U4" s="348" t="n"/>
+      <c r="V4" s="348" t="n"/>
+      <c r="W4" s="348" t="n"/>
+      <c r="X4" s="348" t="n"/>
+      <c r="Y4" s="348" t="n"/>
+      <c r="Z4" s="348" t="n"/>
+      <c r="AA4" s="348" t="n"/>
+      <c r="AB4" s="348" t="n"/>
+      <c r="AC4" s="348" t="n"/>
+      <c r="AD4" s="348" t="n"/>
+      <c r="AE4" s="348" t="n"/>
+      <c r="AF4" s="348" t="n"/>
+      <c r="AG4" s="348" t="n"/>
+      <c r="AH4" s="348" t="n"/>
+      <c r="AI4" s="348" t="n"/>
+      <c r="AJ4" s="348" t="n"/>
+      <c r="AK4" s="348" t="n"/>
+      <c r="AL4" s="348" t="n"/>
+      <c r="AM4" s="348" t="n"/>
+      <c r="AN4" s="348" t="n"/>
     </row>
     <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="318" t="inlineStr">
+      <c r="A5" s="395" t="inlineStr">
         <is>
           <t>Source of Truth</t>
         </is>
       </c>
-      <c r="B5" s="319" t="inlineStr">
+      <c r="B5" s="396" t="inlineStr">
         <is>
           <t>M365 evidence / shared workbook</t>
         </is>
       </c>
-      <c r="C5" s="319" t="inlineStr">
+      <c r="C5" s="396" t="inlineStr">
         <is>
           <t>Do not duplicate ERP/M365/ANNEX master data.</t>
         </is>
       </c>
+      <c r="D5" s="348" t="n"/>
+      <c r="E5" s="348" t="n"/>
+      <c r="F5" s="348" t="n"/>
+      <c r="G5" s="348" t="n"/>
+      <c r="H5" s="348" t="n"/>
+      <c r="I5" s="348" t="n"/>
+      <c r="J5" s="348" t="n"/>
+      <c r="K5" s="348" t="n"/>
+      <c r="L5" s="348" t="n"/>
+      <c r="M5" s="348" t="n"/>
+      <c r="N5" s="348" t="n"/>
+      <c r="O5" s="348" t="n"/>
+      <c r="P5" s="348" t="n"/>
+      <c r="Q5" s="348" t="n"/>
+      <c r="R5" s="348" t="n"/>
+      <c r="S5" s="348" t="n"/>
+      <c r="T5" s="348" t="n"/>
+      <c r="U5" s="348" t="n"/>
+      <c r="V5" s="348" t="n"/>
+      <c r="W5" s="348" t="n"/>
+      <c r="X5" s="348" t="n"/>
+      <c r="Y5" s="348" t="n"/>
+      <c r="Z5" s="348" t="n"/>
+      <c r="AA5" s="348" t="n"/>
+      <c r="AB5" s="348" t="n"/>
+      <c r="AC5" s="348" t="n"/>
+      <c r="AD5" s="348" t="n"/>
+      <c r="AE5" s="348" t="n"/>
+      <c r="AF5" s="348" t="n"/>
+      <c r="AG5" s="348" t="n"/>
+      <c r="AH5" s="348" t="n"/>
+      <c r="AI5" s="348" t="n"/>
+      <c r="AJ5" s="348" t="n"/>
+      <c r="AK5" s="348" t="n"/>
+      <c r="AL5" s="348" t="n"/>
+      <c r="AM5" s="348" t="n"/>
+      <c r="AN5" s="348" t="n"/>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="318" t="inlineStr">
+      <c r="A6" s="395" t="inlineStr">
         <is>
           <t>Cross-Reference Boundary</t>
         </is>
       </c>
-      <c r="B6" s="319" t="inlineStr">
+      <c r="B6" s="396" t="inlineStr">
         <is>
           <t>This form does not replace SOP-702; it records the evidence, data or decision required by that SOP.
 Detailed task execution belongs in WI-716; this form captures results, checks, decisions or exceptions only.
@@ -7537,7 +8935,7 @@
 System-of-record / source-of-truth boundary: M365 evidence / shared workbook. If the master data already live there, reference or import them; do not re-key without need.</t>
         </is>
       </c>
-      <c r="C6" s="319" t="inlineStr">
+      <c r="C6" s="396" t="inlineStr">
         <is>
           <t>This form does not replace SOP-702; it records the evidence, data or decision required by that SOP.
 Detailed task execution belongs in WI-716; this form captures results, checks, decisions or exceptions only.
@@ -7545,118 +8943,451 @@
 System-of-record / source-of-truth boundary: M365 evidence / shared workbook. If the master data already live there, reference or import them; do not re-key without need.</t>
         </is>
       </c>
+      <c r="D6" s="348" t="n"/>
+      <c r="E6" s="348" t="n"/>
+      <c r="F6" s="348" t="n"/>
+      <c r="G6" s="348" t="n"/>
+      <c r="H6" s="348" t="n"/>
+      <c r="I6" s="348" t="n"/>
+      <c r="J6" s="348" t="n"/>
+      <c r="K6" s="348" t="n"/>
+      <c r="L6" s="348" t="n"/>
+      <c r="M6" s="348" t="n"/>
+      <c r="N6" s="348" t="n"/>
+      <c r="O6" s="348" t="n"/>
+      <c r="P6" s="348" t="n"/>
+      <c r="Q6" s="348" t="n"/>
+      <c r="R6" s="348" t="n"/>
+      <c r="S6" s="348" t="n"/>
+      <c r="T6" s="348" t="n"/>
+      <c r="U6" s="348" t="n"/>
+      <c r="V6" s="348" t="n"/>
+      <c r="W6" s="348" t="n"/>
+      <c r="X6" s="348" t="n"/>
+      <c r="Y6" s="348" t="n"/>
+      <c r="Z6" s="348" t="n"/>
+      <c r="AA6" s="348" t="n"/>
+      <c r="AB6" s="348" t="n"/>
+      <c r="AC6" s="348" t="n"/>
+      <c r="AD6" s="348" t="n"/>
+      <c r="AE6" s="348" t="n"/>
+      <c r="AF6" s="348" t="n"/>
+      <c r="AG6" s="348" t="n"/>
+      <c r="AH6" s="348" t="n"/>
+      <c r="AI6" s="348" t="n"/>
+      <c r="AJ6" s="348" t="n"/>
+      <c r="AK6" s="348" t="n"/>
+      <c r="AL6" s="348" t="n"/>
+      <c r="AM6" s="348" t="n"/>
+      <c r="AN6" s="348" t="n"/>
     </row>
     <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="318" t="inlineStr">
+      <c r="A7" s="395" t="inlineStr">
         <is>
           <t>SOP-702</t>
         </is>
       </c>
-      <c r="B7" s="319" t="inlineStr">
+      <c r="B7" s="396" t="inlineStr">
         <is>
           <t>SOP-702 — Kiểm soát nhiễm bẩn, xác nhận độ sạch và tuyến đóng gói sạch | HESEM QMS</t>
         </is>
       </c>
-      <c r="C7" s="319" t="inlineStr">
+      <c r="C7" s="396" t="inlineStr">
         <is>
           <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/01-SOPs/07-SOP-700/sop-702-contamination-control-and-cleanliness.html</t>
         </is>
       </c>
+      <c r="D7" s="348" t="n"/>
+      <c r="E7" s="348" t="n"/>
+      <c r="F7" s="348" t="n"/>
+      <c r="G7" s="348" t="n"/>
+      <c r="H7" s="348" t="n"/>
+      <c r="I7" s="348" t="n"/>
+      <c r="J7" s="348" t="n"/>
+      <c r="K7" s="348" t="n"/>
+      <c r="L7" s="348" t="n"/>
+      <c r="M7" s="348" t="n"/>
+      <c r="N7" s="348" t="n"/>
+      <c r="O7" s="348" t="n"/>
+      <c r="P7" s="348" t="n"/>
+      <c r="Q7" s="348" t="n"/>
+      <c r="R7" s="348" t="n"/>
+      <c r="S7" s="348" t="n"/>
+      <c r="T7" s="348" t="n"/>
+      <c r="U7" s="348" t="n"/>
+      <c r="V7" s="348" t="n"/>
+      <c r="W7" s="348" t="n"/>
+      <c r="X7" s="348" t="n"/>
+      <c r="Y7" s="348" t="n"/>
+      <c r="Z7" s="348" t="n"/>
+      <c r="AA7" s="348" t="n"/>
+      <c r="AB7" s="348" t="n"/>
+      <c r="AC7" s="348" t="n"/>
+      <c r="AD7" s="348" t="n"/>
+      <c r="AE7" s="348" t="n"/>
+      <c r="AF7" s="348" t="n"/>
+      <c r="AG7" s="348" t="n"/>
+      <c r="AH7" s="348" t="n"/>
+      <c r="AI7" s="348" t="n"/>
+      <c r="AJ7" s="348" t="n"/>
+      <c r="AK7" s="348" t="n"/>
+      <c r="AL7" s="348" t="n"/>
+      <c r="AM7" s="348" t="n"/>
+      <c r="AN7" s="348" t="n"/>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="318" t="inlineStr">
+      <c r="A8" s="397" t="inlineStr">
         <is>
           <t>WI-716</t>
         </is>
       </c>
-      <c r="B8" s="319" t="inlineStr">
+      <c r="B8" s="398" t="inlineStr">
         <is>
           <t>WI-716 — Lắp sạch, tương thích chân không, bagging và bảo quản cho Job đặc biệt</t>
         </is>
       </c>
-      <c r="C8" s="319" t="inlineStr">
+      <c r="C8" s="398" t="inlineStr">
         <is>
           <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/02-Work-Instructions/07-WI-700/wi-716-vacuum-compatible-clean-build-and-bagging.html</t>
         </is>
       </c>
+      <c r="D8" s="399" t="n"/>
+      <c r="E8" s="399" t="n"/>
+      <c r="F8" s="399" t="n"/>
+      <c r="G8" s="399" t="n"/>
+      <c r="H8" s="399" t="n"/>
+      <c r="I8" s="399" t="n"/>
+      <c r="J8" s="399" t="n"/>
+      <c r="K8" s="399" t="n"/>
+      <c r="L8" s="399" t="n"/>
+      <c r="M8" s="399" t="n"/>
+      <c r="N8" s="399" t="n"/>
+      <c r="O8" s="399" t="n"/>
+      <c r="P8" s="399" t="n"/>
+      <c r="Q8" s="399" t="n"/>
+      <c r="R8" s="399" t="n"/>
+      <c r="S8" s="399" t="n"/>
+      <c r="T8" s="399" t="n"/>
+      <c r="U8" s="399" t="n"/>
+      <c r="V8" s="399" t="n"/>
+      <c r="W8" s="399" t="n"/>
+      <c r="X8" s="399" t="n"/>
+      <c r="Y8" s="399" t="n"/>
+      <c r="Z8" s="399" t="n"/>
+      <c r="AA8" s="399" t="n"/>
+      <c r="AB8" s="399" t="n"/>
+      <c r="AC8" s="399" t="n"/>
+      <c r="AD8" s="399" t="n"/>
+      <c r="AE8" s="399" t="n"/>
+      <c r="AF8" s="399" t="n"/>
+      <c r="AG8" s="399" t="n"/>
+      <c r="AH8" s="399" t="n"/>
+      <c r="AI8" s="399" t="n"/>
+      <c r="AJ8" s="399" t="n"/>
+      <c r="AK8" s="399" t="n"/>
+      <c r="AL8" s="399" t="n"/>
+      <c r="AM8" s="399" t="n"/>
+      <c r="AN8" s="399" t="n"/>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="318" t="inlineStr">
+      <c r="A9" s="397" t="inlineStr">
         <is>
           <t>ANNEX-QA-007</t>
         </is>
       </c>
-      <c r="B9" s="319" t="inlineStr">
+      <c r="B9" s="398" t="inlineStr">
         <is>
           <t>ANNEX-QA-007 — Chuẩn bề mặt, độ sạch, tương thích chân không, rò rỉ và xử lý đặc biệt</t>
         </is>
       </c>
-      <c r="C9" s="319" t="inlineStr">
+      <c r="C9" s="398" t="inlineStr">
         <is>
           <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/03-Reference/02-ANNEX-Standards/annex-qa-007-surface-finish-vacuum-compatibility.html</t>
         </is>
       </c>
+      <c r="D9" s="399" t="n"/>
+      <c r="E9" s="399" t="n"/>
+      <c r="F9" s="399" t="n"/>
+      <c r="G9" s="399" t="n"/>
+      <c r="H9" s="399" t="n"/>
+      <c r="I9" s="399" t="n"/>
+      <c r="J9" s="399" t="n"/>
+      <c r="K9" s="399" t="n"/>
+      <c r="L9" s="399" t="n"/>
+      <c r="M9" s="399" t="n"/>
+      <c r="N9" s="399" t="n"/>
+      <c r="O9" s="399" t="n"/>
+      <c r="P9" s="399" t="n"/>
+      <c r="Q9" s="399" t="n"/>
+      <c r="R9" s="399" t="n"/>
+      <c r="S9" s="399" t="n"/>
+      <c r="T9" s="399" t="n"/>
+      <c r="U9" s="399" t="n"/>
+      <c r="V9" s="399" t="n"/>
+      <c r="W9" s="399" t="n"/>
+      <c r="X9" s="399" t="n"/>
+      <c r="Y9" s="399" t="n"/>
+      <c r="Z9" s="399" t="n"/>
+      <c r="AA9" s="399" t="n"/>
+      <c r="AB9" s="399" t="n"/>
+      <c r="AC9" s="399" t="n"/>
+      <c r="AD9" s="399" t="n"/>
+      <c r="AE9" s="399" t="n"/>
+      <c r="AF9" s="399" t="n"/>
+      <c r="AG9" s="399" t="n"/>
+      <c r="AH9" s="399" t="n"/>
+      <c r="AI9" s="399" t="n"/>
+      <c r="AJ9" s="399" t="n"/>
+      <c r="AK9" s="399" t="n"/>
+      <c r="AL9" s="399" t="n"/>
+      <c r="AM9" s="399" t="n"/>
+      <c r="AN9" s="399" t="n"/>
     </row>
     <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="318" t="inlineStr">
+      <c r="A10" s="397" t="inlineStr">
         <is>
           <t>ANNEX-WHS-001</t>
         </is>
       </c>
-      <c r="B10" s="319" t="inlineStr">
+      <c r="B10" s="398" t="inlineStr">
         <is>
           <t>ANNEX-WHS-001 — Quy cách đóng gói, nhãn, bảo quản và bằng chứng gói hàng</t>
         </is>
       </c>
-      <c r="C10" s="319" t="inlineStr">
+      <c r="C10" s="398" t="inlineStr">
         <is>
           <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/03-Reference/02-ANNEX-Standards/annex-whs-001-packaging-labeling-spec.html</t>
         </is>
       </c>
+      <c r="D10" s="399" t="n"/>
+      <c r="E10" s="399" t="n"/>
+      <c r="F10" s="399" t="n"/>
+      <c r="G10" s="399" t="n"/>
+      <c r="H10" s="399" t="n"/>
+      <c r="I10" s="399" t="n"/>
+      <c r="J10" s="399" t="n"/>
+      <c r="K10" s="399" t="n"/>
+      <c r="L10" s="399" t="n"/>
+      <c r="M10" s="399" t="n"/>
+      <c r="N10" s="399" t="n"/>
+      <c r="O10" s="399" t="n"/>
+      <c r="P10" s="399" t="n"/>
+      <c r="Q10" s="399" t="n"/>
+      <c r="R10" s="399" t="n"/>
+      <c r="S10" s="399" t="n"/>
+      <c r="T10" s="399" t="n"/>
+      <c r="U10" s="399" t="n"/>
+      <c r="V10" s="399" t="n"/>
+      <c r="W10" s="399" t="n"/>
+      <c r="X10" s="399" t="n"/>
+      <c r="Y10" s="399" t="n"/>
+      <c r="Z10" s="399" t="n"/>
+      <c r="AA10" s="399" t="n"/>
+      <c r="AB10" s="399" t="n"/>
+      <c r="AC10" s="399" t="n"/>
+      <c r="AD10" s="399" t="n"/>
+      <c r="AE10" s="399" t="n"/>
+      <c r="AF10" s="399" t="n"/>
+      <c r="AG10" s="399" t="n"/>
+      <c r="AH10" s="399" t="n"/>
+      <c r="AI10" s="399" t="n"/>
+      <c r="AJ10" s="399" t="n"/>
+      <c r="AK10" s="399" t="n"/>
+      <c r="AL10" s="399" t="n"/>
+      <c r="AM10" s="399" t="n"/>
+      <c r="AN10" s="399" t="n"/>
     </row>
     <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="318" t="inlineStr">
+      <c r="A11" s="397" t="inlineStr">
         <is>
           <t>Open When</t>
         </is>
       </c>
-      <c r="B11" s="319" t="inlineStr">
+      <c r="B11" s="398" t="inlineStr">
         <is>
           <t>Open before the controlled activity starts or before the release decision is taken. Do not populate it retrospectively after execution has already moved forward.</t>
         </is>
       </c>
-      <c r="C11" s="319" t="inlineStr">
+      <c r="C11" s="398" t="inlineStr">
         <is>
           <t>Operational trigger</t>
         </is>
       </c>
+      <c r="D11" s="399" t="n"/>
+      <c r="E11" s="399" t="n"/>
+      <c r="F11" s="399" t="n"/>
+      <c r="G11" s="399" t="n"/>
+      <c r="H11" s="399" t="n"/>
+      <c r="I11" s="399" t="n"/>
+      <c r="J11" s="399" t="n"/>
+      <c r="K11" s="399" t="n"/>
+      <c r="L11" s="399" t="n"/>
+      <c r="M11" s="399" t="n"/>
+      <c r="N11" s="399" t="n"/>
+      <c r="O11" s="399" t="n"/>
+      <c r="P11" s="399" t="n"/>
+      <c r="Q11" s="399" t="n"/>
+      <c r="R11" s="399" t="n"/>
+      <c r="S11" s="399" t="n"/>
+      <c r="T11" s="399" t="n"/>
+      <c r="U11" s="399" t="n"/>
+      <c r="V11" s="399" t="n"/>
+      <c r="W11" s="399" t="n"/>
+      <c r="X11" s="399" t="n"/>
+      <c r="Y11" s="399" t="n"/>
+      <c r="Z11" s="399" t="n"/>
+      <c r="AA11" s="399" t="n"/>
+      <c r="AB11" s="399" t="n"/>
+      <c r="AC11" s="399" t="n"/>
+      <c r="AD11" s="399" t="n"/>
+      <c r="AE11" s="399" t="n"/>
+      <c r="AF11" s="399" t="n"/>
+      <c r="AG11" s="399" t="n"/>
+      <c r="AH11" s="399" t="n"/>
+      <c r="AI11" s="399" t="n"/>
+      <c r="AJ11" s="399" t="n"/>
+      <c r="AK11" s="399" t="n"/>
+      <c r="AL11" s="399" t="n"/>
+      <c r="AM11" s="399" t="n"/>
+      <c r="AN11" s="399" t="n"/>
     </row>
     <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="318" t="inlineStr">
+      <c r="A12" s="397" t="inlineStr">
         <is>
           <t>Close When</t>
         </is>
       </c>
-      <c r="B12" s="319" t="inlineStr">
+      <c r="B12" s="398" t="inlineStr">
         <is>
           <t>Close only after the final gate disposition, result or release status is recorded, all conditions are assigned to an owner, and the evidence package reference is complete.</t>
         </is>
       </c>
-      <c r="C12" s="319" t="inlineStr">
+      <c r="C12" s="398" t="inlineStr">
         <is>
           <t>Release / closure rule</t>
         </is>
       </c>
+      <c r="D12" s="399" t="n"/>
+      <c r="E12" s="399" t="n"/>
+      <c r="F12" s="399" t="n"/>
+      <c r="G12" s="399" t="n"/>
+      <c r="H12" s="399" t="n"/>
+      <c r="I12" s="399" t="n"/>
+      <c r="J12" s="399" t="n"/>
+      <c r="K12" s="399" t="n"/>
+      <c r="L12" s="399" t="n"/>
+      <c r="M12" s="399" t="n"/>
+      <c r="N12" s="399" t="n"/>
+      <c r="O12" s="399" t="n"/>
+      <c r="P12" s="399" t="n"/>
+      <c r="Q12" s="399" t="n"/>
+      <c r="R12" s="399" t="n"/>
+      <c r="S12" s="399" t="n"/>
+      <c r="T12" s="399" t="n"/>
+      <c r="U12" s="399" t="n"/>
+      <c r="V12" s="399" t="n"/>
+      <c r="W12" s="399" t="n"/>
+      <c r="X12" s="399" t="n"/>
+      <c r="Y12" s="399" t="n"/>
+      <c r="Z12" s="399" t="n"/>
+      <c r="AA12" s="399" t="n"/>
+      <c r="AB12" s="399" t="n"/>
+      <c r="AC12" s="399" t="n"/>
+      <c r="AD12" s="399" t="n"/>
+      <c r="AE12" s="399" t="n"/>
+      <c r="AF12" s="399" t="n"/>
+      <c r="AG12" s="399" t="n"/>
+      <c r="AH12" s="399" t="n"/>
+      <c r="AI12" s="399" t="n"/>
+      <c r="AJ12" s="399" t="n"/>
+      <c r="AK12" s="399" t="n"/>
+      <c r="AL12" s="399" t="n"/>
+      <c r="AM12" s="399" t="n"/>
+      <c r="AN12" s="399" t="n"/>
     </row>
     <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="318" t="n"/>
-      <c r="B13" s="319" t="n"/>
-      <c r="C13" s="319" t="n"/>
+      <c r="A13" s="397" t="n"/>
+      <c r="B13" s="398" t="n"/>
+      <c r="C13" s="398" t="n"/>
+      <c r="D13" s="399" t="n"/>
+      <c r="E13" s="399" t="n"/>
+      <c r="F13" s="399" t="n"/>
+      <c r="G13" s="399" t="n"/>
+      <c r="H13" s="399" t="n"/>
+      <c r="I13" s="399" t="n"/>
+      <c r="J13" s="399" t="n"/>
+      <c r="K13" s="399" t="n"/>
+      <c r="L13" s="399" t="n"/>
+      <c r="M13" s="399" t="n"/>
+      <c r="N13" s="399" t="n"/>
+      <c r="O13" s="399" t="n"/>
+      <c r="P13" s="399" t="n"/>
+      <c r="Q13" s="399" t="n"/>
+      <c r="R13" s="399" t="n"/>
+      <c r="S13" s="399" t="n"/>
+      <c r="T13" s="399" t="n"/>
+      <c r="U13" s="399" t="n"/>
+      <c r="V13" s="399" t="n"/>
+      <c r="W13" s="399" t="n"/>
+      <c r="X13" s="399" t="n"/>
+      <c r="Y13" s="399" t="n"/>
+      <c r="Z13" s="399" t="n"/>
+      <c r="AA13" s="399" t="n"/>
+      <c r="AB13" s="399" t="n"/>
+      <c r="AC13" s="399" t="n"/>
+      <c r="AD13" s="399" t="n"/>
+      <c r="AE13" s="399" t="n"/>
+      <c r="AF13" s="399" t="n"/>
+      <c r="AG13" s="399" t="n"/>
+      <c r="AH13" s="399" t="n"/>
+      <c r="AI13" s="399" t="n"/>
+      <c r="AJ13" s="399" t="n"/>
+      <c r="AK13" s="399" t="n"/>
+      <c r="AL13" s="399" t="n"/>
+      <c r="AM13" s="399" t="n"/>
+      <c r="AN13" s="399" t="n"/>
     </row>
     <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="318" t="n"/>
-      <c r="B14" s="319" t="n"/>
-      <c r="C14" s="319" t="n"/>
+      <c r="A14" s="397" t="n"/>
+      <c r="B14" s="398" t="n"/>
+      <c r="C14" s="398" t="n"/>
+      <c r="D14" s="399" t="n"/>
+      <c r="E14" s="399" t="n"/>
+      <c r="F14" s="399" t="n"/>
+      <c r="G14" s="399" t="n"/>
+      <c r="H14" s="399" t="n"/>
+      <c r="I14" s="399" t="n"/>
+      <c r="J14" s="399" t="n"/>
+      <c r="K14" s="399" t="n"/>
+      <c r="L14" s="399" t="n"/>
+      <c r="M14" s="399" t="n"/>
+      <c r="N14" s="399" t="n"/>
+      <c r="O14" s="399" t="n"/>
+      <c r="P14" s="399" t="n"/>
+      <c r="Q14" s="399" t="n"/>
+      <c r="R14" s="399" t="n"/>
+      <c r="S14" s="399" t="n"/>
+      <c r="T14" s="399" t="n"/>
+      <c r="U14" s="399" t="n"/>
+      <c r="V14" s="399" t="n"/>
+      <c r="W14" s="399" t="n"/>
+      <c r="X14" s="399" t="n"/>
+      <c r="Y14" s="399" t="n"/>
+      <c r="Z14" s="399" t="n"/>
+      <c r="AA14" s="399" t="n"/>
+      <c r="AB14" s="399" t="n"/>
+      <c r="AC14" s="399" t="n"/>
+      <c r="AD14" s="399" t="n"/>
+      <c r="AE14" s="399" t="n"/>
+      <c r="AF14" s="399" t="n"/>
+      <c r="AG14" s="399" t="n"/>
+      <c r="AH14" s="399" t="n"/>
+      <c r="AI14" s="399" t="n"/>
+      <c r="AJ14" s="399" t="n"/>
+      <c r="AK14" s="399" t="n"/>
+      <c r="AL14" s="399" t="n"/>
+      <c r="AM14" s="399" t="n"/>
+      <c r="AN14" s="399" t="n"/>
     </row>
     <row r="15" ht="20" customHeight="1"/>
     <row r="16" ht="20" customHeight="1"/>
@@ -7681,7 +9412,8 @@
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.197" right="0.197" top="0.197" bottom="0.197" header="0.1" footer="0.1"/>
+  <pageSetup paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -7691,30 +9423,96 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:AN12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="52" customWidth="1" min="2" max="2"/>
-    <col width="65" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="24" customWidth="1" min="7" max="7"/>
+    <col width="2.33" customWidth="1" min="1" max="1"/>
+    <col width="2.33" customWidth="1" min="2" max="2"/>
+    <col width="2.33" customWidth="1" min="3" max="3"/>
+    <col width="2.33" customWidth="1" min="4" max="4"/>
+    <col width="2.33" customWidth="1" min="5" max="5"/>
+    <col width="2.33" customWidth="1" min="6" max="6"/>
+    <col width="2.33" customWidth="1" min="7" max="7"/>
+    <col width="2.33" customWidth="1" min="8" max="8"/>
+    <col width="2.33" customWidth="1" min="9" max="9"/>
+    <col width="2.33" customWidth="1" min="10" max="10"/>
+    <col width="2.33" customWidth="1" min="11" max="11"/>
+    <col width="2.33" customWidth="1" min="12" max="12"/>
+    <col width="2.33" customWidth="1" min="13" max="13"/>
+    <col width="2.33" customWidth="1" min="14" max="14"/>
+    <col width="2.33" customWidth="1" min="15" max="15"/>
+    <col width="2.33" customWidth="1" min="16" max="16"/>
+    <col width="2.33" customWidth="1" min="17" max="17"/>
+    <col width="2.33" customWidth="1" min="18" max="18"/>
+    <col width="2.33" customWidth="1" min="19" max="19"/>
+    <col width="2.33" customWidth="1" min="20" max="20"/>
+    <col width="2.33" customWidth="1" min="21" max="21"/>
+    <col width="2.33" customWidth="1" min="22" max="22"/>
+    <col width="2.33" customWidth="1" min="23" max="23"/>
+    <col width="2.33" customWidth="1" min="24" max="24"/>
+    <col width="2.33" customWidth="1" min="25" max="25"/>
+    <col width="2.33" customWidth="1" min="26" max="26"/>
+    <col width="2.33" customWidth="1" min="27" max="27"/>
+    <col width="2.33" customWidth="1" min="28" max="28"/>
+    <col width="2.33" customWidth="1" min="29" max="29"/>
+    <col width="2.33" customWidth="1" min="30" max="30"/>
+    <col width="2.33" customWidth="1" min="31" max="31"/>
+    <col width="2.33" customWidth="1" min="32" max="32"/>
+    <col width="2.33" customWidth="1" min="33" max="33"/>
+    <col width="2.33" customWidth="1" min="34" max="34"/>
+    <col width="2.33" customWidth="1" min="35" max="35"/>
+    <col width="2.33" customWidth="1" min="36" max="36"/>
+    <col width="2.33" customWidth="1" min="37" max="37"/>
+    <col width="2.33" customWidth="1" min="38" max="38"/>
+    <col width="2.33" customWidth="1" min="39" max="39"/>
+    <col width="2.33" customWidth="1" min="40" max="40"/>
   </cols>
   <sheetData>
     <row r="1" ht="18" customHeight="1">
-      <c r="A1" s="337" t="inlineStr">
+      <c r="A1" s="393" t="inlineStr">
         <is>
           <t>Evidence Reference / Attachment Guidance</t>
         </is>
       </c>
-      <c r="B1" s="285" t="n"/>
-      <c r="C1" s="285" t="n"/>
-      <c r="D1" s="285" t="n"/>
-      <c r="E1" s="285" t="n"/>
-      <c r="F1" s="285" t="n"/>
-      <c r="G1" s="286" t="n"/>
+      <c r="B1" s="423" t="n"/>
+      <c r="C1" s="423" t="n"/>
+      <c r="D1" s="423" t="n"/>
+      <c r="E1" s="423" t="n"/>
+      <c r="F1" s="423" t="n"/>
+      <c r="G1" s="424" t="n"/>
+      <c r="H1" s="348" t="n"/>
+      <c r="I1" s="348" t="n"/>
+      <c r="J1" s="348" t="n"/>
+      <c r="K1" s="348" t="n"/>
+      <c r="L1" s="348" t="n"/>
+      <c r="M1" s="348" t="n"/>
+      <c r="N1" s="348" t="n"/>
+      <c r="O1" s="348" t="n"/>
+      <c r="P1" s="348" t="n"/>
+      <c r="Q1" s="348" t="n"/>
+      <c r="R1" s="348" t="n"/>
+      <c r="S1" s="348" t="n"/>
+      <c r="T1" s="348" t="n"/>
+      <c r="U1" s="348" t="n"/>
+      <c r="V1" s="348" t="n"/>
+      <c r="W1" s="348" t="n"/>
+      <c r="X1" s="348" t="n"/>
+      <c r="Y1" s="348" t="n"/>
+      <c r="Z1" s="348" t="n"/>
+      <c r="AA1" s="348" t="n"/>
+      <c r="AB1" s="348" t="n"/>
+      <c r="AC1" s="348" t="n"/>
+      <c r="AD1" s="348" t="n"/>
+      <c r="AE1" s="348" t="n"/>
+      <c r="AF1" s="348" t="n"/>
+      <c r="AG1" s="348" t="n"/>
+      <c r="AH1" s="348" t="n"/>
+      <c r="AI1" s="348" t="n"/>
+      <c r="AJ1" s="348" t="n"/>
+      <c r="AK1" s="348" t="n"/>
+      <c r="AL1" s="348" t="n"/>
+      <c r="AM1" s="348" t="n"/>
+      <c r="AN1" s="348" t="n"/>
     </row>
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="338" t="inlineStr">
@@ -7722,49 +9520,197 @@
           <t>Use controlled evidence package references; do not free-type vague placeholders.</t>
         </is>
       </c>
+      <c r="H2" s="348" t="n"/>
+      <c r="I2" s="348" t="n"/>
+      <c r="J2" s="348" t="n"/>
+      <c r="K2" s="348" t="n"/>
+      <c r="L2" s="348" t="n"/>
+      <c r="M2" s="348" t="n"/>
+      <c r="N2" s="348" t="n"/>
+      <c r="O2" s="348" t="n"/>
+      <c r="P2" s="348" t="n"/>
+      <c r="Q2" s="348" t="n"/>
+      <c r="R2" s="348" t="n"/>
+      <c r="S2" s="348" t="n"/>
+      <c r="T2" s="348" t="n"/>
+      <c r="U2" s="348" t="n"/>
+      <c r="V2" s="348" t="n"/>
+      <c r="W2" s="348" t="n"/>
+      <c r="X2" s="348" t="n"/>
+      <c r="Y2" s="348" t="n"/>
+      <c r="Z2" s="348" t="n"/>
+      <c r="AA2" s="348" t="n"/>
+      <c r="AB2" s="348" t="n"/>
+      <c r="AC2" s="348" t="n"/>
+      <c r="AD2" s="348" t="n"/>
+      <c r="AE2" s="348" t="n"/>
+      <c r="AF2" s="348" t="n"/>
+      <c r="AG2" s="348" t="n"/>
+      <c r="AH2" s="348" t="n"/>
+      <c r="AI2" s="348" t="n"/>
+      <c r="AJ2" s="348" t="n"/>
+      <c r="AK2" s="348" t="n"/>
+      <c r="AL2" s="348" t="n"/>
+      <c r="AM2" s="348" t="n"/>
+      <c r="AN2" s="348" t="n"/>
     </row>
-    <row r="3" ht="18" customHeight="1"/>
+    <row r="3" ht="18" customHeight="1">
+      <c r="A3" s="348" t="n"/>
+      <c r="B3" s="348" t="n"/>
+      <c r="C3" s="348" t="n"/>
+      <c r="D3" s="348" t="n"/>
+      <c r="E3" s="348" t="n"/>
+      <c r="F3" s="348" t="n"/>
+      <c r="G3" s="348" t="n"/>
+      <c r="H3" s="348" t="n"/>
+      <c r="I3" s="348" t="n"/>
+      <c r="J3" s="348" t="n"/>
+      <c r="K3" s="348" t="n"/>
+      <c r="L3" s="348" t="n"/>
+      <c r="M3" s="348" t="n"/>
+      <c r="N3" s="348" t="n"/>
+      <c r="O3" s="348" t="n"/>
+      <c r="P3" s="348" t="n"/>
+      <c r="Q3" s="348" t="n"/>
+      <c r="R3" s="348" t="n"/>
+      <c r="S3" s="348" t="n"/>
+      <c r="T3" s="348" t="n"/>
+      <c r="U3" s="348" t="n"/>
+      <c r="V3" s="348" t="n"/>
+      <c r="W3" s="348" t="n"/>
+      <c r="X3" s="348" t="n"/>
+      <c r="Y3" s="348" t="n"/>
+      <c r="Z3" s="348" t="n"/>
+      <c r="AA3" s="348" t="n"/>
+      <c r="AB3" s="348" t="n"/>
+      <c r="AC3" s="348" t="n"/>
+      <c r="AD3" s="348" t="n"/>
+      <c r="AE3" s="348" t="n"/>
+      <c r="AF3" s="348" t="n"/>
+      <c r="AG3" s="348" t="n"/>
+      <c r="AH3" s="348" t="n"/>
+      <c r="AI3" s="348" t="n"/>
+      <c r="AJ3" s="348" t="n"/>
+      <c r="AK3" s="348" t="n"/>
+      <c r="AL3" s="348" t="n"/>
+      <c r="AM3" s="348" t="n"/>
+      <c r="AN3" s="348" t="n"/>
+    </row>
     <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="339" t="inlineStr">
+      <c r="A4" s="394" t="inlineStr">
         <is>
           <t>Field</t>
         </is>
       </c>
-      <c r="B4" s="339" t="inlineStr">
+      <c r="B4" s="394" t="inlineStr">
         <is>
           <t>Value / Reference</t>
         </is>
       </c>
-      <c r="C4" s="339" t="inlineStr">
+      <c r="C4" s="394" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
+      <c r="D4" s="348" t="n"/>
+      <c r="E4" s="348" t="n"/>
+      <c r="F4" s="348" t="n"/>
+      <c r="G4" s="348" t="n"/>
+      <c r="H4" s="348" t="n"/>
+      <c r="I4" s="348" t="n"/>
+      <c r="J4" s="348" t="n"/>
+      <c r="K4" s="348" t="n"/>
+      <c r="L4" s="348" t="n"/>
+      <c r="M4" s="348" t="n"/>
+      <c r="N4" s="348" t="n"/>
+      <c r="O4" s="348" t="n"/>
+      <c r="P4" s="348" t="n"/>
+      <c r="Q4" s="348" t="n"/>
+      <c r="R4" s="348" t="n"/>
+      <c r="S4" s="348" t="n"/>
+      <c r="T4" s="348" t="n"/>
+      <c r="U4" s="348" t="n"/>
+      <c r="V4" s="348" t="n"/>
+      <c r="W4" s="348" t="n"/>
+      <c r="X4" s="348" t="n"/>
+      <c r="Y4" s="348" t="n"/>
+      <c r="Z4" s="348" t="n"/>
+      <c r="AA4" s="348" t="n"/>
+      <c r="AB4" s="348" t="n"/>
+      <c r="AC4" s="348" t="n"/>
+      <c r="AD4" s="348" t="n"/>
+      <c r="AE4" s="348" t="n"/>
+      <c r="AF4" s="348" t="n"/>
+      <c r="AG4" s="348" t="n"/>
+      <c r="AH4" s="348" t="n"/>
+      <c r="AI4" s="348" t="n"/>
+      <c r="AJ4" s="348" t="n"/>
+      <c r="AK4" s="348" t="n"/>
+      <c r="AL4" s="348" t="n"/>
+      <c r="AM4" s="348" t="n"/>
+      <c r="AN4" s="348" t="n"/>
     </row>
     <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="318" t="inlineStr">
+      <c r="A5" s="395" t="inlineStr">
         <is>
           <t>Source of Truth</t>
         </is>
       </c>
-      <c r="B5" s="319" t="inlineStr">
+      <c r="B5" s="396" t="inlineStr">
         <is>
           <t>M365 evidence / shared workbook</t>
         </is>
       </c>
-      <c r="C5" s="319" t="inlineStr">
+      <c r="C5" s="396" t="inlineStr">
         <is>
           <t>Do not duplicate ERP/M365/ANNEX master data.</t>
         </is>
       </c>
+      <c r="D5" s="348" t="n"/>
+      <c r="E5" s="348" t="n"/>
+      <c r="F5" s="348" t="n"/>
+      <c r="G5" s="348" t="n"/>
+      <c r="H5" s="348" t="n"/>
+      <c r="I5" s="348" t="n"/>
+      <c r="J5" s="348" t="n"/>
+      <c r="K5" s="348" t="n"/>
+      <c r="L5" s="348" t="n"/>
+      <c r="M5" s="348" t="n"/>
+      <c r="N5" s="348" t="n"/>
+      <c r="O5" s="348" t="n"/>
+      <c r="P5" s="348" t="n"/>
+      <c r="Q5" s="348" t="n"/>
+      <c r="R5" s="348" t="n"/>
+      <c r="S5" s="348" t="n"/>
+      <c r="T5" s="348" t="n"/>
+      <c r="U5" s="348" t="n"/>
+      <c r="V5" s="348" t="n"/>
+      <c r="W5" s="348" t="n"/>
+      <c r="X5" s="348" t="n"/>
+      <c r="Y5" s="348" t="n"/>
+      <c r="Z5" s="348" t="n"/>
+      <c r="AA5" s="348" t="n"/>
+      <c r="AB5" s="348" t="n"/>
+      <c r="AC5" s="348" t="n"/>
+      <c r="AD5" s="348" t="n"/>
+      <c r="AE5" s="348" t="n"/>
+      <c r="AF5" s="348" t="n"/>
+      <c r="AG5" s="348" t="n"/>
+      <c r="AH5" s="348" t="n"/>
+      <c r="AI5" s="348" t="n"/>
+      <c r="AJ5" s="348" t="n"/>
+      <c r="AK5" s="348" t="n"/>
+      <c r="AL5" s="348" t="n"/>
+      <c r="AM5" s="348" t="n"/>
+      <c r="AN5" s="348" t="n"/>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="318" t="inlineStr">
+      <c r="A6" s="395" t="inlineStr">
         <is>
           <t>Cross-Reference Boundary</t>
         </is>
       </c>
-      <c r="B6" s="319" t="inlineStr">
+      <c r="B6" s="396" t="inlineStr">
         <is>
           <t>This form does not replace SOP-702; it records the evidence, data or decision required by that SOP.
 Detailed task execution belongs in WI-716; this form captures results, checks, decisions or exceptions only.
@@ -7772,7 +9718,7 @@
 System-of-record / source-of-truth boundary: M365 evidence / shared workbook. If the master data already live there, reference or import them; do not re-key without need.</t>
         </is>
       </c>
-      <c r="C6" s="319" t="inlineStr">
+      <c r="C6" s="396" t="inlineStr">
         <is>
           <t>This form does not replace SOP-702; it records the evidence, data or decision required by that SOP.
 Detailed task execution belongs in WI-716; this form captures results, checks, decisions or exceptions only.
@@ -7780,108 +9726,367 @@
 System-of-record / source-of-truth boundary: M365 evidence / shared workbook. If the master data already live there, reference or import them; do not re-key without need.</t>
         </is>
       </c>
+      <c r="D6" s="348" t="n"/>
+      <c r="E6" s="348" t="n"/>
+      <c r="F6" s="348" t="n"/>
+      <c r="G6" s="348" t="n"/>
+      <c r="H6" s="348" t="n"/>
+      <c r="I6" s="348" t="n"/>
+      <c r="J6" s="348" t="n"/>
+      <c r="K6" s="348" t="n"/>
+      <c r="L6" s="348" t="n"/>
+      <c r="M6" s="348" t="n"/>
+      <c r="N6" s="348" t="n"/>
+      <c r="O6" s="348" t="n"/>
+      <c r="P6" s="348" t="n"/>
+      <c r="Q6" s="348" t="n"/>
+      <c r="R6" s="348" t="n"/>
+      <c r="S6" s="348" t="n"/>
+      <c r="T6" s="348" t="n"/>
+      <c r="U6" s="348" t="n"/>
+      <c r="V6" s="348" t="n"/>
+      <c r="W6" s="348" t="n"/>
+      <c r="X6" s="348" t="n"/>
+      <c r="Y6" s="348" t="n"/>
+      <c r="Z6" s="348" t="n"/>
+      <c r="AA6" s="348" t="n"/>
+      <c r="AB6" s="348" t="n"/>
+      <c r="AC6" s="348" t="n"/>
+      <c r="AD6" s="348" t="n"/>
+      <c r="AE6" s="348" t="n"/>
+      <c r="AF6" s="348" t="n"/>
+      <c r="AG6" s="348" t="n"/>
+      <c r="AH6" s="348" t="n"/>
+      <c r="AI6" s="348" t="n"/>
+      <c r="AJ6" s="348" t="n"/>
+      <c r="AK6" s="348" t="n"/>
+      <c r="AL6" s="348" t="n"/>
+      <c r="AM6" s="348" t="n"/>
+      <c r="AN6" s="348" t="n"/>
     </row>
     <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="318" t="inlineStr">
+      <c r="A7" s="395" t="inlineStr">
         <is>
           <t>SOP-702</t>
         </is>
       </c>
-      <c r="B7" s="319" t="inlineStr">
+      <c r="B7" s="396" t="inlineStr">
         <is>
           <t>SOP-702 — Kiểm soát nhiễm bẩn, xác nhận độ sạch và tuyến đóng gói sạch | HESEM QMS</t>
         </is>
       </c>
-      <c r="C7" s="319" t="inlineStr">
+      <c r="C7" s="396" t="inlineStr">
         <is>
           <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/01-SOPs/07-SOP-700/sop-702-contamination-control-and-cleanliness.html</t>
         </is>
       </c>
+      <c r="D7" s="348" t="n"/>
+      <c r="E7" s="348" t="n"/>
+      <c r="F7" s="348" t="n"/>
+      <c r="G7" s="348" t="n"/>
+      <c r="H7" s="348" t="n"/>
+      <c r="I7" s="348" t="n"/>
+      <c r="J7" s="348" t="n"/>
+      <c r="K7" s="348" t="n"/>
+      <c r="L7" s="348" t="n"/>
+      <c r="M7" s="348" t="n"/>
+      <c r="N7" s="348" t="n"/>
+      <c r="O7" s="348" t="n"/>
+      <c r="P7" s="348" t="n"/>
+      <c r="Q7" s="348" t="n"/>
+      <c r="R7" s="348" t="n"/>
+      <c r="S7" s="348" t="n"/>
+      <c r="T7" s="348" t="n"/>
+      <c r="U7" s="348" t="n"/>
+      <c r="V7" s="348" t="n"/>
+      <c r="W7" s="348" t="n"/>
+      <c r="X7" s="348" t="n"/>
+      <c r="Y7" s="348" t="n"/>
+      <c r="Z7" s="348" t="n"/>
+      <c r="AA7" s="348" t="n"/>
+      <c r="AB7" s="348" t="n"/>
+      <c r="AC7" s="348" t="n"/>
+      <c r="AD7" s="348" t="n"/>
+      <c r="AE7" s="348" t="n"/>
+      <c r="AF7" s="348" t="n"/>
+      <c r="AG7" s="348" t="n"/>
+      <c r="AH7" s="348" t="n"/>
+      <c r="AI7" s="348" t="n"/>
+      <c r="AJ7" s="348" t="n"/>
+      <c r="AK7" s="348" t="n"/>
+      <c r="AL7" s="348" t="n"/>
+      <c r="AM7" s="348" t="n"/>
+      <c r="AN7" s="348" t="n"/>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="318" t="inlineStr">
+      <c r="A8" s="397" t="inlineStr">
         <is>
           <t>WI-716</t>
         </is>
       </c>
-      <c r="B8" s="319" t="inlineStr">
+      <c r="B8" s="398" t="inlineStr">
         <is>
           <t>WI-716 — Lắp sạch, tương thích chân không, bagging và bảo quản cho Job đặc biệt</t>
         </is>
       </c>
-      <c r="C8" s="319" t="inlineStr">
+      <c r="C8" s="398" t="inlineStr">
         <is>
           <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/02-Work-Instructions/07-WI-700/wi-716-vacuum-compatible-clean-build-and-bagging.html</t>
         </is>
       </c>
+      <c r="D8" s="399" t="n"/>
+      <c r="E8" s="399" t="n"/>
+      <c r="F8" s="399" t="n"/>
+      <c r="G8" s="399" t="n"/>
+      <c r="H8" s="399" t="n"/>
+      <c r="I8" s="399" t="n"/>
+      <c r="J8" s="399" t="n"/>
+      <c r="K8" s="399" t="n"/>
+      <c r="L8" s="399" t="n"/>
+      <c r="M8" s="399" t="n"/>
+      <c r="N8" s="399" t="n"/>
+      <c r="O8" s="399" t="n"/>
+      <c r="P8" s="399" t="n"/>
+      <c r="Q8" s="399" t="n"/>
+      <c r="R8" s="399" t="n"/>
+      <c r="S8" s="399" t="n"/>
+      <c r="T8" s="399" t="n"/>
+      <c r="U8" s="399" t="n"/>
+      <c r="V8" s="399" t="n"/>
+      <c r="W8" s="399" t="n"/>
+      <c r="X8" s="399" t="n"/>
+      <c r="Y8" s="399" t="n"/>
+      <c r="Z8" s="399" t="n"/>
+      <c r="AA8" s="399" t="n"/>
+      <c r="AB8" s="399" t="n"/>
+      <c r="AC8" s="399" t="n"/>
+      <c r="AD8" s="399" t="n"/>
+      <c r="AE8" s="399" t="n"/>
+      <c r="AF8" s="399" t="n"/>
+      <c r="AG8" s="399" t="n"/>
+      <c r="AH8" s="399" t="n"/>
+      <c r="AI8" s="399" t="n"/>
+      <c r="AJ8" s="399" t="n"/>
+      <c r="AK8" s="399" t="n"/>
+      <c r="AL8" s="399" t="n"/>
+      <c r="AM8" s="399" t="n"/>
+      <c r="AN8" s="399" t="n"/>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="399" t="inlineStr">
         <is>
           <t>ANNEX-QA-007</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="399" t="inlineStr">
         <is>
           <t>ANNEX-QA-007 — Chuẩn bề mặt, độ sạch, tương thích chân không, rò rỉ và xử lý đặc biệt</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" s="399" t="inlineStr">
         <is>
           <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/03-Reference/02-ANNEX-Standards/annex-qa-007-surface-finish-vacuum-compatibility.html</t>
         </is>
       </c>
+      <c r="D9" s="399" t="n"/>
+      <c r="E9" s="399" t="n"/>
+      <c r="F9" s="399" t="n"/>
+      <c r="G9" s="399" t="n"/>
+      <c r="H9" s="399" t="n"/>
+      <c r="I9" s="399" t="n"/>
+      <c r="J9" s="399" t="n"/>
+      <c r="K9" s="399" t="n"/>
+      <c r="L9" s="399" t="n"/>
+      <c r="M9" s="399" t="n"/>
+      <c r="N9" s="399" t="n"/>
+      <c r="O9" s="399" t="n"/>
+      <c r="P9" s="399" t="n"/>
+      <c r="Q9" s="399" t="n"/>
+      <c r="R9" s="399" t="n"/>
+      <c r="S9" s="399" t="n"/>
+      <c r="T9" s="399" t="n"/>
+      <c r="U9" s="399" t="n"/>
+      <c r="V9" s="399" t="n"/>
+      <c r="W9" s="399" t="n"/>
+      <c r="X9" s="399" t="n"/>
+      <c r="Y9" s="399" t="n"/>
+      <c r="Z9" s="399" t="n"/>
+      <c r="AA9" s="399" t="n"/>
+      <c r="AB9" s="399" t="n"/>
+      <c r="AC9" s="399" t="n"/>
+      <c r="AD9" s="399" t="n"/>
+      <c r="AE9" s="399" t="n"/>
+      <c r="AF9" s="399" t="n"/>
+      <c r="AG9" s="399" t="n"/>
+      <c r="AH9" s="399" t="n"/>
+      <c r="AI9" s="399" t="n"/>
+      <c r="AJ9" s="399" t="n"/>
+      <c r="AK9" s="399" t="n"/>
+      <c r="AL9" s="399" t="n"/>
+      <c r="AM9" s="399" t="n"/>
+      <c r="AN9" s="399" t="n"/>
     </row>
     <row r="10" ht="20" customHeight="1">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="399" t="inlineStr">
         <is>
           <t>ANNEX-WHS-001</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="399" t="inlineStr">
         <is>
           <t>ANNEX-WHS-001 — Quy cách đóng gói, nhãn, bảo quản và bằng chứng gói hàng</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C10" s="399" t="inlineStr">
         <is>
           <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/03-Reference/02-ANNEX-Standards/annex-whs-001-packaging-labeling-spec.html</t>
         </is>
       </c>
+      <c r="D10" s="399" t="n"/>
+      <c r="E10" s="399" t="n"/>
+      <c r="F10" s="399" t="n"/>
+      <c r="G10" s="399" t="n"/>
+      <c r="H10" s="399" t="n"/>
+      <c r="I10" s="399" t="n"/>
+      <c r="J10" s="399" t="n"/>
+      <c r="K10" s="399" t="n"/>
+      <c r="L10" s="399" t="n"/>
+      <c r="M10" s="399" t="n"/>
+      <c r="N10" s="399" t="n"/>
+      <c r="O10" s="399" t="n"/>
+      <c r="P10" s="399" t="n"/>
+      <c r="Q10" s="399" t="n"/>
+      <c r="R10" s="399" t="n"/>
+      <c r="S10" s="399" t="n"/>
+      <c r="T10" s="399" t="n"/>
+      <c r="U10" s="399" t="n"/>
+      <c r="V10" s="399" t="n"/>
+      <c r="W10" s="399" t="n"/>
+      <c r="X10" s="399" t="n"/>
+      <c r="Y10" s="399" t="n"/>
+      <c r="Z10" s="399" t="n"/>
+      <c r="AA10" s="399" t="n"/>
+      <c r="AB10" s="399" t="n"/>
+      <c r="AC10" s="399" t="n"/>
+      <c r="AD10" s="399" t="n"/>
+      <c r="AE10" s="399" t="n"/>
+      <c r="AF10" s="399" t="n"/>
+      <c r="AG10" s="399" t="n"/>
+      <c r="AH10" s="399" t="n"/>
+      <c r="AI10" s="399" t="n"/>
+      <c r="AJ10" s="399" t="n"/>
+      <c r="AK10" s="399" t="n"/>
+      <c r="AL10" s="399" t="n"/>
+      <c r="AM10" s="399" t="n"/>
+      <c r="AN10" s="399" t="n"/>
     </row>
     <row r="11" ht="20" customHeight="1">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="399" t="inlineStr">
         <is>
           <t>Open When</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="399" t="inlineStr">
         <is>
           <t>Open before the controlled activity starts or before the release decision is taken. Do not populate it retrospectively after execution has already moved forward.</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C11" s="399" t="inlineStr">
         <is>
           <t>Operational trigger</t>
         </is>
       </c>
+      <c r="D11" s="399" t="n"/>
+      <c r="E11" s="399" t="n"/>
+      <c r="F11" s="399" t="n"/>
+      <c r="G11" s="399" t="n"/>
+      <c r="H11" s="399" t="n"/>
+      <c r="I11" s="399" t="n"/>
+      <c r="J11" s="399" t="n"/>
+      <c r="K11" s="399" t="n"/>
+      <c r="L11" s="399" t="n"/>
+      <c r="M11" s="399" t="n"/>
+      <c r="N11" s="399" t="n"/>
+      <c r="O11" s="399" t="n"/>
+      <c r="P11" s="399" t="n"/>
+      <c r="Q11" s="399" t="n"/>
+      <c r="R11" s="399" t="n"/>
+      <c r="S11" s="399" t="n"/>
+      <c r="T11" s="399" t="n"/>
+      <c r="U11" s="399" t="n"/>
+      <c r="V11" s="399" t="n"/>
+      <c r="W11" s="399" t="n"/>
+      <c r="X11" s="399" t="n"/>
+      <c r="Y11" s="399" t="n"/>
+      <c r="Z11" s="399" t="n"/>
+      <c r="AA11" s="399" t="n"/>
+      <c r="AB11" s="399" t="n"/>
+      <c r="AC11" s="399" t="n"/>
+      <c r="AD11" s="399" t="n"/>
+      <c r="AE11" s="399" t="n"/>
+      <c r="AF11" s="399" t="n"/>
+      <c r="AG11" s="399" t="n"/>
+      <c r="AH11" s="399" t="n"/>
+      <c r="AI11" s="399" t="n"/>
+      <c r="AJ11" s="399" t="n"/>
+      <c r="AK11" s="399" t="n"/>
+      <c r="AL11" s="399" t="n"/>
+      <c r="AM11" s="399" t="n"/>
+      <c r="AN11" s="399" t="n"/>
     </row>
     <row r="12" ht="20" customHeight="1">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="399" t="inlineStr">
         <is>
           <t>Close When</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B12" s="399" t="inlineStr">
         <is>
           <t>Close only after the final gate disposition, result or release status is recorded, all conditions are assigned to an owner, and the evidence package reference is complete.</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C12" s="399" t="inlineStr">
         <is>
           <t>Release / closure rule</t>
         </is>
       </c>
+      <c r="D12" s="399" t="n"/>
+      <c r="E12" s="399" t="n"/>
+      <c r="F12" s="399" t="n"/>
+      <c r="G12" s="399" t="n"/>
+      <c r="H12" s="399" t="n"/>
+      <c r="I12" s="399" t="n"/>
+      <c r="J12" s="399" t="n"/>
+      <c r="K12" s="399" t="n"/>
+      <c r="L12" s="399" t="n"/>
+      <c r="M12" s="399" t="n"/>
+      <c r="N12" s="399" t="n"/>
+      <c r="O12" s="399" t="n"/>
+      <c r="P12" s="399" t="n"/>
+      <c r="Q12" s="399" t="n"/>
+      <c r="R12" s="399" t="n"/>
+      <c r="S12" s="399" t="n"/>
+      <c r="T12" s="399" t="n"/>
+      <c r="U12" s="399" t="n"/>
+      <c r="V12" s="399" t="n"/>
+      <c r="W12" s="399" t="n"/>
+      <c r="X12" s="399" t="n"/>
+      <c r="Y12" s="399" t="n"/>
+      <c r="Z12" s="399" t="n"/>
+      <c r="AA12" s="399" t="n"/>
+      <c r="AB12" s="399" t="n"/>
+      <c r="AC12" s="399" t="n"/>
+      <c r="AD12" s="399" t="n"/>
+      <c r="AE12" s="399" t="n"/>
+      <c r="AF12" s="399" t="n"/>
+      <c r="AG12" s="399" t="n"/>
+      <c r="AH12" s="399" t="n"/>
+      <c r="AI12" s="399" t="n"/>
+      <c r="AJ12" s="399" t="n"/>
+      <c r="AK12" s="399" t="n"/>
+      <c r="AL12" s="399" t="n"/>
+      <c r="AM12" s="399" t="n"/>
+      <c r="AN12" s="399" t="n"/>
     </row>
     <row r="13" ht="20" customHeight="1"/>
     <row r="14" ht="20" customHeight="1"/>
@@ -7908,6 +10113,7 @@
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.197" right="0.197" top="0.197" bottom="0.197" header="0.1" footer="0.1"/>
+  <pageSetup paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
--- a/04-Bieu-Mau/07-FRM-700/FRM-715_Vacuum_Compatible_Clean_Build_and_Bagging_Record.xlsx
+++ b/04-Bieu-Mau/07-FRM-700/FRM-715_Vacuum_Compatible_Clean_Build_and_Bagging_Record.xlsx
@@ -25,7 +25,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="81">
+  <fonts count="86">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -485,8 +485,35 @@
       <color theme="1"/>
       <sz val="8"/>
     </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="000C2D48"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="000C2D48"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="001565C0"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="007A8FA6"/>
+      <sz val="7"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="00BBCCCC"/>
+      <sz val="8"/>
+    </font>
   </fonts>
-  <fills count="47">
+  <fills count="52">
     <fill>
       <patternFill/>
     </fill>
@@ -718,8 +745,33 @@
         <fgColor rgb="007C3AED"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="002C9CD7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E4F0F9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001565C0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F0F7FC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="000C2D48"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="293">
+  <borders count="321">
     <border>
       <left/>
       <right/>
@@ -3853,12 +3905,308 @@
         <color rgb="00C5D9E8"/>
       </bottom>
       <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="002C9CD7"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00C5D9E8"/>
+      </right>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00C5D9E8"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="002C9CD7"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="002C9CD7"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00C5D9E8"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="002C9CD7"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="002C9CD7"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00C5D9E8"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00C5D9E8"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="002C9CD7"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="002C9CD7"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00C5D9E8"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="002C9CD7"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00C5D9E8"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="79" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="428">
+  <cellXfs count="547">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -4884,6 +5232,345 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="291" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="292" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="285" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="79" fillId="4" borderId="293" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="294" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="295" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="81" fillId="4" borderId="293" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="4" borderId="294" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="4" borderId="295" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="48" borderId="293" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="48" borderId="294" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="48" borderId="296" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="4" borderId="297" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="4" borderId="294" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="4" borderId="295" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="298" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="299" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="81" fillId="4" borderId="298" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="4" borderId="299" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="48" borderId="300" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="48" borderId="273" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="48" borderId="282" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="4" borderId="301" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="4" borderId="273" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="4" borderId="302" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="83" fillId="4" borderId="298" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="83" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="83" fillId="4" borderId="299" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="303" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="304" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="305" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="84" fillId="4" borderId="303" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="84" fillId="4" borderId="304" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="84" fillId="4" borderId="305" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="48" borderId="306" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="48" borderId="307" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="48" borderId="308" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="4" borderId="309" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="4" borderId="307" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="4" borderId="310" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="79" fillId="47" borderId="271" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="49" borderId="311" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="49" borderId="312" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="49" borderId="313" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="50" borderId="314" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="79" fillId="0" borderId="315" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="316" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="79" fillId="0" borderId="315" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="50" borderId="316" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="79" fillId="0" borderId="317" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="50" borderId="318" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="272" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="50" borderId="272" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="79" fillId="0" borderId="319" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="50" borderId="306" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="79" fillId="0" borderId="307" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="309" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="79" fillId="0" borderId="307" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="50" borderId="309" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="79" fillId="0" borderId="310" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="51" borderId="311" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="51" borderId="312" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="51" borderId="320" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="51" borderId="313" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="50" borderId="314" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="50" borderId="316" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="50" borderId="316" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="316" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="50" borderId="318" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="50" borderId="272" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="50" borderId="272" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="272" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="50" borderId="306" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="50" borderId="309" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="50" borderId="309" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="309" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="50" borderId="316" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="79" fillId="0" borderId="317" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="85" fillId="4" borderId="318" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="85" fillId="4" borderId="272" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="79" fillId="0" borderId="318" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="79" fillId="0" borderId="272" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="79" fillId="0" borderId="306" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="79" fillId="0" borderId="309" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="4" borderId="311" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="79" fillId="0" borderId="312" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="79" fillId="0" borderId="313" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="77" fillId="4" borderId="293" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="79" fillId="4" borderId="295" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="78" fillId="4" borderId="298" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="79" fillId="4" borderId="299" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="79" fillId="4" borderId="298" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="79" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="53" fillId="4" borderId="298" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="4" borderId="299" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="303" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="304" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="305" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="50" borderId="314" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="316" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="315" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="50" borderId="318" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="272" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="275" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="79" fillId="0" borderId="319" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="82" fillId="50" borderId="318" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="272" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="275" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="0" borderId="319" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="50" borderId="306" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="309" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="307" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="0" borderId="307" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="0" borderId="310" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="79" fillId="4" borderId="304" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="79" fillId="4" borderId="305" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="80" fillId="0" borderId="318" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="0" borderId="272" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="0" borderId="306" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="0" borderId="309" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -4958,6 +5645,126 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1792692" cy="517122"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1303776" cy="376089"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1303776" cy="376089"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1303776" cy="376089"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5345,688 +6152,778 @@
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1">
-      <c r="A1" s="340" t="n"/>
-      <c r="B1" s="422" t="n"/>
-      <c r="C1" s="422" t="n"/>
-      <c r="D1" s="422" t="n"/>
-      <c r="E1" s="422" t="n"/>
-      <c r="F1" s="422" t="n"/>
-      <c r="G1" s="422" t="n"/>
-      <c r="H1" s="422" t="n"/>
-      <c r="I1" s="422" t="n"/>
-      <c r="J1" s="422" t="n"/>
-      <c r="K1" s="422" t="n"/>
-      <c r="L1" s="342" t="inlineStr">
+      <c r="A1" s="428" t="n"/>
+      <c r="B1" s="429" t="n"/>
+      <c r="C1" s="429" t="n"/>
+      <c r="D1" s="429" t="n"/>
+      <c r="E1" s="429" t="n"/>
+      <c r="F1" s="429" t="n"/>
+      <c r="G1" s="429" t="n"/>
+      <c r="H1" s="429" t="n"/>
+      <c r="I1" s="429" t="n"/>
+      <c r="J1" s="429" t="n"/>
+      <c r="K1" s="430" t="n"/>
+      <c r="L1" s="431" t="inlineStr">
         <is>
           <t>Vacuum-Compatible Clean Build and Bagging Record</t>
         </is>
       </c>
-      <c r="M1" s="422" t="n"/>
-      <c r="N1" s="422" t="n"/>
-      <c r="O1" s="422" t="n"/>
-      <c r="P1" s="422" t="n"/>
-      <c r="Q1" s="422" t="n"/>
-      <c r="R1" s="422" t="n"/>
-      <c r="S1" s="422" t="n"/>
-      <c r="T1" s="422" t="n"/>
-      <c r="U1" s="422" t="n"/>
-      <c r="V1" s="422" t="n"/>
-      <c r="W1" s="422" t="n"/>
-      <c r="X1" s="422" t="n"/>
-      <c r="Y1" s="422" t="n"/>
-      <c r="Z1" s="422" t="n"/>
-      <c r="AA1" s="422" t="n"/>
-      <c r="AB1" s="422" t="n"/>
-      <c r="AC1" s="422" t="n"/>
-      <c r="AD1" s="422" t="n"/>
-      <c r="AE1" s="422" t="n"/>
-      <c r="AF1" s="422" t="n"/>
-      <c r="AG1" s="422" t="n"/>
-      <c r="AH1" s="422" t="n"/>
-      <c r="AI1" s="422" t="n"/>
-      <c r="AJ1" s="422" t="n"/>
-      <c r="AK1" s="422" t="n"/>
-      <c r="AL1" s="422" t="n"/>
-      <c r="AM1" s="422" t="n"/>
-      <c r="AN1" s="422" t="n"/>
-      <c r="AO1" s="422" t="n"/>
-      <c r="AP1" s="422" t="n"/>
-      <c r="AQ1" s="343" t="n"/>
-      <c r="AR1" s="423" t="n"/>
-      <c r="AS1" s="423" t="n"/>
-      <c r="AT1" s="423" t="n"/>
-      <c r="AU1" s="423" t="n"/>
-      <c r="AV1" s="424" t="n"/>
-      <c r="AW1" s="346" t="inlineStr">
+      <c r="M1" s="432" t="n"/>
+      <c r="N1" s="432" t="n"/>
+      <c r="O1" s="432" t="n"/>
+      <c r="P1" s="432" t="n"/>
+      <c r="Q1" s="432" t="n"/>
+      <c r="R1" s="432" t="n"/>
+      <c r="S1" s="432" t="n"/>
+      <c r="T1" s="432" t="n"/>
+      <c r="U1" s="432" t="n"/>
+      <c r="V1" s="432" t="n"/>
+      <c r="W1" s="432" t="n"/>
+      <c r="X1" s="432" t="n"/>
+      <c r="Y1" s="432" t="n"/>
+      <c r="Z1" s="432" t="n"/>
+      <c r="AA1" s="432" t="n"/>
+      <c r="AB1" s="432" t="n"/>
+      <c r="AC1" s="432" t="n"/>
+      <c r="AD1" s="432" t="n"/>
+      <c r="AE1" s="432" t="n"/>
+      <c r="AF1" s="432" t="n"/>
+      <c r="AG1" s="432" t="n"/>
+      <c r="AH1" s="432" t="n"/>
+      <c r="AI1" s="432" t="n"/>
+      <c r="AJ1" s="432" t="n"/>
+      <c r="AK1" s="432" t="n"/>
+      <c r="AL1" s="432" t="n"/>
+      <c r="AM1" s="432" t="n"/>
+      <c r="AN1" s="432" t="n"/>
+      <c r="AO1" s="432" t="n"/>
+      <c r="AP1" s="433" t="n"/>
+      <c r="AQ1" s="434" t="n"/>
+      <c r="AR1" s="435" t="n"/>
+      <c r="AS1" s="435" t="n"/>
+      <c r="AT1" s="435" t="n"/>
+      <c r="AU1" s="435" t="n"/>
+      <c r="AV1" s="436" t="n"/>
+      <c r="AW1" s="437" t="inlineStr">
         <is>
           <t>FRM-715</t>
         </is>
       </c>
-      <c r="AX1" s="423" t="n"/>
-      <c r="AY1" s="423" t="n"/>
-      <c r="AZ1" s="423" t="n"/>
-      <c r="BA1" s="423" t="n"/>
-      <c r="BB1" s="423" t="n"/>
-      <c r="BC1" s="423" t="n"/>
-      <c r="BD1" s="424" t="n"/>
+      <c r="AX1" s="438" t="n"/>
+      <c r="AY1" s="438" t="n"/>
+      <c r="AZ1" s="438" t="n"/>
+      <c r="BA1" s="438" t="n"/>
+      <c r="BB1" s="438" t="n"/>
+      <c r="BC1" s="438" t="n"/>
+      <c r="BD1" s="439" t="n"/>
     </row>
     <row r="2" ht="15" customHeight="1">
-      <c r="A2" s="425" t="n"/>
-      <c r="L2" s="425" t="n"/>
-      <c r="AQ2" s="343" t="n"/>
-      <c r="AR2" s="423" t="n"/>
-      <c r="AS2" s="423" t="n"/>
-      <c r="AT2" s="423" t="n"/>
-      <c r="AU2" s="423" t="n"/>
-      <c r="AV2" s="424" t="n"/>
-      <c r="AW2" s="346" t="inlineStr">
+      <c r="A2" s="440" t="n"/>
+      <c r="B2" s="25" t="n"/>
+      <c r="C2" s="25" t="n"/>
+      <c r="D2" s="25" t="n"/>
+      <c r="E2" s="25" t="n"/>
+      <c r="F2" s="25" t="n"/>
+      <c r="G2" s="25" t="n"/>
+      <c r="H2" s="25" t="n"/>
+      <c r="I2" s="25" t="n"/>
+      <c r="J2" s="25" t="n"/>
+      <c r="K2" s="441" t="n"/>
+      <c r="L2" s="442" t="n"/>
+      <c r="M2" s="443" t="n"/>
+      <c r="N2" s="443" t="n"/>
+      <c r="O2" s="443" t="n"/>
+      <c r="P2" s="443" t="n"/>
+      <c r="Q2" s="443" t="n"/>
+      <c r="R2" s="443" t="n"/>
+      <c r="S2" s="443" t="n"/>
+      <c r="T2" s="443" t="n"/>
+      <c r="U2" s="443" t="n"/>
+      <c r="V2" s="443" t="n"/>
+      <c r="W2" s="443" t="n"/>
+      <c r="X2" s="443" t="n"/>
+      <c r="Y2" s="443" t="n"/>
+      <c r="Z2" s="443" t="n"/>
+      <c r="AA2" s="443" t="n"/>
+      <c r="AB2" s="443" t="n"/>
+      <c r="AC2" s="443" t="n"/>
+      <c r="AD2" s="443" t="n"/>
+      <c r="AE2" s="443" t="n"/>
+      <c r="AF2" s="443" t="n"/>
+      <c r="AG2" s="443" t="n"/>
+      <c r="AH2" s="443" t="n"/>
+      <c r="AI2" s="443" t="n"/>
+      <c r="AJ2" s="443" t="n"/>
+      <c r="AK2" s="443" t="n"/>
+      <c r="AL2" s="443" t="n"/>
+      <c r="AM2" s="443" t="n"/>
+      <c r="AN2" s="443" t="n"/>
+      <c r="AO2" s="443" t="n"/>
+      <c r="AP2" s="444" t="n"/>
+      <c r="AQ2" s="445" t="n"/>
+      <c r="AR2" s="446" t="n"/>
+      <c r="AS2" s="446" t="n"/>
+      <c r="AT2" s="446" t="n"/>
+      <c r="AU2" s="446" t="n"/>
+      <c r="AV2" s="447" t="n"/>
+      <c r="AW2" s="448" t="inlineStr">
         <is>
           <t>V0</t>
         </is>
       </c>
-      <c r="AX2" s="423" t="n"/>
-      <c r="AY2" s="423" t="n"/>
-      <c r="AZ2" s="423" t="n"/>
-      <c r="BA2" s="423" t="n"/>
-      <c r="BB2" s="423" t="n"/>
-      <c r="BC2" s="423" t="n"/>
-      <c r="BD2" s="424" t="n"/>
+      <c r="AX2" s="449" t="n"/>
+      <c r="AY2" s="449" t="n"/>
+      <c r="AZ2" s="449" t="n"/>
+      <c r="BA2" s="449" t="n"/>
+      <c r="BB2" s="449" t="n"/>
+      <c r="BC2" s="449" t="n"/>
+      <c r="BD2" s="450" t="n"/>
     </row>
     <row r="3" ht="15" customHeight="1">
-      <c r="A3" s="425" t="n"/>
-      <c r="L3" s="426" t="n"/>
-      <c r="M3" s="427" t="n"/>
-      <c r="N3" s="427" t="n"/>
-      <c r="O3" s="427" t="n"/>
-      <c r="P3" s="427" t="n"/>
-      <c r="Q3" s="427" t="n"/>
-      <c r="R3" s="427" t="n"/>
-      <c r="S3" s="427" t="n"/>
-      <c r="T3" s="427" t="n"/>
-      <c r="U3" s="427" t="n"/>
-      <c r="V3" s="427" t="n"/>
-      <c r="W3" s="427" t="n"/>
-      <c r="X3" s="427" t="n"/>
-      <c r="Y3" s="427" t="n"/>
-      <c r="Z3" s="427" t="n"/>
-      <c r="AA3" s="427" t="n"/>
-      <c r="AB3" s="427" t="n"/>
-      <c r="AC3" s="427" t="n"/>
-      <c r="AD3" s="427" t="n"/>
-      <c r="AE3" s="427" t="n"/>
-      <c r="AF3" s="427" t="n"/>
-      <c r="AG3" s="427" t="n"/>
-      <c r="AH3" s="427" t="n"/>
-      <c r="AI3" s="427" t="n"/>
-      <c r="AJ3" s="427" t="n"/>
-      <c r="AK3" s="427" t="n"/>
-      <c r="AL3" s="427" t="n"/>
-      <c r="AM3" s="427" t="n"/>
-      <c r="AN3" s="427" t="n"/>
-      <c r="AO3" s="427" t="n"/>
-      <c r="AP3" s="427" t="n"/>
-      <c r="AQ3" s="343" t="n"/>
-      <c r="AR3" s="423" t="n"/>
-      <c r="AS3" s="423" t="n"/>
-      <c r="AT3" s="423" t="n"/>
-      <c r="AU3" s="423" t="n"/>
-      <c r="AV3" s="424" t="n"/>
-      <c r="AW3" s="346" t="inlineStr">
+      <c r="A3" s="440" t="n"/>
+      <c r="B3" s="25" t="n"/>
+      <c r="C3" s="25" t="n"/>
+      <c r="D3" s="25" t="n"/>
+      <c r="E3" s="25" t="n"/>
+      <c r="F3" s="25" t="n"/>
+      <c r="G3" s="25" t="n"/>
+      <c r="H3" s="25" t="n"/>
+      <c r="I3" s="25" t="n"/>
+      <c r="J3" s="25" t="n"/>
+      <c r="K3" s="441" t="n"/>
+      <c r="L3" s="442" t="n"/>
+      <c r="M3" s="443" t="n"/>
+      <c r="N3" s="443" t="n"/>
+      <c r="O3" s="443" t="n"/>
+      <c r="P3" s="443" t="n"/>
+      <c r="Q3" s="443" t="n"/>
+      <c r="R3" s="443" t="n"/>
+      <c r="S3" s="443" t="n"/>
+      <c r="T3" s="443" t="n"/>
+      <c r="U3" s="443" t="n"/>
+      <c r="V3" s="443" t="n"/>
+      <c r="W3" s="443" t="n"/>
+      <c r="X3" s="443" t="n"/>
+      <c r="Y3" s="443" t="n"/>
+      <c r="Z3" s="443" t="n"/>
+      <c r="AA3" s="443" t="n"/>
+      <c r="AB3" s="443" t="n"/>
+      <c r="AC3" s="443" t="n"/>
+      <c r="AD3" s="443" t="n"/>
+      <c r="AE3" s="443" t="n"/>
+      <c r="AF3" s="443" t="n"/>
+      <c r="AG3" s="443" t="n"/>
+      <c r="AH3" s="443" t="n"/>
+      <c r="AI3" s="443" t="n"/>
+      <c r="AJ3" s="443" t="n"/>
+      <c r="AK3" s="443" t="n"/>
+      <c r="AL3" s="443" t="n"/>
+      <c r="AM3" s="443" t="n"/>
+      <c r="AN3" s="443" t="n"/>
+      <c r="AO3" s="443" t="n"/>
+      <c r="AP3" s="444" t="n"/>
+      <c r="AQ3" s="445" t="n"/>
+      <c r="AR3" s="446" t="n"/>
+      <c r="AS3" s="446" t="n"/>
+      <c r="AT3" s="446" t="n"/>
+      <c r="AU3" s="446" t="n"/>
+      <c r="AV3" s="447" t="n"/>
+      <c r="AW3" s="448" t="inlineStr">
         <is>
           <t>YYYY-MM-DD</t>
         </is>
       </c>
-      <c r="AX3" s="423" t="n"/>
-      <c r="AY3" s="423" t="n"/>
-      <c r="AZ3" s="423" t="n"/>
-      <c r="BA3" s="423" t="n"/>
-      <c r="BB3" s="423" t="n"/>
-      <c r="BC3" s="423" t="n"/>
-      <c r="BD3" s="424" t="n"/>
+      <c r="AX3" s="449" t="n"/>
+      <c r="AY3" s="449" t="n"/>
+      <c r="AZ3" s="449" t="n"/>
+      <c r="BA3" s="449" t="n"/>
+      <c r="BB3" s="449" t="n"/>
+      <c r="BC3" s="449" t="n"/>
+      <c r="BD3" s="450" t="n"/>
     </row>
     <row r="4" ht="15" customHeight="1">
-      <c r="A4" s="425" t="n"/>
-      <c r="L4" s="351" t="inlineStr">
+      <c r="A4" s="440" t="n"/>
+      <c r="B4" s="25" t="n"/>
+      <c r="C4" s="25" t="n"/>
+      <c r="D4" s="25" t="n"/>
+      <c r="E4" s="25" t="n"/>
+      <c r="F4" s="25" t="n"/>
+      <c r="G4" s="25" t="n"/>
+      <c r="H4" s="25" t="n"/>
+      <c r="I4" s="25" t="n"/>
+      <c r="J4" s="25" t="n"/>
+      <c r="K4" s="441" t="n"/>
+      <c r="L4" s="451" t="inlineStr">
         <is>
           <t>Quality Management System · Controlled Document</t>
         </is>
       </c>
-      <c r="AQ4" s="343" t="n"/>
-      <c r="AR4" s="423" t="n"/>
-      <c r="AS4" s="423" t="n"/>
-      <c r="AT4" s="423" t="n"/>
-      <c r="AU4" s="423" t="n"/>
-      <c r="AV4" s="424" t="n"/>
-      <c r="AW4" s="346" t="inlineStr">
+      <c r="M4" s="452" t="n"/>
+      <c r="N4" s="452" t="n"/>
+      <c r="O4" s="452" t="n"/>
+      <c r="P4" s="452" t="n"/>
+      <c r="Q4" s="452" t="n"/>
+      <c r="R4" s="452" t="n"/>
+      <c r="S4" s="452" t="n"/>
+      <c r="T4" s="452" t="n"/>
+      <c r="U4" s="452" t="n"/>
+      <c r="V4" s="452" t="n"/>
+      <c r="W4" s="452" t="n"/>
+      <c r="X4" s="452" t="n"/>
+      <c r="Y4" s="452" t="n"/>
+      <c r="Z4" s="452" t="n"/>
+      <c r="AA4" s="452" t="n"/>
+      <c r="AB4" s="452" t="n"/>
+      <c r="AC4" s="452" t="n"/>
+      <c r="AD4" s="452" t="n"/>
+      <c r="AE4" s="452" t="n"/>
+      <c r="AF4" s="452" t="n"/>
+      <c r="AG4" s="452" t="n"/>
+      <c r="AH4" s="452" t="n"/>
+      <c r="AI4" s="452" t="n"/>
+      <c r="AJ4" s="452" t="n"/>
+      <c r="AK4" s="452" t="n"/>
+      <c r="AL4" s="452" t="n"/>
+      <c r="AM4" s="452" t="n"/>
+      <c r="AN4" s="452" t="n"/>
+      <c r="AO4" s="452" t="n"/>
+      <c r="AP4" s="453" t="n"/>
+      <c r="AQ4" s="445" t="n"/>
+      <c r="AR4" s="446" t="n"/>
+      <c r="AS4" s="446" t="n"/>
+      <c r="AT4" s="446" t="n"/>
+      <c r="AU4" s="446" t="n"/>
+      <c r="AV4" s="447" t="n"/>
+      <c r="AW4" s="448" t="inlineStr">
         <is>
           <t>Warehouse + QA</t>
         </is>
       </c>
-      <c r="AX4" s="423" t="n"/>
-      <c r="AY4" s="423" t="n"/>
-      <c r="AZ4" s="423" t="n"/>
-      <c r="BA4" s="423" t="n"/>
-      <c r="BB4" s="423" t="n"/>
-      <c r="BC4" s="423" t="n"/>
-      <c r="BD4" s="424" t="n"/>
+      <c r="AX4" s="449" t="n"/>
+      <c r="AY4" s="449" t="n"/>
+      <c r="AZ4" s="449" t="n"/>
+      <c r="BA4" s="449" t="n"/>
+      <c r="BB4" s="449" t="n"/>
+      <c r="BC4" s="449" t="n"/>
+      <c r="BD4" s="450" t="n"/>
     </row>
     <row r="5" ht="15" customHeight="1">
-      <c r="A5" s="426" t="n"/>
-      <c r="B5" s="427" t="n"/>
-      <c r="C5" s="427" t="n"/>
-      <c r="D5" s="427" t="n"/>
-      <c r="E5" s="427" t="n"/>
-      <c r="F5" s="427" t="n"/>
-      <c r="G5" s="427" t="n"/>
-      <c r="H5" s="427" t="n"/>
-      <c r="I5" s="427" t="n"/>
-      <c r="J5" s="427" t="n"/>
-      <c r="K5" s="427" t="n"/>
-      <c r="L5" s="352" t="inlineStr">
+      <c r="A5" s="454" t="n"/>
+      <c r="B5" s="455" t="n"/>
+      <c r="C5" s="455" t="n"/>
+      <c r="D5" s="455" t="n"/>
+      <c r="E5" s="455" t="n"/>
+      <c r="F5" s="455" t="n"/>
+      <c r="G5" s="455" t="n"/>
+      <c r="H5" s="455" t="n"/>
+      <c r="I5" s="455" t="n"/>
+      <c r="J5" s="455" t="n"/>
+      <c r="K5" s="456" t="n"/>
+      <c r="L5" s="457" t="inlineStr">
         <is>
           <t>HESEM Engineering · ISO 9001 / AS9100 · Semiconductor Equipment Parts</t>
         </is>
       </c>
-      <c r="M5" s="427" t="n"/>
-      <c r="N5" s="427" t="n"/>
-      <c r="O5" s="427" t="n"/>
-      <c r="P5" s="427" t="n"/>
-      <c r="Q5" s="427" t="n"/>
-      <c r="R5" s="427" t="n"/>
-      <c r="S5" s="427" t="n"/>
-      <c r="T5" s="427" t="n"/>
-      <c r="U5" s="427" t="n"/>
-      <c r="V5" s="427" t="n"/>
-      <c r="W5" s="427" t="n"/>
-      <c r="X5" s="427" t="n"/>
-      <c r="Y5" s="427" t="n"/>
-      <c r="Z5" s="427" t="n"/>
-      <c r="AA5" s="427" t="n"/>
-      <c r="AB5" s="427" t="n"/>
-      <c r="AC5" s="427" t="n"/>
-      <c r="AD5" s="427" t="n"/>
-      <c r="AE5" s="427" t="n"/>
-      <c r="AF5" s="427" t="n"/>
-      <c r="AG5" s="427" t="n"/>
-      <c r="AH5" s="427" t="n"/>
-      <c r="AI5" s="427" t="n"/>
-      <c r="AJ5" s="427" t="n"/>
-      <c r="AK5" s="427" t="n"/>
-      <c r="AL5" s="427" t="n"/>
-      <c r="AM5" s="427" t="n"/>
-      <c r="AN5" s="427" t="n"/>
-      <c r="AO5" s="427" t="n"/>
-      <c r="AP5" s="427" t="n"/>
-      <c r="AQ5" s="343" t="n"/>
-      <c r="AR5" s="423" t="n"/>
-      <c r="AS5" s="423" t="n"/>
-      <c r="AT5" s="423" t="n"/>
-      <c r="AU5" s="423" t="n"/>
-      <c r="AV5" s="424" t="n"/>
-      <c r="AW5" s="346" t="inlineStr">
+      <c r="M5" s="458" t="n"/>
+      <c r="N5" s="458" t="n"/>
+      <c r="O5" s="458" t="n"/>
+      <c r="P5" s="458" t="n"/>
+      <c r="Q5" s="458" t="n"/>
+      <c r="R5" s="458" t="n"/>
+      <c r="S5" s="458" t="n"/>
+      <c r="T5" s="458" t="n"/>
+      <c r="U5" s="458" t="n"/>
+      <c r="V5" s="458" t="n"/>
+      <c r="W5" s="458" t="n"/>
+      <c r="X5" s="458" t="n"/>
+      <c r="Y5" s="458" t="n"/>
+      <c r="Z5" s="458" t="n"/>
+      <c r="AA5" s="458" t="n"/>
+      <c r="AB5" s="458" t="n"/>
+      <c r="AC5" s="458" t="n"/>
+      <c r="AD5" s="458" t="n"/>
+      <c r="AE5" s="458" t="n"/>
+      <c r="AF5" s="458" t="n"/>
+      <c r="AG5" s="458" t="n"/>
+      <c r="AH5" s="458" t="n"/>
+      <c r="AI5" s="458" t="n"/>
+      <c r="AJ5" s="458" t="n"/>
+      <c r="AK5" s="458" t="n"/>
+      <c r="AL5" s="458" t="n"/>
+      <c r="AM5" s="458" t="n"/>
+      <c r="AN5" s="458" t="n"/>
+      <c r="AO5" s="458" t="n"/>
+      <c r="AP5" s="459" t="n"/>
+      <c r="AQ5" s="460" t="n"/>
+      <c r="AR5" s="461" t="n"/>
+      <c r="AS5" s="461" t="n"/>
+      <c r="AT5" s="461" t="n"/>
+      <c r="AU5" s="461" t="n"/>
+      <c r="AV5" s="462" t="n"/>
+      <c r="AW5" s="463" t="inlineStr">
         <is>
           <t>General Manager</t>
         </is>
       </c>
-      <c r="AX5" s="423" t="n"/>
-      <c r="AY5" s="423" t="n"/>
-      <c r="AZ5" s="423" t="n"/>
-      <c r="BA5" s="423" t="n"/>
-      <c r="BB5" s="423" t="n"/>
-      <c r="BC5" s="423" t="n"/>
-      <c r="BD5" s="424" t="n"/>
+      <c r="AX5" s="464" t="n"/>
+      <c r="AY5" s="464" t="n"/>
+      <c r="AZ5" s="464" t="n"/>
+      <c r="BA5" s="464" t="n"/>
+      <c r="BB5" s="464" t="n"/>
+      <c r="BC5" s="464" t="n"/>
+      <c r="BD5" s="465" t="n"/>
     </row>
-    <row r="6" ht="4" customHeight="1">
-      <c r="A6" s="353" t="n"/>
-      <c r="B6" s="421" t="n"/>
-      <c r="C6" s="421" t="n"/>
-      <c r="D6" s="421" t="n"/>
-      <c r="E6" s="421" t="n"/>
-      <c r="F6" s="421" t="n"/>
-      <c r="G6" s="421" t="n"/>
-      <c r="H6" s="421" t="n"/>
-      <c r="I6" s="421" t="n"/>
-      <c r="J6" s="421" t="n"/>
-      <c r="K6" s="421" t="n"/>
-      <c r="L6" s="421" t="n"/>
-      <c r="M6" s="421" t="n"/>
-      <c r="N6" s="421" t="n"/>
-      <c r="O6" s="421" t="n"/>
-      <c r="P6" s="421" t="n"/>
-      <c r="Q6" s="421" t="n"/>
-      <c r="R6" s="421" t="n"/>
-      <c r="S6" s="421" t="n"/>
-      <c r="T6" s="421" t="n"/>
-      <c r="U6" s="421" t="n"/>
-      <c r="V6" s="421" t="n"/>
-      <c r="W6" s="421" t="n"/>
-      <c r="X6" s="421" t="n"/>
-      <c r="Y6" s="421" t="n"/>
-      <c r="Z6" s="421" t="n"/>
-      <c r="AA6" s="421" t="n"/>
-      <c r="AB6" s="421" t="n"/>
-      <c r="AC6" s="421" t="n"/>
-      <c r="AD6" s="421" t="n"/>
-      <c r="AE6" s="421" t="n"/>
-      <c r="AF6" s="421" t="n"/>
-      <c r="AG6" s="421" t="n"/>
-      <c r="AH6" s="421" t="n"/>
-      <c r="AI6" s="421" t="n"/>
-      <c r="AJ6" s="421" t="n"/>
-      <c r="AK6" s="421" t="n"/>
-      <c r="AL6" s="421" t="n"/>
-      <c r="AM6" s="421" t="n"/>
-      <c r="AN6" s="421" t="n"/>
-      <c r="AO6" s="421" t="n"/>
-      <c r="AP6" s="421" t="n"/>
-      <c r="AQ6" s="421" t="n"/>
-      <c r="AR6" s="421" t="n"/>
-      <c r="AS6" s="421" t="n"/>
-      <c r="AT6" s="421" t="n"/>
-      <c r="AU6" s="421" t="n"/>
-      <c r="AV6" s="421" t="n"/>
-      <c r="AW6" s="421" t="n"/>
-      <c r="AX6" s="421" t="n"/>
-      <c r="AY6" s="421" t="n"/>
-      <c r="AZ6" s="421" t="n"/>
-      <c r="BA6" s="421" t="n"/>
-      <c r="BB6" s="421" t="n"/>
-      <c r="BC6" s="421" t="n"/>
-      <c r="BD6" s="421" t="n"/>
+    <row r="6" ht="1.5" customHeight="1">
+      <c r="A6" s="466" t="n"/>
+      <c r="B6" s="466" t="n"/>
+      <c r="C6" s="466" t="n"/>
+      <c r="D6" s="466" t="n"/>
+      <c r="E6" s="466" t="n"/>
+      <c r="F6" s="466" t="n"/>
+      <c r="G6" s="466" t="n"/>
+      <c r="H6" s="466" t="n"/>
+      <c r="I6" s="466" t="n"/>
+      <c r="J6" s="466" t="n"/>
+      <c r="K6" s="466" t="n"/>
+      <c r="L6" s="466" t="n"/>
+      <c r="M6" s="466" t="n"/>
+      <c r="N6" s="466" t="n"/>
+      <c r="O6" s="466" t="n"/>
+      <c r="P6" s="466" t="n"/>
+      <c r="Q6" s="466" t="n"/>
+      <c r="R6" s="466" t="n"/>
+      <c r="S6" s="466" t="n"/>
+      <c r="T6" s="466" t="n"/>
+      <c r="U6" s="466" t="n"/>
+      <c r="V6" s="466" t="n"/>
+      <c r="W6" s="466" t="n"/>
+      <c r="X6" s="466" t="n"/>
+      <c r="Y6" s="466" t="n"/>
+      <c r="Z6" s="466" t="n"/>
+      <c r="AA6" s="466" t="n"/>
+      <c r="AB6" s="466" t="n"/>
+      <c r="AC6" s="466" t="n"/>
+      <c r="AD6" s="466" t="n"/>
+      <c r="AE6" s="466" t="n"/>
+      <c r="AF6" s="466" t="n"/>
+      <c r="AG6" s="466" t="n"/>
+      <c r="AH6" s="466" t="n"/>
+      <c r="AI6" s="466" t="n"/>
+      <c r="AJ6" s="466" t="n"/>
+      <c r="AK6" s="466" t="n"/>
+      <c r="AL6" s="466" t="n"/>
+      <c r="AM6" s="466" t="n"/>
+      <c r="AN6" s="466" t="n"/>
+      <c r="AO6" s="466" t="n"/>
+      <c r="AP6" s="466" t="n"/>
+      <c r="AQ6" s="466" t="n"/>
+      <c r="AR6" s="466" t="n"/>
+      <c r="AS6" s="466" t="n"/>
+      <c r="AT6" s="466" t="n"/>
+      <c r="AU6" s="466" t="n"/>
+      <c r="AV6" s="466" t="n"/>
+      <c r="AW6" s="466" t="n"/>
+      <c r="AX6" s="466" t="n"/>
+      <c r="AY6" s="466" t="n"/>
+      <c r="AZ6" s="466" t="n"/>
+      <c r="BA6" s="466" t="n"/>
+      <c r="BB6" s="466" t="n"/>
+      <c r="BC6" s="466" t="n"/>
+      <c r="BD6" s="466" t="n"/>
     </row>
-    <row r="7" ht="17" customHeight="1">
-      <c r="A7" s="354" t="inlineStr">
+    <row r="7" ht="18" customHeight="1">
+      <c r="A7" s="467" t="inlineStr">
         <is>
           <t xml:space="preserve">  1. REFERENCE INFORMATION</t>
         </is>
       </c>
-      <c r="B7" s="423" t="n"/>
-      <c r="C7" s="423" t="n"/>
-      <c r="D7" s="423" t="n"/>
-      <c r="E7" s="423" t="n"/>
-      <c r="F7" s="423" t="n"/>
-      <c r="G7" s="423" t="n"/>
-      <c r="H7" s="423" t="n"/>
-      <c r="I7" s="423" t="n"/>
-      <c r="J7" s="423" t="n"/>
-      <c r="K7" s="423" t="n"/>
-      <c r="L7" s="423" t="n"/>
-      <c r="M7" s="423" t="n"/>
-      <c r="N7" s="423" t="n"/>
-      <c r="O7" s="423" t="n"/>
-      <c r="P7" s="423" t="n"/>
-      <c r="Q7" s="423" t="n"/>
-      <c r="R7" s="423" t="n"/>
-      <c r="S7" s="423" t="n"/>
-      <c r="T7" s="423" t="n"/>
-      <c r="U7" s="423" t="n"/>
-      <c r="V7" s="423" t="n"/>
-      <c r="W7" s="423" t="n"/>
-      <c r="X7" s="423" t="n"/>
-      <c r="Y7" s="423" t="n"/>
-      <c r="Z7" s="423" t="n"/>
-      <c r="AA7" s="423" t="n"/>
-      <c r="AB7" s="423" t="n"/>
-      <c r="AC7" s="423" t="n"/>
-      <c r="AD7" s="423" t="n"/>
-      <c r="AE7" s="423" t="n"/>
-      <c r="AF7" s="423" t="n"/>
-      <c r="AG7" s="423" t="n"/>
-      <c r="AH7" s="423" t="n"/>
-      <c r="AI7" s="423" t="n"/>
-      <c r="AJ7" s="423" t="n"/>
-      <c r="AK7" s="423" t="n"/>
-      <c r="AL7" s="423" t="n"/>
-      <c r="AM7" s="423" t="n"/>
-      <c r="AN7" s="423" t="n"/>
-      <c r="AO7" s="423" t="n"/>
-      <c r="AP7" s="423" t="n"/>
-      <c r="AQ7" s="423" t="n"/>
-      <c r="AR7" s="423" t="n"/>
-      <c r="AS7" s="423" t="n"/>
-      <c r="AT7" s="423" t="n"/>
-      <c r="AU7" s="423" t="n"/>
-      <c r="AV7" s="423" t="n"/>
-      <c r="AW7" s="423" t="n"/>
-      <c r="AX7" s="423" t="n"/>
-      <c r="AY7" s="423" t="n"/>
-      <c r="AZ7" s="423" t="n"/>
-      <c r="BA7" s="423" t="n"/>
-      <c r="BB7" s="423" t="n"/>
-      <c r="BC7" s="423" t="n"/>
-      <c r="BD7" s="424" t="n"/>
+      <c r="B7" s="468" t="n"/>
+      <c r="C7" s="468" t="n"/>
+      <c r="D7" s="468" t="n"/>
+      <c r="E7" s="468" t="n"/>
+      <c r="F7" s="468" t="n"/>
+      <c r="G7" s="468" t="n"/>
+      <c r="H7" s="468" t="n"/>
+      <c r="I7" s="468" t="n"/>
+      <c r="J7" s="468" t="n"/>
+      <c r="K7" s="468" t="n"/>
+      <c r="L7" s="468" t="n"/>
+      <c r="M7" s="468" t="n"/>
+      <c r="N7" s="468" t="n"/>
+      <c r="O7" s="468" t="n"/>
+      <c r="P7" s="468" t="n"/>
+      <c r="Q7" s="468" t="n"/>
+      <c r="R7" s="468" t="n"/>
+      <c r="S7" s="468" t="n"/>
+      <c r="T7" s="468" t="n"/>
+      <c r="U7" s="468" t="n"/>
+      <c r="V7" s="468" t="n"/>
+      <c r="W7" s="468" t="n"/>
+      <c r="X7" s="468" t="n"/>
+      <c r="Y7" s="468" t="n"/>
+      <c r="Z7" s="468" t="n"/>
+      <c r="AA7" s="468" t="n"/>
+      <c r="AB7" s="468" t="n"/>
+      <c r="AC7" s="468" t="n"/>
+      <c r="AD7" s="468" t="n"/>
+      <c r="AE7" s="468" t="n"/>
+      <c r="AF7" s="468" t="n"/>
+      <c r="AG7" s="468" t="n"/>
+      <c r="AH7" s="468" t="n"/>
+      <c r="AI7" s="468" t="n"/>
+      <c r="AJ7" s="468" t="n"/>
+      <c r="AK7" s="468" t="n"/>
+      <c r="AL7" s="468" t="n"/>
+      <c r="AM7" s="468" t="n"/>
+      <c r="AN7" s="468" t="n"/>
+      <c r="AO7" s="468" t="n"/>
+      <c r="AP7" s="468" t="n"/>
+      <c r="AQ7" s="468" t="n"/>
+      <c r="AR7" s="468" t="n"/>
+      <c r="AS7" s="468" t="n"/>
+      <c r="AT7" s="468" t="n"/>
+      <c r="AU7" s="468" t="n"/>
+      <c r="AV7" s="468" t="n"/>
+      <c r="AW7" s="468" t="n"/>
+      <c r="AX7" s="468" t="n"/>
+      <c r="AY7" s="468" t="n"/>
+      <c r="AZ7" s="468" t="n"/>
+      <c r="BA7" s="468" t="n"/>
+      <c r="BB7" s="468" t="n"/>
+      <c r="BC7" s="468" t="n"/>
+      <c r="BD7" s="469" t="n"/>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="355" t="inlineStr">
+      <c r="A8" s="470" t="inlineStr">
         <is>
           <t>Clean Build Record ID</t>
         </is>
       </c>
-      <c r="B8" s="406" t="n"/>
-      <c r="C8" s="406" t="n"/>
-      <c r="D8" s="406" t="n"/>
-      <c r="E8" s="406" t="n"/>
-      <c r="F8" s="406" t="n"/>
-      <c r="G8" s="406" t="n"/>
-      <c r="H8" s="406" t="n"/>
-      <c r="I8" s="406" t="n"/>
-      <c r="J8" s="407" t="n"/>
-      <c r="K8" s="358" t="n"/>
-      <c r="L8" s="408" t="n"/>
-      <c r="M8" s="408" t="n"/>
-      <c r="N8" s="408" t="n"/>
-      <c r="O8" s="408" t="n"/>
-      <c r="P8" s="408" t="n"/>
-      <c r="Q8" s="408" t="n"/>
-      <c r="R8" s="408" t="n"/>
-      <c r="S8" s="408" t="n"/>
-      <c r="T8" s="408" t="n"/>
-      <c r="U8" s="408" t="n"/>
-      <c r="V8" s="408" t="n"/>
-      <c r="W8" s="408" t="n"/>
-      <c r="X8" s="408" t="n"/>
-      <c r="Y8" s="408" t="n"/>
-      <c r="Z8" s="408" t="n"/>
-      <c r="AA8" s="408" t="n"/>
-      <c r="AB8" s="409" t="n"/>
-      <c r="AC8" s="361" t="inlineStr">
+      <c r="B8" s="471" t="n"/>
+      <c r="C8" s="471" t="n"/>
+      <c r="D8" s="471" t="n"/>
+      <c r="E8" s="471" t="n"/>
+      <c r="F8" s="471" t="n"/>
+      <c r="G8" s="471" t="n"/>
+      <c r="H8" s="471" t="n"/>
+      <c r="I8" s="471" t="n"/>
+      <c r="J8" s="471" t="n"/>
+      <c r="K8" s="472" t="n"/>
+      <c r="L8" s="473" t="n"/>
+      <c r="M8" s="473" t="n"/>
+      <c r="N8" s="473" t="n"/>
+      <c r="O8" s="473" t="n"/>
+      <c r="P8" s="473" t="n"/>
+      <c r="Q8" s="473" t="n"/>
+      <c r="R8" s="473" t="n"/>
+      <c r="S8" s="473" t="n"/>
+      <c r="T8" s="473" t="n"/>
+      <c r="U8" s="473" t="n"/>
+      <c r="V8" s="473" t="n"/>
+      <c r="W8" s="473" t="n"/>
+      <c r="X8" s="473" t="n"/>
+      <c r="Y8" s="473" t="n"/>
+      <c r="Z8" s="473" t="n"/>
+      <c r="AA8" s="473" t="n"/>
+      <c r="AB8" s="473" t="n"/>
+      <c r="AC8" s="474" t="inlineStr">
         <is>
           <t>Release Status</t>
         </is>
       </c>
-      <c r="AD8" s="406" t="n"/>
-      <c r="AE8" s="406" t="n"/>
-      <c r="AF8" s="406" t="n"/>
-      <c r="AG8" s="406" t="n"/>
-      <c r="AH8" s="406" t="n"/>
-      <c r="AI8" s="406" t="n"/>
-      <c r="AJ8" s="406" t="n"/>
-      <c r="AK8" s="406" t="n"/>
-      <c r="AL8" s="407" t="n"/>
-      <c r="AM8" s="358" t="n"/>
-      <c r="AN8" s="408" t="n"/>
-      <c r="AO8" s="408" t="n"/>
-      <c r="AP8" s="408" t="n"/>
-      <c r="AQ8" s="408" t="n"/>
-      <c r="AR8" s="408" t="n"/>
-      <c r="AS8" s="408" t="n"/>
-      <c r="AT8" s="408" t="n"/>
-      <c r="AU8" s="408" t="n"/>
-      <c r="AV8" s="408" t="n"/>
-      <c r="AW8" s="408" t="n"/>
-      <c r="AX8" s="408" t="n"/>
-      <c r="AY8" s="408" t="n"/>
-      <c r="AZ8" s="408" t="n"/>
-      <c r="BA8" s="408" t="n"/>
-      <c r="BB8" s="408" t="n"/>
-      <c r="BC8" s="408" t="n"/>
-      <c r="BD8" s="409" t="n"/>
+      <c r="AD8" s="471" t="n"/>
+      <c r="AE8" s="471" t="n"/>
+      <c r="AF8" s="471" t="n"/>
+      <c r="AG8" s="471" t="n"/>
+      <c r="AH8" s="471" t="n"/>
+      <c r="AI8" s="471" t="n"/>
+      <c r="AJ8" s="471" t="n"/>
+      <c r="AK8" s="471" t="n"/>
+      <c r="AL8" s="471" t="n"/>
+      <c r="AM8" s="472" t="n"/>
+      <c r="AN8" s="473" t="n"/>
+      <c r="AO8" s="473" t="n"/>
+      <c r="AP8" s="473" t="n"/>
+      <c r="AQ8" s="473" t="n"/>
+      <c r="AR8" s="473" t="n"/>
+      <c r="AS8" s="473" t="n"/>
+      <c r="AT8" s="473" t="n"/>
+      <c r="AU8" s="473" t="n"/>
+      <c r="AV8" s="473" t="n"/>
+      <c r="AW8" s="473" t="n"/>
+      <c r="AX8" s="473" t="n"/>
+      <c r="AY8" s="473" t="n"/>
+      <c r="AZ8" s="473" t="n"/>
+      <c r="BA8" s="473" t="n"/>
+      <c r="BB8" s="473" t="n"/>
+      <c r="BC8" s="473" t="n"/>
+      <c r="BD8" s="475" t="n"/>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="355" t="inlineStr">
+      <c r="A9" s="476" t="inlineStr">
         <is>
           <t>Job / Part / Package Class</t>
         </is>
       </c>
-      <c r="B9" s="406" t="n"/>
-      <c r="C9" s="406" t="n"/>
-      <c r="D9" s="406" t="n"/>
-      <c r="E9" s="406" t="n"/>
-      <c r="F9" s="406" t="n"/>
-      <c r="G9" s="406" t="n"/>
-      <c r="H9" s="406" t="n"/>
-      <c r="I9" s="406" t="n"/>
-      <c r="J9" s="407" t="n"/>
-      <c r="K9" s="358" t="n"/>
-      <c r="L9" s="408" t="n"/>
-      <c r="M9" s="408" t="n"/>
-      <c r="N9" s="408" t="n"/>
-      <c r="O9" s="408" t="n"/>
-      <c r="P9" s="408" t="n"/>
-      <c r="Q9" s="408" t="n"/>
-      <c r="R9" s="408" t="n"/>
-      <c r="S9" s="408" t="n"/>
-      <c r="T9" s="408" t="n"/>
-      <c r="U9" s="408" t="n"/>
-      <c r="V9" s="408" t="n"/>
-      <c r="W9" s="408" t="n"/>
-      <c r="X9" s="408" t="n"/>
-      <c r="Y9" s="408" t="n"/>
-      <c r="Z9" s="408" t="n"/>
-      <c r="AA9" s="408" t="n"/>
-      <c r="AB9" s="409" t="n"/>
-      <c r="AC9" s="361" t="inlineStr">
+      <c r="B9" s="344" t="n"/>
+      <c r="C9" s="344" t="n"/>
+      <c r="D9" s="344" t="n"/>
+      <c r="E9" s="344" t="n"/>
+      <c r="F9" s="344" t="n"/>
+      <c r="G9" s="344" t="n"/>
+      <c r="H9" s="344" t="n"/>
+      <c r="I9" s="344" t="n"/>
+      <c r="J9" s="344" t="n"/>
+      <c r="K9" s="477" t="n"/>
+      <c r="L9" s="362" t="n"/>
+      <c r="M9" s="362" t="n"/>
+      <c r="N9" s="362" t="n"/>
+      <c r="O9" s="362" t="n"/>
+      <c r="P9" s="362" t="n"/>
+      <c r="Q9" s="362" t="n"/>
+      <c r="R9" s="362" t="n"/>
+      <c r="S9" s="362" t="n"/>
+      <c r="T9" s="362" t="n"/>
+      <c r="U9" s="362" t="n"/>
+      <c r="V9" s="362" t="n"/>
+      <c r="W9" s="362" t="n"/>
+      <c r="X9" s="362" t="n"/>
+      <c r="Y9" s="362" t="n"/>
+      <c r="Z9" s="362" t="n"/>
+      <c r="AA9" s="362" t="n"/>
+      <c r="AB9" s="362" t="n"/>
+      <c r="AC9" s="478" t="inlineStr">
         <is>
           <t>Clean Class</t>
         </is>
       </c>
-      <c r="AD9" s="406" t="n"/>
-      <c r="AE9" s="406" t="n"/>
-      <c r="AF9" s="406" t="n"/>
-      <c r="AG9" s="406" t="n"/>
-      <c r="AH9" s="406" t="n"/>
-      <c r="AI9" s="406" t="n"/>
-      <c r="AJ9" s="406" t="n"/>
-      <c r="AK9" s="406" t="n"/>
-      <c r="AL9" s="407" t="n"/>
-      <c r="AM9" s="358" t="n"/>
-      <c r="AN9" s="408" t="n"/>
-      <c r="AO9" s="408" t="n"/>
-      <c r="AP9" s="408" t="n"/>
-      <c r="AQ9" s="408" t="n"/>
-      <c r="AR9" s="408" t="n"/>
-      <c r="AS9" s="408" t="n"/>
-      <c r="AT9" s="408" t="n"/>
-      <c r="AU9" s="408" t="n"/>
-      <c r="AV9" s="408" t="n"/>
-      <c r="AW9" s="408" t="n"/>
-      <c r="AX9" s="408" t="n"/>
-      <c r="AY9" s="408" t="n"/>
-      <c r="AZ9" s="408" t="n"/>
-      <c r="BA9" s="408" t="n"/>
-      <c r="BB9" s="408" t="n"/>
-      <c r="BC9" s="408" t="n"/>
-      <c r="BD9" s="409" t="n"/>
+      <c r="AD9" s="344" t="n"/>
+      <c r="AE9" s="344" t="n"/>
+      <c r="AF9" s="344" t="n"/>
+      <c r="AG9" s="344" t="n"/>
+      <c r="AH9" s="344" t="n"/>
+      <c r="AI9" s="344" t="n"/>
+      <c r="AJ9" s="344" t="n"/>
+      <c r="AK9" s="344" t="n"/>
+      <c r="AL9" s="344" t="n"/>
+      <c r="AM9" s="477" t="n"/>
+      <c r="AN9" s="362" t="n"/>
+      <c r="AO9" s="362" t="n"/>
+      <c r="AP9" s="362" t="n"/>
+      <c r="AQ9" s="362" t="n"/>
+      <c r="AR9" s="362" t="n"/>
+      <c r="AS9" s="362" t="n"/>
+      <c r="AT9" s="362" t="n"/>
+      <c r="AU9" s="362" t="n"/>
+      <c r="AV9" s="362" t="n"/>
+      <c r="AW9" s="362" t="n"/>
+      <c r="AX9" s="362" t="n"/>
+      <c r="AY9" s="362" t="n"/>
+      <c r="AZ9" s="362" t="n"/>
+      <c r="BA9" s="362" t="n"/>
+      <c r="BB9" s="362" t="n"/>
+      <c r="BC9" s="362" t="n"/>
+      <c r="BD9" s="479" t="n"/>
     </row>
     <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="355" t="inlineStr">
+      <c r="A10" s="476" t="inlineStr">
         <is>
           <t>Bagging Configuration</t>
         </is>
       </c>
-      <c r="B10" s="406" t="n"/>
-      <c r="C10" s="406" t="n"/>
-      <c r="D10" s="406" t="n"/>
-      <c r="E10" s="406" t="n"/>
-      <c r="F10" s="406" t="n"/>
-      <c r="G10" s="406" t="n"/>
-      <c r="H10" s="406" t="n"/>
-      <c r="I10" s="406" t="n"/>
-      <c r="J10" s="407" t="n"/>
-      <c r="K10" s="358" t="n"/>
-      <c r="L10" s="408" t="n"/>
-      <c r="M10" s="408" t="n"/>
-      <c r="N10" s="408" t="n"/>
-      <c r="O10" s="408" t="n"/>
-      <c r="P10" s="408" t="n"/>
-      <c r="Q10" s="408" t="n"/>
-      <c r="R10" s="408" t="n"/>
-      <c r="S10" s="408" t="n"/>
-      <c r="T10" s="408" t="n"/>
-      <c r="U10" s="408" t="n"/>
-      <c r="V10" s="408" t="n"/>
-      <c r="W10" s="408" t="n"/>
-      <c r="X10" s="408" t="n"/>
-      <c r="Y10" s="408" t="n"/>
-      <c r="Z10" s="408" t="n"/>
-      <c r="AA10" s="408" t="n"/>
-      <c r="AB10" s="409" t="n"/>
-      <c r="AC10" s="361" t="inlineStr">
+      <c r="B10" s="344" t="n"/>
+      <c r="C10" s="344" t="n"/>
+      <c r="D10" s="344" t="n"/>
+      <c r="E10" s="344" t="n"/>
+      <c r="F10" s="344" t="n"/>
+      <c r="G10" s="344" t="n"/>
+      <c r="H10" s="344" t="n"/>
+      <c r="I10" s="344" t="n"/>
+      <c r="J10" s="344" t="n"/>
+      <c r="K10" s="477" t="n"/>
+      <c r="L10" s="362" t="n"/>
+      <c r="M10" s="362" t="n"/>
+      <c r="N10" s="362" t="n"/>
+      <c r="O10" s="362" t="n"/>
+      <c r="P10" s="362" t="n"/>
+      <c r="Q10" s="362" t="n"/>
+      <c r="R10" s="362" t="n"/>
+      <c r="S10" s="362" t="n"/>
+      <c r="T10" s="362" t="n"/>
+      <c r="U10" s="362" t="n"/>
+      <c r="V10" s="362" t="n"/>
+      <c r="W10" s="362" t="n"/>
+      <c r="X10" s="362" t="n"/>
+      <c r="Y10" s="362" t="n"/>
+      <c r="Z10" s="362" t="n"/>
+      <c r="AA10" s="362" t="n"/>
+      <c r="AB10" s="362" t="n"/>
+      <c r="AC10" s="478" t="inlineStr">
         <is>
           <t>Line Clearance / Gowning</t>
         </is>
       </c>
-      <c r="AD10" s="406" t="n"/>
-      <c r="AE10" s="406" t="n"/>
-      <c r="AF10" s="406" t="n"/>
-      <c r="AG10" s="406" t="n"/>
-      <c r="AH10" s="406" t="n"/>
-      <c r="AI10" s="406" t="n"/>
-      <c r="AJ10" s="406" t="n"/>
-      <c r="AK10" s="406" t="n"/>
-      <c r="AL10" s="407" t="n"/>
-      <c r="AM10" s="358" t="n"/>
-      <c r="AN10" s="408" t="n"/>
-      <c r="AO10" s="408" t="n"/>
-      <c r="AP10" s="408" t="n"/>
-      <c r="AQ10" s="408" t="n"/>
-      <c r="AR10" s="408" t="n"/>
-      <c r="AS10" s="408" t="n"/>
-      <c r="AT10" s="408" t="n"/>
-      <c r="AU10" s="408" t="n"/>
-      <c r="AV10" s="408" t="n"/>
-      <c r="AW10" s="408" t="n"/>
-      <c r="AX10" s="408" t="n"/>
-      <c r="AY10" s="408" t="n"/>
-      <c r="AZ10" s="408" t="n"/>
-      <c r="BA10" s="408" t="n"/>
-      <c r="BB10" s="408" t="n"/>
-      <c r="BC10" s="408" t="n"/>
-      <c r="BD10" s="409" t="n"/>
+      <c r="AD10" s="344" t="n"/>
+      <c r="AE10" s="344" t="n"/>
+      <c r="AF10" s="344" t="n"/>
+      <c r="AG10" s="344" t="n"/>
+      <c r="AH10" s="344" t="n"/>
+      <c r="AI10" s="344" t="n"/>
+      <c r="AJ10" s="344" t="n"/>
+      <c r="AK10" s="344" t="n"/>
+      <c r="AL10" s="344" t="n"/>
+      <c r="AM10" s="477" t="n"/>
+      <c r="AN10" s="362" t="n"/>
+      <c r="AO10" s="362" t="n"/>
+      <c r="AP10" s="362" t="n"/>
+      <c r="AQ10" s="362" t="n"/>
+      <c r="AR10" s="362" t="n"/>
+      <c r="AS10" s="362" t="n"/>
+      <c r="AT10" s="362" t="n"/>
+      <c r="AU10" s="362" t="n"/>
+      <c r="AV10" s="362" t="n"/>
+      <c r="AW10" s="362" t="n"/>
+      <c r="AX10" s="362" t="n"/>
+      <c r="AY10" s="362" t="n"/>
+      <c r="AZ10" s="362" t="n"/>
+      <c r="BA10" s="362" t="n"/>
+      <c r="BB10" s="362" t="n"/>
+      <c r="BC10" s="362" t="n"/>
+      <c r="BD10" s="479" t="n"/>
     </row>
-    <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="355" t="inlineStr">
+    <row r="11" ht="26" customHeight="1">
+      <c r="A11" s="476" t="inlineStr">
         <is>
           <t>Prepared by / Date-Time</t>
         </is>
       </c>
-      <c r="B11" s="401" t="n"/>
-      <c r="C11" s="401" t="n"/>
-      <c r="D11" s="401" t="n"/>
-      <c r="E11" s="401" t="n"/>
-      <c r="F11" s="401" t="n"/>
-      <c r="G11" s="401" t="n"/>
-      <c r="H11" s="401" t="n"/>
-      <c r="I11" s="401" t="n"/>
-      <c r="J11" s="402" t="n"/>
-      <c r="K11" s="358" t="n"/>
-      <c r="L11" s="410" t="n"/>
-      <c r="M11" s="410" t="n"/>
-      <c r="N11" s="410" t="n"/>
-      <c r="O11" s="410" t="n"/>
-      <c r="P11" s="410" t="n"/>
-      <c r="Q11" s="410" t="n"/>
-      <c r="R11" s="410" t="n"/>
-      <c r="S11" s="410" t="n"/>
-      <c r="T11" s="410" t="n"/>
-      <c r="U11" s="410" t="n"/>
-      <c r="V11" s="410" t="n"/>
-      <c r="W11" s="410" t="n"/>
-      <c r="X11" s="410" t="n"/>
-      <c r="Y11" s="410" t="n"/>
-      <c r="Z11" s="410" t="n"/>
-      <c r="AA11" s="410" t="n"/>
-      <c r="AB11" s="411" t="n"/>
-      <c r="AC11" s="361" t="inlineStr">
+      <c r="B11" s="344" t="n"/>
+      <c r="C11" s="344" t="n"/>
+      <c r="D11" s="344" t="n"/>
+      <c r="E11" s="344" t="n"/>
+      <c r="F11" s="344" t="n"/>
+      <c r="G11" s="344" t="n"/>
+      <c r="H11" s="344" t="n"/>
+      <c r="I11" s="344" t="n"/>
+      <c r="J11" s="344" t="n"/>
+      <c r="K11" s="477" t="n"/>
+      <c r="L11" s="362" t="n"/>
+      <c r="M11" s="362" t="n"/>
+      <c r="N11" s="362" t="n"/>
+      <c r="O11" s="362" t="n"/>
+      <c r="P11" s="362" t="n"/>
+      <c r="Q11" s="362" t="n"/>
+      <c r="R11" s="362" t="n"/>
+      <c r="S11" s="362" t="n"/>
+      <c r="T11" s="362" t="n"/>
+      <c r="U11" s="362" t="n"/>
+      <c r="V11" s="362" t="n"/>
+      <c r="W11" s="362" t="n"/>
+      <c r="X11" s="362" t="n"/>
+      <c r="Y11" s="362" t="n"/>
+      <c r="Z11" s="362" t="n"/>
+      <c r="AA11" s="362" t="n"/>
+      <c r="AB11" s="362" t="n"/>
+      <c r="AC11" s="478" t="inlineStr">
         <is>
           <t>Warehouse Owner</t>
         </is>
       </c>
-      <c r="AD11" s="401" t="n"/>
-      <c r="AE11" s="401" t="n"/>
-      <c r="AF11" s="401" t="n"/>
-      <c r="AG11" s="401" t="n"/>
-      <c r="AH11" s="401" t="n"/>
-      <c r="AI11" s="401" t="n"/>
-      <c r="AJ11" s="401" t="n"/>
-      <c r="AK11" s="401" t="n"/>
-      <c r="AL11" s="402" t="n"/>
-      <c r="AM11" s="358" t="n"/>
-      <c r="AN11" s="410" t="n"/>
-      <c r="AO11" s="410" t="n"/>
-      <c r="AP11" s="410" t="n"/>
-      <c r="AQ11" s="410" t="n"/>
-      <c r="AR11" s="410" t="n"/>
-      <c r="AS11" s="410" t="n"/>
-      <c r="AT11" s="410" t="n"/>
-      <c r="AU11" s="410" t="n"/>
-      <c r="AV11" s="410" t="n"/>
-      <c r="AW11" s="410" t="n"/>
-      <c r="AX11" s="410" t="n"/>
-      <c r="AY11" s="410" t="n"/>
-      <c r="AZ11" s="410" t="n"/>
-      <c r="BA11" s="410" t="n"/>
-      <c r="BB11" s="410" t="n"/>
-      <c r="BC11" s="410" t="n"/>
-      <c r="BD11" s="411" t="n"/>
+      <c r="AD11" s="344" t="n"/>
+      <c r="AE11" s="344" t="n"/>
+      <c r="AF11" s="344" t="n"/>
+      <c r="AG11" s="344" t="n"/>
+      <c r="AH11" s="344" t="n"/>
+      <c r="AI11" s="344" t="n"/>
+      <c r="AJ11" s="344" t="n"/>
+      <c r="AK11" s="344" t="n"/>
+      <c r="AL11" s="344" t="n"/>
+      <c r="AM11" s="477" t="n"/>
+      <c r="AN11" s="362" t="n"/>
+      <c r="AO11" s="362" t="n"/>
+      <c r="AP11" s="362" t="n"/>
+      <c r="AQ11" s="362" t="n"/>
+      <c r="AR11" s="362" t="n"/>
+      <c r="AS11" s="362" t="n"/>
+      <c r="AT11" s="362" t="n"/>
+      <c r="AU11" s="362" t="n"/>
+      <c r="AV11" s="362" t="n"/>
+      <c r="AW11" s="362" t="n"/>
+      <c r="AX11" s="362" t="n"/>
+      <c r="AY11" s="362" t="n"/>
+      <c r="AZ11" s="362" t="n"/>
+      <c r="BA11" s="362" t="n"/>
+      <c r="BB11" s="362" t="n"/>
+      <c r="BC11" s="362" t="n"/>
+      <c r="BD11" s="479" t="n"/>
     </row>
     <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="355" t="inlineStr">
+      <c r="A12" s="480" t="inlineStr">
         <is>
           <t>Evidence Package Ref</t>
         </is>
       </c>
-      <c r="B12" s="406" t="n"/>
-      <c r="C12" s="406" t="n"/>
-      <c r="D12" s="406" t="n"/>
-      <c r="E12" s="406" t="n"/>
-      <c r="F12" s="406" t="n"/>
-      <c r="G12" s="406" t="n"/>
-      <c r="H12" s="406" t="n"/>
-      <c r="I12" s="406" t="n"/>
-      <c r="J12" s="407" t="n"/>
-      <c r="K12" s="358" t="n"/>
-      <c r="L12" s="408" t="n"/>
-      <c r="M12" s="408" t="n"/>
-      <c r="N12" s="408" t="n"/>
-      <c r="O12" s="408" t="n"/>
-      <c r="P12" s="408" t="n"/>
-      <c r="Q12" s="408" t="n"/>
-      <c r="R12" s="408" t="n"/>
-      <c r="S12" s="408" t="n"/>
-      <c r="T12" s="408" t="n"/>
-      <c r="U12" s="408" t="n"/>
-      <c r="V12" s="408" t="n"/>
-      <c r="W12" s="408" t="n"/>
-      <c r="X12" s="408" t="n"/>
-      <c r="Y12" s="408" t="n"/>
-      <c r="Z12" s="408" t="n"/>
-      <c r="AA12" s="408" t="n"/>
-      <c r="AB12" s="409" t="n"/>
-      <c r="AC12" s="361" t="inlineStr">
+      <c r="B12" s="481" t="n"/>
+      <c r="C12" s="481" t="n"/>
+      <c r="D12" s="481" t="n"/>
+      <c r="E12" s="481" t="n"/>
+      <c r="F12" s="481" t="n"/>
+      <c r="G12" s="481" t="n"/>
+      <c r="H12" s="481" t="n"/>
+      <c r="I12" s="481" t="n"/>
+      <c r="J12" s="481" t="n"/>
+      <c r="K12" s="482" t="n"/>
+      <c r="L12" s="483" t="n"/>
+      <c r="M12" s="483" t="n"/>
+      <c r="N12" s="483" t="n"/>
+      <c r="O12" s="483" t="n"/>
+      <c r="P12" s="483" t="n"/>
+      <c r="Q12" s="483" t="n"/>
+      <c r="R12" s="483" t="n"/>
+      <c r="S12" s="483" t="n"/>
+      <c r="T12" s="483" t="n"/>
+      <c r="U12" s="483" t="n"/>
+      <c r="V12" s="483" t="n"/>
+      <c r="W12" s="483" t="n"/>
+      <c r="X12" s="483" t="n"/>
+      <c r="Y12" s="483" t="n"/>
+      <c r="Z12" s="483" t="n"/>
+      <c r="AA12" s="483" t="n"/>
+      <c r="AB12" s="483" t="n"/>
+      <c r="AC12" s="484" t="inlineStr">
         <is>
           <t>Record Status</t>
         </is>
       </c>
-      <c r="AD12" s="406" t="n"/>
-      <c r="AE12" s="406" t="n"/>
-      <c r="AF12" s="406" t="n"/>
-      <c r="AG12" s="406" t="n"/>
-      <c r="AH12" s="406" t="n"/>
-      <c r="AI12" s="406" t="n"/>
-      <c r="AJ12" s="406" t="n"/>
-      <c r="AK12" s="406" t="n"/>
-      <c r="AL12" s="407" t="n"/>
-      <c r="AM12" s="358" t="n"/>
-      <c r="AN12" s="408" t="n"/>
-      <c r="AO12" s="408" t="n"/>
-      <c r="AP12" s="408" t="n"/>
-      <c r="AQ12" s="408" t="n"/>
-      <c r="AR12" s="408" t="n"/>
-      <c r="AS12" s="408" t="n"/>
-      <c r="AT12" s="408" t="n"/>
-      <c r="AU12" s="408" t="n"/>
-      <c r="AV12" s="408" t="n"/>
-      <c r="AW12" s="408" t="n"/>
-      <c r="AX12" s="408" t="n"/>
-      <c r="AY12" s="408" t="n"/>
-      <c r="AZ12" s="408" t="n"/>
-      <c r="BA12" s="408" t="n"/>
-      <c r="BB12" s="408" t="n"/>
-      <c r="BC12" s="408" t="n"/>
-      <c r="BD12" s="409" t="n"/>
+      <c r="AD12" s="481" t="n"/>
+      <c r="AE12" s="481" t="n"/>
+      <c r="AF12" s="481" t="n"/>
+      <c r="AG12" s="481" t="n"/>
+      <c r="AH12" s="481" t="n"/>
+      <c r="AI12" s="481" t="n"/>
+      <c r="AJ12" s="481" t="n"/>
+      <c r="AK12" s="481" t="n"/>
+      <c r="AL12" s="481" t="n"/>
+      <c r="AM12" s="482" t="n"/>
+      <c r="AN12" s="483" t="n"/>
+      <c r="AO12" s="483" t="n"/>
+      <c r="AP12" s="483" t="n"/>
+      <c r="AQ12" s="483" t="n"/>
+      <c r="AR12" s="483" t="n"/>
+      <c r="AS12" s="483" t="n"/>
+      <c r="AT12" s="483" t="n"/>
+      <c r="AU12" s="483" t="n"/>
+      <c r="AV12" s="483" t="n"/>
+      <c r="AW12" s="483" t="n"/>
+      <c r="AX12" s="483" t="n"/>
+      <c r="AY12" s="483" t="n"/>
+      <c r="AZ12" s="483" t="n"/>
+      <c r="BA12" s="483" t="n"/>
+      <c r="BB12" s="483" t="n"/>
+      <c r="BC12" s="483" t="n"/>
+      <c r="BD12" s="485" t="n"/>
     </row>
-    <row r="13" ht="4" customHeight="1">
+    <row r="13" ht="3" customHeight="1">
       <c r="A13" s="353" t="n"/>
       <c r="B13" s="353" t="n"/>
       <c r="C13" s="353" t="n"/>
@@ -6084,643 +6981,643 @@
       <c r="BC13" s="353" t="n"/>
       <c r="BD13" s="353" t="n"/>
     </row>
-    <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="354" t="inlineStr">
+    <row r="14" ht="18" customHeight="1">
+      <c r="A14" s="467" t="inlineStr">
         <is>
           <t xml:space="preserve">  2. CLEAN BUILD / BAGGING VERIFICATION</t>
         </is>
       </c>
-      <c r="B14" s="406" t="n"/>
-      <c r="C14" s="406" t="n"/>
-      <c r="D14" s="406" t="n"/>
-      <c r="E14" s="406" t="n"/>
-      <c r="F14" s="406" t="n"/>
-      <c r="G14" s="406" t="n"/>
-      <c r="H14" s="406" t="n"/>
-      <c r="I14" s="406" t="n"/>
-      <c r="J14" s="406" t="n"/>
-      <c r="K14" s="406" t="n"/>
-      <c r="L14" s="406" t="n"/>
-      <c r="M14" s="406" t="n"/>
-      <c r="N14" s="406" t="n"/>
-      <c r="O14" s="406" t="n"/>
-      <c r="P14" s="406" t="n"/>
-      <c r="Q14" s="406" t="n"/>
-      <c r="R14" s="406" t="n"/>
-      <c r="S14" s="406" t="n"/>
-      <c r="T14" s="406" t="n"/>
-      <c r="U14" s="406" t="n"/>
-      <c r="V14" s="406" t="n"/>
-      <c r="W14" s="406" t="n"/>
-      <c r="X14" s="406" t="n"/>
-      <c r="Y14" s="406" t="n"/>
-      <c r="Z14" s="406" t="n"/>
-      <c r="AA14" s="406" t="n"/>
-      <c r="AB14" s="406" t="n"/>
-      <c r="AC14" s="406" t="n"/>
-      <c r="AD14" s="406" t="n"/>
-      <c r="AE14" s="406" t="n"/>
-      <c r="AF14" s="406" t="n"/>
-      <c r="AG14" s="406" t="n"/>
-      <c r="AH14" s="406" t="n"/>
-      <c r="AI14" s="406" t="n"/>
-      <c r="AJ14" s="406" t="n"/>
-      <c r="AK14" s="406" t="n"/>
-      <c r="AL14" s="406" t="n"/>
-      <c r="AM14" s="406" t="n"/>
-      <c r="AN14" s="406" t="n"/>
-      <c r="AO14" s="406" t="n"/>
-      <c r="AP14" s="406" t="n"/>
-      <c r="AQ14" s="406" t="n"/>
-      <c r="AR14" s="406" t="n"/>
-      <c r="AS14" s="406" t="n"/>
-      <c r="AT14" s="406" t="n"/>
-      <c r="AU14" s="406" t="n"/>
-      <c r="AV14" s="406" t="n"/>
-      <c r="AW14" s="406" t="n"/>
-      <c r="AX14" s="406" t="n"/>
-      <c r="AY14" s="406" t="n"/>
-      <c r="AZ14" s="406" t="n"/>
-      <c r="BA14" s="406" t="n"/>
-      <c r="BB14" s="406" t="n"/>
-      <c r="BC14" s="406" t="n"/>
-      <c r="BD14" s="407" t="n"/>
+      <c r="B14" s="468" t="n"/>
+      <c r="C14" s="468" t="n"/>
+      <c r="D14" s="468" t="n"/>
+      <c r="E14" s="468" t="n"/>
+      <c r="F14" s="468" t="n"/>
+      <c r="G14" s="468" t="n"/>
+      <c r="H14" s="468" t="n"/>
+      <c r="I14" s="468" t="n"/>
+      <c r="J14" s="468" t="n"/>
+      <c r="K14" s="468" t="n"/>
+      <c r="L14" s="468" t="n"/>
+      <c r="M14" s="468" t="n"/>
+      <c r="N14" s="468" t="n"/>
+      <c r="O14" s="468" t="n"/>
+      <c r="P14" s="468" t="n"/>
+      <c r="Q14" s="468" t="n"/>
+      <c r="R14" s="468" t="n"/>
+      <c r="S14" s="468" t="n"/>
+      <c r="T14" s="468" t="n"/>
+      <c r="U14" s="468" t="n"/>
+      <c r="V14" s="468" t="n"/>
+      <c r="W14" s="468" t="n"/>
+      <c r="X14" s="468" t="n"/>
+      <c r="Y14" s="468" t="n"/>
+      <c r="Z14" s="468" t="n"/>
+      <c r="AA14" s="468" t="n"/>
+      <c r="AB14" s="468" t="n"/>
+      <c r="AC14" s="468" t="n"/>
+      <c r="AD14" s="468" t="n"/>
+      <c r="AE14" s="468" t="n"/>
+      <c r="AF14" s="468" t="n"/>
+      <c r="AG14" s="468" t="n"/>
+      <c r="AH14" s="468" t="n"/>
+      <c r="AI14" s="468" t="n"/>
+      <c r="AJ14" s="468" t="n"/>
+      <c r="AK14" s="468" t="n"/>
+      <c r="AL14" s="468" t="n"/>
+      <c r="AM14" s="468" t="n"/>
+      <c r="AN14" s="468" t="n"/>
+      <c r="AO14" s="468" t="n"/>
+      <c r="AP14" s="468" t="n"/>
+      <c r="AQ14" s="468" t="n"/>
+      <c r="AR14" s="468" t="n"/>
+      <c r="AS14" s="468" t="n"/>
+      <c r="AT14" s="468" t="n"/>
+      <c r="AU14" s="468" t="n"/>
+      <c r="AV14" s="468" t="n"/>
+      <c r="AW14" s="468" t="n"/>
+      <c r="AX14" s="468" t="n"/>
+      <c r="AY14" s="468" t="n"/>
+      <c r="AZ14" s="468" t="n"/>
+      <c r="BA14" s="468" t="n"/>
+      <c r="BB14" s="468" t="n"/>
+      <c r="BC14" s="468" t="n"/>
+      <c r="BD14" s="469" t="n"/>
     </row>
-    <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="364" t="inlineStr">
+    <row r="15" ht="18" customHeight="1">
+      <c r="A15" s="486" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B15" s="406" t="n"/>
-      <c r="C15" s="407" t="n"/>
-      <c r="D15" s="365" t="inlineStr">
+      <c r="B15" s="487" t="n"/>
+      <c r="C15" s="487" t="n"/>
+      <c r="D15" s="488" t="inlineStr">
         <is>
           <t>Cat.</t>
         </is>
       </c>
-      <c r="E15" s="406" t="n"/>
-      <c r="F15" s="406" t="n"/>
-      <c r="G15" s="407" t="n"/>
-      <c r="H15" s="365" t="inlineStr">
+      <c r="E15" s="487" t="n"/>
+      <c r="F15" s="487" t="n"/>
+      <c r="G15" s="487" t="n"/>
+      <c r="H15" s="488" t="inlineStr">
         <is>
           <t>Clean Build / Bagging Requirement</t>
         </is>
       </c>
-      <c r="I15" s="406" t="n"/>
-      <c r="J15" s="406" t="n"/>
-      <c r="K15" s="406" t="n"/>
-      <c r="L15" s="406" t="n"/>
-      <c r="M15" s="406" t="n"/>
-      <c r="N15" s="406" t="n"/>
-      <c r="O15" s="406" t="n"/>
-      <c r="P15" s="406" t="n"/>
-      <c r="Q15" s="406" t="n"/>
-      <c r="R15" s="406" t="n"/>
-      <c r="S15" s="406" t="n"/>
-      <c r="T15" s="406" t="n"/>
-      <c r="U15" s="406" t="n"/>
-      <c r="V15" s="406" t="n"/>
-      <c r="W15" s="406" t="n"/>
-      <c r="X15" s="406" t="n"/>
-      <c r="Y15" s="406" t="n"/>
-      <c r="Z15" s="407" t="n"/>
-      <c r="AA15" s="365" t="inlineStr">
+      <c r="I15" s="487" t="n"/>
+      <c r="J15" s="487" t="n"/>
+      <c r="K15" s="487" t="n"/>
+      <c r="L15" s="487" t="n"/>
+      <c r="M15" s="487" t="n"/>
+      <c r="N15" s="487" t="n"/>
+      <c r="O15" s="487" t="n"/>
+      <c r="P15" s="487" t="n"/>
+      <c r="Q15" s="487" t="n"/>
+      <c r="R15" s="487" t="n"/>
+      <c r="S15" s="487" t="n"/>
+      <c r="T15" s="487" t="n"/>
+      <c r="U15" s="487" t="n"/>
+      <c r="V15" s="487" t="n"/>
+      <c r="W15" s="487" t="n"/>
+      <c r="X15" s="487" t="n"/>
+      <c r="Y15" s="487" t="n"/>
+      <c r="Z15" s="487" t="n"/>
+      <c r="AA15" s="488" t="inlineStr">
         <is>
           <t>Evidence / Method</t>
         </is>
       </c>
-      <c r="AB15" s="406" t="n"/>
-      <c r="AC15" s="406" t="n"/>
-      <c r="AD15" s="406" t="n"/>
-      <c r="AE15" s="406" t="n"/>
-      <c r="AF15" s="406" t="n"/>
-      <c r="AG15" s="406" t="n"/>
-      <c r="AH15" s="406" t="n"/>
-      <c r="AI15" s="406" t="n"/>
-      <c r="AJ15" s="406" t="n"/>
-      <c r="AK15" s="406" t="n"/>
-      <c r="AL15" s="406" t="n"/>
-      <c r="AM15" s="406" t="n"/>
-      <c r="AN15" s="406" t="n"/>
-      <c r="AO15" s="406" t="n"/>
-      <c r="AP15" s="406" t="n"/>
-      <c r="AQ15" s="407" t="n"/>
-      <c r="AR15" s="365" t="inlineStr">
+      <c r="AB15" s="487" t="n"/>
+      <c r="AC15" s="487" t="n"/>
+      <c r="AD15" s="487" t="n"/>
+      <c r="AE15" s="487" t="n"/>
+      <c r="AF15" s="487" t="n"/>
+      <c r="AG15" s="487" t="n"/>
+      <c r="AH15" s="487" t="n"/>
+      <c r="AI15" s="487" t="n"/>
+      <c r="AJ15" s="487" t="n"/>
+      <c r="AK15" s="487" t="n"/>
+      <c r="AL15" s="487" t="n"/>
+      <c r="AM15" s="487" t="n"/>
+      <c r="AN15" s="487" t="n"/>
+      <c r="AO15" s="487" t="n"/>
+      <c r="AP15" s="487" t="n"/>
+      <c r="AQ15" s="487" t="n"/>
+      <c r="AR15" s="488" t="inlineStr">
         <is>
           <t>Result</t>
         </is>
       </c>
-      <c r="AS15" s="406" t="n"/>
-      <c r="AT15" s="406" t="n"/>
-      <c r="AU15" s="406" t="n"/>
-      <c r="AV15" s="406" t="n"/>
-      <c r="AW15" s="407" t="n"/>
-      <c r="AX15" s="365" t="inlineStr">
+      <c r="AS15" s="487" t="n"/>
+      <c r="AT15" s="487" t="n"/>
+      <c r="AU15" s="487" t="n"/>
+      <c r="AV15" s="487" t="n"/>
+      <c r="AW15" s="487" t="n"/>
+      <c r="AX15" s="488" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="AY15" s="406" t="n"/>
-      <c r="AZ15" s="406" t="n"/>
-      <c r="BA15" s="407" t="n"/>
-      <c r="BB15" s="365" t="inlineStr">
+      <c r="AY15" s="487" t="n"/>
+      <c r="AZ15" s="487" t="n"/>
+      <c r="BA15" s="487" t="n"/>
+      <c r="BB15" s="488" t="inlineStr">
         <is>
           <t>Ref.</t>
         </is>
       </c>
-      <c r="BC15" s="406" t="n"/>
-      <c r="BD15" s="407" t="n"/>
+      <c r="BC15" s="487" t="n"/>
+      <c r="BD15" s="489" t="n"/>
     </row>
     <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="366">
+      <c r="A16" s="490">
         <f>ROW()-ROW($A$16)+1</f>
         <v/>
       </c>
-      <c r="B16" s="412" t="n"/>
-      <c r="C16" s="413" t="n"/>
-      <c r="D16" s="369" t="n"/>
-      <c r="E16" s="414" t="n"/>
-      <c r="F16" s="414" t="n"/>
-      <c r="G16" s="415" t="n"/>
-      <c r="H16" s="372" t="n"/>
-      <c r="I16" s="414" t="n"/>
-      <c r="J16" s="414" t="n"/>
-      <c r="K16" s="414" t="n"/>
-      <c r="L16" s="414" t="n"/>
-      <c r="M16" s="414" t="n"/>
-      <c r="N16" s="414" t="n"/>
-      <c r="O16" s="414" t="n"/>
-      <c r="P16" s="414" t="n"/>
-      <c r="Q16" s="414" t="n"/>
-      <c r="R16" s="414" t="n"/>
-      <c r="S16" s="414" t="n"/>
-      <c r="T16" s="414" t="n"/>
-      <c r="U16" s="414" t="n"/>
-      <c r="V16" s="414" t="n"/>
-      <c r="W16" s="414" t="n"/>
-      <c r="X16" s="414" t="n"/>
-      <c r="Y16" s="414" t="n"/>
-      <c r="Z16" s="415" t="n"/>
-      <c r="AA16" s="373" t="n"/>
-      <c r="AB16" s="414" t="n"/>
-      <c r="AC16" s="414" t="n"/>
-      <c r="AD16" s="414" t="n"/>
-      <c r="AE16" s="414" t="n"/>
-      <c r="AF16" s="414" t="n"/>
-      <c r="AG16" s="414" t="n"/>
-      <c r="AH16" s="414" t="n"/>
-      <c r="AI16" s="414" t="n"/>
-      <c r="AJ16" s="414" t="n"/>
-      <c r="AK16" s="414" t="n"/>
-      <c r="AL16" s="414" t="n"/>
-      <c r="AM16" s="414" t="n"/>
-      <c r="AN16" s="414" t="n"/>
-      <c r="AO16" s="414" t="n"/>
-      <c r="AP16" s="414" t="n"/>
-      <c r="AQ16" s="415" t="n"/>
-      <c r="AR16" s="372" t="n"/>
-      <c r="AS16" s="414" t="n"/>
-      <c r="AT16" s="414" t="n"/>
-      <c r="AU16" s="414" t="n"/>
-      <c r="AV16" s="414" t="n"/>
-      <c r="AW16" s="415" t="n"/>
-      <c r="AX16" s="372" t="n"/>
-      <c r="AY16" s="414" t="n"/>
-      <c r="AZ16" s="414" t="n"/>
-      <c r="BA16" s="415" t="n"/>
-      <c r="BB16" s="374" t="n"/>
-      <c r="BC16" s="414" t="n"/>
-      <c r="BD16" s="415" t="n"/>
+      <c r="B16" s="471" t="n"/>
+      <c r="C16" s="471" t="n"/>
+      <c r="D16" s="491" t="n"/>
+      <c r="E16" s="473" t="n"/>
+      <c r="F16" s="473" t="n"/>
+      <c r="G16" s="473" t="n"/>
+      <c r="H16" s="472" t="n"/>
+      <c r="I16" s="473" t="n"/>
+      <c r="J16" s="473" t="n"/>
+      <c r="K16" s="473" t="n"/>
+      <c r="L16" s="473" t="n"/>
+      <c r="M16" s="473" t="n"/>
+      <c r="N16" s="473" t="n"/>
+      <c r="O16" s="473" t="n"/>
+      <c r="P16" s="473" t="n"/>
+      <c r="Q16" s="473" t="n"/>
+      <c r="R16" s="473" t="n"/>
+      <c r="S16" s="473" t="n"/>
+      <c r="T16" s="473" t="n"/>
+      <c r="U16" s="473" t="n"/>
+      <c r="V16" s="473" t="n"/>
+      <c r="W16" s="473" t="n"/>
+      <c r="X16" s="473" t="n"/>
+      <c r="Y16" s="473" t="n"/>
+      <c r="Z16" s="473" t="n"/>
+      <c r="AA16" s="492" t="n"/>
+      <c r="AB16" s="473" t="n"/>
+      <c r="AC16" s="473" t="n"/>
+      <c r="AD16" s="473" t="n"/>
+      <c r="AE16" s="473" t="n"/>
+      <c r="AF16" s="473" t="n"/>
+      <c r="AG16" s="473" t="n"/>
+      <c r="AH16" s="473" t="n"/>
+      <c r="AI16" s="473" t="n"/>
+      <c r="AJ16" s="473" t="n"/>
+      <c r="AK16" s="473" t="n"/>
+      <c r="AL16" s="473" t="n"/>
+      <c r="AM16" s="473" t="n"/>
+      <c r="AN16" s="473" t="n"/>
+      <c r="AO16" s="473" t="n"/>
+      <c r="AP16" s="473" t="n"/>
+      <c r="AQ16" s="473" t="n"/>
+      <c r="AR16" s="472" t="n"/>
+      <c r="AS16" s="473" t="n"/>
+      <c r="AT16" s="473" t="n"/>
+      <c r="AU16" s="473" t="n"/>
+      <c r="AV16" s="473" t="n"/>
+      <c r="AW16" s="473" t="n"/>
+      <c r="AX16" s="472" t="n"/>
+      <c r="AY16" s="473" t="n"/>
+      <c r="AZ16" s="473" t="n"/>
+      <c r="BA16" s="473" t="n"/>
+      <c r="BB16" s="493" t="n"/>
+      <c r="BC16" s="473" t="n"/>
+      <c r="BD16" s="475" t="n"/>
     </row>
     <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="366">
+      <c r="A17" s="494">
         <f>ROW()-ROW($A$16)+1</f>
         <v/>
       </c>
-      <c r="B17" s="412" t="n"/>
-      <c r="C17" s="413" t="n"/>
-      <c r="D17" s="369" t="n"/>
-      <c r="E17" s="414" t="n"/>
-      <c r="F17" s="414" t="n"/>
-      <c r="G17" s="415" t="n"/>
-      <c r="H17" s="372" t="n"/>
-      <c r="I17" s="414" t="n"/>
-      <c r="J17" s="414" t="n"/>
-      <c r="K17" s="414" t="n"/>
-      <c r="L17" s="414" t="n"/>
-      <c r="M17" s="414" t="n"/>
-      <c r="N17" s="414" t="n"/>
-      <c r="O17" s="414" t="n"/>
-      <c r="P17" s="414" t="n"/>
-      <c r="Q17" s="414" t="n"/>
-      <c r="R17" s="414" t="n"/>
-      <c r="S17" s="414" t="n"/>
-      <c r="T17" s="414" t="n"/>
-      <c r="U17" s="414" t="n"/>
-      <c r="V17" s="414" t="n"/>
-      <c r="W17" s="414" t="n"/>
-      <c r="X17" s="414" t="n"/>
-      <c r="Y17" s="414" t="n"/>
-      <c r="Z17" s="415" t="n"/>
-      <c r="AA17" s="373" t="n"/>
-      <c r="AB17" s="414" t="n"/>
-      <c r="AC17" s="414" t="n"/>
-      <c r="AD17" s="414" t="n"/>
-      <c r="AE17" s="414" t="n"/>
-      <c r="AF17" s="414" t="n"/>
-      <c r="AG17" s="414" t="n"/>
-      <c r="AH17" s="414" t="n"/>
-      <c r="AI17" s="414" t="n"/>
-      <c r="AJ17" s="414" t="n"/>
-      <c r="AK17" s="414" t="n"/>
-      <c r="AL17" s="414" t="n"/>
-      <c r="AM17" s="414" t="n"/>
-      <c r="AN17" s="414" t="n"/>
-      <c r="AO17" s="414" t="n"/>
-      <c r="AP17" s="414" t="n"/>
-      <c r="AQ17" s="415" t="n"/>
-      <c r="AR17" s="372" t="n"/>
-      <c r="AS17" s="414" t="n"/>
-      <c r="AT17" s="414" t="n"/>
-      <c r="AU17" s="414" t="n"/>
-      <c r="AV17" s="414" t="n"/>
-      <c r="AW17" s="415" t="n"/>
-      <c r="AX17" s="372" t="n"/>
-      <c r="AY17" s="414" t="n"/>
-      <c r="AZ17" s="414" t="n"/>
-      <c r="BA17" s="415" t="n"/>
-      <c r="BB17" s="374" t="n"/>
-      <c r="BC17" s="414" t="n"/>
-      <c r="BD17" s="415" t="n"/>
+      <c r="B17" s="344" t="n"/>
+      <c r="C17" s="344" t="n"/>
+      <c r="D17" s="495" t="n"/>
+      <c r="E17" s="362" t="n"/>
+      <c r="F17" s="362" t="n"/>
+      <c r="G17" s="362" t="n"/>
+      <c r="H17" s="477" t="n"/>
+      <c r="I17" s="362" t="n"/>
+      <c r="J17" s="362" t="n"/>
+      <c r="K17" s="362" t="n"/>
+      <c r="L17" s="362" t="n"/>
+      <c r="M17" s="362" t="n"/>
+      <c r="N17" s="362" t="n"/>
+      <c r="O17" s="362" t="n"/>
+      <c r="P17" s="362" t="n"/>
+      <c r="Q17" s="362" t="n"/>
+      <c r="R17" s="362" t="n"/>
+      <c r="S17" s="362" t="n"/>
+      <c r="T17" s="362" t="n"/>
+      <c r="U17" s="362" t="n"/>
+      <c r="V17" s="362" t="n"/>
+      <c r="W17" s="362" t="n"/>
+      <c r="X17" s="362" t="n"/>
+      <c r="Y17" s="362" t="n"/>
+      <c r="Z17" s="362" t="n"/>
+      <c r="AA17" s="496" t="n"/>
+      <c r="AB17" s="362" t="n"/>
+      <c r="AC17" s="362" t="n"/>
+      <c r="AD17" s="362" t="n"/>
+      <c r="AE17" s="362" t="n"/>
+      <c r="AF17" s="362" t="n"/>
+      <c r="AG17" s="362" t="n"/>
+      <c r="AH17" s="362" t="n"/>
+      <c r="AI17" s="362" t="n"/>
+      <c r="AJ17" s="362" t="n"/>
+      <c r="AK17" s="362" t="n"/>
+      <c r="AL17" s="362" t="n"/>
+      <c r="AM17" s="362" t="n"/>
+      <c r="AN17" s="362" t="n"/>
+      <c r="AO17" s="362" t="n"/>
+      <c r="AP17" s="362" t="n"/>
+      <c r="AQ17" s="362" t="n"/>
+      <c r="AR17" s="477" t="n"/>
+      <c r="AS17" s="362" t="n"/>
+      <c r="AT17" s="362" t="n"/>
+      <c r="AU17" s="362" t="n"/>
+      <c r="AV17" s="362" t="n"/>
+      <c r="AW17" s="362" t="n"/>
+      <c r="AX17" s="477" t="n"/>
+      <c r="AY17" s="362" t="n"/>
+      <c r="AZ17" s="362" t="n"/>
+      <c r="BA17" s="362" t="n"/>
+      <c r="BB17" s="497" t="n"/>
+      <c r="BC17" s="362" t="n"/>
+      <c r="BD17" s="479" t="n"/>
     </row>
     <row r="18" ht="20" customHeight="1">
-      <c r="A18" s="366">
+      <c r="A18" s="494">
         <f>ROW()-ROW($A$16)+1</f>
         <v/>
       </c>
-      <c r="B18" s="412" t="n"/>
-      <c r="C18" s="413" t="n"/>
-      <c r="D18" s="369" t="n"/>
-      <c r="E18" s="414" t="n"/>
-      <c r="F18" s="414" t="n"/>
-      <c r="G18" s="415" t="n"/>
-      <c r="H18" s="372" t="n"/>
-      <c r="I18" s="414" t="n"/>
-      <c r="J18" s="414" t="n"/>
-      <c r="K18" s="414" t="n"/>
-      <c r="L18" s="414" t="n"/>
-      <c r="M18" s="414" t="n"/>
-      <c r="N18" s="414" t="n"/>
-      <c r="O18" s="414" t="n"/>
-      <c r="P18" s="414" t="n"/>
-      <c r="Q18" s="414" t="n"/>
-      <c r="R18" s="414" t="n"/>
-      <c r="S18" s="414" t="n"/>
-      <c r="T18" s="414" t="n"/>
-      <c r="U18" s="414" t="n"/>
-      <c r="V18" s="414" t="n"/>
-      <c r="W18" s="414" t="n"/>
-      <c r="X18" s="414" t="n"/>
-      <c r="Y18" s="414" t="n"/>
-      <c r="Z18" s="415" t="n"/>
-      <c r="AA18" s="373" t="n"/>
-      <c r="AB18" s="414" t="n"/>
-      <c r="AC18" s="414" t="n"/>
-      <c r="AD18" s="414" t="n"/>
-      <c r="AE18" s="414" t="n"/>
-      <c r="AF18" s="414" t="n"/>
-      <c r="AG18" s="414" t="n"/>
-      <c r="AH18" s="414" t="n"/>
-      <c r="AI18" s="414" t="n"/>
-      <c r="AJ18" s="414" t="n"/>
-      <c r="AK18" s="414" t="n"/>
-      <c r="AL18" s="414" t="n"/>
-      <c r="AM18" s="414" t="n"/>
-      <c r="AN18" s="414" t="n"/>
-      <c r="AO18" s="414" t="n"/>
-      <c r="AP18" s="414" t="n"/>
-      <c r="AQ18" s="415" t="n"/>
-      <c r="AR18" s="372" t="n"/>
-      <c r="AS18" s="414" t="n"/>
-      <c r="AT18" s="414" t="n"/>
-      <c r="AU18" s="414" t="n"/>
-      <c r="AV18" s="414" t="n"/>
-      <c r="AW18" s="415" t="n"/>
-      <c r="AX18" s="372" t="n"/>
-      <c r="AY18" s="414" t="n"/>
-      <c r="AZ18" s="414" t="n"/>
-      <c r="BA18" s="415" t="n"/>
-      <c r="BB18" s="374" t="n"/>
-      <c r="BC18" s="414" t="n"/>
-      <c r="BD18" s="415" t="n"/>
+      <c r="B18" s="344" t="n"/>
+      <c r="C18" s="344" t="n"/>
+      <c r="D18" s="495" t="n"/>
+      <c r="E18" s="362" t="n"/>
+      <c r="F18" s="362" t="n"/>
+      <c r="G18" s="362" t="n"/>
+      <c r="H18" s="477" t="n"/>
+      <c r="I18" s="362" t="n"/>
+      <c r="J18" s="362" t="n"/>
+      <c r="K18" s="362" t="n"/>
+      <c r="L18" s="362" t="n"/>
+      <c r="M18" s="362" t="n"/>
+      <c r="N18" s="362" t="n"/>
+      <c r="O18" s="362" t="n"/>
+      <c r="P18" s="362" t="n"/>
+      <c r="Q18" s="362" t="n"/>
+      <c r="R18" s="362" t="n"/>
+      <c r="S18" s="362" t="n"/>
+      <c r="T18" s="362" t="n"/>
+      <c r="U18" s="362" t="n"/>
+      <c r="V18" s="362" t="n"/>
+      <c r="W18" s="362" t="n"/>
+      <c r="X18" s="362" t="n"/>
+      <c r="Y18" s="362" t="n"/>
+      <c r="Z18" s="362" t="n"/>
+      <c r="AA18" s="496" t="n"/>
+      <c r="AB18" s="362" t="n"/>
+      <c r="AC18" s="362" t="n"/>
+      <c r="AD18" s="362" t="n"/>
+      <c r="AE18" s="362" t="n"/>
+      <c r="AF18" s="362" t="n"/>
+      <c r="AG18" s="362" t="n"/>
+      <c r="AH18" s="362" t="n"/>
+      <c r="AI18" s="362" t="n"/>
+      <c r="AJ18" s="362" t="n"/>
+      <c r="AK18" s="362" t="n"/>
+      <c r="AL18" s="362" t="n"/>
+      <c r="AM18" s="362" t="n"/>
+      <c r="AN18" s="362" t="n"/>
+      <c r="AO18" s="362" t="n"/>
+      <c r="AP18" s="362" t="n"/>
+      <c r="AQ18" s="362" t="n"/>
+      <c r="AR18" s="477" t="n"/>
+      <c r="AS18" s="362" t="n"/>
+      <c r="AT18" s="362" t="n"/>
+      <c r="AU18" s="362" t="n"/>
+      <c r="AV18" s="362" t="n"/>
+      <c r="AW18" s="362" t="n"/>
+      <c r="AX18" s="477" t="n"/>
+      <c r="AY18" s="362" t="n"/>
+      <c r="AZ18" s="362" t="n"/>
+      <c r="BA18" s="362" t="n"/>
+      <c r="BB18" s="497" t="n"/>
+      <c r="BC18" s="362" t="n"/>
+      <c r="BD18" s="479" t="n"/>
     </row>
     <row r="19" ht="20" customHeight="1">
-      <c r="A19" s="366">
+      <c r="A19" s="494">
         <f>ROW()-ROW($A$16)+1</f>
         <v/>
       </c>
-      <c r="B19" s="412" t="n"/>
-      <c r="C19" s="413" t="n"/>
-      <c r="D19" s="369" t="n"/>
-      <c r="E19" s="414" t="n"/>
-      <c r="F19" s="414" t="n"/>
-      <c r="G19" s="415" t="n"/>
-      <c r="H19" s="372" t="n"/>
-      <c r="I19" s="414" t="n"/>
-      <c r="J19" s="414" t="n"/>
-      <c r="K19" s="414" t="n"/>
-      <c r="L19" s="414" t="n"/>
-      <c r="M19" s="414" t="n"/>
-      <c r="N19" s="414" t="n"/>
-      <c r="O19" s="414" t="n"/>
-      <c r="P19" s="414" t="n"/>
-      <c r="Q19" s="414" t="n"/>
-      <c r="R19" s="414" t="n"/>
-      <c r="S19" s="414" t="n"/>
-      <c r="T19" s="414" t="n"/>
-      <c r="U19" s="414" t="n"/>
-      <c r="V19" s="414" t="n"/>
-      <c r="W19" s="414" t="n"/>
-      <c r="X19" s="414" t="n"/>
-      <c r="Y19" s="414" t="n"/>
-      <c r="Z19" s="415" t="n"/>
-      <c r="AA19" s="373" t="n"/>
-      <c r="AB19" s="414" t="n"/>
-      <c r="AC19" s="414" t="n"/>
-      <c r="AD19" s="414" t="n"/>
-      <c r="AE19" s="414" t="n"/>
-      <c r="AF19" s="414" t="n"/>
-      <c r="AG19" s="414" t="n"/>
-      <c r="AH19" s="414" t="n"/>
-      <c r="AI19" s="414" t="n"/>
-      <c r="AJ19" s="414" t="n"/>
-      <c r="AK19" s="414" t="n"/>
-      <c r="AL19" s="414" t="n"/>
-      <c r="AM19" s="414" t="n"/>
-      <c r="AN19" s="414" t="n"/>
-      <c r="AO19" s="414" t="n"/>
-      <c r="AP19" s="414" t="n"/>
-      <c r="AQ19" s="415" t="n"/>
-      <c r="AR19" s="372" t="n"/>
-      <c r="AS19" s="414" t="n"/>
-      <c r="AT19" s="414" t="n"/>
-      <c r="AU19" s="414" t="n"/>
-      <c r="AV19" s="414" t="n"/>
-      <c r="AW19" s="415" t="n"/>
-      <c r="AX19" s="372" t="n"/>
-      <c r="AY19" s="414" t="n"/>
-      <c r="AZ19" s="414" t="n"/>
-      <c r="BA19" s="415" t="n"/>
-      <c r="BB19" s="374" t="n"/>
-      <c r="BC19" s="414" t="n"/>
-      <c r="BD19" s="415" t="n"/>
+      <c r="B19" s="344" t="n"/>
+      <c r="C19" s="344" t="n"/>
+      <c r="D19" s="495" t="n"/>
+      <c r="E19" s="362" t="n"/>
+      <c r="F19" s="362" t="n"/>
+      <c r="G19" s="362" t="n"/>
+      <c r="H19" s="477" t="n"/>
+      <c r="I19" s="362" t="n"/>
+      <c r="J19" s="362" t="n"/>
+      <c r="K19" s="362" t="n"/>
+      <c r="L19" s="362" t="n"/>
+      <c r="M19" s="362" t="n"/>
+      <c r="N19" s="362" t="n"/>
+      <c r="O19" s="362" t="n"/>
+      <c r="P19" s="362" t="n"/>
+      <c r="Q19" s="362" t="n"/>
+      <c r="R19" s="362" t="n"/>
+      <c r="S19" s="362" t="n"/>
+      <c r="T19" s="362" t="n"/>
+      <c r="U19" s="362" t="n"/>
+      <c r="V19" s="362" t="n"/>
+      <c r="W19" s="362" t="n"/>
+      <c r="X19" s="362" t="n"/>
+      <c r="Y19" s="362" t="n"/>
+      <c r="Z19" s="362" t="n"/>
+      <c r="AA19" s="496" t="n"/>
+      <c r="AB19" s="362" t="n"/>
+      <c r="AC19" s="362" t="n"/>
+      <c r="AD19" s="362" t="n"/>
+      <c r="AE19" s="362" t="n"/>
+      <c r="AF19" s="362" t="n"/>
+      <c r="AG19" s="362" t="n"/>
+      <c r="AH19" s="362" t="n"/>
+      <c r="AI19" s="362" t="n"/>
+      <c r="AJ19" s="362" t="n"/>
+      <c r="AK19" s="362" t="n"/>
+      <c r="AL19" s="362" t="n"/>
+      <c r="AM19" s="362" t="n"/>
+      <c r="AN19" s="362" t="n"/>
+      <c r="AO19" s="362" t="n"/>
+      <c r="AP19" s="362" t="n"/>
+      <c r="AQ19" s="362" t="n"/>
+      <c r="AR19" s="477" t="n"/>
+      <c r="AS19" s="362" t="n"/>
+      <c r="AT19" s="362" t="n"/>
+      <c r="AU19" s="362" t="n"/>
+      <c r="AV19" s="362" t="n"/>
+      <c r="AW19" s="362" t="n"/>
+      <c r="AX19" s="477" t="n"/>
+      <c r="AY19" s="362" t="n"/>
+      <c r="AZ19" s="362" t="n"/>
+      <c r="BA19" s="362" t="n"/>
+      <c r="BB19" s="497" t="n"/>
+      <c r="BC19" s="362" t="n"/>
+      <c r="BD19" s="479" t="n"/>
     </row>
     <row r="20" ht="20" customHeight="1">
-      <c r="A20" s="366">
+      <c r="A20" s="494">
         <f>ROW()-ROW($A$16)+1</f>
         <v/>
       </c>
-      <c r="B20" s="412" t="n"/>
-      <c r="C20" s="413" t="n"/>
-      <c r="D20" s="369" t="n"/>
-      <c r="E20" s="414" t="n"/>
-      <c r="F20" s="414" t="n"/>
-      <c r="G20" s="415" t="n"/>
-      <c r="H20" s="372" t="n"/>
-      <c r="I20" s="414" t="n"/>
-      <c r="J20" s="414" t="n"/>
-      <c r="K20" s="414" t="n"/>
-      <c r="L20" s="414" t="n"/>
-      <c r="M20" s="414" t="n"/>
-      <c r="N20" s="414" t="n"/>
-      <c r="O20" s="414" t="n"/>
-      <c r="P20" s="414" t="n"/>
-      <c r="Q20" s="414" t="n"/>
-      <c r="R20" s="414" t="n"/>
-      <c r="S20" s="414" t="n"/>
-      <c r="T20" s="414" t="n"/>
-      <c r="U20" s="414" t="n"/>
-      <c r="V20" s="414" t="n"/>
-      <c r="W20" s="414" t="n"/>
-      <c r="X20" s="414" t="n"/>
-      <c r="Y20" s="414" t="n"/>
-      <c r="Z20" s="415" t="n"/>
-      <c r="AA20" s="373" t="n"/>
-      <c r="AB20" s="414" t="n"/>
-      <c r="AC20" s="414" t="n"/>
-      <c r="AD20" s="414" t="n"/>
-      <c r="AE20" s="414" t="n"/>
-      <c r="AF20" s="414" t="n"/>
-      <c r="AG20" s="414" t="n"/>
-      <c r="AH20" s="414" t="n"/>
-      <c r="AI20" s="414" t="n"/>
-      <c r="AJ20" s="414" t="n"/>
-      <c r="AK20" s="414" t="n"/>
-      <c r="AL20" s="414" t="n"/>
-      <c r="AM20" s="414" t="n"/>
-      <c r="AN20" s="414" t="n"/>
-      <c r="AO20" s="414" t="n"/>
-      <c r="AP20" s="414" t="n"/>
-      <c r="AQ20" s="415" t="n"/>
-      <c r="AR20" s="372" t="n"/>
-      <c r="AS20" s="414" t="n"/>
-      <c r="AT20" s="414" t="n"/>
-      <c r="AU20" s="414" t="n"/>
-      <c r="AV20" s="414" t="n"/>
-      <c r="AW20" s="415" t="n"/>
-      <c r="AX20" s="372" t="n"/>
-      <c r="AY20" s="414" t="n"/>
-      <c r="AZ20" s="414" t="n"/>
-      <c r="BA20" s="415" t="n"/>
-      <c r="BB20" s="374" t="n"/>
-      <c r="BC20" s="414" t="n"/>
-      <c r="BD20" s="415" t="n"/>
+      <c r="B20" s="344" t="n"/>
+      <c r="C20" s="344" t="n"/>
+      <c r="D20" s="495" t="n"/>
+      <c r="E20" s="362" t="n"/>
+      <c r="F20" s="362" t="n"/>
+      <c r="G20" s="362" t="n"/>
+      <c r="H20" s="477" t="n"/>
+      <c r="I20" s="362" t="n"/>
+      <c r="J20" s="362" t="n"/>
+      <c r="K20" s="362" t="n"/>
+      <c r="L20" s="362" t="n"/>
+      <c r="M20" s="362" t="n"/>
+      <c r="N20" s="362" t="n"/>
+      <c r="O20" s="362" t="n"/>
+      <c r="P20" s="362" t="n"/>
+      <c r="Q20" s="362" t="n"/>
+      <c r="R20" s="362" t="n"/>
+      <c r="S20" s="362" t="n"/>
+      <c r="T20" s="362" t="n"/>
+      <c r="U20" s="362" t="n"/>
+      <c r="V20" s="362" t="n"/>
+      <c r="W20" s="362" t="n"/>
+      <c r="X20" s="362" t="n"/>
+      <c r="Y20" s="362" t="n"/>
+      <c r="Z20" s="362" t="n"/>
+      <c r="AA20" s="496" t="n"/>
+      <c r="AB20" s="362" t="n"/>
+      <c r="AC20" s="362" t="n"/>
+      <c r="AD20" s="362" t="n"/>
+      <c r="AE20" s="362" t="n"/>
+      <c r="AF20" s="362" t="n"/>
+      <c r="AG20" s="362" t="n"/>
+      <c r="AH20" s="362" t="n"/>
+      <c r="AI20" s="362" t="n"/>
+      <c r="AJ20" s="362" t="n"/>
+      <c r="AK20" s="362" t="n"/>
+      <c r="AL20" s="362" t="n"/>
+      <c r="AM20" s="362" t="n"/>
+      <c r="AN20" s="362" t="n"/>
+      <c r="AO20" s="362" t="n"/>
+      <c r="AP20" s="362" t="n"/>
+      <c r="AQ20" s="362" t="n"/>
+      <c r="AR20" s="477" t="n"/>
+      <c r="AS20" s="362" t="n"/>
+      <c r="AT20" s="362" t="n"/>
+      <c r="AU20" s="362" t="n"/>
+      <c r="AV20" s="362" t="n"/>
+      <c r="AW20" s="362" t="n"/>
+      <c r="AX20" s="477" t="n"/>
+      <c r="AY20" s="362" t="n"/>
+      <c r="AZ20" s="362" t="n"/>
+      <c r="BA20" s="362" t="n"/>
+      <c r="BB20" s="497" t="n"/>
+      <c r="BC20" s="362" t="n"/>
+      <c r="BD20" s="479" t="n"/>
     </row>
     <row r="21" ht="20" customHeight="1">
-      <c r="A21" s="366">
+      <c r="A21" s="494">
         <f>ROW()-ROW($A$16)+1</f>
         <v/>
       </c>
-      <c r="B21" s="412" t="n"/>
-      <c r="C21" s="413" t="n"/>
-      <c r="D21" s="369" t="n"/>
-      <c r="E21" s="414" t="n"/>
-      <c r="F21" s="414" t="n"/>
-      <c r="G21" s="415" t="n"/>
-      <c r="H21" s="372" t="n"/>
-      <c r="I21" s="414" t="n"/>
-      <c r="J21" s="414" t="n"/>
-      <c r="K21" s="414" t="n"/>
-      <c r="L21" s="414" t="n"/>
-      <c r="M21" s="414" t="n"/>
-      <c r="N21" s="414" t="n"/>
-      <c r="O21" s="414" t="n"/>
-      <c r="P21" s="414" t="n"/>
-      <c r="Q21" s="414" t="n"/>
-      <c r="R21" s="414" t="n"/>
-      <c r="S21" s="414" t="n"/>
-      <c r="T21" s="414" t="n"/>
-      <c r="U21" s="414" t="n"/>
-      <c r="V21" s="414" t="n"/>
-      <c r="W21" s="414" t="n"/>
-      <c r="X21" s="414" t="n"/>
-      <c r="Y21" s="414" t="n"/>
-      <c r="Z21" s="415" t="n"/>
-      <c r="AA21" s="373" t="n"/>
-      <c r="AB21" s="414" t="n"/>
-      <c r="AC21" s="414" t="n"/>
-      <c r="AD21" s="414" t="n"/>
-      <c r="AE21" s="414" t="n"/>
-      <c r="AF21" s="414" t="n"/>
-      <c r="AG21" s="414" t="n"/>
-      <c r="AH21" s="414" t="n"/>
-      <c r="AI21" s="414" t="n"/>
-      <c r="AJ21" s="414" t="n"/>
-      <c r="AK21" s="414" t="n"/>
-      <c r="AL21" s="414" t="n"/>
-      <c r="AM21" s="414" t="n"/>
-      <c r="AN21" s="414" t="n"/>
-      <c r="AO21" s="414" t="n"/>
-      <c r="AP21" s="414" t="n"/>
-      <c r="AQ21" s="415" t="n"/>
-      <c r="AR21" s="372" t="n"/>
-      <c r="AS21" s="414" t="n"/>
-      <c r="AT21" s="414" t="n"/>
-      <c r="AU21" s="414" t="n"/>
-      <c r="AV21" s="414" t="n"/>
-      <c r="AW21" s="415" t="n"/>
-      <c r="AX21" s="372" t="n"/>
-      <c r="AY21" s="414" t="n"/>
-      <c r="AZ21" s="414" t="n"/>
-      <c r="BA21" s="415" t="n"/>
-      <c r="BB21" s="374" t="n"/>
-      <c r="BC21" s="414" t="n"/>
-      <c r="BD21" s="415" t="n"/>
+      <c r="B21" s="344" t="n"/>
+      <c r="C21" s="344" t="n"/>
+      <c r="D21" s="495" t="n"/>
+      <c r="E21" s="362" t="n"/>
+      <c r="F21" s="362" t="n"/>
+      <c r="G21" s="362" t="n"/>
+      <c r="H21" s="477" t="n"/>
+      <c r="I21" s="362" t="n"/>
+      <c r="J21" s="362" t="n"/>
+      <c r="K21" s="362" t="n"/>
+      <c r="L21" s="362" t="n"/>
+      <c r="M21" s="362" t="n"/>
+      <c r="N21" s="362" t="n"/>
+      <c r="O21" s="362" t="n"/>
+      <c r="P21" s="362" t="n"/>
+      <c r="Q21" s="362" t="n"/>
+      <c r="R21" s="362" t="n"/>
+      <c r="S21" s="362" t="n"/>
+      <c r="T21" s="362" t="n"/>
+      <c r="U21" s="362" t="n"/>
+      <c r="V21" s="362" t="n"/>
+      <c r="W21" s="362" t="n"/>
+      <c r="X21" s="362" t="n"/>
+      <c r="Y21" s="362" t="n"/>
+      <c r="Z21" s="362" t="n"/>
+      <c r="AA21" s="496" t="n"/>
+      <c r="AB21" s="362" t="n"/>
+      <c r="AC21" s="362" t="n"/>
+      <c r="AD21" s="362" t="n"/>
+      <c r="AE21" s="362" t="n"/>
+      <c r="AF21" s="362" t="n"/>
+      <c r="AG21" s="362" t="n"/>
+      <c r="AH21" s="362" t="n"/>
+      <c r="AI21" s="362" t="n"/>
+      <c r="AJ21" s="362" t="n"/>
+      <c r="AK21" s="362" t="n"/>
+      <c r="AL21" s="362" t="n"/>
+      <c r="AM21" s="362" t="n"/>
+      <c r="AN21" s="362" t="n"/>
+      <c r="AO21" s="362" t="n"/>
+      <c r="AP21" s="362" t="n"/>
+      <c r="AQ21" s="362" t="n"/>
+      <c r="AR21" s="477" t="n"/>
+      <c r="AS21" s="362" t="n"/>
+      <c r="AT21" s="362" t="n"/>
+      <c r="AU21" s="362" t="n"/>
+      <c r="AV21" s="362" t="n"/>
+      <c r="AW21" s="362" t="n"/>
+      <c r="AX21" s="477" t="n"/>
+      <c r="AY21" s="362" t="n"/>
+      <c r="AZ21" s="362" t="n"/>
+      <c r="BA21" s="362" t="n"/>
+      <c r="BB21" s="497" t="n"/>
+      <c r="BC21" s="362" t="n"/>
+      <c r="BD21" s="479" t="n"/>
     </row>
     <row r="22" ht="20" customHeight="1">
-      <c r="A22" s="366">
+      <c r="A22" s="494">
         <f>ROW()-ROW($A$16)+1</f>
         <v/>
       </c>
-      <c r="B22" s="412" t="n"/>
-      <c r="C22" s="413" t="n"/>
-      <c r="D22" s="369" t="n"/>
-      <c r="E22" s="414" t="n"/>
-      <c r="F22" s="414" t="n"/>
-      <c r="G22" s="415" t="n"/>
-      <c r="H22" s="372" t="n"/>
-      <c r="I22" s="414" t="n"/>
-      <c r="J22" s="414" t="n"/>
-      <c r="K22" s="414" t="n"/>
-      <c r="L22" s="414" t="n"/>
-      <c r="M22" s="414" t="n"/>
-      <c r="N22" s="414" t="n"/>
-      <c r="O22" s="414" t="n"/>
-      <c r="P22" s="414" t="n"/>
-      <c r="Q22" s="414" t="n"/>
-      <c r="R22" s="414" t="n"/>
-      <c r="S22" s="414" t="n"/>
-      <c r="T22" s="414" t="n"/>
-      <c r="U22" s="414" t="n"/>
-      <c r="V22" s="414" t="n"/>
-      <c r="W22" s="414" t="n"/>
-      <c r="X22" s="414" t="n"/>
-      <c r="Y22" s="414" t="n"/>
-      <c r="Z22" s="415" t="n"/>
-      <c r="AA22" s="373" t="n"/>
-      <c r="AB22" s="414" t="n"/>
-      <c r="AC22" s="414" t="n"/>
-      <c r="AD22" s="414" t="n"/>
-      <c r="AE22" s="414" t="n"/>
-      <c r="AF22" s="414" t="n"/>
-      <c r="AG22" s="414" t="n"/>
-      <c r="AH22" s="414" t="n"/>
-      <c r="AI22" s="414" t="n"/>
-      <c r="AJ22" s="414" t="n"/>
-      <c r="AK22" s="414" t="n"/>
-      <c r="AL22" s="414" t="n"/>
-      <c r="AM22" s="414" t="n"/>
-      <c r="AN22" s="414" t="n"/>
-      <c r="AO22" s="414" t="n"/>
-      <c r="AP22" s="414" t="n"/>
-      <c r="AQ22" s="415" t="n"/>
-      <c r="AR22" s="372" t="n"/>
-      <c r="AS22" s="414" t="n"/>
-      <c r="AT22" s="414" t="n"/>
-      <c r="AU22" s="414" t="n"/>
-      <c r="AV22" s="414" t="n"/>
-      <c r="AW22" s="415" t="n"/>
-      <c r="AX22" s="372" t="n"/>
-      <c r="AY22" s="414" t="n"/>
-      <c r="AZ22" s="414" t="n"/>
-      <c r="BA22" s="415" t="n"/>
-      <c r="BB22" s="374" t="n"/>
-      <c r="BC22" s="414" t="n"/>
-      <c r="BD22" s="415" t="n"/>
+      <c r="B22" s="344" t="n"/>
+      <c r="C22" s="344" t="n"/>
+      <c r="D22" s="495" t="n"/>
+      <c r="E22" s="362" t="n"/>
+      <c r="F22" s="362" t="n"/>
+      <c r="G22" s="362" t="n"/>
+      <c r="H22" s="477" t="n"/>
+      <c r="I22" s="362" t="n"/>
+      <c r="J22" s="362" t="n"/>
+      <c r="K22" s="362" t="n"/>
+      <c r="L22" s="362" t="n"/>
+      <c r="M22" s="362" t="n"/>
+      <c r="N22" s="362" t="n"/>
+      <c r="O22" s="362" t="n"/>
+      <c r="P22" s="362" t="n"/>
+      <c r="Q22" s="362" t="n"/>
+      <c r="R22" s="362" t="n"/>
+      <c r="S22" s="362" t="n"/>
+      <c r="T22" s="362" t="n"/>
+      <c r="U22" s="362" t="n"/>
+      <c r="V22" s="362" t="n"/>
+      <c r="W22" s="362" t="n"/>
+      <c r="X22" s="362" t="n"/>
+      <c r="Y22" s="362" t="n"/>
+      <c r="Z22" s="362" t="n"/>
+      <c r="AA22" s="496" t="n"/>
+      <c r="AB22" s="362" t="n"/>
+      <c r="AC22" s="362" t="n"/>
+      <c r="AD22" s="362" t="n"/>
+      <c r="AE22" s="362" t="n"/>
+      <c r="AF22" s="362" t="n"/>
+      <c r="AG22" s="362" t="n"/>
+      <c r="AH22" s="362" t="n"/>
+      <c r="AI22" s="362" t="n"/>
+      <c r="AJ22" s="362" t="n"/>
+      <c r="AK22" s="362" t="n"/>
+      <c r="AL22" s="362" t="n"/>
+      <c r="AM22" s="362" t="n"/>
+      <c r="AN22" s="362" t="n"/>
+      <c r="AO22" s="362" t="n"/>
+      <c r="AP22" s="362" t="n"/>
+      <c r="AQ22" s="362" t="n"/>
+      <c r="AR22" s="477" t="n"/>
+      <c r="AS22" s="362" t="n"/>
+      <c r="AT22" s="362" t="n"/>
+      <c r="AU22" s="362" t="n"/>
+      <c r="AV22" s="362" t="n"/>
+      <c r="AW22" s="362" t="n"/>
+      <c r="AX22" s="477" t="n"/>
+      <c r="AY22" s="362" t="n"/>
+      <c r="AZ22" s="362" t="n"/>
+      <c r="BA22" s="362" t="n"/>
+      <c r="BB22" s="497" t="n"/>
+      <c r="BC22" s="362" t="n"/>
+      <c r="BD22" s="479" t="n"/>
     </row>
     <row r="23" ht="20" customHeight="1">
-      <c r="A23" s="366">
+      <c r="A23" s="498">
         <f>ROW()-ROW($A$16)+1</f>
         <v/>
       </c>
-      <c r="B23" s="412" t="n"/>
-      <c r="C23" s="413" t="n"/>
-      <c r="D23" s="369" t="n"/>
-      <c r="E23" s="414" t="n"/>
-      <c r="F23" s="414" t="n"/>
-      <c r="G23" s="415" t="n"/>
-      <c r="H23" s="372" t="n"/>
-      <c r="I23" s="414" t="n"/>
-      <c r="J23" s="414" t="n"/>
-      <c r="K23" s="414" t="n"/>
-      <c r="L23" s="414" t="n"/>
-      <c r="M23" s="414" t="n"/>
-      <c r="N23" s="414" t="n"/>
-      <c r="O23" s="414" t="n"/>
-      <c r="P23" s="414" t="n"/>
-      <c r="Q23" s="414" t="n"/>
-      <c r="R23" s="414" t="n"/>
-      <c r="S23" s="414" t="n"/>
-      <c r="T23" s="414" t="n"/>
-      <c r="U23" s="414" t="n"/>
-      <c r="V23" s="414" t="n"/>
-      <c r="W23" s="414" t="n"/>
-      <c r="X23" s="414" t="n"/>
-      <c r="Y23" s="414" t="n"/>
-      <c r="Z23" s="415" t="n"/>
-      <c r="AA23" s="373" t="n"/>
-      <c r="AB23" s="414" t="n"/>
-      <c r="AC23" s="414" t="n"/>
-      <c r="AD23" s="414" t="n"/>
-      <c r="AE23" s="414" t="n"/>
-      <c r="AF23" s="414" t="n"/>
-      <c r="AG23" s="414" t="n"/>
-      <c r="AH23" s="414" t="n"/>
-      <c r="AI23" s="414" t="n"/>
-      <c r="AJ23" s="414" t="n"/>
-      <c r="AK23" s="414" t="n"/>
-      <c r="AL23" s="414" t="n"/>
-      <c r="AM23" s="414" t="n"/>
-      <c r="AN23" s="414" t="n"/>
-      <c r="AO23" s="414" t="n"/>
-      <c r="AP23" s="414" t="n"/>
-      <c r="AQ23" s="415" t="n"/>
-      <c r="AR23" s="372" t="n"/>
-      <c r="AS23" s="414" t="n"/>
-      <c r="AT23" s="414" t="n"/>
-      <c r="AU23" s="414" t="n"/>
-      <c r="AV23" s="414" t="n"/>
-      <c r="AW23" s="415" t="n"/>
-      <c r="AX23" s="372" t="n"/>
-      <c r="AY23" s="414" t="n"/>
-      <c r="AZ23" s="414" t="n"/>
-      <c r="BA23" s="415" t="n"/>
-      <c r="BB23" s="374" t="n"/>
-      <c r="BC23" s="414" t="n"/>
-      <c r="BD23" s="415" t="n"/>
+      <c r="B23" s="481" t="n"/>
+      <c r="C23" s="481" t="n"/>
+      <c r="D23" s="499" t="n"/>
+      <c r="E23" s="483" t="n"/>
+      <c r="F23" s="483" t="n"/>
+      <c r="G23" s="483" t="n"/>
+      <c r="H23" s="482" t="n"/>
+      <c r="I23" s="483" t="n"/>
+      <c r="J23" s="483" t="n"/>
+      <c r="K23" s="483" t="n"/>
+      <c r="L23" s="483" t="n"/>
+      <c r="M23" s="483" t="n"/>
+      <c r="N23" s="483" t="n"/>
+      <c r="O23" s="483" t="n"/>
+      <c r="P23" s="483" t="n"/>
+      <c r="Q23" s="483" t="n"/>
+      <c r="R23" s="483" t="n"/>
+      <c r="S23" s="483" t="n"/>
+      <c r="T23" s="483" t="n"/>
+      <c r="U23" s="483" t="n"/>
+      <c r="V23" s="483" t="n"/>
+      <c r="W23" s="483" t="n"/>
+      <c r="X23" s="483" t="n"/>
+      <c r="Y23" s="483" t="n"/>
+      <c r="Z23" s="483" t="n"/>
+      <c r="AA23" s="500" t="n"/>
+      <c r="AB23" s="483" t="n"/>
+      <c r="AC23" s="483" t="n"/>
+      <c r="AD23" s="483" t="n"/>
+      <c r="AE23" s="483" t="n"/>
+      <c r="AF23" s="483" t="n"/>
+      <c r="AG23" s="483" t="n"/>
+      <c r="AH23" s="483" t="n"/>
+      <c r="AI23" s="483" t="n"/>
+      <c r="AJ23" s="483" t="n"/>
+      <c r="AK23" s="483" t="n"/>
+      <c r="AL23" s="483" t="n"/>
+      <c r="AM23" s="483" t="n"/>
+      <c r="AN23" s="483" t="n"/>
+      <c r="AO23" s="483" t="n"/>
+      <c r="AP23" s="483" t="n"/>
+      <c r="AQ23" s="483" t="n"/>
+      <c r="AR23" s="482" t="n"/>
+      <c r="AS23" s="483" t="n"/>
+      <c r="AT23" s="483" t="n"/>
+      <c r="AU23" s="483" t="n"/>
+      <c r="AV23" s="483" t="n"/>
+      <c r="AW23" s="483" t="n"/>
+      <c r="AX23" s="482" t="n"/>
+      <c r="AY23" s="483" t="n"/>
+      <c r="AZ23" s="483" t="n"/>
+      <c r="BA23" s="483" t="n"/>
+      <c r="BB23" s="501" t="n"/>
+      <c r="BC23" s="483" t="n"/>
+      <c r="BD23" s="485" t="n"/>
     </row>
-    <row r="24" ht="4" customHeight="1">
+    <row r="24" ht="3" customHeight="1">
       <c r="A24" s="375" t="n"/>
       <c r="B24" s="353" t="n"/>
       <c r="C24" s="353" t="n"/>
@@ -6778,201 +7675,201 @@
       <c r="BC24" s="353" t="n"/>
       <c r="BD24" s="353" t="n"/>
     </row>
-    <row r="25" ht="20" customHeight="1">
-      <c r="A25" s="354" t="inlineStr">
+    <row r="25" ht="18" customHeight="1">
+      <c r="A25" s="467" t="inlineStr">
         <is>
           <t xml:space="preserve">  3. CONDITIONS / ACTIONS / RELEASE</t>
         </is>
       </c>
-      <c r="B25" s="406" t="n"/>
-      <c r="C25" s="406" t="n"/>
-      <c r="D25" s="406" t="n"/>
-      <c r="E25" s="406" t="n"/>
-      <c r="F25" s="406" t="n"/>
-      <c r="G25" s="406" t="n"/>
-      <c r="H25" s="406" t="n"/>
-      <c r="I25" s="406" t="n"/>
-      <c r="J25" s="406" t="n"/>
-      <c r="K25" s="406" t="n"/>
-      <c r="L25" s="406" t="n"/>
-      <c r="M25" s="406" t="n"/>
-      <c r="N25" s="406" t="n"/>
-      <c r="O25" s="406" t="n"/>
-      <c r="P25" s="406" t="n"/>
-      <c r="Q25" s="406" t="n"/>
-      <c r="R25" s="406" t="n"/>
-      <c r="S25" s="406" t="n"/>
-      <c r="T25" s="406" t="n"/>
-      <c r="U25" s="406" t="n"/>
-      <c r="V25" s="406" t="n"/>
-      <c r="W25" s="406" t="n"/>
-      <c r="X25" s="406" t="n"/>
-      <c r="Y25" s="406" t="n"/>
-      <c r="Z25" s="406" t="n"/>
-      <c r="AA25" s="406" t="n"/>
-      <c r="AB25" s="406" t="n"/>
-      <c r="AC25" s="406" t="n"/>
-      <c r="AD25" s="406" t="n"/>
-      <c r="AE25" s="406" t="n"/>
-      <c r="AF25" s="406" t="n"/>
-      <c r="AG25" s="406" t="n"/>
-      <c r="AH25" s="406" t="n"/>
-      <c r="AI25" s="406" t="n"/>
-      <c r="AJ25" s="406" t="n"/>
-      <c r="AK25" s="406" t="n"/>
-      <c r="AL25" s="406" t="n"/>
-      <c r="AM25" s="406" t="n"/>
-      <c r="AN25" s="406" t="n"/>
-      <c r="AO25" s="406" t="n"/>
-      <c r="AP25" s="406" t="n"/>
-      <c r="AQ25" s="406" t="n"/>
-      <c r="AR25" s="406" t="n"/>
-      <c r="AS25" s="406" t="n"/>
-      <c r="AT25" s="406" t="n"/>
-      <c r="AU25" s="406" t="n"/>
-      <c r="AV25" s="406" t="n"/>
-      <c r="AW25" s="406" t="n"/>
-      <c r="AX25" s="406" t="n"/>
-      <c r="AY25" s="406" t="n"/>
-      <c r="AZ25" s="406" t="n"/>
-      <c r="BA25" s="406" t="n"/>
-      <c r="BB25" s="406" t="n"/>
-      <c r="BC25" s="406" t="n"/>
-      <c r="BD25" s="407" t="n"/>
+      <c r="B25" s="468" t="n"/>
+      <c r="C25" s="468" t="n"/>
+      <c r="D25" s="468" t="n"/>
+      <c r="E25" s="468" t="n"/>
+      <c r="F25" s="468" t="n"/>
+      <c r="G25" s="468" t="n"/>
+      <c r="H25" s="468" t="n"/>
+      <c r="I25" s="468" t="n"/>
+      <c r="J25" s="468" t="n"/>
+      <c r="K25" s="468" t="n"/>
+      <c r="L25" s="468" t="n"/>
+      <c r="M25" s="468" t="n"/>
+      <c r="N25" s="468" t="n"/>
+      <c r="O25" s="468" t="n"/>
+      <c r="P25" s="468" t="n"/>
+      <c r="Q25" s="468" t="n"/>
+      <c r="R25" s="468" t="n"/>
+      <c r="S25" s="468" t="n"/>
+      <c r="T25" s="468" t="n"/>
+      <c r="U25" s="468" t="n"/>
+      <c r="V25" s="468" t="n"/>
+      <c r="W25" s="468" t="n"/>
+      <c r="X25" s="468" t="n"/>
+      <c r="Y25" s="468" t="n"/>
+      <c r="Z25" s="468" t="n"/>
+      <c r="AA25" s="468" t="n"/>
+      <c r="AB25" s="468" t="n"/>
+      <c r="AC25" s="468" t="n"/>
+      <c r="AD25" s="468" t="n"/>
+      <c r="AE25" s="468" t="n"/>
+      <c r="AF25" s="468" t="n"/>
+      <c r="AG25" s="468" t="n"/>
+      <c r="AH25" s="468" t="n"/>
+      <c r="AI25" s="468" t="n"/>
+      <c r="AJ25" s="468" t="n"/>
+      <c r="AK25" s="468" t="n"/>
+      <c r="AL25" s="468" t="n"/>
+      <c r="AM25" s="468" t="n"/>
+      <c r="AN25" s="468" t="n"/>
+      <c r="AO25" s="468" t="n"/>
+      <c r="AP25" s="468" t="n"/>
+      <c r="AQ25" s="468" t="n"/>
+      <c r="AR25" s="468" t="n"/>
+      <c r="AS25" s="468" t="n"/>
+      <c r="AT25" s="468" t="n"/>
+      <c r="AU25" s="468" t="n"/>
+      <c r="AV25" s="468" t="n"/>
+      <c r="AW25" s="468" t="n"/>
+      <c r="AX25" s="468" t="n"/>
+      <c r="AY25" s="468" t="n"/>
+      <c r="AZ25" s="468" t="n"/>
+      <c r="BA25" s="468" t="n"/>
+      <c r="BB25" s="468" t="n"/>
+      <c r="BC25" s="468" t="n"/>
+      <c r="BD25" s="469" t="n"/>
     </row>
     <row r="26" ht="20" customHeight="1">
-      <c r="A26" s="355" t="inlineStr">
+      <c r="A26" s="470" t="inlineStr">
         <is>
           <t>Conditional Action Required (YES/NO)</t>
         </is>
       </c>
-      <c r="B26" s="406" t="n"/>
-      <c r="C26" s="406" t="n"/>
-      <c r="D26" s="406" t="n"/>
-      <c r="E26" s="406" t="n"/>
-      <c r="F26" s="406" t="n"/>
-      <c r="G26" s="406" t="n"/>
-      <c r="H26" s="406" t="n"/>
-      <c r="I26" s="406" t="n"/>
-      <c r="J26" s="407" t="n"/>
-      <c r="K26" s="358" t="n"/>
-      <c r="L26" s="408" t="n"/>
-      <c r="M26" s="408" t="n"/>
-      <c r="N26" s="408" t="n"/>
-      <c r="O26" s="408" t="n"/>
-      <c r="P26" s="408" t="n"/>
-      <c r="Q26" s="408" t="n"/>
-      <c r="R26" s="408" t="n"/>
-      <c r="S26" s="408" t="n"/>
-      <c r="T26" s="408" t="n"/>
-      <c r="U26" s="408" t="n"/>
-      <c r="V26" s="408" t="n"/>
-      <c r="W26" s="408" t="n"/>
-      <c r="X26" s="408" t="n"/>
-      <c r="Y26" s="408" t="n"/>
-      <c r="Z26" s="408" t="n"/>
-      <c r="AA26" s="408" t="n"/>
-      <c r="AB26" s="409" t="n"/>
-      <c r="AC26" s="361" t="inlineStr">
+      <c r="B26" s="471" t="n"/>
+      <c r="C26" s="471" t="n"/>
+      <c r="D26" s="471" t="n"/>
+      <c r="E26" s="471" t="n"/>
+      <c r="F26" s="471" t="n"/>
+      <c r="G26" s="471" t="n"/>
+      <c r="H26" s="471" t="n"/>
+      <c r="I26" s="471" t="n"/>
+      <c r="J26" s="471" t="n"/>
+      <c r="K26" s="472" t="n"/>
+      <c r="L26" s="473" t="n"/>
+      <c r="M26" s="473" t="n"/>
+      <c r="N26" s="473" t="n"/>
+      <c r="O26" s="473" t="n"/>
+      <c r="P26" s="473" t="n"/>
+      <c r="Q26" s="473" t="n"/>
+      <c r="R26" s="473" t="n"/>
+      <c r="S26" s="473" t="n"/>
+      <c r="T26" s="473" t="n"/>
+      <c r="U26" s="473" t="n"/>
+      <c r="V26" s="473" t="n"/>
+      <c r="W26" s="473" t="n"/>
+      <c r="X26" s="473" t="n"/>
+      <c r="Y26" s="473" t="n"/>
+      <c r="Z26" s="473" t="n"/>
+      <c r="AA26" s="473" t="n"/>
+      <c r="AB26" s="473" t="n"/>
+      <c r="AC26" s="474" t="inlineStr">
         <is>
           <t>Bagging / Seal Ref</t>
         </is>
       </c>
-      <c r="AD26" s="406" t="n"/>
-      <c r="AE26" s="406" t="n"/>
-      <c r="AF26" s="406" t="n"/>
-      <c r="AG26" s="406" t="n"/>
-      <c r="AH26" s="406" t="n"/>
-      <c r="AI26" s="406" t="n"/>
-      <c r="AJ26" s="406" t="n"/>
-      <c r="AK26" s="406" t="n"/>
-      <c r="AL26" s="407" t="n"/>
-      <c r="AM26" s="358" t="n"/>
-      <c r="AN26" s="408" t="n"/>
-      <c r="AO26" s="408" t="n"/>
-      <c r="AP26" s="408" t="n"/>
-      <c r="AQ26" s="408" t="n"/>
-      <c r="AR26" s="408" t="n"/>
-      <c r="AS26" s="408" t="n"/>
-      <c r="AT26" s="408" t="n"/>
-      <c r="AU26" s="408" t="n"/>
-      <c r="AV26" s="408" t="n"/>
-      <c r="AW26" s="408" t="n"/>
-      <c r="AX26" s="408" t="n"/>
-      <c r="AY26" s="408" t="n"/>
-      <c r="AZ26" s="408" t="n"/>
-      <c r="BA26" s="408" t="n"/>
-      <c r="BB26" s="408" t="n"/>
-      <c r="BC26" s="408" t="n"/>
-      <c r="BD26" s="409" t="n"/>
+      <c r="AD26" s="471" t="n"/>
+      <c r="AE26" s="471" t="n"/>
+      <c r="AF26" s="471" t="n"/>
+      <c r="AG26" s="471" t="n"/>
+      <c r="AH26" s="471" t="n"/>
+      <c r="AI26" s="471" t="n"/>
+      <c r="AJ26" s="471" t="n"/>
+      <c r="AK26" s="471" t="n"/>
+      <c r="AL26" s="471" t="n"/>
+      <c r="AM26" s="472" t="n"/>
+      <c r="AN26" s="473" t="n"/>
+      <c r="AO26" s="473" t="n"/>
+      <c r="AP26" s="473" t="n"/>
+      <c r="AQ26" s="473" t="n"/>
+      <c r="AR26" s="473" t="n"/>
+      <c r="AS26" s="473" t="n"/>
+      <c r="AT26" s="473" t="n"/>
+      <c r="AU26" s="473" t="n"/>
+      <c r="AV26" s="473" t="n"/>
+      <c r="AW26" s="473" t="n"/>
+      <c r="AX26" s="473" t="n"/>
+      <c r="AY26" s="473" t="n"/>
+      <c r="AZ26" s="473" t="n"/>
+      <c r="BA26" s="473" t="n"/>
+      <c r="BB26" s="473" t="n"/>
+      <c r="BC26" s="473" t="n"/>
+      <c r="BD26" s="475" t="n"/>
     </row>
     <row r="27" ht="20" customHeight="1">
-      <c r="A27" s="355" t="inlineStr">
+      <c r="A27" s="480" t="inlineStr">
         <is>
           <t>Final Release Decision</t>
         </is>
       </c>
-      <c r="B27" s="406" t="n"/>
-      <c r="C27" s="406" t="n"/>
-      <c r="D27" s="406" t="n"/>
-      <c r="E27" s="406" t="n"/>
-      <c r="F27" s="406" t="n"/>
-      <c r="G27" s="406" t="n"/>
-      <c r="H27" s="406" t="n"/>
-      <c r="I27" s="406" t="n"/>
-      <c r="J27" s="407" t="n"/>
-      <c r="K27" s="358" t="n"/>
-      <c r="L27" s="408" t="n"/>
-      <c r="M27" s="408" t="n"/>
-      <c r="N27" s="408" t="n"/>
-      <c r="O27" s="408" t="n"/>
-      <c r="P27" s="408" t="n"/>
-      <c r="Q27" s="408" t="n"/>
-      <c r="R27" s="408" t="n"/>
-      <c r="S27" s="408" t="n"/>
-      <c r="T27" s="408" t="n"/>
-      <c r="U27" s="408" t="n"/>
-      <c r="V27" s="408" t="n"/>
-      <c r="W27" s="408" t="n"/>
-      <c r="X27" s="408" t="n"/>
-      <c r="Y27" s="408" t="n"/>
-      <c r="Z27" s="408" t="n"/>
-      <c r="AA27" s="408" t="n"/>
-      <c r="AB27" s="409" t="n"/>
-      <c r="AC27" s="361" t="inlineStr">
+      <c r="B27" s="481" t="n"/>
+      <c r="C27" s="481" t="n"/>
+      <c r="D27" s="481" t="n"/>
+      <c r="E27" s="481" t="n"/>
+      <c r="F27" s="481" t="n"/>
+      <c r="G27" s="481" t="n"/>
+      <c r="H27" s="481" t="n"/>
+      <c r="I27" s="481" t="n"/>
+      <c r="J27" s="481" t="n"/>
+      <c r="K27" s="482" t="n"/>
+      <c r="L27" s="483" t="n"/>
+      <c r="M27" s="483" t="n"/>
+      <c r="N27" s="483" t="n"/>
+      <c r="O27" s="483" t="n"/>
+      <c r="P27" s="483" t="n"/>
+      <c r="Q27" s="483" t="n"/>
+      <c r="R27" s="483" t="n"/>
+      <c r="S27" s="483" t="n"/>
+      <c r="T27" s="483" t="n"/>
+      <c r="U27" s="483" t="n"/>
+      <c r="V27" s="483" t="n"/>
+      <c r="W27" s="483" t="n"/>
+      <c r="X27" s="483" t="n"/>
+      <c r="Y27" s="483" t="n"/>
+      <c r="Z27" s="483" t="n"/>
+      <c r="AA27" s="483" t="n"/>
+      <c r="AB27" s="483" t="n"/>
+      <c r="AC27" s="484" t="inlineStr">
         <is>
           <t>Approved by</t>
         </is>
       </c>
-      <c r="AD27" s="406" t="n"/>
-      <c r="AE27" s="406" t="n"/>
-      <c r="AF27" s="406" t="n"/>
-      <c r="AG27" s="406" t="n"/>
-      <c r="AH27" s="406" t="n"/>
-      <c r="AI27" s="406" t="n"/>
-      <c r="AJ27" s="406" t="n"/>
-      <c r="AK27" s="406" t="n"/>
-      <c r="AL27" s="407" t="n"/>
-      <c r="AM27" s="358" t="n"/>
-      <c r="AN27" s="408" t="n"/>
-      <c r="AO27" s="408" t="n"/>
-      <c r="AP27" s="408" t="n"/>
-      <c r="AQ27" s="408" t="n"/>
-      <c r="AR27" s="408" t="n"/>
-      <c r="AS27" s="408" t="n"/>
-      <c r="AT27" s="408" t="n"/>
-      <c r="AU27" s="408" t="n"/>
-      <c r="AV27" s="408" t="n"/>
-      <c r="AW27" s="408" t="n"/>
-      <c r="AX27" s="408" t="n"/>
-      <c r="AY27" s="408" t="n"/>
-      <c r="AZ27" s="408" t="n"/>
-      <c r="BA27" s="408" t="n"/>
-      <c r="BB27" s="408" t="n"/>
-      <c r="BC27" s="408" t="n"/>
-      <c r="BD27" s="409" t="n"/>
+      <c r="AD27" s="481" t="n"/>
+      <c r="AE27" s="481" t="n"/>
+      <c r="AF27" s="481" t="n"/>
+      <c r="AG27" s="481" t="n"/>
+      <c r="AH27" s="481" t="n"/>
+      <c r="AI27" s="481" t="n"/>
+      <c r="AJ27" s="481" t="n"/>
+      <c r="AK27" s="481" t="n"/>
+      <c r="AL27" s="481" t="n"/>
+      <c r="AM27" s="482" t="n"/>
+      <c r="AN27" s="483" t="n"/>
+      <c r="AO27" s="483" t="n"/>
+      <c r="AP27" s="483" t="n"/>
+      <c r="AQ27" s="483" t="n"/>
+      <c r="AR27" s="483" t="n"/>
+      <c r="AS27" s="483" t="n"/>
+      <c r="AT27" s="483" t="n"/>
+      <c r="AU27" s="483" t="n"/>
+      <c r="AV27" s="483" t="n"/>
+      <c r="AW27" s="483" t="n"/>
+      <c r="AX27" s="483" t="n"/>
+      <c r="AY27" s="483" t="n"/>
+      <c r="AZ27" s="483" t="n"/>
+      <c r="BA27" s="483" t="n"/>
+      <c r="BB27" s="483" t="n"/>
+      <c r="BC27" s="483" t="n"/>
+      <c r="BD27" s="485" t="n"/>
     </row>
-    <row r="28" ht="4" customHeight="1">
+    <row r="28" ht="3" customHeight="1">
       <c r="A28" s="375" t="n"/>
       <c r="B28" s="353" t="n"/>
       <c r="C28" s="353" t="n"/>
@@ -7030,325 +7927,325 @@
       <c r="BC28" s="353" t="n"/>
       <c r="BD28" s="353" t="n"/>
     </row>
-    <row r="29" ht="20" customHeight="1">
-      <c r="A29" s="354" t="inlineStr">
+    <row r="29" ht="18" customHeight="1">
+      <c r="A29" s="467" t="inlineStr">
         <is>
           <t xml:space="preserve">  4. APPROVAL / SIGN-OFF</t>
         </is>
       </c>
-      <c r="B29" s="406" t="n"/>
-      <c r="C29" s="406" t="n"/>
-      <c r="D29" s="406" t="n"/>
-      <c r="E29" s="406" t="n"/>
-      <c r="F29" s="406" t="n"/>
-      <c r="G29" s="406" t="n"/>
-      <c r="H29" s="406" t="n"/>
-      <c r="I29" s="406" t="n"/>
-      <c r="J29" s="406" t="n"/>
-      <c r="K29" s="406" t="n"/>
-      <c r="L29" s="406" t="n"/>
-      <c r="M29" s="406" t="n"/>
-      <c r="N29" s="406" t="n"/>
-      <c r="O29" s="406" t="n"/>
-      <c r="P29" s="406" t="n"/>
-      <c r="Q29" s="406" t="n"/>
-      <c r="R29" s="406" t="n"/>
-      <c r="S29" s="406" t="n"/>
-      <c r="T29" s="406" t="n"/>
-      <c r="U29" s="406" t="n"/>
-      <c r="V29" s="406" t="n"/>
-      <c r="W29" s="406" t="n"/>
-      <c r="X29" s="406" t="n"/>
-      <c r="Y29" s="406" t="n"/>
-      <c r="Z29" s="406" t="n"/>
-      <c r="AA29" s="406" t="n"/>
-      <c r="AB29" s="406" t="n"/>
-      <c r="AC29" s="406" t="n"/>
-      <c r="AD29" s="406" t="n"/>
-      <c r="AE29" s="406" t="n"/>
-      <c r="AF29" s="406" t="n"/>
-      <c r="AG29" s="406" t="n"/>
-      <c r="AH29" s="406" t="n"/>
-      <c r="AI29" s="406" t="n"/>
-      <c r="AJ29" s="406" t="n"/>
-      <c r="AK29" s="406" t="n"/>
-      <c r="AL29" s="406" t="n"/>
-      <c r="AM29" s="406" t="n"/>
-      <c r="AN29" s="406" t="n"/>
-      <c r="AO29" s="406" t="n"/>
-      <c r="AP29" s="406" t="n"/>
-      <c r="AQ29" s="406" t="n"/>
-      <c r="AR29" s="406" t="n"/>
-      <c r="AS29" s="406" t="n"/>
-      <c r="AT29" s="406" t="n"/>
-      <c r="AU29" s="406" t="n"/>
-      <c r="AV29" s="406" t="n"/>
-      <c r="AW29" s="406" t="n"/>
-      <c r="AX29" s="406" t="n"/>
-      <c r="AY29" s="406" t="n"/>
-      <c r="AZ29" s="406" t="n"/>
-      <c r="BA29" s="406" t="n"/>
-      <c r="BB29" s="406" t="n"/>
-      <c r="BC29" s="406" t="n"/>
-      <c r="BD29" s="407" t="n"/>
+      <c r="B29" s="468" t="n"/>
+      <c r="C29" s="468" t="n"/>
+      <c r="D29" s="468" t="n"/>
+      <c r="E29" s="468" t="n"/>
+      <c r="F29" s="468" t="n"/>
+      <c r="G29" s="468" t="n"/>
+      <c r="H29" s="468" t="n"/>
+      <c r="I29" s="468" t="n"/>
+      <c r="J29" s="468" t="n"/>
+      <c r="K29" s="468" t="n"/>
+      <c r="L29" s="468" t="n"/>
+      <c r="M29" s="468" t="n"/>
+      <c r="N29" s="468" t="n"/>
+      <c r="O29" s="468" t="n"/>
+      <c r="P29" s="468" t="n"/>
+      <c r="Q29" s="468" t="n"/>
+      <c r="R29" s="468" t="n"/>
+      <c r="S29" s="468" t="n"/>
+      <c r="T29" s="468" t="n"/>
+      <c r="U29" s="468" t="n"/>
+      <c r="V29" s="468" t="n"/>
+      <c r="W29" s="468" t="n"/>
+      <c r="X29" s="468" t="n"/>
+      <c r="Y29" s="468" t="n"/>
+      <c r="Z29" s="468" t="n"/>
+      <c r="AA29" s="468" t="n"/>
+      <c r="AB29" s="468" t="n"/>
+      <c r="AC29" s="468" t="n"/>
+      <c r="AD29" s="468" t="n"/>
+      <c r="AE29" s="468" t="n"/>
+      <c r="AF29" s="468" t="n"/>
+      <c r="AG29" s="468" t="n"/>
+      <c r="AH29" s="468" t="n"/>
+      <c r="AI29" s="468" t="n"/>
+      <c r="AJ29" s="468" t="n"/>
+      <c r="AK29" s="468" t="n"/>
+      <c r="AL29" s="468" t="n"/>
+      <c r="AM29" s="468" t="n"/>
+      <c r="AN29" s="468" t="n"/>
+      <c r="AO29" s="468" t="n"/>
+      <c r="AP29" s="468" t="n"/>
+      <c r="AQ29" s="468" t="n"/>
+      <c r="AR29" s="468" t="n"/>
+      <c r="AS29" s="468" t="n"/>
+      <c r="AT29" s="468" t="n"/>
+      <c r="AU29" s="468" t="n"/>
+      <c r="AV29" s="468" t="n"/>
+      <c r="AW29" s="468" t="n"/>
+      <c r="AX29" s="468" t="n"/>
+      <c r="AY29" s="468" t="n"/>
+      <c r="AZ29" s="468" t="n"/>
+      <c r="BA29" s="468" t="n"/>
+      <c r="BB29" s="468" t="n"/>
+      <c r="BC29" s="468" t="n"/>
+      <c r="BD29" s="469" t="n"/>
     </row>
-    <row r="30" ht="20" customHeight="1">
-      <c r="A30" s="381" t="inlineStr">
+    <row r="30" ht="26" customHeight="1">
+      <c r="A30" s="490" t="inlineStr">
         <is>
           <t>Prepared by</t>
         </is>
       </c>
-      <c r="B30" s="401" t="n"/>
-      <c r="C30" s="401" t="n"/>
-      <c r="D30" s="401" t="n"/>
-      <c r="E30" s="401" t="n"/>
-      <c r="F30" s="401" t="n"/>
-      <c r="G30" s="401" t="n"/>
-      <c r="H30" s="401" t="n"/>
-      <c r="I30" s="401" t="n"/>
-      <c r="J30" s="401" t="n"/>
-      <c r="K30" s="401" t="n"/>
-      <c r="L30" s="401" t="n"/>
-      <c r="M30" s="401" t="n"/>
-      <c r="N30" s="401" t="n"/>
-      <c r="O30" s="401" t="n"/>
-      <c r="P30" s="401" t="n"/>
-      <c r="Q30" s="401" t="n"/>
-      <c r="R30" s="402" t="n"/>
-      <c r="S30" s="382" t="inlineStr">
+      <c r="B30" s="471" t="n"/>
+      <c r="C30" s="471" t="n"/>
+      <c r="D30" s="471" t="n"/>
+      <c r="E30" s="471" t="n"/>
+      <c r="F30" s="471" t="n"/>
+      <c r="G30" s="471" t="n"/>
+      <c r="H30" s="471" t="n"/>
+      <c r="I30" s="471" t="n"/>
+      <c r="J30" s="471" t="n"/>
+      <c r="K30" s="471" t="n"/>
+      <c r="L30" s="471" t="n"/>
+      <c r="M30" s="471" t="n"/>
+      <c r="N30" s="471" t="n"/>
+      <c r="O30" s="471" t="n"/>
+      <c r="P30" s="471" t="n"/>
+      <c r="Q30" s="471" t="n"/>
+      <c r="R30" s="471" t="n"/>
+      <c r="S30" s="502" t="inlineStr">
         <is>
           <t>Reviewed by</t>
         </is>
       </c>
-      <c r="T30" s="401" t="n"/>
-      <c r="U30" s="401" t="n"/>
-      <c r="V30" s="401" t="n"/>
-      <c r="W30" s="401" t="n"/>
-      <c r="X30" s="401" t="n"/>
-      <c r="Y30" s="401" t="n"/>
-      <c r="Z30" s="401" t="n"/>
-      <c r="AA30" s="401" t="n"/>
-      <c r="AB30" s="401" t="n"/>
-      <c r="AC30" s="401" t="n"/>
-      <c r="AD30" s="401" t="n"/>
-      <c r="AE30" s="401" t="n"/>
-      <c r="AF30" s="401" t="n"/>
-      <c r="AG30" s="401" t="n"/>
-      <c r="AH30" s="401" t="n"/>
-      <c r="AI30" s="401" t="n"/>
-      <c r="AJ30" s="401" t="n"/>
-      <c r="AK30" s="383" t="inlineStr">
+      <c r="T30" s="471" t="n"/>
+      <c r="U30" s="471" t="n"/>
+      <c r="V30" s="471" t="n"/>
+      <c r="W30" s="471" t="n"/>
+      <c r="X30" s="471" t="n"/>
+      <c r="Y30" s="471" t="n"/>
+      <c r="Z30" s="471" t="n"/>
+      <c r="AA30" s="471" t="n"/>
+      <c r="AB30" s="471" t="n"/>
+      <c r="AC30" s="471" t="n"/>
+      <c r="AD30" s="471" t="n"/>
+      <c r="AE30" s="471" t="n"/>
+      <c r="AF30" s="471" t="n"/>
+      <c r="AG30" s="471" t="n"/>
+      <c r="AH30" s="471" t="n"/>
+      <c r="AI30" s="471" t="n"/>
+      <c r="AJ30" s="471" t="n"/>
+      <c r="AK30" s="502" t="inlineStr">
         <is>
           <t>Approved by</t>
         </is>
       </c>
-      <c r="AL30" s="401" t="n"/>
-      <c r="AM30" s="401" t="n"/>
-      <c r="AN30" s="401" t="n"/>
-      <c r="AO30" s="401" t="n"/>
-      <c r="AP30" s="401" t="n"/>
-      <c r="AQ30" s="401" t="n"/>
-      <c r="AR30" s="401" t="n"/>
-      <c r="AS30" s="401" t="n"/>
-      <c r="AT30" s="401" t="n"/>
-      <c r="AU30" s="401" t="n"/>
-      <c r="AV30" s="401" t="n"/>
-      <c r="AW30" s="401" t="n"/>
-      <c r="AX30" s="401" t="n"/>
-      <c r="AY30" s="401" t="n"/>
-      <c r="AZ30" s="401" t="n"/>
-      <c r="BA30" s="401" t="n"/>
-      <c r="BB30" s="401" t="n"/>
-      <c r="BC30" s="401" t="n"/>
-      <c r="BD30" s="402" t="n"/>
+      <c r="AL30" s="471" t="n"/>
+      <c r="AM30" s="471" t="n"/>
+      <c r="AN30" s="471" t="n"/>
+      <c r="AO30" s="471" t="n"/>
+      <c r="AP30" s="471" t="n"/>
+      <c r="AQ30" s="471" t="n"/>
+      <c r="AR30" s="471" t="n"/>
+      <c r="AS30" s="471" t="n"/>
+      <c r="AT30" s="471" t="n"/>
+      <c r="AU30" s="471" t="n"/>
+      <c r="AV30" s="471" t="n"/>
+      <c r="AW30" s="471" t="n"/>
+      <c r="AX30" s="471" t="n"/>
+      <c r="AY30" s="471" t="n"/>
+      <c r="AZ30" s="471" t="n"/>
+      <c r="BA30" s="471" t="n"/>
+      <c r="BB30" s="471" t="n"/>
+      <c r="BC30" s="471" t="n"/>
+      <c r="BD30" s="503" t="n"/>
     </row>
-    <row r="31" ht="20" customHeight="1">
-      <c r="A31" s="384" t="inlineStr">
+    <row r="31" ht="26" customHeight="1">
+      <c r="A31" s="504" t="inlineStr">
         <is>
           <t>Name / Signature / Date</t>
         </is>
       </c>
-      <c r="B31" s="416" t="n"/>
-      <c r="C31" s="416" t="n"/>
-      <c r="D31" s="416" t="n"/>
-      <c r="E31" s="416" t="n"/>
-      <c r="F31" s="416" t="n"/>
-      <c r="G31" s="416" t="n"/>
-      <c r="H31" s="416" t="n"/>
-      <c r="I31" s="416" t="n"/>
-      <c r="J31" s="416" t="n"/>
-      <c r="K31" s="416" t="n"/>
-      <c r="L31" s="416" t="n"/>
-      <c r="M31" s="416" t="n"/>
-      <c r="N31" s="416" t="n"/>
-      <c r="O31" s="416" t="n"/>
-      <c r="P31" s="416" t="n"/>
-      <c r="Q31" s="416" t="n"/>
-      <c r="R31" s="417" t="n"/>
-      <c r="S31" s="384" t="inlineStr">
+      <c r="B31" s="362" t="n"/>
+      <c r="C31" s="362" t="n"/>
+      <c r="D31" s="362" t="n"/>
+      <c r="E31" s="362" t="n"/>
+      <c r="F31" s="362" t="n"/>
+      <c r="G31" s="362" t="n"/>
+      <c r="H31" s="362" t="n"/>
+      <c r="I31" s="362" t="n"/>
+      <c r="J31" s="362" t="n"/>
+      <c r="K31" s="362" t="n"/>
+      <c r="L31" s="362" t="n"/>
+      <c r="M31" s="362" t="n"/>
+      <c r="N31" s="362" t="n"/>
+      <c r="O31" s="362" t="n"/>
+      <c r="P31" s="362" t="n"/>
+      <c r="Q31" s="362" t="n"/>
+      <c r="R31" s="362" t="n"/>
+      <c r="S31" s="505" t="inlineStr">
         <is>
           <t>Name / Signature / Date</t>
         </is>
       </c>
-      <c r="T31" s="416" t="n"/>
-      <c r="U31" s="416" t="n"/>
-      <c r="V31" s="416" t="n"/>
-      <c r="W31" s="416" t="n"/>
-      <c r="X31" s="416" t="n"/>
-      <c r="Y31" s="416" t="n"/>
-      <c r="Z31" s="416" t="n"/>
-      <c r="AA31" s="416" t="n"/>
-      <c r="AB31" s="416" t="n"/>
-      <c r="AC31" s="416" t="n"/>
-      <c r="AD31" s="416" t="n"/>
-      <c r="AE31" s="416" t="n"/>
-      <c r="AF31" s="416" t="n"/>
-      <c r="AG31" s="416" t="n"/>
-      <c r="AH31" s="416" t="n"/>
-      <c r="AI31" s="416" t="n"/>
-      <c r="AJ31" s="417" t="n"/>
-      <c r="AK31" s="384" t="inlineStr">
+      <c r="T31" s="362" t="n"/>
+      <c r="U31" s="362" t="n"/>
+      <c r="V31" s="362" t="n"/>
+      <c r="W31" s="362" t="n"/>
+      <c r="X31" s="362" t="n"/>
+      <c r="Y31" s="362" t="n"/>
+      <c r="Z31" s="362" t="n"/>
+      <c r="AA31" s="362" t="n"/>
+      <c r="AB31" s="362" t="n"/>
+      <c r="AC31" s="362" t="n"/>
+      <c r="AD31" s="362" t="n"/>
+      <c r="AE31" s="362" t="n"/>
+      <c r="AF31" s="362" t="n"/>
+      <c r="AG31" s="362" t="n"/>
+      <c r="AH31" s="362" t="n"/>
+      <c r="AI31" s="362" t="n"/>
+      <c r="AJ31" s="362" t="n"/>
+      <c r="AK31" s="505" t="inlineStr">
         <is>
           <t>Name / Signature / Date</t>
         </is>
       </c>
-      <c r="AL31" s="416" t="n"/>
-      <c r="AM31" s="416" t="n"/>
-      <c r="AN31" s="416" t="n"/>
-      <c r="AO31" s="416" t="n"/>
-      <c r="AP31" s="416" t="n"/>
-      <c r="AQ31" s="416" t="n"/>
-      <c r="AR31" s="416" t="n"/>
-      <c r="AS31" s="416" t="n"/>
-      <c r="AT31" s="416" t="n"/>
-      <c r="AU31" s="416" t="n"/>
-      <c r="AV31" s="416" t="n"/>
-      <c r="AW31" s="416" t="n"/>
-      <c r="AX31" s="416" t="n"/>
-      <c r="AY31" s="416" t="n"/>
-      <c r="AZ31" s="416" t="n"/>
-      <c r="BA31" s="416" t="n"/>
-      <c r="BB31" s="416" t="n"/>
-      <c r="BC31" s="416" t="n"/>
-      <c r="BD31" s="417" t="n"/>
+      <c r="AL31" s="362" t="n"/>
+      <c r="AM31" s="362" t="n"/>
+      <c r="AN31" s="362" t="n"/>
+      <c r="AO31" s="362" t="n"/>
+      <c r="AP31" s="362" t="n"/>
+      <c r="AQ31" s="362" t="n"/>
+      <c r="AR31" s="362" t="n"/>
+      <c r="AS31" s="362" t="n"/>
+      <c r="AT31" s="362" t="n"/>
+      <c r="AU31" s="362" t="n"/>
+      <c r="AV31" s="362" t="n"/>
+      <c r="AW31" s="362" t="n"/>
+      <c r="AX31" s="362" t="n"/>
+      <c r="AY31" s="362" t="n"/>
+      <c r="AZ31" s="362" t="n"/>
+      <c r="BA31" s="362" t="n"/>
+      <c r="BB31" s="362" t="n"/>
+      <c r="BC31" s="362" t="n"/>
+      <c r="BD31" s="479" t="n"/>
     </row>
     <row r="32" ht="20" customHeight="1">
-      <c r="A32" s="418" t="n"/>
-      <c r="B32" s="388" t="n"/>
-      <c r="C32" s="388" t="n"/>
-      <c r="D32" s="388" t="n"/>
-      <c r="E32" s="388" t="n"/>
-      <c r="F32" s="388" t="n"/>
-      <c r="G32" s="388" t="n"/>
-      <c r="H32" s="388" t="n"/>
-      <c r="I32" s="388" t="n"/>
-      <c r="J32" s="388" t="n"/>
-      <c r="K32" s="388" t="n"/>
-      <c r="L32" s="388" t="n"/>
-      <c r="M32" s="388" t="n"/>
-      <c r="N32" s="388" t="n"/>
-      <c r="O32" s="388" t="n"/>
-      <c r="P32" s="388" t="n"/>
-      <c r="Q32" s="388" t="n"/>
-      <c r="R32" s="419" t="n"/>
-      <c r="S32" s="418" t="n"/>
-      <c r="T32" s="388" t="n"/>
-      <c r="U32" s="388" t="n"/>
-      <c r="V32" s="388" t="n"/>
-      <c r="W32" s="388" t="n"/>
-      <c r="X32" s="388" t="n"/>
-      <c r="Y32" s="388" t="n"/>
-      <c r="Z32" s="388" t="n"/>
-      <c r="AA32" s="388" t="n"/>
-      <c r="AB32" s="388" t="n"/>
-      <c r="AC32" s="388" t="n"/>
-      <c r="AD32" s="388" t="n"/>
-      <c r="AE32" s="388" t="n"/>
-      <c r="AF32" s="388" t="n"/>
-      <c r="AG32" s="388" t="n"/>
-      <c r="AH32" s="388" t="n"/>
-      <c r="AI32" s="388" t="n"/>
-      <c r="AJ32" s="419" t="n"/>
-      <c r="AK32" s="418" t="n"/>
-      <c r="AL32" s="388" t="n"/>
-      <c r="AM32" s="388" t="n"/>
-      <c r="AN32" s="388" t="n"/>
-      <c r="AO32" s="388" t="n"/>
-      <c r="AP32" s="388" t="n"/>
-      <c r="AQ32" s="388" t="n"/>
-      <c r="AR32" s="388" t="n"/>
-      <c r="AS32" s="388" t="n"/>
-      <c r="AT32" s="388" t="n"/>
-      <c r="AU32" s="388" t="n"/>
-      <c r="AV32" s="388" t="n"/>
-      <c r="AW32" s="388" t="n"/>
-      <c r="AX32" s="388" t="n"/>
-      <c r="AY32" s="388" t="n"/>
-      <c r="AZ32" s="388" t="n"/>
-      <c r="BA32" s="388" t="n"/>
-      <c r="BB32" s="388" t="n"/>
-      <c r="BC32" s="388" t="n"/>
-      <c r="BD32" s="419" t="n"/>
+      <c r="A32" s="506" t="n"/>
+      <c r="B32" s="362" t="n"/>
+      <c r="C32" s="362" t="n"/>
+      <c r="D32" s="362" t="n"/>
+      <c r="E32" s="362" t="n"/>
+      <c r="F32" s="362" t="n"/>
+      <c r="G32" s="362" t="n"/>
+      <c r="H32" s="362" t="n"/>
+      <c r="I32" s="362" t="n"/>
+      <c r="J32" s="362" t="n"/>
+      <c r="K32" s="362" t="n"/>
+      <c r="L32" s="362" t="n"/>
+      <c r="M32" s="362" t="n"/>
+      <c r="N32" s="362" t="n"/>
+      <c r="O32" s="362" t="n"/>
+      <c r="P32" s="362" t="n"/>
+      <c r="Q32" s="362" t="n"/>
+      <c r="R32" s="362" t="n"/>
+      <c r="S32" s="507" t="n"/>
+      <c r="T32" s="362" t="n"/>
+      <c r="U32" s="362" t="n"/>
+      <c r="V32" s="362" t="n"/>
+      <c r="W32" s="362" t="n"/>
+      <c r="X32" s="362" t="n"/>
+      <c r="Y32" s="362" t="n"/>
+      <c r="Z32" s="362" t="n"/>
+      <c r="AA32" s="362" t="n"/>
+      <c r="AB32" s="362" t="n"/>
+      <c r="AC32" s="362" t="n"/>
+      <c r="AD32" s="362" t="n"/>
+      <c r="AE32" s="362" t="n"/>
+      <c r="AF32" s="362" t="n"/>
+      <c r="AG32" s="362" t="n"/>
+      <c r="AH32" s="362" t="n"/>
+      <c r="AI32" s="362" t="n"/>
+      <c r="AJ32" s="362" t="n"/>
+      <c r="AK32" s="507" t="n"/>
+      <c r="AL32" s="362" t="n"/>
+      <c r="AM32" s="362" t="n"/>
+      <c r="AN32" s="362" t="n"/>
+      <c r="AO32" s="362" t="n"/>
+      <c r="AP32" s="362" t="n"/>
+      <c r="AQ32" s="362" t="n"/>
+      <c r="AR32" s="362" t="n"/>
+      <c r="AS32" s="362" t="n"/>
+      <c r="AT32" s="362" t="n"/>
+      <c r="AU32" s="362" t="n"/>
+      <c r="AV32" s="362" t="n"/>
+      <c r="AW32" s="362" t="n"/>
+      <c r="AX32" s="362" t="n"/>
+      <c r="AY32" s="362" t="n"/>
+      <c r="AZ32" s="362" t="n"/>
+      <c r="BA32" s="362" t="n"/>
+      <c r="BB32" s="362" t="n"/>
+      <c r="BC32" s="362" t="n"/>
+      <c r="BD32" s="479" t="n"/>
     </row>
     <row r="33" ht="20" customHeight="1">
-      <c r="A33" s="420" t="n"/>
-      <c r="B33" s="414" t="n"/>
-      <c r="C33" s="414" t="n"/>
-      <c r="D33" s="414" t="n"/>
-      <c r="E33" s="414" t="n"/>
-      <c r="F33" s="414" t="n"/>
-      <c r="G33" s="414" t="n"/>
-      <c r="H33" s="414" t="n"/>
-      <c r="I33" s="414" t="n"/>
-      <c r="J33" s="414" t="n"/>
-      <c r="K33" s="414" t="n"/>
-      <c r="L33" s="414" t="n"/>
-      <c r="M33" s="414" t="n"/>
-      <c r="N33" s="414" t="n"/>
-      <c r="O33" s="414" t="n"/>
-      <c r="P33" s="414" t="n"/>
-      <c r="Q33" s="414" t="n"/>
-      <c r="R33" s="415" t="n"/>
-      <c r="S33" s="420" t="n"/>
-      <c r="T33" s="414" t="n"/>
-      <c r="U33" s="414" t="n"/>
-      <c r="V33" s="414" t="n"/>
-      <c r="W33" s="414" t="n"/>
-      <c r="X33" s="414" t="n"/>
-      <c r="Y33" s="414" t="n"/>
-      <c r="Z33" s="414" t="n"/>
-      <c r="AA33" s="414" t="n"/>
-      <c r="AB33" s="414" t="n"/>
-      <c r="AC33" s="414" t="n"/>
-      <c r="AD33" s="414" t="n"/>
-      <c r="AE33" s="414" t="n"/>
-      <c r="AF33" s="414" t="n"/>
-      <c r="AG33" s="414" t="n"/>
-      <c r="AH33" s="414" t="n"/>
-      <c r="AI33" s="414" t="n"/>
-      <c r="AJ33" s="415" t="n"/>
-      <c r="AK33" s="420" t="n"/>
-      <c r="AL33" s="414" t="n"/>
-      <c r="AM33" s="414" t="n"/>
-      <c r="AN33" s="414" t="n"/>
-      <c r="AO33" s="414" t="n"/>
-      <c r="AP33" s="414" t="n"/>
-      <c r="AQ33" s="414" t="n"/>
-      <c r="AR33" s="414" t="n"/>
-      <c r="AS33" s="414" t="n"/>
-      <c r="AT33" s="414" t="n"/>
-      <c r="AU33" s="414" t="n"/>
-      <c r="AV33" s="414" t="n"/>
-      <c r="AW33" s="414" t="n"/>
-      <c r="AX33" s="414" t="n"/>
-      <c r="AY33" s="414" t="n"/>
-      <c r="AZ33" s="414" t="n"/>
-      <c r="BA33" s="414" t="n"/>
-      <c r="BB33" s="414" t="n"/>
-      <c r="BC33" s="414" t="n"/>
-      <c r="BD33" s="415" t="n"/>
+      <c r="A33" s="508" t="n"/>
+      <c r="B33" s="483" t="n"/>
+      <c r="C33" s="483" t="n"/>
+      <c r="D33" s="483" t="n"/>
+      <c r="E33" s="483" t="n"/>
+      <c r="F33" s="483" t="n"/>
+      <c r="G33" s="483" t="n"/>
+      <c r="H33" s="483" t="n"/>
+      <c r="I33" s="483" t="n"/>
+      <c r="J33" s="483" t="n"/>
+      <c r="K33" s="483" t="n"/>
+      <c r="L33" s="483" t="n"/>
+      <c r="M33" s="483" t="n"/>
+      <c r="N33" s="483" t="n"/>
+      <c r="O33" s="483" t="n"/>
+      <c r="P33" s="483" t="n"/>
+      <c r="Q33" s="483" t="n"/>
+      <c r="R33" s="483" t="n"/>
+      <c r="S33" s="509" t="n"/>
+      <c r="T33" s="483" t="n"/>
+      <c r="U33" s="483" t="n"/>
+      <c r="V33" s="483" t="n"/>
+      <c r="W33" s="483" t="n"/>
+      <c r="X33" s="483" t="n"/>
+      <c r="Y33" s="483" t="n"/>
+      <c r="Z33" s="483" t="n"/>
+      <c r="AA33" s="483" t="n"/>
+      <c r="AB33" s="483" t="n"/>
+      <c r="AC33" s="483" t="n"/>
+      <c r="AD33" s="483" t="n"/>
+      <c r="AE33" s="483" t="n"/>
+      <c r="AF33" s="483" t="n"/>
+      <c r="AG33" s="483" t="n"/>
+      <c r="AH33" s="483" t="n"/>
+      <c r="AI33" s="483" t="n"/>
+      <c r="AJ33" s="483" t="n"/>
+      <c r="AK33" s="509" t="n"/>
+      <c r="AL33" s="483" t="n"/>
+      <c r="AM33" s="483" t="n"/>
+      <c r="AN33" s="483" t="n"/>
+      <c r="AO33" s="483" t="n"/>
+      <c r="AP33" s="483" t="n"/>
+      <c r="AQ33" s="483" t="n"/>
+      <c r="AR33" s="483" t="n"/>
+      <c r="AS33" s="483" t="n"/>
+      <c r="AT33" s="483" t="n"/>
+      <c r="AU33" s="483" t="n"/>
+      <c r="AV33" s="483" t="n"/>
+      <c r="AW33" s="483" t="n"/>
+      <c r="AX33" s="483" t="n"/>
+      <c r="AY33" s="483" t="n"/>
+      <c r="AZ33" s="483" t="n"/>
+      <c r="BA33" s="483" t="n"/>
+      <c r="BB33" s="483" t="n"/>
+      <c r="BC33" s="483" t="n"/>
+      <c r="BD33" s="485" t="n"/>
     </row>
-    <row r="34" ht="4" customHeight="1">
+    <row r="34" ht="3" customHeight="1">
       <c r="A34" s="391" t="n"/>
       <c r="B34" s="353" t="n"/>
       <c r="C34" s="353" t="n"/>
@@ -7406,67 +8303,67 @@
       <c r="BC34" s="353" t="n"/>
       <c r="BD34" s="353" t="n"/>
     </row>
-    <row r="35" ht="20" customHeight="1">
-      <c r="A35" s="392" t="inlineStr">
+    <row r="35" ht="26" customHeight="1">
+      <c r="A35" s="510" t="inlineStr">
         <is>
           <t>NOTICE: Confirm cleanliness, approved materials, line clearance, bagging sequence and seal integrity before release. This is a controlled gap form.</t>
         </is>
       </c>
-      <c r="B35" s="412" t="n"/>
-      <c r="C35" s="412" t="n"/>
-      <c r="D35" s="412" t="n"/>
-      <c r="E35" s="412" t="n"/>
-      <c r="F35" s="412" t="n"/>
-      <c r="G35" s="412" t="n"/>
-      <c r="H35" s="412" t="n"/>
-      <c r="I35" s="412" t="n"/>
-      <c r="J35" s="412" t="n"/>
-      <c r="K35" s="412" t="n"/>
-      <c r="L35" s="412" t="n"/>
-      <c r="M35" s="412" t="n"/>
-      <c r="N35" s="412" t="n"/>
-      <c r="O35" s="412" t="n"/>
-      <c r="P35" s="412" t="n"/>
-      <c r="Q35" s="412" t="n"/>
-      <c r="R35" s="412" t="n"/>
-      <c r="S35" s="412" t="n"/>
-      <c r="T35" s="412" t="n"/>
-      <c r="U35" s="412" t="n"/>
-      <c r="V35" s="412" t="n"/>
-      <c r="W35" s="412" t="n"/>
-      <c r="X35" s="412" t="n"/>
-      <c r="Y35" s="412" t="n"/>
-      <c r="Z35" s="412" t="n"/>
-      <c r="AA35" s="412" t="n"/>
-      <c r="AB35" s="412" t="n"/>
-      <c r="AC35" s="412" t="n"/>
-      <c r="AD35" s="412" t="n"/>
-      <c r="AE35" s="412" t="n"/>
-      <c r="AF35" s="412" t="n"/>
-      <c r="AG35" s="412" t="n"/>
-      <c r="AH35" s="412" t="n"/>
-      <c r="AI35" s="412" t="n"/>
-      <c r="AJ35" s="412" t="n"/>
-      <c r="AK35" s="412" t="n"/>
-      <c r="AL35" s="412" t="n"/>
-      <c r="AM35" s="412" t="n"/>
-      <c r="AN35" s="412" t="n"/>
-      <c r="AO35" s="412" t="n"/>
-      <c r="AP35" s="412" t="n"/>
-      <c r="AQ35" s="412" t="n"/>
-      <c r="AR35" s="412" t="n"/>
-      <c r="AS35" s="412" t="n"/>
-      <c r="AT35" s="412" t="n"/>
-      <c r="AU35" s="412" t="n"/>
-      <c r="AV35" s="412" t="n"/>
-      <c r="AW35" s="412" t="n"/>
-      <c r="AX35" s="412" t="n"/>
-      <c r="AY35" s="412" t="n"/>
-      <c r="AZ35" s="412" t="n"/>
-      <c r="BA35" s="412" t="n"/>
-      <c r="BB35" s="412" t="n"/>
-      <c r="BC35" s="412" t="n"/>
-      <c r="BD35" s="413" t="n"/>
+      <c r="B35" s="511" t="n"/>
+      <c r="C35" s="511" t="n"/>
+      <c r="D35" s="511" t="n"/>
+      <c r="E35" s="511" t="n"/>
+      <c r="F35" s="511" t="n"/>
+      <c r="G35" s="511" t="n"/>
+      <c r="H35" s="511" t="n"/>
+      <c r="I35" s="511" t="n"/>
+      <c r="J35" s="511" t="n"/>
+      <c r="K35" s="511" t="n"/>
+      <c r="L35" s="511" t="n"/>
+      <c r="M35" s="511" t="n"/>
+      <c r="N35" s="511" t="n"/>
+      <c r="O35" s="511" t="n"/>
+      <c r="P35" s="511" t="n"/>
+      <c r="Q35" s="511" t="n"/>
+      <c r="R35" s="511" t="n"/>
+      <c r="S35" s="511" t="n"/>
+      <c r="T35" s="511" t="n"/>
+      <c r="U35" s="511" t="n"/>
+      <c r="V35" s="511" t="n"/>
+      <c r="W35" s="511" t="n"/>
+      <c r="X35" s="511" t="n"/>
+      <c r="Y35" s="511" t="n"/>
+      <c r="Z35" s="511" t="n"/>
+      <c r="AA35" s="511" t="n"/>
+      <c r="AB35" s="511" t="n"/>
+      <c r="AC35" s="511" t="n"/>
+      <c r="AD35" s="511" t="n"/>
+      <c r="AE35" s="511" t="n"/>
+      <c r="AF35" s="511" t="n"/>
+      <c r="AG35" s="511" t="n"/>
+      <c r="AH35" s="511" t="n"/>
+      <c r="AI35" s="511" t="n"/>
+      <c r="AJ35" s="511" t="n"/>
+      <c r="AK35" s="511" t="n"/>
+      <c r="AL35" s="511" t="n"/>
+      <c r="AM35" s="511" t="n"/>
+      <c r="AN35" s="511" t="n"/>
+      <c r="AO35" s="511" t="n"/>
+      <c r="AP35" s="511" t="n"/>
+      <c r="AQ35" s="511" t="n"/>
+      <c r="AR35" s="511" t="n"/>
+      <c r="AS35" s="511" t="n"/>
+      <c r="AT35" s="511" t="n"/>
+      <c r="AU35" s="511" t="n"/>
+      <c r="AV35" s="511" t="n"/>
+      <c r="AW35" s="511" t="n"/>
+      <c r="AX35" s="511" t="n"/>
+      <c r="AY35" s="511" t="n"/>
+      <c r="AZ35" s="511" t="n"/>
+      <c r="BA35" s="511" t="n"/>
+      <c r="BB35" s="511" t="n"/>
+      <c r="BC35" s="511" t="n"/>
+      <c r="BD35" s="512" t="n"/>
     </row>
     <row r="36" ht="20" customHeight="1"/>
     <row r="37" ht="20" customHeight="1"/>
@@ -7482,7 +8379,7 @@
     <row r="47" ht="24" customHeight="1"/>
   </sheetData>
   <sheetProtection selectLockedCells="1" selectUnlockedCells="1" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="0" insertColumns="0" pivotTables="1" deleteRows="0" formatCells="0" formatRows="0" sort="1"/>
-  <mergeCells count="117">
+  <mergeCells count="116">
     <mergeCell ref="D18:G18"/>
     <mergeCell ref="AX18:BA18"/>
     <mergeCell ref="H19:Z19"/>
@@ -7495,7 +8392,6 @@
     <mergeCell ref="BB22:BD22"/>
     <mergeCell ref="AQ4:AV4"/>
     <mergeCell ref="D22:G22"/>
-    <mergeCell ref="A6:BD6"/>
     <mergeCell ref="S30:AJ30"/>
     <mergeCell ref="AW5:BD5"/>
     <mergeCell ref="AA20:AQ20"/>
@@ -7619,6 +8515,7 @@
     <firstHeader/>
     <firstFooter/>
   </headerFooter>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -7805,7 +8702,7 @@
         </is>
       </c>
       <c r="D5" s="266" t="n"/>
-      <c r="E5" t="inlineStr">
+      <c r="E5" s="348" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
@@ -7822,7 +8719,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="E6" t="inlineStr">
+      <c r="E6" s="348" t="inlineStr">
         <is>
           <t>INEFFECTIVE</t>
         </is>
@@ -7835,7 +8732,7 @@
       <c r="G6" s="266" t="n"/>
     </row>
     <row r="7">
-      <c r="E7" t="inlineStr">
+      <c r="E7" s="348" t="inlineStr">
         <is>
           <t>CLOSED</t>
         </is>
@@ -7930,657 +8827,663 @@
     <col width="2.33" customWidth="1" min="40" max="40"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18" customHeight="1">
-      <c r="A1" s="393" t="inlineStr">
+    <row r="1" ht="15" customHeight="1">
+      <c r="A1" s="513" t="inlineStr">
         <is>
           <t>Conditions / Exceptions / Actions</t>
         </is>
       </c>
-      <c r="B1" s="423" t="n"/>
-      <c r="C1" s="423" t="n"/>
-      <c r="D1" s="423" t="n"/>
-      <c r="E1" s="423" t="n"/>
-      <c r="F1" s="423" t="n"/>
-      <c r="G1" s="424" t="n"/>
-      <c r="H1" s="348" t="n"/>
-      <c r="I1" s="348" t="n"/>
-      <c r="J1" s="348" t="n"/>
-      <c r="K1" s="348" t="n"/>
-      <c r="L1" s="348" t="n"/>
-      <c r="M1" s="348" t="n"/>
-      <c r="N1" s="348" t="n"/>
-      <c r="O1" s="348" t="n"/>
-      <c r="P1" s="348" t="n"/>
-      <c r="Q1" s="348" t="n"/>
-      <c r="R1" s="348" t="n"/>
-      <c r="S1" s="348" t="n"/>
-      <c r="T1" s="348" t="n"/>
-      <c r="U1" s="348" t="n"/>
-      <c r="V1" s="348" t="n"/>
-      <c r="W1" s="348" t="n"/>
-      <c r="X1" s="348" t="n"/>
-      <c r="Y1" s="348" t="n"/>
-      <c r="Z1" s="348" t="n"/>
-      <c r="AA1" s="348" t="n"/>
-      <c r="AB1" s="348" t="n"/>
-      <c r="AC1" s="348" t="n"/>
-      <c r="AD1" s="348" t="n"/>
-      <c r="AE1" s="348" t="n"/>
-      <c r="AF1" s="348" t="n"/>
-      <c r="AG1" s="348" t="n"/>
-      <c r="AH1" s="348" t="n"/>
-      <c r="AI1" s="348" t="n"/>
-      <c r="AJ1" s="348" t="n"/>
-      <c r="AK1" s="348" t="n"/>
-      <c r="AL1" s="348" t="n"/>
-      <c r="AM1" s="348" t="n"/>
-      <c r="AN1" s="348" t="n"/>
+      <c r="B1" s="429" t="n"/>
+      <c r="C1" s="429" t="n"/>
+      <c r="D1" s="429" t="n"/>
+      <c r="E1" s="429" t="n"/>
+      <c r="F1" s="429" t="n"/>
+      <c r="G1" s="429" t="n"/>
+      <c r="H1" s="514" t="n"/>
+      <c r="I1" s="431" t="n"/>
+      <c r="J1" s="432" t="n"/>
+      <c r="K1" s="432" t="n"/>
+      <c r="L1" s="432" t="n"/>
+      <c r="M1" s="432" t="n"/>
+      <c r="N1" s="432" t="n"/>
+      <c r="O1" s="432" t="n"/>
+      <c r="P1" s="432" t="n"/>
+      <c r="Q1" s="432" t="n"/>
+      <c r="R1" s="432" t="n"/>
+      <c r="S1" s="432" t="n"/>
+      <c r="T1" s="432" t="n"/>
+      <c r="U1" s="432" t="n"/>
+      <c r="V1" s="432" t="n"/>
+      <c r="W1" s="432" t="n"/>
+      <c r="X1" s="432" t="n"/>
+      <c r="Y1" s="432" t="n"/>
+      <c r="Z1" s="432" t="n"/>
+      <c r="AA1" s="432" t="n"/>
+      <c r="AB1" s="432" t="n"/>
+      <c r="AC1" s="432" t="n"/>
+      <c r="AD1" s="433" t="n"/>
+      <c r="AE1" s="434" t="n"/>
+      <c r="AF1" s="435" t="n"/>
+      <c r="AG1" s="435" t="n"/>
+      <c r="AH1" s="436" t="n"/>
+      <c r="AI1" s="437" t="n"/>
+      <c r="AJ1" s="438" t="n"/>
+      <c r="AK1" s="438" t="n"/>
+      <c r="AL1" s="438" t="n"/>
+      <c r="AM1" s="438" t="n"/>
+      <c r="AN1" s="439" t="n"/>
     </row>
-    <row r="2" ht="18" customHeight="1">
-      <c r="A2" s="338" t="inlineStr">
+    <row r="2" ht="15" customHeight="1">
+      <c r="A2" s="515" t="inlineStr">
         <is>
           <t>Vacuum-compatible clean build and bagging gate for controlled preservation and packaging release.</t>
         </is>
       </c>
-      <c r="H2" s="348" t="n"/>
-      <c r="I2" s="348" t="n"/>
-      <c r="J2" s="348" t="n"/>
-      <c r="K2" s="348" t="n"/>
-      <c r="L2" s="348" t="n"/>
-      <c r="M2" s="348" t="n"/>
-      <c r="N2" s="348" t="n"/>
-      <c r="O2" s="348" t="n"/>
-      <c r="P2" s="348" t="n"/>
-      <c r="Q2" s="348" t="n"/>
-      <c r="R2" s="348" t="n"/>
-      <c r="S2" s="348" t="n"/>
-      <c r="T2" s="348" t="n"/>
-      <c r="U2" s="348" t="n"/>
-      <c r="V2" s="348" t="n"/>
-      <c r="W2" s="348" t="n"/>
-      <c r="X2" s="348" t="n"/>
-      <c r="Y2" s="348" t="n"/>
-      <c r="Z2" s="348" t="n"/>
-      <c r="AA2" s="348" t="n"/>
-      <c r="AB2" s="348" t="n"/>
-      <c r="AC2" s="348" t="n"/>
-      <c r="AD2" s="348" t="n"/>
-      <c r="AE2" s="348" t="n"/>
-      <c r="AF2" s="348" t="n"/>
-      <c r="AG2" s="348" t="n"/>
-      <c r="AH2" s="348" t="n"/>
-      <c r="AI2" s="348" t="n"/>
-      <c r="AJ2" s="348" t="n"/>
-      <c r="AK2" s="348" t="n"/>
-      <c r="AL2" s="348" t="n"/>
-      <c r="AM2" s="348" t="n"/>
-      <c r="AN2" s="348" t="n"/>
+      <c r="B2" s="25" t="n"/>
+      <c r="C2" s="25" t="n"/>
+      <c r="D2" s="25" t="n"/>
+      <c r="E2" s="25" t="n"/>
+      <c r="F2" s="25" t="n"/>
+      <c r="G2" s="25" t="n"/>
+      <c r="H2" s="516" t="n"/>
+      <c r="I2" s="442" t="n"/>
+      <c r="J2" s="443" t="n"/>
+      <c r="K2" s="443" t="n"/>
+      <c r="L2" s="443" t="n"/>
+      <c r="M2" s="443" t="n"/>
+      <c r="N2" s="443" t="n"/>
+      <c r="O2" s="443" t="n"/>
+      <c r="P2" s="443" t="n"/>
+      <c r="Q2" s="443" t="n"/>
+      <c r="R2" s="443" t="n"/>
+      <c r="S2" s="443" t="n"/>
+      <c r="T2" s="443" t="n"/>
+      <c r="U2" s="443" t="n"/>
+      <c r="V2" s="443" t="n"/>
+      <c r="W2" s="443" t="n"/>
+      <c r="X2" s="443" t="n"/>
+      <c r="Y2" s="443" t="n"/>
+      <c r="Z2" s="443" t="n"/>
+      <c r="AA2" s="443" t="n"/>
+      <c r="AB2" s="443" t="n"/>
+      <c r="AC2" s="443" t="n"/>
+      <c r="AD2" s="444" t="n"/>
+      <c r="AE2" s="445" t="n"/>
+      <c r="AF2" s="446" t="n"/>
+      <c r="AG2" s="446" t="n"/>
+      <c r="AH2" s="447" t="n"/>
+      <c r="AI2" s="448" t="n"/>
+      <c r="AJ2" s="449" t="n"/>
+      <c r="AK2" s="449" t="n"/>
+      <c r="AL2" s="449" t="n"/>
+      <c r="AM2" s="449" t="n"/>
+      <c r="AN2" s="450" t="n"/>
     </row>
-    <row r="3" ht="18" customHeight="1">
-      <c r="A3" s="348" t="n"/>
-      <c r="B3" s="348" t="n"/>
-      <c r="C3" s="348" t="n"/>
-      <c r="D3" s="348" t="n"/>
-      <c r="E3" s="348" t="n"/>
-      <c r="F3" s="348" t="n"/>
-      <c r="G3" s="348" t="n"/>
-      <c r="H3" s="348" t="n"/>
-      <c r="I3" s="348" t="n"/>
-      <c r="J3" s="348" t="n"/>
-      <c r="K3" s="348" t="n"/>
-      <c r="L3" s="348" t="n"/>
-      <c r="M3" s="348" t="n"/>
-      <c r="N3" s="348" t="n"/>
-      <c r="O3" s="348" t="n"/>
-      <c r="P3" s="348" t="n"/>
-      <c r="Q3" s="348" t="n"/>
-      <c r="R3" s="348" t="n"/>
-      <c r="S3" s="348" t="n"/>
-      <c r="T3" s="348" t="n"/>
-      <c r="U3" s="348" t="n"/>
-      <c r="V3" s="348" t="n"/>
-      <c r="W3" s="348" t="n"/>
-      <c r="X3" s="348" t="n"/>
-      <c r="Y3" s="348" t="n"/>
-      <c r="Z3" s="348" t="n"/>
-      <c r="AA3" s="348" t="n"/>
-      <c r="AB3" s="348" t="n"/>
-      <c r="AC3" s="348" t="n"/>
-      <c r="AD3" s="348" t="n"/>
-      <c r="AE3" s="348" t="n"/>
-      <c r="AF3" s="348" t="n"/>
-      <c r="AG3" s="348" t="n"/>
-      <c r="AH3" s="348" t="n"/>
-      <c r="AI3" s="348" t="n"/>
-      <c r="AJ3" s="348" t="n"/>
-      <c r="AK3" s="348" t="n"/>
-      <c r="AL3" s="348" t="n"/>
-      <c r="AM3" s="348" t="n"/>
-      <c r="AN3" s="348" t="n"/>
+    <row r="3" ht="15" customHeight="1">
+      <c r="A3" s="517" t="n"/>
+      <c r="B3" s="518" t="n"/>
+      <c r="C3" s="518" t="n"/>
+      <c r="D3" s="518" t="n"/>
+      <c r="E3" s="518" t="n"/>
+      <c r="F3" s="518" t="n"/>
+      <c r="G3" s="518" t="n"/>
+      <c r="H3" s="516" t="n"/>
+      <c r="I3" s="442" t="n"/>
+      <c r="J3" s="443" t="n"/>
+      <c r="K3" s="443" t="n"/>
+      <c r="L3" s="443" t="n"/>
+      <c r="M3" s="443" t="n"/>
+      <c r="N3" s="443" t="n"/>
+      <c r="O3" s="443" t="n"/>
+      <c r="P3" s="443" t="n"/>
+      <c r="Q3" s="443" t="n"/>
+      <c r="R3" s="443" t="n"/>
+      <c r="S3" s="443" t="n"/>
+      <c r="T3" s="443" t="n"/>
+      <c r="U3" s="443" t="n"/>
+      <c r="V3" s="443" t="n"/>
+      <c r="W3" s="443" t="n"/>
+      <c r="X3" s="443" t="n"/>
+      <c r="Y3" s="443" t="n"/>
+      <c r="Z3" s="443" t="n"/>
+      <c r="AA3" s="443" t="n"/>
+      <c r="AB3" s="443" t="n"/>
+      <c r="AC3" s="443" t="n"/>
+      <c r="AD3" s="444" t="n"/>
+      <c r="AE3" s="445" t="n"/>
+      <c r="AF3" s="446" t="n"/>
+      <c r="AG3" s="446" t="n"/>
+      <c r="AH3" s="447" t="n"/>
+      <c r="AI3" s="448" t="n"/>
+      <c r="AJ3" s="449" t="n"/>
+      <c r="AK3" s="449" t="n"/>
+      <c r="AL3" s="449" t="n"/>
+      <c r="AM3" s="449" t="n"/>
+      <c r="AN3" s="450" t="n"/>
     </row>
-    <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="394" t="inlineStr">
+    <row r="4" ht="15" customHeight="1">
+      <c r="A4" s="519" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B4" s="394" t="inlineStr">
+      <c r="B4" s="520" t="inlineStr">
         <is>
           <t>Condition / Exception</t>
         </is>
       </c>
-      <c r="C4" s="394" t="inlineStr">
+      <c r="C4" s="520" t="inlineStr">
         <is>
           <t>Required Action</t>
         </is>
       </c>
-      <c r="D4" s="394" t="inlineStr">
+      <c r="D4" s="520" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="E4" s="394" t="inlineStr">
+      <c r="E4" s="520" t="inlineStr">
         <is>
           <t>Due Date</t>
         </is>
       </c>
-      <c r="F4" s="394" t="inlineStr">
+      <c r="F4" s="520" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="G4" s="394" t="inlineStr">
+      <c r="G4" s="520" t="inlineStr">
         <is>
           <t>Evidence Ref</t>
         </is>
       </c>
-      <c r="H4" s="394" t="inlineStr">
+      <c r="H4" s="521" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="I4" s="348" t="n"/>
-      <c r="J4" s="348" t="n"/>
-      <c r="K4" s="348" t="n"/>
-      <c r="L4" s="348" t="n"/>
-      <c r="M4" s="348" t="n"/>
-      <c r="N4" s="348" t="n"/>
-      <c r="O4" s="348" t="n"/>
-      <c r="P4" s="348" t="n"/>
-      <c r="Q4" s="348" t="n"/>
-      <c r="R4" s="348" t="n"/>
-      <c r="S4" s="348" t="n"/>
-      <c r="T4" s="348" t="n"/>
-      <c r="U4" s="348" t="n"/>
-      <c r="V4" s="348" t="n"/>
-      <c r="W4" s="348" t="n"/>
-      <c r="X4" s="348" t="n"/>
-      <c r="Y4" s="348" t="n"/>
-      <c r="Z4" s="348" t="n"/>
-      <c r="AA4" s="348" t="n"/>
-      <c r="AB4" s="348" t="n"/>
-      <c r="AC4" s="348" t="n"/>
-      <c r="AD4" s="348" t="n"/>
-      <c r="AE4" s="348" t="n"/>
-      <c r="AF4" s="348" t="n"/>
-      <c r="AG4" s="348" t="n"/>
-      <c r="AH4" s="348" t="n"/>
-      <c r="AI4" s="348" t="n"/>
-      <c r="AJ4" s="348" t="n"/>
-      <c r="AK4" s="348" t="n"/>
-      <c r="AL4" s="348" t="n"/>
-      <c r="AM4" s="348" t="n"/>
-      <c r="AN4" s="348" t="n"/>
+      <c r="I4" s="451" t="n"/>
+      <c r="J4" s="452" t="n"/>
+      <c r="K4" s="452" t="n"/>
+      <c r="L4" s="452" t="n"/>
+      <c r="M4" s="452" t="n"/>
+      <c r="N4" s="452" t="n"/>
+      <c r="O4" s="452" t="n"/>
+      <c r="P4" s="452" t="n"/>
+      <c r="Q4" s="452" t="n"/>
+      <c r="R4" s="452" t="n"/>
+      <c r="S4" s="452" t="n"/>
+      <c r="T4" s="452" t="n"/>
+      <c r="U4" s="452" t="n"/>
+      <c r="V4" s="452" t="n"/>
+      <c r="W4" s="452" t="n"/>
+      <c r="X4" s="452" t="n"/>
+      <c r="Y4" s="452" t="n"/>
+      <c r="Z4" s="452" t="n"/>
+      <c r="AA4" s="452" t="n"/>
+      <c r="AB4" s="452" t="n"/>
+      <c r="AC4" s="452" t="n"/>
+      <c r="AD4" s="453" t="n"/>
+      <c r="AE4" s="445" t="n"/>
+      <c r="AF4" s="446" t="n"/>
+      <c r="AG4" s="446" t="n"/>
+      <c r="AH4" s="447" t="n"/>
+      <c r="AI4" s="448" t="n"/>
+      <c r="AJ4" s="449" t="n"/>
+      <c r="AK4" s="449" t="n"/>
+      <c r="AL4" s="449" t="n"/>
+      <c r="AM4" s="449" t="n"/>
+      <c r="AN4" s="450" t="n"/>
     </row>
-    <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="395">
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" s="522">
         <f>ROW()-ROW($A$5)+1</f>
         <v/>
       </c>
-      <c r="B5" s="396" t="n"/>
-      <c r="C5" s="396" t="n"/>
-      <c r="D5" s="396" t="n"/>
-      <c r="E5" s="396" t="n"/>
-      <c r="F5" s="396" t="n"/>
-      <c r="G5" s="396" t="n"/>
-      <c r="H5" s="396" t="n"/>
-      <c r="I5" s="348" t="n"/>
-      <c r="J5" s="348" t="n"/>
-      <c r="K5" s="348" t="n"/>
-      <c r="L5" s="348" t="n"/>
-      <c r="M5" s="348" t="n"/>
-      <c r="N5" s="348" t="n"/>
-      <c r="O5" s="348" t="n"/>
-      <c r="P5" s="348" t="n"/>
-      <c r="Q5" s="348" t="n"/>
-      <c r="R5" s="348" t="n"/>
-      <c r="S5" s="348" t="n"/>
-      <c r="T5" s="348" t="n"/>
-      <c r="U5" s="348" t="n"/>
-      <c r="V5" s="348" t="n"/>
-      <c r="W5" s="348" t="n"/>
-      <c r="X5" s="348" t="n"/>
-      <c r="Y5" s="348" t="n"/>
-      <c r="Z5" s="348" t="n"/>
-      <c r="AA5" s="348" t="n"/>
-      <c r="AB5" s="348" t="n"/>
-      <c r="AC5" s="348" t="n"/>
-      <c r="AD5" s="348" t="n"/>
-      <c r="AE5" s="348" t="n"/>
-      <c r="AF5" s="348" t="n"/>
-      <c r="AG5" s="348" t="n"/>
-      <c r="AH5" s="348" t="n"/>
-      <c r="AI5" s="348" t="n"/>
-      <c r="AJ5" s="348" t="n"/>
-      <c r="AK5" s="348" t="n"/>
-      <c r="AL5" s="348" t="n"/>
-      <c r="AM5" s="348" t="n"/>
-      <c r="AN5" s="348" t="n"/>
+      <c r="B5" s="523" t="n"/>
+      <c r="C5" s="523" t="n"/>
+      <c r="D5" s="523" t="n"/>
+      <c r="E5" s="523" t="n"/>
+      <c r="F5" s="523" t="n"/>
+      <c r="G5" s="523" t="n"/>
+      <c r="H5" s="524" t="n"/>
+      <c r="I5" s="457" t="n"/>
+      <c r="J5" s="458" t="n"/>
+      <c r="K5" s="458" t="n"/>
+      <c r="L5" s="458" t="n"/>
+      <c r="M5" s="458" t="n"/>
+      <c r="N5" s="458" t="n"/>
+      <c r="O5" s="458" t="n"/>
+      <c r="P5" s="458" t="n"/>
+      <c r="Q5" s="458" t="n"/>
+      <c r="R5" s="458" t="n"/>
+      <c r="S5" s="458" t="n"/>
+      <c r="T5" s="458" t="n"/>
+      <c r="U5" s="458" t="n"/>
+      <c r="V5" s="458" t="n"/>
+      <c r="W5" s="458" t="n"/>
+      <c r="X5" s="458" t="n"/>
+      <c r="Y5" s="458" t="n"/>
+      <c r="Z5" s="458" t="n"/>
+      <c r="AA5" s="458" t="n"/>
+      <c r="AB5" s="458" t="n"/>
+      <c r="AC5" s="458" t="n"/>
+      <c r="AD5" s="459" t="n"/>
+      <c r="AE5" s="460" t="n"/>
+      <c r="AF5" s="461" t="n"/>
+      <c r="AG5" s="461" t="n"/>
+      <c r="AH5" s="462" t="n"/>
+      <c r="AI5" s="463" t="n"/>
+      <c r="AJ5" s="464" t="n"/>
+      <c r="AK5" s="464" t="n"/>
+      <c r="AL5" s="464" t="n"/>
+      <c r="AM5" s="464" t="n"/>
+      <c r="AN5" s="465" t="n"/>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="395">
+      <c r="A6" s="525">
         <f>ROW()-ROW($A$5)+1</f>
         <v/>
       </c>
-      <c r="B6" s="396" t="n"/>
-      <c r="C6" s="396" t="n"/>
-      <c r="D6" s="396" t="n"/>
-      <c r="E6" s="396" t="n"/>
-      <c r="F6" s="396" t="n"/>
-      <c r="G6" s="396" t="n"/>
-      <c r="H6" s="396" t="n"/>
-      <c r="I6" s="348" t="n"/>
-      <c r="J6" s="348" t="n"/>
-      <c r="K6" s="348" t="n"/>
-      <c r="L6" s="348" t="n"/>
-      <c r="M6" s="348" t="n"/>
-      <c r="N6" s="348" t="n"/>
-      <c r="O6" s="348" t="n"/>
-      <c r="P6" s="348" t="n"/>
-      <c r="Q6" s="348" t="n"/>
-      <c r="R6" s="348" t="n"/>
-      <c r="S6" s="348" t="n"/>
-      <c r="T6" s="348" t="n"/>
-      <c r="U6" s="348" t="n"/>
-      <c r="V6" s="348" t="n"/>
-      <c r="W6" s="348" t="n"/>
-      <c r="X6" s="348" t="n"/>
-      <c r="Y6" s="348" t="n"/>
-      <c r="Z6" s="348" t="n"/>
-      <c r="AA6" s="348" t="n"/>
-      <c r="AB6" s="348" t="n"/>
-      <c r="AC6" s="348" t="n"/>
-      <c r="AD6" s="348" t="n"/>
-      <c r="AE6" s="348" t="n"/>
-      <c r="AF6" s="348" t="n"/>
-      <c r="AG6" s="348" t="n"/>
-      <c r="AH6" s="348" t="n"/>
-      <c r="AI6" s="348" t="n"/>
-      <c r="AJ6" s="348" t="n"/>
-      <c r="AK6" s="348" t="n"/>
-      <c r="AL6" s="348" t="n"/>
-      <c r="AM6" s="348" t="n"/>
-      <c r="AN6" s="348" t="n"/>
+      <c r="B6" s="526" t="n"/>
+      <c r="C6" s="527" t="n"/>
+      <c r="D6" s="527" t="n"/>
+      <c r="E6" s="527" t="n"/>
+      <c r="F6" s="527" t="n"/>
+      <c r="G6" s="527" t="n"/>
+      <c r="H6" s="527" t="n"/>
+      <c r="I6" s="471" t="n"/>
+      <c r="J6" s="471" t="n"/>
+      <c r="K6" s="471" t="n"/>
+      <c r="L6" s="471" t="n"/>
+      <c r="M6" s="471" t="n"/>
+      <c r="N6" s="471" t="n"/>
+      <c r="O6" s="471" t="n"/>
+      <c r="P6" s="471" t="n"/>
+      <c r="Q6" s="471" t="n"/>
+      <c r="R6" s="471" t="n"/>
+      <c r="S6" s="471" t="n"/>
+      <c r="T6" s="471" t="n"/>
+      <c r="U6" s="471" t="n"/>
+      <c r="V6" s="471" t="n"/>
+      <c r="W6" s="471" t="n"/>
+      <c r="X6" s="471" t="n"/>
+      <c r="Y6" s="471" t="n"/>
+      <c r="Z6" s="471" t="n"/>
+      <c r="AA6" s="471" t="n"/>
+      <c r="AB6" s="471" t="n"/>
+      <c r="AC6" s="471" t="n"/>
+      <c r="AD6" s="471" t="n"/>
+      <c r="AE6" s="471" t="n"/>
+      <c r="AF6" s="471" t="n"/>
+      <c r="AG6" s="471" t="n"/>
+      <c r="AH6" s="471" t="n"/>
+      <c r="AI6" s="471" t="n"/>
+      <c r="AJ6" s="471" t="n"/>
+      <c r="AK6" s="471" t="n"/>
+      <c r="AL6" s="471" t="n"/>
+      <c r="AM6" s="471" t="n"/>
+      <c r="AN6" s="503" t="n"/>
     </row>
     <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="395">
+      <c r="A7" s="528">
         <f>ROW()-ROW($A$5)+1</f>
         <v/>
       </c>
-      <c r="B7" s="396" t="n"/>
-      <c r="C7" s="396" t="n"/>
-      <c r="D7" s="396" t="n"/>
-      <c r="E7" s="396" t="n"/>
-      <c r="F7" s="396" t="n"/>
-      <c r="G7" s="396" t="n"/>
-      <c r="H7" s="396" t="n"/>
-      <c r="I7" s="348" t="n"/>
-      <c r="J7" s="348" t="n"/>
-      <c r="K7" s="348" t="n"/>
-      <c r="L7" s="348" t="n"/>
-      <c r="M7" s="348" t="n"/>
-      <c r="N7" s="348" t="n"/>
-      <c r="O7" s="348" t="n"/>
-      <c r="P7" s="348" t="n"/>
-      <c r="Q7" s="348" t="n"/>
-      <c r="R7" s="348" t="n"/>
-      <c r="S7" s="348" t="n"/>
-      <c r="T7" s="348" t="n"/>
-      <c r="U7" s="348" t="n"/>
-      <c r="V7" s="348" t="n"/>
-      <c r="W7" s="348" t="n"/>
-      <c r="X7" s="348" t="n"/>
-      <c r="Y7" s="348" t="n"/>
-      <c r="Z7" s="348" t="n"/>
-      <c r="AA7" s="348" t="n"/>
-      <c r="AB7" s="348" t="n"/>
-      <c r="AC7" s="348" t="n"/>
-      <c r="AD7" s="348" t="n"/>
-      <c r="AE7" s="348" t="n"/>
-      <c r="AF7" s="348" t="n"/>
-      <c r="AG7" s="348" t="n"/>
-      <c r="AH7" s="348" t="n"/>
-      <c r="AI7" s="348" t="n"/>
-      <c r="AJ7" s="348" t="n"/>
-      <c r="AK7" s="348" t="n"/>
-      <c r="AL7" s="348" t="n"/>
-      <c r="AM7" s="348" t="n"/>
-      <c r="AN7" s="348" t="n"/>
+      <c r="B7" s="529" t="n"/>
+      <c r="C7" s="530" t="n"/>
+      <c r="D7" s="530" t="n"/>
+      <c r="E7" s="530" t="n"/>
+      <c r="F7" s="530" t="n"/>
+      <c r="G7" s="530" t="n"/>
+      <c r="H7" s="530" t="n"/>
+      <c r="I7" s="344" t="n"/>
+      <c r="J7" s="344" t="n"/>
+      <c r="K7" s="344" t="n"/>
+      <c r="L7" s="344" t="n"/>
+      <c r="M7" s="344" t="n"/>
+      <c r="N7" s="344" t="n"/>
+      <c r="O7" s="344" t="n"/>
+      <c r="P7" s="344" t="n"/>
+      <c r="Q7" s="344" t="n"/>
+      <c r="R7" s="344" t="n"/>
+      <c r="S7" s="344" t="n"/>
+      <c r="T7" s="344" t="n"/>
+      <c r="U7" s="344" t="n"/>
+      <c r="V7" s="344" t="n"/>
+      <c r="W7" s="344" t="n"/>
+      <c r="X7" s="344" t="n"/>
+      <c r="Y7" s="344" t="n"/>
+      <c r="Z7" s="344" t="n"/>
+      <c r="AA7" s="344" t="n"/>
+      <c r="AB7" s="344" t="n"/>
+      <c r="AC7" s="344" t="n"/>
+      <c r="AD7" s="344" t="n"/>
+      <c r="AE7" s="344" t="n"/>
+      <c r="AF7" s="344" t="n"/>
+      <c r="AG7" s="344" t="n"/>
+      <c r="AH7" s="344" t="n"/>
+      <c r="AI7" s="344" t="n"/>
+      <c r="AJ7" s="344" t="n"/>
+      <c r="AK7" s="344" t="n"/>
+      <c r="AL7" s="344" t="n"/>
+      <c r="AM7" s="344" t="n"/>
+      <c r="AN7" s="531" t="n"/>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="397">
+      <c r="A8" s="532">
         <f>ROW()-ROW($A$5)+1</f>
         <v/>
       </c>
-      <c r="B8" s="398" t="n"/>
-      <c r="C8" s="398" t="n"/>
-      <c r="D8" s="398" t="n"/>
-      <c r="E8" s="398" t="n"/>
-      <c r="F8" s="398" t="n"/>
-      <c r="G8" s="398" t="n"/>
-      <c r="H8" s="398" t="n"/>
-      <c r="I8" s="399" t="n"/>
-      <c r="J8" s="399" t="n"/>
-      <c r="K8" s="399" t="n"/>
-      <c r="L8" s="399" t="n"/>
-      <c r="M8" s="399" t="n"/>
-      <c r="N8" s="399" t="n"/>
-      <c r="O8" s="399" t="n"/>
-      <c r="P8" s="399" t="n"/>
-      <c r="Q8" s="399" t="n"/>
-      <c r="R8" s="399" t="n"/>
-      <c r="S8" s="399" t="n"/>
-      <c r="T8" s="399" t="n"/>
-      <c r="U8" s="399" t="n"/>
-      <c r="V8" s="399" t="n"/>
-      <c r="W8" s="399" t="n"/>
-      <c r="X8" s="399" t="n"/>
-      <c r="Y8" s="399" t="n"/>
-      <c r="Z8" s="399" t="n"/>
-      <c r="AA8" s="399" t="n"/>
-      <c r="AB8" s="399" t="n"/>
-      <c r="AC8" s="399" t="n"/>
-      <c r="AD8" s="399" t="n"/>
-      <c r="AE8" s="399" t="n"/>
-      <c r="AF8" s="399" t="n"/>
-      <c r="AG8" s="399" t="n"/>
-      <c r="AH8" s="399" t="n"/>
-      <c r="AI8" s="399" t="n"/>
-      <c r="AJ8" s="399" t="n"/>
-      <c r="AK8" s="399" t="n"/>
-      <c r="AL8" s="399" t="n"/>
-      <c r="AM8" s="399" t="n"/>
-      <c r="AN8" s="399" t="n"/>
+      <c r="B8" s="533" t="n"/>
+      <c r="C8" s="534" t="n"/>
+      <c r="D8" s="534" t="n"/>
+      <c r="E8" s="534" t="n"/>
+      <c r="F8" s="534" t="n"/>
+      <c r="G8" s="534" t="n"/>
+      <c r="H8" s="534" t="n"/>
+      <c r="I8" s="356" t="n"/>
+      <c r="J8" s="356" t="n"/>
+      <c r="K8" s="356" t="n"/>
+      <c r="L8" s="356" t="n"/>
+      <c r="M8" s="356" t="n"/>
+      <c r="N8" s="356" t="n"/>
+      <c r="O8" s="356" t="n"/>
+      <c r="P8" s="356" t="n"/>
+      <c r="Q8" s="356" t="n"/>
+      <c r="R8" s="356" t="n"/>
+      <c r="S8" s="356" t="n"/>
+      <c r="T8" s="356" t="n"/>
+      <c r="U8" s="356" t="n"/>
+      <c r="V8" s="356" t="n"/>
+      <c r="W8" s="356" t="n"/>
+      <c r="X8" s="356" t="n"/>
+      <c r="Y8" s="356" t="n"/>
+      <c r="Z8" s="356" t="n"/>
+      <c r="AA8" s="356" t="n"/>
+      <c r="AB8" s="356" t="n"/>
+      <c r="AC8" s="356" t="n"/>
+      <c r="AD8" s="356" t="n"/>
+      <c r="AE8" s="356" t="n"/>
+      <c r="AF8" s="356" t="n"/>
+      <c r="AG8" s="356" t="n"/>
+      <c r="AH8" s="356" t="n"/>
+      <c r="AI8" s="356" t="n"/>
+      <c r="AJ8" s="356" t="n"/>
+      <c r="AK8" s="356" t="n"/>
+      <c r="AL8" s="356" t="n"/>
+      <c r="AM8" s="356" t="n"/>
+      <c r="AN8" s="535" t="n"/>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="397">
+      <c r="A9" s="532">
         <f>ROW()-ROW($A$5)+1</f>
         <v/>
       </c>
-      <c r="B9" s="398" t="n"/>
-      <c r="C9" s="398" t="n"/>
-      <c r="D9" s="398" t="n"/>
-      <c r="E9" s="398" t="n"/>
-      <c r="F9" s="398" t="n"/>
-      <c r="G9" s="398" t="n"/>
-      <c r="H9" s="398" t="n"/>
-      <c r="I9" s="399" t="n"/>
-      <c r="J9" s="399" t="n"/>
-      <c r="K9" s="399" t="n"/>
-      <c r="L9" s="399" t="n"/>
-      <c r="M9" s="399" t="n"/>
-      <c r="N9" s="399" t="n"/>
-      <c r="O9" s="399" t="n"/>
-      <c r="P9" s="399" t="n"/>
-      <c r="Q9" s="399" t="n"/>
-      <c r="R9" s="399" t="n"/>
-      <c r="S9" s="399" t="n"/>
-      <c r="T9" s="399" t="n"/>
-      <c r="U9" s="399" t="n"/>
-      <c r="V9" s="399" t="n"/>
-      <c r="W9" s="399" t="n"/>
-      <c r="X9" s="399" t="n"/>
-      <c r="Y9" s="399" t="n"/>
-      <c r="Z9" s="399" t="n"/>
-      <c r="AA9" s="399" t="n"/>
-      <c r="AB9" s="399" t="n"/>
-      <c r="AC9" s="399" t="n"/>
-      <c r="AD9" s="399" t="n"/>
-      <c r="AE9" s="399" t="n"/>
-      <c r="AF9" s="399" t="n"/>
-      <c r="AG9" s="399" t="n"/>
-      <c r="AH9" s="399" t="n"/>
-      <c r="AI9" s="399" t="n"/>
-      <c r="AJ9" s="399" t="n"/>
-      <c r="AK9" s="399" t="n"/>
-      <c r="AL9" s="399" t="n"/>
-      <c r="AM9" s="399" t="n"/>
-      <c r="AN9" s="399" t="n"/>
+      <c r="B9" s="533" t="n"/>
+      <c r="C9" s="534" t="n"/>
+      <c r="D9" s="534" t="n"/>
+      <c r="E9" s="534" t="n"/>
+      <c r="F9" s="534" t="n"/>
+      <c r="G9" s="534" t="n"/>
+      <c r="H9" s="534" t="n"/>
+      <c r="I9" s="356" t="n"/>
+      <c r="J9" s="356" t="n"/>
+      <c r="K9" s="356" t="n"/>
+      <c r="L9" s="356" t="n"/>
+      <c r="M9" s="356" t="n"/>
+      <c r="N9" s="356" t="n"/>
+      <c r="O9" s="356" t="n"/>
+      <c r="P9" s="356" t="n"/>
+      <c r="Q9" s="356" t="n"/>
+      <c r="R9" s="356" t="n"/>
+      <c r="S9" s="356" t="n"/>
+      <c r="T9" s="356" t="n"/>
+      <c r="U9" s="356" t="n"/>
+      <c r="V9" s="356" t="n"/>
+      <c r="W9" s="356" t="n"/>
+      <c r="X9" s="356" t="n"/>
+      <c r="Y9" s="356" t="n"/>
+      <c r="Z9" s="356" t="n"/>
+      <c r="AA9" s="356" t="n"/>
+      <c r="AB9" s="356" t="n"/>
+      <c r="AC9" s="356" t="n"/>
+      <c r="AD9" s="356" t="n"/>
+      <c r="AE9" s="356" t="n"/>
+      <c r="AF9" s="356" t="n"/>
+      <c r="AG9" s="356" t="n"/>
+      <c r="AH9" s="356" t="n"/>
+      <c r="AI9" s="356" t="n"/>
+      <c r="AJ9" s="356" t="n"/>
+      <c r="AK9" s="356" t="n"/>
+      <c r="AL9" s="356" t="n"/>
+      <c r="AM9" s="356" t="n"/>
+      <c r="AN9" s="535" t="n"/>
     </row>
     <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="397">
+      <c r="A10" s="532">
         <f>ROW()-ROW($A$5)+1</f>
         <v/>
       </c>
-      <c r="B10" s="398" t="n"/>
-      <c r="C10" s="398" t="n"/>
-      <c r="D10" s="398" t="n"/>
-      <c r="E10" s="398" t="n"/>
-      <c r="F10" s="398" t="n"/>
-      <c r="G10" s="398" t="n"/>
-      <c r="H10" s="398" t="n"/>
-      <c r="I10" s="399" t="n"/>
-      <c r="J10" s="399" t="n"/>
-      <c r="K10" s="399" t="n"/>
-      <c r="L10" s="399" t="n"/>
-      <c r="M10" s="399" t="n"/>
-      <c r="N10" s="399" t="n"/>
-      <c r="O10" s="399" t="n"/>
-      <c r="P10" s="399" t="n"/>
-      <c r="Q10" s="399" t="n"/>
-      <c r="R10" s="399" t="n"/>
-      <c r="S10" s="399" t="n"/>
-      <c r="T10" s="399" t="n"/>
-      <c r="U10" s="399" t="n"/>
-      <c r="V10" s="399" t="n"/>
-      <c r="W10" s="399" t="n"/>
-      <c r="X10" s="399" t="n"/>
-      <c r="Y10" s="399" t="n"/>
-      <c r="Z10" s="399" t="n"/>
-      <c r="AA10" s="399" t="n"/>
-      <c r="AB10" s="399" t="n"/>
-      <c r="AC10" s="399" t="n"/>
-      <c r="AD10" s="399" t="n"/>
-      <c r="AE10" s="399" t="n"/>
-      <c r="AF10" s="399" t="n"/>
-      <c r="AG10" s="399" t="n"/>
-      <c r="AH10" s="399" t="n"/>
-      <c r="AI10" s="399" t="n"/>
-      <c r="AJ10" s="399" t="n"/>
-      <c r="AK10" s="399" t="n"/>
-      <c r="AL10" s="399" t="n"/>
-      <c r="AM10" s="399" t="n"/>
-      <c r="AN10" s="399" t="n"/>
+      <c r="B10" s="533" t="n"/>
+      <c r="C10" s="534" t="n"/>
+      <c r="D10" s="534" t="n"/>
+      <c r="E10" s="534" t="n"/>
+      <c r="F10" s="534" t="n"/>
+      <c r="G10" s="534" t="n"/>
+      <c r="H10" s="534" t="n"/>
+      <c r="I10" s="356" t="n"/>
+      <c r="J10" s="356" t="n"/>
+      <c r="K10" s="356" t="n"/>
+      <c r="L10" s="356" t="n"/>
+      <c r="M10" s="356" t="n"/>
+      <c r="N10" s="356" t="n"/>
+      <c r="O10" s="356" t="n"/>
+      <c r="P10" s="356" t="n"/>
+      <c r="Q10" s="356" t="n"/>
+      <c r="R10" s="356" t="n"/>
+      <c r="S10" s="356" t="n"/>
+      <c r="T10" s="356" t="n"/>
+      <c r="U10" s="356" t="n"/>
+      <c r="V10" s="356" t="n"/>
+      <c r="W10" s="356" t="n"/>
+      <c r="X10" s="356" t="n"/>
+      <c r="Y10" s="356" t="n"/>
+      <c r="Z10" s="356" t="n"/>
+      <c r="AA10" s="356" t="n"/>
+      <c r="AB10" s="356" t="n"/>
+      <c r="AC10" s="356" t="n"/>
+      <c r="AD10" s="356" t="n"/>
+      <c r="AE10" s="356" t="n"/>
+      <c r="AF10" s="356" t="n"/>
+      <c r="AG10" s="356" t="n"/>
+      <c r="AH10" s="356" t="n"/>
+      <c r="AI10" s="356" t="n"/>
+      <c r="AJ10" s="356" t="n"/>
+      <c r="AK10" s="356" t="n"/>
+      <c r="AL10" s="356" t="n"/>
+      <c r="AM10" s="356" t="n"/>
+      <c r="AN10" s="535" t="n"/>
     </row>
     <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="397">
+      <c r="A11" s="532">
         <f>ROW()-ROW($A$5)+1</f>
         <v/>
       </c>
-      <c r="B11" s="398" t="n"/>
-      <c r="C11" s="398" t="n"/>
-      <c r="D11" s="398" t="n"/>
-      <c r="E11" s="398" t="n"/>
-      <c r="F11" s="398" t="n"/>
-      <c r="G11" s="398" t="n"/>
-      <c r="H11" s="398" t="n"/>
-      <c r="I11" s="399" t="n"/>
-      <c r="J11" s="399" t="n"/>
-      <c r="K11" s="399" t="n"/>
-      <c r="L11" s="399" t="n"/>
-      <c r="M11" s="399" t="n"/>
-      <c r="N11" s="399" t="n"/>
-      <c r="O11" s="399" t="n"/>
-      <c r="P11" s="399" t="n"/>
-      <c r="Q11" s="399" t="n"/>
-      <c r="R11" s="399" t="n"/>
-      <c r="S11" s="399" t="n"/>
-      <c r="T11" s="399" t="n"/>
-      <c r="U11" s="399" t="n"/>
-      <c r="V11" s="399" t="n"/>
-      <c r="W11" s="399" t="n"/>
-      <c r="X11" s="399" t="n"/>
-      <c r="Y11" s="399" t="n"/>
-      <c r="Z11" s="399" t="n"/>
-      <c r="AA11" s="399" t="n"/>
-      <c r="AB11" s="399" t="n"/>
-      <c r="AC11" s="399" t="n"/>
-      <c r="AD11" s="399" t="n"/>
-      <c r="AE11" s="399" t="n"/>
-      <c r="AF11" s="399" t="n"/>
-      <c r="AG11" s="399" t="n"/>
-      <c r="AH11" s="399" t="n"/>
-      <c r="AI11" s="399" t="n"/>
-      <c r="AJ11" s="399" t="n"/>
-      <c r="AK11" s="399" t="n"/>
-      <c r="AL11" s="399" t="n"/>
-      <c r="AM11" s="399" t="n"/>
-      <c r="AN11" s="399" t="n"/>
+      <c r="B11" s="533" t="n"/>
+      <c r="C11" s="534" t="n"/>
+      <c r="D11" s="534" t="n"/>
+      <c r="E11" s="534" t="n"/>
+      <c r="F11" s="534" t="n"/>
+      <c r="G11" s="534" t="n"/>
+      <c r="H11" s="534" t="n"/>
+      <c r="I11" s="356" t="n"/>
+      <c r="J11" s="356" t="n"/>
+      <c r="K11" s="356" t="n"/>
+      <c r="L11" s="356" t="n"/>
+      <c r="M11" s="356" t="n"/>
+      <c r="N11" s="356" t="n"/>
+      <c r="O11" s="356" t="n"/>
+      <c r="P11" s="356" t="n"/>
+      <c r="Q11" s="356" t="n"/>
+      <c r="R11" s="356" t="n"/>
+      <c r="S11" s="356" t="n"/>
+      <c r="T11" s="356" t="n"/>
+      <c r="U11" s="356" t="n"/>
+      <c r="V11" s="356" t="n"/>
+      <c r="W11" s="356" t="n"/>
+      <c r="X11" s="356" t="n"/>
+      <c r="Y11" s="356" t="n"/>
+      <c r="Z11" s="356" t="n"/>
+      <c r="AA11" s="356" t="n"/>
+      <c r="AB11" s="356" t="n"/>
+      <c r="AC11" s="356" t="n"/>
+      <c r="AD11" s="356" t="n"/>
+      <c r="AE11" s="356" t="n"/>
+      <c r="AF11" s="356" t="n"/>
+      <c r="AG11" s="356" t="n"/>
+      <c r="AH11" s="356" t="n"/>
+      <c r="AI11" s="356" t="n"/>
+      <c r="AJ11" s="356" t="n"/>
+      <c r="AK11" s="356" t="n"/>
+      <c r="AL11" s="356" t="n"/>
+      <c r="AM11" s="356" t="n"/>
+      <c r="AN11" s="535" t="n"/>
     </row>
     <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="397">
+      <c r="A12" s="532">
         <f>ROW()-ROW($A$5)+1</f>
         <v/>
       </c>
-      <c r="B12" s="398" t="n"/>
-      <c r="C12" s="398" t="n"/>
-      <c r="D12" s="398" t="n"/>
-      <c r="E12" s="398" t="n"/>
-      <c r="F12" s="398" t="n"/>
-      <c r="G12" s="398" t="n"/>
-      <c r="H12" s="398" t="n"/>
-      <c r="I12" s="399" t="n"/>
-      <c r="J12" s="399" t="n"/>
-      <c r="K12" s="399" t="n"/>
-      <c r="L12" s="399" t="n"/>
-      <c r="M12" s="399" t="n"/>
-      <c r="N12" s="399" t="n"/>
-      <c r="O12" s="399" t="n"/>
-      <c r="P12" s="399" t="n"/>
-      <c r="Q12" s="399" t="n"/>
-      <c r="R12" s="399" t="n"/>
-      <c r="S12" s="399" t="n"/>
-      <c r="T12" s="399" t="n"/>
-      <c r="U12" s="399" t="n"/>
-      <c r="V12" s="399" t="n"/>
-      <c r="W12" s="399" t="n"/>
-      <c r="X12" s="399" t="n"/>
-      <c r="Y12" s="399" t="n"/>
-      <c r="Z12" s="399" t="n"/>
-      <c r="AA12" s="399" t="n"/>
-      <c r="AB12" s="399" t="n"/>
-      <c r="AC12" s="399" t="n"/>
-      <c r="AD12" s="399" t="n"/>
-      <c r="AE12" s="399" t="n"/>
-      <c r="AF12" s="399" t="n"/>
-      <c r="AG12" s="399" t="n"/>
-      <c r="AH12" s="399" t="n"/>
-      <c r="AI12" s="399" t="n"/>
-      <c r="AJ12" s="399" t="n"/>
-      <c r="AK12" s="399" t="n"/>
-      <c r="AL12" s="399" t="n"/>
-      <c r="AM12" s="399" t="n"/>
-      <c r="AN12" s="399" t="n"/>
+      <c r="B12" s="533" t="n"/>
+      <c r="C12" s="534" t="n"/>
+      <c r="D12" s="534" t="n"/>
+      <c r="E12" s="534" t="n"/>
+      <c r="F12" s="534" t="n"/>
+      <c r="G12" s="534" t="n"/>
+      <c r="H12" s="534" t="n"/>
+      <c r="I12" s="356" t="n"/>
+      <c r="J12" s="356" t="n"/>
+      <c r="K12" s="356" t="n"/>
+      <c r="L12" s="356" t="n"/>
+      <c r="M12" s="356" t="n"/>
+      <c r="N12" s="356" t="n"/>
+      <c r="O12" s="356" t="n"/>
+      <c r="P12" s="356" t="n"/>
+      <c r="Q12" s="356" t="n"/>
+      <c r="R12" s="356" t="n"/>
+      <c r="S12" s="356" t="n"/>
+      <c r="T12" s="356" t="n"/>
+      <c r="U12" s="356" t="n"/>
+      <c r="V12" s="356" t="n"/>
+      <c r="W12" s="356" t="n"/>
+      <c r="X12" s="356" t="n"/>
+      <c r="Y12" s="356" t="n"/>
+      <c r="Z12" s="356" t="n"/>
+      <c r="AA12" s="356" t="n"/>
+      <c r="AB12" s="356" t="n"/>
+      <c r="AC12" s="356" t="n"/>
+      <c r="AD12" s="356" t="n"/>
+      <c r="AE12" s="356" t="n"/>
+      <c r="AF12" s="356" t="n"/>
+      <c r="AG12" s="356" t="n"/>
+      <c r="AH12" s="356" t="n"/>
+      <c r="AI12" s="356" t="n"/>
+      <c r="AJ12" s="356" t="n"/>
+      <c r="AK12" s="356" t="n"/>
+      <c r="AL12" s="356" t="n"/>
+      <c r="AM12" s="356" t="n"/>
+      <c r="AN12" s="535" t="n"/>
     </row>
     <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="397">
+      <c r="A13" s="532">
         <f>ROW()-ROW($A$5)+1</f>
         <v/>
       </c>
-      <c r="B13" s="398" t="n"/>
-      <c r="C13" s="398" t="n"/>
-      <c r="D13" s="398" t="n"/>
-      <c r="E13" s="398" t="n"/>
-      <c r="F13" s="398" t="n"/>
-      <c r="G13" s="398" t="n"/>
-      <c r="H13" s="398" t="n"/>
-      <c r="I13" s="399" t="n"/>
-      <c r="J13" s="399" t="n"/>
-      <c r="K13" s="399" t="n"/>
-      <c r="L13" s="399" t="n"/>
-      <c r="M13" s="399" t="n"/>
-      <c r="N13" s="399" t="n"/>
-      <c r="O13" s="399" t="n"/>
-      <c r="P13" s="399" t="n"/>
-      <c r="Q13" s="399" t="n"/>
-      <c r="R13" s="399" t="n"/>
-      <c r="S13" s="399" t="n"/>
-      <c r="T13" s="399" t="n"/>
-      <c r="U13" s="399" t="n"/>
-      <c r="V13" s="399" t="n"/>
-      <c r="W13" s="399" t="n"/>
-      <c r="X13" s="399" t="n"/>
-      <c r="Y13" s="399" t="n"/>
-      <c r="Z13" s="399" t="n"/>
-      <c r="AA13" s="399" t="n"/>
-      <c r="AB13" s="399" t="n"/>
-      <c r="AC13" s="399" t="n"/>
-      <c r="AD13" s="399" t="n"/>
-      <c r="AE13" s="399" t="n"/>
-      <c r="AF13" s="399" t="n"/>
-      <c r="AG13" s="399" t="n"/>
-      <c r="AH13" s="399" t="n"/>
-      <c r="AI13" s="399" t="n"/>
-      <c r="AJ13" s="399" t="n"/>
-      <c r="AK13" s="399" t="n"/>
-      <c r="AL13" s="399" t="n"/>
-      <c r="AM13" s="399" t="n"/>
-      <c r="AN13" s="399" t="n"/>
+      <c r="B13" s="533" t="n"/>
+      <c r="C13" s="534" t="n"/>
+      <c r="D13" s="534" t="n"/>
+      <c r="E13" s="534" t="n"/>
+      <c r="F13" s="534" t="n"/>
+      <c r="G13" s="534" t="n"/>
+      <c r="H13" s="534" t="n"/>
+      <c r="I13" s="356" t="n"/>
+      <c r="J13" s="356" t="n"/>
+      <c r="K13" s="356" t="n"/>
+      <c r="L13" s="356" t="n"/>
+      <c r="M13" s="356" t="n"/>
+      <c r="N13" s="356" t="n"/>
+      <c r="O13" s="356" t="n"/>
+      <c r="P13" s="356" t="n"/>
+      <c r="Q13" s="356" t="n"/>
+      <c r="R13" s="356" t="n"/>
+      <c r="S13" s="356" t="n"/>
+      <c r="T13" s="356" t="n"/>
+      <c r="U13" s="356" t="n"/>
+      <c r="V13" s="356" t="n"/>
+      <c r="W13" s="356" t="n"/>
+      <c r="X13" s="356" t="n"/>
+      <c r="Y13" s="356" t="n"/>
+      <c r="Z13" s="356" t="n"/>
+      <c r="AA13" s="356" t="n"/>
+      <c r="AB13" s="356" t="n"/>
+      <c r="AC13" s="356" t="n"/>
+      <c r="AD13" s="356" t="n"/>
+      <c r="AE13" s="356" t="n"/>
+      <c r="AF13" s="356" t="n"/>
+      <c r="AG13" s="356" t="n"/>
+      <c r="AH13" s="356" t="n"/>
+      <c r="AI13" s="356" t="n"/>
+      <c r="AJ13" s="356" t="n"/>
+      <c r="AK13" s="356" t="n"/>
+      <c r="AL13" s="356" t="n"/>
+      <c r="AM13" s="356" t="n"/>
+      <c r="AN13" s="535" t="n"/>
     </row>
     <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="397">
+      <c r="A14" s="536">
         <f>ROW()-ROW($A$5)+1</f>
         <v/>
       </c>
-      <c r="B14" s="398" t="n"/>
-      <c r="C14" s="398" t="n"/>
-      <c r="D14" s="398" t="n"/>
-      <c r="E14" s="398" t="n"/>
-      <c r="F14" s="398" t="n"/>
-      <c r="G14" s="398" t="n"/>
-      <c r="H14" s="398" t="n"/>
-      <c r="I14" s="399" t="n"/>
-      <c r="J14" s="399" t="n"/>
-      <c r="K14" s="399" t="n"/>
-      <c r="L14" s="399" t="n"/>
-      <c r="M14" s="399" t="n"/>
-      <c r="N14" s="399" t="n"/>
-      <c r="O14" s="399" t="n"/>
-      <c r="P14" s="399" t="n"/>
-      <c r="Q14" s="399" t="n"/>
-      <c r="R14" s="399" t="n"/>
-      <c r="S14" s="399" t="n"/>
-      <c r="T14" s="399" t="n"/>
-      <c r="U14" s="399" t="n"/>
-      <c r="V14" s="399" t="n"/>
-      <c r="W14" s="399" t="n"/>
-      <c r="X14" s="399" t="n"/>
-      <c r="Y14" s="399" t="n"/>
-      <c r="Z14" s="399" t="n"/>
-      <c r="AA14" s="399" t="n"/>
-      <c r="AB14" s="399" t="n"/>
-      <c r="AC14" s="399" t="n"/>
-      <c r="AD14" s="399" t="n"/>
-      <c r="AE14" s="399" t="n"/>
-      <c r="AF14" s="399" t="n"/>
-      <c r="AG14" s="399" t="n"/>
-      <c r="AH14" s="399" t="n"/>
-      <c r="AI14" s="399" t="n"/>
-      <c r="AJ14" s="399" t="n"/>
-      <c r="AK14" s="399" t="n"/>
-      <c r="AL14" s="399" t="n"/>
-      <c r="AM14" s="399" t="n"/>
-      <c r="AN14" s="399" t="n"/>
+      <c r="B14" s="537" t="n"/>
+      <c r="C14" s="538" t="n"/>
+      <c r="D14" s="538" t="n"/>
+      <c r="E14" s="538" t="n"/>
+      <c r="F14" s="538" t="n"/>
+      <c r="G14" s="538" t="n"/>
+      <c r="H14" s="538" t="n"/>
+      <c r="I14" s="539" t="n"/>
+      <c r="J14" s="539" t="n"/>
+      <c r="K14" s="539" t="n"/>
+      <c r="L14" s="539" t="n"/>
+      <c r="M14" s="539" t="n"/>
+      <c r="N14" s="539" t="n"/>
+      <c r="O14" s="539" t="n"/>
+      <c r="P14" s="539" t="n"/>
+      <c r="Q14" s="539" t="n"/>
+      <c r="R14" s="539" t="n"/>
+      <c r="S14" s="539" t="n"/>
+      <c r="T14" s="539" t="n"/>
+      <c r="U14" s="539" t="n"/>
+      <c r="V14" s="539" t="n"/>
+      <c r="W14" s="539" t="n"/>
+      <c r="X14" s="539" t="n"/>
+      <c r="Y14" s="539" t="n"/>
+      <c r="Z14" s="539" t="n"/>
+      <c r="AA14" s="539" t="n"/>
+      <c r="AB14" s="539" t="n"/>
+      <c r="AC14" s="539" t="n"/>
+      <c r="AD14" s="539" t="n"/>
+      <c r="AE14" s="539" t="n"/>
+      <c r="AF14" s="539" t="n"/>
+      <c r="AG14" s="539" t="n"/>
+      <c r="AH14" s="539" t="n"/>
+      <c r="AI14" s="539" t="n"/>
+      <c r="AJ14" s="539" t="n"/>
+      <c r="AK14" s="539" t="n"/>
+      <c r="AL14" s="539" t="n"/>
+      <c r="AM14" s="539" t="n"/>
+      <c r="AN14" s="540" t="n"/>
     </row>
     <row r="15" ht="20" customHeight="1"/>
     <row r="16" ht="20" customHeight="1"/>
@@ -8627,9 +9530,10 @@
   </dataValidations>
   <pageMargins left="0.197" right="0.197" top="0.197" bottom="0.197" header="0.1" footer="0.1"/>
   <pageSetup paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   <tableParts count="2">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
   </tableParts>
 </worksheet>
 </file>
@@ -8685,249 +9589,255 @@
     <col width="2.33" customWidth="1" min="40" max="40"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18" customHeight="1">
-      <c r="A1" s="393" t="inlineStr">
+    <row r="1" ht="15" customHeight="1">
+      <c r="A1" s="513" t="inlineStr">
         <is>
           <t>Upstream References / Import Guidance</t>
         </is>
       </c>
-      <c r="B1" s="423" t="n"/>
-      <c r="C1" s="423" t="n"/>
-      <c r="D1" s="423" t="n"/>
-      <c r="E1" s="423" t="n"/>
-      <c r="F1" s="423" t="n"/>
-      <c r="G1" s="424" t="n"/>
-      <c r="H1" s="348" t="n"/>
-      <c r="I1" s="348" t="n"/>
-      <c r="J1" s="348" t="n"/>
-      <c r="K1" s="348" t="n"/>
-      <c r="L1" s="348" t="n"/>
-      <c r="M1" s="348" t="n"/>
-      <c r="N1" s="348" t="n"/>
-      <c r="O1" s="348" t="n"/>
-      <c r="P1" s="348" t="n"/>
-      <c r="Q1" s="348" t="n"/>
-      <c r="R1" s="348" t="n"/>
-      <c r="S1" s="348" t="n"/>
-      <c r="T1" s="348" t="n"/>
-      <c r="U1" s="348" t="n"/>
-      <c r="V1" s="348" t="n"/>
-      <c r="W1" s="348" t="n"/>
-      <c r="X1" s="348" t="n"/>
-      <c r="Y1" s="348" t="n"/>
-      <c r="Z1" s="348" t="n"/>
-      <c r="AA1" s="348" t="n"/>
-      <c r="AB1" s="348" t="n"/>
-      <c r="AC1" s="348" t="n"/>
-      <c r="AD1" s="348" t="n"/>
-      <c r="AE1" s="348" t="n"/>
-      <c r="AF1" s="348" t="n"/>
-      <c r="AG1" s="348" t="n"/>
-      <c r="AH1" s="348" t="n"/>
-      <c r="AI1" s="348" t="n"/>
-      <c r="AJ1" s="348" t="n"/>
-      <c r="AK1" s="348" t="n"/>
-      <c r="AL1" s="348" t="n"/>
-      <c r="AM1" s="348" t="n"/>
-      <c r="AN1" s="348" t="n"/>
+      <c r="B1" s="429" t="n"/>
+      <c r="C1" s="429" t="n"/>
+      <c r="D1" s="429" t="n"/>
+      <c r="E1" s="429" t="n"/>
+      <c r="F1" s="429" t="n"/>
+      <c r="G1" s="429" t="n"/>
+      <c r="H1" s="514" t="n"/>
+      <c r="I1" s="431" t="n"/>
+      <c r="J1" s="432" t="n"/>
+      <c r="K1" s="432" t="n"/>
+      <c r="L1" s="432" t="n"/>
+      <c r="M1" s="432" t="n"/>
+      <c r="N1" s="432" t="n"/>
+      <c r="O1" s="432" t="n"/>
+      <c r="P1" s="432" t="n"/>
+      <c r="Q1" s="432" t="n"/>
+      <c r="R1" s="432" t="n"/>
+      <c r="S1" s="432" t="n"/>
+      <c r="T1" s="432" t="n"/>
+      <c r="U1" s="432" t="n"/>
+      <c r="V1" s="432" t="n"/>
+      <c r="W1" s="432" t="n"/>
+      <c r="X1" s="432" t="n"/>
+      <c r="Y1" s="432" t="n"/>
+      <c r="Z1" s="432" t="n"/>
+      <c r="AA1" s="432" t="n"/>
+      <c r="AB1" s="432" t="n"/>
+      <c r="AC1" s="432" t="n"/>
+      <c r="AD1" s="433" t="n"/>
+      <c r="AE1" s="434" t="n"/>
+      <c r="AF1" s="435" t="n"/>
+      <c r="AG1" s="435" t="n"/>
+      <c r="AH1" s="436" t="n"/>
+      <c r="AI1" s="437" t="n"/>
+      <c r="AJ1" s="438" t="n"/>
+      <c r="AK1" s="438" t="n"/>
+      <c r="AL1" s="438" t="n"/>
+      <c r="AM1" s="438" t="n"/>
+      <c r="AN1" s="439" t="n"/>
     </row>
-    <row r="2" ht="18" customHeight="1">
-      <c r="A2" s="338" t="inlineStr">
+    <row r="2" ht="15" customHeight="1">
+      <c r="A2" s="515" t="inlineStr">
         <is>
           <t>Vacuum-compatible clean build and bagging gate for controlled preservation and packaging release.</t>
         </is>
       </c>
-      <c r="H2" s="348" t="n"/>
-      <c r="I2" s="348" t="n"/>
-      <c r="J2" s="348" t="n"/>
-      <c r="K2" s="348" t="n"/>
-      <c r="L2" s="348" t="n"/>
-      <c r="M2" s="348" t="n"/>
-      <c r="N2" s="348" t="n"/>
-      <c r="O2" s="348" t="n"/>
-      <c r="P2" s="348" t="n"/>
-      <c r="Q2" s="348" t="n"/>
-      <c r="R2" s="348" t="n"/>
-      <c r="S2" s="348" t="n"/>
-      <c r="T2" s="348" t="n"/>
-      <c r="U2" s="348" t="n"/>
-      <c r="V2" s="348" t="n"/>
-      <c r="W2" s="348" t="n"/>
-      <c r="X2" s="348" t="n"/>
-      <c r="Y2" s="348" t="n"/>
-      <c r="Z2" s="348" t="n"/>
-      <c r="AA2" s="348" t="n"/>
-      <c r="AB2" s="348" t="n"/>
-      <c r="AC2" s="348" t="n"/>
-      <c r="AD2" s="348" t="n"/>
-      <c r="AE2" s="348" t="n"/>
-      <c r="AF2" s="348" t="n"/>
-      <c r="AG2" s="348" t="n"/>
-      <c r="AH2" s="348" t="n"/>
-      <c r="AI2" s="348" t="n"/>
-      <c r="AJ2" s="348" t="n"/>
-      <c r="AK2" s="348" t="n"/>
-      <c r="AL2" s="348" t="n"/>
-      <c r="AM2" s="348" t="n"/>
-      <c r="AN2" s="348" t="n"/>
+      <c r="B2" s="25" t="n"/>
+      <c r="C2" s="25" t="n"/>
+      <c r="D2" s="25" t="n"/>
+      <c r="E2" s="25" t="n"/>
+      <c r="F2" s="25" t="n"/>
+      <c r="G2" s="25" t="n"/>
+      <c r="H2" s="516" t="n"/>
+      <c r="I2" s="442" t="n"/>
+      <c r="J2" s="443" t="n"/>
+      <c r="K2" s="443" t="n"/>
+      <c r="L2" s="443" t="n"/>
+      <c r="M2" s="443" t="n"/>
+      <c r="N2" s="443" t="n"/>
+      <c r="O2" s="443" t="n"/>
+      <c r="P2" s="443" t="n"/>
+      <c r="Q2" s="443" t="n"/>
+      <c r="R2" s="443" t="n"/>
+      <c r="S2" s="443" t="n"/>
+      <c r="T2" s="443" t="n"/>
+      <c r="U2" s="443" t="n"/>
+      <c r="V2" s="443" t="n"/>
+      <c r="W2" s="443" t="n"/>
+      <c r="X2" s="443" t="n"/>
+      <c r="Y2" s="443" t="n"/>
+      <c r="Z2" s="443" t="n"/>
+      <c r="AA2" s="443" t="n"/>
+      <c r="AB2" s="443" t="n"/>
+      <c r="AC2" s="443" t="n"/>
+      <c r="AD2" s="444" t="n"/>
+      <c r="AE2" s="445" t="n"/>
+      <c r="AF2" s="446" t="n"/>
+      <c r="AG2" s="446" t="n"/>
+      <c r="AH2" s="447" t="n"/>
+      <c r="AI2" s="448" t="n"/>
+      <c r="AJ2" s="449" t="n"/>
+      <c r="AK2" s="449" t="n"/>
+      <c r="AL2" s="449" t="n"/>
+      <c r="AM2" s="449" t="n"/>
+      <c r="AN2" s="450" t="n"/>
     </row>
-    <row r="3" ht="18" customHeight="1">
-      <c r="A3" s="348" t="n"/>
-      <c r="B3" s="348" t="n"/>
-      <c r="C3" s="348" t="n"/>
-      <c r="D3" s="348" t="n"/>
-      <c r="E3" s="348" t="n"/>
-      <c r="F3" s="348" t="n"/>
-      <c r="G3" s="348" t="n"/>
-      <c r="H3" s="348" t="n"/>
-      <c r="I3" s="348" t="n"/>
-      <c r="J3" s="348" t="n"/>
-      <c r="K3" s="348" t="n"/>
-      <c r="L3" s="348" t="n"/>
-      <c r="M3" s="348" t="n"/>
-      <c r="N3" s="348" t="n"/>
-      <c r="O3" s="348" t="n"/>
-      <c r="P3" s="348" t="n"/>
-      <c r="Q3" s="348" t="n"/>
-      <c r="R3" s="348" t="n"/>
-      <c r="S3" s="348" t="n"/>
-      <c r="T3" s="348" t="n"/>
-      <c r="U3" s="348" t="n"/>
-      <c r="V3" s="348" t="n"/>
-      <c r="W3" s="348" t="n"/>
-      <c r="X3" s="348" t="n"/>
-      <c r="Y3" s="348" t="n"/>
-      <c r="Z3" s="348" t="n"/>
-      <c r="AA3" s="348" t="n"/>
-      <c r="AB3" s="348" t="n"/>
-      <c r="AC3" s="348" t="n"/>
-      <c r="AD3" s="348" t="n"/>
-      <c r="AE3" s="348" t="n"/>
-      <c r="AF3" s="348" t="n"/>
-      <c r="AG3" s="348" t="n"/>
-      <c r="AH3" s="348" t="n"/>
-      <c r="AI3" s="348" t="n"/>
-      <c r="AJ3" s="348" t="n"/>
-      <c r="AK3" s="348" t="n"/>
-      <c r="AL3" s="348" t="n"/>
-      <c r="AM3" s="348" t="n"/>
-      <c r="AN3" s="348" t="n"/>
+    <row r="3" ht="15" customHeight="1">
+      <c r="A3" s="517" t="n"/>
+      <c r="B3" s="518" t="n"/>
+      <c r="C3" s="518" t="n"/>
+      <c r="D3" s="518" t="n"/>
+      <c r="E3" s="518" t="n"/>
+      <c r="F3" s="518" t="n"/>
+      <c r="G3" s="518" t="n"/>
+      <c r="H3" s="516" t="n"/>
+      <c r="I3" s="442" t="n"/>
+      <c r="J3" s="443" t="n"/>
+      <c r="K3" s="443" t="n"/>
+      <c r="L3" s="443" t="n"/>
+      <c r="M3" s="443" t="n"/>
+      <c r="N3" s="443" t="n"/>
+      <c r="O3" s="443" t="n"/>
+      <c r="P3" s="443" t="n"/>
+      <c r="Q3" s="443" t="n"/>
+      <c r="R3" s="443" t="n"/>
+      <c r="S3" s="443" t="n"/>
+      <c r="T3" s="443" t="n"/>
+      <c r="U3" s="443" t="n"/>
+      <c r="V3" s="443" t="n"/>
+      <c r="W3" s="443" t="n"/>
+      <c r="X3" s="443" t="n"/>
+      <c r="Y3" s="443" t="n"/>
+      <c r="Z3" s="443" t="n"/>
+      <c r="AA3" s="443" t="n"/>
+      <c r="AB3" s="443" t="n"/>
+      <c r="AC3" s="443" t="n"/>
+      <c r="AD3" s="444" t="n"/>
+      <c r="AE3" s="445" t="n"/>
+      <c r="AF3" s="446" t="n"/>
+      <c r="AG3" s="446" t="n"/>
+      <c r="AH3" s="447" t="n"/>
+      <c r="AI3" s="448" t="n"/>
+      <c r="AJ3" s="449" t="n"/>
+      <c r="AK3" s="449" t="n"/>
+      <c r="AL3" s="449" t="n"/>
+      <c r="AM3" s="449" t="n"/>
+      <c r="AN3" s="450" t="n"/>
     </row>
-    <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="394" t="inlineStr">
+    <row r="4" ht="15" customHeight="1">
+      <c r="A4" s="519" t="inlineStr">
         <is>
           <t>Field</t>
         </is>
       </c>
-      <c r="B4" s="394" t="inlineStr">
+      <c r="B4" s="520" t="inlineStr">
         <is>
           <t>Value / Reference</t>
         </is>
       </c>
-      <c r="C4" s="394" t="inlineStr">
+      <c r="C4" s="520" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="D4" s="348" t="n"/>
-      <c r="E4" s="348" t="n"/>
-      <c r="F4" s="348" t="n"/>
-      <c r="G4" s="348" t="n"/>
-      <c r="H4" s="348" t="n"/>
-      <c r="I4" s="348" t="n"/>
-      <c r="J4" s="348" t="n"/>
-      <c r="K4" s="348" t="n"/>
-      <c r="L4" s="348" t="n"/>
-      <c r="M4" s="348" t="n"/>
-      <c r="N4" s="348" t="n"/>
-      <c r="O4" s="348" t="n"/>
-      <c r="P4" s="348" t="n"/>
-      <c r="Q4" s="348" t="n"/>
-      <c r="R4" s="348" t="n"/>
-      <c r="S4" s="348" t="n"/>
-      <c r="T4" s="348" t="n"/>
-      <c r="U4" s="348" t="n"/>
-      <c r="V4" s="348" t="n"/>
-      <c r="W4" s="348" t="n"/>
-      <c r="X4" s="348" t="n"/>
-      <c r="Y4" s="348" t="n"/>
-      <c r="Z4" s="348" t="n"/>
-      <c r="AA4" s="348" t="n"/>
-      <c r="AB4" s="348" t="n"/>
-      <c r="AC4" s="348" t="n"/>
-      <c r="AD4" s="348" t="n"/>
-      <c r="AE4" s="348" t="n"/>
-      <c r="AF4" s="348" t="n"/>
-      <c r="AG4" s="348" t="n"/>
-      <c r="AH4" s="348" t="n"/>
-      <c r="AI4" s="348" t="n"/>
-      <c r="AJ4" s="348" t="n"/>
-      <c r="AK4" s="348" t="n"/>
-      <c r="AL4" s="348" t="n"/>
-      <c r="AM4" s="348" t="n"/>
-      <c r="AN4" s="348" t="n"/>
+      <c r="D4" s="518" t="n"/>
+      <c r="E4" s="518" t="n"/>
+      <c r="F4" s="518" t="n"/>
+      <c r="G4" s="518" t="n"/>
+      <c r="H4" s="516" t="n"/>
+      <c r="I4" s="451" t="n"/>
+      <c r="J4" s="452" t="n"/>
+      <c r="K4" s="452" t="n"/>
+      <c r="L4" s="452" t="n"/>
+      <c r="M4" s="452" t="n"/>
+      <c r="N4" s="452" t="n"/>
+      <c r="O4" s="452" t="n"/>
+      <c r="P4" s="452" t="n"/>
+      <c r="Q4" s="452" t="n"/>
+      <c r="R4" s="452" t="n"/>
+      <c r="S4" s="452" t="n"/>
+      <c r="T4" s="452" t="n"/>
+      <c r="U4" s="452" t="n"/>
+      <c r="V4" s="452" t="n"/>
+      <c r="W4" s="452" t="n"/>
+      <c r="X4" s="452" t="n"/>
+      <c r="Y4" s="452" t="n"/>
+      <c r="Z4" s="452" t="n"/>
+      <c r="AA4" s="452" t="n"/>
+      <c r="AB4" s="452" t="n"/>
+      <c r="AC4" s="452" t="n"/>
+      <c r="AD4" s="453" t="n"/>
+      <c r="AE4" s="445" t="n"/>
+      <c r="AF4" s="446" t="n"/>
+      <c r="AG4" s="446" t="n"/>
+      <c r="AH4" s="447" t="n"/>
+      <c r="AI4" s="448" t="n"/>
+      <c r="AJ4" s="449" t="n"/>
+      <c r="AK4" s="449" t="n"/>
+      <c r="AL4" s="449" t="n"/>
+      <c r="AM4" s="449" t="n"/>
+      <c r="AN4" s="450" t="n"/>
     </row>
-    <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="395" t="inlineStr">
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" s="522" t="inlineStr">
         <is>
           <t>Source of Truth</t>
         </is>
       </c>
-      <c r="B5" s="396" t="inlineStr">
+      <c r="B5" s="523" t="inlineStr">
         <is>
           <t>M365 evidence / shared workbook</t>
         </is>
       </c>
-      <c r="C5" s="396" t="inlineStr">
+      <c r="C5" s="523" t="inlineStr">
         <is>
           <t>Do not duplicate ERP/M365/ANNEX master data.</t>
         </is>
       </c>
-      <c r="D5" s="348" t="n"/>
-      <c r="E5" s="348" t="n"/>
-      <c r="F5" s="348" t="n"/>
-      <c r="G5" s="348" t="n"/>
-      <c r="H5" s="348" t="n"/>
-      <c r="I5" s="348" t="n"/>
-      <c r="J5" s="348" t="n"/>
-      <c r="K5" s="348" t="n"/>
-      <c r="L5" s="348" t="n"/>
-      <c r="M5" s="348" t="n"/>
-      <c r="N5" s="348" t="n"/>
-      <c r="O5" s="348" t="n"/>
-      <c r="P5" s="348" t="n"/>
-      <c r="Q5" s="348" t="n"/>
-      <c r="R5" s="348" t="n"/>
-      <c r="S5" s="348" t="n"/>
-      <c r="T5" s="348" t="n"/>
-      <c r="U5" s="348" t="n"/>
-      <c r="V5" s="348" t="n"/>
-      <c r="W5" s="348" t="n"/>
-      <c r="X5" s="348" t="n"/>
-      <c r="Y5" s="348" t="n"/>
-      <c r="Z5" s="348" t="n"/>
-      <c r="AA5" s="348" t="n"/>
-      <c r="AB5" s="348" t="n"/>
-      <c r="AC5" s="348" t="n"/>
-      <c r="AD5" s="348" t="n"/>
-      <c r="AE5" s="348" t="n"/>
-      <c r="AF5" s="348" t="n"/>
-      <c r="AG5" s="348" t="n"/>
-      <c r="AH5" s="348" t="n"/>
-      <c r="AI5" s="348" t="n"/>
-      <c r="AJ5" s="348" t="n"/>
-      <c r="AK5" s="348" t="n"/>
-      <c r="AL5" s="348" t="n"/>
-      <c r="AM5" s="348" t="n"/>
-      <c r="AN5" s="348" t="n"/>
+      <c r="D5" s="541" t="n"/>
+      <c r="E5" s="541" t="n"/>
+      <c r="F5" s="541" t="n"/>
+      <c r="G5" s="541" t="n"/>
+      <c r="H5" s="542" t="n"/>
+      <c r="I5" s="457" t="n"/>
+      <c r="J5" s="458" t="n"/>
+      <c r="K5" s="458" t="n"/>
+      <c r="L5" s="458" t="n"/>
+      <c r="M5" s="458" t="n"/>
+      <c r="N5" s="458" t="n"/>
+      <c r="O5" s="458" t="n"/>
+      <c r="P5" s="458" t="n"/>
+      <c r="Q5" s="458" t="n"/>
+      <c r="R5" s="458" t="n"/>
+      <c r="S5" s="458" t="n"/>
+      <c r="T5" s="458" t="n"/>
+      <c r="U5" s="458" t="n"/>
+      <c r="V5" s="458" t="n"/>
+      <c r="W5" s="458" t="n"/>
+      <c r="X5" s="458" t="n"/>
+      <c r="Y5" s="458" t="n"/>
+      <c r="Z5" s="458" t="n"/>
+      <c r="AA5" s="458" t="n"/>
+      <c r="AB5" s="458" t="n"/>
+      <c r="AC5" s="458" t="n"/>
+      <c r="AD5" s="459" t="n"/>
+      <c r="AE5" s="460" t="n"/>
+      <c r="AF5" s="461" t="n"/>
+      <c r="AG5" s="461" t="n"/>
+      <c r="AH5" s="462" t="n"/>
+      <c r="AI5" s="463" t="n"/>
+      <c r="AJ5" s="464" t="n"/>
+      <c r="AK5" s="464" t="n"/>
+      <c r="AL5" s="464" t="n"/>
+      <c r="AM5" s="464" t="n"/>
+      <c r="AN5" s="465" t="n"/>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="395" t="inlineStr">
+      <c r="A6" s="525" t="inlineStr">
         <is>
           <t>Cross-Reference Boundary</t>
         </is>
       </c>
-      <c r="B6" s="396" t="inlineStr">
+      <c r="B6" s="526" t="inlineStr">
         <is>
           <t>This form does not replace SOP-702; it records the evidence, data or decision required by that SOP.
 Detailed task execution belongs in WI-716; this form captures results, checks, decisions or exceptions only.
@@ -8935,7 +9845,7 @@
 System-of-record / source-of-truth boundary: M365 evidence / shared workbook. If the master data already live there, reference or import them; do not re-key without need.</t>
         </is>
       </c>
-      <c r="C6" s="396" t="inlineStr">
+      <c r="C6" s="527" t="inlineStr">
         <is>
           <t>This form does not replace SOP-702; it records the evidence, data or decision required by that SOP.
 Detailed task execution belongs in WI-716; this form captures results, checks, decisions or exceptions only.
@@ -8943,451 +9853,451 @@
 System-of-record / source-of-truth boundary: M365 evidence / shared workbook. If the master data already live there, reference or import them; do not re-key without need.</t>
         </is>
       </c>
-      <c r="D6" s="348" t="n"/>
-      <c r="E6" s="348" t="n"/>
-      <c r="F6" s="348" t="n"/>
-      <c r="G6" s="348" t="n"/>
-      <c r="H6" s="348" t="n"/>
-      <c r="I6" s="348" t="n"/>
-      <c r="J6" s="348" t="n"/>
-      <c r="K6" s="348" t="n"/>
-      <c r="L6" s="348" t="n"/>
-      <c r="M6" s="348" t="n"/>
-      <c r="N6" s="348" t="n"/>
-      <c r="O6" s="348" t="n"/>
-      <c r="P6" s="348" t="n"/>
-      <c r="Q6" s="348" t="n"/>
-      <c r="R6" s="348" t="n"/>
-      <c r="S6" s="348" t="n"/>
-      <c r="T6" s="348" t="n"/>
-      <c r="U6" s="348" t="n"/>
-      <c r="V6" s="348" t="n"/>
-      <c r="W6" s="348" t="n"/>
-      <c r="X6" s="348" t="n"/>
-      <c r="Y6" s="348" t="n"/>
-      <c r="Z6" s="348" t="n"/>
-      <c r="AA6" s="348" t="n"/>
-      <c r="AB6" s="348" t="n"/>
-      <c r="AC6" s="348" t="n"/>
-      <c r="AD6" s="348" t="n"/>
-      <c r="AE6" s="348" t="n"/>
-      <c r="AF6" s="348" t="n"/>
-      <c r="AG6" s="348" t="n"/>
-      <c r="AH6" s="348" t="n"/>
-      <c r="AI6" s="348" t="n"/>
-      <c r="AJ6" s="348" t="n"/>
-      <c r="AK6" s="348" t="n"/>
-      <c r="AL6" s="348" t="n"/>
-      <c r="AM6" s="348" t="n"/>
-      <c r="AN6" s="348" t="n"/>
+      <c r="D6" s="471" t="n"/>
+      <c r="E6" s="471" t="n"/>
+      <c r="F6" s="471" t="n"/>
+      <c r="G6" s="471" t="n"/>
+      <c r="H6" s="471" t="n"/>
+      <c r="I6" s="471" t="n"/>
+      <c r="J6" s="471" t="n"/>
+      <c r="K6" s="471" t="n"/>
+      <c r="L6" s="471" t="n"/>
+      <c r="M6" s="471" t="n"/>
+      <c r="N6" s="471" t="n"/>
+      <c r="O6" s="471" t="n"/>
+      <c r="P6" s="471" t="n"/>
+      <c r="Q6" s="471" t="n"/>
+      <c r="R6" s="471" t="n"/>
+      <c r="S6" s="471" t="n"/>
+      <c r="T6" s="471" t="n"/>
+      <c r="U6" s="471" t="n"/>
+      <c r="V6" s="471" t="n"/>
+      <c r="W6" s="471" t="n"/>
+      <c r="X6" s="471" t="n"/>
+      <c r="Y6" s="471" t="n"/>
+      <c r="Z6" s="471" t="n"/>
+      <c r="AA6" s="471" t="n"/>
+      <c r="AB6" s="471" t="n"/>
+      <c r="AC6" s="471" t="n"/>
+      <c r="AD6" s="471" t="n"/>
+      <c r="AE6" s="471" t="n"/>
+      <c r="AF6" s="471" t="n"/>
+      <c r="AG6" s="471" t="n"/>
+      <c r="AH6" s="471" t="n"/>
+      <c r="AI6" s="471" t="n"/>
+      <c r="AJ6" s="471" t="n"/>
+      <c r="AK6" s="471" t="n"/>
+      <c r="AL6" s="471" t="n"/>
+      <c r="AM6" s="471" t="n"/>
+      <c r="AN6" s="503" t="n"/>
     </row>
     <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="395" t="inlineStr">
+      <c r="A7" s="528" t="inlineStr">
         <is>
           <t>SOP-702</t>
         </is>
       </c>
-      <c r="B7" s="396" t="inlineStr">
+      <c r="B7" s="529" t="inlineStr">
         <is>
           <t>SOP-702 — Kiểm soát nhiễm bẩn, xác nhận độ sạch và tuyến đóng gói sạch | HESEM QMS</t>
         </is>
       </c>
-      <c r="C7" s="396" t="inlineStr">
+      <c r="C7" s="530" t="inlineStr">
         <is>
           <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/01-SOPs/07-SOP-700/sop-702-contamination-control-and-cleanliness.html</t>
         </is>
       </c>
-      <c r="D7" s="348" t="n"/>
-      <c r="E7" s="348" t="n"/>
-      <c r="F7" s="348" t="n"/>
-      <c r="G7" s="348" t="n"/>
-      <c r="H7" s="348" t="n"/>
-      <c r="I7" s="348" t="n"/>
-      <c r="J7" s="348" t="n"/>
-      <c r="K7" s="348" t="n"/>
-      <c r="L7" s="348" t="n"/>
-      <c r="M7" s="348" t="n"/>
-      <c r="N7" s="348" t="n"/>
-      <c r="O7" s="348" t="n"/>
-      <c r="P7" s="348" t="n"/>
-      <c r="Q7" s="348" t="n"/>
-      <c r="R7" s="348" t="n"/>
-      <c r="S7" s="348" t="n"/>
-      <c r="T7" s="348" t="n"/>
-      <c r="U7" s="348" t="n"/>
-      <c r="V7" s="348" t="n"/>
-      <c r="W7" s="348" t="n"/>
-      <c r="X7" s="348" t="n"/>
-      <c r="Y7" s="348" t="n"/>
-      <c r="Z7" s="348" t="n"/>
-      <c r="AA7" s="348" t="n"/>
-      <c r="AB7" s="348" t="n"/>
-      <c r="AC7" s="348" t="n"/>
-      <c r="AD7" s="348" t="n"/>
-      <c r="AE7" s="348" t="n"/>
-      <c r="AF7" s="348" t="n"/>
-      <c r="AG7" s="348" t="n"/>
-      <c r="AH7" s="348" t="n"/>
-      <c r="AI7" s="348" t="n"/>
-      <c r="AJ7" s="348" t="n"/>
-      <c r="AK7" s="348" t="n"/>
-      <c r="AL7" s="348" t="n"/>
-      <c r="AM7" s="348" t="n"/>
-      <c r="AN7" s="348" t="n"/>
+      <c r="D7" s="344" t="n"/>
+      <c r="E7" s="344" t="n"/>
+      <c r="F7" s="344" t="n"/>
+      <c r="G7" s="344" t="n"/>
+      <c r="H7" s="344" t="n"/>
+      <c r="I7" s="344" t="n"/>
+      <c r="J7" s="344" t="n"/>
+      <c r="K7" s="344" t="n"/>
+      <c r="L7" s="344" t="n"/>
+      <c r="M7" s="344" t="n"/>
+      <c r="N7" s="344" t="n"/>
+      <c r="O7" s="344" t="n"/>
+      <c r="P7" s="344" t="n"/>
+      <c r="Q7" s="344" t="n"/>
+      <c r="R7" s="344" t="n"/>
+      <c r="S7" s="344" t="n"/>
+      <c r="T7" s="344" t="n"/>
+      <c r="U7" s="344" t="n"/>
+      <c r="V7" s="344" t="n"/>
+      <c r="W7" s="344" t="n"/>
+      <c r="X7" s="344" t="n"/>
+      <c r="Y7" s="344" t="n"/>
+      <c r="Z7" s="344" t="n"/>
+      <c r="AA7" s="344" t="n"/>
+      <c r="AB7" s="344" t="n"/>
+      <c r="AC7" s="344" t="n"/>
+      <c r="AD7" s="344" t="n"/>
+      <c r="AE7" s="344" t="n"/>
+      <c r="AF7" s="344" t="n"/>
+      <c r="AG7" s="344" t="n"/>
+      <c r="AH7" s="344" t="n"/>
+      <c r="AI7" s="344" t="n"/>
+      <c r="AJ7" s="344" t="n"/>
+      <c r="AK7" s="344" t="n"/>
+      <c r="AL7" s="344" t="n"/>
+      <c r="AM7" s="344" t="n"/>
+      <c r="AN7" s="531" t="n"/>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="397" t="inlineStr">
+      <c r="A8" s="532" t="inlineStr">
         <is>
           <t>WI-716</t>
         </is>
       </c>
-      <c r="B8" s="398" t="inlineStr">
+      <c r="B8" s="533" t="inlineStr">
         <is>
           <t>WI-716 — Lắp sạch, tương thích chân không, bagging và bảo quản cho Job đặc biệt</t>
         </is>
       </c>
-      <c r="C8" s="398" t="inlineStr">
+      <c r="C8" s="534" t="inlineStr">
         <is>
           <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/02-Work-Instructions/07-WI-700/wi-716-vacuum-compatible-clean-build-and-bagging.html</t>
         </is>
       </c>
-      <c r="D8" s="399" t="n"/>
-      <c r="E8" s="399" t="n"/>
-      <c r="F8" s="399" t="n"/>
-      <c r="G8" s="399" t="n"/>
-      <c r="H8" s="399" t="n"/>
-      <c r="I8" s="399" t="n"/>
-      <c r="J8" s="399" t="n"/>
-      <c r="K8" s="399" t="n"/>
-      <c r="L8" s="399" t="n"/>
-      <c r="M8" s="399" t="n"/>
-      <c r="N8" s="399" t="n"/>
-      <c r="O8" s="399" t="n"/>
-      <c r="P8" s="399" t="n"/>
-      <c r="Q8" s="399" t="n"/>
-      <c r="R8" s="399" t="n"/>
-      <c r="S8" s="399" t="n"/>
-      <c r="T8" s="399" t="n"/>
-      <c r="U8" s="399" t="n"/>
-      <c r="V8" s="399" t="n"/>
-      <c r="W8" s="399" t="n"/>
-      <c r="X8" s="399" t="n"/>
-      <c r="Y8" s="399" t="n"/>
-      <c r="Z8" s="399" t="n"/>
-      <c r="AA8" s="399" t="n"/>
-      <c r="AB8" s="399" t="n"/>
-      <c r="AC8" s="399" t="n"/>
-      <c r="AD8" s="399" t="n"/>
-      <c r="AE8" s="399" t="n"/>
-      <c r="AF8" s="399" t="n"/>
-      <c r="AG8" s="399" t="n"/>
-      <c r="AH8" s="399" t="n"/>
-      <c r="AI8" s="399" t="n"/>
-      <c r="AJ8" s="399" t="n"/>
-      <c r="AK8" s="399" t="n"/>
-      <c r="AL8" s="399" t="n"/>
-      <c r="AM8" s="399" t="n"/>
-      <c r="AN8" s="399" t="n"/>
+      <c r="D8" s="356" t="n"/>
+      <c r="E8" s="356" t="n"/>
+      <c r="F8" s="356" t="n"/>
+      <c r="G8" s="356" t="n"/>
+      <c r="H8" s="356" t="n"/>
+      <c r="I8" s="356" t="n"/>
+      <c r="J8" s="356" t="n"/>
+      <c r="K8" s="356" t="n"/>
+      <c r="L8" s="356" t="n"/>
+      <c r="M8" s="356" t="n"/>
+      <c r="N8" s="356" t="n"/>
+      <c r="O8" s="356" t="n"/>
+      <c r="P8" s="356" t="n"/>
+      <c r="Q8" s="356" t="n"/>
+      <c r="R8" s="356" t="n"/>
+      <c r="S8" s="356" t="n"/>
+      <c r="T8" s="356" t="n"/>
+      <c r="U8" s="356" t="n"/>
+      <c r="V8" s="356" t="n"/>
+      <c r="W8" s="356" t="n"/>
+      <c r="X8" s="356" t="n"/>
+      <c r="Y8" s="356" t="n"/>
+      <c r="Z8" s="356" t="n"/>
+      <c r="AA8" s="356" t="n"/>
+      <c r="AB8" s="356" t="n"/>
+      <c r="AC8" s="356" t="n"/>
+      <c r="AD8" s="356" t="n"/>
+      <c r="AE8" s="356" t="n"/>
+      <c r="AF8" s="356" t="n"/>
+      <c r="AG8" s="356" t="n"/>
+      <c r="AH8" s="356" t="n"/>
+      <c r="AI8" s="356" t="n"/>
+      <c r="AJ8" s="356" t="n"/>
+      <c r="AK8" s="356" t="n"/>
+      <c r="AL8" s="356" t="n"/>
+      <c r="AM8" s="356" t="n"/>
+      <c r="AN8" s="535" t="n"/>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="397" t="inlineStr">
+      <c r="A9" s="532" t="inlineStr">
         <is>
           <t>ANNEX-QA-007</t>
         </is>
       </c>
-      <c r="B9" s="398" t="inlineStr">
+      <c r="B9" s="533" t="inlineStr">
         <is>
           <t>ANNEX-QA-007 — Chuẩn bề mặt, độ sạch, tương thích chân không, rò rỉ và xử lý đặc biệt</t>
         </is>
       </c>
-      <c r="C9" s="398" t="inlineStr">
+      <c r="C9" s="534" t="inlineStr">
         <is>
           <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/03-Reference/02-ANNEX-Standards/annex-qa-007-surface-finish-vacuum-compatibility.html</t>
         </is>
       </c>
-      <c r="D9" s="399" t="n"/>
-      <c r="E9" s="399" t="n"/>
-      <c r="F9" s="399" t="n"/>
-      <c r="G9" s="399" t="n"/>
-      <c r="H9" s="399" t="n"/>
-      <c r="I9" s="399" t="n"/>
-      <c r="J9" s="399" t="n"/>
-      <c r="K9" s="399" t="n"/>
-      <c r="L9" s="399" t="n"/>
-      <c r="M9" s="399" t="n"/>
-      <c r="N9" s="399" t="n"/>
-      <c r="O9" s="399" t="n"/>
-      <c r="P9" s="399" t="n"/>
-      <c r="Q9" s="399" t="n"/>
-      <c r="R9" s="399" t="n"/>
-      <c r="S9" s="399" t="n"/>
-      <c r="T9" s="399" t="n"/>
-      <c r="U9" s="399" t="n"/>
-      <c r="V9" s="399" t="n"/>
-      <c r="W9" s="399" t="n"/>
-      <c r="X9" s="399" t="n"/>
-      <c r="Y9" s="399" t="n"/>
-      <c r="Z9" s="399" t="n"/>
-      <c r="AA9" s="399" t="n"/>
-      <c r="AB9" s="399" t="n"/>
-      <c r="AC9" s="399" t="n"/>
-      <c r="AD9" s="399" t="n"/>
-      <c r="AE9" s="399" t="n"/>
-      <c r="AF9" s="399" t="n"/>
-      <c r="AG9" s="399" t="n"/>
-      <c r="AH9" s="399" t="n"/>
-      <c r="AI9" s="399" t="n"/>
-      <c r="AJ9" s="399" t="n"/>
-      <c r="AK9" s="399" t="n"/>
-      <c r="AL9" s="399" t="n"/>
-      <c r="AM9" s="399" t="n"/>
-      <c r="AN9" s="399" t="n"/>
+      <c r="D9" s="356" t="n"/>
+      <c r="E9" s="356" t="n"/>
+      <c r="F9" s="356" t="n"/>
+      <c r="G9" s="356" t="n"/>
+      <c r="H9" s="356" t="n"/>
+      <c r="I9" s="356" t="n"/>
+      <c r="J9" s="356" t="n"/>
+      <c r="K9" s="356" t="n"/>
+      <c r="L9" s="356" t="n"/>
+      <c r="M9" s="356" t="n"/>
+      <c r="N9" s="356" t="n"/>
+      <c r="O9" s="356" t="n"/>
+      <c r="P9" s="356" t="n"/>
+      <c r="Q9" s="356" t="n"/>
+      <c r="R9" s="356" t="n"/>
+      <c r="S9" s="356" t="n"/>
+      <c r="T9" s="356" t="n"/>
+      <c r="U9" s="356" t="n"/>
+      <c r="V9" s="356" t="n"/>
+      <c r="W9" s="356" t="n"/>
+      <c r="X9" s="356" t="n"/>
+      <c r="Y9" s="356" t="n"/>
+      <c r="Z9" s="356" t="n"/>
+      <c r="AA9" s="356" t="n"/>
+      <c r="AB9" s="356" t="n"/>
+      <c r="AC9" s="356" t="n"/>
+      <c r="AD9" s="356" t="n"/>
+      <c r="AE9" s="356" t="n"/>
+      <c r="AF9" s="356" t="n"/>
+      <c r="AG9" s="356" t="n"/>
+      <c r="AH9" s="356" t="n"/>
+      <c r="AI9" s="356" t="n"/>
+      <c r="AJ9" s="356" t="n"/>
+      <c r="AK9" s="356" t="n"/>
+      <c r="AL9" s="356" t="n"/>
+      <c r="AM9" s="356" t="n"/>
+      <c r="AN9" s="535" t="n"/>
     </row>
     <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="397" t="inlineStr">
+      <c r="A10" s="532" t="inlineStr">
         <is>
           <t>ANNEX-WHS-001</t>
         </is>
       </c>
-      <c r="B10" s="398" t="inlineStr">
+      <c r="B10" s="533" t="inlineStr">
         <is>
           <t>ANNEX-WHS-001 — Quy cách đóng gói, nhãn, bảo quản và bằng chứng gói hàng</t>
         </is>
       </c>
-      <c r="C10" s="398" t="inlineStr">
+      <c r="C10" s="534" t="inlineStr">
         <is>
           <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/03-Reference/02-ANNEX-Standards/annex-whs-001-packaging-labeling-spec.html</t>
         </is>
       </c>
-      <c r="D10" s="399" t="n"/>
-      <c r="E10" s="399" t="n"/>
-      <c r="F10" s="399" t="n"/>
-      <c r="G10" s="399" t="n"/>
-      <c r="H10" s="399" t="n"/>
-      <c r="I10" s="399" t="n"/>
-      <c r="J10" s="399" t="n"/>
-      <c r="K10" s="399" t="n"/>
-      <c r="L10" s="399" t="n"/>
-      <c r="M10" s="399" t="n"/>
-      <c r="N10" s="399" t="n"/>
-      <c r="O10" s="399" t="n"/>
-      <c r="P10" s="399" t="n"/>
-      <c r="Q10" s="399" t="n"/>
-      <c r="R10" s="399" t="n"/>
-      <c r="S10" s="399" t="n"/>
-      <c r="T10" s="399" t="n"/>
-      <c r="U10" s="399" t="n"/>
-      <c r="V10" s="399" t="n"/>
-      <c r="W10" s="399" t="n"/>
-      <c r="X10" s="399" t="n"/>
-      <c r="Y10" s="399" t="n"/>
-      <c r="Z10" s="399" t="n"/>
-      <c r="AA10" s="399" t="n"/>
-      <c r="AB10" s="399" t="n"/>
-      <c r="AC10" s="399" t="n"/>
-      <c r="AD10" s="399" t="n"/>
-      <c r="AE10" s="399" t="n"/>
-      <c r="AF10" s="399" t="n"/>
-      <c r="AG10" s="399" t="n"/>
-      <c r="AH10" s="399" t="n"/>
-      <c r="AI10" s="399" t="n"/>
-      <c r="AJ10" s="399" t="n"/>
-      <c r="AK10" s="399" t="n"/>
-      <c r="AL10" s="399" t="n"/>
-      <c r="AM10" s="399" t="n"/>
-      <c r="AN10" s="399" t="n"/>
+      <c r="D10" s="356" t="n"/>
+      <c r="E10" s="356" t="n"/>
+      <c r="F10" s="356" t="n"/>
+      <c r="G10" s="356" t="n"/>
+      <c r="H10" s="356" t="n"/>
+      <c r="I10" s="356" t="n"/>
+      <c r="J10" s="356" t="n"/>
+      <c r="K10" s="356" t="n"/>
+      <c r="L10" s="356" t="n"/>
+      <c r="M10" s="356" t="n"/>
+      <c r="N10" s="356" t="n"/>
+      <c r="O10" s="356" t="n"/>
+      <c r="P10" s="356" t="n"/>
+      <c r="Q10" s="356" t="n"/>
+      <c r="R10" s="356" t="n"/>
+      <c r="S10" s="356" t="n"/>
+      <c r="T10" s="356" t="n"/>
+      <c r="U10" s="356" t="n"/>
+      <c r="V10" s="356" t="n"/>
+      <c r="W10" s="356" t="n"/>
+      <c r="X10" s="356" t="n"/>
+      <c r="Y10" s="356" t="n"/>
+      <c r="Z10" s="356" t="n"/>
+      <c r="AA10" s="356" t="n"/>
+      <c r="AB10" s="356" t="n"/>
+      <c r="AC10" s="356" t="n"/>
+      <c r="AD10" s="356" t="n"/>
+      <c r="AE10" s="356" t="n"/>
+      <c r="AF10" s="356" t="n"/>
+      <c r="AG10" s="356" t="n"/>
+      <c r="AH10" s="356" t="n"/>
+      <c r="AI10" s="356" t="n"/>
+      <c r="AJ10" s="356" t="n"/>
+      <c r="AK10" s="356" t="n"/>
+      <c r="AL10" s="356" t="n"/>
+      <c r="AM10" s="356" t="n"/>
+      <c r="AN10" s="535" t="n"/>
     </row>
     <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="397" t="inlineStr">
+      <c r="A11" s="532" t="inlineStr">
         <is>
           <t>Open When</t>
         </is>
       </c>
-      <c r="B11" s="398" t="inlineStr">
+      <c r="B11" s="533" t="inlineStr">
         <is>
           <t>Open before the controlled activity starts or before the release decision is taken. Do not populate it retrospectively after execution has already moved forward.</t>
         </is>
       </c>
-      <c r="C11" s="398" t="inlineStr">
+      <c r="C11" s="534" t="inlineStr">
         <is>
           <t>Operational trigger</t>
         </is>
       </c>
-      <c r="D11" s="399" t="n"/>
-      <c r="E11" s="399" t="n"/>
-      <c r="F11" s="399" t="n"/>
-      <c r="G11" s="399" t="n"/>
-      <c r="H11" s="399" t="n"/>
-      <c r="I11" s="399" t="n"/>
-      <c r="J11" s="399" t="n"/>
-      <c r="K11" s="399" t="n"/>
-      <c r="L11" s="399" t="n"/>
-      <c r="M11" s="399" t="n"/>
-      <c r="N11" s="399" t="n"/>
-      <c r="O11" s="399" t="n"/>
-      <c r="P11" s="399" t="n"/>
-      <c r="Q11" s="399" t="n"/>
-      <c r="R11" s="399" t="n"/>
-      <c r="S11" s="399" t="n"/>
-      <c r="T11" s="399" t="n"/>
-      <c r="U11" s="399" t="n"/>
-      <c r="V11" s="399" t="n"/>
-      <c r="W11" s="399" t="n"/>
-      <c r="X11" s="399" t="n"/>
-      <c r="Y11" s="399" t="n"/>
-      <c r="Z11" s="399" t="n"/>
-      <c r="AA11" s="399" t="n"/>
-      <c r="AB11" s="399" t="n"/>
-      <c r="AC11" s="399" t="n"/>
-      <c r="AD11" s="399" t="n"/>
-      <c r="AE11" s="399" t="n"/>
-      <c r="AF11" s="399" t="n"/>
-      <c r="AG11" s="399" t="n"/>
-      <c r="AH11" s="399" t="n"/>
-      <c r="AI11" s="399" t="n"/>
-      <c r="AJ11" s="399" t="n"/>
-      <c r="AK11" s="399" t="n"/>
-      <c r="AL11" s="399" t="n"/>
-      <c r="AM11" s="399" t="n"/>
-      <c r="AN11" s="399" t="n"/>
+      <c r="D11" s="356" t="n"/>
+      <c r="E11" s="356" t="n"/>
+      <c r="F11" s="356" t="n"/>
+      <c r="G11" s="356" t="n"/>
+      <c r="H11" s="356" t="n"/>
+      <c r="I11" s="356" t="n"/>
+      <c r="J11" s="356" t="n"/>
+      <c r="K11" s="356" t="n"/>
+      <c r="L11" s="356" t="n"/>
+      <c r="M11" s="356" t="n"/>
+      <c r="N11" s="356" t="n"/>
+      <c r="O11" s="356" t="n"/>
+      <c r="P11" s="356" t="n"/>
+      <c r="Q11" s="356" t="n"/>
+      <c r="R11" s="356" t="n"/>
+      <c r="S11" s="356" t="n"/>
+      <c r="T11" s="356" t="n"/>
+      <c r="U11" s="356" t="n"/>
+      <c r="V11" s="356" t="n"/>
+      <c r="W11" s="356" t="n"/>
+      <c r="X11" s="356" t="n"/>
+      <c r="Y11" s="356" t="n"/>
+      <c r="Z11" s="356" t="n"/>
+      <c r="AA11" s="356" t="n"/>
+      <c r="AB11" s="356" t="n"/>
+      <c r="AC11" s="356" t="n"/>
+      <c r="AD11" s="356" t="n"/>
+      <c r="AE11" s="356" t="n"/>
+      <c r="AF11" s="356" t="n"/>
+      <c r="AG11" s="356" t="n"/>
+      <c r="AH11" s="356" t="n"/>
+      <c r="AI11" s="356" t="n"/>
+      <c r="AJ11" s="356" t="n"/>
+      <c r="AK11" s="356" t="n"/>
+      <c r="AL11" s="356" t="n"/>
+      <c r="AM11" s="356" t="n"/>
+      <c r="AN11" s="535" t="n"/>
     </row>
     <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="397" t="inlineStr">
+      <c r="A12" s="532" t="inlineStr">
         <is>
           <t>Close When</t>
         </is>
       </c>
-      <c r="B12" s="398" t="inlineStr">
+      <c r="B12" s="533" t="inlineStr">
         <is>
           <t>Close only after the final gate disposition, result or release status is recorded, all conditions are assigned to an owner, and the evidence package reference is complete.</t>
         </is>
       </c>
-      <c r="C12" s="398" t="inlineStr">
+      <c r="C12" s="534" t="inlineStr">
         <is>
           <t>Release / closure rule</t>
         </is>
       </c>
-      <c r="D12" s="399" t="n"/>
-      <c r="E12" s="399" t="n"/>
-      <c r="F12" s="399" t="n"/>
-      <c r="G12" s="399" t="n"/>
-      <c r="H12" s="399" t="n"/>
-      <c r="I12" s="399" t="n"/>
-      <c r="J12" s="399" t="n"/>
-      <c r="K12" s="399" t="n"/>
-      <c r="L12" s="399" t="n"/>
-      <c r="M12" s="399" t="n"/>
-      <c r="N12" s="399" t="n"/>
-      <c r="O12" s="399" t="n"/>
-      <c r="P12" s="399" t="n"/>
-      <c r="Q12" s="399" t="n"/>
-      <c r="R12" s="399" t="n"/>
-      <c r="S12" s="399" t="n"/>
-      <c r="T12" s="399" t="n"/>
-      <c r="U12" s="399" t="n"/>
-      <c r="V12" s="399" t="n"/>
-      <c r="W12" s="399" t="n"/>
-      <c r="X12" s="399" t="n"/>
-      <c r="Y12" s="399" t="n"/>
-      <c r="Z12" s="399" t="n"/>
-      <c r="AA12" s="399" t="n"/>
-      <c r="AB12" s="399" t="n"/>
-      <c r="AC12" s="399" t="n"/>
-      <c r="AD12" s="399" t="n"/>
-      <c r="AE12" s="399" t="n"/>
-      <c r="AF12" s="399" t="n"/>
-      <c r="AG12" s="399" t="n"/>
-      <c r="AH12" s="399" t="n"/>
-      <c r="AI12" s="399" t="n"/>
-      <c r="AJ12" s="399" t="n"/>
-      <c r="AK12" s="399" t="n"/>
-      <c r="AL12" s="399" t="n"/>
-      <c r="AM12" s="399" t="n"/>
-      <c r="AN12" s="399" t="n"/>
+      <c r="D12" s="356" t="n"/>
+      <c r="E12" s="356" t="n"/>
+      <c r="F12" s="356" t="n"/>
+      <c r="G12" s="356" t="n"/>
+      <c r="H12" s="356" t="n"/>
+      <c r="I12" s="356" t="n"/>
+      <c r="J12" s="356" t="n"/>
+      <c r="K12" s="356" t="n"/>
+      <c r="L12" s="356" t="n"/>
+      <c r="M12" s="356" t="n"/>
+      <c r="N12" s="356" t="n"/>
+      <c r="O12" s="356" t="n"/>
+      <c r="P12" s="356" t="n"/>
+      <c r="Q12" s="356" t="n"/>
+      <c r="R12" s="356" t="n"/>
+      <c r="S12" s="356" t="n"/>
+      <c r="T12" s="356" t="n"/>
+      <c r="U12" s="356" t="n"/>
+      <c r="V12" s="356" t="n"/>
+      <c r="W12" s="356" t="n"/>
+      <c r="X12" s="356" t="n"/>
+      <c r="Y12" s="356" t="n"/>
+      <c r="Z12" s="356" t="n"/>
+      <c r="AA12" s="356" t="n"/>
+      <c r="AB12" s="356" t="n"/>
+      <c r="AC12" s="356" t="n"/>
+      <c r="AD12" s="356" t="n"/>
+      <c r="AE12" s="356" t="n"/>
+      <c r="AF12" s="356" t="n"/>
+      <c r="AG12" s="356" t="n"/>
+      <c r="AH12" s="356" t="n"/>
+      <c r="AI12" s="356" t="n"/>
+      <c r="AJ12" s="356" t="n"/>
+      <c r="AK12" s="356" t="n"/>
+      <c r="AL12" s="356" t="n"/>
+      <c r="AM12" s="356" t="n"/>
+      <c r="AN12" s="535" t="n"/>
     </row>
     <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="397" t="n"/>
-      <c r="B13" s="398" t="n"/>
-      <c r="C13" s="398" t="n"/>
-      <c r="D13" s="399" t="n"/>
-      <c r="E13" s="399" t="n"/>
-      <c r="F13" s="399" t="n"/>
-      <c r="G13" s="399" t="n"/>
-      <c r="H13" s="399" t="n"/>
-      <c r="I13" s="399" t="n"/>
-      <c r="J13" s="399" t="n"/>
-      <c r="K13" s="399" t="n"/>
-      <c r="L13" s="399" t="n"/>
-      <c r="M13" s="399" t="n"/>
-      <c r="N13" s="399" t="n"/>
-      <c r="O13" s="399" t="n"/>
-      <c r="P13" s="399" t="n"/>
-      <c r="Q13" s="399" t="n"/>
-      <c r="R13" s="399" t="n"/>
-      <c r="S13" s="399" t="n"/>
-      <c r="T13" s="399" t="n"/>
-      <c r="U13" s="399" t="n"/>
-      <c r="V13" s="399" t="n"/>
-      <c r="W13" s="399" t="n"/>
-      <c r="X13" s="399" t="n"/>
-      <c r="Y13" s="399" t="n"/>
-      <c r="Z13" s="399" t="n"/>
-      <c r="AA13" s="399" t="n"/>
-      <c r="AB13" s="399" t="n"/>
-      <c r="AC13" s="399" t="n"/>
-      <c r="AD13" s="399" t="n"/>
-      <c r="AE13" s="399" t="n"/>
-      <c r="AF13" s="399" t="n"/>
-      <c r="AG13" s="399" t="n"/>
-      <c r="AH13" s="399" t="n"/>
-      <c r="AI13" s="399" t="n"/>
-      <c r="AJ13" s="399" t="n"/>
-      <c r="AK13" s="399" t="n"/>
-      <c r="AL13" s="399" t="n"/>
-      <c r="AM13" s="399" t="n"/>
-      <c r="AN13" s="399" t="n"/>
+      <c r="A13" s="532" t="n"/>
+      <c r="B13" s="533" t="n"/>
+      <c r="C13" s="534" t="n"/>
+      <c r="D13" s="356" t="n"/>
+      <c r="E13" s="356" t="n"/>
+      <c r="F13" s="356" t="n"/>
+      <c r="G13" s="356" t="n"/>
+      <c r="H13" s="356" t="n"/>
+      <c r="I13" s="356" t="n"/>
+      <c r="J13" s="356" t="n"/>
+      <c r="K13" s="356" t="n"/>
+      <c r="L13" s="356" t="n"/>
+      <c r="M13" s="356" t="n"/>
+      <c r="N13" s="356" t="n"/>
+      <c r="O13" s="356" t="n"/>
+      <c r="P13" s="356" t="n"/>
+      <c r="Q13" s="356" t="n"/>
+      <c r="R13" s="356" t="n"/>
+      <c r="S13" s="356" t="n"/>
+      <c r="T13" s="356" t="n"/>
+      <c r="U13" s="356" t="n"/>
+      <c r="V13" s="356" t="n"/>
+      <c r="W13" s="356" t="n"/>
+      <c r="X13" s="356" t="n"/>
+      <c r="Y13" s="356" t="n"/>
+      <c r="Z13" s="356" t="n"/>
+      <c r="AA13" s="356" t="n"/>
+      <c r="AB13" s="356" t="n"/>
+      <c r="AC13" s="356" t="n"/>
+      <c r="AD13" s="356" t="n"/>
+      <c r="AE13" s="356" t="n"/>
+      <c r="AF13" s="356" t="n"/>
+      <c r="AG13" s="356" t="n"/>
+      <c r="AH13" s="356" t="n"/>
+      <c r="AI13" s="356" t="n"/>
+      <c r="AJ13" s="356" t="n"/>
+      <c r="AK13" s="356" t="n"/>
+      <c r="AL13" s="356" t="n"/>
+      <c r="AM13" s="356" t="n"/>
+      <c r="AN13" s="535" t="n"/>
     </row>
     <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="397" t="n"/>
-      <c r="B14" s="398" t="n"/>
-      <c r="C14" s="398" t="n"/>
-      <c r="D14" s="399" t="n"/>
-      <c r="E14" s="399" t="n"/>
-      <c r="F14" s="399" t="n"/>
-      <c r="G14" s="399" t="n"/>
-      <c r="H14" s="399" t="n"/>
-      <c r="I14" s="399" t="n"/>
-      <c r="J14" s="399" t="n"/>
-      <c r="K14" s="399" t="n"/>
-      <c r="L14" s="399" t="n"/>
-      <c r="M14" s="399" t="n"/>
-      <c r="N14" s="399" t="n"/>
-      <c r="O14" s="399" t="n"/>
-      <c r="P14" s="399" t="n"/>
-      <c r="Q14" s="399" t="n"/>
-      <c r="R14" s="399" t="n"/>
-      <c r="S14" s="399" t="n"/>
-      <c r="T14" s="399" t="n"/>
-      <c r="U14" s="399" t="n"/>
-      <c r="V14" s="399" t="n"/>
-      <c r="W14" s="399" t="n"/>
-      <c r="X14" s="399" t="n"/>
-      <c r="Y14" s="399" t="n"/>
-      <c r="Z14" s="399" t="n"/>
-      <c r="AA14" s="399" t="n"/>
-      <c r="AB14" s="399" t="n"/>
-      <c r="AC14" s="399" t="n"/>
-      <c r="AD14" s="399" t="n"/>
-      <c r="AE14" s="399" t="n"/>
-      <c r="AF14" s="399" t="n"/>
-      <c r="AG14" s="399" t="n"/>
-      <c r="AH14" s="399" t="n"/>
-      <c r="AI14" s="399" t="n"/>
-      <c r="AJ14" s="399" t="n"/>
-      <c r="AK14" s="399" t="n"/>
-      <c r="AL14" s="399" t="n"/>
-      <c r="AM14" s="399" t="n"/>
-      <c r="AN14" s="399" t="n"/>
+      <c r="A14" s="536" t="n"/>
+      <c r="B14" s="537" t="n"/>
+      <c r="C14" s="538" t="n"/>
+      <c r="D14" s="539" t="n"/>
+      <c r="E14" s="539" t="n"/>
+      <c r="F14" s="539" t="n"/>
+      <c r="G14" s="539" t="n"/>
+      <c r="H14" s="539" t="n"/>
+      <c r="I14" s="539" t="n"/>
+      <c r="J14" s="539" t="n"/>
+      <c r="K14" s="539" t="n"/>
+      <c r="L14" s="539" t="n"/>
+      <c r="M14" s="539" t="n"/>
+      <c r="N14" s="539" t="n"/>
+      <c r="O14" s="539" t="n"/>
+      <c r="P14" s="539" t="n"/>
+      <c r="Q14" s="539" t="n"/>
+      <c r="R14" s="539" t="n"/>
+      <c r="S14" s="539" t="n"/>
+      <c r="T14" s="539" t="n"/>
+      <c r="U14" s="539" t="n"/>
+      <c r="V14" s="539" t="n"/>
+      <c r="W14" s="539" t="n"/>
+      <c r="X14" s="539" t="n"/>
+      <c r="Y14" s="539" t="n"/>
+      <c r="Z14" s="539" t="n"/>
+      <c r="AA14" s="539" t="n"/>
+      <c r="AB14" s="539" t="n"/>
+      <c r="AC14" s="539" t="n"/>
+      <c r="AD14" s="539" t="n"/>
+      <c r="AE14" s="539" t="n"/>
+      <c r="AF14" s="539" t="n"/>
+      <c r="AG14" s="539" t="n"/>
+      <c r="AH14" s="539" t="n"/>
+      <c r="AI14" s="539" t="n"/>
+      <c r="AJ14" s="539" t="n"/>
+      <c r="AK14" s="539" t="n"/>
+      <c r="AL14" s="539" t="n"/>
+      <c r="AM14" s="539" t="n"/>
+      <c r="AN14" s="540" t="n"/>
     </row>
     <row r="15" ht="20" customHeight="1"/>
     <row r="16" ht="20" customHeight="1"/>
@@ -9414,6 +10324,7 @@
   </mergeCells>
   <pageMargins left="0.197" right="0.197" top="0.197" bottom="0.197" header="0.1" footer="0.1"/>
   <pageSetup paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -9468,249 +10379,255 @@
     <col width="2.33" customWidth="1" min="40" max="40"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18" customHeight="1">
-      <c r="A1" s="393" t="inlineStr">
+    <row r="1" ht="15" customHeight="1">
+      <c r="A1" s="513" t="inlineStr">
         <is>
           <t>Evidence Reference / Attachment Guidance</t>
         </is>
       </c>
-      <c r="B1" s="423" t="n"/>
-      <c r="C1" s="423" t="n"/>
-      <c r="D1" s="423" t="n"/>
-      <c r="E1" s="423" t="n"/>
-      <c r="F1" s="423" t="n"/>
-      <c r="G1" s="424" t="n"/>
-      <c r="H1" s="348" t="n"/>
-      <c r="I1" s="348" t="n"/>
-      <c r="J1" s="348" t="n"/>
-      <c r="K1" s="348" t="n"/>
-      <c r="L1" s="348" t="n"/>
-      <c r="M1" s="348" t="n"/>
-      <c r="N1" s="348" t="n"/>
-      <c r="O1" s="348" t="n"/>
-      <c r="P1" s="348" t="n"/>
-      <c r="Q1" s="348" t="n"/>
-      <c r="R1" s="348" t="n"/>
-      <c r="S1" s="348" t="n"/>
-      <c r="T1" s="348" t="n"/>
-      <c r="U1" s="348" t="n"/>
-      <c r="V1" s="348" t="n"/>
-      <c r="W1" s="348" t="n"/>
-      <c r="X1" s="348" t="n"/>
-      <c r="Y1" s="348" t="n"/>
-      <c r="Z1" s="348" t="n"/>
-      <c r="AA1" s="348" t="n"/>
-      <c r="AB1" s="348" t="n"/>
-      <c r="AC1" s="348" t="n"/>
-      <c r="AD1" s="348" t="n"/>
-      <c r="AE1" s="348" t="n"/>
-      <c r="AF1" s="348" t="n"/>
-      <c r="AG1" s="348" t="n"/>
-      <c r="AH1" s="348" t="n"/>
-      <c r="AI1" s="348" t="n"/>
-      <c r="AJ1" s="348" t="n"/>
-      <c r="AK1" s="348" t="n"/>
-      <c r="AL1" s="348" t="n"/>
-      <c r="AM1" s="348" t="n"/>
-      <c r="AN1" s="348" t="n"/>
+      <c r="B1" s="429" t="n"/>
+      <c r="C1" s="429" t="n"/>
+      <c r="D1" s="429" t="n"/>
+      <c r="E1" s="429" t="n"/>
+      <c r="F1" s="429" t="n"/>
+      <c r="G1" s="429" t="n"/>
+      <c r="H1" s="514" t="n"/>
+      <c r="I1" s="431" t="n"/>
+      <c r="J1" s="432" t="n"/>
+      <c r="K1" s="432" t="n"/>
+      <c r="L1" s="432" t="n"/>
+      <c r="M1" s="432" t="n"/>
+      <c r="N1" s="432" t="n"/>
+      <c r="O1" s="432" t="n"/>
+      <c r="P1" s="432" t="n"/>
+      <c r="Q1" s="432" t="n"/>
+      <c r="R1" s="432" t="n"/>
+      <c r="S1" s="432" t="n"/>
+      <c r="T1" s="432" t="n"/>
+      <c r="U1" s="432" t="n"/>
+      <c r="V1" s="432" t="n"/>
+      <c r="W1" s="432" t="n"/>
+      <c r="X1" s="432" t="n"/>
+      <c r="Y1" s="432" t="n"/>
+      <c r="Z1" s="432" t="n"/>
+      <c r="AA1" s="432" t="n"/>
+      <c r="AB1" s="432" t="n"/>
+      <c r="AC1" s="432" t="n"/>
+      <c r="AD1" s="433" t="n"/>
+      <c r="AE1" s="434" t="n"/>
+      <c r="AF1" s="435" t="n"/>
+      <c r="AG1" s="435" t="n"/>
+      <c r="AH1" s="436" t="n"/>
+      <c r="AI1" s="437" t="n"/>
+      <c r="AJ1" s="438" t="n"/>
+      <c r="AK1" s="438" t="n"/>
+      <c r="AL1" s="438" t="n"/>
+      <c r="AM1" s="438" t="n"/>
+      <c r="AN1" s="439" t="n"/>
     </row>
-    <row r="2" ht="18" customHeight="1">
-      <c r="A2" s="338" t="inlineStr">
+    <row r="2" ht="15" customHeight="1">
+      <c r="A2" s="515" t="inlineStr">
         <is>
           <t>Use controlled evidence package references; do not free-type vague placeholders.</t>
         </is>
       </c>
-      <c r="H2" s="348" t="n"/>
-      <c r="I2" s="348" t="n"/>
-      <c r="J2" s="348" t="n"/>
-      <c r="K2" s="348" t="n"/>
-      <c r="L2" s="348" t="n"/>
-      <c r="M2" s="348" t="n"/>
-      <c r="N2" s="348" t="n"/>
-      <c r="O2" s="348" t="n"/>
-      <c r="P2" s="348" t="n"/>
-      <c r="Q2" s="348" t="n"/>
-      <c r="R2" s="348" t="n"/>
-      <c r="S2" s="348" t="n"/>
-      <c r="T2" s="348" t="n"/>
-      <c r="U2" s="348" t="n"/>
-      <c r="V2" s="348" t="n"/>
-      <c r="W2" s="348" t="n"/>
-      <c r="X2" s="348" t="n"/>
-      <c r="Y2" s="348" t="n"/>
-      <c r="Z2" s="348" t="n"/>
-      <c r="AA2" s="348" t="n"/>
-      <c r="AB2" s="348" t="n"/>
-      <c r="AC2" s="348" t="n"/>
-      <c r="AD2" s="348" t="n"/>
-      <c r="AE2" s="348" t="n"/>
-      <c r="AF2" s="348" t="n"/>
-      <c r="AG2" s="348" t="n"/>
-      <c r="AH2" s="348" t="n"/>
-      <c r="AI2" s="348" t="n"/>
-      <c r="AJ2" s="348" t="n"/>
-      <c r="AK2" s="348" t="n"/>
-      <c r="AL2" s="348" t="n"/>
-      <c r="AM2" s="348" t="n"/>
-      <c r="AN2" s="348" t="n"/>
+      <c r="B2" s="25" t="n"/>
+      <c r="C2" s="25" t="n"/>
+      <c r="D2" s="25" t="n"/>
+      <c r="E2" s="25" t="n"/>
+      <c r="F2" s="25" t="n"/>
+      <c r="G2" s="25" t="n"/>
+      <c r="H2" s="516" t="n"/>
+      <c r="I2" s="442" t="n"/>
+      <c r="J2" s="443" t="n"/>
+      <c r="K2" s="443" t="n"/>
+      <c r="L2" s="443" t="n"/>
+      <c r="M2" s="443" t="n"/>
+      <c r="N2" s="443" t="n"/>
+      <c r="O2" s="443" t="n"/>
+      <c r="P2" s="443" t="n"/>
+      <c r="Q2" s="443" t="n"/>
+      <c r="R2" s="443" t="n"/>
+      <c r="S2" s="443" t="n"/>
+      <c r="T2" s="443" t="n"/>
+      <c r="U2" s="443" t="n"/>
+      <c r="V2" s="443" t="n"/>
+      <c r="W2" s="443" t="n"/>
+      <c r="X2" s="443" t="n"/>
+      <c r="Y2" s="443" t="n"/>
+      <c r="Z2" s="443" t="n"/>
+      <c r="AA2" s="443" t="n"/>
+      <c r="AB2" s="443" t="n"/>
+      <c r="AC2" s="443" t="n"/>
+      <c r="AD2" s="444" t="n"/>
+      <c r="AE2" s="445" t="n"/>
+      <c r="AF2" s="446" t="n"/>
+      <c r="AG2" s="446" t="n"/>
+      <c r="AH2" s="447" t="n"/>
+      <c r="AI2" s="448" t="n"/>
+      <c r="AJ2" s="449" t="n"/>
+      <c r="AK2" s="449" t="n"/>
+      <c r="AL2" s="449" t="n"/>
+      <c r="AM2" s="449" t="n"/>
+      <c r="AN2" s="450" t="n"/>
     </row>
-    <row r="3" ht="18" customHeight="1">
-      <c r="A3" s="348" t="n"/>
-      <c r="B3" s="348" t="n"/>
-      <c r="C3" s="348" t="n"/>
-      <c r="D3" s="348" t="n"/>
-      <c r="E3" s="348" t="n"/>
-      <c r="F3" s="348" t="n"/>
-      <c r="G3" s="348" t="n"/>
-      <c r="H3" s="348" t="n"/>
-      <c r="I3" s="348" t="n"/>
-      <c r="J3" s="348" t="n"/>
-      <c r="K3" s="348" t="n"/>
-      <c r="L3" s="348" t="n"/>
-      <c r="M3" s="348" t="n"/>
-      <c r="N3" s="348" t="n"/>
-      <c r="O3" s="348" t="n"/>
-      <c r="P3" s="348" t="n"/>
-      <c r="Q3" s="348" t="n"/>
-      <c r="R3" s="348" t="n"/>
-      <c r="S3" s="348" t="n"/>
-      <c r="T3" s="348" t="n"/>
-      <c r="U3" s="348" t="n"/>
-      <c r="V3" s="348" t="n"/>
-      <c r="W3" s="348" t="n"/>
-      <c r="X3" s="348" t="n"/>
-      <c r="Y3" s="348" t="n"/>
-      <c r="Z3" s="348" t="n"/>
-      <c r="AA3" s="348" t="n"/>
-      <c r="AB3" s="348" t="n"/>
-      <c r="AC3" s="348" t="n"/>
-      <c r="AD3" s="348" t="n"/>
-      <c r="AE3" s="348" t="n"/>
-      <c r="AF3" s="348" t="n"/>
-      <c r="AG3" s="348" t="n"/>
-      <c r="AH3" s="348" t="n"/>
-      <c r="AI3" s="348" t="n"/>
-      <c r="AJ3" s="348" t="n"/>
-      <c r="AK3" s="348" t="n"/>
-      <c r="AL3" s="348" t="n"/>
-      <c r="AM3" s="348" t="n"/>
-      <c r="AN3" s="348" t="n"/>
+    <row r="3" ht="15" customHeight="1">
+      <c r="A3" s="517" t="n"/>
+      <c r="B3" s="518" t="n"/>
+      <c r="C3" s="518" t="n"/>
+      <c r="D3" s="518" t="n"/>
+      <c r="E3" s="518" t="n"/>
+      <c r="F3" s="518" t="n"/>
+      <c r="G3" s="518" t="n"/>
+      <c r="H3" s="516" t="n"/>
+      <c r="I3" s="442" t="n"/>
+      <c r="J3" s="443" t="n"/>
+      <c r="K3" s="443" t="n"/>
+      <c r="L3" s="443" t="n"/>
+      <c r="M3" s="443" t="n"/>
+      <c r="N3" s="443" t="n"/>
+      <c r="O3" s="443" t="n"/>
+      <c r="P3" s="443" t="n"/>
+      <c r="Q3" s="443" t="n"/>
+      <c r="R3" s="443" t="n"/>
+      <c r="S3" s="443" t="n"/>
+      <c r="T3" s="443" t="n"/>
+      <c r="U3" s="443" t="n"/>
+      <c r="V3" s="443" t="n"/>
+      <c r="W3" s="443" t="n"/>
+      <c r="X3" s="443" t="n"/>
+      <c r="Y3" s="443" t="n"/>
+      <c r="Z3" s="443" t="n"/>
+      <c r="AA3" s="443" t="n"/>
+      <c r="AB3" s="443" t="n"/>
+      <c r="AC3" s="443" t="n"/>
+      <c r="AD3" s="444" t="n"/>
+      <c r="AE3" s="445" t="n"/>
+      <c r="AF3" s="446" t="n"/>
+      <c r="AG3" s="446" t="n"/>
+      <c r="AH3" s="447" t="n"/>
+      <c r="AI3" s="448" t="n"/>
+      <c r="AJ3" s="449" t="n"/>
+      <c r="AK3" s="449" t="n"/>
+      <c r="AL3" s="449" t="n"/>
+      <c r="AM3" s="449" t="n"/>
+      <c r="AN3" s="450" t="n"/>
     </row>
-    <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="394" t="inlineStr">
+    <row r="4" ht="15" customHeight="1">
+      <c r="A4" s="519" t="inlineStr">
         <is>
           <t>Field</t>
         </is>
       </c>
-      <c r="B4" s="394" t="inlineStr">
+      <c r="B4" s="520" t="inlineStr">
         <is>
           <t>Value / Reference</t>
         </is>
       </c>
-      <c r="C4" s="394" t="inlineStr">
+      <c r="C4" s="520" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="D4" s="348" t="n"/>
-      <c r="E4" s="348" t="n"/>
-      <c r="F4" s="348" t="n"/>
-      <c r="G4" s="348" t="n"/>
-      <c r="H4" s="348" t="n"/>
-      <c r="I4" s="348" t="n"/>
-      <c r="J4" s="348" t="n"/>
-      <c r="K4" s="348" t="n"/>
-      <c r="L4" s="348" t="n"/>
-      <c r="M4" s="348" t="n"/>
-      <c r="N4" s="348" t="n"/>
-      <c r="O4" s="348" t="n"/>
-      <c r="P4" s="348" t="n"/>
-      <c r="Q4" s="348" t="n"/>
-      <c r="R4" s="348" t="n"/>
-      <c r="S4" s="348" t="n"/>
-      <c r="T4" s="348" t="n"/>
-      <c r="U4" s="348" t="n"/>
-      <c r="V4" s="348" t="n"/>
-      <c r="W4" s="348" t="n"/>
-      <c r="X4" s="348" t="n"/>
-      <c r="Y4" s="348" t="n"/>
-      <c r="Z4" s="348" t="n"/>
-      <c r="AA4" s="348" t="n"/>
-      <c r="AB4" s="348" t="n"/>
-      <c r="AC4" s="348" t="n"/>
-      <c r="AD4" s="348" t="n"/>
-      <c r="AE4" s="348" t="n"/>
-      <c r="AF4" s="348" t="n"/>
-      <c r="AG4" s="348" t="n"/>
-      <c r="AH4" s="348" t="n"/>
-      <c r="AI4" s="348" t="n"/>
-      <c r="AJ4" s="348" t="n"/>
-      <c r="AK4" s="348" t="n"/>
-      <c r="AL4" s="348" t="n"/>
-      <c r="AM4" s="348" t="n"/>
-      <c r="AN4" s="348" t="n"/>
+      <c r="D4" s="518" t="n"/>
+      <c r="E4" s="518" t="n"/>
+      <c r="F4" s="518" t="n"/>
+      <c r="G4" s="518" t="n"/>
+      <c r="H4" s="516" t="n"/>
+      <c r="I4" s="451" t="n"/>
+      <c r="J4" s="452" t="n"/>
+      <c r="K4" s="452" t="n"/>
+      <c r="L4" s="452" t="n"/>
+      <c r="M4" s="452" t="n"/>
+      <c r="N4" s="452" t="n"/>
+      <c r="O4" s="452" t="n"/>
+      <c r="P4" s="452" t="n"/>
+      <c r="Q4" s="452" t="n"/>
+      <c r="R4" s="452" t="n"/>
+      <c r="S4" s="452" t="n"/>
+      <c r="T4" s="452" t="n"/>
+      <c r="U4" s="452" t="n"/>
+      <c r="V4" s="452" t="n"/>
+      <c r="W4" s="452" t="n"/>
+      <c r="X4" s="452" t="n"/>
+      <c r="Y4" s="452" t="n"/>
+      <c r="Z4" s="452" t="n"/>
+      <c r="AA4" s="452" t="n"/>
+      <c r="AB4" s="452" t="n"/>
+      <c r="AC4" s="452" t="n"/>
+      <c r="AD4" s="453" t="n"/>
+      <c r="AE4" s="445" t="n"/>
+      <c r="AF4" s="446" t="n"/>
+      <c r="AG4" s="446" t="n"/>
+      <c r="AH4" s="447" t="n"/>
+      <c r="AI4" s="448" t="n"/>
+      <c r="AJ4" s="449" t="n"/>
+      <c r="AK4" s="449" t="n"/>
+      <c r="AL4" s="449" t="n"/>
+      <c r="AM4" s="449" t="n"/>
+      <c r="AN4" s="450" t="n"/>
     </row>
-    <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="395" t="inlineStr">
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" s="522" t="inlineStr">
         <is>
           <t>Source of Truth</t>
         </is>
       </c>
-      <c r="B5" s="396" t="inlineStr">
+      <c r="B5" s="523" t="inlineStr">
         <is>
           <t>M365 evidence / shared workbook</t>
         </is>
       </c>
-      <c r="C5" s="396" t="inlineStr">
+      <c r="C5" s="523" t="inlineStr">
         <is>
           <t>Do not duplicate ERP/M365/ANNEX master data.</t>
         </is>
       </c>
-      <c r="D5" s="348" t="n"/>
-      <c r="E5" s="348" t="n"/>
-      <c r="F5" s="348" t="n"/>
-      <c r="G5" s="348" t="n"/>
-      <c r="H5" s="348" t="n"/>
-      <c r="I5" s="348" t="n"/>
-      <c r="J5" s="348" t="n"/>
-      <c r="K5" s="348" t="n"/>
-      <c r="L5" s="348" t="n"/>
-      <c r="M5" s="348" t="n"/>
-      <c r="N5" s="348" t="n"/>
-      <c r="O5" s="348" t="n"/>
-      <c r="P5" s="348" t="n"/>
-      <c r="Q5" s="348" t="n"/>
-      <c r="R5" s="348" t="n"/>
-      <c r="S5" s="348" t="n"/>
-      <c r="T5" s="348" t="n"/>
-      <c r="U5" s="348" t="n"/>
-      <c r="V5" s="348" t="n"/>
-      <c r="W5" s="348" t="n"/>
-      <c r="X5" s="348" t="n"/>
-      <c r="Y5" s="348" t="n"/>
-      <c r="Z5" s="348" t="n"/>
-      <c r="AA5" s="348" t="n"/>
-      <c r="AB5" s="348" t="n"/>
-      <c r="AC5" s="348" t="n"/>
-      <c r="AD5" s="348" t="n"/>
-      <c r="AE5" s="348" t="n"/>
-      <c r="AF5" s="348" t="n"/>
-      <c r="AG5" s="348" t="n"/>
-      <c r="AH5" s="348" t="n"/>
-      <c r="AI5" s="348" t="n"/>
-      <c r="AJ5" s="348" t="n"/>
-      <c r="AK5" s="348" t="n"/>
-      <c r="AL5" s="348" t="n"/>
-      <c r="AM5" s="348" t="n"/>
-      <c r="AN5" s="348" t="n"/>
+      <c r="D5" s="541" t="n"/>
+      <c r="E5" s="541" t="n"/>
+      <c r="F5" s="541" t="n"/>
+      <c r="G5" s="541" t="n"/>
+      <c r="H5" s="542" t="n"/>
+      <c r="I5" s="457" t="n"/>
+      <c r="J5" s="458" t="n"/>
+      <c r="K5" s="458" t="n"/>
+      <c r="L5" s="458" t="n"/>
+      <c r="M5" s="458" t="n"/>
+      <c r="N5" s="458" t="n"/>
+      <c r="O5" s="458" t="n"/>
+      <c r="P5" s="458" t="n"/>
+      <c r="Q5" s="458" t="n"/>
+      <c r="R5" s="458" t="n"/>
+      <c r="S5" s="458" t="n"/>
+      <c r="T5" s="458" t="n"/>
+      <c r="U5" s="458" t="n"/>
+      <c r="V5" s="458" t="n"/>
+      <c r="W5" s="458" t="n"/>
+      <c r="X5" s="458" t="n"/>
+      <c r="Y5" s="458" t="n"/>
+      <c r="Z5" s="458" t="n"/>
+      <c r="AA5" s="458" t="n"/>
+      <c r="AB5" s="458" t="n"/>
+      <c r="AC5" s="458" t="n"/>
+      <c r="AD5" s="459" t="n"/>
+      <c r="AE5" s="460" t="n"/>
+      <c r="AF5" s="461" t="n"/>
+      <c r="AG5" s="461" t="n"/>
+      <c r="AH5" s="462" t="n"/>
+      <c r="AI5" s="463" t="n"/>
+      <c r="AJ5" s="464" t="n"/>
+      <c r="AK5" s="464" t="n"/>
+      <c r="AL5" s="464" t="n"/>
+      <c r="AM5" s="464" t="n"/>
+      <c r="AN5" s="465" t="n"/>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="395" t="inlineStr">
+      <c r="A6" s="525" t="inlineStr">
         <is>
           <t>Cross-Reference Boundary</t>
         </is>
       </c>
-      <c r="B6" s="396" t="inlineStr">
+      <c r="B6" s="526" t="inlineStr">
         <is>
           <t>This form does not replace SOP-702; it records the evidence, data or decision required by that SOP.
 Detailed task execution belongs in WI-716; this form captures results, checks, decisions or exceptions only.
@@ -9718,7 +10635,7 @@
 System-of-record / source-of-truth boundary: M365 evidence / shared workbook. If the master data already live there, reference or import them; do not re-key without need.</t>
         </is>
       </c>
-      <c r="C6" s="396" t="inlineStr">
+      <c r="C6" s="527" t="inlineStr">
         <is>
           <t>This form does not replace SOP-702; it records the evidence, data or decision required by that SOP.
 Detailed task execution belongs in WI-716; this form captures results, checks, decisions or exceptions only.
@@ -9726,367 +10643,367 @@
 System-of-record / source-of-truth boundary: M365 evidence / shared workbook. If the master data already live there, reference or import them; do not re-key without need.</t>
         </is>
       </c>
-      <c r="D6" s="348" t="n"/>
-      <c r="E6" s="348" t="n"/>
-      <c r="F6" s="348" t="n"/>
-      <c r="G6" s="348" t="n"/>
-      <c r="H6" s="348" t="n"/>
-      <c r="I6" s="348" t="n"/>
-      <c r="J6" s="348" t="n"/>
-      <c r="K6" s="348" t="n"/>
-      <c r="L6" s="348" t="n"/>
-      <c r="M6" s="348" t="n"/>
-      <c r="N6" s="348" t="n"/>
-      <c r="O6" s="348" t="n"/>
-      <c r="P6" s="348" t="n"/>
-      <c r="Q6" s="348" t="n"/>
-      <c r="R6" s="348" t="n"/>
-      <c r="S6" s="348" t="n"/>
-      <c r="T6" s="348" t="n"/>
-      <c r="U6" s="348" t="n"/>
-      <c r="V6" s="348" t="n"/>
-      <c r="W6" s="348" t="n"/>
-      <c r="X6" s="348" t="n"/>
-      <c r="Y6" s="348" t="n"/>
-      <c r="Z6" s="348" t="n"/>
-      <c r="AA6" s="348" t="n"/>
-      <c r="AB6" s="348" t="n"/>
-      <c r="AC6" s="348" t="n"/>
-      <c r="AD6" s="348" t="n"/>
-      <c r="AE6" s="348" t="n"/>
-      <c r="AF6" s="348" t="n"/>
-      <c r="AG6" s="348" t="n"/>
-      <c r="AH6" s="348" t="n"/>
-      <c r="AI6" s="348" t="n"/>
-      <c r="AJ6" s="348" t="n"/>
-      <c r="AK6" s="348" t="n"/>
-      <c r="AL6" s="348" t="n"/>
-      <c r="AM6" s="348" t="n"/>
-      <c r="AN6" s="348" t="n"/>
+      <c r="D6" s="471" t="n"/>
+      <c r="E6" s="471" t="n"/>
+      <c r="F6" s="471" t="n"/>
+      <c r="G6" s="471" t="n"/>
+      <c r="H6" s="471" t="n"/>
+      <c r="I6" s="471" t="n"/>
+      <c r="J6" s="471" t="n"/>
+      <c r="K6" s="471" t="n"/>
+      <c r="L6" s="471" t="n"/>
+      <c r="M6" s="471" t="n"/>
+      <c r="N6" s="471" t="n"/>
+      <c r="O6" s="471" t="n"/>
+      <c r="P6" s="471" t="n"/>
+      <c r="Q6" s="471" t="n"/>
+      <c r="R6" s="471" t="n"/>
+      <c r="S6" s="471" t="n"/>
+      <c r="T6" s="471" t="n"/>
+      <c r="U6" s="471" t="n"/>
+      <c r="V6" s="471" t="n"/>
+      <c r="W6" s="471" t="n"/>
+      <c r="X6" s="471" t="n"/>
+      <c r="Y6" s="471" t="n"/>
+      <c r="Z6" s="471" t="n"/>
+      <c r="AA6" s="471" t="n"/>
+      <c r="AB6" s="471" t="n"/>
+      <c r="AC6" s="471" t="n"/>
+      <c r="AD6" s="471" t="n"/>
+      <c r="AE6" s="471" t="n"/>
+      <c r="AF6" s="471" t="n"/>
+      <c r="AG6" s="471" t="n"/>
+      <c r="AH6" s="471" t="n"/>
+      <c r="AI6" s="471" t="n"/>
+      <c r="AJ6" s="471" t="n"/>
+      <c r="AK6" s="471" t="n"/>
+      <c r="AL6" s="471" t="n"/>
+      <c r="AM6" s="471" t="n"/>
+      <c r="AN6" s="503" t="n"/>
     </row>
     <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="395" t="inlineStr">
+      <c r="A7" s="528" t="inlineStr">
         <is>
           <t>SOP-702</t>
         </is>
       </c>
-      <c r="B7" s="396" t="inlineStr">
+      <c r="B7" s="529" t="inlineStr">
         <is>
           <t>SOP-702 — Kiểm soát nhiễm bẩn, xác nhận độ sạch và tuyến đóng gói sạch | HESEM QMS</t>
         </is>
       </c>
-      <c r="C7" s="396" t="inlineStr">
+      <c r="C7" s="530" t="inlineStr">
         <is>
           <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/01-SOPs/07-SOP-700/sop-702-contamination-control-and-cleanliness.html</t>
         </is>
       </c>
-      <c r="D7" s="348" t="n"/>
-      <c r="E7" s="348" t="n"/>
-      <c r="F7" s="348" t="n"/>
-      <c r="G7" s="348" t="n"/>
-      <c r="H7" s="348" t="n"/>
-      <c r="I7" s="348" t="n"/>
-      <c r="J7" s="348" t="n"/>
-      <c r="K7" s="348" t="n"/>
-      <c r="L7" s="348" t="n"/>
-      <c r="M7" s="348" t="n"/>
-      <c r="N7" s="348" t="n"/>
-      <c r="O7" s="348" t="n"/>
-      <c r="P7" s="348" t="n"/>
-      <c r="Q7" s="348" t="n"/>
-      <c r="R7" s="348" t="n"/>
-      <c r="S7" s="348" t="n"/>
-      <c r="T7" s="348" t="n"/>
-      <c r="U7" s="348" t="n"/>
-      <c r="V7" s="348" t="n"/>
-      <c r="W7" s="348" t="n"/>
-      <c r="X7" s="348" t="n"/>
-      <c r="Y7" s="348" t="n"/>
-      <c r="Z7" s="348" t="n"/>
-      <c r="AA7" s="348" t="n"/>
-      <c r="AB7" s="348" t="n"/>
-      <c r="AC7" s="348" t="n"/>
-      <c r="AD7" s="348" t="n"/>
-      <c r="AE7" s="348" t="n"/>
-      <c r="AF7" s="348" t="n"/>
-      <c r="AG7" s="348" t="n"/>
-      <c r="AH7" s="348" t="n"/>
-      <c r="AI7" s="348" t="n"/>
-      <c r="AJ7" s="348" t="n"/>
-      <c r="AK7" s="348" t="n"/>
-      <c r="AL7" s="348" t="n"/>
-      <c r="AM7" s="348" t="n"/>
-      <c r="AN7" s="348" t="n"/>
+      <c r="D7" s="344" t="n"/>
+      <c r="E7" s="344" t="n"/>
+      <c r="F7" s="344" t="n"/>
+      <c r="G7" s="344" t="n"/>
+      <c r="H7" s="344" t="n"/>
+      <c r="I7" s="344" t="n"/>
+      <c r="J7" s="344" t="n"/>
+      <c r="K7" s="344" t="n"/>
+      <c r="L7" s="344" t="n"/>
+      <c r="M7" s="344" t="n"/>
+      <c r="N7" s="344" t="n"/>
+      <c r="O7" s="344" t="n"/>
+      <c r="P7" s="344" t="n"/>
+      <c r="Q7" s="344" t="n"/>
+      <c r="R7" s="344" t="n"/>
+      <c r="S7" s="344" t="n"/>
+      <c r="T7" s="344" t="n"/>
+      <c r="U7" s="344" t="n"/>
+      <c r="V7" s="344" t="n"/>
+      <c r="W7" s="344" t="n"/>
+      <c r="X7" s="344" t="n"/>
+      <c r="Y7" s="344" t="n"/>
+      <c r="Z7" s="344" t="n"/>
+      <c r="AA7" s="344" t="n"/>
+      <c r="AB7" s="344" t="n"/>
+      <c r="AC7" s="344" t="n"/>
+      <c r="AD7" s="344" t="n"/>
+      <c r="AE7" s="344" t="n"/>
+      <c r="AF7" s="344" t="n"/>
+      <c r="AG7" s="344" t="n"/>
+      <c r="AH7" s="344" t="n"/>
+      <c r="AI7" s="344" t="n"/>
+      <c r="AJ7" s="344" t="n"/>
+      <c r="AK7" s="344" t="n"/>
+      <c r="AL7" s="344" t="n"/>
+      <c r="AM7" s="344" t="n"/>
+      <c r="AN7" s="531" t="n"/>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="397" t="inlineStr">
+      <c r="A8" s="532" t="inlineStr">
         <is>
           <t>WI-716</t>
         </is>
       </c>
-      <c r="B8" s="398" t="inlineStr">
+      <c r="B8" s="533" t="inlineStr">
         <is>
           <t>WI-716 — Lắp sạch, tương thích chân không, bagging và bảo quản cho Job đặc biệt</t>
         </is>
       </c>
-      <c r="C8" s="398" t="inlineStr">
+      <c r="C8" s="534" t="inlineStr">
         <is>
           <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/02-Work-Instructions/07-WI-700/wi-716-vacuum-compatible-clean-build-and-bagging.html</t>
         </is>
       </c>
-      <c r="D8" s="399" t="n"/>
-      <c r="E8" s="399" t="n"/>
-      <c r="F8" s="399" t="n"/>
-      <c r="G8" s="399" t="n"/>
-      <c r="H8" s="399" t="n"/>
-      <c r="I8" s="399" t="n"/>
-      <c r="J8" s="399" t="n"/>
-      <c r="K8" s="399" t="n"/>
-      <c r="L8" s="399" t="n"/>
-      <c r="M8" s="399" t="n"/>
-      <c r="N8" s="399" t="n"/>
-      <c r="O8" s="399" t="n"/>
-      <c r="P8" s="399" t="n"/>
-      <c r="Q8" s="399" t="n"/>
-      <c r="R8" s="399" t="n"/>
-      <c r="S8" s="399" t="n"/>
-      <c r="T8" s="399" t="n"/>
-      <c r="U8" s="399" t="n"/>
-      <c r="V8" s="399" t="n"/>
-      <c r="W8" s="399" t="n"/>
-      <c r="X8" s="399" t="n"/>
-      <c r="Y8" s="399" t="n"/>
-      <c r="Z8" s="399" t="n"/>
-      <c r="AA8" s="399" t="n"/>
-      <c r="AB8" s="399" t="n"/>
-      <c r="AC8" s="399" t="n"/>
-      <c r="AD8" s="399" t="n"/>
-      <c r="AE8" s="399" t="n"/>
-      <c r="AF8" s="399" t="n"/>
-      <c r="AG8" s="399" t="n"/>
-      <c r="AH8" s="399" t="n"/>
-      <c r="AI8" s="399" t="n"/>
-      <c r="AJ8" s="399" t="n"/>
-      <c r="AK8" s="399" t="n"/>
-      <c r="AL8" s="399" t="n"/>
-      <c r="AM8" s="399" t="n"/>
-      <c r="AN8" s="399" t="n"/>
+      <c r="D8" s="356" t="n"/>
+      <c r="E8" s="356" t="n"/>
+      <c r="F8" s="356" t="n"/>
+      <c r="G8" s="356" t="n"/>
+      <c r="H8" s="356" t="n"/>
+      <c r="I8" s="356" t="n"/>
+      <c r="J8" s="356" t="n"/>
+      <c r="K8" s="356" t="n"/>
+      <c r="L8" s="356" t="n"/>
+      <c r="M8" s="356" t="n"/>
+      <c r="N8" s="356" t="n"/>
+      <c r="O8" s="356" t="n"/>
+      <c r="P8" s="356" t="n"/>
+      <c r="Q8" s="356" t="n"/>
+      <c r="R8" s="356" t="n"/>
+      <c r="S8" s="356" t="n"/>
+      <c r="T8" s="356" t="n"/>
+      <c r="U8" s="356" t="n"/>
+      <c r="V8" s="356" t="n"/>
+      <c r="W8" s="356" t="n"/>
+      <c r="X8" s="356" t="n"/>
+      <c r="Y8" s="356" t="n"/>
+      <c r="Z8" s="356" t="n"/>
+      <c r="AA8" s="356" t="n"/>
+      <c r="AB8" s="356" t="n"/>
+      <c r="AC8" s="356" t="n"/>
+      <c r="AD8" s="356" t="n"/>
+      <c r="AE8" s="356" t="n"/>
+      <c r="AF8" s="356" t="n"/>
+      <c r="AG8" s="356" t="n"/>
+      <c r="AH8" s="356" t="n"/>
+      <c r="AI8" s="356" t="n"/>
+      <c r="AJ8" s="356" t="n"/>
+      <c r="AK8" s="356" t="n"/>
+      <c r="AL8" s="356" t="n"/>
+      <c r="AM8" s="356" t="n"/>
+      <c r="AN8" s="535" t="n"/>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="399" t="inlineStr">
+      <c r="A9" s="543" t="inlineStr">
         <is>
           <t>ANNEX-QA-007</t>
         </is>
       </c>
-      <c r="B9" s="399" t="inlineStr">
+      <c r="B9" s="544" t="inlineStr">
         <is>
           <t>ANNEX-QA-007 — Chuẩn bề mặt, độ sạch, tương thích chân không, rò rỉ và xử lý đặc biệt</t>
         </is>
       </c>
-      <c r="C9" s="399" t="inlineStr">
+      <c r="C9" s="356" t="inlineStr">
         <is>
           <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/03-Reference/02-ANNEX-Standards/annex-qa-007-surface-finish-vacuum-compatibility.html</t>
         </is>
       </c>
-      <c r="D9" s="399" t="n"/>
-      <c r="E9" s="399" t="n"/>
-      <c r="F9" s="399" t="n"/>
-      <c r="G9" s="399" t="n"/>
-      <c r="H9" s="399" t="n"/>
-      <c r="I9" s="399" t="n"/>
-      <c r="J9" s="399" t="n"/>
-      <c r="K9" s="399" t="n"/>
-      <c r="L9" s="399" t="n"/>
-      <c r="M9" s="399" t="n"/>
-      <c r="N9" s="399" t="n"/>
-      <c r="O9" s="399" t="n"/>
-      <c r="P9" s="399" t="n"/>
-      <c r="Q9" s="399" t="n"/>
-      <c r="R9" s="399" t="n"/>
-      <c r="S9" s="399" t="n"/>
-      <c r="T9" s="399" t="n"/>
-      <c r="U9" s="399" t="n"/>
-      <c r="V9" s="399" t="n"/>
-      <c r="W9" s="399" t="n"/>
-      <c r="X9" s="399" t="n"/>
-      <c r="Y9" s="399" t="n"/>
-      <c r="Z9" s="399" t="n"/>
-      <c r="AA9" s="399" t="n"/>
-      <c r="AB9" s="399" t="n"/>
-      <c r="AC9" s="399" t="n"/>
-      <c r="AD9" s="399" t="n"/>
-      <c r="AE9" s="399" t="n"/>
-      <c r="AF9" s="399" t="n"/>
-      <c r="AG9" s="399" t="n"/>
-      <c r="AH9" s="399" t="n"/>
-      <c r="AI9" s="399" t="n"/>
-      <c r="AJ9" s="399" t="n"/>
-      <c r="AK9" s="399" t="n"/>
-      <c r="AL9" s="399" t="n"/>
-      <c r="AM9" s="399" t="n"/>
-      <c r="AN9" s="399" t="n"/>
+      <c r="D9" s="356" t="n"/>
+      <c r="E9" s="356" t="n"/>
+      <c r="F9" s="356" t="n"/>
+      <c r="G9" s="356" t="n"/>
+      <c r="H9" s="356" t="n"/>
+      <c r="I9" s="356" t="n"/>
+      <c r="J9" s="356" t="n"/>
+      <c r="K9" s="356" t="n"/>
+      <c r="L9" s="356" t="n"/>
+      <c r="M9" s="356" t="n"/>
+      <c r="N9" s="356" t="n"/>
+      <c r="O9" s="356" t="n"/>
+      <c r="P9" s="356" t="n"/>
+      <c r="Q9" s="356" t="n"/>
+      <c r="R9" s="356" t="n"/>
+      <c r="S9" s="356" t="n"/>
+      <c r="T9" s="356" t="n"/>
+      <c r="U9" s="356" t="n"/>
+      <c r="V9" s="356" t="n"/>
+      <c r="W9" s="356" t="n"/>
+      <c r="X9" s="356" t="n"/>
+      <c r="Y9" s="356" t="n"/>
+      <c r="Z9" s="356" t="n"/>
+      <c r="AA9" s="356" t="n"/>
+      <c r="AB9" s="356" t="n"/>
+      <c r="AC9" s="356" t="n"/>
+      <c r="AD9" s="356" t="n"/>
+      <c r="AE9" s="356" t="n"/>
+      <c r="AF9" s="356" t="n"/>
+      <c r="AG9" s="356" t="n"/>
+      <c r="AH9" s="356" t="n"/>
+      <c r="AI9" s="356" t="n"/>
+      <c r="AJ9" s="356" t="n"/>
+      <c r="AK9" s="356" t="n"/>
+      <c r="AL9" s="356" t="n"/>
+      <c r="AM9" s="356" t="n"/>
+      <c r="AN9" s="535" t="n"/>
     </row>
     <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="399" t="inlineStr">
+      <c r="A10" s="543" t="inlineStr">
         <is>
           <t>ANNEX-WHS-001</t>
         </is>
       </c>
-      <c r="B10" s="399" t="inlineStr">
+      <c r="B10" s="544" t="inlineStr">
         <is>
           <t>ANNEX-WHS-001 — Quy cách đóng gói, nhãn, bảo quản và bằng chứng gói hàng</t>
         </is>
       </c>
-      <c r="C10" s="399" t="inlineStr">
+      <c r="C10" s="356" t="inlineStr">
         <is>
           <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/03-Reference/02-ANNEX-Standards/annex-whs-001-packaging-labeling-spec.html</t>
         </is>
       </c>
-      <c r="D10" s="399" t="n"/>
-      <c r="E10" s="399" t="n"/>
-      <c r="F10" s="399" t="n"/>
-      <c r="G10" s="399" t="n"/>
-      <c r="H10" s="399" t="n"/>
-      <c r="I10" s="399" t="n"/>
-      <c r="J10" s="399" t="n"/>
-      <c r="K10" s="399" t="n"/>
-      <c r="L10" s="399" t="n"/>
-      <c r="M10" s="399" t="n"/>
-      <c r="N10" s="399" t="n"/>
-      <c r="O10" s="399" t="n"/>
-      <c r="P10" s="399" t="n"/>
-      <c r="Q10" s="399" t="n"/>
-      <c r="R10" s="399" t="n"/>
-      <c r="S10" s="399" t="n"/>
-      <c r="T10" s="399" t="n"/>
-      <c r="U10" s="399" t="n"/>
-      <c r="V10" s="399" t="n"/>
-      <c r="W10" s="399" t="n"/>
-      <c r="X10" s="399" t="n"/>
-      <c r="Y10" s="399" t="n"/>
-      <c r="Z10" s="399" t="n"/>
-      <c r="AA10" s="399" t="n"/>
-      <c r="AB10" s="399" t="n"/>
-      <c r="AC10" s="399" t="n"/>
-      <c r="AD10" s="399" t="n"/>
-      <c r="AE10" s="399" t="n"/>
-      <c r="AF10" s="399" t="n"/>
-      <c r="AG10" s="399" t="n"/>
-      <c r="AH10" s="399" t="n"/>
-      <c r="AI10" s="399" t="n"/>
-      <c r="AJ10" s="399" t="n"/>
-      <c r="AK10" s="399" t="n"/>
-      <c r="AL10" s="399" t="n"/>
-      <c r="AM10" s="399" t="n"/>
-      <c r="AN10" s="399" t="n"/>
+      <c r="D10" s="356" t="n"/>
+      <c r="E10" s="356" t="n"/>
+      <c r="F10" s="356" t="n"/>
+      <c r="G10" s="356" t="n"/>
+      <c r="H10" s="356" t="n"/>
+      <c r="I10" s="356" t="n"/>
+      <c r="J10" s="356" t="n"/>
+      <c r="K10" s="356" t="n"/>
+      <c r="L10" s="356" t="n"/>
+      <c r="M10" s="356" t="n"/>
+      <c r="N10" s="356" t="n"/>
+      <c r="O10" s="356" t="n"/>
+      <c r="P10" s="356" t="n"/>
+      <c r="Q10" s="356" t="n"/>
+      <c r="R10" s="356" t="n"/>
+      <c r="S10" s="356" t="n"/>
+      <c r="T10" s="356" t="n"/>
+      <c r="U10" s="356" t="n"/>
+      <c r="V10" s="356" t="n"/>
+      <c r="W10" s="356" t="n"/>
+      <c r="X10" s="356" t="n"/>
+      <c r="Y10" s="356" t="n"/>
+      <c r="Z10" s="356" t="n"/>
+      <c r="AA10" s="356" t="n"/>
+      <c r="AB10" s="356" t="n"/>
+      <c r="AC10" s="356" t="n"/>
+      <c r="AD10" s="356" t="n"/>
+      <c r="AE10" s="356" t="n"/>
+      <c r="AF10" s="356" t="n"/>
+      <c r="AG10" s="356" t="n"/>
+      <c r="AH10" s="356" t="n"/>
+      <c r="AI10" s="356" t="n"/>
+      <c r="AJ10" s="356" t="n"/>
+      <c r="AK10" s="356" t="n"/>
+      <c r="AL10" s="356" t="n"/>
+      <c r="AM10" s="356" t="n"/>
+      <c r="AN10" s="535" t="n"/>
     </row>
     <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="399" t="inlineStr">
+      <c r="A11" s="543" t="inlineStr">
         <is>
           <t>Open When</t>
         </is>
       </c>
-      <c r="B11" s="399" t="inlineStr">
+      <c r="B11" s="544" t="inlineStr">
         <is>
           <t>Open before the controlled activity starts or before the release decision is taken. Do not populate it retrospectively after execution has already moved forward.</t>
         </is>
       </c>
-      <c r="C11" s="399" t="inlineStr">
+      <c r="C11" s="356" t="inlineStr">
         <is>
           <t>Operational trigger</t>
         </is>
       </c>
-      <c r="D11" s="399" t="n"/>
-      <c r="E11" s="399" t="n"/>
-      <c r="F11" s="399" t="n"/>
-      <c r="G11" s="399" t="n"/>
-      <c r="H11" s="399" t="n"/>
-      <c r="I11" s="399" t="n"/>
-      <c r="J11" s="399" t="n"/>
-      <c r="K11" s="399" t="n"/>
-      <c r="L11" s="399" t="n"/>
-      <c r="M11" s="399" t="n"/>
-      <c r="N11" s="399" t="n"/>
-      <c r="O11" s="399" t="n"/>
-      <c r="P11" s="399" t="n"/>
-      <c r="Q11" s="399" t="n"/>
-      <c r="R11" s="399" t="n"/>
-      <c r="S11" s="399" t="n"/>
-      <c r="T11" s="399" t="n"/>
-      <c r="U11" s="399" t="n"/>
-      <c r="V11" s="399" t="n"/>
-      <c r="W11" s="399" t="n"/>
-      <c r="X11" s="399" t="n"/>
-      <c r="Y11" s="399" t="n"/>
-      <c r="Z11" s="399" t="n"/>
-      <c r="AA11" s="399" t="n"/>
-      <c r="AB11" s="399" t="n"/>
-      <c r="AC11" s="399" t="n"/>
-      <c r="AD11" s="399" t="n"/>
-      <c r="AE11" s="399" t="n"/>
-      <c r="AF11" s="399" t="n"/>
-      <c r="AG11" s="399" t="n"/>
-      <c r="AH11" s="399" t="n"/>
-      <c r="AI11" s="399" t="n"/>
-      <c r="AJ11" s="399" t="n"/>
-      <c r="AK11" s="399" t="n"/>
-      <c r="AL11" s="399" t="n"/>
-      <c r="AM11" s="399" t="n"/>
-      <c r="AN11" s="399" t="n"/>
+      <c r="D11" s="356" t="n"/>
+      <c r="E11" s="356" t="n"/>
+      <c r="F11" s="356" t="n"/>
+      <c r="G11" s="356" t="n"/>
+      <c r="H11" s="356" t="n"/>
+      <c r="I11" s="356" t="n"/>
+      <c r="J11" s="356" t="n"/>
+      <c r="K11" s="356" t="n"/>
+      <c r="L11" s="356" t="n"/>
+      <c r="M11" s="356" t="n"/>
+      <c r="N11" s="356" t="n"/>
+      <c r="O11" s="356" t="n"/>
+      <c r="P11" s="356" t="n"/>
+      <c r="Q11" s="356" t="n"/>
+      <c r="R11" s="356" t="n"/>
+      <c r="S11" s="356" t="n"/>
+      <c r="T11" s="356" t="n"/>
+      <c r="U11" s="356" t="n"/>
+      <c r="V11" s="356" t="n"/>
+      <c r="W11" s="356" t="n"/>
+      <c r="X11" s="356" t="n"/>
+      <c r="Y11" s="356" t="n"/>
+      <c r="Z11" s="356" t="n"/>
+      <c r="AA11" s="356" t="n"/>
+      <c r="AB11" s="356" t="n"/>
+      <c r="AC11" s="356" t="n"/>
+      <c r="AD11" s="356" t="n"/>
+      <c r="AE11" s="356" t="n"/>
+      <c r="AF11" s="356" t="n"/>
+      <c r="AG11" s="356" t="n"/>
+      <c r="AH11" s="356" t="n"/>
+      <c r="AI11" s="356" t="n"/>
+      <c r="AJ11" s="356" t="n"/>
+      <c r="AK11" s="356" t="n"/>
+      <c r="AL11" s="356" t="n"/>
+      <c r="AM11" s="356" t="n"/>
+      <c r="AN11" s="535" t="n"/>
     </row>
     <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="399" t="inlineStr">
+      <c r="A12" s="545" t="inlineStr">
         <is>
           <t>Close When</t>
         </is>
       </c>
-      <c r="B12" s="399" t="inlineStr">
+      <c r="B12" s="546" t="inlineStr">
         <is>
           <t>Close only after the final gate disposition, result or release status is recorded, all conditions are assigned to an owner, and the evidence package reference is complete.</t>
         </is>
       </c>
-      <c r="C12" s="399" t="inlineStr">
+      <c r="C12" s="539" t="inlineStr">
         <is>
           <t>Release / closure rule</t>
         </is>
       </c>
-      <c r="D12" s="399" t="n"/>
-      <c r="E12" s="399" t="n"/>
-      <c r="F12" s="399" t="n"/>
-      <c r="G12" s="399" t="n"/>
-      <c r="H12" s="399" t="n"/>
-      <c r="I12" s="399" t="n"/>
-      <c r="J12" s="399" t="n"/>
-      <c r="K12" s="399" t="n"/>
-      <c r="L12" s="399" t="n"/>
-      <c r="M12" s="399" t="n"/>
-      <c r="N12" s="399" t="n"/>
-      <c r="O12" s="399" t="n"/>
-      <c r="P12" s="399" t="n"/>
-      <c r="Q12" s="399" t="n"/>
-      <c r="R12" s="399" t="n"/>
-      <c r="S12" s="399" t="n"/>
-      <c r="T12" s="399" t="n"/>
-      <c r="U12" s="399" t="n"/>
-      <c r="V12" s="399" t="n"/>
-      <c r="W12" s="399" t="n"/>
-      <c r="X12" s="399" t="n"/>
-      <c r="Y12" s="399" t="n"/>
-      <c r="Z12" s="399" t="n"/>
-      <c r="AA12" s="399" t="n"/>
-      <c r="AB12" s="399" t="n"/>
-      <c r="AC12" s="399" t="n"/>
-      <c r="AD12" s="399" t="n"/>
-      <c r="AE12" s="399" t="n"/>
-      <c r="AF12" s="399" t="n"/>
-      <c r="AG12" s="399" t="n"/>
-      <c r="AH12" s="399" t="n"/>
-      <c r="AI12" s="399" t="n"/>
-      <c r="AJ12" s="399" t="n"/>
-      <c r="AK12" s="399" t="n"/>
-      <c r="AL12" s="399" t="n"/>
-      <c r="AM12" s="399" t="n"/>
-      <c r="AN12" s="399" t="n"/>
+      <c r="D12" s="539" t="n"/>
+      <c r="E12" s="539" t="n"/>
+      <c r="F12" s="539" t="n"/>
+      <c r="G12" s="539" t="n"/>
+      <c r="H12" s="539" t="n"/>
+      <c r="I12" s="539" t="n"/>
+      <c r="J12" s="539" t="n"/>
+      <c r="K12" s="539" t="n"/>
+      <c r="L12" s="539" t="n"/>
+      <c r="M12" s="539" t="n"/>
+      <c r="N12" s="539" t="n"/>
+      <c r="O12" s="539" t="n"/>
+      <c r="P12" s="539" t="n"/>
+      <c r="Q12" s="539" t="n"/>
+      <c r="R12" s="539" t="n"/>
+      <c r="S12" s="539" t="n"/>
+      <c r="T12" s="539" t="n"/>
+      <c r="U12" s="539" t="n"/>
+      <c r="V12" s="539" t="n"/>
+      <c r="W12" s="539" t="n"/>
+      <c r="X12" s="539" t="n"/>
+      <c r="Y12" s="539" t="n"/>
+      <c r="Z12" s="539" t="n"/>
+      <c r="AA12" s="539" t="n"/>
+      <c r="AB12" s="539" t="n"/>
+      <c r="AC12" s="539" t="n"/>
+      <c r="AD12" s="539" t="n"/>
+      <c r="AE12" s="539" t="n"/>
+      <c r="AF12" s="539" t="n"/>
+      <c r="AG12" s="539" t="n"/>
+      <c r="AH12" s="539" t="n"/>
+      <c r="AI12" s="539" t="n"/>
+      <c r="AJ12" s="539" t="n"/>
+      <c r="AK12" s="539" t="n"/>
+      <c r="AL12" s="539" t="n"/>
+      <c r="AM12" s="539" t="n"/>
+      <c r="AN12" s="540" t="n"/>
     </row>
     <row r="13" ht="20" customHeight="1"/>
     <row r="14" ht="20" customHeight="1"/>
@@ -10115,5 +11032,6 @@
   </mergeCells>
   <pageMargins left="0.197" right="0.197" top="0.197" bottom="0.197" header="0.1" footer="0.1"/>
   <pageSetup paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
--- a/04-Bieu-Mau/07-FRM-700/FRM-715_Vacuum_Compatible_Clean_Build_and_Bagging_Record.xlsx
+++ b/04-Bieu-Mau/07-FRM-700/FRM-715_Vacuum_Compatible_Clean_Build_and_Bagging_Record.xlsx
@@ -8,10 +8,10 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VAC_BAG_GATE" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LISTS" sheetId="2" state="hidden" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CONDITIONS_ACTIONS" sheetId="3" state="hidden" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="REF_IMPORT" sheetId="4" state="hidden" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EVIDENCE_REF" sheetId="5" state="hidden" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LISTS" sheetId="2" state="veryHidden" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CONDITIONS_ACTIONS" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="REF_IMPORT" sheetId="4" state="veryHidden" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EVIDENCE_REF" sheetId="5" state="veryHidden" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'VAC_BAG_GATE'!$A$1:$BD$35</definedName>
@@ -771,7 +771,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="321">
+  <borders count="353">
     <border>
       <left/>
       <right/>
@@ -4201,12 +4201,389 @@
       <bottom style="medium">
         <color rgb="002C9CD7"/>
       </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00C5D9E8"/>
+      </left>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="002C9CD7"/>
+      </left>
+      <right style="thin">
+        <color rgb="00C5D9E8"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00C5D9E8"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00C5D9E8"/>
+      </left>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="002C9CD7"/>
+      </left>
+      <right style="thin">
+        <color rgb="00C5D9E8"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00C5D9E8"/>
+      </left>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="002C9CD7"/>
+      </left>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="002C9CD7"/>
+      </left>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top/>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="002C9CD7"/>
+      </left>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="002C9CD7"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="002C9CD7"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00C5D9E8"/>
+      </left>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="002C9CD7"/>
+      </left>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00C5D9E8"/>
+      </left>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="002C9CD7"/>
+      </left>
+      <right style="thin">
+        <color rgb="00C5D9E8"/>
+      </right>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00C5D9E8"/>
+      </right>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00C5D9E8"/>
+      </left>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="002C9CD7"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="002C9CD7"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="79" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="547">
+  <cellXfs count="600">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -5570,6 +5947,136 @@
     </xf>
     <xf numFmtId="0" fontId="80" fillId="0" borderId="309" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="79" fillId="4" borderId="333" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="329" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="334" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="81" fillId="4" borderId="339" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="48" borderId="348" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="349" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="51" fillId="4" borderId="350" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="340" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="338" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="82" fillId="48" borderId="328" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="288" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="51" fillId="4" borderId="321" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="322" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="83" fillId="4" borderId="337" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="341" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="342" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="343" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="84" fillId="4" borderId="346" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="48" borderId="323" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="324" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="325" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="51" fillId="4" borderId="331" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="332" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="49" borderId="333" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="335" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="336" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="330" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="330" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="344" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="345" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="289" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="326" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="327" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="324" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="331" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="332" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="51" borderId="347" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="344" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="326" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="331" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="50" borderId="344" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="345" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="287" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="85" fillId="4" borderId="326" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="322" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="340" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="291" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="338" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="352" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="285" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="292" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="351" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="4" borderId="333" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -5670,6 +6177,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -5700,6 +6210,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -5730,6 +6243,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -5760,6 +6276,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -6152,326 +6671,212 @@
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1">
-      <c r="A1" s="428" t="n"/>
-      <c r="B1" s="429" t="n"/>
-      <c r="C1" s="429" t="n"/>
-      <c r="D1" s="429" t="n"/>
-      <c r="E1" s="429" t="n"/>
-      <c r="F1" s="429" t="n"/>
-      <c r="G1" s="429" t="n"/>
-      <c r="H1" s="429" t="n"/>
-      <c r="I1" s="429" t="n"/>
-      <c r="J1" s="429" t="n"/>
-      <c r="K1" s="430" t="n"/>
-      <c r="L1" s="431" t="inlineStr">
+      <c r="A1" s="547" t="n"/>
+      <c r="B1" s="548" t="n"/>
+      <c r="C1" s="548" t="n"/>
+      <c r="D1" s="548" t="n"/>
+      <c r="E1" s="548" t="n"/>
+      <c r="F1" s="548" t="n"/>
+      <c r="G1" s="548" t="n"/>
+      <c r="H1" s="548" t="n"/>
+      <c r="I1" s="548" t="n"/>
+      <c r="J1" s="548" t="n"/>
+      <c r="K1" s="549" t="n"/>
+      <c r="L1" s="550" t="inlineStr">
         <is>
           <t>Vacuum-Compatible Clean Build and Bagging Record</t>
         </is>
       </c>
-      <c r="M1" s="432" t="n"/>
-      <c r="N1" s="432" t="n"/>
-      <c r="O1" s="432" t="n"/>
-      <c r="P1" s="432" t="n"/>
-      <c r="Q1" s="432" t="n"/>
-      <c r="R1" s="432" t="n"/>
-      <c r="S1" s="432" t="n"/>
-      <c r="T1" s="432" t="n"/>
-      <c r="U1" s="432" t="n"/>
-      <c r="V1" s="432" t="n"/>
-      <c r="W1" s="432" t="n"/>
-      <c r="X1" s="432" t="n"/>
-      <c r="Y1" s="432" t="n"/>
-      <c r="Z1" s="432" t="n"/>
-      <c r="AA1" s="432" t="n"/>
-      <c r="AB1" s="432" t="n"/>
-      <c r="AC1" s="432" t="n"/>
-      <c r="AD1" s="432" t="n"/>
-      <c r="AE1" s="432" t="n"/>
-      <c r="AF1" s="432" t="n"/>
-      <c r="AG1" s="432" t="n"/>
-      <c r="AH1" s="432" t="n"/>
-      <c r="AI1" s="432" t="n"/>
-      <c r="AJ1" s="432" t="n"/>
-      <c r="AK1" s="432" t="n"/>
-      <c r="AL1" s="432" t="n"/>
-      <c r="AM1" s="432" t="n"/>
-      <c r="AN1" s="432" t="n"/>
-      <c r="AO1" s="432" t="n"/>
-      <c r="AP1" s="433" t="n"/>
-      <c r="AQ1" s="434" t="n"/>
-      <c r="AR1" s="435" t="n"/>
-      <c r="AS1" s="435" t="n"/>
-      <c r="AT1" s="435" t="n"/>
-      <c r="AU1" s="435" t="n"/>
-      <c r="AV1" s="436" t="n"/>
-      <c r="AW1" s="437" t="inlineStr">
+      <c r="M1" s="548" t="n"/>
+      <c r="N1" s="548" t="n"/>
+      <c r="O1" s="548" t="n"/>
+      <c r="P1" s="548" t="n"/>
+      <c r="Q1" s="548" t="n"/>
+      <c r="R1" s="548" t="n"/>
+      <c r="S1" s="548" t="n"/>
+      <c r="T1" s="548" t="n"/>
+      <c r="U1" s="548" t="n"/>
+      <c r="V1" s="548" t="n"/>
+      <c r="W1" s="548" t="n"/>
+      <c r="X1" s="548" t="n"/>
+      <c r="Y1" s="548" t="n"/>
+      <c r="Z1" s="548" t="n"/>
+      <c r="AA1" s="548" t="n"/>
+      <c r="AB1" s="548" t="n"/>
+      <c r="AC1" s="548" t="n"/>
+      <c r="AD1" s="548" t="n"/>
+      <c r="AE1" s="548" t="n"/>
+      <c r="AF1" s="548" t="n"/>
+      <c r="AG1" s="548" t="n"/>
+      <c r="AH1" s="548" t="n"/>
+      <c r="AI1" s="548" t="n"/>
+      <c r="AJ1" s="548" t="n"/>
+      <c r="AK1" s="548" t="n"/>
+      <c r="AL1" s="548" t="n"/>
+      <c r="AM1" s="548" t="n"/>
+      <c r="AN1" s="548" t="n"/>
+      <c r="AO1" s="548" t="n"/>
+      <c r="AP1" s="549" t="n"/>
+      <c r="AQ1" s="551" t="n"/>
+      <c r="AR1" s="548" t="n"/>
+      <c r="AS1" s="548" t="n"/>
+      <c r="AT1" s="548" t="n"/>
+      <c r="AU1" s="548" t="n"/>
+      <c r="AV1" s="552" t="n"/>
+      <c r="AW1" s="553" t="inlineStr">
         <is>
           <t>FRM-715</t>
         </is>
       </c>
-      <c r="AX1" s="438" t="n"/>
-      <c r="AY1" s="438" t="n"/>
-      <c r="AZ1" s="438" t="n"/>
-      <c r="BA1" s="438" t="n"/>
-      <c r="BB1" s="438" t="n"/>
-      <c r="BC1" s="438" t="n"/>
-      <c r="BD1" s="439" t="n"/>
+      <c r="AX1" s="548" t="n"/>
+      <c r="AY1" s="548" t="n"/>
+      <c r="AZ1" s="548" t="n"/>
+      <c r="BA1" s="548" t="n"/>
+      <c r="BB1" s="548" t="n"/>
+      <c r="BC1" s="548" t="n"/>
+      <c r="BD1" s="549" t="n"/>
     </row>
     <row r="2" ht="15" customHeight="1">
-      <c r="A2" s="440" t="n"/>
-      <c r="B2" s="25" t="n"/>
-      <c r="C2" s="25" t="n"/>
-      <c r="D2" s="25" t="n"/>
-      <c r="E2" s="25" t="n"/>
-      <c r="F2" s="25" t="n"/>
-      <c r="G2" s="25" t="n"/>
-      <c r="H2" s="25" t="n"/>
-      <c r="I2" s="25" t="n"/>
-      <c r="J2" s="25" t="n"/>
-      <c r="K2" s="441" t="n"/>
-      <c r="L2" s="442" t="n"/>
-      <c r="M2" s="443" t="n"/>
-      <c r="N2" s="443" t="n"/>
-      <c r="O2" s="443" t="n"/>
-      <c r="P2" s="443" t="n"/>
-      <c r="Q2" s="443" t="n"/>
-      <c r="R2" s="443" t="n"/>
-      <c r="S2" s="443" t="n"/>
-      <c r="T2" s="443" t="n"/>
-      <c r="U2" s="443" t="n"/>
-      <c r="V2" s="443" t="n"/>
-      <c r="W2" s="443" t="n"/>
-      <c r="X2" s="443" t="n"/>
-      <c r="Y2" s="443" t="n"/>
-      <c r="Z2" s="443" t="n"/>
-      <c r="AA2" s="443" t="n"/>
-      <c r="AB2" s="443" t="n"/>
-      <c r="AC2" s="443" t="n"/>
-      <c r="AD2" s="443" t="n"/>
-      <c r="AE2" s="443" t="n"/>
-      <c r="AF2" s="443" t="n"/>
-      <c r="AG2" s="443" t="n"/>
-      <c r="AH2" s="443" t="n"/>
-      <c r="AI2" s="443" t="n"/>
-      <c r="AJ2" s="443" t="n"/>
-      <c r="AK2" s="443" t="n"/>
-      <c r="AL2" s="443" t="n"/>
-      <c r="AM2" s="443" t="n"/>
-      <c r="AN2" s="443" t="n"/>
-      <c r="AO2" s="443" t="n"/>
-      <c r="AP2" s="444" t="n"/>
-      <c r="AQ2" s="445" t="n"/>
-      <c r="AR2" s="446" t="n"/>
-      <c r="AS2" s="446" t="n"/>
-      <c r="AT2" s="446" t="n"/>
-      <c r="AU2" s="446" t="n"/>
-      <c r="AV2" s="447" t="n"/>
-      <c r="AW2" s="448" t="inlineStr">
+      <c r="A2" s="554" t="n"/>
+      <c r="K2" s="555" t="n"/>
+      <c r="L2" s="554" t="n"/>
+      <c r="AP2" s="555" t="n"/>
+      <c r="AQ2" s="556" t="n"/>
+      <c r="AR2" s="422" t="n"/>
+      <c r="AS2" s="422" t="n"/>
+      <c r="AT2" s="422" t="n"/>
+      <c r="AU2" s="422" t="n"/>
+      <c r="AV2" s="557" t="n"/>
+      <c r="AW2" s="558" t="inlineStr">
         <is>
           <t>V0</t>
         </is>
       </c>
-      <c r="AX2" s="449" t="n"/>
-      <c r="AY2" s="449" t="n"/>
-      <c r="AZ2" s="449" t="n"/>
-      <c r="BA2" s="449" t="n"/>
-      <c r="BB2" s="449" t="n"/>
-      <c r="BC2" s="449" t="n"/>
-      <c r="BD2" s="450" t="n"/>
+      <c r="AX2" s="422" t="n"/>
+      <c r="AY2" s="422" t="n"/>
+      <c r="AZ2" s="422" t="n"/>
+      <c r="BA2" s="422" t="n"/>
+      <c r="BB2" s="422" t="n"/>
+      <c r="BC2" s="422" t="n"/>
+      <c r="BD2" s="559" t="n"/>
     </row>
     <row r="3" ht="15" customHeight="1">
-      <c r="A3" s="440" t="n"/>
-      <c r="B3" s="25" t="n"/>
-      <c r="C3" s="25" t="n"/>
-      <c r="D3" s="25" t="n"/>
-      <c r="E3" s="25" t="n"/>
-      <c r="F3" s="25" t="n"/>
-      <c r="G3" s="25" t="n"/>
-      <c r="H3" s="25" t="n"/>
-      <c r="I3" s="25" t="n"/>
-      <c r="J3" s="25" t="n"/>
-      <c r="K3" s="441" t="n"/>
-      <c r="L3" s="442" t="n"/>
-      <c r="M3" s="443" t="n"/>
-      <c r="N3" s="443" t="n"/>
-      <c r="O3" s="443" t="n"/>
-      <c r="P3" s="443" t="n"/>
-      <c r="Q3" s="443" t="n"/>
-      <c r="R3" s="443" t="n"/>
-      <c r="S3" s="443" t="n"/>
-      <c r="T3" s="443" t="n"/>
-      <c r="U3" s="443" t="n"/>
-      <c r="V3" s="443" t="n"/>
-      <c r="W3" s="443" t="n"/>
-      <c r="X3" s="443" t="n"/>
-      <c r="Y3" s="443" t="n"/>
-      <c r="Z3" s="443" t="n"/>
-      <c r="AA3" s="443" t="n"/>
-      <c r="AB3" s="443" t="n"/>
-      <c r="AC3" s="443" t="n"/>
-      <c r="AD3" s="443" t="n"/>
-      <c r="AE3" s="443" t="n"/>
-      <c r="AF3" s="443" t="n"/>
-      <c r="AG3" s="443" t="n"/>
-      <c r="AH3" s="443" t="n"/>
-      <c r="AI3" s="443" t="n"/>
-      <c r="AJ3" s="443" t="n"/>
-      <c r="AK3" s="443" t="n"/>
-      <c r="AL3" s="443" t="n"/>
-      <c r="AM3" s="443" t="n"/>
-      <c r="AN3" s="443" t="n"/>
-      <c r="AO3" s="443" t="n"/>
-      <c r="AP3" s="444" t="n"/>
-      <c r="AQ3" s="445" t="n"/>
-      <c r="AR3" s="446" t="n"/>
-      <c r="AS3" s="446" t="n"/>
-      <c r="AT3" s="446" t="n"/>
-      <c r="AU3" s="446" t="n"/>
-      <c r="AV3" s="447" t="n"/>
-      <c r="AW3" s="448" t="inlineStr">
+      <c r="A3" s="554" t="n"/>
+      <c r="K3" s="555" t="n"/>
+      <c r="L3" s="554" t="n"/>
+      <c r="AP3" s="555" t="n"/>
+      <c r="AQ3" s="556" t="n"/>
+      <c r="AR3" s="422" t="n"/>
+      <c r="AS3" s="422" t="n"/>
+      <c r="AT3" s="422" t="n"/>
+      <c r="AU3" s="422" t="n"/>
+      <c r="AV3" s="557" t="n"/>
+      <c r="AW3" s="558" t="inlineStr">
         <is>
           <t>YYYY-MM-DD</t>
         </is>
       </c>
-      <c r="AX3" s="449" t="n"/>
-      <c r="AY3" s="449" t="n"/>
-      <c r="AZ3" s="449" t="n"/>
-      <c r="BA3" s="449" t="n"/>
-      <c r="BB3" s="449" t="n"/>
-      <c r="BC3" s="449" t="n"/>
-      <c r="BD3" s="450" t="n"/>
+      <c r="AX3" s="422" t="n"/>
+      <c r="AY3" s="422" t="n"/>
+      <c r="AZ3" s="422" t="n"/>
+      <c r="BA3" s="422" t="n"/>
+      <c r="BB3" s="422" t="n"/>
+      <c r="BC3" s="422" t="n"/>
+      <c r="BD3" s="559" t="n"/>
     </row>
     <row r="4" ht="15" customHeight="1">
-      <c r="A4" s="440" t="n"/>
-      <c r="B4" s="25" t="n"/>
-      <c r="C4" s="25" t="n"/>
-      <c r="D4" s="25" t="n"/>
-      <c r="E4" s="25" t="n"/>
-      <c r="F4" s="25" t="n"/>
-      <c r="G4" s="25" t="n"/>
-      <c r="H4" s="25" t="n"/>
-      <c r="I4" s="25" t="n"/>
-      <c r="J4" s="25" t="n"/>
-      <c r="K4" s="441" t="n"/>
-      <c r="L4" s="451" t="inlineStr">
+      <c r="A4" s="554" t="n"/>
+      <c r="K4" s="555" t="n"/>
+      <c r="L4" s="560" t="inlineStr">
         <is>
           <t>Quality Management System · Controlled Document</t>
         </is>
       </c>
-      <c r="M4" s="452" t="n"/>
-      <c r="N4" s="452" t="n"/>
-      <c r="O4" s="452" t="n"/>
-      <c r="P4" s="452" t="n"/>
-      <c r="Q4" s="452" t="n"/>
-      <c r="R4" s="452" t="n"/>
-      <c r="S4" s="452" t="n"/>
-      <c r="T4" s="452" t="n"/>
-      <c r="U4" s="452" t="n"/>
-      <c r="V4" s="452" t="n"/>
-      <c r="W4" s="452" t="n"/>
-      <c r="X4" s="452" t="n"/>
-      <c r="Y4" s="452" t="n"/>
-      <c r="Z4" s="452" t="n"/>
-      <c r="AA4" s="452" t="n"/>
-      <c r="AB4" s="452" t="n"/>
-      <c r="AC4" s="452" t="n"/>
-      <c r="AD4" s="452" t="n"/>
-      <c r="AE4" s="452" t="n"/>
-      <c r="AF4" s="452" t="n"/>
-      <c r="AG4" s="452" t="n"/>
-      <c r="AH4" s="452" t="n"/>
-      <c r="AI4" s="452" t="n"/>
-      <c r="AJ4" s="452" t="n"/>
-      <c r="AK4" s="452" t="n"/>
-      <c r="AL4" s="452" t="n"/>
-      <c r="AM4" s="452" t="n"/>
-      <c r="AN4" s="452" t="n"/>
-      <c r="AO4" s="452" t="n"/>
-      <c r="AP4" s="453" t="n"/>
-      <c r="AQ4" s="445" t="n"/>
-      <c r="AR4" s="446" t="n"/>
-      <c r="AS4" s="446" t="n"/>
-      <c r="AT4" s="446" t="n"/>
-      <c r="AU4" s="446" t="n"/>
-      <c r="AV4" s="447" t="n"/>
-      <c r="AW4" s="448" t="inlineStr">
+      <c r="AP4" s="555" t="n"/>
+      <c r="AQ4" s="556" t="n"/>
+      <c r="AR4" s="422" t="n"/>
+      <c r="AS4" s="422" t="n"/>
+      <c r="AT4" s="422" t="n"/>
+      <c r="AU4" s="422" t="n"/>
+      <c r="AV4" s="557" t="n"/>
+      <c r="AW4" s="558" t="inlineStr">
         <is>
           <t>Warehouse + QA</t>
         </is>
       </c>
-      <c r="AX4" s="449" t="n"/>
-      <c r="AY4" s="449" t="n"/>
-      <c r="AZ4" s="449" t="n"/>
-      <c r="BA4" s="449" t="n"/>
-      <c r="BB4" s="449" t="n"/>
-      <c r="BC4" s="449" t="n"/>
-      <c r="BD4" s="450" t="n"/>
+      <c r="AX4" s="422" t="n"/>
+      <c r="AY4" s="422" t="n"/>
+      <c r="AZ4" s="422" t="n"/>
+      <c r="BA4" s="422" t="n"/>
+      <c r="BB4" s="422" t="n"/>
+      <c r="BC4" s="422" t="n"/>
+      <c r="BD4" s="559" t="n"/>
     </row>
     <row r="5" ht="15" customHeight="1">
-      <c r="A5" s="454" t="n"/>
-      <c r="B5" s="455" t="n"/>
-      <c r="C5" s="455" t="n"/>
-      <c r="D5" s="455" t="n"/>
-      <c r="E5" s="455" t="n"/>
-      <c r="F5" s="455" t="n"/>
-      <c r="G5" s="455" t="n"/>
-      <c r="H5" s="455" t="n"/>
-      <c r="I5" s="455" t="n"/>
-      <c r="J5" s="455" t="n"/>
-      <c r="K5" s="456" t="n"/>
-      <c r="L5" s="457" t="inlineStr">
+      <c r="A5" s="561" t="n"/>
+      <c r="B5" s="562" t="n"/>
+      <c r="C5" s="562" t="n"/>
+      <c r="D5" s="562" t="n"/>
+      <c r="E5" s="562" t="n"/>
+      <c r="F5" s="562" t="n"/>
+      <c r="G5" s="562" t="n"/>
+      <c r="H5" s="562" t="n"/>
+      <c r="I5" s="562" t="n"/>
+      <c r="J5" s="562" t="n"/>
+      <c r="K5" s="563" t="n"/>
+      <c r="L5" s="564" t="inlineStr">
         <is>
           <t>HESEM Engineering · ISO 9001 / AS9100 · Semiconductor Equipment Parts</t>
         </is>
       </c>
-      <c r="M5" s="458" t="n"/>
-      <c r="N5" s="458" t="n"/>
-      <c r="O5" s="458" t="n"/>
-      <c r="P5" s="458" t="n"/>
-      <c r="Q5" s="458" t="n"/>
-      <c r="R5" s="458" t="n"/>
-      <c r="S5" s="458" t="n"/>
-      <c r="T5" s="458" t="n"/>
-      <c r="U5" s="458" t="n"/>
-      <c r="V5" s="458" t="n"/>
-      <c r="W5" s="458" t="n"/>
-      <c r="X5" s="458" t="n"/>
-      <c r="Y5" s="458" t="n"/>
-      <c r="Z5" s="458" t="n"/>
-      <c r="AA5" s="458" t="n"/>
-      <c r="AB5" s="458" t="n"/>
-      <c r="AC5" s="458" t="n"/>
-      <c r="AD5" s="458" t="n"/>
-      <c r="AE5" s="458" t="n"/>
-      <c r="AF5" s="458" t="n"/>
-      <c r="AG5" s="458" t="n"/>
-      <c r="AH5" s="458" t="n"/>
-      <c r="AI5" s="458" t="n"/>
-      <c r="AJ5" s="458" t="n"/>
-      <c r="AK5" s="458" t="n"/>
-      <c r="AL5" s="458" t="n"/>
-      <c r="AM5" s="458" t="n"/>
-      <c r="AN5" s="458" t="n"/>
-      <c r="AO5" s="458" t="n"/>
-      <c r="AP5" s="459" t="n"/>
-      <c r="AQ5" s="460" t="n"/>
-      <c r="AR5" s="461" t="n"/>
-      <c r="AS5" s="461" t="n"/>
-      <c r="AT5" s="461" t="n"/>
-      <c r="AU5" s="461" t="n"/>
-      <c r="AV5" s="462" t="n"/>
-      <c r="AW5" s="463" t="inlineStr">
+      <c r="M5" s="562" t="n"/>
+      <c r="N5" s="562" t="n"/>
+      <c r="O5" s="562" t="n"/>
+      <c r="P5" s="562" t="n"/>
+      <c r="Q5" s="562" t="n"/>
+      <c r="R5" s="562" t="n"/>
+      <c r="S5" s="562" t="n"/>
+      <c r="T5" s="562" t="n"/>
+      <c r="U5" s="562" t="n"/>
+      <c r="V5" s="562" t="n"/>
+      <c r="W5" s="562" t="n"/>
+      <c r="X5" s="562" t="n"/>
+      <c r="Y5" s="562" t="n"/>
+      <c r="Z5" s="562" t="n"/>
+      <c r="AA5" s="562" t="n"/>
+      <c r="AB5" s="562" t="n"/>
+      <c r="AC5" s="562" t="n"/>
+      <c r="AD5" s="562" t="n"/>
+      <c r="AE5" s="562" t="n"/>
+      <c r="AF5" s="562" t="n"/>
+      <c r="AG5" s="562" t="n"/>
+      <c r="AH5" s="562" t="n"/>
+      <c r="AI5" s="562" t="n"/>
+      <c r="AJ5" s="562" t="n"/>
+      <c r="AK5" s="562" t="n"/>
+      <c r="AL5" s="562" t="n"/>
+      <c r="AM5" s="562" t="n"/>
+      <c r="AN5" s="562" t="n"/>
+      <c r="AO5" s="562" t="n"/>
+      <c r="AP5" s="563" t="n"/>
+      <c r="AQ5" s="565" t="n"/>
+      <c r="AR5" s="566" t="n"/>
+      <c r="AS5" s="566" t="n"/>
+      <c r="AT5" s="566" t="n"/>
+      <c r="AU5" s="566" t="n"/>
+      <c r="AV5" s="567" t="n"/>
+      <c r="AW5" s="568" t="inlineStr">
         <is>
           <t>General Manager</t>
         </is>
       </c>
-      <c r="AX5" s="464" t="n"/>
-      <c r="AY5" s="464" t="n"/>
-      <c r="AZ5" s="464" t="n"/>
-      <c r="BA5" s="464" t="n"/>
-      <c r="BB5" s="464" t="n"/>
-      <c r="BC5" s="464" t="n"/>
-      <c r="BD5" s="465" t="n"/>
+      <c r="AX5" s="566" t="n"/>
+      <c r="AY5" s="566" t="n"/>
+      <c r="AZ5" s="566" t="n"/>
+      <c r="BA5" s="566" t="n"/>
+      <c r="BB5" s="566" t="n"/>
+      <c r="BC5" s="566" t="n"/>
+      <c r="BD5" s="569" t="n"/>
     </row>
     <row r="6" ht="1.5" customHeight="1">
       <c r="A6" s="466" t="n"/>
@@ -6532,66 +6937,66 @@
       <c r="BD6" s="466" t="n"/>
     </row>
     <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="467" t="inlineStr">
+      <c r="A7" s="570" t="inlineStr">
         <is>
           <t xml:space="preserve">  1. REFERENCE INFORMATION</t>
         </is>
       </c>
-      <c r="B7" s="468" t="n"/>
-      <c r="C7" s="468" t="n"/>
-      <c r="D7" s="468" t="n"/>
-      <c r="E7" s="468" t="n"/>
-      <c r="F7" s="468" t="n"/>
-      <c r="G7" s="468" t="n"/>
-      <c r="H7" s="468" t="n"/>
-      <c r="I7" s="468" t="n"/>
-      <c r="J7" s="468" t="n"/>
-      <c r="K7" s="468" t="n"/>
-      <c r="L7" s="468" t="n"/>
-      <c r="M7" s="468" t="n"/>
-      <c r="N7" s="468" t="n"/>
-      <c r="O7" s="468" t="n"/>
-      <c r="P7" s="468" t="n"/>
-      <c r="Q7" s="468" t="n"/>
-      <c r="R7" s="468" t="n"/>
-      <c r="S7" s="468" t="n"/>
-      <c r="T7" s="468" t="n"/>
-      <c r="U7" s="468" t="n"/>
-      <c r="V7" s="468" t="n"/>
-      <c r="W7" s="468" t="n"/>
-      <c r="X7" s="468" t="n"/>
-      <c r="Y7" s="468" t="n"/>
-      <c r="Z7" s="468" t="n"/>
-      <c r="AA7" s="468" t="n"/>
-      <c r="AB7" s="468" t="n"/>
-      <c r="AC7" s="468" t="n"/>
-      <c r="AD7" s="468" t="n"/>
-      <c r="AE7" s="468" t="n"/>
-      <c r="AF7" s="468" t="n"/>
-      <c r="AG7" s="468" t="n"/>
-      <c r="AH7" s="468" t="n"/>
-      <c r="AI7" s="468" t="n"/>
-      <c r="AJ7" s="468" t="n"/>
-      <c r="AK7" s="468" t="n"/>
-      <c r="AL7" s="468" t="n"/>
-      <c r="AM7" s="468" t="n"/>
-      <c r="AN7" s="468" t="n"/>
-      <c r="AO7" s="468" t="n"/>
-      <c r="AP7" s="468" t="n"/>
-      <c r="AQ7" s="468" t="n"/>
-      <c r="AR7" s="468" t="n"/>
-      <c r="AS7" s="468" t="n"/>
-      <c r="AT7" s="468" t="n"/>
-      <c r="AU7" s="468" t="n"/>
-      <c r="AV7" s="468" t="n"/>
-      <c r="AW7" s="468" t="n"/>
-      <c r="AX7" s="468" t="n"/>
-      <c r="AY7" s="468" t="n"/>
-      <c r="AZ7" s="468" t="n"/>
-      <c r="BA7" s="468" t="n"/>
-      <c r="BB7" s="468" t="n"/>
-      <c r="BC7" s="468" t="n"/>
-      <c r="BD7" s="469" t="n"/>
+      <c r="B7" s="571" t="n"/>
+      <c r="C7" s="571" t="n"/>
+      <c r="D7" s="571" t="n"/>
+      <c r="E7" s="571" t="n"/>
+      <c r="F7" s="571" t="n"/>
+      <c r="G7" s="571" t="n"/>
+      <c r="H7" s="571" t="n"/>
+      <c r="I7" s="571" t="n"/>
+      <c r="J7" s="571" t="n"/>
+      <c r="K7" s="571" t="n"/>
+      <c r="L7" s="571" t="n"/>
+      <c r="M7" s="571" t="n"/>
+      <c r="N7" s="571" t="n"/>
+      <c r="O7" s="571" t="n"/>
+      <c r="P7" s="571" t="n"/>
+      <c r="Q7" s="571" t="n"/>
+      <c r="R7" s="571" t="n"/>
+      <c r="S7" s="571" t="n"/>
+      <c r="T7" s="571" t="n"/>
+      <c r="U7" s="571" t="n"/>
+      <c r="V7" s="571" t="n"/>
+      <c r="W7" s="571" t="n"/>
+      <c r="X7" s="571" t="n"/>
+      <c r="Y7" s="571" t="n"/>
+      <c r="Z7" s="571" t="n"/>
+      <c r="AA7" s="571" t="n"/>
+      <c r="AB7" s="571" t="n"/>
+      <c r="AC7" s="571" t="n"/>
+      <c r="AD7" s="571" t="n"/>
+      <c r="AE7" s="571" t="n"/>
+      <c r="AF7" s="571" t="n"/>
+      <c r="AG7" s="571" t="n"/>
+      <c r="AH7" s="571" t="n"/>
+      <c r="AI7" s="571" t="n"/>
+      <c r="AJ7" s="571" t="n"/>
+      <c r="AK7" s="571" t="n"/>
+      <c r="AL7" s="571" t="n"/>
+      <c r="AM7" s="571" t="n"/>
+      <c r="AN7" s="571" t="n"/>
+      <c r="AO7" s="571" t="n"/>
+      <c r="AP7" s="571" t="n"/>
+      <c r="AQ7" s="571" t="n"/>
+      <c r="AR7" s="571" t="n"/>
+      <c r="AS7" s="571" t="n"/>
+      <c r="AT7" s="571" t="n"/>
+      <c r="AU7" s="571" t="n"/>
+      <c r="AV7" s="571" t="n"/>
+      <c r="AW7" s="571" t="n"/>
+      <c r="AX7" s="571" t="n"/>
+      <c r="AY7" s="571" t="n"/>
+      <c r="AZ7" s="571" t="n"/>
+      <c r="BA7" s="571" t="n"/>
+      <c r="BB7" s="571" t="n"/>
+      <c r="BC7" s="571" t="n"/>
+      <c r="BD7" s="572" t="n"/>
     </row>
     <row r="8" ht="20" customHeight="1">
       <c r="A8" s="470" t="inlineStr">
@@ -6599,65 +7004,65 @@
           <t>Clean Build Record ID</t>
         </is>
       </c>
-      <c r="B8" s="471" t="n"/>
-      <c r="C8" s="471" t="n"/>
-      <c r="D8" s="471" t="n"/>
-      <c r="E8" s="471" t="n"/>
-      <c r="F8" s="471" t="n"/>
-      <c r="G8" s="471" t="n"/>
-      <c r="H8" s="471" t="n"/>
-      <c r="I8" s="471" t="n"/>
-      <c r="J8" s="471" t="n"/>
+      <c r="B8" s="573" t="n"/>
+      <c r="C8" s="573" t="n"/>
+      <c r="D8" s="573" t="n"/>
+      <c r="E8" s="573" t="n"/>
+      <c r="F8" s="573" t="n"/>
+      <c r="G8" s="573" t="n"/>
+      <c r="H8" s="573" t="n"/>
+      <c r="I8" s="573" t="n"/>
+      <c r="J8" s="573" t="n"/>
       <c r="K8" s="472" t="n"/>
-      <c r="L8" s="473" t="n"/>
-      <c r="M8" s="473" t="n"/>
-      <c r="N8" s="473" t="n"/>
-      <c r="O8" s="473" t="n"/>
-      <c r="P8" s="473" t="n"/>
-      <c r="Q8" s="473" t="n"/>
-      <c r="R8" s="473" t="n"/>
-      <c r="S8" s="473" t="n"/>
-      <c r="T8" s="473" t="n"/>
-      <c r="U8" s="473" t="n"/>
-      <c r="V8" s="473" t="n"/>
-      <c r="W8" s="473" t="n"/>
-      <c r="X8" s="473" t="n"/>
-      <c r="Y8" s="473" t="n"/>
-      <c r="Z8" s="473" t="n"/>
-      <c r="AA8" s="473" t="n"/>
-      <c r="AB8" s="473" t="n"/>
+      <c r="L8" s="574" t="n"/>
+      <c r="M8" s="574" t="n"/>
+      <c r="N8" s="574" t="n"/>
+      <c r="O8" s="574" t="n"/>
+      <c r="P8" s="574" t="n"/>
+      <c r="Q8" s="574" t="n"/>
+      <c r="R8" s="574" t="n"/>
+      <c r="S8" s="574" t="n"/>
+      <c r="T8" s="574" t="n"/>
+      <c r="U8" s="574" t="n"/>
+      <c r="V8" s="574" t="n"/>
+      <c r="W8" s="574" t="n"/>
+      <c r="X8" s="574" t="n"/>
+      <c r="Y8" s="574" t="n"/>
+      <c r="Z8" s="574" t="n"/>
+      <c r="AA8" s="574" t="n"/>
+      <c r="AB8" s="574" t="n"/>
       <c r="AC8" s="474" t="inlineStr">
         <is>
           <t>Release Status</t>
         </is>
       </c>
-      <c r="AD8" s="471" t="n"/>
-      <c r="AE8" s="471" t="n"/>
-      <c r="AF8" s="471" t="n"/>
-      <c r="AG8" s="471" t="n"/>
-      <c r="AH8" s="471" t="n"/>
-      <c r="AI8" s="471" t="n"/>
-      <c r="AJ8" s="471" t="n"/>
-      <c r="AK8" s="471" t="n"/>
-      <c r="AL8" s="471" t="n"/>
-      <c r="AM8" s="472" t="n"/>
-      <c r="AN8" s="473" t="n"/>
-      <c r="AO8" s="473" t="n"/>
-      <c r="AP8" s="473" t="n"/>
-      <c r="AQ8" s="473" t="n"/>
-      <c r="AR8" s="473" t="n"/>
-      <c r="AS8" s="473" t="n"/>
-      <c r="AT8" s="473" t="n"/>
-      <c r="AU8" s="473" t="n"/>
-      <c r="AV8" s="473" t="n"/>
-      <c r="AW8" s="473" t="n"/>
-      <c r="AX8" s="473" t="n"/>
-      <c r="AY8" s="473" t="n"/>
-      <c r="AZ8" s="473" t="n"/>
-      <c r="BA8" s="473" t="n"/>
-      <c r="BB8" s="473" t="n"/>
-      <c r="BC8" s="473" t="n"/>
-      <c r="BD8" s="475" t="n"/>
+      <c r="AD8" s="573" t="n"/>
+      <c r="AE8" s="573" t="n"/>
+      <c r="AF8" s="573" t="n"/>
+      <c r="AG8" s="573" t="n"/>
+      <c r="AH8" s="573" t="n"/>
+      <c r="AI8" s="573" t="n"/>
+      <c r="AJ8" s="573" t="n"/>
+      <c r="AK8" s="573" t="n"/>
+      <c r="AL8" s="573" t="n"/>
+      <c r="AM8" s="575" t="n"/>
+      <c r="AN8" s="574" t="n"/>
+      <c r="AO8" s="574" t="n"/>
+      <c r="AP8" s="574" t="n"/>
+      <c r="AQ8" s="574" t="n"/>
+      <c r="AR8" s="574" t="n"/>
+      <c r="AS8" s="574" t="n"/>
+      <c r="AT8" s="574" t="n"/>
+      <c r="AU8" s="574" t="n"/>
+      <c r="AV8" s="574" t="n"/>
+      <c r="AW8" s="574" t="n"/>
+      <c r="AX8" s="574" t="n"/>
+      <c r="AY8" s="574" t="n"/>
+      <c r="AZ8" s="574" t="n"/>
+      <c r="BA8" s="574" t="n"/>
+      <c r="BB8" s="574" t="n"/>
+      <c r="BC8" s="574" t="n"/>
+      <c r="BD8" s="576" t="n"/>
     </row>
     <row r="9" ht="20" customHeight="1">
       <c r="A9" s="476" t="inlineStr">
@@ -6665,65 +7070,65 @@
           <t>Job / Part / Package Class</t>
         </is>
       </c>
-      <c r="B9" s="344" t="n"/>
-      <c r="C9" s="344" t="n"/>
-      <c r="D9" s="344" t="n"/>
-      <c r="E9" s="344" t="n"/>
-      <c r="F9" s="344" t="n"/>
-      <c r="G9" s="344" t="n"/>
-      <c r="H9" s="344" t="n"/>
-      <c r="I9" s="344" t="n"/>
-      <c r="J9" s="344" t="n"/>
+      <c r="B9" s="423" t="n"/>
+      <c r="C9" s="423" t="n"/>
+      <c r="D9" s="423" t="n"/>
+      <c r="E9" s="423" t="n"/>
+      <c r="F9" s="423" t="n"/>
+      <c r="G9" s="423" t="n"/>
+      <c r="H9" s="423" t="n"/>
+      <c r="I9" s="423" t="n"/>
+      <c r="J9" s="423" t="n"/>
       <c r="K9" s="477" t="n"/>
-      <c r="L9" s="362" t="n"/>
-      <c r="M9" s="362" t="n"/>
-      <c r="N9" s="362" t="n"/>
-      <c r="O9" s="362" t="n"/>
-      <c r="P9" s="362" t="n"/>
-      <c r="Q9" s="362" t="n"/>
-      <c r="R9" s="362" t="n"/>
-      <c r="S9" s="362" t="n"/>
-      <c r="T9" s="362" t="n"/>
-      <c r="U9" s="362" t="n"/>
-      <c r="V9" s="362" t="n"/>
-      <c r="W9" s="362" t="n"/>
-      <c r="X9" s="362" t="n"/>
-      <c r="Y9" s="362" t="n"/>
-      <c r="Z9" s="362" t="n"/>
-      <c r="AA9" s="362" t="n"/>
-      <c r="AB9" s="362" t="n"/>
+      <c r="L9" s="577" t="n"/>
+      <c r="M9" s="577" t="n"/>
+      <c r="N9" s="577" t="n"/>
+      <c r="O9" s="577" t="n"/>
+      <c r="P9" s="577" t="n"/>
+      <c r="Q9" s="577" t="n"/>
+      <c r="R9" s="577" t="n"/>
+      <c r="S9" s="577" t="n"/>
+      <c r="T9" s="577" t="n"/>
+      <c r="U9" s="577" t="n"/>
+      <c r="V9" s="577" t="n"/>
+      <c r="W9" s="577" t="n"/>
+      <c r="X9" s="577" t="n"/>
+      <c r="Y9" s="577" t="n"/>
+      <c r="Z9" s="577" t="n"/>
+      <c r="AA9" s="577" t="n"/>
+      <c r="AB9" s="577" t="n"/>
       <c r="AC9" s="478" t="inlineStr">
         <is>
           <t>Clean Class</t>
         </is>
       </c>
-      <c r="AD9" s="344" t="n"/>
-      <c r="AE9" s="344" t="n"/>
-      <c r="AF9" s="344" t="n"/>
-      <c r="AG9" s="344" t="n"/>
-      <c r="AH9" s="344" t="n"/>
-      <c r="AI9" s="344" t="n"/>
-      <c r="AJ9" s="344" t="n"/>
-      <c r="AK9" s="344" t="n"/>
-      <c r="AL9" s="344" t="n"/>
-      <c r="AM9" s="477" t="n"/>
-      <c r="AN9" s="362" t="n"/>
-      <c r="AO9" s="362" t="n"/>
-      <c r="AP9" s="362" t="n"/>
-      <c r="AQ9" s="362" t="n"/>
-      <c r="AR9" s="362" t="n"/>
-      <c r="AS9" s="362" t="n"/>
-      <c r="AT9" s="362" t="n"/>
-      <c r="AU9" s="362" t="n"/>
-      <c r="AV9" s="362" t="n"/>
-      <c r="AW9" s="362" t="n"/>
-      <c r="AX9" s="362" t="n"/>
-      <c r="AY9" s="362" t="n"/>
-      <c r="AZ9" s="362" t="n"/>
-      <c r="BA9" s="362" t="n"/>
-      <c r="BB9" s="362" t="n"/>
-      <c r="BC9" s="362" t="n"/>
-      <c r="BD9" s="479" t="n"/>
+      <c r="AD9" s="423" t="n"/>
+      <c r="AE9" s="423" t="n"/>
+      <c r="AF9" s="423" t="n"/>
+      <c r="AG9" s="423" t="n"/>
+      <c r="AH9" s="423" t="n"/>
+      <c r="AI9" s="423" t="n"/>
+      <c r="AJ9" s="423" t="n"/>
+      <c r="AK9" s="423" t="n"/>
+      <c r="AL9" s="423" t="n"/>
+      <c r="AM9" s="578" t="n"/>
+      <c r="AN9" s="577" t="n"/>
+      <c r="AO9" s="577" t="n"/>
+      <c r="AP9" s="577" t="n"/>
+      <c r="AQ9" s="577" t="n"/>
+      <c r="AR9" s="577" t="n"/>
+      <c r="AS9" s="577" t="n"/>
+      <c r="AT9" s="577" t="n"/>
+      <c r="AU9" s="577" t="n"/>
+      <c r="AV9" s="577" t="n"/>
+      <c r="AW9" s="577" t="n"/>
+      <c r="AX9" s="577" t="n"/>
+      <c r="AY9" s="577" t="n"/>
+      <c r="AZ9" s="577" t="n"/>
+      <c r="BA9" s="577" t="n"/>
+      <c r="BB9" s="577" t="n"/>
+      <c r="BC9" s="577" t="n"/>
+      <c r="BD9" s="579" t="n"/>
     </row>
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="476" t="inlineStr">
@@ -6731,65 +7136,65 @@
           <t>Bagging Configuration</t>
         </is>
       </c>
-      <c r="B10" s="344" t="n"/>
-      <c r="C10" s="344" t="n"/>
-      <c r="D10" s="344" t="n"/>
-      <c r="E10" s="344" t="n"/>
-      <c r="F10" s="344" t="n"/>
-      <c r="G10" s="344" t="n"/>
-      <c r="H10" s="344" t="n"/>
-      <c r="I10" s="344" t="n"/>
-      <c r="J10" s="344" t="n"/>
+      <c r="B10" s="423" t="n"/>
+      <c r="C10" s="423" t="n"/>
+      <c r="D10" s="423" t="n"/>
+      <c r="E10" s="423" t="n"/>
+      <c r="F10" s="423" t="n"/>
+      <c r="G10" s="423" t="n"/>
+      <c r="H10" s="423" t="n"/>
+      <c r="I10" s="423" t="n"/>
+      <c r="J10" s="423" t="n"/>
       <c r="K10" s="477" t="n"/>
-      <c r="L10" s="362" t="n"/>
-      <c r="M10" s="362" t="n"/>
-      <c r="N10" s="362" t="n"/>
-      <c r="O10" s="362" t="n"/>
-      <c r="P10" s="362" t="n"/>
-      <c r="Q10" s="362" t="n"/>
-      <c r="R10" s="362" t="n"/>
-      <c r="S10" s="362" t="n"/>
-      <c r="T10" s="362" t="n"/>
-      <c r="U10" s="362" t="n"/>
-      <c r="V10" s="362" t="n"/>
-      <c r="W10" s="362" t="n"/>
-      <c r="X10" s="362" t="n"/>
-      <c r="Y10" s="362" t="n"/>
-      <c r="Z10" s="362" t="n"/>
-      <c r="AA10" s="362" t="n"/>
-      <c r="AB10" s="362" t="n"/>
+      <c r="L10" s="577" t="n"/>
+      <c r="M10" s="577" t="n"/>
+      <c r="N10" s="577" t="n"/>
+      <c r="O10" s="577" t="n"/>
+      <c r="P10" s="577" t="n"/>
+      <c r="Q10" s="577" t="n"/>
+      <c r="R10" s="577" t="n"/>
+      <c r="S10" s="577" t="n"/>
+      <c r="T10" s="577" t="n"/>
+      <c r="U10" s="577" t="n"/>
+      <c r="V10" s="577" t="n"/>
+      <c r="W10" s="577" t="n"/>
+      <c r="X10" s="577" t="n"/>
+      <c r="Y10" s="577" t="n"/>
+      <c r="Z10" s="577" t="n"/>
+      <c r="AA10" s="577" t="n"/>
+      <c r="AB10" s="577" t="n"/>
       <c r="AC10" s="478" t="inlineStr">
         <is>
           <t>Line Clearance / Gowning</t>
         </is>
       </c>
-      <c r="AD10" s="344" t="n"/>
-      <c r="AE10" s="344" t="n"/>
-      <c r="AF10" s="344" t="n"/>
-      <c r="AG10" s="344" t="n"/>
-      <c r="AH10" s="344" t="n"/>
-      <c r="AI10" s="344" t="n"/>
-      <c r="AJ10" s="344" t="n"/>
-      <c r="AK10" s="344" t="n"/>
-      <c r="AL10" s="344" t="n"/>
-      <c r="AM10" s="477" t="n"/>
-      <c r="AN10" s="362" t="n"/>
-      <c r="AO10" s="362" t="n"/>
-      <c r="AP10" s="362" t="n"/>
-      <c r="AQ10" s="362" t="n"/>
-      <c r="AR10" s="362" t="n"/>
-      <c r="AS10" s="362" t="n"/>
-      <c r="AT10" s="362" t="n"/>
-      <c r="AU10" s="362" t="n"/>
-      <c r="AV10" s="362" t="n"/>
-      <c r="AW10" s="362" t="n"/>
-      <c r="AX10" s="362" t="n"/>
-      <c r="AY10" s="362" t="n"/>
-      <c r="AZ10" s="362" t="n"/>
-      <c r="BA10" s="362" t="n"/>
-      <c r="BB10" s="362" t="n"/>
-      <c r="BC10" s="362" t="n"/>
-      <c r="BD10" s="479" t="n"/>
+      <c r="AD10" s="423" t="n"/>
+      <c r="AE10" s="423" t="n"/>
+      <c r="AF10" s="423" t="n"/>
+      <c r="AG10" s="423" t="n"/>
+      <c r="AH10" s="423" t="n"/>
+      <c r="AI10" s="423" t="n"/>
+      <c r="AJ10" s="423" t="n"/>
+      <c r="AK10" s="423" t="n"/>
+      <c r="AL10" s="423" t="n"/>
+      <c r="AM10" s="578" t="n"/>
+      <c r="AN10" s="577" t="n"/>
+      <c r="AO10" s="577" t="n"/>
+      <c r="AP10" s="577" t="n"/>
+      <c r="AQ10" s="577" t="n"/>
+      <c r="AR10" s="577" t="n"/>
+      <c r="AS10" s="577" t="n"/>
+      <c r="AT10" s="577" t="n"/>
+      <c r="AU10" s="577" t="n"/>
+      <c r="AV10" s="577" t="n"/>
+      <c r="AW10" s="577" t="n"/>
+      <c r="AX10" s="577" t="n"/>
+      <c r="AY10" s="577" t="n"/>
+      <c r="AZ10" s="577" t="n"/>
+      <c r="BA10" s="577" t="n"/>
+      <c r="BB10" s="577" t="n"/>
+      <c r="BC10" s="577" t="n"/>
+      <c r="BD10" s="579" t="n"/>
     </row>
     <row r="11" ht="26" customHeight="1">
       <c r="A11" s="476" t="inlineStr">
@@ -6797,65 +7202,65 @@
           <t>Prepared by / Date-Time</t>
         </is>
       </c>
-      <c r="B11" s="344" t="n"/>
-      <c r="C11" s="344" t="n"/>
-      <c r="D11" s="344" t="n"/>
-      <c r="E11" s="344" t="n"/>
-      <c r="F11" s="344" t="n"/>
-      <c r="G11" s="344" t="n"/>
-      <c r="H11" s="344" t="n"/>
-      <c r="I11" s="344" t="n"/>
-      <c r="J11" s="344" t="n"/>
+      <c r="B11" s="423" t="n"/>
+      <c r="C11" s="423" t="n"/>
+      <c r="D11" s="423" t="n"/>
+      <c r="E11" s="423" t="n"/>
+      <c r="F11" s="423" t="n"/>
+      <c r="G11" s="423" t="n"/>
+      <c r="H11" s="423" t="n"/>
+      <c r="I11" s="423" t="n"/>
+      <c r="J11" s="423" t="n"/>
       <c r="K11" s="477" t="n"/>
-      <c r="L11" s="362" t="n"/>
-      <c r="M11" s="362" t="n"/>
-      <c r="N11" s="362" t="n"/>
-      <c r="O11" s="362" t="n"/>
-      <c r="P11" s="362" t="n"/>
-      <c r="Q11" s="362" t="n"/>
-      <c r="R11" s="362" t="n"/>
-      <c r="S11" s="362" t="n"/>
-      <c r="T11" s="362" t="n"/>
-      <c r="U11" s="362" t="n"/>
-      <c r="V11" s="362" t="n"/>
-      <c r="W11" s="362" t="n"/>
-      <c r="X11" s="362" t="n"/>
-      <c r="Y11" s="362" t="n"/>
-      <c r="Z11" s="362" t="n"/>
-      <c r="AA11" s="362" t="n"/>
-      <c r="AB11" s="362" t="n"/>
+      <c r="L11" s="577" t="n"/>
+      <c r="M11" s="577" t="n"/>
+      <c r="N11" s="577" t="n"/>
+      <c r="O11" s="577" t="n"/>
+      <c r="P11" s="577" t="n"/>
+      <c r="Q11" s="577" t="n"/>
+      <c r="R11" s="577" t="n"/>
+      <c r="S11" s="577" t="n"/>
+      <c r="T11" s="577" t="n"/>
+      <c r="U11" s="577" t="n"/>
+      <c r="V11" s="577" t="n"/>
+      <c r="W11" s="577" t="n"/>
+      <c r="X11" s="577" t="n"/>
+      <c r="Y11" s="577" t="n"/>
+      <c r="Z11" s="577" t="n"/>
+      <c r="AA11" s="577" t="n"/>
+      <c r="AB11" s="577" t="n"/>
       <c r="AC11" s="478" t="inlineStr">
         <is>
           <t>Warehouse Owner</t>
         </is>
       </c>
-      <c r="AD11" s="344" t="n"/>
-      <c r="AE11" s="344" t="n"/>
-      <c r="AF11" s="344" t="n"/>
-      <c r="AG11" s="344" t="n"/>
-      <c r="AH11" s="344" t="n"/>
-      <c r="AI11" s="344" t="n"/>
-      <c r="AJ11" s="344" t="n"/>
-      <c r="AK11" s="344" t="n"/>
-      <c r="AL11" s="344" t="n"/>
-      <c r="AM11" s="477" t="n"/>
-      <c r="AN11" s="362" t="n"/>
-      <c r="AO11" s="362" t="n"/>
-      <c r="AP11" s="362" t="n"/>
-      <c r="AQ11" s="362" t="n"/>
-      <c r="AR11" s="362" t="n"/>
-      <c r="AS11" s="362" t="n"/>
-      <c r="AT11" s="362" t="n"/>
-      <c r="AU11" s="362" t="n"/>
-      <c r="AV11" s="362" t="n"/>
-      <c r="AW11" s="362" t="n"/>
-      <c r="AX11" s="362" t="n"/>
-      <c r="AY11" s="362" t="n"/>
-      <c r="AZ11" s="362" t="n"/>
-      <c r="BA11" s="362" t="n"/>
-      <c r="BB11" s="362" t="n"/>
-      <c r="BC11" s="362" t="n"/>
-      <c r="BD11" s="479" t="n"/>
+      <c r="AD11" s="423" t="n"/>
+      <c r="AE11" s="423" t="n"/>
+      <c r="AF11" s="423" t="n"/>
+      <c r="AG11" s="423" t="n"/>
+      <c r="AH11" s="423" t="n"/>
+      <c r="AI11" s="423" t="n"/>
+      <c r="AJ11" s="423" t="n"/>
+      <c r="AK11" s="423" t="n"/>
+      <c r="AL11" s="423" t="n"/>
+      <c r="AM11" s="578" t="n"/>
+      <c r="AN11" s="577" t="n"/>
+      <c r="AO11" s="577" t="n"/>
+      <c r="AP11" s="577" t="n"/>
+      <c r="AQ11" s="577" t="n"/>
+      <c r="AR11" s="577" t="n"/>
+      <c r="AS11" s="577" t="n"/>
+      <c r="AT11" s="577" t="n"/>
+      <c r="AU11" s="577" t="n"/>
+      <c r="AV11" s="577" t="n"/>
+      <c r="AW11" s="577" t="n"/>
+      <c r="AX11" s="577" t="n"/>
+      <c r="AY11" s="577" t="n"/>
+      <c r="AZ11" s="577" t="n"/>
+      <c r="BA11" s="577" t="n"/>
+      <c r="BB11" s="577" t="n"/>
+      <c r="BC11" s="577" t="n"/>
+      <c r="BD11" s="579" t="n"/>
     </row>
     <row r="12" ht="20" customHeight="1">
       <c r="A12" s="480" t="inlineStr">
@@ -6863,65 +7268,65 @@
           <t>Evidence Package Ref</t>
         </is>
       </c>
-      <c r="B12" s="481" t="n"/>
-      <c r="C12" s="481" t="n"/>
-      <c r="D12" s="481" t="n"/>
-      <c r="E12" s="481" t="n"/>
-      <c r="F12" s="481" t="n"/>
-      <c r="G12" s="481" t="n"/>
-      <c r="H12" s="481" t="n"/>
-      <c r="I12" s="481" t="n"/>
-      <c r="J12" s="481" t="n"/>
+      <c r="B12" s="566" t="n"/>
+      <c r="C12" s="566" t="n"/>
+      <c r="D12" s="566" t="n"/>
+      <c r="E12" s="566" t="n"/>
+      <c r="F12" s="566" t="n"/>
+      <c r="G12" s="566" t="n"/>
+      <c r="H12" s="566" t="n"/>
+      <c r="I12" s="566" t="n"/>
+      <c r="J12" s="566" t="n"/>
       <c r="K12" s="482" t="n"/>
-      <c r="L12" s="483" t="n"/>
-      <c r="M12" s="483" t="n"/>
-      <c r="N12" s="483" t="n"/>
-      <c r="O12" s="483" t="n"/>
-      <c r="P12" s="483" t="n"/>
-      <c r="Q12" s="483" t="n"/>
-      <c r="R12" s="483" t="n"/>
-      <c r="S12" s="483" t="n"/>
-      <c r="T12" s="483" t="n"/>
-      <c r="U12" s="483" t="n"/>
-      <c r="V12" s="483" t="n"/>
-      <c r="W12" s="483" t="n"/>
-      <c r="X12" s="483" t="n"/>
-      <c r="Y12" s="483" t="n"/>
-      <c r="Z12" s="483" t="n"/>
-      <c r="AA12" s="483" t="n"/>
-      <c r="AB12" s="483" t="n"/>
+      <c r="L12" s="580" t="n"/>
+      <c r="M12" s="580" t="n"/>
+      <c r="N12" s="580" t="n"/>
+      <c r="O12" s="580" t="n"/>
+      <c r="P12" s="580" t="n"/>
+      <c r="Q12" s="580" t="n"/>
+      <c r="R12" s="580" t="n"/>
+      <c r="S12" s="580" t="n"/>
+      <c r="T12" s="580" t="n"/>
+      <c r="U12" s="580" t="n"/>
+      <c r="V12" s="580" t="n"/>
+      <c r="W12" s="580" t="n"/>
+      <c r="X12" s="580" t="n"/>
+      <c r="Y12" s="580" t="n"/>
+      <c r="Z12" s="580" t="n"/>
+      <c r="AA12" s="580" t="n"/>
+      <c r="AB12" s="580" t="n"/>
       <c r="AC12" s="484" t="inlineStr">
         <is>
           <t>Record Status</t>
         </is>
       </c>
-      <c r="AD12" s="481" t="n"/>
-      <c r="AE12" s="481" t="n"/>
-      <c r="AF12" s="481" t="n"/>
-      <c r="AG12" s="481" t="n"/>
-      <c r="AH12" s="481" t="n"/>
-      <c r="AI12" s="481" t="n"/>
-      <c r="AJ12" s="481" t="n"/>
-      <c r="AK12" s="481" t="n"/>
-      <c r="AL12" s="481" t="n"/>
-      <c r="AM12" s="482" t="n"/>
-      <c r="AN12" s="483" t="n"/>
-      <c r="AO12" s="483" t="n"/>
-      <c r="AP12" s="483" t="n"/>
-      <c r="AQ12" s="483" t="n"/>
-      <c r="AR12" s="483" t="n"/>
-      <c r="AS12" s="483" t="n"/>
-      <c r="AT12" s="483" t="n"/>
-      <c r="AU12" s="483" t="n"/>
-      <c r="AV12" s="483" t="n"/>
-      <c r="AW12" s="483" t="n"/>
-      <c r="AX12" s="483" t="n"/>
-      <c r="AY12" s="483" t="n"/>
-      <c r="AZ12" s="483" t="n"/>
-      <c r="BA12" s="483" t="n"/>
-      <c r="BB12" s="483" t="n"/>
-      <c r="BC12" s="483" t="n"/>
-      <c r="BD12" s="485" t="n"/>
+      <c r="AD12" s="566" t="n"/>
+      <c r="AE12" s="566" t="n"/>
+      <c r="AF12" s="566" t="n"/>
+      <c r="AG12" s="566" t="n"/>
+      <c r="AH12" s="566" t="n"/>
+      <c r="AI12" s="566" t="n"/>
+      <c r="AJ12" s="566" t="n"/>
+      <c r="AK12" s="566" t="n"/>
+      <c r="AL12" s="566" t="n"/>
+      <c r="AM12" s="581" t="n"/>
+      <c r="AN12" s="580" t="n"/>
+      <c r="AO12" s="580" t="n"/>
+      <c r="AP12" s="580" t="n"/>
+      <c r="AQ12" s="580" t="n"/>
+      <c r="AR12" s="580" t="n"/>
+      <c r="AS12" s="580" t="n"/>
+      <c r="AT12" s="580" t="n"/>
+      <c r="AU12" s="580" t="n"/>
+      <c r="AV12" s="580" t="n"/>
+      <c r="AW12" s="580" t="n"/>
+      <c r="AX12" s="580" t="n"/>
+      <c r="AY12" s="580" t="n"/>
+      <c r="AZ12" s="580" t="n"/>
+      <c r="BA12" s="580" t="n"/>
+      <c r="BB12" s="580" t="n"/>
+      <c r="BC12" s="580" t="n"/>
+      <c r="BD12" s="582" t="n"/>
     </row>
     <row r="13" ht="3" customHeight="1">
       <c r="A13" s="353" t="n"/>
@@ -6982,66 +7387,66 @@
       <c r="BD13" s="353" t="n"/>
     </row>
     <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="467" t="inlineStr">
+      <c r="A14" s="570" t="inlineStr">
         <is>
           <t xml:space="preserve">  2. CLEAN BUILD / BAGGING VERIFICATION</t>
         </is>
       </c>
-      <c r="B14" s="468" t="n"/>
-      <c r="C14" s="468" t="n"/>
-      <c r="D14" s="468" t="n"/>
-      <c r="E14" s="468" t="n"/>
-      <c r="F14" s="468" t="n"/>
-      <c r="G14" s="468" t="n"/>
-      <c r="H14" s="468" t="n"/>
-      <c r="I14" s="468" t="n"/>
-      <c r="J14" s="468" t="n"/>
-      <c r="K14" s="468" t="n"/>
-      <c r="L14" s="468" t="n"/>
-      <c r="M14" s="468" t="n"/>
-      <c r="N14" s="468" t="n"/>
-      <c r="O14" s="468" t="n"/>
-      <c r="P14" s="468" t="n"/>
-      <c r="Q14" s="468" t="n"/>
-      <c r="R14" s="468" t="n"/>
-      <c r="S14" s="468" t="n"/>
-      <c r="T14" s="468" t="n"/>
-      <c r="U14" s="468" t="n"/>
-      <c r="V14" s="468" t="n"/>
-      <c r="W14" s="468" t="n"/>
-      <c r="X14" s="468" t="n"/>
-      <c r="Y14" s="468" t="n"/>
-      <c r="Z14" s="468" t="n"/>
-      <c r="AA14" s="468" t="n"/>
-      <c r="AB14" s="468" t="n"/>
-      <c r="AC14" s="468" t="n"/>
-      <c r="AD14" s="468" t="n"/>
-      <c r="AE14" s="468" t="n"/>
-      <c r="AF14" s="468" t="n"/>
-      <c r="AG14" s="468" t="n"/>
-      <c r="AH14" s="468" t="n"/>
-      <c r="AI14" s="468" t="n"/>
-      <c r="AJ14" s="468" t="n"/>
-      <c r="AK14" s="468" t="n"/>
-      <c r="AL14" s="468" t="n"/>
-      <c r="AM14" s="468" t="n"/>
-      <c r="AN14" s="468" t="n"/>
-      <c r="AO14" s="468" t="n"/>
-      <c r="AP14" s="468" t="n"/>
-      <c r="AQ14" s="468" t="n"/>
-      <c r="AR14" s="468" t="n"/>
-      <c r="AS14" s="468" t="n"/>
-      <c r="AT14" s="468" t="n"/>
-      <c r="AU14" s="468" t="n"/>
-      <c r="AV14" s="468" t="n"/>
-      <c r="AW14" s="468" t="n"/>
-      <c r="AX14" s="468" t="n"/>
-      <c r="AY14" s="468" t="n"/>
-      <c r="AZ14" s="468" t="n"/>
-      <c r="BA14" s="468" t="n"/>
-      <c r="BB14" s="468" t="n"/>
-      <c r="BC14" s="468" t="n"/>
-      <c r="BD14" s="469" t="n"/>
+      <c r="B14" s="571" t="n"/>
+      <c r="C14" s="571" t="n"/>
+      <c r="D14" s="571" t="n"/>
+      <c r="E14" s="571" t="n"/>
+      <c r="F14" s="571" t="n"/>
+      <c r="G14" s="571" t="n"/>
+      <c r="H14" s="571" t="n"/>
+      <c r="I14" s="571" t="n"/>
+      <c r="J14" s="571" t="n"/>
+      <c r="K14" s="571" t="n"/>
+      <c r="L14" s="571" t="n"/>
+      <c r="M14" s="571" t="n"/>
+      <c r="N14" s="571" t="n"/>
+      <c r="O14" s="571" t="n"/>
+      <c r="P14" s="571" t="n"/>
+      <c r="Q14" s="571" t="n"/>
+      <c r="R14" s="571" t="n"/>
+      <c r="S14" s="571" t="n"/>
+      <c r="T14" s="571" t="n"/>
+      <c r="U14" s="571" t="n"/>
+      <c r="V14" s="571" t="n"/>
+      <c r="W14" s="571" t="n"/>
+      <c r="X14" s="571" t="n"/>
+      <c r="Y14" s="571" t="n"/>
+      <c r="Z14" s="571" t="n"/>
+      <c r="AA14" s="571" t="n"/>
+      <c r="AB14" s="571" t="n"/>
+      <c r="AC14" s="571" t="n"/>
+      <c r="AD14" s="571" t="n"/>
+      <c r="AE14" s="571" t="n"/>
+      <c r="AF14" s="571" t="n"/>
+      <c r="AG14" s="571" t="n"/>
+      <c r="AH14" s="571" t="n"/>
+      <c r="AI14" s="571" t="n"/>
+      <c r="AJ14" s="571" t="n"/>
+      <c r="AK14" s="571" t="n"/>
+      <c r="AL14" s="571" t="n"/>
+      <c r="AM14" s="571" t="n"/>
+      <c r="AN14" s="571" t="n"/>
+      <c r="AO14" s="571" t="n"/>
+      <c r="AP14" s="571" t="n"/>
+      <c r="AQ14" s="571" t="n"/>
+      <c r="AR14" s="571" t="n"/>
+      <c r="AS14" s="571" t="n"/>
+      <c r="AT14" s="571" t="n"/>
+      <c r="AU14" s="571" t="n"/>
+      <c r="AV14" s="571" t="n"/>
+      <c r="AW14" s="571" t="n"/>
+      <c r="AX14" s="571" t="n"/>
+      <c r="AY14" s="571" t="n"/>
+      <c r="AZ14" s="571" t="n"/>
+      <c r="BA14" s="571" t="n"/>
+      <c r="BB14" s="571" t="n"/>
+      <c r="BC14" s="571" t="n"/>
+      <c r="BD14" s="572" t="n"/>
     </row>
     <row r="15" ht="18" customHeight="1">
       <c r="A15" s="486" t="inlineStr">
@@ -7049,573 +7454,573 @@
           <t>#</t>
         </is>
       </c>
-      <c r="B15" s="487" t="n"/>
-      <c r="C15" s="487" t="n"/>
+      <c r="B15" s="571" t="n"/>
+      <c r="C15" s="571" t="n"/>
       <c r="D15" s="488" t="inlineStr">
         <is>
           <t>Cat.</t>
         </is>
       </c>
-      <c r="E15" s="487" t="n"/>
-      <c r="F15" s="487" t="n"/>
-      <c r="G15" s="487" t="n"/>
+      <c r="E15" s="571" t="n"/>
+      <c r="F15" s="571" t="n"/>
+      <c r="G15" s="571" t="n"/>
       <c r="H15" s="488" t="inlineStr">
         <is>
           <t>Clean Build / Bagging Requirement</t>
         </is>
       </c>
-      <c r="I15" s="487" t="n"/>
-      <c r="J15" s="487" t="n"/>
-      <c r="K15" s="487" t="n"/>
-      <c r="L15" s="487" t="n"/>
-      <c r="M15" s="487" t="n"/>
-      <c r="N15" s="487" t="n"/>
-      <c r="O15" s="487" t="n"/>
-      <c r="P15" s="487" t="n"/>
-      <c r="Q15" s="487" t="n"/>
-      <c r="R15" s="487" t="n"/>
-      <c r="S15" s="487" t="n"/>
-      <c r="T15" s="487" t="n"/>
-      <c r="U15" s="487" t="n"/>
-      <c r="V15" s="487" t="n"/>
-      <c r="W15" s="487" t="n"/>
-      <c r="X15" s="487" t="n"/>
-      <c r="Y15" s="487" t="n"/>
-      <c r="Z15" s="487" t="n"/>
+      <c r="I15" s="571" t="n"/>
+      <c r="J15" s="571" t="n"/>
+      <c r="K15" s="571" t="n"/>
+      <c r="L15" s="571" t="n"/>
+      <c r="M15" s="571" t="n"/>
+      <c r="N15" s="571" t="n"/>
+      <c r="O15" s="571" t="n"/>
+      <c r="P15" s="571" t="n"/>
+      <c r="Q15" s="571" t="n"/>
+      <c r="R15" s="571" t="n"/>
+      <c r="S15" s="571" t="n"/>
+      <c r="T15" s="571" t="n"/>
+      <c r="U15" s="571" t="n"/>
+      <c r="V15" s="571" t="n"/>
+      <c r="W15" s="571" t="n"/>
+      <c r="X15" s="571" t="n"/>
+      <c r="Y15" s="571" t="n"/>
+      <c r="Z15" s="571" t="n"/>
       <c r="AA15" s="488" t="inlineStr">
         <is>
           <t>Evidence / Method</t>
         </is>
       </c>
-      <c r="AB15" s="487" t="n"/>
-      <c r="AC15" s="487" t="n"/>
-      <c r="AD15" s="487" t="n"/>
-      <c r="AE15" s="487" t="n"/>
-      <c r="AF15" s="487" t="n"/>
-      <c r="AG15" s="487" t="n"/>
-      <c r="AH15" s="487" t="n"/>
-      <c r="AI15" s="487" t="n"/>
-      <c r="AJ15" s="487" t="n"/>
-      <c r="AK15" s="487" t="n"/>
-      <c r="AL15" s="487" t="n"/>
-      <c r="AM15" s="487" t="n"/>
-      <c r="AN15" s="487" t="n"/>
-      <c r="AO15" s="487" t="n"/>
-      <c r="AP15" s="487" t="n"/>
-      <c r="AQ15" s="487" t="n"/>
+      <c r="AB15" s="571" t="n"/>
+      <c r="AC15" s="571" t="n"/>
+      <c r="AD15" s="571" t="n"/>
+      <c r="AE15" s="571" t="n"/>
+      <c r="AF15" s="571" t="n"/>
+      <c r="AG15" s="571" t="n"/>
+      <c r="AH15" s="571" t="n"/>
+      <c r="AI15" s="571" t="n"/>
+      <c r="AJ15" s="571" t="n"/>
+      <c r="AK15" s="571" t="n"/>
+      <c r="AL15" s="571" t="n"/>
+      <c r="AM15" s="571" t="n"/>
+      <c r="AN15" s="571" t="n"/>
+      <c r="AO15" s="571" t="n"/>
+      <c r="AP15" s="571" t="n"/>
+      <c r="AQ15" s="571" t="n"/>
       <c r="AR15" s="488" t="inlineStr">
         <is>
           <t>Result</t>
         </is>
       </c>
-      <c r="AS15" s="487" t="n"/>
-      <c r="AT15" s="487" t="n"/>
-      <c r="AU15" s="487" t="n"/>
-      <c r="AV15" s="487" t="n"/>
-      <c r="AW15" s="487" t="n"/>
+      <c r="AS15" s="571" t="n"/>
+      <c r="AT15" s="571" t="n"/>
+      <c r="AU15" s="571" t="n"/>
+      <c r="AV15" s="571" t="n"/>
+      <c r="AW15" s="571" t="n"/>
       <c r="AX15" s="488" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="AY15" s="487" t="n"/>
-      <c r="AZ15" s="487" t="n"/>
-      <c r="BA15" s="487" t="n"/>
-      <c r="BB15" s="488" t="inlineStr">
+      <c r="AY15" s="571" t="n"/>
+      <c r="AZ15" s="571" t="n"/>
+      <c r="BA15" s="571" t="n"/>
+      <c r="BB15" s="583" t="inlineStr">
         <is>
           <t>Ref.</t>
         </is>
       </c>
-      <c r="BC15" s="487" t="n"/>
-      <c r="BD15" s="489" t="n"/>
+      <c r="BC15" s="571" t="n"/>
+      <c r="BD15" s="572" t="n"/>
     </row>
     <row r="16" ht="20" customHeight="1">
       <c r="A16" s="490">
         <f>ROW()-ROW($A$16)+1</f>
         <v/>
       </c>
-      <c r="B16" s="471" t="n"/>
-      <c r="C16" s="471" t="n"/>
+      <c r="B16" s="573" t="n"/>
+      <c r="C16" s="573" t="n"/>
       <c r="D16" s="491" t="n"/>
-      <c r="E16" s="473" t="n"/>
-      <c r="F16" s="473" t="n"/>
-      <c r="G16" s="473" t="n"/>
+      <c r="E16" s="574" t="n"/>
+      <c r="F16" s="574" t="n"/>
+      <c r="G16" s="574" t="n"/>
       <c r="H16" s="472" t="n"/>
-      <c r="I16" s="473" t="n"/>
-      <c r="J16" s="473" t="n"/>
-      <c r="K16" s="473" t="n"/>
-      <c r="L16" s="473" t="n"/>
-      <c r="M16" s="473" t="n"/>
-      <c r="N16" s="473" t="n"/>
-      <c r="O16" s="473" t="n"/>
-      <c r="P16" s="473" t="n"/>
-      <c r="Q16" s="473" t="n"/>
-      <c r="R16" s="473" t="n"/>
-      <c r="S16" s="473" t="n"/>
-      <c r="T16" s="473" t="n"/>
-      <c r="U16" s="473" t="n"/>
-      <c r="V16" s="473" t="n"/>
-      <c r="W16" s="473" t="n"/>
-      <c r="X16" s="473" t="n"/>
-      <c r="Y16" s="473" t="n"/>
-      <c r="Z16" s="473" t="n"/>
+      <c r="I16" s="574" t="n"/>
+      <c r="J16" s="574" t="n"/>
+      <c r="K16" s="574" t="n"/>
+      <c r="L16" s="574" t="n"/>
+      <c r="M16" s="574" t="n"/>
+      <c r="N16" s="574" t="n"/>
+      <c r="O16" s="574" t="n"/>
+      <c r="P16" s="574" t="n"/>
+      <c r="Q16" s="574" t="n"/>
+      <c r="R16" s="574" t="n"/>
+      <c r="S16" s="574" t="n"/>
+      <c r="T16" s="574" t="n"/>
+      <c r="U16" s="574" t="n"/>
+      <c r="V16" s="574" t="n"/>
+      <c r="W16" s="574" t="n"/>
+      <c r="X16" s="574" t="n"/>
+      <c r="Y16" s="574" t="n"/>
+      <c r="Z16" s="574" t="n"/>
       <c r="AA16" s="492" t="n"/>
-      <c r="AB16" s="473" t="n"/>
-      <c r="AC16" s="473" t="n"/>
-      <c r="AD16" s="473" t="n"/>
-      <c r="AE16" s="473" t="n"/>
-      <c r="AF16" s="473" t="n"/>
-      <c r="AG16" s="473" t="n"/>
-      <c r="AH16" s="473" t="n"/>
-      <c r="AI16" s="473" t="n"/>
-      <c r="AJ16" s="473" t="n"/>
-      <c r="AK16" s="473" t="n"/>
-      <c r="AL16" s="473" t="n"/>
-      <c r="AM16" s="473" t="n"/>
-      <c r="AN16" s="473" t="n"/>
-      <c r="AO16" s="473" t="n"/>
-      <c r="AP16" s="473" t="n"/>
-      <c r="AQ16" s="473" t="n"/>
+      <c r="AB16" s="574" t="n"/>
+      <c r="AC16" s="574" t="n"/>
+      <c r="AD16" s="574" t="n"/>
+      <c r="AE16" s="574" t="n"/>
+      <c r="AF16" s="574" t="n"/>
+      <c r="AG16" s="574" t="n"/>
+      <c r="AH16" s="574" t="n"/>
+      <c r="AI16" s="574" t="n"/>
+      <c r="AJ16" s="574" t="n"/>
+      <c r="AK16" s="574" t="n"/>
+      <c r="AL16" s="574" t="n"/>
+      <c r="AM16" s="574" t="n"/>
+      <c r="AN16" s="574" t="n"/>
+      <c r="AO16" s="574" t="n"/>
+      <c r="AP16" s="574" t="n"/>
+      <c r="AQ16" s="574" t="n"/>
       <c r="AR16" s="472" t="n"/>
-      <c r="AS16" s="473" t="n"/>
-      <c r="AT16" s="473" t="n"/>
-      <c r="AU16" s="473" t="n"/>
-      <c r="AV16" s="473" t="n"/>
-      <c r="AW16" s="473" t="n"/>
+      <c r="AS16" s="574" t="n"/>
+      <c r="AT16" s="574" t="n"/>
+      <c r="AU16" s="574" t="n"/>
+      <c r="AV16" s="574" t="n"/>
+      <c r="AW16" s="574" t="n"/>
       <c r="AX16" s="472" t="n"/>
-      <c r="AY16" s="473" t="n"/>
-      <c r="AZ16" s="473" t="n"/>
-      <c r="BA16" s="473" t="n"/>
-      <c r="BB16" s="493" t="n"/>
-      <c r="BC16" s="473" t="n"/>
-      <c r="BD16" s="475" t="n"/>
+      <c r="AY16" s="574" t="n"/>
+      <c r="AZ16" s="574" t="n"/>
+      <c r="BA16" s="574" t="n"/>
+      <c r="BB16" s="584" t="n"/>
+      <c r="BC16" s="574" t="n"/>
+      <c r="BD16" s="576" t="n"/>
     </row>
     <row r="17" ht="20" customHeight="1">
       <c r="A17" s="494">
         <f>ROW()-ROW($A$16)+1</f>
         <v/>
       </c>
-      <c r="B17" s="344" t="n"/>
-      <c r="C17" s="344" t="n"/>
+      <c r="B17" s="423" t="n"/>
+      <c r="C17" s="423" t="n"/>
       <c r="D17" s="495" t="n"/>
-      <c r="E17" s="362" t="n"/>
-      <c r="F17" s="362" t="n"/>
-      <c r="G17" s="362" t="n"/>
+      <c r="E17" s="577" t="n"/>
+      <c r="F17" s="577" t="n"/>
+      <c r="G17" s="577" t="n"/>
       <c r="H17" s="477" t="n"/>
-      <c r="I17" s="362" t="n"/>
-      <c r="J17" s="362" t="n"/>
-      <c r="K17" s="362" t="n"/>
-      <c r="L17" s="362" t="n"/>
-      <c r="M17" s="362" t="n"/>
-      <c r="N17" s="362" t="n"/>
-      <c r="O17" s="362" t="n"/>
-      <c r="P17" s="362" t="n"/>
-      <c r="Q17" s="362" t="n"/>
-      <c r="R17" s="362" t="n"/>
-      <c r="S17" s="362" t="n"/>
-      <c r="T17" s="362" t="n"/>
-      <c r="U17" s="362" t="n"/>
-      <c r="V17" s="362" t="n"/>
-      <c r="W17" s="362" t="n"/>
-      <c r="X17" s="362" t="n"/>
-      <c r="Y17" s="362" t="n"/>
-      <c r="Z17" s="362" t="n"/>
+      <c r="I17" s="577" t="n"/>
+      <c r="J17" s="577" t="n"/>
+      <c r="K17" s="577" t="n"/>
+      <c r="L17" s="577" t="n"/>
+      <c r="M17" s="577" t="n"/>
+      <c r="N17" s="577" t="n"/>
+      <c r="O17" s="577" t="n"/>
+      <c r="P17" s="577" t="n"/>
+      <c r="Q17" s="577" t="n"/>
+      <c r="R17" s="577" t="n"/>
+      <c r="S17" s="577" t="n"/>
+      <c r="T17" s="577" t="n"/>
+      <c r="U17" s="577" t="n"/>
+      <c r="V17" s="577" t="n"/>
+      <c r="W17" s="577" t="n"/>
+      <c r="X17" s="577" t="n"/>
+      <c r="Y17" s="577" t="n"/>
+      <c r="Z17" s="577" t="n"/>
       <c r="AA17" s="496" t="n"/>
-      <c r="AB17" s="362" t="n"/>
-      <c r="AC17" s="362" t="n"/>
-      <c r="AD17" s="362" t="n"/>
-      <c r="AE17" s="362" t="n"/>
-      <c r="AF17" s="362" t="n"/>
-      <c r="AG17" s="362" t="n"/>
-      <c r="AH17" s="362" t="n"/>
-      <c r="AI17" s="362" t="n"/>
-      <c r="AJ17" s="362" t="n"/>
-      <c r="AK17" s="362" t="n"/>
-      <c r="AL17" s="362" t="n"/>
-      <c r="AM17" s="362" t="n"/>
-      <c r="AN17" s="362" t="n"/>
-      <c r="AO17" s="362" t="n"/>
-      <c r="AP17" s="362" t="n"/>
-      <c r="AQ17" s="362" t="n"/>
+      <c r="AB17" s="577" t="n"/>
+      <c r="AC17" s="577" t="n"/>
+      <c r="AD17" s="577" t="n"/>
+      <c r="AE17" s="577" t="n"/>
+      <c r="AF17" s="577" t="n"/>
+      <c r="AG17" s="577" t="n"/>
+      <c r="AH17" s="577" t="n"/>
+      <c r="AI17" s="577" t="n"/>
+      <c r="AJ17" s="577" t="n"/>
+      <c r="AK17" s="577" t="n"/>
+      <c r="AL17" s="577" t="n"/>
+      <c r="AM17" s="577" t="n"/>
+      <c r="AN17" s="577" t="n"/>
+      <c r="AO17" s="577" t="n"/>
+      <c r="AP17" s="577" t="n"/>
+      <c r="AQ17" s="577" t="n"/>
       <c r="AR17" s="477" t="n"/>
-      <c r="AS17" s="362" t="n"/>
-      <c r="AT17" s="362" t="n"/>
-      <c r="AU17" s="362" t="n"/>
-      <c r="AV17" s="362" t="n"/>
-      <c r="AW17" s="362" t="n"/>
+      <c r="AS17" s="577" t="n"/>
+      <c r="AT17" s="577" t="n"/>
+      <c r="AU17" s="577" t="n"/>
+      <c r="AV17" s="577" t="n"/>
+      <c r="AW17" s="577" t="n"/>
       <c r="AX17" s="477" t="n"/>
-      <c r="AY17" s="362" t="n"/>
-      <c r="AZ17" s="362" t="n"/>
-      <c r="BA17" s="362" t="n"/>
-      <c r="BB17" s="497" t="n"/>
-      <c r="BC17" s="362" t="n"/>
-      <c r="BD17" s="479" t="n"/>
+      <c r="AY17" s="577" t="n"/>
+      <c r="AZ17" s="577" t="n"/>
+      <c r="BA17" s="577" t="n"/>
+      <c r="BB17" s="585" t="n"/>
+      <c r="BC17" s="577" t="n"/>
+      <c r="BD17" s="579" t="n"/>
     </row>
     <row r="18" ht="20" customHeight="1">
       <c r="A18" s="494">
         <f>ROW()-ROW($A$16)+1</f>
         <v/>
       </c>
-      <c r="B18" s="344" t="n"/>
-      <c r="C18" s="344" t="n"/>
+      <c r="B18" s="423" t="n"/>
+      <c r="C18" s="423" t="n"/>
       <c r="D18" s="495" t="n"/>
-      <c r="E18" s="362" t="n"/>
-      <c r="F18" s="362" t="n"/>
-      <c r="G18" s="362" t="n"/>
+      <c r="E18" s="577" t="n"/>
+      <c r="F18" s="577" t="n"/>
+      <c r="G18" s="577" t="n"/>
       <c r="H18" s="477" t="n"/>
-      <c r="I18" s="362" t="n"/>
-      <c r="J18" s="362" t="n"/>
-      <c r="K18" s="362" t="n"/>
-      <c r="L18" s="362" t="n"/>
-      <c r="M18" s="362" t="n"/>
-      <c r="N18" s="362" t="n"/>
-      <c r="O18" s="362" t="n"/>
-      <c r="P18" s="362" t="n"/>
-      <c r="Q18" s="362" t="n"/>
-      <c r="R18" s="362" t="n"/>
-      <c r="S18" s="362" t="n"/>
-      <c r="T18" s="362" t="n"/>
-      <c r="U18" s="362" t="n"/>
-      <c r="V18" s="362" t="n"/>
-      <c r="W18" s="362" t="n"/>
-      <c r="X18" s="362" t="n"/>
-      <c r="Y18" s="362" t="n"/>
-      <c r="Z18" s="362" t="n"/>
+      <c r="I18" s="577" t="n"/>
+      <c r="J18" s="577" t="n"/>
+      <c r="K18" s="577" t="n"/>
+      <c r="L18" s="577" t="n"/>
+      <c r="M18" s="577" t="n"/>
+      <c r="N18" s="577" t="n"/>
+      <c r="O18" s="577" t="n"/>
+      <c r="P18" s="577" t="n"/>
+      <c r="Q18" s="577" t="n"/>
+      <c r="R18" s="577" t="n"/>
+      <c r="S18" s="577" t="n"/>
+      <c r="T18" s="577" t="n"/>
+      <c r="U18" s="577" t="n"/>
+      <c r="V18" s="577" t="n"/>
+      <c r="W18" s="577" t="n"/>
+      <c r="X18" s="577" t="n"/>
+      <c r="Y18" s="577" t="n"/>
+      <c r="Z18" s="577" t="n"/>
       <c r="AA18" s="496" t="n"/>
-      <c r="AB18" s="362" t="n"/>
-      <c r="AC18" s="362" t="n"/>
-      <c r="AD18" s="362" t="n"/>
-      <c r="AE18" s="362" t="n"/>
-      <c r="AF18" s="362" t="n"/>
-      <c r="AG18" s="362" t="n"/>
-      <c r="AH18" s="362" t="n"/>
-      <c r="AI18" s="362" t="n"/>
-      <c r="AJ18" s="362" t="n"/>
-      <c r="AK18" s="362" t="n"/>
-      <c r="AL18" s="362" t="n"/>
-      <c r="AM18" s="362" t="n"/>
-      <c r="AN18" s="362" t="n"/>
-      <c r="AO18" s="362" t="n"/>
-      <c r="AP18" s="362" t="n"/>
-      <c r="AQ18" s="362" t="n"/>
+      <c r="AB18" s="577" t="n"/>
+      <c r="AC18" s="577" t="n"/>
+      <c r="AD18" s="577" t="n"/>
+      <c r="AE18" s="577" t="n"/>
+      <c r="AF18" s="577" t="n"/>
+      <c r="AG18" s="577" t="n"/>
+      <c r="AH18" s="577" t="n"/>
+      <c r="AI18" s="577" t="n"/>
+      <c r="AJ18" s="577" t="n"/>
+      <c r="AK18" s="577" t="n"/>
+      <c r="AL18" s="577" t="n"/>
+      <c r="AM18" s="577" t="n"/>
+      <c r="AN18" s="577" t="n"/>
+      <c r="AO18" s="577" t="n"/>
+      <c r="AP18" s="577" t="n"/>
+      <c r="AQ18" s="577" t="n"/>
       <c r="AR18" s="477" t="n"/>
-      <c r="AS18" s="362" t="n"/>
-      <c r="AT18" s="362" t="n"/>
-      <c r="AU18" s="362" t="n"/>
-      <c r="AV18" s="362" t="n"/>
-      <c r="AW18" s="362" t="n"/>
+      <c r="AS18" s="577" t="n"/>
+      <c r="AT18" s="577" t="n"/>
+      <c r="AU18" s="577" t="n"/>
+      <c r="AV18" s="577" t="n"/>
+      <c r="AW18" s="577" t="n"/>
       <c r="AX18" s="477" t="n"/>
-      <c r="AY18" s="362" t="n"/>
-      <c r="AZ18" s="362" t="n"/>
-      <c r="BA18" s="362" t="n"/>
-      <c r="BB18" s="497" t="n"/>
-      <c r="BC18" s="362" t="n"/>
-      <c r="BD18" s="479" t="n"/>
+      <c r="AY18" s="577" t="n"/>
+      <c r="AZ18" s="577" t="n"/>
+      <c r="BA18" s="577" t="n"/>
+      <c r="BB18" s="585" t="n"/>
+      <c r="BC18" s="577" t="n"/>
+      <c r="BD18" s="579" t="n"/>
     </row>
     <row r="19" ht="20" customHeight="1">
       <c r="A19" s="494">
         <f>ROW()-ROW($A$16)+1</f>
         <v/>
       </c>
-      <c r="B19" s="344" t="n"/>
-      <c r="C19" s="344" t="n"/>
+      <c r="B19" s="423" t="n"/>
+      <c r="C19" s="423" t="n"/>
       <c r="D19" s="495" t="n"/>
-      <c r="E19" s="362" t="n"/>
-      <c r="F19" s="362" t="n"/>
-      <c r="G19" s="362" t="n"/>
+      <c r="E19" s="577" t="n"/>
+      <c r="F19" s="577" t="n"/>
+      <c r="G19" s="577" t="n"/>
       <c r="H19" s="477" t="n"/>
-      <c r="I19" s="362" t="n"/>
-      <c r="J19" s="362" t="n"/>
-      <c r="K19" s="362" t="n"/>
-      <c r="L19" s="362" t="n"/>
-      <c r="M19" s="362" t="n"/>
-      <c r="N19" s="362" t="n"/>
-      <c r="O19" s="362" t="n"/>
-      <c r="P19" s="362" t="n"/>
-      <c r="Q19" s="362" t="n"/>
-      <c r="R19" s="362" t="n"/>
-      <c r="S19" s="362" t="n"/>
-      <c r="T19" s="362" t="n"/>
-      <c r="U19" s="362" t="n"/>
-      <c r="V19" s="362" t="n"/>
-      <c r="W19" s="362" t="n"/>
-      <c r="X19" s="362" t="n"/>
-      <c r="Y19" s="362" t="n"/>
-      <c r="Z19" s="362" t="n"/>
+      <c r="I19" s="577" t="n"/>
+      <c r="J19" s="577" t="n"/>
+      <c r="K19" s="577" t="n"/>
+      <c r="L19" s="577" t="n"/>
+      <c r="M19" s="577" t="n"/>
+      <c r="N19" s="577" t="n"/>
+      <c r="O19" s="577" t="n"/>
+      <c r="P19" s="577" t="n"/>
+      <c r="Q19" s="577" t="n"/>
+      <c r="R19" s="577" t="n"/>
+      <c r="S19" s="577" t="n"/>
+      <c r="T19" s="577" t="n"/>
+      <c r="U19" s="577" t="n"/>
+      <c r="V19" s="577" t="n"/>
+      <c r="W19" s="577" t="n"/>
+      <c r="X19" s="577" t="n"/>
+      <c r="Y19" s="577" t="n"/>
+      <c r="Z19" s="577" t="n"/>
       <c r="AA19" s="496" t="n"/>
-      <c r="AB19" s="362" t="n"/>
-      <c r="AC19" s="362" t="n"/>
-      <c r="AD19" s="362" t="n"/>
-      <c r="AE19" s="362" t="n"/>
-      <c r="AF19" s="362" t="n"/>
-      <c r="AG19" s="362" t="n"/>
-      <c r="AH19" s="362" t="n"/>
-      <c r="AI19" s="362" t="n"/>
-      <c r="AJ19" s="362" t="n"/>
-      <c r="AK19" s="362" t="n"/>
-      <c r="AL19" s="362" t="n"/>
-      <c r="AM19" s="362" t="n"/>
-      <c r="AN19" s="362" t="n"/>
-      <c r="AO19" s="362" t="n"/>
-      <c r="AP19" s="362" t="n"/>
-      <c r="AQ19" s="362" t="n"/>
+      <c r="AB19" s="577" t="n"/>
+      <c r="AC19" s="577" t="n"/>
+      <c r="AD19" s="577" t="n"/>
+      <c r="AE19" s="577" t="n"/>
+      <c r="AF19" s="577" t="n"/>
+      <c r="AG19" s="577" t="n"/>
+      <c r="AH19" s="577" t="n"/>
+      <c r="AI19" s="577" t="n"/>
+      <c r="AJ19" s="577" t="n"/>
+      <c r="AK19" s="577" t="n"/>
+      <c r="AL19" s="577" t="n"/>
+      <c r="AM19" s="577" t="n"/>
+      <c r="AN19" s="577" t="n"/>
+      <c r="AO19" s="577" t="n"/>
+      <c r="AP19" s="577" t="n"/>
+      <c r="AQ19" s="577" t="n"/>
       <c r="AR19" s="477" t="n"/>
-      <c r="AS19" s="362" t="n"/>
-      <c r="AT19" s="362" t="n"/>
-      <c r="AU19" s="362" t="n"/>
-      <c r="AV19" s="362" t="n"/>
-      <c r="AW19" s="362" t="n"/>
+      <c r="AS19" s="577" t="n"/>
+      <c r="AT19" s="577" t="n"/>
+      <c r="AU19" s="577" t="n"/>
+      <c r="AV19" s="577" t="n"/>
+      <c r="AW19" s="577" t="n"/>
       <c r="AX19" s="477" t="n"/>
-      <c r="AY19" s="362" t="n"/>
-      <c r="AZ19" s="362" t="n"/>
-      <c r="BA19" s="362" t="n"/>
-      <c r="BB19" s="497" t="n"/>
-      <c r="BC19" s="362" t="n"/>
-      <c r="BD19" s="479" t="n"/>
+      <c r="AY19" s="577" t="n"/>
+      <c r="AZ19" s="577" t="n"/>
+      <c r="BA19" s="577" t="n"/>
+      <c r="BB19" s="585" t="n"/>
+      <c r="BC19" s="577" t="n"/>
+      <c r="BD19" s="579" t="n"/>
     </row>
     <row r="20" ht="20" customHeight="1">
       <c r="A20" s="494">
         <f>ROW()-ROW($A$16)+1</f>
         <v/>
       </c>
-      <c r="B20" s="344" t="n"/>
-      <c r="C20" s="344" t="n"/>
+      <c r="B20" s="423" t="n"/>
+      <c r="C20" s="423" t="n"/>
       <c r="D20" s="495" t="n"/>
-      <c r="E20" s="362" t="n"/>
-      <c r="F20" s="362" t="n"/>
-      <c r="G20" s="362" t="n"/>
+      <c r="E20" s="577" t="n"/>
+      <c r="F20" s="577" t="n"/>
+      <c r="G20" s="577" t="n"/>
       <c r="H20" s="477" t="n"/>
-      <c r="I20" s="362" t="n"/>
-      <c r="J20" s="362" t="n"/>
-      <c r="K20" s="362" t="n"/>
-      <c r="L20" s="362" t="n"/>
-      <c r="M20" s="362" t="n"/>
-      <c r="N20" s="362" t="n"/>
-      <c r="O20" s="362" t="n"/>
-      <c r="P20" s="362" t="n"/>
-      <c r="Q20" s="362" t="n"/>
-      <c r="R20" s="362" t="n"/>
-      <c r="S20" s="362" t="n"/>
-      <c r="T20" s="362" t="n"/>
-      <c r="U20" s="362" t="n"/>
-      <c r="V20" s="362" t="n"/>
-      <c r="W20" s="362" t="n"/>
-      <c r="X20" s="362" t="n"/>
-      <c r="Y20" s="362" t="n"/>
-      <c r="Z20" s="362" t="n"/>
+      <c r="I20" s="577" t="n"/>
+      <c r="J20" s="577" t="n"/>
+      <c r="K20" s="577" t="n"/>
+      <c r="L20" s="577" t="n"/>
+      <c r="M20" s="577" t="n"/>
+      <c r="N20" s="577" t="n"/>
+      <c r="O20" s="577" t="n"/>
+      <c r="P20" s="577" t="n"/>
+      <c r="Q20" s="577" t="n"/>
+      <c r="R20" s="577" t="n"/>
+      <c r="S20" s="577" t="n"/>
+      <c r="T20" s="577" t="n"/>
+      <c r="U20" s="577" t="n"/>
+      <c r="V20" s="577" t="n"/>
+      <c r="W20" s="577" t="n"/>
+      <c r="X20" s="577" t="n"/>
+      <c r="Y20" s="577" t="n"/>
+      <c r="Z20" s="577" t="n"/>
       <c r="AA20" s="496" t="n"/>
-      <c r="AB20" s="362" t="n"/>
-      <c r="AC20" s="362" t="n"/>
-      <c r="AD20" s="362" t="n"/>
-      <c r="AE20" s="362" t="n"/>
-      <c r="AF20" s="362" t="n"/>
-      <c r="AG20" s="362" t="n"/>
-      <c r="AH20" s="362" t="n"/>
-      <c r="AI20" s="362" t="n"/>
-      <c r="AJ20" s="362" t="n"/>
-      <c r="AK20" s="362" t="n"/>
-      <c r="AL20" s="362" t="n"/>
-      <c r="AM20" s="362" t="n"/>
-      <c r="AN20" s="362" t="n"/>
-      <c r="AO20" s="362" t="n"/>
-      <c r="AP20" s="362" t="n"/>
-      <c r="AQ20" s="362" t="n"/>
+      <c r="AB20" s="577" t="n"/>
+      <c r="AC20" s="577" t="n"/>
+      <c r="AD20" s="577" t="n"/>
+      <c r="AE20" s="577" t="n"/>
+      <c r="AF20" s="577" t="n"/>
+      <c r="AG20" s="577" t="n"/>
+      <c r="AH20" s="577" t="n"/>
+      <c r="AI20" s="577" t="n"/>
+      <c r="AJ20" s="577" t="n"/>
+      <c r="AK20" s="577" t="n"/>
+      <c r="AL20" s="577" t="n"/>
+      <c r="AM20" s="577" t="n"/>
+      <c r="AN20" s="577" t="n"/>
+      <c r="AO20" s="577" t="n"/>
+      <c r="AP20" s="577" t="n"/>
+      <c r="AQ20" s="577" t="n"/>
       <c r="AR20" s="477" t="n"/>
-      <c r="AS20" s="362" t="n"/>
-      <c r="AT20" s="362" t="n"/>
-      <c r="AU20" s="362" t="n"/>
-      <c r="AV20" s="362" t="n"/>
-      <c r="AW20" s="362" t="n"/>
+      <c r="AS20" s="577" t="n"/>
+      <c r="AT20" s="577" t="n"/>
+      <c r="AU20" s="577" t="n"/>
+      <c r="AV20" s="577" t="n"/>
+      <c r="AW20" s="577" t="n"/>
       <c r="AX20" s="477" t="n"/>
-      <c r="AY20" s="362" t="n"/>
-      <c r="AZ20" s="362" t="n"/>
-      <c r="BA20" s="362" t="n"/>
-      <c r="BB20" s="497" t="n"/>
-      <c r="BC20" s="362" t="n"/>
-      <c r="BD20" s="479" t="n"/>
+      <c r="AY20" s="577" t="n"/>
+      <c r="AZ20" s="577" t="n"/>
+      <c r="BA20" s="577" t="n"/>
+      <c r="BB20" s="585" t="n"/>
+      <c r="BC20" s="577" t="n"/>
+      <c r="BD20" s="579" t="n"/>
     </row>
     <row r="21" ht="20" customHeight="1">
       <c r="A21" s="494">
         <f>ROW()-ROW($A$16)+1</f>
         <v/>
       </c>
-      <c r="B21" s="344" t="n"/>
-      <c r="C21" s="344" t="n"/>
+      <c r="B21" s="423" t="n"/>
+      <c r="C21" s="423" t="n"/>
       <c r="D21" s="495" t="n"/>
-      <c r="E21" s="362" t="n"/>
-      <c r="F21" s="362" t="n"/>
-      <c r="G21" s="362" t="n"/>
+      <c r="E21" s="577" t="n"/>
+      <c r="F21" s="577" t="n"/>
+      <c r="G21" s="577" t="n"/>
       <c r="H21" s="477" t="n"/>
-      <c r="I21" s="362" t="n"/>
-      <c r="J21" s="362" t="n"/>
-      <c r="K21" s="362" t="n"/>
-      <c r="L21" s="362" t="n"/>
-      <c r="M21" s="362" t="n"/>
-      <c r="N21" s="362" t="n"/>
-      <c r="O21" s="362" t="n"/>
-      <c r="P21" s="362" t="n"/>
-      <c r="Q21" s="362" t="n"/>
-      <c r="R21" s="362" t="n"/>
-      <c r="S21" s="362" t="n"/>
-      <c r="T21" s="362" t="n"/>
-      <c r="U21" s="362" t="n"/>
-      <c r="V21" s="362" t="n"/>
-      <c r="W21" s="362" t="n"/>
-      <c r="X21" s="362" t="n"/>
-      <c r="Y21" s="362" t="n"/>
-      <c r="Z21" s="362" t="n"/>
+      <c r="I21" s="577" t="n"/>
+      <c r="J21" s="577" t="n"/>
+      <c r="K21" s="577" t="n"/>
+      <c r="L21" s="577" t="n"/>
+      <c r="M21" s="577" t="n"/>
+      <c r="N21" s="577" t="n"/>
+      <c r="O21" s="577" t="n"/>
+      <c r="P21" s="577" t="n"/>
+      <c r="Q21" s="577" t="n"/>
+      <c r="R21" s="577" t="n"/>
+      <c r="S21" s="577" t="n"/>
+      <c r="T21" s="577" t="n"/>
+      <c r="U21" s="577" t="n"/>
+      <c r="V21" s="577" t="n"/>
+      <c r="W21" s="577" t="n"/>
+      <c r="X21" s="577" t="n"/>
+      <c r="Y21" s="577" t="n"/>
+      <c r="Z21" s="577" t="n"/>
       <c r="AA21" s="496" t="n"/>
-      <c r="AB21" s="362" t="n"/>
-      <c r="AC21" s="362" t="n"/>
-      <c r="AD21" s="362" t="n"/>
-      <c r="AE21" s="362" t="n"/>
-      <c r="AF21" s="362" t="n"/>
-      <c r="AG21" s="362" t="n"/>
-      <c r="AH21" s="362" t="n"/>
-      <c r="AI21" s="362" t="n"/>
-      <c r="AJ21" s="362" t="n"/>
-      <c r="AK21" s="362" t="n"/>
-      <c r="AL21" s="362" t="n"/>
-      <c r="AM21" s="362" t="n"/>
-      <c r="AN21" s="362" t="n"/>
-      <c r="AO21" s="362" t="n"/>
-      <c r="AP21" s="362" t="n"/>
-      <c r="AQ21" s="362" t="n"/>
+      <c r="AB21" s="577" t="n"/>
+      <c r="AC21" s="577" t="n"/>
+      <c r="AD21" s="577" t="n"/>
+      <c r="AE21" s="577" t="n"/>
+      <c r="AF21" s="577" t="n"/>
+      <c r="AG21" s="577" t="n"/>
+      <c r="AH21" s="577" t="n"/>
+      <c r="AI21" s="577" t="n"/>
+      <c r="AJ21" s="577" t="n"/>
+      <c r="AK21" s="577" t="n"/>
+      <c r="AL21" s="577" t="n"/>
+      <c r="AM21" s="577" t="n"/>
+      <c r="AN21" s="577" t="n"/>
+      <c r="AO21" s="577" t="n"/>
+      <c r="AP21" s="577" t="n"/>
+      <c r="AQ21" s="577" t="n"/>
       <c r="AR21" s="477" t="n"/>
-      <c r="AS21" s="362" t="n"/>
-      <c r="AT21" s="362" t="n"/>
-      <c r="AU21" s="362" t="n"/>
-      <c r="AV21" s="362" t="n"/>
-      <c r="AW21" s="362" t="n"/>
+      <c r="AS21" s="577" t="n"/>
+      <c r="AT21" s="577" t="n"/>
+      <c r="AU21" s="577" t="n"/>
+      <c r="AV21" s="577" t="n"/>
+      <c r="AW21" s="577" t="n"/>
       <c r="AX21" s="477" t="n"/>
-      <c r="AY21" s="362" t="n"/>
-      <c r="AZ21" s="362" t="n"/>
-      <c r="BA21" s="362" t="n"/>
-      <c r="BB21" s="497" t="n"/>
-      <c r="BC21" s="362" t="n"/>
-      <c r="BD21" s="479" t="n"/>
+      <c r="AY21" s="577" t="n"/>
+      <c r="AZ21" s="577" t="n"/>
+      <c r="BA21" s="577" t="n"/>
+      <c r="BB21" s="585" t="n"/>
+      <c r="BC21" s="577" t="n"/>
+      <c r="BD21" s="579" t="n"/>
     </row>
     <row r="22" ht="20" customHeight="1">
       <c r="A22" s="494">
         <f>ROW()-ROW($A$16)+1</f>
         <v/>
       </c>
-      <c r="B22" s="344" t="n"/>
-      <c r="C22" s="344" t="n"/>
+      <c r="B22" s="423" t="n"/>
+      <c r="C22" s="423" t="n"/>
       <c r="D22" s="495" t="n"/>
-      <c r="E22" s="362" t="n"/>
-      <c r="F22" s="362" t="n"/>
-      <c r="G22" s="362" t="n"/>
+      <c r="E22" s="577" t="n"/>
+      <c r="F22" s="577" t="n"/>
+      <c r="G22" s="577" t="n"/>
       <c r="H22" s="477" t="n"/>
-      <c r="I22" s="362" t="n"/>
-      <c r="J22" s="362" t="n"/>
-      <c r="K22" s="362" t="n"/>
-      <c r="L22" s="362" t="n"/>
-      <c r="M22" s="362" t="n"/>
-      <c r="N22" s="362" t="n"/>
-      <c r="O22" s="362" t="n"/>
-      <c r="P22" s="362" t="n"/>
-      <c r="Q22" s="362" t="n"/>
-      <c r="R22" s="362" t="n"/>
-      <c r="S22" s="362" t="n"/>
-      <c r="T22" s="362" t="n"/>
-      <c r="U22" s="362" t="n"/>
-      <c r="V22" s="362" t="n"/>
-      <c r="W22" s="362" t="n"/>
-      <c r="X22" s="362" t="n"/>
-      <c r="Y22" s="362" t="n"/>
-      <c r="Z22" s="362" t="n"/>
+      <c r="I22" s="577" t="n"/>
+      <c r="J22" s="577" t="n"/>
+      <c r="K22" s="577" t="n"/>
+      <c r="L22" s="577" t="n"/>
+      <c r="M22" s="577" t="n"/>
+      <c r="N22" s="577" t="n"/>
+      <c r="O22" s="577" t="n"/>
+      <c r="P22" s="577" t="n"/>
+      <c r="Q22" s="577" t="n"/>
+      <c r="R22" s="577" t="n"/>
+      <c r="S22" s="577" t="n"/>
+      <c r="T22" s="577" t="n"/>
+      <c r="U22" s="577" t="n"/>
+      <c r="V22" s="577" t="n"/>
+      <c r="W22" s="577" t="n"/>
+      <c r="X22" s="577" t="n"/>
+      <c r="Y22" s="577" t="n"/>
+      <c r="Z22" s="577" t="n"/>
       <c r="AA22" s="496" t="n"/>
-      <c r="AB22" s="362" t="n"/>
-      <c r="AC22" s="362" t="n"/>
-      <c r="AD22" s="362" t="n"/>
-      <c r="AE22" s="362" t="n"/>
-      <c r="AF22" s="362" t="n"/>
-      <c r="AG22" s="362" t="n"/>
-      <c r="AH22" s="362" t="n"/>
-      <c r="AI22" s="362" t="n"/>
-      <c r="AJ22" s="362" t="n"/>
-      <c r="AK22" s="362" t="n"/>
-      <c r="AL22" s="362" t="n"/>
-      <c r="AM22" s="362" t="n"/>
-      <c r="AN22" s="362" t="n"/>
-      <c r="AO22" s="362" t="n"/>
-      <c r="AP22" s="362" t="n"/>
-      <c r="AQ22" s="362" t="n"/>
+      <c r="AB22" s="577" t="n"/>
+      <c r="AC22" s="577" t="n"/>
+      <c r="AD22" s="577" t="n"/>
+      <c r="AE22" s="577" t="n"/>
+      <c r="AF22" s="577" t="n"/>
+      <c r="AG22" s="577" t="n"/>
+      <c r="AH22" s="577" t="n"/>
+      <c r="AI22" s="577" t="n"/>
+      <c r="AJ22" s="577" t="n"/>
+      <c r="AK22" s="577" t="n"/>
+      <c r="AL22" s="577" t="n"/>
+      <c r="AM22" s="577" t="n"/>
+      <c r="AN22" s="577" t="n"/>
+      <c r="AO22" s="577" t="n"/>
+      <c r="AP22" s="577" t="n"/>
+      <c r="AQ22" s="577" t="n"/>
       <c r="AR22" s="477" t="n"/>
-      <c r="AS22" s="362" t="n"/>
-      <c r="AT22" s="362" t="n"/>
-      <c r="AU22" s="362" t="n"/>
-      <c r="AV22" s="362" t="n"/>
-      <c r="AW22" s="362" t="n"/>
+      <c r="AS22" s="577" t="n"/>
+      <c r="AT22" s="577" t="n"/>
+      <c r="AU22" s="577" t="n"/>
+      <c r="AV22" s="577" t="n"/>
+      <c r="AW22" s="577" t="n"/>
       <c r="AX22" s="477" t="n"/>
-      <c r="AY22" s="362" t="n"/>
-      <c r="AZ22" s="362" t="n"/>
-      <c r="BA22" s="362" t="n"/>
-      <c r="BB22" s="497" t="n"/>
-      <c r="BC22" s="362" t="n"/>
-      <c r="BD22" s="479" t="n"/>
+      <c r="AY22" s="577" t="n"/>
+      <c r="AZ22" s="577" t="n"/>
+      <c r="BA22" s="577" t="n"/>
+      <c r="BB22" s="585" t="n"/>
+      <c r="BC22" s="577" t="n"/>
+      <c r="BD22" s="579" t="n"/>
     </row>
     <row r="23" ht="20" customHeight="1">
       <c r="A23" s="498">
         <f>ROW()-ROW($A$16)+1</f>
         <v/>
       </c>
-      <c r="B23" s="481" t="n"/>
-      <c r="C23" s="481" t="n"/>
+      <c r="B23" s="566" t="n"/>
+      <c r="C23" s="566" t="n"/>
       <c r="D23" s="499" t="n"/>
-      <c r="E23" s="483" t="n"/>
-      <c r="F23" s="483" t="n"/>
-      <c r="G23" s="483" t="n"/>
+      <c r="E23" s="580" t="n"/>
+      <c r="F23" s="580" t="n"/>
+      <c r="G23" s="580" t="n"/>
       <c r="H23" s="482" t="n"/>
-      <c r="I23" s="483" t="n"/>
-      <c r="J23" s="483" t="n"/>
-      <c r="K23" s="483" t="n"/>
-      <c r="L23" s="483" t="n"/>
-      <c r="M23" s="483" t="n"/>
-      <c r="N23" s="483" t="n"/>
-      <c r="O23" s="483" t="n"/>
-      <c r="P23" s="483" t="n"/>
-      <c r="Q23" s="483" t="n"/>
-      <c r="R23" s="483" t="n"/>
-      <c r="S23" s="483" t="n"/>
-      <c r="T23" s="483" t="n"/>
-      <c r="U23" s="483" t="n"/>
-      <c r="V23" s="483" t="n"/>
-      <c r="W23" s="483" t="n"/>
-      <c r="X23" s="483" t="n"/>
-      <c r="Y23" s="483" t="n"/>
-      <c r="Z23" s="483" t="n"/>
+      <c r="I23" s="580" t="n"/>
+      <c r="J23" s="580" t="n"/>
+      <c r="K23" s="580" t="n"/>
+      <c r="L23" s="580" t="n"/>
+      <c r="M23" s="580" t="n"/>
+      <c r="N23" s="580" t="n"/>
+      <c r="O23" s="580" t="n"/>
+      <c r="P23" s="580" t="n"/>
+      <c r="Q23" s="580" t="n"/>
+      <c r="R23" s="580" t="n"/>
+      <c r="S23" s="580" t="n"/>
+      <c r="T23" s="580" t="n"/>
+      <c r="U23" s="580" t="n"/>
+      <c r="V23" s="580" t="n"/>
+      <c r="W23" s="580" t="n"/>
+      <c r="X23" s="580" t="n"/>
+      <c r="Y23" s="580" t="n"/>
+      <c r="Z23" s="580" t="n"/>
       <c r="AA23" s="500" t="n"/>
-      <c r="AB23" s="483" t="n"/>
-      <c r="AC23" s="483" t="n"/>
-      <c r="AD23" s="483" t="n"/>
-      <c r="AE23" s="483" t="n"/>
-      <c r="AF23" s="483" t="n"/>
-      <c r="AG23" s="483" t="n"/>
-      <c r="AH23" s="483" t="n"/>
-      <c r="AI23" s="483" t="n"/>
-      <c r="AJ23" s="483" t="n"/>
-      <c r="AK23" s="483" t="n"/>
-      <c r="AL23" s="483" t="n"/>
-      <c r="AM23" s="483" t="n"/>
-      <c r="AN23" s="483" t="n"/>
-      <c r="AO23" s="483" t="n"/>
-      <c r="AP23" s="483" t="n"/>
-      <c r="AQ23" s="483" t="n"/>
+      <c r="AB23" s="580" t="n"/>
+      <c r="AC23" s="580" t="n"/>
+      <c r="AD23" s="580" t="n"/>
+      <c r="AE23" s="580" t="n"/>
+      <c r="AF23" s="580" t="n"/>
+      <c r="AG23" s="580" t="n"/>
+      <c r="AH23" s="580" t="n"/>
+      <c r="AI23" s="580" t="n"/>
+      <c r="AJ23" s="580" t="n"/>
+      <c r="AK23" s="580" t="n"/>
+      <c r="AL23" s="580" t="n"/>
+      <c r="AM23" s="580" t="n"/>
+      <c r="AN23" s="580" t="n"/>
+      <c r="AO23" s="580" t="n"/>
+      <c r="AP23" s="580" t="n"/>
+      <c r="AQ23" s="580" t="n"/>
       <c r="AR23" s="482" t="n"/>
-      <c r="AS23" s="483" t="n"/>
-      <c r="AT23" s="483" t="n"/>
-      <c r="AU23" s="483" t="n"/>
-      <c r="AV23" s="483" t="n"/>
-      <c r="AW23" s="483" t="n"/>
+      <c r="AS23" s="580" t="n"/>
+      <c r="AT23" s="580" t="n"/>
+      <c r="AU23" s="580" t="n"/>
+      <c r="AV23" s="580" t="n"/>
+      <c r="AW23" s="580" t="n"/>
       <c r="AX23" s="482" t="n"/>
-      <c r="AY23" s="483" t="n"/>
-      <c r="AZ23" s="483" t="n"/>
-      <c r="BA23" s="483" t="n"/>
-      <c r="BB23" s="501" t="n"/>
-      <c r="BC23" s="483" t="n"/>
-      <c r="BD23" s="485" t="n"/>
+      <c r="AY23" s="580" t="n"/>
+      <c r="AZ23" s="580" t="n"/>
+      <c r="BA23" s="580" t="n"/>
+      <c r="BB23" s="586" t="n"/>
+      <c r="BC23" s="580" t="n"/>
+      <c r="BD23" s="582" t="n"/>
     </row>
     <row r="24" ht="3" customHeight="1">
       <c r="A24" s="375" t="n"/>
@@ -7676,66 +8081,66 @@
       <c r="BD24" s="353" t="n"/>
     </row>
     <row r="25" ht="18" customHeight="1">
-      <c r="A25" s="467" t="inlineStr">
+      <c r="A25" s="570" t="inlineStr">
         <is>
           <t xml:space="preserve">  3. CONDITIONS / ACTIONS / RELEASE</t>
         </is>
       </c>
-      <c r="B25" s="468" t="n"/>
-      <c r="C25" s="468" t="n"/>
-      <c r="D25" s="468" t="n"/>
-      <c r="E25" s="468" t="n"/>
-      <c r="F25" s="468" t="n"/>
-      <c r="G25" s="468" t="n"/>
-      <c r="H25" s="468" t="n"/>
-      <c r="I25" s="468" t="n"/>
-      <c r="J25" s="468" t="n"/>
-      <c r="K25" s="468" t="n"/>
-      <c r="L25" s="468" t="n"/>
-      <c r="M25" s="468" t="n"/>
-      <c r="N25" s="468" t="n"/>
-      <c r="O25" s="468" t="n"/>
-      <c r="P25" s="468" t="n"/>
-      <c r="Q25" s="468" t="n"/>
-      <c r="R25" s="468" t="n"/>
-      <c r="S25" s="468" t="n"/>
-      <c r="T25" s="468" t="n"/>
-      <c r="U25" s="468" t="n"/>
-      <c r="V25" s="468" t="n"/>
-      <c r="W25" s="468" t="n"/>
-      <c r="X25" s="468" t="n"/>
-      <c r="Y25" s="468" t="n"/>
-      <c r="Z25" s="468" t="n"/>
-      <c r="AA25" s="468" t="n"/>
-      <c r="AB25" s="468" t="n"/>
-      <c r="AC25" s="468" t="n"/>
-      <c r="AD25" s="468" t="n"/>
-      <c r="AE25" s="468" t="n"/>
-      <c r="AF25" s="468" t="n"/>
-      <c r="AG25" s="468" t="n"/>
-      <c r="AH25" s="468" t="n"/>
-      <c r="AI25" s="468" t="n"/>
-      <c r="AJ25" s="468" t="n"/>
-      <c r="AK25" s="468" t="n"/>
-      <c r="AL25" s="468" t="n"/>
-      <c r="AM25" s="468" t="n"/>
-      <c r="AN25" s="468" t="n"/>
-      <c r="AO25" s="468" t="n"/>
-      <c r="AP25" s="468" t="n"/>
-      <c r="AQ25" s="468" t="n"/>
-      <c r="AR25" s="468" t="n"/>
-      <c r="AS25" s="468" t="n"/>
-      <c r="AT25" s="468" t="n"/>
-      <c r="AU25" s="468" t="n"/>
-      <c r="AV25" s="468" t="n"/>
-      <c r="AW25" s="468" t="n"/>
-      <c r="AX25" s="468" t="n"/>
-      <c r="AY25" s="468" t="n"/>
-      <c r="AZ25" s="468" t="n"/>
-      <c r="BA25" s="468" t="n"/>
-      <c r="BB25" s="468" t="n"/>
-      <c r="BC25" s="468" t="n"/>
-      <c r="BD25" s="469" t="n"/>
+      <c r="B25" s="571" t="n"/>
+      <c r="C25" s="571" t="n"/>
+      <c r="D25" s="571" t="n"/>
+      <c r="E25" s="571" t="n"/>
+      <c r="F25" s="571" t="n"/>
+      <c r="G25" s="571" t="n"/>
+      <c r="H25" s="571" t="n"/>
+      <c r="I25" s="571" t="n"/>
+      <c r="J25" s="571" t="n"/>
+      <c r="K25" s="571" t="n"/>
+      <c r="L25" s="571" t="n"/>
+      <c r="M25" s="571" t="n"/>
+      <c r="N25" s="571" t="n"/>
+      <c r="O25" s="571" t="n"/>
+      <c r="P25" s="571" t="n"/>
+      <c r="Q25" s="571" t="n"/>
+      <c r="R25" s="571" t="n"/>
+      <c r="S25" s="571" t="n"/>
+      <c r="T25" s="571" t="n"/>
+      <c r="U25" s="571" t="n"/>
+      <c r="V25" s="571" t="n"/>
+      <c r="W25" s="571" t="n"/>
+      <c r="X25" s="571" t="n"/>
+      <c r="Y25" s="571" t="n"/>
+      <c r="Z25" s="571" t="n"/>
+      <c r="AA25" s="571" t="n"/>
+      <c r="AB25" s="571" t="n"/>
+      <c r="AC25" s="571" t="n"/>
+      <c r="AD25" s="571" t="n"/>
+      <c r="AE25" s="571" t="n"/>
+      <c r="AF25" s="571" t="n"/>
+      <c r="AG25" s="571" t="n"/>
+      <c r="AH25" s="571" t="n"/>
+      <c r="AI25" s="571" t="n"/>
+      <c r="AJ25" s="571" t="n"/>
+      <c r="AK25" s="571" t="n"/>
+      <c r="AL25" s="571" t="n"/>
+      <c r="AM25" s="571" t="n"/>
+      <c r="AN25" s="571" t="n"/>
+      <c r="AO25" s="571" t="n"/>
+      <c r="AP25" s="571" t="n"/>
+      <c r="AQ25" s="571" t="n"/>
+      <c r="AR25" s="571" t="n"/>
+      <c r="AS25" s="571" t="n"/>
+      <c r="AT25" s="571" t="n"/>
+      <c r="AU25" s="571" t="n"/>
+      <c r="AV25" s="571" t="n"/>
+      <c r="AW25" s="571" t="n"/>
+      <c r="AX25" s="571" t="n"/>
+      <c r="AY25" s="571" t="n"/>
+      <c r="AZ25" s="571" t="n"/>
+      <c r="BA25" s="571" t="n"/>
+      <c r="BB25" s="571" t="n"/>
+      <c r="BC25" s="571" t="n"/>
+      <c r="BD25" s="572" t="n"/>
     </row>
     <row r="26" ht="20" customHeight="1">
       <c r="A26" s="470" t="inlineStr">
@@ -7743,65 +8148,65 @@
           <t>Conditional Action Required (YES/NO)</t>
         </is>
       </c>
-      <c r="B26" s="471" t="n"/>
-      <c r="C26" s="471" t="n"/>
-      <c r="D26" s="471" t="n"/>
-      <c r="E26" s="471" t="n"/>
-      <c r="F26" s="471" t="n"/>
-      <c r="G26" s="471" t="n"/>
-      <c r="H26" s="471" t="n"/>
-      <c r="I26" s="471" t="n"/>
-      <c r="J26" s="471" t="n"/>
+      <c r="B26" s="573" t="n"/>
+      <c r="C26" s="573" t="n"/>
+      <c r="D26" s="573" t="n"/>
+      <c r="E26" s="573" t="n"/>
+      <c r="F26" s="573" t="n"/>
+      <c r="G26" s="573" t="n"/>
+      <c r="H26" s="573" t="n"/>
+      <c r="I26" s="573" t="n"/>
+      <c r="J26" s="573" t="n"/>
       <c r="K26" s="472" t="n"/>
-      <c r="L26" s="473" t="n"/>
-      <c r="M26" s="473" t="n"/>
-      <c r="N26" s="473" t="n"/>
-      <c r="O26" s="473" t="n"/>
-      <c r="P26" s="473" t="n"/>
-      <c r="Q26" s="473" t="n"/>
-      <c r="R26" s="473" t="n"/>
-      <c r="S26" s="473" t="n"/>
-      <c r="T26" s="473" t="n"/>
-      <c r="U26" s="473" t="n"/>
-      <c r="V26" s="473" t="n"/>
-      <c r="W26" s="473" t="n"/>
-      <c r="X26" s="473" t="n"/>
-      <c r="Y26" s="473" t="n"/>
-      <c r="Z26" s="473" t="n"/>
-      <c r="AA26" s="473" t="n"/>
-      <c r="AB26" s="473" t="n"/>
+      <c r="L26" s="574" t="n"/>
+      <c r="M26" s="574" t="n"/>
+      <c r="N26" s="574" t="n"/>
+      <c r="O26" s="574" t="n"/>
+      <c r="P26" s="574" t="n"/>
+      <c r="Q26" s="574" t="n"/>
+      <c r="R26" s="574" t="n"/>
+      <c r="S26" s="574" t="n"/>
+      <c r="T26" s="574" t="n"/>
+      <c r="U26" s="574" t="n"/>
+      <c r="V26" s="574" t="n"/>
+      <c r="W26" s="574" t="n"/>
+      <c r="X26" s="574" t="n"/>
+      <c r="Y26" s="574" t="n"/>
+      <c r="Z26" s="574" t="n"/>
+      <c r="AA26" s="574" t="n"/>
+      <c r="AB26" s="574" t="n"/>
       <c r="AC26" s="474" t="inlineStr">
         <is>
           <t>Bagging / Seal Ref</t>
         </is>
       </c>
-      <c r="AD26" s="471" t="n"/>
-      <c r="AE26" s="471" t="n"/>
-      <c r="AF26" s="471" t="n"/>
-      <c r="AG26" s="471" t="n"/>
-      <c r="AH26" s="471" t="n"/>
-      <c r="AI26" s="471" t="n"/>
-      <c r="AJ26" s="471" t="n"/>
-      <c r="AK26" s="471" t="n"/>
-      <c r="AL26" s="471" t="n"/>
-      <c r="AM26" s="472" t="n"/>
-      <c r="AN26" s="473" t="n"/>
-      <c r="AO26" s="473" t="n"/>
-      <c r="AP26" s="473" t="n"/>
-      <c r="AQ26" s="473" t="n"/>
-      <c r="AR26" s="473" t="n"/>
-      <c r="AS26" s="473" t="n"/>
-      <c r="AT26" s="473" t="n"/>
-      <c r="AU26" s="473" t="n"/>
-      <c r="AV26" s="473" t="n"/>
-      <c r="AW26" s="473" t="n"/>
-      <c r="AX26" s="473" t="n"/>
-      <c r="AY26" s="473" t="n"/>
-      <c r="AZ26" s="473" t="n"/>
-      <c r="BA26" s="473" t="n"/>
-      <c r="BB26" s="473" t="n"/>
-      <c r="BC26" s="473" t="n"/>
-      <c r="BD26" s="475" t="n"/>
+      <c r="AD26" s="573" t="n"/>
+      <c r="AE26" s="573" t="n"/>
+      <c r="AF26" s="573" t="n"/>
+      <c r="AG26" s="573" t="n"/>
+      <c r="AH26" s="573" t="n"/>
+      <c r="AI26" s="573" t="n"/>
+      <c r="AJ26" s="573" t="n"/>
+      <c r="AK26" s="573" t="n"/>
+      <c r="AL26" s="573" t="n"/>
+      <c r="AM26" s="575" t="n"/>
+      <c r="AN26" s="574" t="n"/>
+      <c r="AO26" s="574" t="n"/>
+      <c r="AP26" s="574" t="n"/>
+      <c r="AQ26" s="574" t="n"/>
+      <c r="AR26" s="574" t="n"/>
+      <c r="AS26" s="574" t="n"/>
+      <c r="AT26" s="574" t="n"/>
+      <c r="AU26" s="574" t="n"/>
+      <c r="AV26" s="574" t="n"/>
+      <c r="AW26" s="574" t="n"/>
+      <c r="AX26" s="574" t="n"/>
+      <c r="AY26" s="574" t="n"/>
+      <c r="AZ26" s="574" t="n"/>
+      <c r="BA26" s="574" t="n"/>
+      <c r="BB26" s="574" t="n"/>
+      <c r="BC26" s="574" t="n"/>
+      <c r="BD26" s="576" t="n"/>
     </row>
     <row r="27" ht="20" customHeight="1">
       <c r="A27" s="480" t="inlineStr">
@@ -7809,65 +8214,65 @@
           <t>Final Release Decision</t>
         </is>
       </c>
-      <c r="B27" s="481" t="n"/>
-      <c r="C27" s="481" t="n"/>
-      <c r="D27" s="481" t="n"/>
-      <c r="E27" s="481" t="n"/>
-      <c r="F27" s="481" t="n"/>
-      <c r="G27" s="481" t="n"/>
-      <c r="H27" s="481" t="n"/>
-      <c r="I27" s="481" t="n"/>
-      <c r="J27" s="481" t="n"/>
+      <c r="B27" s="566" t="n"/>
+      <c r="C27" s="566" t="n"/>
+      <c r="D27" s="566" t="n"/>
+      <c r="E27" s="566" t="n"/>
+      <c r="F27" s="566" t="n"/>
+      <c r="G27" s="566" t="n"/>
+      <c r="H27" s="566" t="n"/>
+      <c r="I27" s="566" t="n"/>
+      <c r="J27" s="566" t="n"/>
       <c r="K27" s="482" t="n"/>
-      <c r="L27" s="483" t="n"/>
-      <c r="M27" s="483" t="n"/>
-      <c r="N27" s="483" t="n"/>
-      <c r="O27" s="483" t="n"/>
-      <c r="P27" s="483" t="n"/>
-      <c r="Q27" s="483" t="n"/>
-      <c r="R27" s="483" t="n"/>
-      <c r="S27" s="483" t="n"/>
-      <c r="T27" s="483" t="n"/>
-      <c r="U27" s="483" t="n"/>
-      <c r="V27" s="483" t="n"/>
-      <c r="W27" s="483" t="n"/>
-      <c r="X27" s="483" t="n"/>
-      <c r="Y27" s="483" t="n"/>
-      <c r="Z27" s="483" t="n"/>
-      <c r="AA27" s="483" t="n"/>
-      <c r="AB27" s="483" t="n"/>
+      <c r="L27" s="580" t="n"/>
+      <c r="M27" s="580" t="n"/>
+      <c r="N27" s="580" t="n"/>
+      <c r="O27" s="580" t="n"/>
+      <c r="P27" s="580" t="n"/>
+      <c r="Q27" s="580" t="n"/>
+      <c r="R27" s="580" t="n"/>
+      <c r="S27" s="580" t="n"/>
+      <c r="T27" s="580" t="n"/>
+      <c r="U27" s="580" t="n"/>
+      <c r="V27" s="580" t="n"/>
+      <c r="W27" s="580" t="n"/>
+      <c r="X27" s="580" t="n"/>
+      <c r="Y27" s="580" t="n"/>
+      <c r="Z27" s="580" t="n"/>
+      <c r="AA27" s="580" t="n"/>
+      <c r="AB27" s="580" t="n"/>
       <c r="AC27" s="484" t="inlineStr">
         <is>
           <t>Approved by</t>
         </is>
       </c>
-      <c r="AD27" s="481" t="n"/>
-      <c r="AE27" s="481" t="n"/>
-      <c r="AF27" s="481" t="n"/>
-      <c r="AG27" s="481" t="n"/>
-      <c r="AH27" s="481" t="n"/>
-      <c r="AI27" s="481" t="n"/>
-      <c r="AJ27" s="481" t="n"/>
-      <c r="AK27" s="481" t="n"/>
-      <c r="AL27" s="481" t="n"/>
-      <c r="AM27" s="482" t="n"/>
-      <c r="AN27" s="483" t="n"/>
-      <c r="AO27" s="483" t="n"/>
-      <c r="AP27" s="483" t="n"/>
-      <c r="AQ27" s="483" t="n"/>
-      <c r="AR27" s="483" t="n"/>
-      <c r="AS27" s="483" t="n"/>
-      <c r="AT27" s="483" t="n"/>
-      <c r="AU27" s="483" t="n"/>
-      <c r="AV27" s="483" t="n"/>
-      <c r="AW27" s="483" t="n"/>
-      <c r="AX27" s="483" t="n"/>
-      <c r="AY27" s="483" t="n"/>
-      <c r="AZ27" s="483" t="n"/>
-      <c r="BA27" s="483" t="n"/>
-      <c r="BB27" s="483" t="n"/>
-      <c r="BC27" s="483" t="n"/>
-      <c r="BD27" s="485" t="n"/>
+      <c r="AD27" s="566" t="n"/>
+      <c r="AE27" s="566" t="n"/>
+      <c r="AF27" s="566" t="n"/>
+      <c r="AG27" s="566" t="n"/>
+      <c r="AH27" s="566" t="n"/>
+      <c r="AI27" s="566" t="n"/>
+      <c r="AJ27" s="566" t="n"/>
+      <c r="AK27" s="566" t="n"/>
+      <c r="AL27" s="566" t="n"/>
+      <c r="AM27" s="581" t="n"/>
+      <c r="AN27" s="580" t="n"/>
+      <c r="AO27" s="580" t="n"/>
+      <c r="AP27" s="580" t="n"/>
+      <c r="AQ27" s="580" t="n"/>
+      <c r="AR27" s="580" t="n"/>
+      <c r="AS27" s="580" t="n"/>
+      <c r="AT27" s="580" t="n"/>
+      <c r="AU27" s="580" t="n"/>
+      <c r="AV27" s="580" t="n"/>
+      <c r="AW27" s="580" t="n"/>
+      <c r="AX27" s="580" t="n"/>
+      <c r="AY27" s="580" t="n"/>
+      <c r="AZ27" s="580" t="n"/>
+      <c r="BA27" s="580" t="n"/>
+      <c r="BB27" s="580" t="n"/>
+      <c r="BC27" s="580" t="n"/>
+      <c r="BD27" s="582" t="n"/>
     </row>
     <row r="28" ht="3" customHeight="1">
       <c r="A28" s="375" t="n"/>
@@ -7928,66 +8333,66 @@
       <c r="BD28" s="353" t="n"/>
     </row>
     <row r="29" ht="18" customHeight="1">
-      <c r="A29" s="467" t="inlineStr">
+      <c r="A29" s="570" t="inlineStr">
         <is>
           <t xml:space="preserve">  4. APPROVAL / SIGN-OFF</t>
         </is>
       </c>
-      <c r="B29" s="468" t="n"/>
-      <c r="C29" s="468" t="n"/>
-      <c r="D29" s="468" t="n"/>
-      <c r="E29" s="468" t="n"/>
-      <c r="F29" s="468" t="n"/>
-      <c r="G29" s="468" t="n"/>
-      <c r="H29" s="468" t="n"/>
-      <c r="I29" s="468" t="n"/>
-      <c r="J29" s="468" t="n"/>
-      <c r="K29" s="468" t="n"/>
-      <c r="L29" s="468" t="n"/>
-      <c r="M29" s="468" t="n"/>
-      <c r="N29" s="468" t="n"/>
-      <c r="O29" s="468" t="n"/>
-      <c r="P29" s="468" t="n"/>
-      <c r="Q29" s="468" t="n"/>
-      <c r="R29" s="468" t="n"/>
-      <c r="S29" s="468" t="n"/>
-      <c r="T29" s="468" t="n"/>
-      <c r="U29" s="468" t="n"/>
-      <c r="V29" s="468" t="n"/>
-      <c r="W29" s="468" t="n"/>
-      <c r="X29" s="468" t="n"/>
-      <c r="Y29" s="468" t="n"/>
-      <c r="Z29" s="468" t="n"/>
-      <c r="AA29" s="468" t="n"/>
-      <c r="AB29" s="468" t="n"/>
-      <c r="AC29" s="468" t="n"/>
-      <c r="AD29" s="468" t="n"/>
-      <c r="AE29" s="468" t="n"/>
-      <c r="AF29" s="468" t="n"/>
-      <c r="AG29" s="468" t="n"/>
-      <c r="AH29" s="468" t="n"/>
-      <c r="AI29" s="468" t="n"/>
-      <c r="AJ29" s="468" t="n"/>
-      <c r="AK29" s="468" t="n"/>
-      <c r="AL29" s="468" t="n"/>
-      <c r="AM29" s="468" t="n"/>
-      <c r="AN29" s="468" t="n"/>
-      <c r="AO29" s="468" t="n"/>
-      <c r="AP29" s="468" t="n"/>
-      <c r="AQ29" s="468" t="n"/>
-      <c r="AR29" s="468" t="n"/>
-      <c r="AS29" s="468" t="n"/>
-      <c r="AT29" s="468" t="n"/>
-      <c r="AU29" s="468" t="n"/>
-      <c r="AV29" s="468" t="n"/>
-      <c r="AW29" s="468" t="n"/>
-      <c r="AX29" s="468" t="n"/>
-      <c r="AY29" s="468" t="n"/>
-      <c r="AZ29" s="468" t="n"/>
-      <c r="BA29" s="468" t="n"/>
-      <c r="BB29" s="468" t="n"/>
-      <c r="BC29" s="468" t="n"/>
-      <c r="BD29" s="469" t="n"/>
+      <c r="B29" s="571" t="n"/>
+      <c r="C29" s="571" t="n"/>
+      <c r="D29" s="571" t="n"/>
+      <c r="E29" s="571" t="n"/>
+      <c r="F29" s="571" t="n"/>
+      <c r="G29" s="571" t="n"/>
+      <c r="H29" s="571" t="n"/>
+      <c r="I29" s="571" t="n"/>
+      <c r="J29" s="571" t="n"/>
+      <c r="K29" s="571" t="n"/>
+      <c r="L29" s="571" t="n"/>
+      <c r="M29" s="571" t="n"/>
+      <c r="N29" s="571" t="n"/>
+      <c r="O29" s="571" t="n"/>
+      <c r="P29" s="571" t="n"/>
+      <c r="Q29" s="571" t="n"/>
+      <c r="R29" s="571" t="n"/>
+      <c r="S29" s="571" t="n"/>
+      <c r="T29" s="571" t="n"/>
+      <c r="U29" s="571" t="n"/>
+      <c r="V29" s="571" t="n"/>
+      <c r="W29" s="571" t="n"/>
+      <c r="X29" s="571" t="n"/>
+      <c r="Y29" s="571" t="n"/>
+      <c r="Z29" s="571" t="n"/>
+      <c r="AA29" s="571" t="n"/>
+      <c r="AB29" s="571" t="n"/>
+      <c r="AC29" s="571" t="n"/>
+      <c r="AD29" s="571" t="n"/>
+      <c r="AE29" s="571" t="n"/>
+      <c r="AF29" s="571" t="n"/>
+      <c r="AG29" s="571" t="n"/>
+      <c r="AH29" s="571" t="n"/>
+      <c r="AI29" s="571" t="n"/>
+      <c r="AJ29" s="571" t="n"/>
+      <c r="AK29" s="571" t="n"/>
+      <c r="AL29" s="571" t="n"/>
+      <c r="AM29" s="571" t="n"/>
+      <c r="AN29" s="571" t="n"/>
+      <c r="AO29" s="571" t="n"/>
+      <c r="AP29" s="571" t="n"/>
+      <c r="AQ29" s="571" t="n"/>
+      <c r="AR29" s="571" t="n"/>
+      <c r="AS29" s="571" t="n"/>
+      <c r="AT29" s="571" t="n"/>
+      <c r="AU29" s="571" t="n"/>
+      <c r="AV29" s="571" t="n"/>
+      <c r="AW29" s="571" t="n"/>
+      <c r="AX29" s="571" t="n"/>
+      <c r="AY29" s="571" t="n"/>
+      <c r="AZ29" s="571" t="n"/>
+      <c r="BA29" s="571" t="n"/>
+      <c r="BB29" s="571" t="n"/>
+      <c r="BC29" s="571" t="n"/>
+      <c r="BD29" s="572" t="n"/>
     </row>
     <row r="30" ht="26" customHeight="1">
       <c r="A30" s="490" t="inlineStr">
@@ -7995,69 +8400,69 @@
           <t>Prepared by</t>
         </is>
       </c>
-      <c r="B30" s="471" t="n"/>
-      <c r="C30" s="471" t="n"/>
-      <c r="D30" s="471" t="n"/>
-      <c r="E30" s="471" t="n"/>
-      <c r="F30" s="471" t="n"/>
-      <c r="G30" s="471" t="n"/>
-      <c r="H30" s="471" t="n"/>
-      <c r="I30" s="471" t="n"/>
-      <c r="J30" s="471" t="n"/>
-      <c r="K30" s="471" t="n"/>
-      <c r="L30" s="471" t="n"/>
-      <c r="M30" s="471" t="n"/>
-      <c r="N30" s="471" t="n"/>
-      <c r="O30" s="471" t="n"/>
-      <c r="P30" s="471" t="n"/>
-      <c r="Q30" s="471" t="n"/>
-      <c r="R30" s="471" t="n"/>
+      <c r="B30" s="573" t="n"/>
+      <c r="C30" s="573" t="n"/>
+      <c r="D30" s="573" t="n"/>
+      <c r="E30" s="573" t="n"/>
+      <c r="F30" s="573" t="n"/>
+      <c r="G30" s="573" t="n"/>
+      <c r="H30" s="573" t="n"/>
+      <c r="I30" s="573" t="n"/>
+      <c r="J30" s="573" t="n"/>
+      <c r="K30" s="573" t="n"/>
+      <c r="L30" s="573" t="n"/>
+      <c r="M30" s="573" t="n"/>
+      <c r="N30" s="573" t="n"/>
+      <c r="O30" s="573" t="n"/>
+      <c r="P30" s="573" t="n"/>
+      <c r="Q30" s="573" t="n"/>
+      <c r="R30" s="573" t="n"/>
       <c r="S30" s="502" t="inlineStr">
         <is>
           <t>Reviewed by</t>
         </is>
       </c>
-      <c r="T30" s="471" t="n"/>
-      <c r="U30" s="471" t="n"/>
-      <c r="V30" s="471" t="n"/>
-      <c r="W30" s="471" t="n"/>
-      <c r="X30" s="471" t="n"/>
-      <c r="Y30" s="471" t="n"/>
-      <c r="Z30" s="471" t="n"/>
-      <c r="AA30" s="471" t="n"/>
-      <c r="AB30" s="471" t="n"/>
-      <c r="AC30" s="471" t="n"/>
-      <c r="AD30" s="471" t="n"/>
-      <c r="AE30" s="471" t="n"/>
-      <c r="AF30" s="471" t="n"/>
-      <c r="AG30" s="471" t="n"/>
-      <c r="AH30" s="471" t="n"/>
-      <c r="AI30" s="471" t="n"/>
-      <c r="AJ30" s="471" t="n"/>
-      <c r="AK30" s="502" t="inlineStr">
+      <c r="T30" s="573" t="n"/>
+      <c r="U30" s="573" t="n"/>
+      <c r="V30" s="573" t="n"/>
+      <c r="W30" s="573" t="n"/>
+      <c r="X30" s="573" t="n"/>
+      <c r="Y30" s="573" t="n"/>
+      <c r="Z30" s="573" t="n"/>
+      <c r="AA30" s="573" t="n"/>
+      <c r="AB30" s="573" t="n"/>
+      <c r="AC30" s="573" t="n"/>
+      <c r="AD30" s="573" t="n"/>
+      <c r="AE30" s="573" t="n"/>
+      <c r="AF30" s="573" t="n"/>
+      <c r="AG30" s="573" t="n"/>
+      <c r="AH30" s="573" t="n"/>
+      <c r="AI30" s="573" t="n"/>
+      <c r="AJ30" s="573" t="n"/>
+      <c r="AK30" s="587" t="inlineStr">
         <is>
           <t>Approved by</t>
         </is>
       </c>
-      <c r="AL30" s="471" t="n"/>
-      <c r="AM30" s="471" t="n"/>
-      <c r="AN30" s="471" t="n"/>
-      <c r="AO30" s="471" t="n"/>
-      <c r="AP30" s="471" t="n"/>
-      <c r="AQ30" s="471" t="n"/>
-      <c r="AR30" s="471" t="n"/>
-      <c r="AS30" s="471" t="n"/>
-      <c r="AT30" s="471" t="n"/>
-      <c r="AU30" s="471" t="n"/>
-      <c r="AV30" s="471" t="n"/>
-      <c r="AW30" s="471" t="n"/>
-      <c r="AX30" s="471" t="n"/>
-      <c r="AY30" s="471" t="n"/>
-      <c r="AZ30" s="471" t="n"/>
-      <c r="BA30" s="471" t="n"/>
-      <c r="BB30" s="471" t="n"/>
-      <c r="BC30" s="471" t="n"/>
-      <c r="BD30" s="503" t="n"/>
+      <c r="AL30" s="573" t="n"/>
+      <c r="AM30" s="573" t="n"/>
+      <c r="AN30" s="573" t="n"/>
+      <c r="AO30" s="573" t="n"/>
+      <c r="AP30" s="573" t="n"/>
+      <c r="AQ30" s="573" t="n"/>
+      <c r="AR30" s="573" t="n"/>
+      <c r="AS30" s="573" t="n"/>
+      <c r="AT30" s="573" t="n"/>
+      <c r="AU30" s="573" t="n"/>
+      <c r="AV30" s="573" t="n"/>
+      <c r="AW30" s="573" t="n"/>
+      <c r="AX30" s="573" t="n"/>
+      <c r="AY30" s="573" t="n"/>
+      <c r="AZ30" s="573" t="n"/>
+      <c r="BA30" s="573" t="n"/>
+      <c r="BB30" s="573" t="n"/>
+      <c r="BC30" s="573" t="n"/>
+      <c r="BD30" s="588" t="n"/>
     </row>
     <row r="31" ht="26" customHeight="1">
       <c r="A31" s="504" t="inlineStr">
@@ -8065,185 +8470,185 @@
           <t>Name / Signature / Date</t>
         </is>
       </c>
-      <c r="B31" s="362" t="n"/>
-      <c r="C31" s="362" t="n"/>
-      <c r="D31" s="362" t="n"/>
-      <c r="E31" s="362" t="n"/>
-      <c r="F31" s="362" t="n"/>
-      <c r="G31" s="362" t="n"/>
-      <c r="H31" s="362" t="n"/>
-      <c r="I31" s="362" t="n"/>
-      <c r="J31" s="362" t="n"/>
-      <c r="K31" s="362" t="n"/>
-      <c r="L31" s="362" t="n"/>
-      <c r="M31" s="362" t="n"/>
-      <c r="N31" s="362" t="n"/>
-      <c r="O31" s="362" t="n"/>
-      <c r="P31" s="362" t="n"/>
-      <c r="Q31" s="362" t="n"/>
-      <c r="R31" s="362" t="n"/>
+      <c r="B31" s="589" t="n"/>
+      <c r="C31" s="589" t="n"/>
+      <c r="D31" s="589" t="n"/>
+      <c r="E31" s="589" t="n"/>
+      <c r="F31" s="589" t="n"/>
+      <c r="G31" s="589" t="n"/>
+      <c r="H31" s="589" t="n"/>
+      <c r="I31" s="589" t="n"/>
+      <c r="J31" s="589" t="n"/>
+      <c r="K31" s="589" t="n"/>
+      <c r="L31" s="589" t="n"/>
+      <c r="M31" s="589" t="n"/>
+      <c r="N31" s="589" t="n"/>
+      <c r="O31" s="589" t="n"/>
+      <c r="P31" s="589" t="n"/>
+      <c r="Q31" s="589" t="n"/>
+      <c r="R31" s="589" t="n"/>
       <c r="S31" s="505" t="inlineStr">
         <is>
           <t>Name / Signature / Date</t>
         </is>
       </c>
-      <c r="T31" s="362" t="n"/>
-      <c r="U31" s="362" t="n"/>
-      <c r="V31" s="362" t="n"/>
-      <c r="W31" s="362" t="n"/>
-      <c r="X31" s="362" t="n"/>
-      <c r="Y31" s="362" t="n"/>
-      <c r="Z31" s="362" t="n"/>
-      <c r="AA31" s="362" t="n"/>
-      <c r="AB31" s="362" t="n"/>
-      <c r="AC31" s="362" t="n"/>
-      <c r="AD31" s="362" t="n"/>
-      <c r="AE31" s="362" t="n"/>
-      <c r="AF31" s="362" t="n"/>
-      <c r="AG31" s="362" t="n"/>
-      <c r="AH31" s="362" t="n"/>
-      <c r="AI31" s="362" t="n"/>
-      <c r="AJ31" s="362" t="n"/>
-      <c r="AK31" s="505" t="inlineStr">
+      <c r="T31" s="589" t="n"/>
+      <c r="U31" s="589" t="n"/>
+      <c r="V31" s="589" t="n"/>
+      <c r="W31" s="589" t="n"/>
+      <c r="X31" s="589" t="n"/>
+      <c r="Y31" s="589" t="n"/>
+      <c r="Z31" s="589" t="n"/>
+      <c r="AA31" s="589" t="n"/>
+      <c r="AB31" s="589" t="n"/>
+      <c r="AC31" s="589" t="n"/>
+      <c r="AD31" s="589" t="n"/>
+      <c r="AE31" s="589" t="n"/>
+      <c r="AF31" s="589" t="n"/>
+      <c r="AG31" s="589" t="n"/>
+      <c r="AH31" s="589" t="n"/>
+      <c r="AI31" s="589" t="n"/>
+      <c r="AJ31" s="589" t="n"/>
+      <c r="AK31" s="590" t="inlineStr">
         <is>
           <t>Name / Signature / Date</t>
         </is>
       </c>
-      <c r="AL31" s="362" t="n"/>
-      <c r="AM31" s="362" t="n"/>
-      <c r="AN31" s="362" t="n"/>
-      <c r="AO31" s="362" t="n"/>
-      <c r="AP31" s="362" t="n"/>
-      <c r="AQ31" s="362" t="n"/>
-      <c r="AR31" s="362" t="n"/>
-      <c r="AS31" s="362" t="n"/>
-      <c r="AT31" s="362" t="n"/>
-      <c r="AU31" s="362" t="n"/>
-      <c r="AV31" s="362" t="n"/>
-      <c r="AW31" s="362" t="n"/>
-      <c r="AX31" s="362" t="n"/>
-      <c r="AY31" s="362" t="n"/>
-      <c r="AZ31" s="362" t="n"/>
-      <c r="BA31" s="362" t="n"/>
-      <c r="BB31" s="362" t="n"/>
-      <c r="BC31" s="362" t="n"/>
-      <c r="BD31" s="479" t="n"/>
+      <c r="AL31" s="589" t="n"/>
+      <c r="AM31" s="589" t="n"/>
+      <c r="AN31" s="589" t="n"/>
+      <c r="AO31" s="589" t="n"/>
+      <c r="AP31" s="589" t="n"/>
+      <c r="AQ31" s="589" t="n"/>
+      <c r="AR31" s="589" t="n"/>
+      <c r="AS31" s="589" t="n"/>
+      <c r="AT31" s="589" t="n"/>
+      <c r="AU31" s="589" t="n"/>
+      <c r="AV31" s="589" t="n"/>
+      <c r="AW31" s="589" t="n"/>
+      <c r="AX31" s="589" t="n"/>
+      <c r="AY31" s="589" t="n"/>
+      <c r="AZ31" s="589" t="n"/>
+      <c r="BA31" s="589" t="n"/>
+      <c r="BB31" s="589" t="n"/>
+      <c r="BC31" s="589" t="n"/>
+      <c r="BD31" s="591" t="n"/>
     </row>
     <row r="32" ht="20" customHeight="1">
-      <c r="A32" s="506" t="n"/>
-      <c r="B32" s="362" t="n"/>
-      <c r="C32" s="362" t="n"/>
-      <c r="D32" s="362" t="n"/>
-      <c r="E32" s="362" t="n"/>
-      <c r="F32" s="362" t="n"/>
-      <c r="G32" s="362" t="n"/>
-      <c r="H32" s="362" t="n"/>
-      <c r="I32" s="362" t="n"/>
-      <c r="J32" s="362" t="n"/>
-      <c r="K32" s="362" t="n"/>
-      <c r="L32" s="362" t="n"/>
-      <c r="M32" s="362" t="n"/>
-      <c r="N32" s="362" t="n"/>
-      <c r="O32" s="362" t="n"/>
-      <c r="P32" s="362" t="n"/>
-      <c r="Q32" s="362" t="n"/>
-      <c r="R32" s="362" t="n"/>
-      <c r="S32" s="507" t="n"/>
-      <c r="T32" s="362" t="n"/>
-      <c r="U32" s="362" t="n"/>
-      <c r="V32" s="362" t="n"/>
-      <c r="W32" s="362" t="n"/>
-      <c r="X32" s="362" t="n"/>
-      <c r="Y32" s="362" t="n"/>
-      <c r="Z32" s="362" t="n"/>
-      <c r="AA32" s="362" t="n"/>
-      <c r="AB32" s="362" t="n"/>
-      <c r="AC32" s="362" t="n"/>
-      <c r="AD32" s="362" t="n"/>
-      <c r="AE32" s="362" t="n"/>
-      <c r="AF32" s="362" t="n"/>
-      <c r="AG32" s="362" t="n"/>
-      <c r="AH32" s="362" t="n"/>
-      <c r="AI32" s="362" t="n"/>
-      <c r="AJ32" s="362" t="n"/>
-      <c r="AK32" s="507" t="n"/>
-      <c r="AL32" s="362" t="n"/>
-      <c r="AM32" s="362" t="n"/>
-      <c r="AN32" s="362" t="n"/>
-      <c r="AO32" s="362" t="n"/>
-      <c r="AP32" s="362" t="n"/>
-      <c r="AQ32" s="362" t="n"/>
-      <c r="AR32" s="362" t="n"/>
-      <c r="AS32" s="362" t="n"/>
-      <c r="AT32" s="362" t="n"/>
-      <c r="AU32" s="362" t="n"/>
-      <c r="AV32" s="362" t="n"/>
-      <c r="AW32" s="362" t="n"/>
-      <c r="AX32" s="362" t="n"/>
-      <c r="AY32" s="362" t="n"/>
-      <c r="AZ32" s="362" t="n"/>
-      <c r="BA32" s="362" t="n"/>
-      <c r="BB32" s="362" t="n"/>
-      <c r="BC32" s="362" t="n"/>
-      <c r="BD32" s="479" t="n"/>
+      <c r="A32" s="592" t="n"/>
+      <c r="B32" s="331" t="n"/>
+      <c r="C32" s="331" t="n"/>
+      <c r="D32" s="331" t="n"/>
+      <c r="E32" s="331" t="n"/>
+      <c r="F32" s="331" t="n"/>
+      <c r="G32" s="331" t="n"/>
+      <c r="H32" s="331" t="n"/>
+      <c r="I32" s="331" t="n"/>
+      <c r="J32" s="331" t="n"/>
+      <c r="K32" s="331" t="n"/>
+      <c r="L32" s="331" t="n"/>
+      <c r="M32" s="331" t="n"/>
+      <c r="N32" s="331" t="n"/>
+      <c r="O32" s="331" t="n"/>
+      <c r="P32" s="331" t="n"/>
+      <c r="Q32" s="331" t="n"/>
+      <c r="R32" s="331" t="n"/>
+      <c r="S32" s="593" t="n"/>
+      <c r="T32" s="331" t="n"/>
+      <c r="U32" s="331" t="n"/>
+      <c r="V32" s="331" t="n"/>
+      <c r="W32" s="331" t="n"/>
+      <c r="X32" s="331" t="n"/>
+      <c r="Y32" s="331" t="n"/>
+      <c r="Z32" s="331" t="n"/>
+      <c r="AA32" s="331" t="n"/>
+      <c r="AB32" s="331" t="n"/>
+      <c r="AC32" s="331" t="n"/>
+      <c r="AD32" s="331" t="n"/>
+      <c r="AE32" s="331" t="n"/>
+      <c r="AF32" s="331" t="n"/>
+      <c r="AG32" s="331" t="n"/>
+      <c r="AH32" s="331" t="n"/>
+      <c r="AI32" s="331" t="n"/>
+      <c r="AJ32" s="331" t="n"/>
+      <c r="AK32" s="593" t="n"/>
+      <c r="AL32" s="331" t="n"/>
+      <c r="AM32" s="331" t="n"/>
+      <c r="AN32" s="331" t="n"/>
+      <c r="AO32" s="331" t="n"/>
+      <c r="AP32" s="331" t="n"/>
+      <c r="AQ32" s="331" t="n"/>
+      <c r="AR32" s="331" t="n"/>
+      <c r="AS32" s="331" t="n"/>
+      <c r="AT32" s="331" t="n"/>
+      <c r="AU32" s="331" t="n"/>
+      <c r="AV32" s="331" t="n"/>
+      <c r="AW32" s="331" t="n"/>
+      <c r="AX32" s="331" t="n"/>
+      <c r="AY32" s="331" t="n"/>
+      <c r="AZ32" s="331" t="n"/>
+      <c r="BA32" s="331" t="n"/>
+      <c r="BB32" s="331" t="n"/>
+      <c r="BC32" s="331" t="n"/>
+      <c r="BD32" s="594" t="n"/>
     </row>
     <row r="33" ht="20" customHeight="1">
-      <c r="A33" s="508" t="n"/>
-      <c r="B33" s="483" t="n"/>
-      <c r="C33" s="483" t="n"/>
-      <c r="D33" s="483" t="n"/>
-      <c r="E33" s="483" t="n"/>
-      <c r="F33" s="483" t="n"/>
-      <c r="G33" s="483" t="n"/>
-      <c r="H33" s="483" t="n"/>
-      <c r="I33" s="483" t="n"/>
-      <c r="J33" s="483" t="n"/>
-      <c r="K33" s="483" t="n"/>
-      <c r="L33" s="483" t="n"/>
-      <c r="M33" s="483" t="n"/>
-      <c r="N33" s="483" t="n"/>
-      <c r="O33" s="483" t="n"/>
-      <c r="P33" s="483" t="n"/>
-      <c r="Q33" s="483" t="n"/>
-      <c r="R33" s="483" t="n"/>
-      <c r="S33" s="509" t="n"/>
-      <c r="T33" s="483" t="n"/>
-      <c r="U33" s="483" t="n"/>
-      <c r="V33" s="483" t="n"/>
-      <c r="W33" s="483" t="n"/>
-      <c r="X33" s="483" t="n"/>
-      <c r="Y33" s="483" t="n"/>
-      <c r="Z33" s="483" t="n"/>
-      <c r="AA33" s="483" t="n"/>
-      <c r="AB33" s="483" t="n"/>
-      <c r="AC33" s="483" t="n"/>
-      <c r="AD33" s="483" t="n"/>
-      <c r="AE33" s="483" t="n"/>
-      <c r="AF33" s="483" t="n"/>
-      <c r="AG33" s="483" t="n"/>
-      <c r="AH33" s="483" t="n"/>
-      <c r="AI33" s="483" t="n"/>
-      <c r="AJ33" s="483" t="n"/>
-      <c r="AK33" s="509" t="n"/>
-      <c r="AL33" s="483" t="n"/>
-      <c r="AM33" s="483" t="n"/>
-      <c r="AN33" s="483" t="n"/>
-      <c r="AO33" s="483" t="n"/>
-      <c r="AP33" s="483" t="n"/>
-      <c r="AQ33" s="483" t="n"/>
-      <c r="AR33" s="483" t="n"/>
-      <c r="AS33" s="483" t="n"/>
-      <c r="AT33" s="483" t="n"/>
-      <c r="AU33" s="483" t="n"/>
-      <c r="AV33" s="483" t="n"/>
-      <c r="AW33" s="483" t="n"/>
-      <c r="AX33" s="483" t="n"/>
-      <c r="AY33" s="483" t="n"/>
-      <c r="AZ33" s="483" t="n"/>
-      <c r="BA33" s="483" t="n"/>
-      <c r="BB33" s="483" t="n"/>
-      <c r="BC33" s="483" t="n"/>
-      <c r="BD33" s="485" t="n"/>
+      <c r="A33" s="595" t="n"/>
+      <c r="B33" s="596" t="n"/>
+      <c r="C33" s="596" t="n"/>
+      <c r="D33" s="596" t="n"/>
+      <c r="E33" s="596" t="n"/>
+      <c r="F33" s="596" t="n"/>
+      <c r="G33" s="596" t="n"/>
+      <c r="H33" s="596" t="n"/>
+      <c r="I33" s="596" t="n"/>
+      <c r="J33" s="596" t="n"/>
+      <c r="K33" s="596" t="n"/>
+      <c r="L33" s="596" t="n"/>
+      <c r="M33" s="596" t="n"/>
+      <c r="N33" s="596" t="n"/>
+      <c r="O33" s="596" t="n"/>
+      <c r="P33" s="596" t="n"/>
+      <c r="Q33" s="596" t="n"/>
+      <c r="R33" s="596" t="n"/>
+      <c r="S33" s="597" t="n"/>
+      <c r="T33" s="596" t="n"/>
+      <c r="U33" s="596" t="n"/>
+      <c r="V33" s="596" t="n"/>
+      <c r="W33" s="596" t="n"/>
+      <c r="X33" s="596" t="n"/>
+      <c r="Y33" s="596" t="n"/>
+      <c r="Z33" s="596" t="n"/>
+      <c r="AA33" s="596" t="n"/>
+      <c r="AB33" s="596" t="n"/>
+      <c r="AC33" s="596" t="n"/>
+      <c r="AD33" s="596" t="n"/>
+      <c r="AE33" s="596" t="n"/>
+      <c r="AF33" s="596" t="n"/>
+      <c r="AG33" s="596" t="n"/>
+      <c r="AH33" s="596" t="n"/>
+      <c r="AI33" s="596" t="n"/>
+      <c r="AJ33" s="596" t="n"/>
+      <c r="AK33" s="597" t="n"/>
+      <c r="AL33" s="596" t="n"/>
+      <c r="AM33" s="596" t="n"/>
+      <c r="AN33" s="596" t="n"/>
+      <c r="AO33" s="596" t="n"/>
+      <c r="AP33" s="596" t="n"/>
+      <c r="AQ33" s="596" t="n"/>
+      <c r="AR33" s="596" t="n"/>
+      <c r="AS33" s="596" t="n"/>
+      <c r="AT33" s="596" t="n"/>
+      <c r="AU33" s="596" t="n"/>
+      <c r="AV33" s="596" t="n"/>
+      <c r="AW33" s="596" t="n"/>
+      <c r="AX33" s="596" t="n"/>
+      <c r="AY33" s="596" t="n"/>
+      <c r="AZ33" s="596" t="n"/>
+      <c r="BA33" s="596" t="n"/>
+      <c r="BB33" s="596" t="n"/>
+      <c r="BC33" s="596" t="n"/>
+      <c r="BD33" s="598" t="n"/>
     </row>
     <row r="34" ht="3" customHeight="1">
       <c r="A34" s="391" t="n"/>
@@ -8304,66 +8709,66 @@
       <c r="BD34" s="353" t="n"/>
     </row>
     <row r="35" ht="26" customHeight="1">
-      <c r="A35" s="510" t="inlineStr">
+      <c r="A35" s="599" t="inlineStr">
         <is>
           <t>NOTICE: Confirm cleanliness, approved materials, line clearance, bagging sequence and seal integrity before release. This is a controlled gap form.</t>
         </is>
       </c>
-      <c r="B35" s="511" t="n"/>
-      <c r="C35" s="511" t="n"/>
-      <c r="D35" s="511" t="n"/>
-      <c r="E35" s="511" t="n"/>
-      <c r="F35" s="511" t="n"/>
-      <c r="G35" s="511" t="n"/>
-      <c r="H35" s="511" t="n"/>
-      <c r="I35" s="511" t="n"/>
-      <c r="J35" s="511" t="n"/>
-      <c r="K35" s="511" t="n"/>
-      <c r="L35" s="511" t="n"/>
-      <c r="M35" s="511" t="n"/>
-      <c r="N35" s="511" t="n"/>
-      <c r="O35" s="511" t="n"/>
-      <c r="P35" s="511" t="n"/>
-      <c r="Q35" s="511" t="n"/>
-      <c r="R35" s="511" t="n"/>
-      <c r="S35" s="511" t="n"/>
-      <c r="T35" s="511" t="n"/>
-      <c r="U35" s="511" t="n"/>
-      <c r="V35" s="511" t="n"/>
-      <c r="W35" s="511" t="n"/>
-      <c r="X35" s="511" t="n"/>
-      <c r="Y35" s="511" t="n"/>
-      <c r="Z35" s="511" t="n"/>
-      <c r="AA35" s="511" t="n"/>
-      <c r="AB35" s="511" t="n"/>
-      <c r="AC35" s="511" t="n"/>
-      <c r="AD35" s="511" t="n"/>
-      <c r="AE35" s="511" t="n"/>
-      <c r="AF35" s="511" t="n"/>
-      <c r="AG35" s="511" t="n"/>
-      <c r="AH35" s="511" t="n"/>
-      <c r="AI35" s="511" t="n"/>
-      <c r="AJ35" s="511" t="n"/>
-      <c r="AK35" s="511" t="n"/>
-      <c r="AL35" s="511" t="n"/>
-      <c r="AM35" s="511" t="n"/>
-      <c r="AN35" s="511" t="n"/>
-      <c r="AO35" s="511" t="n"/>
-      <c r="AP35" s="511" t="n"/>
-      <c r="AQ35" s="511" t="n"/>
-      <c r="AR35" s="511" t="n"/>
-      <c r="AS35" s="511" t="n"/>
-      <c r="AT35" s="511" t="n"/>
-      <c r="AU35" s="511" t="n"/>
-      <c r="AV35" s="511" t="n"/>
-      <c r="AW35" s="511" t="n"/>
-      <c r="AX35" s="511" t="n"/>
-      <c r="AY35" s="511" t="n"/>
-      <c r="AZ35" s="511" t="n"/>
-      <c r="BA35" s="511" t="n"/>
-      <c r="BB35" s="511" t="n"/>
-      <c r="BC35" s="511" t="n"/>
-      <c r="BD35" s="512" t="n"/>
+      <c r="B35" s="571" t="n"/>
+      <c r="C35" s="571" t="n"/>
+      <c r="D35" s="571" t="n"/>
+      <c r="E35" s="571" t="n"/>
+      <c r="F35" s="571" t="n"/>
+      <c r="G35" s="571" t="n"/>
+      <c r="H35" s="571" t="n"/>
+      <c r="I35" s="571" t="n"/>
+      <c r="J35" s="571" t="n"/>
+      <c r="K35" s="571" t="n"/>
+      <c r="L35" s="571" t="n"/>
+      <c r="M35" s="571" t="n"/>
+      <c r="N35" s="571" t="n"/>
+      <c r="O35" s="571" t="n"/>
+      <c r="P35" s="571" t="n"/>
+      <c r="Q35" s="571" t="n"/>
+      <c r="R35" s="571" t="n"/>
+      <c r="S35" s="571" t="n"/>
+      <c r="T35" s="571" t="n"/>
+      <c r="U35" s="571" t="n"/>
+      <c r="V35" s="571" t="n"/>
+      <c r="W35" s="571" t="n"/>
+      <c r="X35" s="571" t="n"/>
+      <c r="Y35" s="571" t="n"/>
+      <c r="Z35" s="571" t="n"/>
+      <c r="AA35" s="571" t="n"/>
+      <c r="AB35" s="571" t="n"/>
+      <c r="AC35" s="571" t="n"/>
+      <c r="AD35" s="571" t="n"/>
+      <c r="AE35" s="571" t="n"/>
+      <c r="AF35" s="571" t="n"/>
+      <c r="AG35" s="571" t="n"/>
+      <c r="AH35" s="571" t="n"/>
+      <c r="AI35" s="571" t="n"/>
+      <c r="AJ35" s="571" t="n"/>
+      <c r="AK35" s="571" t="n"/>
+      <c r="AL35" s="571" t="n"/>
+      <c r="AM35" s="571" t="n"/>
+      <c r="AN35" s="571" t="n"/>
+      <c r="AO35" s="571" t="n"/>
+      <c r="AP35" s="571" t="n"/>
+      <c r="AQ35" s="571" t="n"/>
+      <c r="AR35" s="571" t="n"/>
+      <c r="AS35" s="571" t="n"/>
+      <c r="AT35" s="571" t="n"/>
+      <c r="AU35" s="571" t="n"/>
+      <c r="AV35" s="571" t="n"/>
+      <c r="AW35" s="571" t="n"/>
+      <c r="AX35" s="571" t="n"/>
+      <c r="AY35" s="571" t="n"/>
+      <c r="AZ35" s="571" t="n"/>
+      <c r="BA35" s="571" t="n"/>
+      <c r="BB35" s="571" t="n"/>
+      <c r="BC35" s="571" t="n"/>
+      <c r="BD35" s="572" t="n"/>
     </row>
     <row r="36" ht="20" customHeight="1"/>
     <row r="37" ht="20" customHeight="1"/>
@@ -8833,12 +9238,12 @@
           <t>Conditions / Exceptions / Actions</t>
         </is>
       </c>
-      <c r="B1" s="429" t="n"/>
-      <c r="C1" s="429" t="n"/>
-      <c r="D1" s="429" t="n"/>
-      <c r="E1" s="429" t="n"/>
-      <c r="F1" s="429" t="n"/>
-      <c r="G1" s="429" t="n"/>
+      <c r="B1" s="548" t="n"/>
+      <c r="C1" s="548" t="n"/>
+      <c r="D1" s="548" t="n"/>
+      <c r="E1" s="548" t="n"/>
+      <c r="F1" s="548" t="n"/>
+      <c r="G1" s="548" t="n"/>
       <c r="H1" s="514" t="n"/>
       <c r="I1" s="431" t="n"/>
       <c r="J1" s="432" t="n"/>
@@ -8879,12 +9284,6 @@
           <t>Vacuum-compatible clean build and bagging gate for controlled preservation and packaging release.</t>
         </is>
       </c>
-      <c r="B2" s="25" t="n"/>
-      <c r="C2" s="25" t="n"/>
-      <c r="D2" s="25" t="n"/>
-      <c r="E2" s="25" t="n"/>
-      <c r="F2" s="25" t="n"/>
-      <c r="G2" s="25" t="n"/>
       <c r="H2" s="516" t="n"/>
       <c r="I2" s="442" t="n"/>
       <c r="J2" s="443" t="n"/>
@@ -9595,12 +9994,12 @@
           <t>Upstream References / Import Guidance</t>
         </is>
       </c>
-      <c r="B1" s="429" t="n"/>
-      <c r="C1" s="429" t="n"/>
-      <c r="D1" s="429" t="n"/>
-      <c r="E1" s="429" t="n"/>
-      <c r="F1" s="429" t="n"/>
-      <c r="G1" s="429" t="n"/>
+      <c r="B1" s="548" t="n"/>
+      <c r="C1" s="548" t="n"/>
+      <c r="D1" s="548" t="n"/>
+      <c r="E1" s="548" t="n"/>
+      <c r="F1" s="548" t="n"/>
+      <c r="G1" s="548" t="n"/>
       <c r="H1" s="514" t="n"/>
       <c r="I1" s="431" t="n"/>
       <c r="J1" s="432" t="n"/>
@@ -9641,12 +10040,6 @@
           <t>Vacuum-compatible clean build and bagging gate for controlled preservation and packaging release.</t>
         </is>
       </c>
-      <c r="B2" s="25" t="n"/>
-      <c r="C2" s="25" t="n"/>
-      <c r="D2" s="25" t="n"/>
-      <c r="E2" s="25" t="n"/>
-      <c r="F2" s="25" t="n"/>
-      <c r="G2" s="25" t="n"/>
       <c r="H2" s="516" t="n"/>
       <c r="I2" s="442" t="n"/>
       <c r="J2" s="443" t="n"/>
@@ -10385,12 +10778,12 @@
           <t>Evidence Reference / Attachment Guidance</t>
         </is>
       </c>
-      <c r="B1" s="429" t="n"/>
-      <c r="C1" s="429" t="n"/>
-      <c r="D1" s="429" t="n"/>
-      <c r="E1" s="429" t="n"/>
-      <c r="F1" s="429" t="n"/>
-      <c r="G1" s="429" t="n"/>
+      <c r="B1" s="548" t="n"/>
+      <c r="C1" s="548" t="n"/>
+      <c r="D1" s="548" t="n"/>
+      <c r="E1" s="548" t="n"/>
+      <c r="F1" s="548" t="n"/>
+      <c r="G1" s="548" t="n"/>
       <c r="H1" s="514" t="n"/>
       <c r="I1" s="431" t="n"/>
       <c r="J1" s="432" t="n"/>
@@ -10431,12 +10824,6 @@
           <t>Use controlled evidence package references; do not free-type vague placeholders.</t>
         </is>
       </c>
-      <c r="B2" s="25" t="n"/>
-      <c r="C2" s="25" t="n"/>
-      <c r="D2" s="25" t="n"/>
-      <c r="E2" s="25" t="n"/>
-      <c r="F2" s="25" t="n"/>
-      <c r="G2" s="25" t="n"/>
       <c r="H2" s="516" t="n"/>
       <c r="I2" s="442" t="n"/>
       <c r="J2" s="443" t="n"/>

--- a/04-Bieu-Mau/07-FRM-700/FRM-715_Vacuum_Compatible_Clean_Build_and_Bagging_Record.xlsx
+++ b/04-Bieu-Mau/07-FRM-700/FRM-715_Vacuum_Compatible_Clean_Build_and_Bagging_Record.xlsx
@@ -22,10 +22,354 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="112">
+  <si>
+    <t>  1. REFERENCE INFORMATION</t>
+  </si>
+  <si>
+    <t>  2. CLEAN BUILD / BAGGING VERIFICATION</t>
+  </si>
+  <si>
+    <t>  3. CONDITIONS / ACTIONS / RELEASE</t>
+  </si>
+  <si>
+    <t>  4. APPROVAL / SIGN-OFF</t>
+  </si>
+  <si>
+    <t>#</t>
+  </si>
+  <si>
+    <t>=ROW()-ROW($A$16)+1</t>
+  </si>
+  <si>
+    <t>=ROW()-ROW($A$5)+1</t>
+  </si>
+  <si>
+    <t>ACTION_STATUS</t>
+  </si>
+  <si>
+    <t>ANNEX-QA-007</t>
+  </si>
+  <si>
+    <t>ANNEX-QA-007 — Chuẩn bề mặt, độ sạch, tương thích chân không, rò rỉ và xử lý đặc biệt</t>
+  </si>
+  <si>
+    <t>ANNEX-WHS-001</t>
+  </si>
+  <si>
+    <t>ANNEX-WHS-001 — Quy cách đóng gói, nhãn, bảo quản và bằng chứng gói hàng</t>
+  </si>
+  <si>
+    <t>APPROVED</t>
+  </si>
+  <si>
+    <t>Approved by</t>
+  </si>
+  <si>
+    <t>Bagging / Seal Ref</t>
+  </si>
+  <si>
+    <t>Bagging Configuration</t>
+  </si>
+  <si>
+    <t>CLEAN</t>
+  </si>
+  <si>
+    <t>CLEAN_CLASS_LIST</t>
+  </si>
+  <si>
+    <t>CLOSED</t>
+  </si>
+  <si>
+    <t>CONDITIONAL</t>
+  </si>
+  <si>
+    <t>Cat.</t>
+  </si>
+  <si>
+    <t>Clean Build / Bagging Requirement</t>
+  </si>
+  <si>
+    <t>Clean Build Record ID</t>
+  </si>
+  <si>
+    <t>Clean Class</t>
+  </si>
+  <si>
+    <t>Close When</t>
+  </si>
+  <si>
+    <t>Close only after the final gate disposition, result or release status is recorded, all conditions are assigned to an owner, and the evidence package reference is complete.</t>
+  </si>
+  <si>
+    <t>Condition / Exception</t>
+  </si>
+  <si>
+    <t>Conditional Action Required (YES/NO)</t>
+  </si>
+  <si>
+    <t>Conditions / Exceptions / Actions</t>
+  </si>
+  <si>
+    <t>Cross-Reference Boundary</t>
+  </si>
+  <si>
+    <t>DISPOSITION_GATE</t>
+  </si>
+  <si>
+    <t>Do not duplicate ERP/M365/ANNEX master data.</t>
+  </si>
+  <si>
+    <t>Due Date</t>
+  </si>
+  <si>
+    <t>ENG</t>
+  </si>
+  <si>
+    <t>Evidence / Method</t>
+  </si>
+  <si>
+    <t>Evidence Package Ref</t>
+  </si>
+  <si>
+    <t>Evidence Ref</t>
+  </si>
+  <si>
+    <t>Evidence Reference / Attachment Guidance</t>
+  </si>
+  <si>
+    <t>FAIL</t>
+  </si>
+  <si>
+    <t>FRM-715</t>
+  </si>
+  <si>
+    <t>Field</t>
+  </si>
+  <si>
+    <t>Final Release Decision</t>
+  </si>
+  <si>
+    <t>General Manager</t>
+  </si>
+  <si>
+    <t>HESEM Engineering · ISO 9001 / AS9100 · Semiconductor Equipment Parts</t>
+  </si>
+  <si>
+    <t>HIGH CLEAN</t>
+  </si>
+  <si>
+    <t>HOLD</t>
+  </si>
+  <si>
+    <t>HR</t>
+  </si>
+  <si>
+    <t>IN PROGRESS</t>
+  </si>
+  <si>
+    <t>INEFFECTIVE</t>
+  </si>
+  <si>
+    <t>IT</t>
+  </si>
+  <si>
+    <t>Job / Part / Package Class</t>
+  </si>
+  <si>
+    <t>Line Clearance / Gowning</t>
+  </si>
+  <si>
+    <t>M365 evidence / shared workbook</t>
+  </si>
+  <si>
+    <t>MGT</t>
+  </si>
+  <si>
+    <t>MONITORING</t>
+  </si>
+  <si>
+    <t>NA</t>
+  </si>
+  <si>
+    <t>NO</t>
+  </si>
+  <si>
+    <t>NOTICE: Confirm cleanliness, approved materials, line clearance, bagging sequence and seal integrity before release. This is a controlled gap form.</t>
+  </si>
+  <si>
+    <t>Name / Signature / Date</t>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>OPEN</t>
+  </si>
+  <si>
+    <t>OVERDUE</t>
+  </si>
+  <si>
+    <t>OWNER_DEPT</t>
+  </si>
+  <si>
+    <t>Open When</t>
+  </si>
+  <si>
+    <t>Open before the controlled activity starts or before the release decision is taken. Do not populate it retrospectively after execution has already moved forward.</t>
+  </si>
+  <si>
+    <t>Operational trigger</t>
+  </si>
+  <si>
+    <t>Owner</t>
+  </si>
+  <si>
+    <t>PASS</t>
+  </si>
+  <si>
+    <t>PLANNING</t>
+  </si>
+  <si>
+    <t>PROD</t>
+  </si>
+  <si>
+    <t>PUR</t>
+  </si>
+  <si>
+    <t>Prepared by</t>
+  </si>
+  <si>
+    <t>Prepared by / Date-Time</t>
+  </si>
+  <si>
+    <t>QA</t>
+  </si>
+  <si>
+    <t>Quality Management System · Controlled Document</t>
+  </si>
+  <si>
+    <t>REJECT</t>
+  </si>
+  <si>
+    <t>RESULT</t>
+  </si>
+  <si>
+    <t>Record Status</t>
+  </si>
+  <si>
+    <t>Ref.</t>
+  </si>
+  <si>
+    <t>Release / closure rule</t>
+  </si>
+  <si>
+    <t>Release Status</t>
+  </si>
+  <si>
+    <t>Required Action</t>
+  </si>
+  <si>
+    <t>Result</t>
+  </si>
+  <si>
+    <t>Reviewed by</t>
+  </si>
+  <si>
+    <t>SALES</t>
+  </si>
+  <si>
+    <t>SOP-702</t>
+  </si>
+  <si>
+    <t>SOP-702 — Kiểm soát nhiễm bẩn, xác nhận độ sạch và tuyến đóng gói sạch | HESEM QMS</t>
+  </si>
+  <si>
+    <t>STANDARD</t>
+  </si>
+  <si>
+    <t>STATUS</t>
+  </si>
+  <si>
+    <t>Source of Truth</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>This form does not replace SOP-702; it records the evidence, data or decision required by that SOP.
+Detailed task execution belongs in WI-716; this form captures results, checks, decisions or exceptions only.
+Rules, matrices, dictionaries, acceptance criteria and data definitions belong in ANNEX-QA-007 + ANNEX-WHS-001; do not copy ANNEX content into the live data-entry body.
+System-of-record / source-of-truth boundary: M365 evidence / shared workbook. If the master data already live there, reference or import them; do not re-key without need.</t>
+  </si>
+  <si>
+    <t>Upstream References / Import Guidance</t>
+  </si>
+  <si>
+    <t>Use controlled evidence package references; do not free-type vague placeholders.</t>
+  </si>
+  <si>
+    <t>V0</t>
+  </si>
+  <si>
+    <t>VACUUM-COMPATIBLE</t>
+  </si>
+  <si>
+    <t>VERIFIED</t>
+  </si>
+  <si>
+    <t>Vacuum-Compatible Clean Build and Bagging Record</t>
+  </si>
+  <si>
+    <t>Vacuum-compatible clean build and bagging gate for controlled preservation and packaging release.</t>
+  </si>
+  <si>
+    <t>Value / Reference</t>
+  </si>
+  <si>
+    <t>WHS</t>
+  </si>
+  <si>
+    <t>WI-716</t>
+  </si>
+  <si>
+    <t>WI-716 — Lắp sạch, tương thích chân không, bagging và bảo quản cho Job đặc biệt</t>
+  </si>
+  <si>
+    <t>Warehouse + QA</t>
+  </si>
+  <si>
+    <t>Warehouse Owner</t>
+  </si>
+  <si>
+    <t>YES</t>
+  </si>
+  <si>
+    <t>YES_NO</t>
+  </si>
+  <si>
+    <t>YYYY-MM-DD</t>
+  </si>
+  <si>
+    <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/01-SOPs/07-SOP-700/sop-702-contamination-control-and-cleanliness.html</t>
+  </si>
+  <si>
+    <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/02-Work-Instructions/07-WI-700/wi-716-vacuum-compatible-clean-build-and-bagging.html</t>
+  </si>
+  <si>
+    <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/03-Reference/02-ANNEX-Standards/annex-qa-007-surface-finish-vacuum-compatibility.html</t>
+  </si>
+  <si>
+    <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/03-Reference/02-ANNEX-Standards/annex-whs-001-packaging-labeling-spec.html</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="86">
+  <fonts count="87">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -512,8 +856,13 @@
       <color rgb="00BBCCCC"/>
       <sz val="8"/>
     </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="007B4F00"/>
+      <sz val="7"/>
+    </font>
   </fonts>
-  <fills count="52">
+  <fills count="53">
     <fill>
       <patternFill/>
     </fill>
@@ -770,8 +1119,13 @@
         <fgColor rgb="000C2D48"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF8E1"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="353">
+  <borders count="356">
     <border>
       <left/>
       <right/>
@@ -4579,11 +4933,45 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00F9A825"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00F9A825"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00F9A825"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00F9A825"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00F9A825"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00F9A825"/>
+      </right>
+      <top style="thin">
+        <color rgb="00F9A825"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00F9A825"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="79" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="600">
+  <cellXfs count="603">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -6077,6 +6465,15 @@
     </xf>
     <xf numFmtId="0" fontId="80" fillId="4" borderId="333" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="86" fillId="52" borderId="353" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="86" fillId="52" borderId="354" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="86" fillId="52" borderId="355" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -8709,66 +9106,66 @@
       <c r="BD34" s="353" t="n"/>
     </row>
     <row r="35" ht="26" customHeight="1">
-      <c r="A35" s="599" t="inlineStr">
+      <c r="A35" s="600" t="inlineStr">
         <is>
           <t>NOTICE: Confirm cleanliness, approved materials, line clearance, bagging sequence and seal integrity before release. This is a controlled gap form.</t>
         </is>
       </c>
-      <c r="B35" s="571" t="n"/>
-      <c r="C35" s="571" t="n"/>
-      <c r="D35" s="571" t="n"/>
-      <c r="E35" s="571" t="n"/>
-      <c r="F35" s="571" t="n"/>
-      <c r="G35" s="571" t="n"/>
-      <c r="H35" s="571" t="n"/>
-      <c r="I35" s="571" t="n"/>
-      <c r="J35" s="571" t="n"/>
-      <c r="K35" s="571" t="n"/>
-      <c r="L35" s="571" t="n"/>
-      <c r="M35" s="571" t="n"/>
-      <c r="N35" s="571" t="n"/>
-      <c r="O35" s="571" t="n"/>
-      <c r="P35" s="571" t="n"/>
-      <c r="Q35" s="571" t="n"/>
-      <c r="R35" s="571" t="n"/>
-      <c r="S35" s="571" t="n"/>
-      <c r="T35" s="571" t="n"/>
-      <c r="U35" s="571" t="n"/>
-      <c r="V35" s="571" t="n"/>
-      <c r="W35" s="571" t="n"/>
-      <c r="X35" s="571" t="n"/>
-      <c r="Y35" s="571" t="n"/>
-      <c r="Z35" s="571" t="n"/>
-      <c r="AA35" s="571" t="n"/>
-      <c r="AB35" s="571" t="n"/>
-      <c r="AC35" s="571" t="n"/>
-      <c r="AD35" s="571" t="n"/>
-      <c r="AE35" s="571" t="n"/>
-      <c r="AF35" s="571" t="n"/>
-      <c r="AG35" s="571" t="n"/>
-      <c r="AH35" s="571" t="n"/>
-      <c r="AI35" s="571" t="n"/>
-      <c r="AJ35" s="571" t="n"/>
-      <c r="AK35" s="571" t="n"/>
-      <c r="AL35" s="571" t="n"/>
-      <c r="AM35" s="571" t="n"/>
-      <c r="AN35" s="571" t="n"/>
-      <c r="AO35" s="571" t="n"/>
-      <c r="AP35" s="571" t="n"/>
-      <c r="AQ35" s="571" t="n"/>
-      <c r="AR35" s="571" t="n"/>
-      <c r="AS35" s="571" t="n"/>
-      <c r="AT35" s="571" t="n"/>
-      <c r="AU35" s="571" t="n"/>
-      <c r="AV35" s="571" t="n"/>
-      <c r="AW35" s="571" t="n"/>
-      <c r="AX35" s="571" t="n"/>
-      <c r="AY35" s="571" t="n"/>
-      <c r="AZ35" s="571" t="n"/>
-      <c r="BA35" s="571" t="n"/>
-      <c r="BB35" s="571" t="n"/>
-      <c r="BC35" s="571" t="n"/>
-      <c r="BD35" s="572" t="n"/>
+      <c r="B35" s="601" t="n"/>
+      <c r="C35" s="601" t="n"/>
+      <c r="D35" s="601" t="n"/>
+      <c r="E35" s="601" t="n"/>
+      <c r="F35" s="601" t="n"/>
+      <c r="G35" s="601" t="n"/>
+      <c r="H35" s="601" t="n"/>
+      <c r="I35" s="601" t="n"/>
+      <c r="J35" s="601" t="n"/>
+      <c r="K35" s="601" t="n"/>
+      <c r="L35" s="601" t="n"/>
+      <c r="M35" s="601" t="n"/>
+      <c r="N35" s="601" t="n"/>
+      <c r="O35" s="601" t="n"/>
+      <c r="P35" s="601" t="n"/>
+      <c r="Q35" s="601" t="n"/>
+      <c r="R35" s="601" t="n"/>
+      <c r="S35" s="601" t="n"/>
+      <c r="T35" s="601" t="n"/>
+      <c r="U35" s="601" t="n"/>
+      <c r="V35" s="601" t="n"/>
+      <c r="W35" s="601" t="n"/>
+      <c r="X35" s="601" t="n"/>
+      <c r="Y35" s="601" t="n"/>
+      <c r="Z35" s="601" t="n"/>
+      <c r="AA35" s="601" t="n"/>
+      <c r="AB35" s="601" t="n"/>
+      <c r="AC35" s="601" t="n"/>
+      <c r="AD35" s="601" t="n"/>
+      <c r="AE35" s="601" t="n"/>
+      <c r="AF35" s="601" t="n"/>
+      <c r="AG35" s="601" t="n"/>
+      <c r="AH35" s="601" t="n"/>
+      <c r="AI35" s="601" t="n"/>
+      <c r="AJ35" s="601" t="n"/>
+      <c r="AK35" s="601" t="n"/>
+      <c r="AL35" s="601" t="n"/>
+      <c r="AM35" s="601" t="n"/>
+      <c r="AN35" s="601" t="n"/>
+      <c r="AO35" s="601" t="n"/>
+      <c r="AP35" s="601" t="n"/>
+      <c r="AQ35" s="601" t="n"/>
+      <c r="AR35" s="601" t="n"/>
+      <c r="AS35" s="601" t="n"/>
+      <c r="AT35" s="601" t="n"/>
+      <c r="AU35" s="601" t="n"/>
+      <c r="AV35" s="601" t="n"/>
+      <c r="AW35" s="601" t="n"/>
+      <c r="AX35" s="601" t="n"/>
+      <c r="AY35" s="601" t="n"/>
+      <c r="AZ35" s="601" t="n"/>
+      <c r="BA35" s="601" t="n"/>
+      <c r="BB35" s="601" t="n"/>
+      <c r="BC35" s="601" t="n"/>
+      <c r="BD35" s="602" t="n"/>
     </row>
     <row r="36" ht="20" customHeight="1"/>
     <row r="37" ht="20" customHeight="1"/>

--- a/04-Bieu-Mau/07-FRM-700/FRM-715_Vacuum_Compatible_Clean_Build_and_Bagging_Record.xlsx
+++ b/04-Bieu-Mau/07-FRM-700/FRM-715_Vacuum_Compatible_Clean_Build_and_Bagging_Record.xlsx
@@ -10,20 +10,16 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VAC_BAG_GATE" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LISTS" sheetId="2" state="veryHidden" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CONDITIONS_ACTIONS" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="REF_IMPORT" sheetId="4" state="veryHidden" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EVIDENCE_REF" sheetId="5" state="veryHidden" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'VAC_BAG_GATE'!$A$1:$BD$35</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'REF_IMPORT'!$A$4:$C$14</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'EVIDENCE_REF'!$A$4:$C$8</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="82">
   <si>
     <t>  1. REFERENCE INFORMATION</t>
   </si>
@@ -43,22 +39,10 @@
     <t>=ROW()-ROW($A$16)+1</t>
   </si>
   <si>
-    <t>=ROW()-ROW($A$5)+1</t>
+    <t>=ROW()-ROW($A$9)+1</t>
   </si>
   <si>
     <t>ACTION_STATUS</t>
-  </si>
-  <si>
-    <t>ANNEX-QA-007</t>
-  </si>
-  <si>
-    <t>ANNEX-QA-007 — Chuẩn bề mặt, độ sạch, tương thích chân không, rò rỉ và xử lý đặc biệt</t>
-  </si>
-  <si>
-    <t>ANNEX-WHS-001</t>
-  </si>
-  <si>
-    <t>ANNEX-WHS-001 — Quy cách đóng gói, nhãn, bảo quản và bằng chứng gói hàng</t>
   </si>
   <si>
     <t>APPROVED</t>
@@ -97,28 +81,13 @@
     <t>Clean Class</t>
   </si>
   <si>
-    <t>Close When</t>
-  </si>
-  <si>
-    <t>Close only after the final gate disposition, result or release status is recorded, all conditions are assigned to an owner, and the evidence package reference is complete.</t>
-  </si>
-  <si>
     <t>Condition / Exception</t>
   </si>
   <si>
     <t>Conditional Action Required (YES/NO)</t>
   </si>
   <si>
-    <t>Conditions / Exceptions / Actions</t>
-  </si>
-  <si>
-    <t>Cross-Reference Boundary</t>
-  </si>
-  <si>
     <t>DISPOSITION_GATE</t>
-  </si>
-  <si>
-    <t>Do not duplicate ERP/M365/ANNEX master data.</t>
   </si>
   <si>
     <t>Due Date</t>
@@ -133,19 +102,10 @@
     <t>Evidence Package Ref</t>
   </si>
   <si>
-    <t>Evidence Ref</t>
-  </si>
-  <si>
-    <t>Evidence Reference / Attachment Guidance</t>
-  </si>
-  <si>
     <t>FAIL</t>
   </si>
   <si>
     <t>FRM-715</t>
-  </si>
-  <si>
-    <t>Field</t>
   </si>
   <si>
     <t>Final Release Decision</t>
@@ -181,9 +141,6 @@
     <t>Line Clearance / Gowning</t>
   </si>
   <si>
-    <t>M365 evidence / shared workbook</t>
-  </si>
-  <si>
     <t>MGT</t>
   </si>
   <si>
@@ -202,9 +159,6 @@
     <t>Name / Signature / Date</t>
   </si>
   <si>
-    <t>Notes</t>
-  </si>
-  <si>
     <t>OPEN</t>
   </si>
   <si>
@@ -212,15 +166,6 @@
   </si>
   <si>
     <t>OWNER_DEPT</t>
-  </si>
-  <si>
-    <t>Open When</t>
-  </si>
-  <si>
-    <t>Open before the controlled activity starts or before the release decision is taken. Do not populate it retrospectively after execution has already moved forward.</t>
-  </si>
-  <si>
-    <t>Operational trigger</t>
   </si>
   <si>
     <t>Owner</t>
@@ -262,9 +207,6 @@
     <t>Ref.</t>
   </si>
   <si>
-    <t>Release / closure rule</t>
-  </si>
-  <si>
     <t>Release Status</t>
   </si>
   <si>
@@ -280,37 +222,19 @@
     <t>SALES</t>
   </si>
   <si>
-    <t>SOP-702</t>
-  </si>
-  <si>
-    <t>SOP-702 — Kiểm soát nhiễm bẩn, xác nhận độ sạch và tuyến đóng gói sạch | HESEM QMS</t>
-  </si>
-  <si>
     <t>STANDARD</t>
   </si>
   <si>
     <t>STATUS</t>
   </si>
   <si>
-    <t>Source of Truth</t>
-  </si>
-  <si>
     <t>Status</t>
   </si>
   <si>
-    <t>This form does not replace SOP-702; it records the evidence, data or decision required by that SOP.
-Detailed task execution belongs in WI-716; this form captures results, checks, decisions or exceptions only.
-Rules, matrices, dictionaries, acceptance criteria and data definitions belong in ANNEX-QA-007 + ANNEX-WHS-001; do not copy ANNEX content into the live data-entry body.
-System-of-record / source-of-truth boundary: M365 evidence / shared workbook. If the master data already live there, reference or import them; do not re-key without need.</t>
+    <t>V0</t>
   </si>
   <si>
-    <t>Upstream References / Import Guidance</t>
-  </si>
-  <si>
-    <t>Use controlled evidence package references; do not free-type vague placeholders.</t>
-  </si>
-  <si>
-    <t>V0</t>
+    <t>VAC-BUILD CONDITIONS / ACTIONS</t>
   </si>
   <si>
     <t>VACUUM-COMPATIBLE</t>
@@ -322,19 +246,10 @@
     <t>Vacuum-Compatible Clean Build and Bagging Record</t>
   </si>
   <si>
-    <t>Vacuum-compatible clean build and bagging gate for controlled preservation and packaging release.</t>
-  </si>
-  <si>
-    <t>Value / Reference</t>
+    <t>Verified by</t>
   </si>
   <si>
     <t>WHS</t>
-  </si>
-  <si>
-    <t>WI-716</t>
-  </si>
-  <si>
-    <t>WI-716 — Lắp sạch, tương thích chân không, bagging và bảo quản cho Job đặc biệt</t>
   </si>
   <si>
     <t>Warehouse + QA</t>
@@ -351,25 +266,13 @@
   <si>
     <t>YYYY-MM-DD</t>
   </si>
-  <si>
-    <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/01-SOPs/07-SOP-700/sop-702-contamination-control-and-cleanliness.html</t>
-  </si>
-  <si>
-    <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/02-Work-Instructions/07-WI-700/wi-716-vacuum-compatible-clean-build-and-bagging.html</t>
-  </si>
-  <si>
-    <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/03-Reference/02-ANNEX-Standards/annex-qa-007-surface-finish-vacuum-compatibility.html</t>
-  </si>
-  <si>
-    <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/03-Reference/02-ANNEX-Standards/annex-whs-001-packaging-labeling-spec.html</t>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="87">
+  <fonts count="89">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -861,8 +764,17 @@
       <color rgb="007B4F00"/>
       <sz val="7"/>
     </font>
+    <font>
+      <name val="Segoe UI"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color theme="1"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="53">
+  <fills count="54">
     <fill>
       <patternFill/>
     </fill>
@@ -1124,8 +1036,13 @@
         <fgColor rgb="00FFF8E1"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F7FBFF"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="356">
+  <borders count="367">
     <border>
       <left/>
       <right/>
@@ -4967,11 +4884,150 @@
         <color rgb="00F9A825"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00F9A825"/>
+      </left>
+      <right style="thin">
+        <color rgb="00F9A825"/>
+      </right>
+      <top style="thin">
+        <color rgb="00F9A825"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00F9A825"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00F9A825"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00F9A825"/>
+      </right>
+      <top style="thin">
+        <color rgb="00F9A825"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00F9A825"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00F9A825"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00F9A825"/>
+      </right>
+      <top style="thin">
+        <color rgb="00F9A825"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00F9A825"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00C5D9E8"/>
+      </right>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00C5D9E8"/>
+      </left>
+      <right style="thin">
+        <color rgb="00C5D9E8"/>
+      </right>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00C5D9E8"/>
+      </right>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="002C9CD7"/>
+      </left>
+      <right style="thin">
+        <color rgb="00C5D9E8"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C5D9E8"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00C5D9E8"/>
+      </left>
+      <right style="thin">
+        <color rgb="00C5D9E8"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C5D9E8"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="002C9CD7"/>
+      </left>
+      <right style="thin">
+        <color rgb="00C5D9E8"/>
+      </right>
+      <top style="medium">
+        <color rgb="002C9CD7"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="79" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="603">
+  <cellXfs count="674">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -6474,6 +6530,188 @@
     </xf>
     <xf numFmtId="0" fontId="86" fillId="52" borderId="355" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="86" fillId="52" borderId="356" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="359" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="360" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="49" borderId="312" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="49" borderId="313" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="84" fillId="50" borderId="271" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="4" borderId="271" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="51" borderId="311" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="51" borderId="361" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="53" fillId="51" borderId="320" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="51" borderId="312" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="51" borderId="313" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="82" fillId="4" borderId="318" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="276" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="51" fillId="4" borderId="272" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="275" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="276" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="4" borderId="272" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="275" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="319" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="82" fillId="53" borderId="318" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="53" borderId="276" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="51" fillId="53" borderId="272" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="53" borderId="275" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="53" borderId="276" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="53" borderId="272" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="53" borderId="275" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="53" borderId="319" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="82" fillId="53" borderId="306" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="53" borderId="308" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="51" fillId="53" borderId="309" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="53" borderId="307" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="53" borderId="308" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="53" borderId="309" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="53" borderId="307" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="53" borderId="310" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="51" fillId="4" borderId="271" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="51" borderId="366" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="363" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="53" fillId="51" borderId="362" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="51" borderId="347" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="4" borderId="364" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="4" borderId="274" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="290" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="4" borderId="274" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="4" borderId="326" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="327" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="82" fillId="53" borderId="364" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="53" borderId="274" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="53" borderId="274" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="53" borderId="326" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="53" borderId="323" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="53" borderId="365" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="325" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="53" borderId="365" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="53" borderId="331" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="87" fillId="47" borderId="271" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="87" fillId="47" borderId="271" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="51" borderId="320" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="51" borderId="312" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="51" borderId="361" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="4" borderId="318" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="53" borderId="318" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="53" borderId="306" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="87" fillId="0" borderId="271" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="53" fillId="51" borderId="362" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="335" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="363" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="4" borderId="364" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="53" borderId="364" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="53" borderId="323" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -6614,59 +6852,21 @@
     </pic>
     <clientData/>
   </oneCellAnchor>
-</wsDr>
-</file>
-
-<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>0</col>
+      <col>1</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1303776" cy="376089"/>
+    <ext cx="619125" cy="619125"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-</wsDr>
-</file>
-
-<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>1</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1303776" cy="376089"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="1" name="Image 1" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId2"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -9584,7 +9784,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN14"/>
+  <dimension ref="A1:BD50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.33" customWidth="1" min="1" max="1"/>
@@ -9627,691 +9827,2979 @@
     <col width="2.33" customWidth="1" min="38" max="38"/>
     <col width="2.33" customWidth="1" min="39" max="39"/>
     <col width="2.33" customWidth="1" min="40" max="40"/>
+    <col width="2.33" customWidth="1" min="41" max="41"/>
+    <col width="2.33" customWidth="1" min="42" max="42"/>
+    <col width="2.33" customWidth="1" min="43" max="43"/>
+    <col width="2.33" customWidth="1" min="44" max="44"/>
+    <col width="2.33" customWidth="1" min="45" max="45"/>
+    <col width="2.33" customWidth="1" min="46" max="46"/>
+    <col width="2.33" customWidth="1" min="47" max="47"/>
+    <col width="2.33" customWidth="1" min="48" max="48"/>
+    <col width="2.33" customWidth="1" min="49" max="49"/>
+    <col width="2.33" customWidth="1" min="50" max="50"/>
+    <col width="2.33" customWidth="1" min="51" max="51"/>
+    <col width="2.33" customWidth="1" min="52" max="52"/>
+    <col width="2.33" customWidth="1" min="53" max="53"/>
+    <col width="2.33" customWidth="1" min="54" max="54"/>
+    <col width="2.33" customWidth="1" min="55" max="55"/>
+    <col width="2.33" customWidth="1" min="56" max="56"/>
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1">
-      <c r="A1" s="513" t="inlineStr">
-        <is>
-          <t>Conditions / Exceptions / Actions</t>
-        </is>
-      </c>
+      <c r="A1" s="547" t="n"/>
       <c r="B1" s="548" t="n"/>
       <c r="C1" s="548" t="n"/>
       <c r="D1" s="548" t="n"/>
       <c r="E1" s="548" t="n"/>
       <c r="F1" s="548" t="n"/>
       <c r="G1" s="548" t="n"/>
-      <c r="H1" s="514" t="n"/>
-      <c r="I1" s="431" t="n"/>
-      <c r="J1" s="432" t="n"/>
-      <c r="K1" s="432" t="n"/>
-      <c r="L1" s="432" t="n"/>
-      <c r="M1" s="432" t="n"/>
-      <c r="N1" s="432" t="n"/>
-      <c r="O1" s="432" t="n"/>
-      <c r="P1" s="432" t="n"/>
-      <c r="Q1" s="432" t="n"/>
-      <c r="R1" s="432" t="n"/>
-      <c r="S1" s="432" t="n"/>
-      <c r="T1" s="432" t="n"/>
-      <c r="U1" s="432" t="n"/>
-      <c r="V1" s="432" t="n"/>
-      <c r="W1" s="432" t="n"/>
-      <c r="X1" s="432" t="n"/>
-      <c r="Y1" s="432" t="n"/>
-      <c r="Z1" s="432" t="n"/>
-      <c r="AA1" s="432" t="n"/>
-      <c r="AB1" s="432" t="n"/>
-      <c r="AC1" s="432" t="n"/>
-      <c r="AD1" s="433" t="n"/>
-      <c r="AE1" s="434" t="n"/>
-      <c r="AF1" s="435" t="n"/>
-      <c r="AG1" s="435" t="n"/>
-      <c r="AH1" s="436" t="n"/>
-      <c r="AI1" s="437" t="n"/>
-      <c r="AJ1" s="438" t="n"/>
-      <c r="AK1" s="438" t="n"/>
-      <c r="AL1" s="438" t="n"/>
-      <c r="AM1" s="438" t="n"/>
-      <c r="AN1" s="439" t="n"/>
+      <c r="H1" s="548" t="n"/>
+      <c r="I1" s="548" t="n"/>
+      <c r="J1" s="548" t="n"/>
+      <c r="K1" s="549" t="n"/>
+      <c r="L1" s="550" t="inlineStr">
+        <is>
+          <t>Vacuum-Compatible Clean Build and Bagging Record</t>
+        </is>
+      </c>
+      <c r="M1" s="548" t="n"/>
+      <c r="N1" s="548" t="n"/>
+      <c r="O1" s="548" t="n"/>
+      <c r="P1" s="548" t="n"/>
+      <c r="Q1" s="548" t="n"/>
+      <c r="R1" s="548" t="n"/>
+      <c r="S1" s="548" t="n"/>
+      <c r="T1" s="548" t="n"/>
+      <c r="U1" s="548" t="n"/>
+      <c r="V1" s="548" t="n"/>
+      <c r="W1" s="548" t="n"/>
+      <c r="X1" s="548" t="n"/>
+      <c r="Y1" s="548" t="n"/>
+      <c r="Z1" s="548" t="n"/>
+      <c r="AA1" s="548" t="n"/>
+      <c r="AB1" s="548" t="n"/>
+      <c r="AC1" s="548" t="n"/>
+      <c r="AD1" s="548" t="n"/>
+      <c r="AE1" s="548" t="n"/>
+      <c r="AF1" s="548" t="n"/>
+      <c r="AG1" s="548" t="n"/>
+      <c r="AH1" s="548" t="n"/>
+      <c r="AI1" s="548" t="n"/>
+      <c r="AJ1" s="548" t="n"/>
+      <c r="AK1" s="548" t="n"/>
+      <c r="AL1" s="548" t="n"/>
+      <c r="AM1" s="548" t="n"/>
+      <c r="AN1" s="548" t="n"/>
+      <c r="AO1" s="548" t="n"/>
+      <c r="AP1" s="549" t="n"/>
+      <c r="AQ1" s="551" t="n"/>
+      <c r="AR1" s="548" t="n"/>
+      <c r="AS1" s="548" t="n"/>
+      <c r="AT1" s="548" t="n"/>
+      <c r="AU1" s="548" t="n"/>
+      <c r="AV1" s="552" t="n"/>
+      <c r="AW1" s="553" t="inlineStr">
+        <is>
+          <t>FRM-715</t>
+        </is>
+      </c>
+      <c r="AX1" s="548" t="n"/>
+      <c r="AY1" s="548" t="n"/>
+      <c r="AZ1" s="548" t="n"/>
+      <c r="BA1" s="548" t="n"/>
+      <c r="BB1" s="548" t="n"/>
+      <c r="BC1" s="548" t="n"/>
+      <c r="BD1" s="549" t="n"/>
     </row>
     <row r="2" ht="15" customHeight="1">
-      <c r="A2" s="515" t="inlineStr">
+      <c r="A2" s="554" t="n"/>
+      <c r="K2" s="555" t="n"/>
+      <c r="L2" s="554" t="n"/>
+      <c r="AP2" s="555" t="n"/>
+      <c r="AQ2" s="556" t="n"/>
+      <c r="AR2" s="422" t="n"/>
+      <c r="AS2" s="422" t="n"/>
+      <c r="AT2" s="422" t="n"/>
+      <c r="AU2" s="422" t="n"/>
+      <c r="AV2" s="557" t="n"/>
+      <c r="AW2" s="558" t="inlineStr">
         <is>
-          <t>Vacuum-compatible clean build and bagging gate for controlled preservation and packaging release.</t>
+          <t>V0</t>
         </is>
       </c>
-      <c r="H2" s="516" t="n"/>
-      <c r="I2" s="442" t="n"/>
-      <c r="J2" s="443" t="n"/>
-      <c r="K2" s="443" t="n"/>
-      <c r="L2" s="443" t="n"/>
-      <c r="M2" s="443" t="n"/>
-      <c r="N2" s="443" t="n"/>
-      <c r="O2" s="443" t="n"/>
-      <c r="P2" s="443" t="n"/>
-      <c r="Q2" s="443" t="n"/>
-      <c r="R2" s="443" t="n"/>
-      <c r="S2" s="443" t="n"/>
-      <c r="T2" s="443" t="n"/>
-      <c r="U2" s="443" t="n"/>
-      <c r="V2" s="443" t="n"/>
-      <c r="W2" s="443" t="n"/>
-      <c r="X2" s="443" t="n"/>
-      <c r="Y2" s="443" t="n"/>
-      <c r="Z2" s="443" t="n"/>
-      <c r="AA2" s="443" t="n"/>
-      <c r="AB2" s="443" t="n"/>
-      <c r="AC2" s="443" t="n"/>
-      <c r="AD2" s="444" t="n"/>
-      <c r="AE2" s="445" t="n"/>
-      <c r="AF2" s="446" t="n"/>
-      <c r="AG2" s="446" t="n"/>
-      <c r="AH2" s="447" t="n"/>
-      <c r="AI2" s="448" t="n"/>
-      <c r="AJ2" s="449" t="n"/>
-      <c r="AK2" s="449" t="n"/>
-      <c r="AL2" s="449" t="n"/>
-      <c r="AM2" s="449" t="n"/>
-      <c r="AN2" s="450" t="n"/>
+      <c r="AX2" s="422" t="n"/>
+      <c r="AY2" s="422" t="n"/>
+      <c r="AZ2" s="422" t="n"/>
+      <c r="BA2" s="422" t="n"/>
+      <c r="BB2" s="422" t="n"/>
+      <c r="BC2" s="422" t="n"/>
+      <c r="BD2" s="559" t="n"/>
     </row>
     <row r="3" ht="15" customHeight="1">
-      <c r="A3" s="517" t="n"/>
-      <c r="B3" s="518" t="n"/>
-      <c r="C3" s="518" t="n"/>
-      <c r="D3" s="518" t="n"/>
-      <c r="E3" s="518" t="n"/>
-      <c r="F3" s="518" t="n"/>
-      <c r="G3" s="518" t="n"/>
-      <c r="H3" s="516" t="n"/>
-      <c r="I3" s="442" t="n"/>
-      <c r="J3" s="443" t="n"/>
-      <c r="K3" s="443" t="n"/>
-      <c r="L3" s="443" t="n"/>
-      <c r="M3" s="443" t="n"/>
-      <c r="N3" s="443" t="n"/>
-      <c r="O3" s="443" t="n"/>
-      <c r="P3" s="443" t="n"/>
-      <c r="Q3" s="443" t="n"/>
-      <c r="R3" s="443" t="n"/>
-      <c r="S3" s="443" t="n"/>
-      <c r="T3" s="443" t="n"/>
-      <c r="U3" s="443" t="n"/>
-      <c r="V3" s="443" t="n"/>
-      <c r="W3" s="443" t="n"/>
-      <c r="X3" s="443" t="n"/>
-      <c r="Y3" s="443" t="n"/>
-      <c r="Z3" s="443" t="n"/>
-      <c r="AA3" s="443" t="n"/>
-      <c r="AB3" s="443" t="n"/>
-      <c r="AC3" s="443" t="n"/>
-      <c r="AD3" s="444" t="n"/>
-      <c r="AE3" s="445" t="n"/>
-      <c r="AF3" s="446" t="n"/>
-      <c r="AG3" s="446" t="n"/>
-      <c r="AH3" s="447" t="n"/>
-      <c r="AI3" s="448" t="n"/>
-      <c r="AJ3" s="449" t="n"/>
-      <c r="AK3" s="449" t="n"/>
-      <c r="AL3" s="449" t="n"/>
-      <c r="AM3" s="449" t="n"/>
-      <c r="AN3" s="450" t="n"/>
+      <c r="A3" s="554" t="n"/>
+      <c r="K3" s="555" t="n"/>
+      <c r="L3" s="554" t="n"/>
+      <c r="AP3" s="555" t="n"/>
+      <c r="AQ3" s="556" t="n"/>
+      <c r="AR3" s="422" t="n"/>
+      <c r="AS3" s="422" t="n"/>
+      <c r="AT3" s="422" t="n"/>
+      <c r="AU3" s="422" t="n"/>
+      <c r="AV3" s="557" t="n"/>
+      <c r="AW3" s="558" t="inlineStr">
+        <is>
+          <t>YYYY-MM-DD</t>
+        </is>
+      </c>
+      <c r="AX3" s="422" t="n"/>
+      <c r="AY3" s="422" t="n"/>
+      <c r="AZ3" s="422" t="n"/>
+      <c r="BA3" s="422" t="n"/>
+      <c r="BB3" s="422" t="n"/>
+      <c r="BC3" s="422" t="n"/>
+      <c r="BD3" s="559" t="n"/>
     </row>
     <row r="4" ht="15" customHeight="1">
-      <c r="A4" s="519" t="inlineStr">
+      <c r="A4" s="554" t="n"/>
+      <c r="K4" s="555" t="n"/>
+      <c r="L4" s="560" t="inlineStr">
+        <is>
+          <t>Quality Management System · Controlled Document</t>
+        </is>
+      </c>
+      <c r="AP4" s="555" t="n"/>
+      <c r="AQ4" s="556" t="n"/>
+      <c r="AR4" s="422" t="n"/>
+      <c r="AS4" s="422" t="n"/>
+      <c r="AT4" s="422" t="n"/>
+      <c r="AU4" s="422" t="n"/>
+      <c r="AV4" s="557" t="n"/>
+      <c r="AW4" s="558" t="inlineStr">
+        <is>
+          <t>Warehouse + QA</t>
+        </is>
+      </c>
+      <c r="AX4" s="422" t="n"/>
+      <c r="AY4" s="422" t="n"/>
+      <c r="AZ4" s="422" t="n"/>
+      <c r="BA4" s="422" t="n"/>
+      <c r="BB4" s="422" t="n"/>
+      <c r="BC4" s="422" t="n"/>
+      <c r="BD4" s="559" t="n"/>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" s="561" t="n"/>
+      <c r="B5" s="562" t="n"/>
+      <c r="C5" s="562" t="n"/>
+      <c r="D5" s="562" t="n"/>
+      <c r="E5" s="562" t="n"/>
+      <c r="F5" s="562" t="n"/>
+      <c r="G5" s="562" t="n"/>
+      <c r="H5" s="562" t="n"/>
+      <c r="I5" s="562" t="n"/>
+      <c r="J5" s="562" t="n"/>
+      <c r="K5" s="563" t="n"/>
+      <c r="L5" s="564" t="inlineStr">
+        <is>
+          <t>HESEM Engineering · ISO 9001 / AS9100 · Semiconductor Equipment Parts</t>
+        </is>
+      </c>
+      <c r="M5" s="562" t="n"/>
+      <c r="N5" s="562" t="n"/>
+      <c r="O5" s="562" t="n"/>
+      <c r="P5" s="562" t="n"/>
+      <c r="Q5" s="562" t="n"/>
+      <c r="R5" s="562" t="n"/>
+      <c r="S5" s="562" t="n"/>
+      <c r="T5" s="562" t="n"/>
+      <c r="U5" s="562" t="n"/>
+      <c r="V5" s="562" t="n"/>
+      <c r="W5" s="562" t="n"/>
+      <c r="X5" s="562" t="n"/>
+      <c r="Y5" s="562" t="n"/>
+      <c r="Z5" s="562" t="n"/>
+      <c r="AA5" s="562" t="n"/>
+      <c r="AB5" s="562" t="n"/>
+      <c r="AC5" s="562" t="n"/>
+      <c r="AD5" s="562" t="n"/>
+      <c r="AE5" s="562" t="n"/>
+      <c r="AF5" s="562" t="n"/>
+      <c r="AG5" s="562" t="n"/>
+      <c r="AH5" s="562" t="n"/>
+      <c r="AI5" s="562" t="n"/>
+      <c r="AJ5" s="562" t="n"/>
+      <c r="AK5" s="562" t="n"/>
+      <c r="AL5" s="562" t="n"/>
+      <c r="AM5" s="562" t="n"/>
+      <c r="AN5" s="562" t="n"/>
+      <c r="AO5" s="562" t="n"/>
+      <c r="AP5" s="563" t="n"/>
+      <c r="AQ5" s="565" t="n"/>
+      <c r="AR5" s="566" t="n"/>
+      <c r="AS5" s="566" t="n"/>
+      <c r="AT5" s="566" t="n"/>
+      <c r="AU5" s="566" t="n"/>
+      <c r="AV5" s="567" t="n"/>
+      <c r="AW5" s="568" t="inlineStr">
+        <is>
+          <t>General Manager</t>
+        </is>
+      </c>
+      <c r="AX5" s="566" t="n"/>
+      <c r="AY5" s="566" t="n"/>
+      <c r="AZ5" s="566" t="n"/>
+      <c r="BA5" s="566" t="n"/>
+      <c r="BB5" s="566" t="n"/>
+      <c r="BC5" s="566" t="n"/>
+      <c r="BD5" s="569" t="n"/>
+    </row>
+    <row r="6" ht="1.5" customHeight="1">
+      <c r="A6" s="659" t="n"/>
+      <c r="B6" s="659" t="n"/>
+      <c r="C6" s="660" t="n"/>
+      <c r="D6" s="659" t="n"/>
+      <c r="E6" s="659" t="n"/>
+      <c r="F6" s="659" t="n"/>
+      <c r="G6" s="659" t="n"/>
+      <c r="H6" s="659" t="n"/>
+      <c r="I6" s="659" t="n"/>
+      <c r="J6" s="659" t="n"/>
+      <c r="K6" s="659" t="n"/>
+      <c r="L6" s="659" t="n"/>
+      <c r="M6" s="659" t="n"/>
+      <c r="N6" s="659" t="n"/>
+      <c r="O6" s="659" t="n"/>
+      <c r="P6" s="659" t="n"/>
+      <c r="Q6" s="659" t="n"/>
+      <c r="R6" s="659" t="n"/>
+      <c r="S6" s="659" t="n"/>
+      <c r="T6" s="659" t="n"/>
+      <c r="U6" s="659" t="n"/>
+      <c r="V6" s="659" t="n"/>
+      <c r="W6" s="659" t="n"/>
+      <c r="X6" s="659" t="n"/>
+      <c r="Y6" s="659" t="n"/>
+      <c r="Z6" s="659" t="n"/>
+      <c r="AA6" s="659" t="n"/>
+      <c r="AB6" s="659" t="n"/>
+      <c r="AC6" s="659" t="n"/>
+      <c r="AD6" s="659" t="n"/>
+      <c r="AE6" s="659" t="n"/>
+      <c r="AF6" s="659" t="n"/>
+      <c r="AG6" s="659" t="n"/>
+      <c r="AH6" s="659" t="n"/>
+      <c r="AI6" s="659" t="n"/>
+      <c r="AJ6" s="659" t="n"/>
+      <c r="AK6" s="659" t="n"/>
+      <c r="AL6" s="659" t="n"/>
+      <c r="AM6" s="659" t="n"/>
+      <c r="AN6" s="659" t="n"/>
+      <c r="AO6" s="659" t="n"/>
+      <c r="AP6" s="659" t="n"/>
+      <c r="AQ6" s="659" t="n"/>
+      <c r="AR6" s="659" t="n"/>
+      <c r="AS6" s="659" t="n"/>
+      <c r="AT6" s="659" t="n"/>
+      <c r="AU6" s="659" t="n"/>
+      <c r="AV6" s="659" t="n"/>
+      <c r="AW6" s="659" t="n"/>
+      <c r="AX6" s="659" t="n"/>
+      <c r="AY6" s="659" t="n"/>
+      <c r="AZ6" s="659" t="n"/>
+      <c r="BA6" s="659" t="n"/>
+      <c r="BB6" s="659" t="n"/>
+      <c r="BC6" s="659" t="n"/>
+      <c r="BD6" s="659" t="n"/>
+    </row>
+    <row r="7" ht="18" customHeight="1">
+      <c r="A7" s="570" t="inlineStr">
+        <is>
+          <t>VAC-BUILD CONDITIONS / ACTIONS</t>
+        </is>
+      </c>
+      <c r="B7" s="571" t="n"/>
+      <c r="C7" s="571" t="n"/>
+      <c r="D7" s="571" t="n"/>
+      <c r="E7" s="571" t="n"/>
+      <c r="F7" s="571" t="n"/>
+      <c r="G7" s="571" t="n"/>
+      <c r="H7" s="571" t="n"/>
+      <c r="I7" s="571" t="n"/>
+      <c r="J7" s="571" t="n"/>
+      <c r="K7" s="571" t="n"/>
+      <c r="L7" s="571" t="n"/>
+      <c r="M7" s="571" t="n"/>
+      <c r="N7" s="571" t="n"/>
+      <c r="O7" s="571" t="n"/>
+      <c r="P7" s="571" t="n"/>
+      <c r="Q7" s="571" t="n"/>
+      <c r="R7" s="571" t="n"/>
+      <c r="S7" s="571" t="n"/>
+      <c r="T7" s="571" t="n"/>
+      <c r="U7" s="571" t="n"/>
+      <c r="V7" s="571" t="n"/>
+      <c r="W7" s="571" t="n"/>
+      <c r="X7" s="571" t="n"/>
+      <c r="Y7" s="571" t="n"/>
+      <c r="Z7" s="571" t="n"/>
+      <c r="AA7" s="571" t="n"/>
+      <c r="AB7" s="571" t="n"/>
+      <c r="AC7" s="571" t="n"/>
+      <c r="AD7" s="571" t="n"/>
+      <c r="AE7" s="571" t="n"/>
+      <c r="AF7" s="571" t="n"/>
+      <c r="AG7" s="571" t="n"/>
+      <c r="AH7" s="571" t="n"/>
+      <c r="AI7" s="571" t="n"/>
+      <c r="AJ7" s="571" t="n"/>
+      <c r="AK7" s="571" t="n"/>
+      <c r="AL7" s="571" t="n"/>
+      <c r="AM7" s="571" t="n"/>
+      <c r="AN7" s="571" t="n"/>
+      <c r="AO7" s="571" t="n"/>
+      <c r="AP7" s="571" t="n"/>
+      <c r="AQ7" s="571" t="n"/>
+      <c r="AR7" s="571" t="n"/>
+      <c r="AS7" s="571" t="n"/>
+      <c r="AT7" s="571" t="n"/>
+      <c r="AU7" s="571" t="n"/>
+      <c r="AV7" s="571" t="n"/>
+      <c r="AW7" s="571" t="n"/>
+      <c r="AX7" s="571" t="n"/>
+      <c r="AY7" s="571" t="n"/>
+      <c r="AZ7" s="571" t="n"/>
+      <c r="BA7" s="571" t="n"/>
+      <c r="BB7" s="571" t="n"/>
+      <c r="BC7" s="571" t="n"/>
+      <c r="BD7" s="572" t="n"/>
+    </row>
+    <row r="8" ht="18" customHeight="1">
+      <c r="A8" s="640" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B4" s="520" t="inlineStr">
+      <c r="B8" s="641" t="n"/>
+      <c r="C8" s="668" t="inlineStr">
         <is>
           <t>Condition / Exception</t>
         </is>
       </c>
-      <c r="C4" s="520" t="inlineStr">
+      <c r="D8" s="669" t="n"/>
+      <c r="E8" s="669" t="n"/>
+      <c r="F8" s="669" t="n"/>
+      <c r="G8" s="669" t="n"/>
+      <c r="H8" s="669" t="n"/>
+      <c r="I8" s="669" t="n"/>
+      <c r="J8" s="669" t="n"/>
+      <c r="K8" s="669" t="n"/>
+      <c r="L8" s="669" t="n"/>
+      <c r="M8" s="669" t="n"/>
+      <c r="N8" s="669" t="n"/>
+      <c r="O8" s="669" t="n"/>
+      <c r="P8" s="670" t="n"/>
+      <c r="Q8" s="642" t="inlineStr">
         <is>
           <t>Required Action</t>
         </is>
       </c>
-      <c r="D4" s="520" t="inlineStr">
+      <c r="R8" s="571" t="n"/>
+      <c r="S8" s="571" t="n"/>
+      <c r="T8" s="571" t="n"/>
+      <c r="U8" s="571" t="n"/>
+      <c r="V8" s="571" t="n"/>
+      <c r="W8" s="571" t="n"/>
+      <c r="X8" s="571" t="n"/>
+      <c r="Y8" s="571" t="n"/>
+      <c r="Z8" s="571" t="n"/>
+      <c r="AA8" s="571" t="n"/>
+      <c r="AB8" s="571" t="n"/>
+      <c r="AC8" s="571" t="n"/>
+      <c r="AD8" s="571" t="n"/>
+      <c r="AE8" s="571" t="n"/>
+      <c r="AF8" s="571" t="n"/>
+      <c r="AG8" s="641" t="n"/>
+      <c r="AH8" s="642" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="E4" s="520" t="inlineStr">
+      <c r="AI8" s="571" t="n"/>
+      <c r="AJ8" s="571" t="n"/>
+      <c r="AK8" s="571" t="n"/>
+      <c r="AL8" s="571" t="n"/>
+      <c r="AM8" s="571" t="n"/>
+      <c r="AN8" s="641" t="n"/>
+      <c r="AO8" s="642" t="inlineStr">
         <is>
           <t>Due Date</t>
         </is>
       </c>
-      <c r="F4" s="520" t="inlineStr">
+      <c r="AP8" s="571" t="n"/>
+      <c r="AQ8" s="571" t="n"/>
+      <c r="AR8" s="571" t="n"/>
+      <c r="AS8" s="571" t="n"/>
+      <c r="AT8" s="571" t="n"/>
+      <c r="AU8" s="641" t="n"/>
+      <c r="AV8" s="642" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="G4" s="520" t="inlineStr">
+      <c r="AW8" s="571" t="n"/>
+      <c r="AX8" s="571" t="n"/>
+      <c r="AY8" s="641" t="n"/>
+      <c r="AZ8" s="643" t="inlineStr">
         <is>
-          <t>Evidence Ref</t>
+          <t>Verified by</t>
         </is>
       </c>
-      <c r="H4" s="521" t="inlineStr">
-        <is>
-          <t>Notes</t>
-        </is>
-      </c>
-      <c r="I4" s="451" t="n"/>
-      <c r="J4" s="452" t="n"/>
-      <c r="K4" s="452" t="n"/>
-      <c r="L4" s="452" t="n"/>
-      <c r="M4" s="452" t="n"/>
-      <c r="N4" s="452" t="n"/>
-      <c r="O4" s="452" t="n"/>
-      <c r="P4" s="452" t="n"/>
-      <c r="Q4" s="452" t="n"/>
-      <c r="R4" s="452" t="n"/>
-      <c r="S4" s="452" t="n"/>
-      <c r="T4" s="452" t="n"/>
-      <c r="U4" s="452" t="n"/>
-      <c r="V4" s="452" t="n"/>
-      <c r="W4" s="452" t="n"/>
-      <c r="X4" s="452" t="n"/>
-      <c r="Y4" s="452" t="n"/>
-      <c r="Z4" s="452" t="n"/>
-      <c r="AA4" s="452" t="n"/>
-      <c r="AB4" s="452" t="n"/>
-      <c r="AC4" s="452" t="n"/>
-      <c r="AD4" s="453" t="n"/>
-      <c r="AE4" s="445" t="n"/>
-      <c r="AF4" s="446" t="n"/>
-      <c r="AG4" s="446" t="n"/>
-      <c r="AH4" s="447" t="n"/>
-      <c r="AI4" s="448" t="n"/>
-      <c r="AJ4" s="449" t="n"/>
-      <c r="AK4" s="449" t="n"/>
-      <c r="AL4" s="449" t="n"/>
-      <c r="AM4" s="449" t="n"/>
-      <c r="AN4" s="450" t="n"/>
+      <c r="BA8" s="571" t="n"/>
+      <c r="BB8" s="571" t="n"/>
+      <c r="BC8" s="571" t="n"/>
+      <c r="BD8" s="572" t="n"/>
     </row>
-    <row r="5" ht="15" customHeight="1">
-      <c r="A5" s="522">
-        <f>ROW()-ROW($A$5)+1</f>
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="671">
+        <f>ROW()-ROW($A$9)+1</f>
         <v/>
       </c>
-      <c r="B5" s="523" t="n"/>
-      <c r="C5" s="523" t="n"/>
-      <c r="D5" s="523" t="n"/>
-      <c r="E5" s="523" t="n"/>
-      <c r="F5" s="523" t="n"/>
-      <c r="G5" s="523" t="n"/>
-      <c r="H5" s="524" t="n"/>
-      <c r="I5" s="457" t="n"/>
-      <c r="J5" s="458" t="n"/>
-      <c r="K5" s="458" t="n"/>
-      <c r="L5" s="458" t="n"/>
-      <c r="M5" s="458" t="n"/>
-      <c r="N5" s="458" t="n"/>
-      <c r="O5" s="458" t="n"/>
-      <c r="P5" s="458" t="n"/>
-      <c r="Q5" s="458" t="n"/>
-      <c r="R5" s="458" t="n"/>
-      <c r="S5" s="458" t="n"/>
-      <c r="T5" s="458" t="n"/>
-      <c r="U5" s="458" t="n"/>
-      <c r="V5" s="458" t="n"/>
-      <c r="W5" s="458" t="n"/>
-      <c r="X5" s="458" t="n"/>
-      <c r="Y5" s="458" t="n"/>
-      <c r="Z5" s="458" t="n"/>
-      <c r="AA5" s="458" t="n"/>
-      <c r="AB5" s="458" t="n"/>
-      <c r="AC5" s="458" t="n"/>
-      <c r="AD5" s="459" t="n"/>
-      <c r="AE5" s="460" t="n"/>
-      <c r="AF5" s="461" t="n"/>
-      <c r="AG5" s="461" t="n"/>
-      <c r="AH5" s="462" t="n"/>
-      <c r="AI5" s="463" t="n"/>
-      <c r="AJ5" s="464" t="n"/>
-      <c r="AK5" s="464" t="n"/>
-      <c r="AL5" s="464" t="n"/>
-      <c r="AM5" s="464" t="n"/>
-      <c r="AN5" s="465" t="n"/>
+      <c r="B9" s="424" t="n"/>
+      <c r="C9" s="645" t="n"/>
+      <c r="D9" s="577" t="n"/>
+      <c r="E9" s="577" t="n"/>
+      <c r="F9" s="577" t="n"/>
+      <c r="G9" s="577" t="n"/>
+      <c r="H9" s="577" t="n"/>
+      <c r="I9" s="577" t="n"/>
+      <c r="J9" s="577" t="n"/>
+      <c r="K9" s="577" t="n"/>
+      <c r="L9" s="577" t="n"/>
+      <c r="M9" s="577" t="n"/>
+      <c r="N9" s="577" t="n"/>
+      <c r="O9" s="577" t="n"/>
+      <c r="P9" s="646" t="n"/>
+      <c r="Q9" s="647" t="n"/>
+      <c r="R9" s="423" t="n"/>
+      <c r="S9" s="423" t="n"/>
+      <c r="T9" s="423" t="n"/>
+      <c r="U9" s="423" t="n"/>
+      <c r="V9" s="423" t="n"/>
+      <c r="W9" s="423" t="n"/>
+      <c r="X9" s="423" t="n"/>
+      <c r="Y9" s="423" t="n"/>
+      <c r="Z9" s="423" t="n"/>
+      <c r="AA9" s="423" t="n"/>
+      <c r="AB9" s="423" t="n"/>
+      <c r="AC9" s="423" t="n"/>
+      <c r="AD9" s="423" t="n"/>
+      <c r="AE9" s="423" t="n"/>
+      <c r="AF9" s="423" t="n"/>
+      <c r="AG9" s="424" t="n"/>
+      <c r="AH9" s="647" t="n"/>
+      <c r="AI9" s="423" t="n"/>
+      <c r="AJ9" s="423" t="n"/>
+      <c r="AK9" s="423" t="n"/>
+      <c r="AL9" s="423" t="n"/>
+      <c r="AM9" s="423" t="n"/>
+      <c r="AN9" s="424" t="n"/>
+      <c r="AO9" s="647" t="n"/>
+      <c r="AP9" s="423" t="n"/>
+      <c r="AQ9" s="423" t="n"/>
+      <c r="AR9" s="423" t="n"/>
+      <c r="AS9" s="423" t="n"/>
+      <c r="AT9" s="423" t="n"/>
+      <c r="AU9" s="424" t="n"/>
+      <c r="AV9" s="647" t="n"/>
+      <c r="AW9" s="423" t="n"/>
+      <c r="AX9" s="423" t="n"/>
+      <c r="AY9" s="424" t="n"/>
+      <c r="AZ9" s="648" t="n"/>
+      <c r="BA9" s="423" t="n"/>
+      <c r="BB9" s="423" t="n"/>
+      <c r="BC9" s="423" t="n"/>
+      <c r="BD9" s="649" t="n"/>
     </row>
-    <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="525">
-        <f>ROW()-ROW($A$5)+1</f>
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="672">
+        <f>ROW()-ROW($A$9)+1</f>
         <v/>
       </c>
-      <c r="B6" s="526" t="n"/>
-      <c r="C6" s="527" t="n"/>
-      <c r="D6" s="527" t="n"/>
-      <c r="E6" s="527" t="n"/>
-      <c r="F6" s="527" t="n"/>
-      <c r="G6" s="527" t="n"/>
-      <c r="H6" s="527" t="n"/>
-      <c r="I6" s="471" t="n"/>
-      <c r="J6" s="471" t="n"/>
-      <c r="K6" s="471" t="n"/>
-      <c r="L6" s="471" t="n"/>
-      <c r="M6" s="471" t="n"/>
-      <c r="N6" s="471" t="n"/>
-      <c r="O6" s="471" t="n"/>
-      <c r="P6" s="471" t="n"/>
-      <c r="Q6" s="471" t="n"/>
-      <c r="R6" s="471" t="n"/>
-      <c r="S6" s="471" t="n"/>
-      <c r="T6" s="471" t="n"/>
-      <c r="U6" s="471" t="n"/>
-      <c r="V6" s="471" t="n"/>
-      <c r="W6" s="471" t="n"/>
-      <c r="X6" s="471" t="n"/>
-      <c r="Y6" s="471" t="n"/>
-      <c r="Z6" s="471" t="n"/>
-      <c r="AA6" s="471" t="n"/>
-      <c r="AB6" s="471" t="n"/>
-      <c r="AC6" s="471" t="n"/>
-      <c r="AD6" s="471" t="n"/>
-      <c r="AE6" s="471" t="n"/>
-      <c r="AF6" s="471" t="n"/>
-      <c r="AG6" s="471" t="n"/>
-      <c r="AH6" s="471" t="n"/>
-      <c r="AI6" s="471" t="n"/>
-      <c r="AJ6" s="471" t="n"/>
-      <c r="AK6" s="471" t="n"/>
-      <c r="AL6" s="471" t="n"/>
-      <c r="AM6" s="471" t="n"/>
-      <c r="AN6" s="503" t="n"/>
+      <c r="B10" s="424" t="n"/>
+      <c r="C10" s="651" t="n"/>
+      <c r="D10" s="577" t="n"/>
+      <c r="E10" s="577" t="n"/>
+      <c r="F10" s="577" t="n"/>
+      <c r="G10" s="577" t="n"/>
+      <c r="H10" s="577" t="n"/>
+      <c r="I10" s="577" t="n"/>
+      <c r="J10" s="577" t="n"/>
+      <c r="K10" s="577" t="n"/>
+      <c r="L10" s="577" t="n"/>
+      <c r="M10" s="577" t="n"/>
+      <c r="N10" s="577" t="n"/>
+      <c r="O10" s="577" t="n"/>
+      <c r="P10" s="646" t="n"/>
+      <c r="Q10" s="652" t="n"/>
+      <c r="R10" s="423" t="n"/>
+      <c r="S10" s="423" t="n"/>
+      <c r="T10" s="423" t="n"/>
+      <c r="U10" s="423" t="n"/>
+      <c r="V10" s="423" t="n"/>
+      <c r="W10" s="423" t="n"/>
+      <c r="X10" s="423" t="n"/>
+      <c r="Y10" s="423" t="n"/>
+      <c r="Z10" s="423" t="n"/>
+      <c r="AA10" s="423" t="n"/>
+      <c r="AB10" s="423" t="n"/>
+      <c r="AC10" s="423" t="n"/>
+      <c r="AD10" s="423" t="n"/>
+      <c r="AE10" s="423" t="n"/>
+      <c r="AF10" s="423" t="n"/>
+      <c r="AG10" s="424" t="n"/>
+      <c r="AH10" s="652" t="n"/>
+      <c r="AI10" s="423" t="n"/>
+      <c r="AJ10" s="423" t="n"/>
+      <c r="AK10" s="423" t="n"/>
+      <c r="AL10" s="423" t="n"/>
+      <c r="AM10" s="423" t="n"/>
+      <c r="AN10" s="424" t="n"/>
+      <c r="AO10" s="652" t="n"/>
+      <c r="AP10" s="423" t="n"/>
+      <c r="AQ10" s="423" t="n"/>
+      <c r="AR10" s="423" t="n"/>
+      <c r="AS10" s="423" t="n"/>
+      <c r="AT10" s="423" t="n"/>
+      <c r="AU10" s="424" t="n"/>
+      <c r="AV10" s="652" t="n"/>
+      <c r="AW10" s="423" t="n"/>
+      <c r="AX10" s="423" t="n"/>
+      <c r="AY10" s="424" t="n"/>
+      <c r="AZ10" s="653" t="n"/>
+      <c r="BA10" s="423" t="n"/>
+      <c r="BB10" s="423" t="n"/>
+      <c r="BC10" s="423" t="n"/>
+      <c r="BD10" s="649" t="n"/>
     </row>
-    <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="528">
-        <f>ROW()-ROW($A$5)+1</f>
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="671">
+        <f>ROW()-ROW($A$9)+1</f>
         <v/>
       </c>
-      <c r="B7" s="529" t="n"/>
-      <c r="C7" s="530" t="n"/>
-      <c r="D7" s="530" t="n"/>
-      <c r="E7" s="530" t="n"/>
-      <c r="F7" s="530" t="n"/>
-      <c r="G7" s="530" t="n"/>
-      <c r="H7" s="530" t="n"/>
-      <c r="I7" s="344" t="n"/>
-      <c r="J7" s="344" t="n"/>
-      <c r="K7" s="344" t="n"/>
-      <c r="L7" s="344" t="n"/>
-      <c r="M7" s="344" t="n"/>
-      <c r="N7" s="344" t="n"/>
-      <c r="O7" s="344" t="n"/>
-      <c r="P7" s="344" t="n"/>
-      <c r="Q7" s="344" t="n"/>
-      <c r="R7" s="344" t="n"/>
-      <c r="S7" s="344" t="n"/>
-      <c r="T7" s="344" t="n"/>
-      <c r="U7" s="344" t="n"/>
-      <c r="V7" s="344" t="n"/>
-      <c r="W7" s="344" t="n"/>
-      <c r="X7" s="344" t="n"/>
-      <c r="Y7" s="344" t="n"/>
-      <c r="Z7" s="344" t="n"/>
-      <c r="AA7" s="344" t="n"/>
-      <c r="AB7" s="344" t="n"/>
-      <c r="AC7" s="344" t="n"/>
-      <c r="AD7" s="344" t="n"/>
-      <c r="AE7" s="344" t="n"/>
-      <c r="AF7" s="344" t="n"/>
-      <c r="AG7" s="344" t="n"/>
-      <c r="AH7" s="344" t="n"/>
-      <c r="AI7" s="344" t="n"/>
-      <c r="AJ7" s="344" t="n"/>
-      <c r="AK7" s="344" t="n"/>
-      <c r="AL7" s="344" t="n"/>
-      <c r="AM7" s="344" t="n"/>
-      <c r="AN7" s="531" t="n"/>
+      <c r="B11" s="424" t="n"/>
+      <c r="C11" s="645" t="n"/>
+      <c r="D11" s="577" t="n"/>
+      <c r="E11" s="577" t="n"/>
+      <c r="F11" s="577" t="n"/>
+      <c r="G11" s="577" t="n"/>
+      <c r="H11" s="577" t="n"/>
+      <c r="I11" s="577" t="n"/>
+      <c r="J11" s="577" t="n"/>
+      <c r="K11" s="577" t="n"/>
+      <c r="L11" s="577" t="n"/>
+      <c r="M11" s="577" t="n"/>
+      <c r="N11" s="577" t="n"/>
+      <c r="O11" s="577" t="n"/>
+      <c r="P11" s="646" t="n"/>
+      <c r="Q11" s="647" t="n"/>
+      <c r="R11" s="423" t="n"/>
+      <c r="S11" s="423" t="n"/>
+      <c r="T11" s="423" t="n"/>
+      <c r="U11" s="423" t="n"/>
+      <c r="V11" s="423" t="n"/>
+      <c r="W11" s="423" t="n"/>
+      <c r="X11" s="423" t="n"/>
+      <c r="Y11" s="423" t="n"/>
+      <c r="Z11" s="423" t="n"/>
+      <c r="AA11" s="423" t="n"/>
+      <c r="AB11" s="423" t="n"/>
+      <c r="AC11" s="423" t="n"/>
+      <c r="AD11" s="423" t="n"/>
+      <c r="AE11" s="423" t="n"/>
+      <c r="AF11" s="423" t="n"/>
+      <c r="AG11" s="424" t="n"/>
+      <c r="AH11" s="647" t="n"/>
+      <c r="AI11" s="423" t="n"/>
+      <c r="AJ11" s="423" t="n"/>
+      <c r="AK11" s="423" t="n"/>
+      <c r="AL11" s="423" t="n"/>
+      <c r="AM11" s="423" t="n"/>
+      <c r="AN11" s="424" t="n"/>
+      <c r="AO11" s="647" t="n"/>
+      <c r="AP11" s="423" t="n"/>
+      <c r="AQ11" s="423" t="n"/>
+      <c r="AR11" s="423" t="n"/>
+      <c r="AS11" s="423" t="n"/>
+      <c r="AT11" s="423" t="n"/>
+      <c r="AU11" s="424" t="n"/>
+      <c r="AV11" s="647" t="n"/>
+      <c r="AW11" s="423" t="n"/>
+      <c r="AX11" s="423" t="n"/>
+      <c r="AY11" s="424" t="n"/>
+      <c r="AZ11" s="648" t="n"/>
+      <c r="BA11" s="423" t="n"/>
+      <c r="BB11" s="423" t="n"/>
+      <c r="BC11" s="423" t="n"/>
+      <c r="BD11" s="649" t="n"/>
     </row>
-    <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="532">
-        <f>ROW()-ROW($A$5)+1</f>
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="672">
+        <f>ROW()-ROW($A$9)+1</f>
         <v/>
       </c>
-      <c r="B8" s="533" t="n"/>
-      <c r="C8" s="534" t="n"/>
-      <c r="D8" s="534" t="n"/>
-      <c r="E8" s="534" t="n"/>
-      <c r="F8" s="534" t="n"/>
-      <c r="G8" s="534" t="n"/>
-      <c r="H8" s="534" t="n"/>
-      <c r="I8" s="356" t="n"/>
-      <c r="J8" s="356" t="n"/>
-      <c r="K8" s="356" t="n"/>
-      <c r="L8" s="356" t="n"/>
-      <c r="M8" s="356" t="n"/>
-      <c r="N8" s="356" t="n"/>
-      <c r="O8" s="356" t="n"/>
-      <c r="P8" s="356" t="n"/>
-      <c r="Q8" s="356" t="n"/>
-      <c r="R8" s="356" t="n"/>
-      <c r="S8" s="356" t="n"/>
-      <c r="T8" s="356" t="n"/>
-      <c r="U8" s="356" t="n"/>
-      <c r="V8" s="356" t="n"/>
-      <c r="W8" s="356" t="n"/>
-      <c r="X8" s="356" t="n"/>
-      <c r="Y8" s="356" t="n"/>
-      <c r="Z8" s="356" t="n"/>
-      <c r="AA8" s="356" t="n"/>
-      <c r="AB8" s="356" t="n"/>
-      <c r="AC8" s="356" t="n"/>
-      <c r="AD8" s="356" t="n"/>
-      <c r="AE8" s="356" t="n"/>
-      <c r="AF8" s="356" t="n"/>
-      <c r="AG8" s="356" t="n"/>
-      <c r="AH8" s="356" t="n"/>
-      <c r="AI8" s="356" t="n"/>
-      <c r="AJ8" s="356" t="n"/>
-      <c r="AK8" s="356" t="n"/>
-      <c r="AL8" s="356" t="n"/>
-      <c r="AM8" s="356" t="n"/>
-      <c r="AN8" s="535" t="n"/>
+      <c r="B12" s="424" t="n"/>
+      <c r="C12" s="651" t="n"/>
+      <c r="D12" s="577" t="n"/>
+      <c r="E12" s="577" t="n"/>
+      <c r="F12" s="577" t="n"/>
+      <c r="G12" s="577" t="n"/>
+      <c r="H12" s="577" t="n"/>
+      <c r="I12" s="577" t="n"/>
+      <c r="J12" s="577" t="n"/>
+      <c r="K12" s="577" t="n"/>
+      <c r="L12" s="577" t="n"/>
+      <c r="M12" s="577" t="n"/>
+      <c r="N12" s="577" t="n"/>
+      <c r="O12" s="577" t="n"/>
+      <c r="P12" s="646" t="n"/>
+      <c r="Q12" s="652" t="n"/>
+      <c r="R12" s="423" t="n"/>
+      <c r="S12" s="423" t="n"/>
+      <c r="T12" s="423" t="n"/>
+      <c r="U12" s="423" t="n"/>
+      <c r="V12" s="423" t="n"/>
+      <c r="W12" s="423" t="n"/>
+      <c r="X12" s="423" t="n"/>
+      <c r="Y12" s="423" t="n"/>
+      <c r="Z12" s="423" t="n"/>
+      <c r="AA12" s="423" t="n"/>
+      <c r="AB12" s="423" t="n"/>
+      <c r="AC12" s="423" t="n"/>
+      <c r="AD12" s="423" t="n"/>
+      <c r="AE12" s="423" t="n"/>
+      <c r="AF12" s="423" t="n"/>
+      <c r="AG12" s="424" t="n"/>
+      <c r="AH12" s="652" t="n"/>
+      <c r="AI12" s="423" t="n"/>
+      <c r="AJ12" s="423" t="n"/>
+      <c r="AK12" s="423" t="n"/>
+      <c r="AL12" s="423" t="n"/>
+      <c r="AM12" s="423" t="n"/>
+      <c r="AN12" s="424" t="n"/>
+      <c r="AO12" s="652" t="n"/>
+      <c r="AP12" s="423" t="n"/>
+      <c r="AQ12" s="423" t="n"/>
+      <c r="AR12" s="423" t="n"/>
+      <c r="AS12" s="423" t="n"/>
+      <c r="AT12" s="423" t="n"/>
+      <c r="AU12" s="424" t="n"/>
+      <c r="AV12" s="652" t="n"/>
+      <c r="AW12" s="423" t="n"/>
+      <c r="AX12" s="423" t="n"/>
+      <c r="AY12" s="424" t="n"/>
+      <c r="AZ12" s="653" t="n"/>
+      <c r="BA12" s="423" t="n"/>
+      <c r="BB12" s="423" t="n"/>
+      <c r="BC12" s="423" t="n"/>
+      <c r="BD12" s="649" t="n"/>
     </row>
-    <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="532">
-        <f>ROW()-ROW($A$5)+1</f>
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="671">
+        <f>ROW()-ROW($A$9)+1</f>
         <v/>
       </c>
-      <c r="B9" s="533" t="n"/>
-      <c r="C9" s="534" t="n"/>
-      <c r="D9" s="534" t="n"/>
-      <c r="E9" s="534" t="n"/>
-      <c r="F9" s="534" t="n"/>
-      <c r="G9" s="534" t="n"/>
-      <c r="H9" s="534" t="n"/>
-      <c r="I9" s="356" t="n"/>
-      <c r="J9" s="356" t="n"/>
-      <c r="K9" s="356" t="n"/>
-      <c r="L9" s="356" t="n"/>
-      <c r="M9" s="356" t="n"/>
-      <c r="N9" s="356" t="n"/>
-      <c r="O9" s="356" t="n"/>
-      <c r="P9" s="356" t="n"/>
-      <c r="Q9" s="356" t="n"/>
-      <c r="R9" s="356" t="n"/>
-      <c r="S9" s="356" t="n"/>
-      <c r="T9" s="356" t="n"/>
-      <c r="U9" s="356" t="n"/>
-      <c r="V9" s="356" t="n"/>
-      <c r="W9" s="356" t="n"/>
-      <c r="X9" s="356" t="n"/>
-      <c r="Y9" s="356" t="n"/>
-      <c r="Z9" s="356" t="n"/>
-      <c r="AA9" s="356" t="n"/>
-      <c r="AB9" s="356" t="n"/>
-      <c r="AC9" s="356" t="n"/>
-      <c r="AD9" s="356" t="n"/>
-      <c r="AE9" s="356" t="n"/>
-      <c r="AF9" s="356" t="n"/>
-      <c r="AG9" s="356" t="n"/>
-      <c r="AH9" s="356" t="n"/>
-      <c r="AI9" s="356" t="n"/>
-      <c r="AJ9" s="356" t="n"/>
-      <c r="AK9" s="356" t="n"/>
-      <c r="AL9" s="356" t="n"/>
-      <c r="AM9" s="356" t="n"/>
-      <c r="AN9" s="535" t="n"/>
+      <c r="B13" s="424" t="n"/>
+      <c r="C13" s="645" t="n"/>
+      <c r="D13" s="577" t="n"/>
+      <c r="E13" s="577" t="n"/>
+      <c r="F13" s="577" t="n"/>
+      <c r="G13" s="577" t="n"/>
+      <c r="H13" s="577" t="n"/>
+      <c r="I13" s="577" t="n"/>
+      <c r="J13" s="577" t="n"/>
+      <c r="K13" s="577" t="n"/>
+      <c r="L13" s="577" t="n"/>
+      <c r="M13" s="577" t="n"/>
+      <c r="N13" s="577" t="n"/>
+      <c r="O13" s="577" t="n"/>
+      <c r="P13" s="646" t="n"/>
+      <c r="Q13" s="647" t="n"/>
+      <c r="R13" s="423" t="n"/>
+      <c r="S13" s="423" t="n"/>
+      <c r="T13" s="423" t="n"/>
+      <c r="U13" s="423" t="n"/>
+      <c r="V13" s="423" t="n"/>
+      <c r="W13" s="423" t="n"/>
+      <c r="X13" s="423" t="n"/>
+      <c r="Y13" s="423" t="n"/>
+      <c r="Z13" s="423" t="n"/>
+      <c r="AA13" s="423" t="n"/>
+      <c r="AB13" s="423" t="n"/>
+      <c r="AC13" s="423" t="n"/>
+      <c r="AD13" s="423" t="n"/>
+      <c r="AE13" s="423" t="n"/>
+      <c r="AF13" s="423" t="n"/>
+      <c r="AG13" s="424" t="n"/>
+      <c r="AH13" s="647" t="n"/>
+      <c r="AI13" s="423" t="n"/>
+      <c r="AJ13" s="423" t="n"/>
+      <c r="AK13" s="423" t="n"/>
+      <c r="AL13" s="423" t="n"/>
+      <c r="AM13" s="423" t="n"/>
+      <c r="AN13" s="424" t="n"/>
+      <c r="AO13" s="647" t="n"/>
+      <c r="AP13" s="423" t="n"/>
+      <c r="AQ13" s="423" t="n"/>
+      <c r="AR13" s="423" t="n"/>
+      <c r="AS13" s="423" t="n"/>
+      <c r="AT13" s="423" t="n"/>
+      <c r="AU13" s="424" t="n"/>
+      <c r="AV13" s="647" t="n"/>
+      <c r="AW13" s="423" t="n"/>
+      <c r="AX13" s="423" t="n"/>
+      <c r="AY13" s="424" t="n"/>
+      <c r="AZ13" s="648" t="n"/>
+      <c r="BA13" s="423" t="n"/>
+      <c r="BB13" s="423" t="n"/>
+      <c r="BC13" s="423" t="n"/>
+      <c r="BD13" s="649" t="n"/>
     </row>
-    <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="532">
-        <f>ROW()-ROW($A$5)+1</f>
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="672">
+        <f>ROW()-ROW($A$9)+1</f>
         <v/>
       </c>
-      <c r="B10" s="533" t="n"/>
-      <c r="C10" s="534" t="n"/>
-      <c r="D10" s="534" t="n"/>
-      <c r="E10" s="534" t="n"/>
-      <c r="F10" s="534" t="n"/>
-      <c r="G10" s="534" t="n"/>
-      <c r="H10" s="534" t="n"/>
-      <c r="I10" s="356" t="n"/>
-      <c r="J10" s="356" t="n"/>
-      <c r="K10" s="356" t="n"/>
-      <c r="L10" s="356" t="n"/>
-      <c r="M10" s="356" t="n"/>
-      <c r="N10" s="356" t="n"/>
-      <c r="O10" s="356" t="n"/>
-      <c r="P10" s="356" t="n"/>
-      <c r="Q10" s="356" t="n"/>
-      <c r="R10" s="356" t="n"/>
-      <c r="S10" s="356" t="n"/>
-      <c r="T10" s="356" t="n"/>
-      <c r="U10" s="356" t="n"/>
-      <c r="V10" s="356" t="n"/>
-      <c r="W10" s="356" t="n"/>
-      <c r="X10" s="356" t="n"/>
-      <c r="Y10" s="356" t="n"/>
-      <c r="Z10" s="356" t="n"/>
-      <c r="AA10" s="356" t="n"/>
-      <c r="AB10" s="356" t="n"/>
-      <c r="AC10" s="356" t="n"/>
-      <c r="AD10" s="356" t="n"/>
-      <c r="AE10" s="356" t="n"/>
-      <c r="AF10" s="356" t="n"/>
-      <c r="AG10" s="356" t="n"/>
-      <c r="AH10" s="356" t="n"/>
-      <c r="AI10" s="356" t="n"/>
-      <c r="AJ10" s="356" t="n"/>
-      <c r="AK10" s="356" t="n"/>
-      <c r="AL10" s="356" t="n"/>
-      <c r="AM10" s="356" t="n"/>
-      <c r="AN10" s="535" t="n"/>
+      <c r="B14" s="424" t="n"/>
+      <c r="C14" s="651" t="n"/>
+      <c r="D14" s="577" t="n"/>
+      <c r="E14" s="577" t="n"/>
+      <c r="F14" s="577" t="n"/>
+      <c r="G14" s="577" t="n"/>
+      <c r="H14" s="577" t="n"/>
+      <c r="I14" s="577" t="n"/>
+      <c r="J14" s="577" t="n"/>
+      <c r="K14" s="577" t="n"/>
+      <c r="L14" s="577" t="n"/>
+      <c r="M14" s="577" t="n"/>
+      <c r="N14" s="577" t="n"/>
+      <c r="O14" s="577" t="n"/>
+      <c r="P14" s="646" t="n"/>
+      <c r="Q14" s="652" t="n"/>
+      <c r="R14" s="423" t="n"/>
+      <c r="S14" s="423" t="n"/>
+      <c r="T14" s="423" t="n"/>
+      <c r="U14" s="423" t="n"/>
+      <c r="V14" s="423" t="n"/>
+      <c r="W14" s="423" t="n"/>
+      <c r="X14" s="423" t="n"/>
+      <c r="Y14" s="423" t="n"/>
+      <c r="Z14" s="423" t="n"/>
+      <c r="AA14" s="423" t="n"/>
+      <c r="AB14" s="423" t="n"/>
+      <c r="AC14" s="423" t="n"/>
+      <c r="AD14" s="423" t="n"/>
+      <c r="AE14" s="423" t="n"/>
+      <c r="AF14" s="423" t="n"/>
+      <c r="AG14" s="424" t="n"/>
+      <c r="AH14" s="652" t="n"/>
+      <c r="AI14" s="423" t="n"/>
+      <c r="AJ14" s="423" t="n"/>
+      <c r="AK14" s="423" t="n"/>
+      <c r="AL14" s="423" t="n"/>
+      <c r="AM14" s="423" t="n"/>
+      <c r="AN14" s="424" t="n"/>
+      <c r="AO14" s="652" t="n"/>
+      <c r="AP14" s="423" t="n"/>
+      <c r="AQ14" s="423" t="n"/>
+      <c r="AR14" s="423" t="n"/>
+      <c r="AS14" s="423" t="n"/>
+      <c r="AT14" s="423" t="n"/>
+      <c r="AU14" s="424" t="n"/>
+      <c r="AV14" s="652" t="n"/>
+      <c r="AW14" s="423" t="n"/>
+      <c r="AX14" s="423" t="n"/>
+      <c r="AY14" s="424" t="n"/>
+      <c r="AZ14" s="653" t="n"/>
+      <c r="BA14" s="423" t="n"/>
+      <c r="BB14" s="423" t="n"/>
+      <c r="BC14" s="423" t="n"/>
+      <c r="BD14" s="649" t="n"/>
     </row>
-    <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="532">
-        <f>ROW()-ROW($A$5)+1</f>
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="671">
+        <f>ROW()-ROW($A$9)+1</f>
         <v/>
       </c>
-      <c r="B11" s="533" t="n"/>
-      <c r="C11" s="534" t="n"/>
-      <c r="D11" s="534" t="n"/>
-      <c r="E11" s="534" t="n"/>
-      <c r="F11" s="534" t="n"/>
-      <c r="G11" s="534" t="n"/>
-      <c r="H11" s="534" t="n"/>
-      <c r="I11" s="356" t="n"/>
-      <c r="J11" s="356" t="n"/>
-      <c r="K11" s="356" t="n"/>
-      <c r="L11" s="356" t="n"/>
-      <c r="M11" s="356" t="n"/>
-      <c r="N11" s="356" t="n"/>
-      <c r="O11" s="356" t="n"/>
-      <c r="P11" s="356" t="n"/>
-      <c r="Q11" s="356" t="n"/>
-      <c r="R11" s="356" t="n"/>
-      <c r="S11" s="356" t="n"/>
-      <c r="T11" s="356" t="n"/>
-      <c r="U11" s="356" t="n"/>
-      <c r="V11" s="356" t="n"/>
-      <c r="W11" s="356" t="n"/>
-      <c r="X11" s="356" t="n"/>
-      <c r="Y11" s="356" t="n"/>
-      <c r="Z11" s="356" t="n"/>
-      <c r="AA11" s="356" t="n"/>
-      <c r="AB11" s="356" t="n"/>
-      <c r="AC11" s="356" t="n"/>
-      <c r="AD11" s="356" t="n"/>
-      <c r="AE11" s="356" t="n"/>
-      <c r="AF11" s="356" t="n"/>
-      <c r="AG11" s="356" t="n"/>
-      <c r="AH11" s="356" t="n"/>
-      <c r="AI11" s="356" t="n"/>
-      <c r="AJ11" s="356" t="n"/>
-      <c r="AK11" s="356" t="n"/>
-      <c r="AL11" s="356" t="n"/>
-      <c r="AM11" s="356" t="n"/>
-      <c r="AN11" s="535" t="n"/>
+      <c r="B15" s="424" t="n"/>
+      <c r="C15" s="647" t="n"/>
+      <c r="D15" s="423" t="n"/>
+      <c r="E15" s="423" t="n"/>
+      <c r="F15" s="423" t="n"/>
+      <c r="G15" s="423" t="n"/>
+      <c r="H15" s="423" t="n"/>
+      <c r="I15" s="423" t="n"/>
+      <c r="J15" s="423" t="n"/>
+      <c r="K15" s="423" t="n"/>
+      <c r="L15" s="423" t="n"/>
+      <c r="M15" s="423" t="n"/>
+      <c r="N15" s="423" t="n"/>
+      <c r="O15" s="423" t="n"/>
+      <c r="P15" s="424" t="n"/>
+      <c r="Q15" s="647" t="n"/>
+      <c r="R15" s="423" t="n"/>
+      <c r="S15" s="423" t="n"/>
+      <c r="T15" s="423" t="n"/>
+      <c r="U15" s="423" t="n"/>
+      <c r="V15" s="423" t="n"/>
+      <c r="W15" s="423" t="n"/>
+      <c r="X15" s="423" t="n"/>
+      <c r="Y15" s="423" t="n"/>
+      <c r="Z15" s="423" t="n"/>
+      <c r="AA15" s="423" t="n"/>
+      <c r="AB15" s="423" t="n"/>
+      <c r="AC15" s="423" t="n"/>
+      <c r="AD15" s="423" t="n"/>
+      <c r="AE15" s="423" t="n"/>
+      <c r="AF15" s="423" t="n"/>
+      <c r="AG15" s="424" t="n"/>
+      <c r="AH15" s="647" t="n"/>
+      <c r="AI15" s="423" t="n"/>
+      <c r="AJ15" s="423" t="n"/>
+      <c r="AK15" s="423" t="n"/>
+      <c r="AL15" s="423" t="n"/>
+      <c r="AM15" s="423" t="n"/>
+      <c r="AN15" s="424" t="n"/>
+      <c r="AO15" s="647" t="n"/>
+      <c r="AP15" s="423" t="n"/>
+      <c r="AQ15" s="423" t="n"/>
+      <c r="AR15" s="423" t="n"/>
+      <c r="AS15" s="423" t="n"/>
+      <c r="AT15" s="423" t="n"/>
+      <c r="AU15" s="424" t="n"/>
+      <c r="AV15" s="647" t="n"/>
+      <c r="AW15" s="423" t="n"/>
+      <c r="AX15" s="423" t="n"/>
+      <c r="AY15" s="424" t="n"/>
+      <c r="AZ15" s="648" t="n"/>
+      <c r="BA15" s="423" t="n"/>
+      <c r="BB15" s="423" t="n"/>
+      <c r="BC15" s="423" t="n"/>
+      <c r="BD15" s="649" t="n"/>
     </row>
-    <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="532">
-        <f>ROW()-ROW($A$5)+1</f>
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" s="673">
+        <f>ROW()-ROW($A$9)+1</f>
         <v/>
       </c>
-      <c r="B12" s="533" t="n"/>
-      <c r="C12" s="534" t="n"/>
-      <c r="D12" s="534" t="n"/>
-      <c r="E12" s="534" t="n"/>
-      <c r="F12" s="534" t="n"/>
-      <c r="G12" s="534" t="n"/>
-      <c r="H12" s="534" t="n"/>
-      <c r="I12" s="356" t="n"/>
-      <c r="J12" s="356" t="n"/>
-      <c r="K12" s="356" t="n"/>
-      <c r="L12" s="356" t="n"/>
-      <c r="M12" s="356" t="n"/>
-      <c r="N12" s="356" t="n"/>
-      <c r="O12" s="356" t="n"/>
-      <c r="P12" s="356" t="n"/>
-      <c r="Q12" s="356" t="n"/>
-      <c r="R12" s="356" t="n"/>
-      <c r="S12" s="356" t="n"/>
-      <c r="T12" s="356" t="n"/>
-      <c r="U12" s="356" t="n"/>
-      <c r="V12" s="356" t="n"/>
-      <c r="W12" s="356" t="n"/>
-      <c r="X12" s="356" t="n"/>
-      <c r="Y12" s="356" t="n"/>
-      <c r="Z12" s="356" t="n"/>
-      <c r="AA12" s="356" t="n"/>
-      <c r="AB12" s="356" t="n"/>
-      <c r="AC12" s="356" t="n"/>
-      <c r="AD12" s="356" t="n"/>
-      <c r="AE12" s="356" t="n"/>
-      <c r="AF12" s="356" t="n"/>
-      <c r="AG12" s="356" t="n"/>
-      <c r="AH12" s="356" t="n"/>
-      <c r="AI12" s="356" t="n"/>
-      <c r="AJ12" s="356" t="n"/>
-      <c r="AK12" s="356" t="n"/>
-      <c r="AL12" s="356" t="n"/>
-      <c r="AM12" s="356" t="n"/>
-      <c r="AN12" s="535" t="n"/>
+      <c r="B16" s="567" t="n"/>
+      <c r="C16" s="657" t="n"/>
+      <c r="D16" s="566" t="n"/>
+      <c r="E16" s="566" t="n"/>
+      <c r="F16" s="566" t="n"/>
+      <c r="G16" s="566" t="n"/>
+      <c r="H16" s="566" t="n"/>
+      <c r="I16" s="566" t="n"/>
+      <c r="J16" s="566" t="n"/>
+      <c r="K16" s="566" t="n"/>
+      <c r="L16" s="566" t="n"/>
+      <c r="M16" s="566" t="n"/>
+      <c r="N16" s="566" t="n"/>
+      <c r="O16" s="566" t="n"/>
+      <c r="P16" s="567" t="n"/>
+      <c r="Q16" s="657" t="n"/>
+      <c r="R16" s="566" t="n"/>
+      <c r="S16" s="566" t="n"/>
+      <c r="T16" s="566" t="n"/>
+      <c r="U16" s="566" t="n"/>
+      <c r="V16" s="566" t="n"/>
+      <c r="W16" s="566" t="n"/>
+      <c r="X16" s="566" t="n"/>
+      <c r="Y16" s="566" t="n"/>
+      <c r="Z16" s="566" t="n"/>
+      <c r="AA16" s="566" t="n"/>
+      <c r="AB16" s="566" t="n"/>
+      <c r="AC16" s="566" t="n"/>
+      <c r="AD16" s="566" t="n"/>
+      <c r="AE16" s="566" t="n"/>
+      <c r="AF16" s="566" t="n"/>
+      <c r="AG16" s="567" t="n"/>
+      <c r="AH16" s="657" t="n"/>
+      <c r="AI16" s="566" t="n"/>
+      <c r="AJ16" s="566" t="n"/>
+      <c r="AK16" s="566" t="n"/>
+      <c r="AL16" s="566" t="n"/>
+      <c r="AM16" s="566" t="n"/>
+      <c r="AN16" s="567" t="n"/>
+      <c r="AO16" s="657" t="n"/>
+      <c r="AP16" s="566" t="n"/>
+      <c r="AQ16" s="566" t="n"/>
+      <c r="AR16" s="566" t="n"/>
+      <c r="AS16" s="566" t="n"/>
+      <c r="AT16" s="566" t="n"/>
+      <c r="AU16" s="567" t="n"/>
+      <c r="AV16" s="657" t="n"/>
+      <c r="AW16" s="566" t="n"/>
+      <c r="AX16" s="566" t="n"/>
+      <c r="AY16" s="567" t="n"/>
+      <c r="AZ16" s="658" t="n"/>
+      <c r="BA16" s="566" t="n"/>
+      <c r="BB16" s="566" t="n"/>
+      <c r="BC16" s="566" t="n"/>
+      <c r="BD16" s="569" t="n"/>
     </row>
-    <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="532">
-        <f>ROW()-ROW($A$5)+1</f>
-        <v/>
-      </c>
-      <c r="B13" s="533" t="n"/>
-      <c r="C13" s="534" t="n"/>
-      <c r="D13" s="534" t="n"/>
-      <c r="E13" s="534" t="n"/>
-      <c r="F13" s="534" t="n"/>
-      <c r="G13" s="534" t="n"/>
-      <c r="H13" s="534" t="n"/>
-      <c r="I13" s="356" t="n"/>
-      <c r="J13" s="356" t="n"/>
-      <c r="K13" s="356" t="n"/>
-      <c r="L13" s="356" t="n"/>
-      <c r="M13" s="356" t="n"/>
-      <c r="N13" s="356" t="n"/>
-      <c r="O13" s="356" t="n"/>
-      <c r="P13" s="356" t="n"/>
-      <c r="Q13" s="356" t="n"/>
-      <c r="R13" s="356" t="n"/>
-      <c r="S13" s="356" t="n"/>
-      <c r="T13" s="356" t="n"/>
-      <c r="U13" s="356" t="n"/>
-      <c r="V13" s="356" t="n"/>
-      <c r="W13" s="356" t="n"/>
-      <c r="X13" s="356" t="n"/>
-      <c r="Y13" s="356" t="n"/>
-      <c r="Z13" s="356" t="n"/>
-      <c r="AA13" s="356" t="n"/>
-      <c r="AB13" s="356" t="n"/>
-      <c r="AC13" s="356" t="n"/>
-      <c r="AD13" s="356" t="n"/>
-      <c r="AE13" s="356" t="n"/>
-      <c r="AF13" s="356" t="n"/>
-      <c r="AG13" s="356" t="n"/>
-      <c r="AH13" s="356" t="n"/>
-      <c r="AI13" s="356" t="n"/>
-      <c r="AJ13" s="356" t="n"/>
-      <c r="AK13" s="356" t="n"/>
-      <c r="AL13" s="356" t="n"/>
-      <c r="AM13" s="356" t="n"/>
-      <c r="AN13" s="535" t="n"/>
+    <row r="17" ht="20" customHeight="1">
+      <c r="A17" s="667" t="n"/>
+      <c r="B17" s="667" t="n"/>
+      <c r="C17" s="667" t="n"/>
+      <c r="D17" s="667" t="n"/>
+      <c r="E17" s="667" t="n"/>
+      <c r="F17" s="667" t="n"/>
+      <c r="G17" s="667" t="n"/>
+      <c r="H17" s="667" t="n"/>
+      <c r="I17" s="667" t="n"/>
+      <c r="J17" s="667" t="n"/>
+      <c r="K17" s="667" t="n"/>
+      <c r="L17" s="667" t="n"/>
+      <c r="M17" s="667" t="n"/>
+      <c r="N17" s="667" t="n"/>
+      <c r="O17" s="667" t="n"/>
+      <c r="P17" s="667" t="n"/>
+      <c r="Q17" s="667" t="n"/>
+      <c r="R17" s="667" t="n"/>
+      <c r="S17" s="667" t="n"/>
+      <c r="T17" s="667" t="n"/>
+      <c r="U17" s="667" t="n"/>
+      <c r="V17" s="667" t="n"/>
+      <c r="W17" s="667" t="n"/>
+      <c r="X17" s="667" t="n"/>
+      <c r="Y17" s="667" t="n"/>
+      <c r="Z17" s="667" t="n"/>
+      <c r="AA17" s="667" t="n"/>
+      <c r="AB17" s="667" t="n"/>
+      <c r="AC17" s="667" t="n"/>
+      <c r="AD17" s="667" t="n"/>
+      <c r="AE17" s="667" t="n"/>
+      <c r="AF17" s="667" t="n"/>
+      <c r="AG17" s="667" t="n"/>
+      <c r="AH17" s="667" t="n"/>
+      <c r="AI17" s="667" t="n"/>
+      <c r="AJ17" s="667" t="n"/>
+      <c r="AK17" s="667" t="n"/>
+      <c r="AL17" s="667" t="n"/>
+      <c r="AM17" s="667" t="n"/>
+      <c r="AN17" s="667" t="n"/>
+      <c r="AO17" s="667" t="n"/>
+      <c r="AP17" s="667" t="n"/>
+      <c r="AQ17" s="667" t="n"/>
+      <c r="AR17" s="667" t="n"/>
+      <c r="AS17" s="667" t="n"/>
+      <c r="AT17" s="667" t="n"/>
+      <c r="AU17" s="667" t="n"/>
+      <c r="AV17" s="667" t="n"/>
+      <c r="AW17" s="667" t="n"/>
+      <c r="AX17" s="667" t="n"/>
+      <c r="AY17" s="667" t="n"/>
+      <c r="AZ17" s="667" t="n"/>
+      <c r="BA17" s="667" t="n"/>
+      <c r="BB17" s="667" t="n"/>
+      <c r="BC17" s="667" t="n"/>
+      <c r="BD17" s="667" t="n"/>
     </row>
-    <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="536">
-        <f>ROW()-ROW($A$5)+1</f>
-        <v/>
-      </c>
-      <c r="B14" s="537" t="n"/>
-      <c r="C14" s="538" t="n"/>
-      <c r="D14" s="538" t="n"/>
-      <c r="E14" s="538" t="n"/>
-      <c r="F14" s="538" t="n"/>
-      <c r="G14" s="538" t="n"/>
-      <c r="H14" s="538" t="n"/>
-      <c r="I14" s="539" t="n"/>
-      <c r="J14" s="539" t="n"/>
-      <c r="K14" s="539" t="n"/>
-      <c r="L14" s="539" t="n"/>
-      <c r="M14" s="539" t="n"/>
-      <c r="N14" s="539" t="n"/>
-      <c r="O14" s="539" t="n"/>
-      <c r="P14" s="539" t="n"/>
-      <c r="Q14" s="539" t="n"/>
-      <c r="R14" s="539" t="n"/>
-      <c r="S14" s="539" t="n"/>
-      <c r="T14" s="539" t="n"/>
-      <c r="U14" s="539" t="n"/>
-      <c r="V14" s="539" t="n"/>
-      <c r="W14" s="539" t="n"/>
-      <c r="X14" s="539" t="n"/>
-      <c r="Y14" s="539" t="n"/>
-      <c r="Z14" s="539" t="n"/>
-      <c r="AA14" s="539" t="n"/>
-      <c r="AB14" s="539" t="n"/>
-      <c r="AC14" s="539" t="n"/>
-      <c r="AD14" s="539" t="n"/>
-      <c r="AE14" s="539" t="n"/>
-      <c r="AF14" s="539" t="n"/>
-      <c r="AG14" s="539" t="n"/>
-      <c r="AH14" s="539" t="n"/>
-      <c r="AI14" s="539" t="n"/>
-      <c r="AJ14" s="539" t="n"/>
-      <c r="AK14" s="539" t="n"/>
-      <c r="AL14" s="539" t="n"/>
-      <c r="AM14" s="539" t="n"/>
-      <c r="AN14" s="540" t="n"/>
+    <row r="18" ht="20" customHeight="1">
+      <c r="A18" s="667" t="n"/>
+      <c r="B18" s="667" t="n"/>
+      <c r="C18" s="667" t="n"/>
+      <c r="D18" s="667" t="n"/>
+      <c r="E18" s="667" t="n"/>
+      <c r="F18" s="667" t="n"/>
+      <c r="G18" s="667" t="n"/>
+      <c r="H18" s="667" t="n"/>
+      <c r="I18" s="667" t="n"/>
+      <c r="J18" s="667" t="n"/>
+      <c r="K18" s="667" t="n"/>
+      <c r="L18" s="667" t="n"/>
+      <c r="M18" s="667" t="n"/>
+      <c r="N18" s="667" t="n"/>
+      <c r="O18" s="667" t="n"/>
+      <c r="P18" s="667" t="n"/>
+      <c r="Q18" s="667" t="n"/>
+      <c r="R18" s="667" t="n"/>
+      <c r="S18" s="667" t="n"/>
+      <c r="T18" s="667" t="n"/>
+      <c r="U18" s="667" t="n"/>
+      <c r="V18" s="667" t="n"/>
+      <c r="W18" s="667" t="n"/>
+      <c r="X18" s="667" t="n"/>
+      <c r="Y18" s="667" t="n"/>
+      <c r="Z18" s="667" t="n"/>
+      <c r="AA18" s="667" t="n"/>
+      <c r="AB18" s="667" t="n"/>
+      <c r="AC18" s="667" t="n"/>
+      <c r="AD18" s="667" t="n"/>
+      <c r="AE18" s="667" t="n"/>
+      <c r="AF18" s="667" t="n"/>
+      <c r="AG18" s="667" t="n"/>
+      <c r="AH18" s="667" t="n"/>
+      <c r="AI18" s="667" t="n"/>
+      <c r="AJ18" s="667" t="n"/>
+      <c r="AK18" s="667" t="n"/>
+      <c r="AL18" s="667" t="n"/>
+      <c r="AM18" s="667" t="n"/>
+      <c r="AN18" s="667" t="n"/>
+      <c r="AO18" s="667" t="n"/>
+      <c r="AP18" s="667" t="n"/>
+      <c r="AQ18" s="667" t="n"/>
+      <c r="AR18" s="667" t="n"/>
+      <c r="AS18" s="667" t="n"/>
+      <c r="AT18" s="667" t="n"/>
+      <c r="AU18" s="667" t="n"/>
+      <c r="AV18" s="667" t="n"/>
+      <c r="AW18" s="667" t="n"/>
+      <c r="AX18" s="667" t="n"/>
+      <c r="AY18" s="667" t="n"/>
+      <c r="AZ18" s="667" t="n"/>
+      <c r="BA18" s="667" t="n"/>
+      <c r="BB18" s="667" t="n"/>
+      <c r="BC18" s="667" t="n"/>
+      <c r="BD18" s="667" t="n"/>
     </row>
-    <row r="15" ht="20" customHeight="1"/>
-    <row r="16" ht="20" customHeight="1"/>
-    <row r="17" ht="20" customHeight="1"/>
-    <row r="18" ht="20" customHeight="1"/>
-    <row r="19" ht="20" customHeight="1"/>
-    <row r="20" ht="20" customHeight="1"/>
-    <row r="21" ht="20" customHeight="1"/>
-    <row r="22" ht="20" customHeight="1"/>
-    <row r="23" ht="20" customHeight="1"/>
-    <row r="24" ht="20" customHeight="1"/>
-    <row r="25" ht="20" customHeight="1"/>
-    <row r="26" ht="20" customHeight="1"/>
-    <row r="27" ht="20" customHeight="1"/>
-    <row r="28" ht="20" customHeight="1"/>
-    <row r="29" ht="20" customHeight="1"/>
-    <row r="30" ht="20" customHeight="1"/>
-    <row r="31" ht="20" customHeight="1"/>
-    <row r="32" ht="20" customHeight="1"/>
-    <row r="33" ht="20" customHeight="1"/>
-    <row r="34" ht="20" customHeight="1"/>
-    <row r="35" ht="20" customHeight="1"/>
-    <row r="36" ht="20" customHeight="1"/>
-    <row r="37" ht="20" customHeight="1"/>
-    <row r="38" ht="20" customHeight="1"/>
-    <row r="39" ht="20" customHeight="1"/>
-    <row r="40" ht="20" customHeight="1"/>
+    <row r="19" ht="20" customHeight="1">
+      <c r="A19" s="667" t="n"/>
+      <c r="B19" s="667" t="n"/>
+      <c r="C19" s="667" t="n"/>
+      <c r="D19" s="667" t="n"/>
+      <c r="E19" s="667" t="n"/>
+      <c r="F19" s="667" t="n"/>
+      <c r="G19" s="667" t="n"/>
+      <c r="H19" s="667" t="n"/>
+      <c r="I19" s="667" t="n"/>
+      <c r="J19" s="667" t="n"/>
+      <c r="K19" s="667" t="n"/>
+      <c r="L19" s="667" t="n"/>
+      <c r="M19" s="667" t="n"/>
+      <c r="N19" s="667" t="n"/>
+      <c r="O19" s="667" t="n"/>
+      <c r="P19" s="667" t="n"/>
+      <c r="Q19" s="667" t="n"/>
+      <c r="R19" s="667" t="n"/>
+      <c r="S19" s="667" t="n"/>
+      <c r="T19" s="667" t="n"/>
+      <c r="U19" s="667" t="n"/>
+      <c r="V19" s="667" t="n"/>
+      <c r="W19" s="667" t="n"/>
+      <c r="X19" s="667" t="n"/>
+      <c r="Y19" s="667" t="n"/>
+      <c r="Z19" s="667" t="n"/>
+      <c r="AA19" s="667" t="n"/>
+      <c r="AB19" s="667" t="n"/>
+      <c r="AC19" s="667" t="n"/>
+      <c r="AD19" s="667" t="n"/>
+      <c r="AE19" s="667" t="n"/>
+      <c r="AF19" s="667" t="n"/>
+      <c r="AG19" s="667" t="n"/>
+      <c r="AH19" s="667" t="n"/>
+      <c r="AI19" s="667" t="n"/>
+      <c r="AJ19" s="667" t="n"/>
+      <c r="AK19" s="667" t="n"/>
+      <c r="AL19" s="667" t="n"/>
+      <c r="AM19" s="667" t="n"/>
+      <c r="AN19" s="667" t="n"/>
+      <c r="AO19" s="667" t="n"/>
+      <c r="AP19" s="667" t="n"/>
+      <c r="AQ19" s="667" t="n"/>
+      <c r="AR19" s="667" t="n"/>
+      <c r="AS19" s="667" t="n"/>
+      <c r="AT19" s="667" t="n"/>
+      <c r="AU19" s="667" t="n"/>
+      <c r="AV19" s="667" t="n"/>
+      <c r="AW19" s="667" t="n"/>
+      <c r="AX19" s="667" t="n"/>
+      <c r="AY19" s="667" t="n"/>
+      <c r="AZ19" s="667" t="n"/>
+      <c r="BA19" s="667" t="n"/>
+      <c r="BB19" s="667" t="n"/>
+      <c r="BC19" s="667" t="n"/>
+      <c r="BD19" s="667" t="n"/>
+    </row>
+    <row r="20" ht="20" customHeight="1">
+      <c r="A20" s="667" t="n"/>
+      <c r="B20" s="667" t="n"/>
+      <c r="C20" s="667" t="n"/>
+      <c r="D20" s="667" t="n"/>
+      <c r="E20" s="667" t="n"/>
+      <c r="F20" s="667" t="n"/>
+      <c r="G20" s="667" t="n"/>
+      <c r="H20" s="667" t="n"/>
+      <c r="I20" s="667" t="n"/>
+      <c r="J20" s="667" t="n"/>
+      <c r="K20" s="667" t="n"/>
+      <c r="L20" s="667" t="n"/>
+      <c r="M20" s="667" t="n"/>
+      <c r="N20" s="667" t="n"/>
+      <c r="O20" s="667" t="n"/>
+      <c r="P20" s="667" t="n"/>
+      <c r="Q20" s="667" t="n"/>
+      <c r="R20" s="667" t="n"/>
+      <c r="S20" s="667" t="n"/>
+      <c r="T20" s="667" t="n"/>
+      <c r="U20" s="667" t="n"/>
+      <c r="V20" s="667" t="n"/>
+      <c r="W20" s="667" t="n"/>
+      <c r="X20" s="667" t="n"/>
+      <c r="Y20" s="667" t="n"/>
+      <c r="Z20" s="667" t="n"/>
+      <c r="AA20" s="667" t="n"/>
+      <c r="AB20" s="667" t="n"/>
+      <c r="AC20" s="667" t="n"/>
+      <c r="AD20" s="667" t="n"/>
+      <c r="AE20" s="667" t="n"/>
+      <c r="AF20" s="667" t="n"/>
+      <c r="AG20" s="667" t="n"/>
+      <c r="AH20" s="667" t="n"/>
+      <c r="AI20" s="667" t="n"/>
+      <c r="AJ20" s="667" t="n"/>
+      <c r="AK20" s="667" t="n"/>
+      <c r="AL20" s="667" t="n"/>
+      <c r="AM20" s="667" t="n"/>
+      <c r="AN20" s="667" t="n"/>
+      <c r="AO20" s="667" t="n"/>
+      <c r="AP20" s="667" t="n"/>
+      <c r="AQ20" s="667" t="n"/>
+      <c r="AR20" s="667" t="n"/>
+      <c r="AS20" s="667" t="n"/>
+      <c r="AT20" s="667" t="n"/>
+      <c r="AU20" s="667" t="n"/>
+      <c r="AV20" s="667" t="n"/>
+      <c r="AW20" s="667" t="n"/>
+      <c r="AX20" s="667" t="n"/>
+      <c r="AY20" s="667" t="n"/>
+      <c r="AZ20" s="667" t="n"/>
+      <c r="BA20" s="667" t="n"/>
+      <c r="BB20" s="667" t="n"/>
+      <c r="BC20" s="667" t="n"/>
+      <c r="BD20" s="667" t="n"/>
+    </row>
+    <row r="21" ht="20" customHeight="1">
+      <c r="A21" s="667" t="n"/>
+      <c r="B21" s="667" t="n"/>
+      <c r="C21" s="667" t="n"/>
+      <c r="D21" s="667" t="n"/>
+      <c r="E21" s="667" t="n"/>
+      <c r="F21" s="667" t="n"/>
+      <c r="G21" s="667" t="n"/>
+      <c r="H21" s="667" t="n"/>
+      <c r="I21" s="667" t="n"/>
+      <c r="J21" s="667" t="n"/>
+      <c r="K21" s="667" t="n"/>
+      <c r="L21" s="667" t="n"/>
+      <c r="M21" s="667" t="n"/>
+      <c r="N21" s="667" t="n"/>
+      <c r="O21" s="667" t="n"/>
+      <c r="P21" s="667" t="n"/>
+      <c r="Q21" s="667" t="n"/>
+      <c r="R21" s="667" t="n"/>
+      <c r="S21" s="667" t="n"/>
+      <c r="T21" s="667" t="n"/>
+      <c r="U21" s="667" t="n"/>
+      <c r="V21" s="667" t="n"/>
+      <c r="W21" s="667" t="n"/>
+      <c r="X21" s="667" t="n"/>
+      <c r="Y21" s="667" t="n"/>
+      <c r="Z21" s="667" t="n"/>
+      <c r="AA21" s="667" t="n"/>
+      <c r="AB21" s="667" t="n"/>
+      <c r="AC21" s="667" t="n"/>
+      <c r="AD21" s="667" t="n"/>
+      <c r="AE21" s="667" t="n"/>
+      <c r="AF21" s="667" t="n"/>
+      <c r="AG21" s="667" t="n"/>
+      <c r="AH21" s="667" t="n"/>
+      <c r="AI21" s="667" t="n"/>
+      <c r="AJ21" s="667" t="n"/>
+      <c r="AK21" s="667" t="n"/>
+      <c r="AL21" s="667" t="n"/>
+      <c r="AM21" s="667" t="n"/>
+      <c r="AN21" s="667" t="n"/>
+      <c r="AO21" s="667" t="n"/>
+      <c r="AP21" s="667" t="n"/>
+      <c r="AQ21" s="667" t="n"/>
+      <c r="AR21" s="667" t="n"/>
+      <c r="AS21" s="667" t="n"/>
+      <c r="AT21" s="667" t="n"/>
+      <c r="AU21" s="667" t="n"/>
+      <c r="AV21" s="667" t="n"/>
+      <c r="AW21" s="667" t="n"/>
+      <c r="AX21" s="667" t="n"/>
+      <c r="AY21" s="667" t="n"/>
+      <c r="AZ21" s="667" t="n"/>
+      <c r="BA21" s="667" t="n"/>
+      <c r="BB21" s="667" t="n"/>
+      <c r="BC21" s="667" t="n"/>
+      <c r="BD21" s="667" t="n"/>
+    </row>
+    <row r="22" ht="20" customHeight="1">
+      <c r="A22" s="667" t="n"/>
+      <c r="B22" s="667" t="n"/>
+      <c r="C22" s="667" t="n"/>
+      <c r="D22" s="667" t="n"/>
+      <c r="E22" s="667" t="n"/>
+      <c r="F22" s="667" t="n"/>
+      <c r="G22" s="667" t="n"/>
+      <c r="H22" s="667" t="n"/>
+      <c r="I22" s="667" t="n"/>
+      <c r="J22" s="667" t="n"/>
+      <c r="K22" s="667" t="n"/>
+      <c r="L22" s="667" t="n"/>
+      <c r="M22" s="667" t="n"/>
+      <c r="N22" s="667" t="n"/>
+      <c r="O22" s="667" t="n"/>
+      <c r="P22" s="667" t="n"/>
+      <c r="Q22" s="667" t="n"/>
+      <c r="R22" s="667" t="n"/>
+      <c r="S22" s="667" t="n"/>
+      <c r="T22" s="667" t="n"/>
+      <c r="U22" s="667" t="n"/>
+      <c r="V22" s="667" t="n"/>
+      <c r="W22" s="667" t="n"/>
+      <c r="X22" s="667" t="n"/>
+      <c r="Y22" s="667" t="n"/>
+      <c r="Z22" s="667" t="n"/>
+      <c r="AA22" s="667" t="n"/>
+      <c r="AB22" s="667" t="n"/>
+      <c r="AC22" s="667" t="n"/>
+      <c r="AD22" s="667" t="n"/>
+      <c r="AE22" s="667" t="n"/>
+      <c r="AF22" s="667" t="n"/>
+      <c r="AG22" s="667" t="n"/>
+      <c r="AH22" s="667" t="n"/>
+      <c r="AI22" s="667" t="n"/>
+      <c r="AJ22" s="667" t="n"/>
+      <c r="AK22" s="667" t="n"/>
+      <c r="AL22" s="667" t="n"/>
+      <c r="AM22" s="667" t="n"/>
+      <c r="AN22" s="667" t="n"/>
+      <c r="AO22" s="667" t="n"/>
+      <c r="AP22" s="667" t="n"/>
+      <c r="AQ22" s="667" t="n"/>
+      <c r="AR22" s="667" t="n"/>
+      <c r="AS22" s="667" t="n"/>
+      <c r="AT22" s="667" t="n"/>
+      <c r="AU22" s="667" t="n"/>
+      <c r="AV22" s="667" t="n"/>
+      <c r="AW22" s="667" t="n"/>
+      <c r="AX22" s="667" t="n"/>
+      <c r="AY22" s="667" t="n"/>
+      <c r="AZ22" s="667" t="n"/>
+      <c r="BA22" s="667" t="n"/>
+      <c r="BB22" s="667" t="n"/>
+      <c r="BC22" s="667" t="n"/>
+      <c r="BD22" s="667" t="n"/>
+    </row>
+    <row r="23" ht="20" customHeight="1">
+      <c r="A23" s="667" t="n"/>
+      <c r="B23" s="667" t="n"/>
+      <c r="C23" s="667" t="n"/>
+      <c r="D23" s="667" t="n"/>
+      <c r="E23" s="667" t="n"/>
+      <c r="F23" s="667" t="n"/>
+      <c r="G23" s="667" t="n"/>
+      <c r="H23" s="667" t="n"/>
+      <c r="I23" s="667" t="n"/>
+      <c r="J23" s="667" t="n"/>
+      <c r="K23" s="667" t="n"/>
+      <c r="L23" s="667" t="n"/>
+      <c r="M23" s="667" t="n"/>
+      <c r="N23" s="667" t="n"/>
+      <c r="O23" s="667" t="n"/>
+      <c r="P23" s="667" t="n"/>
+      <c r="Q23" s="667" t="n"/>
+      <c r="R23" s="667" t="n"/>
+      <c r="S23" s="667" t="n"/>
+      <c r="T23" s="667" t="n"/>
+      <c r="U23" s="667" t="n"/>
+      <c r="V23" s="667" t="n"/>
+      <c r="W23" s="667" t="n"/>
+      <c r="X23" s="667" t="n"/>
+      <c r="Y23" s="667" t="n"/>
+      <c r="Z23" s="667" t="n"/>
+      <c r="AA23" s="667" t="n"/>
+      <c r="AB23" s="667" t="n"/>
+      <c r="AC23" s="667" t="n"/>
+      <c r="AD23" s="667" t="n"/>
+      <c r="AE23" s="667" t="n"/>
+      <c r="AF23" s="667" t="n"/>
+      <c r="AG23" s="667" t="n"/>
+      <c r="AH23" s="667" t="n"/>
+      <c r="AI23" s="667" t="n"/>
+      <c r="AJ23" s="667" t="n"/>
+      <c r="AK23" s="667" t="n"/>
+      <c r="AL23" s="667" t="n"/>
+      <c r="AM23" s="667" t="n"/>
+      <c r="AN23" s="667" t="n"/>
+      <c r="AO23" s="667" t="n"/>
+      <c r="AP23" s="667" t="n"/>
+      <c r="AQ23" s="667" t="n"/>
+      <c r="AR23" s="667" t="n"/>
+      <c r="AS23" s="667" t="n"/>
+      <c r="AT23" s="667" t="n"/>
+      <c r="AU23" s="667" t="n"/>
+      <c r="AV23" s="667" t="n"/>
+      <c r="AW23" s="667" t="n"/>
+      <c r="AX23" s="667" t="n"/>
+      <c r="AY23" s="667" t="n"/>
+      <c r="AZ23" s="667" t="n"/>
+      <c r="BA23" s="667" t="n"/>
+      <c r="BB23" s="667" t="n"/>
+      <c r="BC23" s="667" t="n"/>
+      <c r="BD23" s="667" t="n"/>
+    </row>
+    <row r="24" ht="20" customHeight="1">
+      <c r="A24" s="667" t="n"/>
+      <c r="B24" s="667" t="n"/>
+      <c r="C24" s="667" t="n"/>
+      <c r="D24" s="667" t="n"/>
+      <c r="E24" s="667" t="n"/>
+      <c r="F24" s="667" t="n"/>
+      <c r="G24" s="667" t="n"/>
+      <c r="H24" s="667" t="n"/>
+      <c r="I24" s="667" t="n"/>
+      <c r="J24" s="667" t="n"/>
+      <c r="K24" s="667" t="n"/>
+      <c r="L24" s="667" t="n"/>
+      <c r="M24" s="667" t="n"/>
+      <c r="N24" s="667" t="n"/>
+      <c r="O24" s="667" t="n"/>
+      <c r="P24" s="667" t="n"/>
+      <c r="Q24" s="667" t="n"/>
+      <c r="R24" s="667" t="n"/>
+      <c r="S24" s="667" t="n"/>
+      <c r="T24" s="667" t="n"/>
+      <c r="U24" s="667" t="n"/>
+      <c r="V24" s="667" t="n"/>
+      <c r="W24" s="667" t="n"/>
+      <c r="X24" s="667" t="n"/>
+      <c r="Y24" s="667" t="n"/>
+      <c r="Z24" s="667" t="n"/>
+      <c r="AA24" s="667" t="n"/>
+      <c r="AB24" s="667" t="n"/>
+      <c r="AC24" s="667" t="n"/>
+      <c r="AD24" s="667" t="n"/>
+      <c r="AE24" s="667" t="n"/>
+      <c r="AF24" s="667" t="n"/>
+      <c r="AG24" s="667" t="n"/>
+      <c r="AH24" s="667" t="n"/>
+      <c r="AI24" s="667" t="n"/>
+      <c r="AJ24" s="667" t="n"/>
+      <c r="AK24" s="667" t="n"/>
+      <c r="AL24" s="667" t="n"/>
+      <c r="AM24" s="667" t="n"/>
+      <c r="AN24" s="667" t="n"/>
+      <c r="AO24" s="667" t="n"/>
+      <c r="AP24" s="667" t="n"/>
+      <c r="AQ24" s="667" t="n"/>
+      <c r="AR24" s="667" t="n"/>
+      <c r="AS24" s="667" t="n"/>
+      <c r="AT24" s="667" t="n"/>
+      <c r="AU24" s="667" t="n"/>
+      <c r="AV24" s="667" t="n"/>
+      <c r="AW24" s="667" t="n"/>
+      <c r="AX24" s="667" t="n"/>
+      <c r="AY24" s="667" t="n"/>
+      <c r="AZ24" s="667" t="n"/>
+      <c r="BA24" s="667" t="n"/>
+      <c r="BB24" s="667" t="n"/>
+      <c r="BC24" s="667" t="n"/>
+      <c r="BD24" s="667" t="n"/>
+    </row>
+    <row r="25" ht="20" customHeight="1">
+      <c r="A25" s="667" t="n"/>
+      <c r="B25" s="667" t="n"/>
+      <c r="C25" s="667" t="n"/>
+      <c r="D25" s="667" t="n"/>
+      <c r="E25" s="667" t="n"/>
+      <c r="F25" s="667" t="n"/>
+      <c r="G25" s="667" t="n"/>
+      <c r="H25" s="667" t="n"/>
+      <c r="I25" s="667" t="n"/>
+      <c r="J25" s="667" t="n"/>
+      <c r="K25" s="667" t="n"/>
+      <c r="L25" s="667" t="n"/>
+      <c r="M25" s="667" t="n"/>
+      <c r="N25" s="667" t="n"/>
+      <c r="O25" s="667" t="n"/>
+      <c r="P25" s="667" t="n"/>
+      <c r="Q25" s="667" t="n"/>
+      <c r="R25" s="667" t="n"/>
+      <c r="S25" s="667" t="n"/>
+      <c r="T25" s="667" t="n"/>
+      <c r="U25" s="667" t="n"/>
+      <c r="V25" s="667" t="n"/>
+      <c r="W25" s="667" t="n"/>
+      <c r="X25" s="667" t="n"/>
+      <c r="Y25" s="667" t="n"/>
+      <c r="Z25" s="667" t="n"/>
+      <c r="AA25" s="667" t="n"/>
+      <c r="AB25" s="667" t="n"/>
+      <c r="AC25" s="667" t="n"/>
+      <c r="AD25" s="667" t="n"/>
+      <c r="AE25" s="667" t="n"/>
+      <c r="AF25" s="667" t="n"/>
+      <c r="AG25" s="667" t="n"/>
+      <c r="AH25" s="667" t="n"/>
+      <c r="AI25" s="667" t="n"/>
+      <c r="AJ25" s="667" t="n"/>
+      <c r="AK25" s="667" t="n"/>
+      <c r="AL25" s="667" t="n"/>
+      <c r="AM25" s="667" t="n"/>
+      <c r="AN25" s="667" t="n"/>
+      <c r="AO25" s="667" t="n"/>
+      <c r="AP25" s="667" t="n"/>
+      <c r="AQ25" s="667" t="n"/>
+      <c r="AR25" s="667" t="n"/>
+      <c r="AS25" s="667" t="n"/>
+      <c r="AT25" s="667" t="n"/>
+      <c r="AU25" s="667" t="n"/>
+      <c r="AV25" s="667" t="n"/>
+      <c r="AW25" s="667" t="n"/>
+      <c r="AX25" s="667" t="n"/>
+      <c r="AY25" s="667" t="n"/>
+      <c r="AZ25" s="667" t="n"/>
+      <c r="BA25" s="667" t="n"/>
+      <c r="BB25" s="667" t="n"/>
+      <c r="BC25" s="667" t="n"/>
+      <c r="BD25" s="667" t="n"/>
+    </row>
+    <row r="26" ht="20" customHeight="1">
+      <c r="A26" s="667" t="n"/>
+      <c r="B26" s="667" t="n"/>
+      <c r="C26" s="667" t="n"/>
+      <c r="D26" s="667" t="n"/>
+      <c r="E26" s="667" t="n"/>
+      <c r="F26" s="667" t="n"/>
+      <c r="G26" s="667" t="n"/>
+      <c r="H26" s="667" t="n"/>
+      <c r="I26" s="667" t="n"/>
+      <c r="J26" s="667" t="n"/>
+      <c r="K26" s="667" t="n"/>
+      <c r="L26" s="667" t="n"/>
+      <c r="M26" s="667" t="n"/>
+      <c r="N26" s="667" t="n"/>
+      <c r="O26" s="667" t="n"/>
+      <c r="P26" s="667" t="n"/>
+      <c r="Q26" s="667" t="n"/>
+      <c r="R26" s="667" t="n"/>
+      <c r="S26" s="667" t="n"/>
+      <c r="T26" s="667" t="n"/>
+      <c r="U26" s="667" t="n"/>
+      <c r="V26" s="667" t="n"/>
+      <c r="W26" s="667" t="n"/>
+      <c r="X26" s="667" t="n"/>
+      <c r="Y26" s="667" t="n"/>
+      <c r="Z26" s="667" t="n"/>
+      <c r="AA26" s="667" t="n"/>
+      <c r="AB26" s="667" t="n"/>
+      <c r="AC26" s="667" t="n"/>
+      <c r="AD26" s="667" t="n"/>
+      <c r="AE26" s="667" t="n"/>
+      <c r="AF26" s="667" t="n"/>
+      <c r="AG26" s="667" t="n"/>
+      <c r="AH26" s="667" t="n"/>
+      <c r="AI26" s="667" t="n"/>
+      <c r="AJ26" s="667" t="n"/>
+      <c r="AK26" s="667" t="n"/>
+      <c r="AL26" s="667" t="n"/>
+      <c r="AM26" s="667" t="n"/>
+      <c r="AN26" s="667" t="n"/>
+      <c r="AO26" s="667" t="n"/>
+      <c r="AP26" s="667" t="n"/>
+      <c r="AQ26" s="667" t="n"/>
+      <c r="AR26" s="667" t="n"/>
+      <c r="AS26" s="667" t="n"/>
+      <c r="AT26" s="667" t="n"/>
+      <c r="AU26" s="667" t="n"/>
+      <c r="AV26" s="667" t="n"/>
+      <c r="AW26" s="667" t="n"/>
+      <c r="AX26" s="667" t="n"/>
+      <c r="AY26" s="667" t="n"/>
+      <c r="AZ26" s="667" t="n"/>
+      <c r="BA26" s="667" t="n"/>
+      <c r="BB26" s="667" t="n"/>
+      <c r="BC26" s="667" t="n"/>
+      <c r="BD26" s="667" t="n"/>
+    </row>
+    <row r="27" ht="20" customHeight="1">
+      <c r="A27" s="667" t="n"/>
+      <c r="B27" s="667" t="n"/>
+      <c r="C27" s="667" t="n"/>
+      <c r="D27" s="667" t="n"/>
+      <c r="E27" s="667" t="n"/>
+      <c r="F27" s="667" t="n"/>
+      <c r="G27" s="667" t="n"/>
+      <c r="H27" s="667" t="n"/>
+      <c r="I27" s="667" t="n"/>
+      <c r="J27" s="667" t="n"/>
+      <c r="K27" s="667" t="n"/>
+      <c r="L27" s="667" t="n"/>
+      <c r="M27" s="667" t="n"/>
+      <c r="N27" s="667" t="n"/>
+      <c r="O27" s="667" t="n"/>
+      <c r="P27" s="667" t="n"/>
+      <c r="Q27" s="667" t="n"/>
+      <c r="R27" s="667" t="n"/>
+      <c r="S27" s="667" t="n"/>
+      <c r="T27" s="667" t="n"/>
+      <c r="U27" s="667" t="n"/>
+      <c r="V27" s="667" t="n"/>
+      <c r="W27" s="667" t="n"/>
+      <c r="X27" s="667" t="n"/>
+      <c r="Y27" s="667" t="n"/>
+      <c r="Z27" s="667" t="n"/>
+      <c r="AA27" s="667" t="n"/>
+      <c r="AB27" s="667" t="n"/>
+      <c r="AC27" s="667" t="n"/>
+      <c r="AD27" s="667" t="n"/>
+      <c r="AE27" s="667" t="n"/>
+      <c r="AF27" s="667" t="n"/>
+      <c r="AG27" s="667" t="n"/>
+      <c r="AH27" s="667" t="n"/>
+      <c r="AI27" s="667" t="n"/>
+      <c r="AJ27" s="667" t="n"/>
+      <c r="AK27" s="667" t="n"/>
+      <c r="AL27" s="667" t="n"/>
+      <c r="AM27" s="667" t="n"/>
+      <c r="AN27" s="667" t="n"/>
+      <c r="AO27" s="667" t="n"/>
+      <c r="AP27" s="667" t="n"/>
+      <c r="AQ27" s="667" t="n"/>
+      <c r="AR27" s="667" t="n"/>
+      <c r="AS27" s="667" t="n"/>
+      <c r="AT27" s="667" t="n"/>
+      <c r="AU27" s="667" t="n"/>
+      <c r="AV27" s="667" t="n"/>
+      <c r="AW27" s="667" t="n"/>
+      <c r="AX27" s="667" t="n"/>
+      <c r="AY27" s="667" t="n"/>
+      <c r="AZ27" s="667" t="n"/>
+      <c r="BA27" s="667" t="n"/>
+      <c r="BB27" s="667" t="n"/>
+      <c r="BC27" s="667" t="n"/>
+      <c r="BD27" s="667" t="n"/>
+    </row>
+    <row r="28" ht="20" customHeight="1">
+      <c r="A28" s="667" t="n"/>
+      <c r="B28" s="667" t="n"/>
+      <c r="C28" s="667" t="n"/>
+      <c r="D28" s="667" t="n"/>
+      <c r="E28" s="667" t="n"/>
+      <c r="F28" s="667" t="n"/>
+      <c r="G28" s="667" t="n"/>
+      <c r="H28" s="667" t="n"/>
+      <c r="I28" s="667" t="n"/>
+      <c r="J28" s="667" t="n"/>
+      <c r="K28" s="667" t="n"/>
+      <c r="L28" s="667" t="n"/>
+      <c r="M28" s="667" t="n"/>
+      <c r="N28" s="667" t="n"/>
+      <c r="O28" s="667" t="n"/>
+      <c r="P28" s="667" t="n"/>
+      <c r="Q28" s="667" t="n"/>
+      <c r="R28" s="667" t="n"/>
+      <c r="S28" s="667" t="n"/>
+      <c r="T28" s="667" t="n"/>
+      <c r="U28" s="667" t="n"/>
+      <c r="V28" s="667" t="n"/>
+      <c r="W28" s="667" t="n"/>
+      <c r="X28" s="667" t="n"/>
+      <c r="Y28" s="667" t="n"/>
+      <c r="Z28" s="667" t="n"/>
+      <c r="AA28" s="667" t="n"/>
+      <c r="AB28" s="667" t="n"/>
+      <c r="AC28" s="667" t="n"/>
+      <c r="AD28" s="667" t="n"/>
+      <c r="AE28" s="667" t="n"/>
+      <c r="AF28" s="667" t="n"/>
+      <c r="AG28" s="667" t="n"/>
+      <c r="AH28" s="667" t="n"/>
+      <c r="AI28" s="667" t="n"/>
+      <c r="AJ28" s="667" t="n"/>
+      <c r="AK28" s="667" t="n"/>
+      <c r="AL28" s="667" t="n"/>
+      <c r="AM28" s="667" t="n"/>
+      <c r="AN28" s="667" t="n"/>
+      <c r="AO28" s="667" t="n"/>
+      <c r="AP28" s="667" t="n"/>
+      <c r="AQ28" s="667" t="n"/>
+      <c r="AR28" s="667" t="n"/>
+      <c r="AS28" s="667" t="n"/>
+      <c r="AT28" s="667" t="n"/>
+      <c r="AU28" s="667" t="n"/>
+      <c r="AV28" s="667" t="n"/>
+      <c r="AW28" s="667" t="n"/>
+      <c r="AX28" s="667" t="n"/>
+      <c r="AY28" s="667" t="n"/>
+      <c r="AZ28" s="667" t="n"/>
+      <c r="BA28" s="667" t="n"/>
+      <c r="BB28" s="667" t="n"/>
+      <c r="BC28" s="667" t="n"/>
+      <c r="BD28" s="667" t="n"/>
+    </row>
+    <row r="29" ht="20" customHeight="1">
+      <c r="A29" s="667" t="n"/>
+      <c r="B29" s="667" t="n"/>
+      <c r="C29" s="667" t="n"/>
+      <c r="D29" s="667" t="n"/>
+      <c r="E29" s="667" t="n"/>
+      <c r="F29" s="667" t="n"/>
+      <c r="G29" s="667" t="n"/>
+      <c r="H29" s="667" t="n"/>
+      <c r="I29" s="667" t="n"/>
+      <c r="J29" s="667" t="n"/>
+      <c r="K29" s="667" t="n"/>
+      <c r="L29" s="667" t="n"/>
+      <c r="M29" s="667" t="n"/>
+      <c r="N29" s="667" t="n"/>
+      <c r="O29" s="667" t="n"/>
+      <c r="P29" s="667" t="n"/>
+      <c r="Q29" s="667" t="n"/>
+      <c r="R29" s="667" t="n"/>
+      <c r="S29" s="667" t="n"/>
+      <c r="T29" s="667" t="n"/>
+      <c r="U29" s="667" t="n"/>
+      <c r="V29" s="667" t="n"/>
+      <c r="W29" s="667" t="n"/>
+      <c r="X29" s="667" t="n"/>
+      <c r="Y29" s="667" t="n"/>
+      <c r="Z29" s="667" t="n"/>
+      <c r="AA29" s="667" t="n"/>
+      <c r="AB29" s="667" t="n"/>
+      <c r="AC29" s="667" t="n"/>
+      <c r="AD29" s="667" t="n"/>
+      <c r="AE29" s="667" t="n"/>
+      <c r="AF29" s="667" t="n"/>
+      <c r="AG29" s="667" t="n"/>
+      <c r="AH29" s="667" t="n"/>
+      <c r="AI29" s="667" t="n"/>
+      <c r="AJ29" s="667" t="n"/>
+      <c r="AK29" s="667" t="n"/>
+      <c r="AL29" s="667" t="n"/>
+      <c r="AM29" s="667" t="n"/>
+      <c r="AN29" s="667" t="n"/>
+      <c r="AO29" s="667" t="n"/>
+      <c r="AP29" s="667" t="n"/>
+      <c r="AQ29" s="667" t="n"/>
+      <c r="AR29" s="667" t="n"/>
+      <c r="AS29" s="667" t="n"/>
+      <c r="AT29" s="667" t="n"/>
+      <c r="AU29" s="667" t="n"/>
+      <c r="AV29" s="667" t="n"/>
+      <c r="AW29" s="667" t="n"/>
+      <c r="AX29" s="667" t="n"/>
+      <c r="AY29" s="667" t="n"/>
+      <c r="AZ29" s="667" t="n"/>
+      <c r="BA29" s="667" t="n"/>
+      <c r="BB29" s="667" t="n"/>
+      <c r="BC29" s="667" t="n"/>
+      <c r="BD29" s="667" t="n"/>
+    </row>
+    <row r="30" ht="20" customHeight="1">
+      <c r="A30" s="667" t="n"/>
+      <c r="B30" s="667" t="n"/>
+      <c r="C30" s="667" t="n"/>
+      <c r="D30" s="667" t="n"/>
+      <c r="E30" s="667" t="n"/>
+      <c r="F30" s="667" t="n"/>
+      <c r="G30" s="667" t="n"/>
+      <c r="H30" s="667" t="n"/>
+      <c r="I30" s="667" t="n"/>
+      <c r="J30" s="667" t="n"/>
+      <c r="K30" s="667" t="n"/>
+      <c r="L30" s="667" t="n"/>
+      <c r="M30" s="667" t="n"/>
+      <c r="N30" s="667" t="n"/>
+      <c r="O30" s="667" t="n"/>
+      <c r="P30" s="667" t="n"/>
+      <c r="Q30" s="667" t="n"/>
+      <c r="R30" s="667" t="n"/>
+      <c r="S30" s="667" t="n"/>
+      <c r="T30" s="667" t="n"/>
+      <c r="U30" s="667" t="n"/>
+      <c r="V30" s="667" t="n"/>
+      <c r="W30" s="667" t="n"/>
+      <c r="X30" s="667" t="n"/>
+      <c r="Y30" s="667" t="n"/>
+      <c r="Z30" s="667" t="n"/>
+      <c r="AA30" s="667" t="n"/>
+      <c r="AB30" s="667" t="n"/>
+      <c r="AC30" s="667" t="n"/>
+      <c r="AD30" s="667" t="n"/>
+      <c r="AE30" s="667" t="n"/>
+      <c r="AF30" s="667" t="n"/>
+      <c r="AG30" s="667" t="n"/>
+      <c r="AH30" s="667" t="n"/>
+      <c r="AI30" s="667" t="n"/>
+      <c r="AJ30" s="667" t="n"/>
+      <c r="AK30" s="667" t="n"/>
+      <c r="AL30" s="667" t="n"/>
+      <c r="AM30" s="667" t="n"/>
+      <c r="AN30" s="667" t="n"/>
+      <c r="AO30" s="667" t="n"/>
+      <c r="AP30" s="667" t="n"/>
+      <c r="AQ30" s="667" t="n"/>
+      <c r="AR30" s="667" t="n"/>
+      <c r="AS30" s="667" t="n"/>
+      <c r="AT30" s="667" t="n"/>
+      <c r="AU30" s="667" t="n"/>
+      <c r="AV30" s="667" t="n"/>
+      <c r="AW30" s="667" t="n"/>
+      <c r="AX30" s="667" t="n"/>
+      <c r="AY30" s="667" t="n"/>
+      <c r="AZ30" s="667" t="n"/>
+      <c r="BA30" s="667" t="n"/>
+      <c r="BB30" s="667" t="n"/>
+      <c r="BC30" s="667" t="n"/>
+      <c r="BD30" s="667" t="n"/>
+    </row>
+    <row r="31" ht="20" customHeight="1">
+      <c r="A31" s="667" t="n"/>
+      <c r="B31" s="667" t="n"/>
+      <c r="C31" s="667" t="n"/>
+      <c r="D31" s="667" t="n"/>
+      <c r="E31" s="667" t="n"/>
+      <c r="F31" s="667" t="n"/>
+      <c r="G31" s="667" t="n"/>
+      <c r="H31" s="667" t="n"/>
+      <c r="I31" s="667" t="n"/>
+      <c r="J31" s="667" t="n"/>
+      <c r="K31" s="667" t="n"/>
+      <c r="L31" s="667" t="n"/>
+      <c r="M31" s="667" t="n"/>
+      <c r="N31" s="667" t="n"/>
+      <c r="O31" s="667" t="n"/>
+      <c r="P31" s="667" t="n"/>
+      <c r="Q31" s="667" t="n"/>
+      <c r="R31" s="667" t="n"/>
+      <c r="S31" s="667" t="n"/>
+      <c r="T31" s="667" t="n"/>
+      <c r="U31" s="667" t="n"/>
+      <c r="V31" s="667" t="n"/>
+      <c r="W31" s="667" t="n"/>
+      <c r="X31" s="667" t="n"/>
+      <c r="Y31" s="667" t="n"/>
+      <c r="Z31" s="667" t="n"/>
+      <c r="AA31" s="667" t="n"/>
+      <c r="AB31" s="667" t="n"/>
+      <c r="AC31" s="667" t="n"/>
+      <c r="AD31" s="667" t="n"/>
+      <c r="AE31" s="667" t="n"/>
+      <c r="AF31" s="667" t="n"/>
+      <c r="AG31" s="667" t="n"/>
+      <c r="AH31" s="667" t="n"/>
+      <c r="AI31" s="667" t="n"/>
+      <c r="AJ31" s="667" t="n"/>
+      <c r="AK31" s="667" t="n"/>
+      <c r="AL31" s="667" t="n"/>
+      <c r="AM31" s="667" t="n"/>
+      <c r="AN31" s="667" t="n"/>
+      <c r="AO31" s="667" t="n"/>
+      <c r="AP31" s="667" t="n"/>
+      <c r="AQ31" s="667" t="n"/>
+      <c r="AR31" s="667" t="n"/>
+      <c r="AS31" s="667" t="n"/>
+      <c r="AT31" s="667" t="n"/>
+      <c r="AU31" s="667" t="n"/>
+      <c r="AV31" s="667" t="n"/>
+      <c r="AW31" s="667" t="n"/>
+      <c r="AX31" s="667" t="n"/>
+      <c r="AY31" s="667" t="n"/>
+      <c r="AZ31" s="667" t="n"/>
+      <c r="BA31" s="667" t="n"/>
+      <c r="BB31" s="667" t="n"/>
+      <c r="BC31" s="667" t="n"/>
+      <c r="BD31" s="667" t="n"/>
+    </row>
+    <row r="32" ht="20" customHeight="1">
+      <c r="A32" s="667" t="n"/>
+      <c r="B32" s="667" t="n"/>
+      <c r="C32" s="667" t="n"/>
+      <c r="D32" s="667" t="n"/>
+      <c r="E32" s="667" t="n"/>
+      <c r="F32" s="667" t="n"/>
+      <c r="G32" s="667" t="n"/>
+      <c r="H32" s="667" t="n"/>
+      <c r="I32" s="667" t="n"/>
+      <c r="J32" s="667" t="n"/>
+      <c r="K32" s="667" t="n"/>
+      <c r="L32" s="667" t="n"/>
+      <c r="M32" s="667" t="n"/>
+      <c r="N32" s="667" t="n"/>
+      <c r="O32" s="667" t="n"/>
+      <c r="P32" s="667" t="n"/>
+      <c r="Q32" s="667" t="n"/>
+      <c r="R32" s="667" t="n"/>
+      <c r="S32" s="667" t="n"/>
+      <c r="T32" s="667" t="n"/>
+      <c r="U32" s="667" t="n"/>
+      <c r="V32" s="667" t="n"/>
+      <c r="W32" s="667" t="n"/>
+      <c r="X32" s="667" t="n"/>
+      <c r="Y32" s="667" t="n"/>
+      <c r="Z32" s="667" t="n"/>
+      <c r="AA32" s="667" t="n"/>
+      <c r="AB32" s="667" t="n"/>
+      <c r="AC32" s="667" t="n"/>
+      <c r="AD32" s="667" t="n"/>
+      <c r="AE32" s="667" t="n"/>
+      <c r="AF32" s="667" t="n"/>
+      <c r="AG32" s="667" t="n"/>
+      <c r="AH32" s="667" t="n"/>
+      <c r="AI32" s="667" t="n"/>
+      <c r="AJ32" s="667" t="n"/>
+      <c r="AK32" s="667" t="n"/>
+      <c r="AL32" s="667" t="n"/>
+      <c r="AM32" s="667" t="n"/>
+      <c r="AN32" s="667" t="n"/>
+      <c r="AO32" s="667" t="n"/>
+      <c r="AP32" s="667" t="n"/>
+      <c r="AQ32" s="667" t="n"/>
+      <c r="AR32" s="667" t="n"/>
+      <c r="AS32" s="667" t="n"/>
+      <c r="AT32" s="667" t="n"/>
+      <c r="AU32" s="667" t="n"/>
+      <c r="AV32" s="667" t="n"/>
+      <c r="AW32" s="667" t="n"/>
+      <c r="AX32" s="667" t="n"/>
+      <c r="AY32" s="667" t="n"/>
+      <c r="AZ32" s="667" t="n"/>
+      <c r="BA32" s="667" t="n"/>
+      <c r="BB32" s="667" t="n"/>
+      <c r="BC32" s="667" t="n"/>
+      <c r="BD32" s="667" t="n"/>
+    </row>
+    <row r="33" ht="20" customHeight="1">
+      <c r="A33" s="667" t="n"/>
+      <c r="B33" s="667" t="n"/>
+      <c r="C33" s="667" t="n"/>
+      <c r="D33" s="667" t="n"/>
+      <c r="E33" s="667" t="n"/>
+      <c r="F33" s="667" t="n"/>
+      <c r="G33" s="667" t="n"/>
+      <c r="H33" s="667" t="n"/>
+      <c r="I33" s="667" t="n"/>
+      <c r="J33" s="667" t="n"/>
+      <c r="K33" s="667" t="n"/>
+      <c r="L33" s="667" t="n"/>
+      <c r="M33" s="667" t="n"/>
+      <c r="N33" s="667" t="n"/>
+      <c r="O33" s="667" t="n"/>
+      <c r="P33" s="667" t="n"/>
+      <c r="Q33" s="667" t="n"/>
+      <c r="R33" s="667" t="n"/>
+      <c r="S33" s="667" t="n"/>
+      <c r="T33" s="667" t="n"/>
+      <c r="U33" s="667" t="n"/>
+      <c r="V33" s="667" t="n"/>
+      <c r="W33" s="667" t="n"/>
+      <c r="X33" s="667" t="n"/>
+      <c r="Y33" s="667" t="n"/>
+      <c r="Z33" s="667" t="n"/>
+      <c r="AA33" s="667" t="n"/>
+      <c r="AB33" s="667" t="n"/>
+      <c r="AC33" s="667" t="n"/>
+      <c r="AD33" s="667" t="n"/>
+      <c r="AE33" s="667" t="n"/>
+      <c r="AF33" s="667" t="n"/>
+      <c r="AG33" s="667" t="n"/>
+      <c r="AH33" s="667" t="n"/>
+      <c r="AI33" s="667" t="n"/>
+      <c r="AJ33" s="667" t="n"/>
+      <c r="AK33" s="667" t="n"/>
+      <c r="AL33" s="667" t="n"/>
+      <c r="AM33" s="667" t="n"/>
+      <c r="AN33" s="667" t="n"/>
+      <c r="AO33" s="667" t="n"/>
+      <c r="AP33" s="667" t="n"/>
+      <c r="AQ33" s="667" t="n"/>
+      <c r="AR33" s="667" t="n"/>
+      <c r="AS33" s="667" t="n"/>
+      <c r="AT33" s="667" t="n"/>
+      <c r="AU33" s="667" t="n"/>
+      <c r="AV33" s="667" t="n"/>
+      <c r="AW33" s="667" t="n"/>
+      <c r="AX33" s="667" t="n"/>
+      <c r="AY33" s="667" t="n"/>
+      <c r="AZ33" s="667" t="n"/>
+      <c r="BA33" s="667" t="n"/>
+      <c r="BB33" s="667" t="n"/>
+      <c r="BC33" s="667" t="n"/>
+      <c r="BD33" s="667" t="n"/>
+    </row>
+    <row r="34" ht="20" customHeight="1">
+      <c r="A34" s="667" t="n"/>
+      <c r="B34" s="667" t="n"/>
+      <c r="C34" s="667" t="n"/>
+      <c r="D34" s="667" t="n"/>
+      <c r="E34" s="667" t="n"/>
+      <c r="F34" s="667" t="n"/>
+      <c r="G34" s="667" t="n"/>
+      <c r="H34" s="667" t="n"/>
+      <c r="I34" s="667" t="n"/>
+      <c r="J34" s="667" t="n"/>
+      <c r="K34" s="667" t="n"/>
+      <c r="L34" s="667" t="n"/>
+      <c r="M34" s="667" t="n"/>
+      <c r="N34" s="667" t="n"/>
+      <c r="O34" s="667" t="n"/>
+      <c r="P34" s="667" t="n"/>
+      <c r="Q34" s="667" t="n"/>
+      <c r="R34" s="667" t="n"/>
+      <c r="S34" s="667" t="n"/>
+      <c r="T34" s="667" t="n"/>
+      <c r="U34" s="667" t="n"/>
+      <c r="V34" s="667" t="n"/>
+      <c r="W34" s="667" t="n"/>
+      <c r="X34" s="667" t="n"/>
+      <c r="Y34" s="667" t="n"/>
+      <c r="Z34" s="667" t="n"/>
+      <c r="AA34" s="667" t="n"/>
+      <c r="AB34" s="667" t="n"/>
+      <c r="AC34" s="667" t="n"/>
+      <c r="AD34" s="667" t="n"/>
+      <c r="AE34" s="667" t="n"/>
+      <c r="AF34" s="667" t="n"/>
+      <c r="AG34" s="667" t="n"/>
+      <c r="AH34" s="667" t="n"/>
+      <c r="AI34" s="667" t="n"/>
+      <c r="AJ34" s="667" t="n"/>
+      <c r="AK34" s="667" t="n"/>
+      <c r="AL34" s="667" t="n"/>
+      <c r="AM34" s="667" t="n"/>
+      <c r="AN34" s="667" t="n"/>
+      <c r="AO34" s="667" t="n"/>
+      <c r="AP34" s="667" t="n"/>
+      <c r="AQ34" s="667" t="n"/>
+      <c r="AR34" s="667" t="n"/>
+      <c r="AS34" s="667" t="n"/>
+      <c r="AT34" s="667" t="n"/>
+      <c r="AU34" s="667" t="n"/>
+      <c r="AV34" s="667" t="n"/>
+      <c r="AW34" s="667" t="n"/>
+      <c r="AX34" s="667" t="n"/>
+      <c r="AY34" s="667" t="n"/>
+      <c r="AZ34" s="667" t="n"/>
+      <c r="BA34" s="667" t="n"/>
+      <c r="BB34" s="667" t="n"/>
+      <c r="BC34" s="667" t="n"/>
+      <c r="BD34" s="667" t="n"/>
+    </row>
+    <row r="35" ht="20" customHeight="1">
+      <c r="A35" s="667" t="n"/>
+      <c r="B35" s="667" t="n"/>
+      <c r="C35" s="667" t="n"/>
+      <c r="D35" s="667" t="n"/>
+      <c r="E35" s="667" t="n"/>
+      <c r="F35" s="667" t="n"/>
+      <c r="G35" s="667" t="n"/>
+      <c r="H35" s="667" t="n"/>
+      <c r="I35" s="667" t="n"/>
+      <c r="J35" s="667" t="n"/>
+      <c r="K35" s="667" t="n"/>
+      <c r="L35" s="667" t="n"/>
+      <c r="M35" s="667" t="n"/>
+      <c r="N35" s="667" t="n"/>
+      <c r="O35" s="667" t="n"/>
+      <c r="P35" s="667" t="n"/>
+      <c r="Q35" s="667" t="n"/>
+      <c r="R35" s="667" t="n"/>
+      <c r="S35" s="667" t="n"/>
+      <c r="T35" s="667" t="n"/>
+      <c r="U35" s="667" t="n"/>
+      <c r="V35" s="667" t="n"/>
+      <c r="W35" s="667" t="n"/>
+      <c r="X35" s="667" t="n"/>
+      <c r="Y35" s="667" t="n"/>
+      <c r="Z35" s="667" t="n"/>
+      <c r="AA35" s="667" t="n"/>
+      <c r="AB35" s="667" t="n"/>
+      <c r="AC35" s="667" t="n"/>
+      <c r="AD35" s="667" t="n"/>
+      <c r="AE35" s="667" t="n"/>
+      <c r="AF35" s="667" t="n"/>
+      <c r="AG35" s="667" t="n"/>
+      <c r="AH35" s="667" t="n"/>
+      <c r="AI35" s="667" t="n"/>
+      <c r="AJ35" s="667" t="n"/>
+      <c r="AK35" s="667" t="n"/>
+      <c r="AL35" s="667" t="n"/>
+      <c r="AM35" s="667" t="n"/>
+      <c r="AN35" s="667" t="n"/>
+      <c r="AO35" s="667" t="n"/>
+      <c r="AP35" s="667" t="n"/>
+      <c r="AQ35" s="667" t="n"/>
+      <c r="AR35" s="667" t="n"/>
+      <c r="AS35" s="667" t="n"/>
+      <c r="AT35" s="667" t="n"/>
+      <c r="AU35" s="667" t="n"/>
+      <c r="AV35" s="667" t="n"/>
+      <c r="AW35" s="667" t="n"/>
+      <c r="AX35" s="667" t="n"/>
+      <c r="AY35" s="667" t="n"/>
+      <c r="AZ35" s="667" t="n"/>
+      <c r="BA35" s="667" t="n"/>
+      <c r="BB35" s="667" t="n"/>
+      <c r="BC35" s="667" t="n"/>
+      <c r="BD35" s="667" t="n"/>
+    </row>
+    <row r="36" ht="20" customHeight="1">
+      <c r="A36" s="667" t="n"/>
+      <c r="B36" s="667" t="n"/>
+      <c r="C36" s="667" t="n"/>
+      <c r="D36" s="667" t="n"/>
+      <c r="E36" s="667" t="n"/>
+      <c r="F36" s="667" t="n"/>
+      <c r="G36" s="667" t="n"/>
+      <c r="H36" s="667" t="n"/>
+      <c r="I36" s="667" t="n"/>
+      <c r="J36" s="667" t="n"/>
+      <c r="K36" s="667" t="n"/>
+      <c r="L36" s="667" t="n"/>
+      <c r="M36" s="667" t="n"/>
+      <c r="N36" s="667" t="n"/>
+      <c r="O36" s="667" t="n"/>
+      <c r="P36" s="667" t="n"/>
+      <c r="Q36" s="667" t="n"/>
+      <c r="R36" s="667" t="n"/>
+      <c r="S36" s="667" t="n"/>
+      <c r="T36" s="667" t="n"/>
+      <c r="U36" s="667" t="n"/>
+      <c r="V36" s="667" t="n"/>
+      <c r="W36" s="667" t="n"/>
+      <c r="X36" s="667" t="n"/>
+      <c r="Y36" s="667" t="n"/>
+      <c r="Z36" s="667" t="n"/>
+      <c r="AA36" s="667" t="n"/>
+      <c r="AB36" s="667" t="n"/>
+      <c r="AC36" s="667" t="n"/>
+      <c r="AD36" s="667" t="n"/>
+      <c r="AE36" s="667" t="n"/>
+      <c r="AF36" s="667" t="n"/>
+      <c r="AG36" s="667" t="n"/>
+      <c r="AH36" s="667" t="n"/>
+      <c r="AI36" s="667" t="n"/>
+      <c r="AJ36" s="667" t="n"/>
+      <c r="AK36" s="667" t="n"/>
+      <c r="AL36" s="667" t="n"/>
+      <c r="AM36" s="667" t="n"/>
+      <c r="AN36" s="667" t="n"/>
+      <c r="AO36" s="667" t="n"/>
+      <c r="AP36" s="667" t="n"/>
+      <c r="AQ36" s="667" t="n"/>
+      <c r="AR36" s="667" t="n"/>
+      <c r="AS36" s="667" t="n"/>
+      <c r="AT36" s="667" t="n"/>
+      <c r="AU36" s="667" t="n"/>
+      <c r="AV36" s="667" t="n"/>
+      <c r="AW36" s="667" t="n"/>
+      <c r="AX36" s="667" t="n"/>
+      <c r="AY36" s="667" t="n"/>
+      <c r="AZ36" s="667" t="n"/>
+      <c r="BA36" s="667" t="n"/>
+      <c r="BB36" s="667" t="n"/>
+      <c r="BC36" s="667" t="n"/>
+      <c r="BD36" s="667" t="n"/>
+    </row>
+    <row r="37" ht="20" customHeight="1">
+      <c r="A37" s="667" t="n"/>
+      <c r="B37" s="667" t="n"/>
+      <c r="C37" s="667" t="n"/>
+      <c r="D37" s="667" t="n"/>
+      <c r="E37" s="667" t="n"/>
+      <c r="F37" s="667" t="n"/>
+      <c r="G37" s="667" t="n"/>
+      <c r="H37" s="667" t="n"/>
+      <c r="I37" s="667" t="n"/>
+      <c r="J37" s="667" t="n"/>
+      <c r="K37" s="667" t="n"/>
+      <c r="L37" s="667" t="n"/>
+      <c r="M37" s="667" t="n"/>
+      <c r="N37" s="667" t="n"/>
+      <c r="O37" s="667" t="n"/>
+      <c r="P37" s="667" t="n"/>
+      <c r="Q37" s="667" t="n"/>
+      <c r="R37" s="667" t="n"/>
+      <c r="S37" s="667" t="n"/>
+      <c r="T37" s="667" t="n"/>
+      <c r="U37" s="667" t="n"/>
+      <c r="V37" s="667" t="n"/>
+      <c r="W37" s="667" t="n"/>
+      <c r="X37" s="667" t="n"/>
+      <c r="Y37" s="667" t="n"/>
+      <c r="Z37" s="667" t="n"/>
+      <c r="AA37" s="667" t="n"/>
+      <c r="AB37" s="667" t="n"/>
+      <c r="AC37" s="667" t="n"/>
+      <c r="AD37" s="667" t="n"/>
+      <c r="AE37" s="667" t="n"/>
+      <c r="AF37" s="667" t="n"/>
+      <c r="AG37" s="667" t="n"/>
+      <c r="AH37" s="667" t="n"/>
+      <c r="AI37" s="667" t="n"/>
+      <c r="AJ37" s="667" t="n"/>
+      <c r="AK37" s="667" t="n"/>
+      <c r="AL37" s="667" t="n"/>
+      <c r="AM37" s="667" t="n"/>
+      <c r="AN37" s="667" t="n"/>
+      <c r="AO37" s="667" t="n"/>
+      <c r="AP37" s="667" t="n"/>
+      <c r="AQ37" s="667" t="n"/>
+      <c r="AR37" s="667" t="n"/>
+      <c r="AS37" s="667" t="n"/>
+      <c r="AT37" s="667" t="n"/>
+      <c r="AU37" s="667" t="n"/>
+      <c r="AV37" s="667" t="n"/>
+      <c r="AW37" s="667" t="n"/>
+      <c r="AX37" s="667" t="n"/>
+      <c r="AY37" s="667" t="n"/>
+      <c r="AZ37" s="667" t="n"/>
+      <c r="BA37" s="667" t="n"/>
+      <c r="BB37" s="667" t="n"/>
+      <c r="BC37" s="667" t="n"/>
+      <c r="BD37" s="667" t="n"/>
+    </row>
+    <row r="38" ht="20" customHeight="1">
+      <c r="A38" s="667" t="n"/>
+      <c r="B38" s="667" t="n"/>
+      <c r="C38" s="667" t="n"/>
+      <c r="D38" s="667" t="n"/>
+      <c r="E38" s="667" t="n"/>
+      <c r="F38" s="667" t="n"/>
+      <c r="G38" s="667" t="n"/>
+      <c r="H38" s="667" t="n"/>
+      <c r="I38" s="667" t="n"/>
+      <c r="J38" s="667" t="n"/>
+      <c r="K38" s="667" t="n"/>
+      <c r="L38" s="667" t="n"/>
+      <c r="M38" s="667" t="n"/>
+      <c r="N38" s="667" t="n"/>
+      <c r="O38" s="667" t="n"/>
+      <c r="P38" s="667" t="n"/>
+      <c r="Q38" s="667" t="n"/>
+      <c r="R38" s="667" t="n"/>
+      <c r="S38" s="667" t="n"/>
+      <c r="T38" s="667" t="n"/>
+      <c r="U38" s="667" t="n"/>
+      <c r="V38" s="667" t="n"/>
+      <c r="W38" s="667" t="n"/>
+      <c r="X38" s="667" t="n"/>
+      <c r="Y38" s="667" t="n"/>
+      <c r="Z38" s="667" t="n"/>
+      <c r="AA38" s="667" t="n"/>
+      <c r="AB38" s="667" t="n"/>
+      <c r="AC38" s="667" t="n"/>
+      <c r="AD38" s="667" t="n"/>
+      <c r="AE38" s="667" t="n"/>
+      <c r="AF38" s="667" t="n"/>
+      <c r="AG38" s="667" t="n"/>
+      <c r="AH38" s="667" t="n"/>
+      <c r="AI38" s="667" t="n"/>
+      <c r="AJ38" s="667" t="n"/>
+      <c r="AK38" s="667" t="n"/>
+      <c r="AL38" s="667" t="n"/>
+      <c r="AM38" s="667" t="n"/>
+      <c r="AN38" s="667" t="n"/>
+      <c r="AO38" s="667" t="n"/>
+      <c r="AP38" s="667" t="n"/>
+      <c r="AQ38" s="667" t="n"/>
+      <c r="AR38" s="667" t="n"/>
+      <c r="AS38" s="667" t="n"/>
+      <c r="AT38" s="667" t="n"/>
+      <c r="AU38" s="667" t="n"/>
+      <c r="AV38" s="667" t="n"/>
+      <c r="AW38" s="667" t="n"/>
+      <c r="AX38" s="667" t="n"/>
+      <c r="AY38" s="667" t="n"/>
+      <c r="AZ38" s="667" t="n"/>
+      <c r="BA38" s="667" t="n"/>
+      <c r="BB38" s="667" t="n"/>
+      <c r="BC38" s="667" t="n"/>
+      <c r="BD38" s="667" t="n"/>
+    </row>
+    <row r="39" ht="20" customHeight="1">
+      <c r="A39" s="667" t="n"/>
+      <c r="B39" s="667" t="n"/>
+      <c r="C39" s="667" t="n"/>
+      <c r="D39" s="667" t="n"/>
+      <c r="E39" s="667" t="n"/>
+      <c r="F39" s="667" t="n"/>
+      <c r="G39" s="667" t="n"/>
+      <c r="H39" s="667" t="n"/>
+      <c r="I39" s="667" t="n"/>
+      <c r="J39" s="667" t="n"/>
+      <c r="K39" s="667" t="n"/>
+      <c r="L39" s="667" t="n"/>
+      <c r="M39" s="667" t="n"/>
+      <c r="N39" s="667" t="n"/>
+      <c r="O39" s="667" t="n"/>
+      <c r="P39" s="667" t="n"/>
+      <c r="Q39" s="667" t="n"/>
+      <c r="R39" s="667" t="n"/>
+      <c r="S39" s="667" t="n"/>
+      <c r="T39" s="667" t="n"/>
+      <c r="U39" s="667" t="n"/>
+      <c r="V39" s="667" t="n"/>
+      <c r="W39" s="667" t="n"/>
+      <c r="X39" s="667" t="n"/>
+      <c r="Y39" s="667" t="n"/>
+      <c r="Z39" s="667" t="n"/>
+      <c r="AA39" s="667" t="n"/>
+      <c r="AB39" s="667" t="n"/>
+      <c r="AC39" s="667" t="n"/>
+      <c r="AD39" s="667" t="n"/>
+      <c r="AE39" s="667" t="n"/>
+      <c r="AF39" s="667" t="n"/>
+      <c r="AG39" s="667" t="n"/>
+      <c r="AH39" s="667" t="n"/>
+      <c r="AI39" s="667" t="n"/>
+      <c r="AJ39" s="667" t="n"/>
+      <c r="AK39" s="667" t="n"/>
+      <c r="AL39" s="667" t="n"/>
+      <c r="AM39" s="667" t="n"/>
+      <c r="AN39" s="667" t="n"/>
+      <c r="AO39" s="667" t="n"/>
+      <c r="AP39" s="667" t="n"/>
+      <c r="AQ39" s="667" t="n"/>
+      <c r="AR39" s="667" t="n"/>
+      <c r="AS39" s="667" t="n"/>
+      <c r="AT39" s="667" t="n"/>
+      <c r="AU39" s="667" t="n"/>
+      <c r="AV39" s="667" t="n"/>
+      <c r="AW39" s="667" t="n"/>
+      <c r="AX39" s="667" t="n"/>
+      <c r="AY39" s="667" t="n"/>
+      <c r="AZ39" s="667" t="n"/>
+      <c r="BA39" s="667" t="n"/>
+      <c r="BB39" s="667" t="n"/>
+      <c r="BC39" s="667" t="n"/>
+      <c r="BD39" s="667" t="n"/>
+    </row>
+    <row r="40" ht="20" customHeight="1">
+      <c r="A40" s="667" t="n"/>
+      <c r="B40" s="667" t="n"/>
+      <c r="C40" s="667" t="n"/>
+      <c r="D40" s="667" t="n"/>
+      <c r="E40" s="667" t="n"/>
+      <c r="F40" s="667" t="n"/>
+      <c r="G40" s="667" t="n"/>
+      <c r="H40" s="667" t="n"/>
+      <c r="I40" s="667" t="n"/>
+      <c r="J40" s="667" t="n"/>
+      <c r="K40" s="667" t="n"/>
+      <c r="L40" s="667" t="n"/>
+      <c r="M40" s="667" t="n"/>
+      <c r="N40" s="667" t="n"/>
+      <c r="O40" s="667" t="n"/>
+      <c r="P40" s="667" t="n"/>
+      <c r="Q40" s="667" t="n"/>
+      <c r="R40" s="667" t="n"/>
+      <c r="S40" s="667" t="n"/>
+      <c r="T40" s="667" t="n"/>
+      <c r="U40" s="667" t="n"/>
+      <c r="V40" s="667" t="n"/>
+      <c r="W40" s="667" t="n"/>
+      <c r="X40" s="667" t="n"/>
+      <c r="Y40" s="667" t="n"/>
+      <c r="Z40" s="667" t="n"/>
+      <c r="AA40" s="667" t="n"/>
+      <c r="AB40" s="667" t="n"/>
+      <c r="AC40" s="667" t="n"/>
+      <c r="AD40" s="667" t="n"/>
+      <c r="AE40" s="667" t="n"/>
+      <c r="AF40" s="667" t="n"/>
+      <c r="AG40" s="667" t="n"/>
+      <c r="AH40" s="667" t="n"/>
+      <c r="AI40" s="667" t="n"/>
+      <c r="AJ40" s="667" t="n"/>
+      <c r="AK40" s="667" t="n"/>
+      <c r="AL40" s="667" t="n"/>
+      <c r="AM40" s="667" t="n"/>
+      <c r="AN40" s="667" t="n"/>
+      <c r="AO40" s="667" t="n"/>
+      <c r="AP40" s="667" t="n"/>
+      <c r="AQ40" s="667" t="n"/>
+      <c r="AR40" s="667" t="n"/>
+      <c r="AS40" s="667" t="n"/>
+      <c r="AT40" s="667" t="n"/>
+      <c r="AU40" s="667" t="n"/>
+      <c r="AV40" s="667" t="n"/>
+      <c r="AW40" s="667" t="n"/>
+      <c r="AX40" s="667" t="n"/>
+      <c r="AY40" s="667" t="n"/>
+      <c r="AZ40" s="667" t="n"/>
+      <c r="BA40" s="667" t="n"/>
+      <c r="BB40" s="667" t="n"/>
+      <c r="BC40" s="667" t="n"/>
+      <c r="BD40" s="667" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="667" t="n"/>
+      <c r="B41" s="667" t="n"/>
+      <c r="C41" s="667" t="n"/>
+      <c r="D41" s="667" t="n"/>
+      <c r="E41" s="667" t="n"/>
+      <c r="F41" s="667" t="n"/>
+      <c r="G41" s="667" t="n"/>
+      <c r="H41" s="667" t="n"/>
+      <c r="I41" s="667" t="n"/>
+      <c r="J41" s="667" t="n"/>
+      <c r="K41" s="667" t="n"/>
+      <c r="L41" s="667" t="n"/>
+      <c r="M41" s="667" t="n"/>
+      <c r="N41" s="667" t="n"/>
+      <c r="O41" s="667" t="n"/>
+      <c r="P41" s="667" t="n"/>
+      <c r="Q41" s="667" t="n"/>
+      <c r="R41" s="667" t="n"/>
+      <c r="S41" s="667" t="n"/>
+      <c r="T41" s="667" t="n"/>
+      <c r="U41" s="667" t="n"/>
+      <c r="V41" s="667" t="n"/>
+      <c r="W41" s="667" t="n"/>
+      <c r="X41" s="667" t="n"/>
+      <c r="Y41" s="667" t="n"/>
+      <c r="Z41" s="667" t="n"/>
+      <c r="AA41" s="667" t="n"/>
+      <c r="AB41" s="667" t="n"/>
+      <c r="AC41" s="667" t="n"/>
+      <c r="AD41" s="667" t="n"/>
+      <c r="AE41" s="667" t="n"/>
+      <c r="AF41" s="667" t="n"/>
+      <c r="AG41" s="667" t="n"/>
+      <c r="AH41" s="667" t="n"/>
+      <c r="AI41" s="667" t="n"/>
+      <c r="AJ41" s="667" t="n"/>
+      <c r="AK41" s="667" t="n"/>
+      <c r="AL41" s="667" t="n"/>
+      <c r="AM41" s="667" t="n"/>
+      <c r="AN41" s="667" t="n"/>
+      <c r="AO41" s="667" t="n"/>
+      <c r="AP41" s="667" t="n"/>
+      <c r="AQ41" s="667" t="n"/>
+      <c r="AR41" s="667" t="n"/>
+      <c r="AS41" s="667" t="n"/>
+      <c r="AT41" s="667" t="n"/>
+      <c r="AU41" s="667" t="n"/>
+      <c r="AV41" s="667" t="n"/>
+      <c r="AW41" s="667" t="n"/>
+      <c r="AX41" s="667" t="n"/>
+      <c r="AY41" s="667" t="n"/>
+      <c r="AZ41" s="667" t="n"/>
+      <c r="BA41" s="667" t="n"/>
+      <c r="BB41" s="667" t="n"/>
+      <c r="BC41" s="667" t="n"/>
+      <c r="BD41" s="667" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="667" t="n"/>
+      <c r="B42" s="667" t="n"/>
+      <c r="C42" s="667" t="n"/>
+      <c r="D42" s="667" t="n"/>
+      <c r="E42" s="667" t="n"/>
+      <c r="F42" s="667" t="n"/>
+      <c r="G42" s="667" t="n"/>
+      <c r="H42" s="667" t="n"/>
+      <c r="I42" s="667" t="n"/>
+      <c r="J42" s="667" t="n"/>
+      <c r="K42" s="667" t="n"/>
+      <c r="L42" s="667" t="n"/>
+      <c r="M42" s="667" t="n"/>
+      <c r="N42" s="667" t="n"/>
+      <c r="O42" s="667" t="n"/>
+      <c r="P42" s="667" t="n"/>
+      <c r="Q42" s="667" t="n"/>
+      <c r="R42" s="667" t="n"/>
+      <c r="S42" s="667" t="n"/>
+      <c r="T42" s="667" t="n"/>
+      <c r="U42" s="667" t="n"/>
+      <c r="V42" s="667" t="n"/>
+      <c r="W42" s="667" t="n"/>
+      <c r="X42" s="667" t="n"/>
+      <c r="Y42" s="667" t="n"/>
+      <c r="Z42" s="667" t="n"/>
+      <c r="AA42" s="667" t="n"/>
+      <c r="AB42" s="667" t="n"/>
+      <c r="AC42" s="667" t="n"/>
+      <c r="AD42" s="667" t="n"/>
+      <c r="AE42" s="667" t="n"/>
+      <c r="AF42" s="667" t="n"/>
+      <c r="AG42" s="667" t="n"/>
+      <c r="AH42" s="667" t="n"/>
+      <c r="AI42" s="667" t="n"/>
+      <c r="AJ42" s="667" t="n"/>
+      <c r="AK42" s="667" t="n"/>
+      <c r="AL42" s="667" t="n"/>
+      <c r="AM42" s="667" t="n"/>
+      <c r="AN42" s="667" t="n"/>
+      <c r="AO42" s="667" t="n"/>
+      <c r="AP42" s="667" t="n"/>
+      <c r="AQ42" s="667" t="n"/>
+      <c r="AR42" s="667" t="n"/>
+      <c r="AS42" s="667" t="n"/>
+      <c r="AT42" s="667" t="n"/>
+      <c r="AU42" s="667" t="n"/>
+      <c r="AV42" s="667" t="n"/>
+      <c r="AW42" s="667" t="n"/>
+      <c r="AX42" s="667" t="n"/>
+      <c r="AY42" s="667" t="n"/>
+      <c r="AZ42" s="667" t="n"/>
+      <c r="BA42" s="667" t="n"/>
+      <c r="BB42" s="667" t="n"/>
+      <c r="BC42" s="667" t="n"/>
+      <c r="BD42" s="667" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="667" t="n"/>
+      <c r="B43" s="667" t="n"/>
+      <c r="C43" s="667" t="n"/>
+      <c r="D43" s="667" t="n"/>
+      <c r="E43" s="667" t="n"/>
+      <c r="F43" s="667" t="n"/>
+      <c r="G43" s="667" t="n"/>
+      <c r="H43" s="667" t="n"/>
+      <c r="I43" s="667" t="n"/>
+      <c r="J43" s="667" t="n"/>
+      <c r="K43" s="667" t="n"/>
+      <c r="L43" s="667" t="n"/>
+      <c r="M43" s="667" t="n"/>
+      <c r="N43" s="667" t="n"/>
+      <c r="O43" s="667" t="n"/>
+      <c r="P43" s="667" t="n"/>
+      <c r="Q43" s="667" t="n"/>
+      <c r="R43" s="667" t="n"/>
+      <c r="S43" s="667" t="n"/>
+      <c r="T43" s="667" t="n"/>
+      <c r="U43" s="667" t="n"/>
+      <c r="V43" s="667" t="n"/>
+      <c r="W43" s="667" t="n"/>
+      <c r="X43" s="667" t="n"/>
+      <c r="Y43" s="667" t="n"/>
+      <c r="Z43" s="667" t="n"/>
+      <c r="AA43" s="667" t="n"/>
+      <c r="AB43" s="667" t="n"/>
+      <c r="AC43" s="667" t="n"/>
+      <c r="AD43" s="667" t="n"/>
+      <c r="AE43" s="667" t="n"/>
+      <c r="AF43" s="667" t="n"/>
+      <c r="AG43" s="667" t="n"/>
+      <c r="AH43" s="667" t="n"/>
+      <c r="AI43" s="667" t="n"/>
+      <c r="AJ43" s="667" t="n"/>
+      <c r="AK43" s="667" t="n"/>
+      <c r="AL43" s="667" t="n"/>
+      <c r="AM43" s="667" t="n"/>
+      <c r="AN43" s="667" t="n"/>
+      <c r="AO43" s="667" t="n"/>
+      <c r="AP43" s="667" t="n"/>
+      <c r="AQ43" s="667" t="n"/>
+      <c r="AR43" s="667" t="n"/>
+      <c r="AS43" s="667" t="n"/>
+      <c r="AT43" s="667" t="n"/>
+      <c r="AU43" s="667" t="n"/>
+      <c r="AV43" s="667" t="n"/>
+      <c r="AW43" s="667" t="n"/>
+      <c r="AX43" s="667" t="n"/>
+      <c r="AY43" s="667" t="n"/>
+      <c r="AZ43" s="667" t="n"/>
+      <c r="BA43" s="667" t="n"/>
+      <c r="BB43" s="667" t="n"/>
+      <c r="BC43" s="667" t="n"/>
+      <c r="BD43" s="667" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="667" t="n"/>
+      <c r="B44" s="667" t="n"/>
+      <c r="C44" s="667" t="n"/>
+      <c r="D44" s="667" t="n"/>
+      <c r="E44" s="667" t="n"/>
+      <c r="F44" s="667" t="n"/>
+      <c r="G44" s="667" t="n"/>
+      <c r="H44" s="667" t="n"/>
+      <c r="I44" s="667" t="n"/>
+      <c r="J44" s="667" t="n"/>
+      <c r="K44" s="667" t="n"/>
+      <c r="L44" s="667" t="n"/>
+      <c r="M44" s="667" t="n"/>
+      <c r="N44" s="667" t="n"/>
+      <c r="O44" s="667" t="n"/>
+      <c r="P44" s="667" t="n"/>
+      <c r="Q44" s="667" t="n"/>
+      <c r="R44" s="667" t="n"/>
+      <c r="S44" s="667" t="n"/>
+      <c r="T44" s="667" t="n"/>
+      <c r="U44" s="667" t="n"/>
+      <c r="V44" s="667" t="n"/>
+      <c r="W44" s="667" t="n"/>
+      <c r="X44" s="667" t="n"/>
+      <c r="Y44" s="667" t="n"/>
+      <c r="Z44" s="667" t="n"/>
+      <c r="AA44" s="667" t="n"/>
+      <c r="AB44" s="667" t="n"/>
+      <c r="AC44" s="667" t="n"/>
+      <c r="AD44" s="667" t="n"/>
+      <c r="AE44" s="667" t="n"/>
+      <c r="AF44" s="667" t="n"/>
+      <c r="AG44" s="667" t="n"/>
+      <c r="AH44" s="667" t="n"/>
+      <c r="AI44" s="667" t="n"/>
+      <c r="AJ44" s="667" t="n"/>
+      <c r="AK44" s="667" t="n"/>
+      <c r="AL44" s="667" t="n"/>
+      <c r="AM44" s="667" t="n"/>
+      <c r="AN44" s="667" t="n"/>
+      <c r="AO44" s="667" t="n"/>
+      <c r="AP44" s="667" t="n"/>
+      <c r="AQ44" s="667" t="n"/>
+      <c r="AR44" s="667" t="n"/>
+      <c r="AS44" s="667" t="n"/>
+      <c r="AT44" s="667" t="n"/>
+      <c r="AU44" s="667" t="n"/>
+      <c r="AV44" s="667" t="n"/>
+      <c r="AW44" s="667" t="n"/>
+      <c r="AX44" s="667" t="n"/>
+      <c r="AY44" s="667" t="n"/>
+      <c r="AZ44" s="667" t="n"/>
+      <c r="BA44" s="667" t="n"/>
+      <c r="BB44" s="667" t="n"/>
+      <c r="BC44" s="667" t="n"/>
+      <c r="BD44" s="667" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="667" t="n"/>
+      <c r="B45" s="667" t="n"/>
+      <c r="C45" s="667" t="n"/>
+      <c r="D45" s="667" t="n"/>
+      <c r="E45" s="667" t="n"/>
+      <c r="F45" s="667" t="n"/>
+      <c r="G45" s="667" t="n"/>
+      <c r="H45" s="667" t="n"/>
+      <c r="I45" s="667" t="n"/>
+      <c r="J45" s="667" t="n"/>
+      <c r="K45" s="667" t="n"/>
+      <c r="L45" s="667" t="n"/>
+      <c r="M45" s="667" t="n"/>
+      <c r="N45" s="667" t="n"/>
+      <c r="O45" s="667" t="n"/>
+      <c r="P45" s="667" t="n"/>
+      <c r="Q45" s="667" t="n"/>
+      <c r="R45" s="667" t="n"/>
+      <c r="S45" s="667" t="n"/>
+      <c r="T45" s="667" t="n"/>
+      <c r="U45" s="667" t="n"/>
+      <c r="V45" s="667" t="n"/>
+      <c r="W45" s="667" t="n"/>
+      <c r="X45" s="667" t="n"/>
+      <c r="Y45" s="667" t="n"/>
+      <c r="Z45" s="667" t="n"/>
+      <c r="AA45" s="667" t="n"/>
+      <c r="AB45" s="667" t="n"/>
+      <c r="AC45" s="667" t="n"/>
+      <c r="AD45" s="667" t="n"/>
+      <c r="AE45" s="667" t="n"/>
+      <c r="AF45" s="667" t="n"/>
+      <c r="AG45" s="667" t="n"/>
+      <c r="AH45" s="667" t="n"/>
+      <c r="AI45" s="667" t="n"/>
+      <c r="AJ45" s="667" t="n"/>
+      <c r="AK45" s="667" t="n"/>
+      <c r="AL45" s="667" t="n"/>
+      <c r="AM45" s="667" t="n"/>
+      <c r="AN45" s="667" t="n"/>
+      <c r="AO45" s="667" t="n"/>
+      <c r="AP45" s="667" t="n"/>
+      <c r="AQ45" s="667" t="n"/>
+      <c r="AR45" s="667" t="n"/>
+      <c r="AS45" s="667" t="n"/>
+      <c r="AT45" s="667" t="n"/>
+      <c r="AU45" s="667" t="n"/>
+      <c r="AV45" s="667" t="n"/>
+      <c r="AW45" s="667" t="n"/>
+      <c r="AX45" s="667" t="n"/>
+      <c r="AY45" s="667" t="n"/>
+      <c r="AZ45" s="667" t="n"/>
+      <c r="BA45" s="667" t="n"/>
+      <c r="BB45" s="667" t="n"/>
+      <c r="BC45" s="667" t="n"/>
+      <c r="BD45" s="667" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="667" t="n"/>
+      <c r="B46" s="667" t="n"/>
+      <c r="C46" s="667" t="n"/>
+      <c r="D46" s="667" t="n"/>
+      <c r="E46" s="667" t="n"/>
+      <c r="F46" s="667" t="n"/>
+      <c r="G46" s="667" t="n"/>
+      <c r="H46" s="667" t="n"/>
+      <c r="I46" s="667" t="n"/>
+      <c r="J46" s="667" t="n"/>
+      <c r="K46" s="667" t="n"/>
+      <c r="L46" s="667" t="n"/>
+      <c r="M46" s="667" t="n"/>
+      <c r="N46" s="667" t="n"/>
+      <c r="O46" s="667" t="n"/>
+      <c r="P46" s="667" t="n"/>
+      <c r="Q46" s="667" t="n"/>
+      <c r="R46" s="667" t="n"/>
+      <c r="S46" s="667" t="n"/>
+      <c r="T46" s="667" t="n"/>
+      <c r="U46" s="667" t="n"/>
+      <c r="V46" s="667" t="n"/>
+      <c r="W46" s="667" t="n"/>
+      <c r="X46" s="667" t="n"/>
+      <c r="Y46" s="667" t="n"/>
+      <c r="Z46" s="667" t="n"/>
+      <c r="AA46" s="667" t="n"/>
+      <c r="AB46" s="667" t="n"/>
+      <c r="AC46" s="667" t="n"/>
+      <c r="AD46" s="667" t="n"/>
+      <c r="AE46" s="667" t="n"/>
+      <c r="AF46" s="667" t="n"/>
+      <c r="AG46" s="667" t="n"/>
+      <c r="AH46" s="667" t="n"/>
+      <c r="AI46" s="667" t="n"/>
+      <c r="AJ46" s="667" t="n"/>
+      <c r="AK46" s="667" t="n"/>
+      <c r="AL46" s="667" t="n"/>
+      <c r="AM46" s="667" t="n"/>
+      <c r="AN46" s="667" t="n"/>
+      <c r="AO46" s="667" t="n"/>
+      <c r="AP46" s="667" t="n"/>
+      <c r="AQ46" s="667" t="n"/>
+      <c r="AR46" s="667" t="n"/>
+      <c r="AS46" s="667" t="n"/>
+      <c r="AT46" s="667" t="n"/>
+      <c r="AU46" s="667" t="n"/>
+      <c r="AV46" s="667" t="n"/>
+      <c r="AW46" s="667" t="n"/>
+      <c r="AX46" s="667" t="n"/>
+      <c r="AY46" s="667" t="n"/>
+      <c r="AZ46" s="667" t="n"/>
+      <c r="BA46" s="667" t="n"/>
+      <c r="BB46" s="667" t="n"/>
+      <c r="BC46" s="667" t="n"/>
+      <c r="BD46" s="667" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="667" t="n"/>
+      <c r="B47" s="667" t="n"/>
+      <c r="C47" s="667" t="n"/>
+      <c r="D47" s="667" t="n"/>
+      <c r="E47" s="667" t="n"/>
+      <c r="F47" s="667" t="n"/>
+      <c r="G47" s="667" t="n"/>
+      <c r="H47" s="667" t="n"/>
+      <c r="I47" s="667" t="n"/>
+      <c r="J47" s="667" t="n"/>
+      <c r="K47" s="667" t="n"/>
+      <c r="L47" s="667" t="n"/>
+      <c r="M47" s="667" t="n"/>
+      <c r="N47" s="667" t="n"/>
+      <c r="O47" s="667" t="n"/>
+      <c r="P47" s="667" t="n"/>
+      <c r="Q47" s="667" t="n"/>
+      <c r="R47" s="667" t="n"/>
+      <c r="S47" s="667" t="n"/>
+      <c r="T47" s="667" t="n"/>
+      <c r="U47" s="667" t="n"/>
+      <c r="V47" s="667" t="n"/>
+      <c r="W47" s="667" t="n"/>
+      <c r="X47" s="667" t="n"/>
+      <c r="Y47" s="667" t="n"/>
+      <c r="Z47" s="667" t="n"/>
+      <c r="AA47" s="667" t="n"/>
+      <c r="AB47" s="667" t="n"/>
+      <c r="AC47" s="667" t="n"/>
+      <c r="AD47" s="667" t="n"/>
+      <c r="AE47" s="667" t="n"/>
+      <c r="AF47" s="667" t="n"/>
+      <c r="AG47" s="667" t="n"/>
+      <c r="AH47" s="667" t="n"/>
+      <c r="AI47" s="667" t="n"/>
+      <c r="AJ47" s="667" t="n"/>
+      <c r="AK47" s="667" t="n"/>
+      <c r="AL47" s="667" t="n"/>
+      <c r="AM47" s="667" t="n"/>
+      <c r="AN47" s="667" t="n"/>
+      <c r="AO47" s="667" t="n"/>
+      <c r="AP47" s="667" t="n"/>
+      <c r="AQ47" s="667" t="n"/>
+      <c r="AR47" s="667" t="n"/>
+      <c r="AS47" s="667" t="n"/>
+      <c r="AT47" s="667" t="n"/>
+      <c r="AU47" s="667" t="n"/>
+      <c r="AV47" s="667" t="n"/>
+      <c r="AW47" s="667" t="n"/>
+      <c r="AX47" s="667" t="n"/>
+      <c r="AY47" s="667" t="n"/>
+      <c r="AZ47" s="667" t="n"/>
+      <c r="BA47" s="667" t="n"/>
+      <c r="BB47" s="667" t="n"/>
+      <c r="BC47" s="667" t="n"/>
+      <c r="BD47" s="667" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="667" t="n"/>
+      <c r="B48" s="667" t="n"/>
+      <c r="C48" s="667" t="n"/>
+      <c r="D48" s="667" t="n"/>
+      <c r="E48" s="667" t="n"/>
+      <c r="F48" s="667" t="n"/>
+      <c r="G48" s="667" t="n"/>
+      <c r="H48" s="667" t="n"/>
+      <c r="I48" s="667" t="n"/>
+      <c r="J48" s="667" t="n"/>
+      <c r="K48" s="667" t="n"/>
+      <c r="L48" s="667" t="n"/>
+      <c r="M48" s="667" t="n"/>
+      <c r="N48" s="667" t="n"/>
+      <c r="O48" s="667" t="n"/>
+      <c r="P48" s="667" t="n"/>
+      <c r="Q48" s="667" t="n"/>
+      <c r="R48" s="667" t="n"/>
+      <c r="S48" s="667" t="n"/>
+      <c r="T48" s="667" t="n"/>
+      <c r="U48" s="667" t="n"/>
+      <c r="V48" s="667" t="n"/>
+      <c r="W48" s="667" t="n"/>
+      <c r="X48" s="667" t="n"/>
+      <c r="Y48" s="667" t="n"/>
+      <c r="Z48" s="667" t="n"/>
+      <c r="AA48" s="667" t="n"/>
+      <c r="AB48" s="667" t="n"/>
+      <c r="AC48" s="667" t="n"/>
+      <c r="AD48" s="667" t="n"/>
+      <c r="AE48" s="667" t="n"/>
+      <c r="AF48" s="667" t="n"/>
+      <c r="AG48" s="667" t="n"/>
+      <c r="AH48" s="667" t="n"/>
+      <c r="AI48" s="667" t="n"/>
+      <c r="AJ48" s="667" t="n"/>
+      <c r="AK48" s="667" t="n"/>
+      <c r="AL48" s="667" t="n"/>
+      <c r="AM48" s="667" t="n"/>
+      <c r="AN48" s="667" t="n"/>
+      <c r="AO48" s="667" t="n"/>
+      <c r="AP48" s="667" t="n"/>
+      <c r="AQ48" s="667" t="n"/>
+      <c r="AR48" s="667" t="n"/>
+      <c r="AS48" s="667" t="n"/>
+      <c r="AT48" s="667" t="n"/>
+      <c r="AU48" s="667" t="n"/>
+      <c r="AV48" s="667" t="n"/>
+      <c r="AW48" s="667" t="n"/>
+      <c r="AX48" s="667" t="n"/>
+      <c r="AY48" s="667" t="n"/>
+      <c r="AZ48" s="667" t="n"/>
+      <c r="BA48" s="667" t="n"/>
+      <c r="BB48" s="667" t="n"/>
+      <c r="BC48" s="667" t="n"/>
+      <c r="BD48" s="667" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="667" t="n"/>
+      <c r="B49" s="667" t="n"/>
+      <c r="C49" s="667" t="n"/>
+      <c r="D49" s="667" t="n"/>
+      <c r="E49" s="667" t="n"/>
+      <c r="F49" s="667" t="n"/>
+      <c r="G49" s="667" t="n"/>
+      <c r="H49" s="667" t="n"/>
+      <c r="I49" s="667" t="n"/>
+      <c r="J49" s="667" t="n"/>
+      <c r="K49" s="667" t="n"/>
+      <c r="L49" s="667" t="n"/>
+      <c r="M49" s="667" t="n"/>
+      <c r="N49" s="667" t="n"/>
+      <c r="O49" s="667" t="n"/>
+      <c r="P49" s="667" t="n"/>
+      <c r="Q49" s="667" t="n"/>
+      <c r="R49" s="667" t="n"/>
+      <c r="S49" s="667" t="n"/>
+      <c r="T49" s="667" t="n"/>
+      <c r="U49" s="667" t="n"/>
+      <c r="V49" s="667" t="n"/>
+      <c r="W49" s="667" t="n"/>
+      <c r="X49" s="667" t="n"/>
+      <c r="Y49" s="667" t="n"/>
+      <c r="Z49" s="667" t="n"/>
+      <c r="AA49" s="667" t="n"/>
+      <c r="AB49" s="667" t="n"/>
+      <c r="AC49" s="667" t="n"/>
+      <c r="AD49" s="667" t="n"/>
+      <c r="AE49" s="667" t="n"/>
+      <c r="AF49" s="667" t="n"/>
+      <c r="AG49" s="667" t="n"/>
+      <c r="AH49" s="667" t="n"/>
+      <c r="AI49" s="667" t="n"/>
+      <c r="AJ49" s="667" t="n"/>
+      <c r="AK49" s="667" t="n"/>
+      <c r="AL49" s="667" t="n"/>
+      <c r="AM49" s="667" t="n"/>
+      <c r="AN49" s="667" t="n"/>
+      <c r="AO49" s="667" t="n"/>
+      <c r="AP49" s="667" t="n"/>
+      <c r="AQ49" s="667" t="n"/>
+      <c r="AR49" s="667" t="n"/>
+      <c r="AS49" s="667" t="n"/>
+      <c r="AT49" s="667" t="n"/>
+      <c r="AU49" s="667" t="n"/>
+      <c r="AV49" s="667" t="n"/>
+      <c r="AW49" s="667" t="n"/>
+      <c r="AX49" s="667" t="n"/>
+      <c r="AY49" s="667" t="n"/>
+      <c r="AZ49" s="667" t="n"/>
+      <c r="BA49" s="667" t="n"/>
+      <c r="BB49" s="667" t="n"/>
+      <c r="BC49" s="667" t="n"/>
+      <c r="BD49" s="667" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="667" t="n"/>
+      <c r="B50" s="667" t="n"/>
+      <c r="C50" s="667" t="n"/>
+      <c r="D50" s="667" t="n"/>
+      <c r="E50" s="667" t="n"/>
+      <c r="F50" s="667" t="n"/>
+      <c r="G50" s="667" t="n"/>
+      <c r="H50" s="667" t="n"/>
+      <c r="I50" s="667" t="n"/>
+      <c r="J50" s="667" t="n"/>
+      <c r="K50" s="667" t="n"/>
+      <c r="L50" s="667" t="n"/>
+      <c r="M50" s="667" t="n"/>
+      <c r="N50" s="667" t="n"/>
+      <c r="O50" s="667" t="n"/>
+      <c r="P50" s="667" t="n"/>
+      <c r="Q50" s="667" t="n"/>
+      <c r="R50" s="667" t="n"/>
+      <c r="S50" s="667" t="n"/>
+      <c r="T50" s="667" t="n"/>
+      <c r="U50" s="667" t="n"/>
+      <c r="V50" s="667" t="n"/>
+      <c r="W50" s="667" t="n"/>
+      <c r="X50" s="667" t="n"/>
+      <c r="Y50" s="667" t="n"/>
+      <c r="Z50" s="667" t="n"/>
+      <c r="AA50" s="667" t="n"/>
+      <c r="AB50" s="667" t="n"/>
+      <c r="AC50" s="667" t="n"/>
+      <c r="AD50" s="667" t="n"/>
+      <c r="AE50" s="667" t="n"/>
+      <c r="AF50" s="667" t="n"/>
+      <c r="AG50" s="667" t="n"/>
+      <c r="AH50" s="667" t="n"/>
+      <c r="AI50" s="667" t="n"/>
+      <c r="AJ50" s="667" t="n"/>
+      <c r="AK50" s="667" t="n"/>
+      <c r="AL50" s="667" t="n"/>
+      <c r="AM50" s="667" t="n"/>
+      <c r="AN50" s="667" t="n"/>
+      <c r="AO50" s="667" t="n"/>
+      <c r="AP50" s="667" t="n"/>
+      <c r="AQ50" s="667" t="n"/>
+      <c r="AR50" s="667" t="n"/>
+      <c r="AS50" s="667" t="n"/>
+      <c r="AT50" s="667" t="n"/>
+      <c r="AU50" s="667" t="n"/>
+      <c r="AV50" s="667" t="n"/>
+      <c r="AW50" s="667" t="n"/>
+      <c r="AX50" s="667" t="n"/>
+      <c r="AY50" s="667" t="n"/>
+      <c r="AZ50" s="667" t="n"/>
+      <c r="BA50" s="667" t="n"/>
+      <c r="BB50" s="667" t="n"/>
+      <c r="BC50" s="667" t="n"/>
+      <c r="BD50" s="667" t="n"/>
+    </row>
   </sheetData>
   <sheetProtection selectLockedCells="1" selectUnlockedCells="1" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="0" insertColumns="0" pivotTables="1" deleteRows="0" formatCells="0" formatRows="0" sort="1"/>
-  <mergeCells count="2">
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A1:G1"/>
+  <mergeCells count="78">
+    <mergeCell ref="AO10:AU10"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="AW2:BD2"/>
+    <mergeCell ref="AZ15:BD15"/>
+    <mergeCell ref="AZ10:BD10"/>
+    <mergeCell ref="C14:P14"/>
+    <mergeCell ref="AQ5:AV5"/>
+    <mergeCell ref="AH13:AN13"/>
+    <mergeCell ref="AW3:BD3"/>
+    <mergeCell ref="AO11:AU11"/>
+    <mergeCell ref="AQ4:AV4"/>
+    <mergeCell ref="AW5:BD5"/>
+    <mergeCell ref="AH8:AN8"/>
+    <mergeCell ref="AO12:AU12"/>
+    <mergeCell ref="AH10:AN10"/>
+    <mergeCell ref="C8:P8"/>
+    <mergeCell ref="AZ12:BD12"/>
+    <mergeCell ref="AO14:AU14"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="AZ14:BD14"/>
+    <mergeCell ref="L4:AP4"/>
+    <mergeCell ref="Q13:AG13"/>
+    <mergeCell ref="AZ13:BD13"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="Q16:AG16"/>
+    <mergeCell ref="L1:AP3"/>
+    <mergeCell ref="AV15:AY15"/>
+    <mergeCell ref="AQ2:AV2"/>
+    <mergeCell ref="Q8:AG8"/>
+    <mergeCell ref="AH12:AN12"/>
+    <mergeCell ref="AO8:AU8"/>
+    <mergeCell ref="A1:K5"/>
+    <mergeCell ref="AV16:AY16"/>
+    <mergeCell ref="AO16:AU16"/>
+    <mergeCell ref="Q10:AG10"/>
+    <mergeCell ref="AH14:AN14"/>
+    <mergeCell ref="C12:P12"/>
+    <mergeCell ref="A7:BD7"/>
+    <mergeCell ref="AZ16:BD16"/>
+    <mergeCell ref="AV8:AY8"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="AV11:AY11"/>
+    <mergeCell ref="AZ8:BD8"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="AZ11:BD11"/>
+    <mergeCell ref="L5:AP5"/>
+    <mergeCell ref="Q12:AG12"/>
+    <mergeCell ref="AW4:BD4"/>
+    <mergeCell ref="C10:P10"/>
+    <mergeCell ref="C16:P16"/>
+    <mergeCell ref="AQ1:AV1"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="C9:P9"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="C11:P11"/>
+    <mergeCell ref="AW1:BD1"/>
+    <mergeCell ref="Q9:AG9"/>
+    <mergeCell ref="Q11:AG11"/>
+    <mergeCell ref="AH15:AN15"/>
+    <mergeCell ref="AV10:AY10"/>
+    <mergeCell ref="C13:P13"/>
+    <mergeCell ref="AQ3:AV3"/>
+    <mergeCell ref="AV9:AY9"/>
+    <mergeCell ref="AO9:AU9"/>
+    <mergeCell ref="C15:P15"/>
+    <mergeCell ref="AH16:AN16"/>
+    <mergeCell ref="AZ9:BD9"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="Q14:AG14"/>
+    <mergeCell ref="AV12:AY12"/>
+    <mergeCell ref="AO13:AU13"/>
+    <mergeCell ref="Q15:AG15"/>
+    <mergeCell ref="AV14:AY14"/>
+    <mergeCell ref="AO15:AU15"/>
+    <mergeCell ref="AH9:AN9"/>
+    <mergeCell ref="AV13:AY13"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="AH11:AN11"/>
   </mergeCells>
   <dataValidations count="3">
     <dataValidation sqref="F5:F14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid value" error="Use only the controlled dropdown values." promptTitle="Controlled dropdown" prompt="Select a controlled value from the list." type="list">
@@ -10332,1490 +12820,4 @@
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
   </tableParts>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:AN14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="2.33" customWidth="1" min="1" max="1"/>
-    <col width="2.33" customWidth="1" min="2" max="2"/>
-    <col width="2.33" customWidth="1" min="3" max="3"/>
-    <col width="2.33" customWidth="1" min="4" max="4"/>
-    <col width="2.33" customWidth="1" min="5" max="5"/>
-    <col width="2.33" customWidth="1" min="6" max="6"/>
-    <col width="2.33" customWidth="1" min="7" max="7"/>
-    <col width="2.33" customWidth="1" min="8" max="8"/>
-    <col width="2.33" customWidth="1" min="9" max="9"/>
-    <col width="2.33" customWidth="1" min="10" max="10"/>
-    <col width="2.33" customWidth="1" min="11" max="11"/>
-    <col width="2.33" customWidth="1" min="12" max="12"/>
-    <col width="2.33" customWidth="1" min="13" max="13"/>
-    <col width="2.33" customWidth="1" min="14" max="14"/>
-    <col width="2.33" customWidth="1" min="15" max="15"/>
-    <col width="2.33" customWidth="1" min="16" max="16"/>
-    <col width="2.33" customWidth="1" min="17" max="17"/>
-    <col width="2.33" customWidth="1" min="18" max="18"/>
-    <col width="2.33" customWidth="1" min="19" max="19"/>
-    <col width="2.33" customWidth="1" min="20" max="20"/>
-    <col width="2.33" customWidth="1" min="21" max="21"/>
-    <col width="2.33" customWidth="1" min="22" max="22"/>
-    <col width="2.33" customWidth="1" min="23" max="23"/>
-    <col width="2.33" customWidth="1" min="24" max="24"/>
-    <col width="2.33" customWidth="1" min="25" max="25"/>
-    <col width="2.33" customWidth="1" min="26" max="26"/>
-    <col width="2.33" customWidth="1" min="27" max="27"/>
-    <col width="2.33" customWidth="1" min="28" max="28"/>
-    <col width="2.33" customWidth="1" min="29" max="29"/>
-    <col width="2.33" customWidth="1" min="30" max="30"/>
-    <col width="2.33" customWidth="1" min="31" max="31"/>
-    <col width="2.33" customWidth="1" min="32" max="32"/>
-    <col width="2.33" customWidth="1" min="33" max="33"/>
-    <col width="2.33" customWidth="1" min="34" max="34"/>
-    <col width="2.33" customWidth="1" min="35" max="35"/>
-    <col width="2.33" customWidth="1" min="36" max="36"/>
-    <col width="2.33" customWidth="1" min="37" max="37"/>
-    <col width="2.33" customWidth="1" min="38" max="38"/>
-    <col width="2.33" customWidth="1" min="39" max="39"/>
-    <col width="2.33" customWidth="1" min="40" max="40"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="15" customHeight="1">
-      <c r="A1" s="513" t="inlineStr">
-        <is>
-          <t>Upstream References / Import Guidance</t>
-        </is>
-      </c>
-      <c r="B1" s="548" t="n"/>
-      <c r="C1" s="548" t="n"/>
-      <c r="D1" s="548" t="n"/>
-      <c r="E1" s="548" t="n"/>
-      <c r="F1" s="548" t="n"/>
-      <c r="G1" s="548" t="n"/>
-      <c r="H1" s="514" t="n"/>
-      <c r="I1" s="431" t="n"/>
-      <c r="J1" s="432" t="n"/>
-      <c r="K1" s="432" t="n"/>
-      <c r="L1" s="432" t="n"/>
-      <c r="M1" s="432" t="n"/>
-      <c r="N1" s="432" t="n"/>
-      <c r="O1" s="432" t="n"/>
-      <c r="P1" s="432" t="n"/>
-      <c r="Q1" s="432" t="n"/>
-      <c r="R1" s="432" t="n"/>
-      <c r="S1" s="432" t="n"/>
-      <c r="T1" s="432" t="n"/>
-      <c r="U1" s="432" t="n"/>
-      <c r="V1" s="432" t="n"/>
-      <c r="W1" s="432" t="n"/>
-      <c r="X1" s="432" t="n"/>
-      <c r="Y1" s="432" t="n"/>
-      <c r="Z1" s="432" t="n"/>
-      <c r="AA1" s="432" t="n"/>
-      <c r="AB1" s="432" t="n"/>
-      <c r="AC1" s="432" t="n"/>
-      <c r="AD1" s="433" t="n"/>
-      <c r="AE1" s="434" t="n"/>
-      <c r="AF1" s="435" t="n"/>
-      <c r="AG1" s="435" t="n"/>
-      <c r="AH1" s="436" t="n"/>
-      <c r="AI1" s="437" t="n"/>
-      <c r="AJ1" s="438" t="n"/>
-      <c r="AK1" s="438" t="n"/>
-      <c r="AL1" s="438" t="n"/>
-      <c r="AM1" s="438" t="n"/>
-      <c r="AN1" s="439" t="n"/>
-    </row>
-    <row r="2" ht="15" customHeight="1">
-      <c r="A2" s="515" t="inlineStr">
-        <is>
-          <t>Vacuum-compatible clean build and bagging gate for controlled preservation and packaging release.</t>
-        </is>
-      </c>
-      <c r="H2" s="516" t="n"/>
-      <c r="I2" s="442" t="n"/>
-      <c r="J2" s="443" t="n"/>
-      <c r="K2" s="443" t="n"/>
-      <c r="L2" s="443" t="n"/>
-      <c r="M2" s="443" t="n"/>
-      <c r="N2" s="443" t="n"/>
-      <c r="O2" s="443" t="n"/>
-      <c r="P2" s="443" t="n"/>
-      <c r="Q2" s="443" t="n"/>
-      <c r="R2" s="443" t="n"/>
-      <c r="S2" s="443" t="n"/>
-      <c r="T2" s="443" t="n"/>
-      <c r="U2" s="443" t="n"/>
-      <c r="V2" s="443" t="n"/>
-      <c r="W2" s="443" t="n"/>
-      <c r="X2" s="443" t="n"/>
-      <c r="Y2" s="443" t="n"/>
-      <c r="Z2" s="443" t="n"/>
-      <c r="AA2" s="443" t="n"/>
-      <c r="AB2" s="443" t="n"/>
-      <c r="AC2" s="443" t="n"/>
-      <c r="AD2" s="444" t="n"/>
-      <c r="AE2" s="445" t="n"/>
-      <c r="AF2" s="446" t="n"/>
-      <c r="AG2" s="446" t="n"/>
-      <c r="AH2" s="447" t="n"/>
-      <c r="AI2" s="448" t="n"/>
-      <c r="AJ2" s="449" t="n"/>
-      <c r="AK2" s="449" t="n"/>
-      <c r="AL2" s="449" t="n"/>
-      <c r="AM2" s="449" t="n"/>
-      <c r="AN2" s="450" t="n"/>
-    </row>
-    <row r="3" ht="15" customHeight="1">
-      <c r="A3" s="517" t="n"/>
-      <c r="B3" s="518" t="n"/>
-      <c r="C3" s="518" t="n"/>
-      <c r="D3" s="518" t="n"/>
-      <c r="E3" s="518" t="n"/>
-      <c r="F3" s="518" t="n"/>
-      <c r="G3" s="518" t="n"/>
-      <c r="H3" s="516" t="n"/>
-      <c r="I3" s="442" t="n"/>
-      <c r="J3" s="443" t="n"/>
-      <c r="K3" s="443" t="n"/>
-      <c r="L3" s="443" t="n"/>
-      <c r="M3" s="443" t="n"/>
-      <c r="N3" s="443" t="n"/>
-      <c r="O3" s="443" t="n"/>
-      <c r="P3" s="443" t="n"/>
-      <c r="Q3" s="443" t="n"/>
-      <c r="R3" s="443" t="n"/>
-      <c r="S3" s="443" t="n"/>
-      <c r="T3" s="443" t="n"/>
-      <c r="U3" s="443" t="n"/>
-      <c r="V3" s="443" t="n"/>
-      <c r="W3" s="443" t="n"/>
-      <c r="X3" s="443" t="n"/>
-      <c r="Y3" s="443" t="n"/>
-      <c r="Z3" s="443" t="n"/>
-      <c r="AA3" s="443" t="n"/>
-      <c r="AB3" s="443" t="n"/>
-      <c r="AC3" s="443" t="n"/>
-      <c r="AD3" s="444" t="n"/>
-      <c r="AE3" s="445" t="n"/>
-      <c r="AF3" s="446" t="n"/>
-      <c r="AG3" s="446" t="n"/>
-      <c r="AH3" s="447" t="n"/>
-      <c r="AI3" s="448" t="n"/>
-      <c r="AJ3" s="449" t="n"/>
-      <c r="AK3" s="449" t="n"/>
-      <c r="AL3" s="449" t="n"/>
-      <c r="AM3" s="449" t="n"/>
-      <c r="AN3" s="450" t="n"/>
-    </row>
-    <row r="4" ht="15" customHeight="1">
-      <c r="A4" s="519" t="inlineStr">
-        <is>
-          <t>Field</t>
-        </is>
-      </c>
-      <c r="B4" s="520" t="inlineStr">
-        <is>
-          <t>Value / Reference</t>
-        </is>
-      </c>
-      <c r="C4" s="520" t="inlineStr">
-        <is>
-          <t>Notes</t>
-        </is>
-      </c>
-      <c r="D4" s="518" t="n"/>
-      <c r="E4" s="518" t="n"/>
-      <c r="F4" s="518" t="n"/>
-      <c r="G4" s="518" t="n"/>
-      <c r="H4" s="516" t="n"/>
-      <c r="I4" s="451" t="n"/>
-      <c r="J4" s="452" t="n"/>
-      <c r="K4" s="452" t="n"/>
-      <c r="L4" s="452" t="n"/>
-      <c r="M4" s="452" t="n"/>
-      <c r="N4" s="452" t="n"/>
-      <c r="O4" s="452" t="n"/>
-      <c r="P4" s="452" t="n"/>
-      <c r="Q4" s="452" t="n"/>
-      <c r="R4" s="452" t="n"/>
-      <c r="S4" s="452" t="n"/>
-      <c r="T4" s="452" t="n"/>
-      <c r="U4" s="452" t="n"/>
-      <c r="V4" s="452" t="n"/>
-      <c r="W4" s="452" t="n"/>
-      <c r="X4" s="452" t="n"/>
-      <c r="Y4" s="452" t="n"/>
-      <c r="Z4" s="452" t="n"/>
-      <c r="AA4" s="452" t="n"/>
-      <c r="AB4" s="452" t="n"/>
-      <c r="AC4" s="452" t="n"/>
-      <c r="AD4" s="453" t="n"/>
-      <c r="AE4" s="445" t="n"/>
-      <c r="AF4" s="446" t="n"/>
-      <c r="AG4" s="446" t="n"/>
-      <c r="AH4" s="447" t="n"/>
-      <c r="AI4" s="448" t="n"/>
-      <c r="AJ4" s="449" t="n"/>
-      <c r="AK4" s="449" t="n"/>
-      <c r="AL4" s="449" t="n"/>
-      <c r="AM4" s="449" t="n"/>
-      <c r="AN4" s="450" t="n"/>
-    </row>
-    <row r="5" ht="15" customHeight="1">
-      <c r="A5" s="522" t="inlineStr">
-        <is>
-          <t>Source of Truth</t>
-        </is>
-      </c>
-      <c r="B5" s="523" t="inlineStr">
-        <is>
-          <t>M365 evidence / shared workbook</t>
-        </is>
-      </c>
-      <c r="C5" s="523" t="inlineStr">
-        <is>
-          <t>Do not duplicate ERP/M365/ANNEX master data.</t>
-        </is>
-      </c>
-      <c r="D5" s="541" t="n"/>
-      <c r="E5" s="541" t="n"/>
-      <c r="F5" s="541" t="n"/>
-      <c r="G5" s="541" t="n"/>
-      <c r="H5" s="542" t="n"/>
-      <c r="I5" s="457" t="n"/>
-      <c r="J5" s="458" t="n"/>
-      <c r="K5" s="458" t="n"/>
-      <c r="L5" s="458" t="n"/>
-      <c r="M5" s="458" t="n"/>
-      <c r="N5" s="458" t="n"/>
-      <c r="O5" s="458" t="n"/>
-      <c r="P5" s="458" t="n"/>
-      <c r="Q5" s="458" t="n"/>
-      <c r="R5" s="458" t="n"/>
-      <c r="S5" s="458" t="n"/>
-      <c r="T5" s="458" t="n"/>
-      <c r="U5" s="458" t="n"/>
-      <c r="V5" s="458" t="n"/>
-      <c r="W5" s="458" t="n"/>
-      <c r="X5" s="458" t="n"/>
-      <c r="Y5" s="458" t="n"/>
-      <c r="Z5" s="458" t="n"/>
-      <c r="AA5" s="458" t="n"/>
-      <c r="AB5" s="458" t="n"/>
-      <c r="AC5" s="458" t="n"/>
-      <c r="AD5" s="459" t="n"/>
-      <c r="AE5" s="460" t="n"/>
-      <c r="AF5" s="461" t="n"/>
-      <c r="AG5" s="461" t="n"/>
-      <c r="AH5" s="462" t="n"/>
-      <c r="AI5" s="463" t="n"/>
-      <c r="AJ5" s="464" t="n"/>
-      <c r="AK5" s="464" t="n"/>
-      <c r="AL5" s="464" t="n"/>
-      <c r="AM5" s="464" t="n"/>
-      <c r="AN5" s="465" t="n"/>
-    </row>
-    <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="525" t="inlineStr">
-        <is>
-          <t>Cross-Reference Boundary</t>
-        </is>
-      </c>
-      <c r="B6" s="526" t="inlineStr">
-        <is>
-          <t>This form does not replace SOP-702; it records the evidence, data or decision required by that SOP.
-Detailed task execution belongs in WI-716; this form captures results, checks, decisions or exceptions only.
-Rules, matrices, dictionaries, acceptance criteria and data definitions belong in ANNEX-QA-007 + ANNEX-WHS-001; do not copy ANNEX content into the live data-entry body.
-System-of-record / source-of-truth boundary: M365 evidence / shared workbook. If the master data already live there, reference or import them; do not re-key without need.</t>
-        </is>
-      </c>
-      <c r="C6" s="527" t="inlineStr">
-        <is>
-          <t>This form does not replace SOP-702; it records the evidence, data or decision required by that SOP.
-Detailed task execution belongs in WI-716; this form captures results, checks, decisions or exceptions only.
-Rules, matrices, dictionaries, acceptance criteria and data definitions belong in ANNEX-QA-007 + ANNEX-WHS-001; do not copy ANNEX content into the live data-entry body.
-System-of-record / source-of-truth boundary: M365 evidence / shared workbook. If the master data already live there, reference or import them; do not re-key without need.</t>
-        </is>
-      </c>
-      <c r="D6" s="471" t="n"/>
-      <c r="E6" s="471" t="n"/>
-      <c r="F6" s="471" t="n"/>
-      <c r="G6" s="471" t="n"/>
-      <c r="H6" s="471" t="n"/>
-      <c r="I6" s="471" t="n"/>
-      <c r="J6" s="471" t="n"/>
-      <c r="K6" s="471" t="n"/>
-      <c r="L6" s="471" t="n"/>
-      <c r="M6" s="471" t="n"/>
-      <c r="N6" s="471" t="n"/>
-      <c r="O6" s="471" t="n"/>
-      <c r="P6" s="471" t="n"/>
-      <c r="Q6" s="471" t="n"/>
-      <c r="R6" s="471" t="n"/>
-      <c r="S6" s="471" t="n"/>
-      <c r="T6" s="471" t="n"/>
-      <c r="U6" s="471" t="n"/>
-      <c r="V6" s="471" t="n"/>
-      <c r="W6" s="471" t="n"/>
-      <c r="X6" s="471" t="n"/>
-      <c r="Y6" s="471" t="n"/>
-      <c r="Z6" s="471" t="n"/>
-      <c r="AA6" s="471" t="n"/>
-      <c r="AB6" s="471" t="n"/>
-      <c r="AC6" s="471" t="n"/>
-      <c r="AD6" s="471" t="n"/>
-      <c r="AE6" s="471" t="n"/>
-      <c r="AF6" s="471" t="n"/>
-      <c r="AG6" s="471" t="n"/>
-      <c r="AH6" s="471" t="n"/>
-      <c r="AI6" s="471" t="n"/>
-      <c r="AJ6" s="471" t="n"/>
-      <c r="AK6" s="471" t="n"/>
-      <c r="AL6" s="471" t="n"/>
-      <c r="AM6" s="471" t="n"/>
-      <c r="AN6" s="503" t="n"/>
-    </row>
-    <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="528" t="inlineStr">
-        <is>
-          <t>SOP-702</t>
-        </is>
-      </c>
-      <c r="B7" s="529" t="inlineStr">
-        <is>
-          <t>SOP-702 — Kiểm soát nhiễm bẩn, xác nhận độ sạch và tuyến đóng gói sạch | HESEM QMS</t>
-        </is>
-      </c>
-      <c r="C7" s="530" t="inlineStr">
-        <is>
-          <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/01-SOPs/07-SOP-700/sop-702-contamination-control-and-cleanliness.html</t>
-        </is>
-      </c>
-      <c r="D7" s="344" t="n"/>
-      <c r="E7" s="344" t="n"/>
-      <c r="F7" s="344" t="n"/>
-      <c r="G7" s="344" t="n"/>
-      <c r="H7" s="344" t="n"/>
-      <c r="I7" s="344" t="n"/>
-      <c r="J7" s="344" t="n"/>
-      <c r="K7" s="344" t="n"/>
-      <c r="L7" s="344" t="n"/>
-      <c r="M7" s="344" t="n"/>
-      <c r="N7" s="344" t="n"/>
-      <c r="O7" s="344" t="n"/>
-      <c r="P7" s="344" t="n"/>
-      <c r="Q7" s="344" t="n"/>
-      <c r="R7" s="344" t="n"/>
-      <c r="S7" s="344" t="n"/>
-      <c r="T7" s="344" t="n"/>
-      <c r="U7" s="344" t="n"/>
-      <c r="V7" s="344" t="n"/>
-      <c r="W7" s="344" t="n"/>
-      <c r="X7" s="344" t="n"/>
-      <c r="Y7" s="344" t="n"/>
-      <c r="Z7" s="344" t="n"/>
-      <c r="AA7" s="344" t="n"/>
-      <c r="AB7" s="344" t="n"/>
-      <c r="AC7" s="344" t="n"/>
-      <c r="AD7" s="344" t="n"/>
-      <c r="AE7" s="344" t="n"/>
-      <c r="AF7" s="344" t="n"/>
-      <c r="AG7" s="344" t="n"/>
-      <c r="AH7" s="344" t="n"/>
-      <c r="AI7" s="344" t="n"/>
-      <c r="AJ7" s="344" t="n"/>
-      <c r="AK7" s="344" t="n"/>
-      <c r="AL7" s="344" t="n"/>
-      <c r="AM7" s="344" t="n"/>
-      <c r="AN7" s="531" t="n"/>
-    </row>
-    <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="532" t="inlineStr">
-        <is>
-          <t>WI-716</t>
-        </is>
-      </c>
-      <c r="B8" s="533" t="inlineStr">
-        <is>
-          <t>WI-716 — Lắp sạch, tương thích chân không, bagging và bảo quản cho Job đặc biệt</t>
-        </is>
-      </c>
-      <c r="C8" s="534" t="inlineStr">
-        <is>
-          <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/02-Work-Instructions/07-WI-700/wi-716-vacuum-compatible-clean-build-and-bagging.html</t>
-        </is>
-      </c>
-      <c r="D8" s="356" t="n"/>
-      <c r="E8" s="356" t="n"/>
-      <c r="F8" s="356" t="n"/>
-      <c r="G8" s="356" t="n"/>
-      <c r="H8" s="356" t="n"/>
-      <c r="I8" s="356" t="n"/>
-      <c r="J8" s="356" t="n"/>
-      <c r="K8" s="356" t="n"/>
-      <c r="L8" s="356" t="n"/>
-      <c r="M8" s="356" t="n"/>
-      <c r="N8" s="356" t="n"/>
-      <c r="O8" s="356" t="n"/>
-      <c r="P8" s="356" t="n"/>
-      <c r="Q8" s="356" t="n"/>
-      <c r="R8" s="356" t="n"/>
-      <c r="S8" s="356" t="n"/>
-      <c r="T8" s="356" t="n"/>
-      <c r="U8" s="356" t="n"/>
-      <c r="V8" s="356" t="n"/>
-      <c r="W8" s="356" t="n"/>
-      <c r="X8" s="356" t="n"/>
-      <c r="Y8" s="356" t="n"/>
-      <c r="Z8" s="356" t="n"/>
-      <c r="AA8" s="356" t="n"/>
-      <c r="AB8" s="356" t="n"/>
-      <c r="AC8" s="356" t="n"/>
-      <c r="AD8" s="356" t="n"/>
-      <c r="AE8" s="356" t="n"/>
-      <c r="AF8" s="356" t="n"/>
-      <c r="AG8" s="356" t="n"/>
-      <c r="AH8" s="356" t="n"/>
-      <c r="AI8" s="356" t="n"/>
-      <c r="AJ8" s="356" t="n"/>
-      <c r="AK8" s="356" t="n"/>
-      <c r="AL8" s="356" t="n"/>
-      <c r="AM8" s="356" t="n"/>
-      <c r="AN8" s="535" t="n"/>
-    </row>
-    <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="532" t="inlineStr">
-        <is>
-          <t>ANNEX-QA-007</t>
-        </is>
-      </c>
-      <c r="B9" s="533" t="inlineStr">
-        <is>
-          <t>ANNEX-QA-007 — Chuẩn bề mặt, độ sạch, tương thích chân không, rò rỉ và xử lý đặc biệt</t>
-        </is>
-      </c>
-      <c r="C9" s="534" t="inlineStr">
-        <is>
-          <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/03-Reference/02-ANNEX-Standards/annex-qa-007-surface-finish-vacuum-compatibility.html</t>
-        </is>
-      </c>
-      <c r="D9" s="356" t="n"/>
-      <c r="E9" s="356" t="n"/>
-      <c r="F9" s="356" t="n"/>
-      <c r="G9" s="356" t="n"/>
-      <c r="H9" s="356" t="n"/>
-      <c r="I9" s="356" t="n"/>
-      <c r="J9" s="356" t="n"/>
-      <c r="K9" s="356" t="n"/>
-      <c r="L9" s="356" t="n"/>
-      <c r="M9" s="356" t="n"/>
-      <c r="N9" s="356" t="n"/>
-      <c r="O9" s="356" t="n"/>
-      <c r="P9" s="356" t="n"/>
-      <c r="Q9" s="356" t="n"/>
-      <c r="R9" s="356" t="n"/>
-      <c r="S9" s="356" t="n"/>
-      <c r="T9" s="356" t="n"/>
-      <c r="U9" s="356" t="n"/>
-      <c r="V9" s="356" t="n"/>
-      <c r="W9" s="356" t="n"/>
-      <c r="X9" s="356" t="n"/>
-      <c r="Y9" s="356" t="n"/>
-      <c r="Z9" s="356" t="n"/>
-      <c r="AA9" s="356" t="n"/>
-      <c r="AB9" s="356" t="n"/>
-      <c r="AC9" s="356" t="n"/>
-      <c r="AD9" s="356" t="n"/>
-      <c r="AE9" s="356" t="n"/>
-      <c r="AF9" s="356" t="n"/>
-      <c r="AG9" s="356" t="n"/>
-      <c r="AH9" s="356" t="n"/>
-      <c r="AI9" s="356" t="n"/>
-      <c r="AJ9" s="356" t="n"/>
-      <c r="AK9" s="356" t="n"/>
-      <c r="AL9" s="356" t="n"/>
-      <c r="AM9" s="356" t="n"/>
-      <c r="AN9" s="535" t="n"/>
-    </row>
-    <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="532" t="inlineStr">
-        <is>
-          <t>ANNEX-WHS-001</t>
-        </is>
-      </c>
-      <c r="B10" s="533" t="inlineStr">
-        <is>
-          <t>ANNEX-WHS-001 — Quy cách đóng gói, nhãn, bảo quản và bằng chứng gói hàng</t>
-        </is>
-      </c>
-      <c r="C10" s="534" t="inlineStr">
-        <is>
-          <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/03-Reference/02-ANNEX-Standards/annex-whs-001-packaging-labeling-spec.html</t>
-        </is>
-      </c>
-      <c r="D10" s="356" t="n"/>
-      <c r="E10" s="356" t="n"/>
-      <c r="F10" s="356" t="n"/>
-      <c r="G10" s="356" t="n"/>
-      <c r="H10" s="356" t="n"/>
-      <c r="I10" s="356" t="n"/>
-      <c r="J10" s="356" t="n"/>
-      <c r="K10" s="356" t="n"/>
-      <c r="L10" s="356" t="n"/>
-      <c r="M10" s="356" t="n"/>
-      <c r="N10" s="356" t="n"/>
-      <c r="O10" s="356" t="n"/>
-      <c r="P10" s="356" t="n"/>
-      <c r="Q10" s="356" t="n"/>
-      <c r="R10" s="356" t="n"/>
-      <c r="S10" s="356" t="n"/>
-      <c r="T10" s="356" t="n"/>
-      <c r="U10" s="356" t="n"/>
-      <c r="V10" s="356" t="n"/>
-      <c r="W10" s="356" t="n"/>
-      <c r="X10" s="356" t="n"/>
-      <c r="Y10" s="356" t="n"/>
-      <c r="Z10" s="356" t="n"/>
-      <c r="AA10" s="356" t="n"/>
-      <c r="AB10" s="356" t="n"/>
-      <c r="AC10" s="356" t="n"/>
-      <c r="AD10" s="356" t="n"/>
-      <c r="AE10" s="356" t="n"/>
-      <c r="AF10" s="356" t="n"/>
-      <c r="AG10" s="356" t="n"/>
-      <c r="AH10" s="356" t="n"/>
-      <c r="AI10" s="356" t="n"/>
-      <c r="AJ10" s="356" t="n"/>
-      <c r="AK10" s="356" t="n"/>
-      <c r="AL10" s="356" t="n"/>
-      <c r="AM10" s="356" t="n"/>
-      <c r="AN10" s="535" t="n"/>
-    </row>
-    <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="532" t="inlineStr">
-        <is>
-          <t>Open When</t>
-        </is>
-      </c>
-      <c r="B11" s="533" t="inlineStr">
-        <is>
-          <t>Open before the controlled activity starts or before the release decision is taken. Do not populate it retrospectively after execution has already moved forward.</t>
-        </is>
-      </c>
-      <c r="C11" s="534" t="inlineStr">
-        <is>
-          <t>Operational trigger</t>
-        </is>
-      </c>
-      <c r="D11" s="356" t="n"/>
-      <c r="E11" s="356" t="n"/>
-      <c r="F11" s="356" t="n"/>
-      <c r="G11" s="356" t="n"/>
-      <c r="H11" s="356" t="n"/>
-      <c r="I11" s="356" t="n"/>
-      <c r="J11" s="356" t="n"/>
-      <c r="K11" s="356" t="n"/>
-      <c r="L11" s="356" t="n"/>
-      <c r="M11" s="356" t="n"/>
-      <c r="N11" s="356" t="n"/>
-      <c r="O11" s="356" t="n"/>
-      <c r="P11" s="356" t="n"/>
-      <c r="Q11" s="356" t="n"/>
-      <c r="R11" s="356" t="n"/>
-      <c r="S11" s="356" t="n"/>
-      <c r="T11" s="356" t="n"/>
-      <c r="U11" s="356" t="n"/>
-      <c r="V11" s="356" t="n"/>
-      <c r="W11" s="356" t="n"/>
-      <c r="X11" s="356" t="n"/>
-      <c r="Y11" s="356" t="n"/>
-      <c r="Z11" s="356" t="n"/>
-      <c r="AA11" s="356" t="n"/>
-      <c r="AB11" s="356" t="n"/>
-      <c r="AC11" s="356" t="n"/>
-      <c r="AD11" s="356" t="n"/>
-      <c r="AE11" s="356" t="n"/>
-      <c r="AF11" s="356" t="n"/>
-      <c r="AG11" s="356" t="n"/>
-      <c r="AH11" s="356" t="n"/>
-      <c r="AI11" s="356" t="n"/>
-      <c r="AJ11" s="356" t="n"/>
-      <c r="AK11" s="356" t="n"/>
-      <c r="AL11" s="356" t="n"/>
-      <c r="AM11" s="356" t="n"/>
-      <c r="AN11" s="535" t="n"/>
-    </row>
-    <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="532" t="inlineStr">
-        <is>
-          <t>Close When</t>
-        </is>
-      </c>
-      <c r="B12" s="533" t="inlineStr">
-        <is>
-          <t>Close only after the final gate disposition, result or release status is recorded, all conditions are assigned to an owner, and the evidence package reference is complete.</t>
-        </is>
-      </c>
-      <c r="C12" s="534" t="inlineStr">
-        <is>
-          <t>Release / closure rule</t>
-        </is>
-      </c>
-      <c r="D12" s="356" t="n"/>
-      <c r="E12" s="356" t="n"/>
-      <c r="F12" s="356" t="n"/>
-      <c r="G12" s="356" t="n"/>
-      <c r="H12" s="356" t="n"/>
-      <c r="I12" s="356" t="n"/>
-      <c r="J12" s="356" t="n"/>
-      <c r="K12" s="356" t="n"/>
-      <c r="L12" s="356" t="n"/>
-      <c r="M12" s="356" t="n"/>
-      <c r="N12" s="356" t="n"/>
-      <c r="O12" s="356" t="n"/>
-      <c r="P12" s="356" t="n"/>
-      <c r="Q12" s="356" t="n"/>
-      <c r="R12" s="356" t="n"/>
-      <c r="S12" s="356" t="n"/>
-      <c r="T12" s="356" t="n"/>
-      <c r="U12" s="356" t="n"/>
-      <c r="V12" s="356" t="n"/>
-      <c r="W12" s="356" t="n"/>
-      <c r="X12" s="356" t="n"/>
-      <c r="Y12" s="356" t="n"/>
-      <c r="Z12" s="356" t="n"/>
-      <c r="AA12" s="356" t="n"/>
-      <c r="AB12" s="356" t="n"/>
-      <c r="AC12" s="356" t="n"/>
-      <c r="AD12" s="356" t="n"/>
-      <c r="AE12" s="356" t="n"/>
-      <c r="AF12" s="356" t="n"/>
-      <c r="AG12" s="356" t="n"/>
-      <c r="AH12" s="356" t="n"/>
-      <c r="AI12" s="356" t="n"/>
-      <c r="AJ12" s="356" t="n"/>
-      <c r="AK12" s="356" t="n"/>
-      <c r="AL12" s="356" t="n"/>
-      <c r="AM12" s="356" t="n"/>
-      <c r="AN12" s="535" t="n"/>
-    </row>
-    <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="532" t="n"/>
-      <c r="B13" s="533" t="n"/>
-      <c r="C13" s="534" t="n"/>
-      <c r="D13" s="356" t="n"/>
-      <c r="E13" s="356" t="n"/>
-      <c r="F13" s="356" t="n"/>
-      <c r="G13" s="356" t="n"/>
-      <c r="H13" s="356" t="n"/>
-      <c r="I13" s="356" t="n"/>
-      <c r="J13" s="356" t="n"/>
-      <c r="K13" s="356" t="n"/>
-      <c r="L13" s="356" t="n"/>
-      <c r="M13" s="356" t="n"/>
-      <c r="N13" s="356" t="n"/>
-      <c r="O13" s="356" t="n"/>
-      <c r="P13" s="356" t="n"/>
-      <c r="Q13" s="356" t="n"/>
-      <c r="R13" s="356" t="n"/>
-      <c r="S13" s="356" t="n"/>
-      <c r="T13" s="356" t="n"/>
-      <c r="U13" s="356" t="n"/>
-      <c r="V13" s="356" t="n"/>
-      <c r="W13" s="356" t="n"/>
-      <c r="X13" s="356" t="n"/>
-      <c r="Y13" s="356" t="n"/>
-      <c r="Z13" s="356" t="n"/>
-      <c r="AA13" s="356" t="n"/>
-      <c r="AB13" s="356" t="n"/>
-      <c r="AC13" s="356" t="n"/>
-      <c r="AD13" s="356" t="n"/>
-      <c r="AE13" s="356" t="n"/>
-      <c r="AF13" s="356" t="n"/>
-      <c r="AG13" s="356" t="n"/>
-      <c r="AH13" s="356" t="n"/>
-      <c r="AI13" s="356" t="n"/>
-      <c r="AJ13" s="356" t="n"/>
-      <c r="AK13" s="356" t="n"/>
-      <c r="AL13" s="356" t="n"/>
-      <c r="AM13" s="356" t="n"/>
-      <c r="AN13" s="535" t="n"/>
-    </row>
-    <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="536" t="n"/>
-      <c r="B14" s="537" t="n"/>
-      <c r="C14" s="538" t="n"/>
-      <c r="D14" s="539" t="n"/>
-      <c r="E14" s="539" t="n"/>
-      <c r="F14" s="539" t="n"/>
-      <c r="G14" s="539" t="n"/>
-      <c r="H14" s="539" t="n"/>
-      <c r="I14" s="539" t="n"/>
-      <c r="J14" s="539" t="n"/>
-      <c r="K14" s="539" t="n"/>
-      <c r="L14" s="539" t="n"/>
-      <c r="M14" s="539" t="n"/>
-      <c r="N14" s="539" t="n"/>
-      <c r="O14" s="539" t="n"/>
-      <c r="P14" s="539" t="n"/>
-      <c r="Q14" s="539" t="n"/>
-      <c r="R14" s="539" t="n"/>
-      <c r="S14" s="539" t="n"/>
-      <c r="T14" s="539" t="n"/>
-      <c r="U14" s="539" t="n"/>
-      <c r="V14" s="539" t="n"/>
-      <c r="W14" s="539" t="n"/>
-      <c r="X14" s="539" t="n"/>
-      <c r="Y14" s="539" t="n"/>
-      <c r="Z14" s="539" t="n"/>
-      <c r="AA14" s="539" t="n"/>
-      <c r="AB14" s="539" t="n"/>
-      <c r="AC14" s="539" t="n"/>
-      <c r="AD14" s="539" t="n"/>
-      <c r="AE14" s="539" t="n"/>
-      <c r="AF14" s="539" t="n"/>
-      <c r="AG14" s="539" t="n"/>
-      <c r="AH14" s="539" t="n"/>
-      <c r="AI14" s="539" t="n"/>
-      <c r="AJ14" s="539" t="n"/>
-      <c r="AK14" s="539" t="n"/>
-      <c r="AL14" s="539" t="n"/>
-      <c r="AM14" s="539" t="n"/>
-      <c r="AN14" s="540" t="n"/>
-    </row>
-    <row r="15" ht="20" customHeight="1"/>
-    <row r="16" ht="20" customHeight="1"/>
-    <row r="17" ht="20" customHeight="1"/>
-    <row r="18" ht="20" customHeight="1"/>
-    <row r="19" ht="20" customHeight="1"/>
-    <row r="20" ht="20" customHeight="1"/>
-    <row r="21" ht="20" customHeight="1"/>
-    <row r="22" ht="20" customHeight="1"/>
-    <row r="23" ht="20" customHeight="1"/>
-    <row r="24" ht="20" customHeight="1"/>
-    <row r="25" ht="20" customHeight="1"/>
-    <row r="26" ht="20" customHeight="1"/>
-    <row r="27" ht="20" customHeight="1"/>
-    <row r="28" ht="20" customHeight="1"/>
-    <row r="29" ht="20" customHeight="1"/>
-    <row r="30" ht="20" customHeight="1"/>
-  </sheetData>
-  <sheetProtection selectLockedCells="1" selectUnlockedCells="1" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="0" insertColumns="0" pivotTables="1" deleteRows="0" formatCells="0" formatRows="0" sort="1"/>
-  <autoFilter ref="A4:C14"/>
-  <mergeCells count="2">
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A1:G1"/>
-  </mergeCells>
-  <pageMargins left="0.197" right="0.197" top="0.197" bottom="0.197" header="0.1" footer="0.1"/>
-  <pageSetup paperSize="9" fitToHeight="0" fitToWidth="1"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:AN12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="2.33" customWidth="1" min="1" max="1"/>
-    <col width="2.33" customWidth="1" min="2" max="2"/>
-    <col width="2.33" customWidth="1" min="3" max="3"/>
-    <col width="2.33" customWidth="1" min="4" max="4"/>
-    <col width="2.33" customWidth="1" min="5" max="5"/>
-    <col width="2.33" customWidth="1" min="6" max="6"/>
-    <col width="2.33" customWidth="1" min="7" max="7"/>
-    <col width="2.33" customWidth="1" min="8" max="8"/>
-    <col width="2.33" customWidth="1" min="9" max="9"/>
-    <col width="2.33" customWidth="1" min="10" max="10"/>
-    <col width="2.33" customWidth="1" min="11" max="11"/>
-    <col width="2.33" customWidth="1" min="12" max="12"/>
-    <col width="2.33" customWidth="1" min="13" max="13"/>
-    <col width="2.33" customWidth="1" min="14" max="14"/>
-    <col width="2.33" customWidth="1" min="15" max="15"/>
-    <col width="2.33" customWidth="1" min="16" max="16"/>
-    <col width="2.33" customWidth="1" min="17" max="17"/>
-    <col width="2.33" customWidth="1" min="18" max="18"/>
-    <col width="2.33" customWidth="1" min="19" max="19"/>
-    <col width="2.33" customWidth="1" min="20" max="20"/>
-    <col width="2.33" customWidth="1" min="21" max="21"/>
-    <col width="2.33" customWidth="1" min="22" max="22"/>
-    <col width="2.33" customWidth="1" min="23" max="23"/>
-    <col width="2.33" customWidth="1" min="24" max="24"/>
-    <col width="2.33" customWidth="1" min="25" max="25"/>
-    <col width="2.33" customWidth="1" min="26" max="26"/>
-    <col width="2.33" customWidth="1" min="27" max="27"/>
-    <col width="2.33" customWidth="1" min="28" max="28"/>
-    <col width="2.33" customWidth="1" min="29" max="29"/>
-    <col width="2.33" customWidth="1" min="30" max="30"/>
-    <col width="2.33" customWidth="1" min="31" max="31"/>
-    <col width="2.33" customWidth="1" min="32" max="32"/>
-    <col width="2.33" customWidth="1" min="33" max="33"/>
-    <col width="2.33" customWidth="1" min="34" max="34"/>
-    <col width="2.33" customWidth="1" min="35" max="35"/>
-    <col width="2.33" customWidth="1" min="36" max="36"/>
-    <col width="2.33" customWidth="1" min="37" max="37"/>
-    <col width="2.33" customWidth="1" min="38" max="38"/>
-    <col width="2.33" customWidth="1" min="39" max="39"/>
-    <col width="2.33" customWidth="1" min="40" max="40"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="15" customHeight="1">
-      <c r="A1" s="513" t="inlineStr">
-        <is>
-          <t>Evidence Reference / Attachment Guidance</t>
-        </is>
-      </c>
-      <c r="B1" s="548" t="n"/>
-      <c r="C1" s="548" t="n"/>
-      <c r="D1" s="548" t="n"/>
-      <c r="E1" s="548" t="n"/>
-      <c r="F1" s="548" t="n"/>
-      <c r="G1" s="548" t="n"/>
-      <c r="H1" s="514" t="n"/>
-      <c r="I1" s="431" t="n"/>
-      <c r="J1" s="432" t="n"/>
-      <c r="K1" s="432" t="n"/>
-      <c r="L1" s="432" t="n"/>
-      <c r="M1" s="432" t="n"/>
-      <c r="N1" s="432" t="n"/>
-      <c r="O1" s="432" t="n"/>
-      <c r="P1" s="432" t="n"/>
-      <c r="Q1" s="432" t="n"/>
-      <c r="R1" s="432" t="n"/>
-      <c r="S1" s="432" t="n"/>
-      <c r="T1" s="432" t="n"/>
-      <c r="U1" s="432" t="n"/>
-      <c r="V1" s="432" t="n"/>
-      <c r="W1" s="432" t="n"/>
-      <c r="X1" s="432" t="n"/>
-      <c r="Y1" s="432" t="n"/>
-      <c r="Z1" s="432" t="n"/>
-      <c r="AA1" s="432" t="n"/>
-      <c r="AB1" s="432" t="n"/>
-      <c r="AC1" s="432" t="n"/>
-      <c r="AD1" s="433" t="n"/>
-      <c r="AE1" s="434" t="n"/>
-      <c r="AF1" s="435" t="n"/>
-      <c r="AG1" s="435" t="n"/>
-      <c r="AH1" s="436" t="n"/>
-      <c r="AI1" s="437" t="n"/>
-      <c r="AJ1" s="438" t="n"/>
-      <c r="AK1" s="438" t="n"/>
-      <c r="AL1" s="438" t="n"/>
-      <c r="AM1" s="438" t="n"/>
-      <c r="AN1" s="439" t="n"/>
-    </row>
-    <row r="2" ht="15" customHeight="1">
-      <c r="A2" s="515" t="inlineStr">
-        <is>
-          <t>Use controlled evidence package references; do not free-type vague placeholders.</t>
-        </is>
-      </c>
-      <c r="H2" s="516" t="n"/>
-      <c r="I2" s="442" t="n"/>
-      <c r="J2" s="443" t="n"/>
-      <c r="K2" s="443" t="n"/>
-      <c r="L2" s="443" t="n"/>
-      <c r="M2" s="443" t="n"/>
-      <c r="N2" s="443" t="n"/>
-      <c r="O2" s="443" t="n"/>
-      <c r="P2" s="443" t="n"/>
-      <c r="Q2" s="443" t="n"/>
-      <c r="R2" s="443" t="n"/>
-      <c r="S2" s="443" t="n"/>
-      <c r="T2" s="443" t="n"/>
-      <c r="U2" s="443" t="n"/>
-      <c r="V2" s="443" t="n"/>
-      <c r="W2" s="443" t="n"/>
-      <c r="X2" s="443" t="n"/>
-      <c r="Y2" s="443" t="n"/>
-      <c r="Z2" s="443" t="n"/>
-      <c r="AA2" s="443" t="n"/>
-      <c r="AB2" s="443" t="n"/>
-      <c r="AC2" s="443" t="n"/>
-      <c r="AD2" s="444" t="n"/>
-      <c r="AE2" s="445" t="n"/>
-      <c r="AF2" s="446" t="n"/>
-      <c r="AG2" s="446" t="n"/>
-      <c r="AH2" s="447" t="n"/>
-      <c r="AI2" s="448" t="n"/>
-      <c r="AJ2" s="449" t="n"/>
-      <c r="AK2" s="449" t="n"/>
-      <c r="AL2" s="449" t="n"/>
-      <c r="AM2" s="449" t="n"/>
-      <c r="AN2" s="450" t="n"/>
-    </row>
-    <row r="3" ht="15" customHeight="1">
-      <c r="A3" s="517" t="n"/>
-      <c r="B3" s="518" t="n"/>
-      <c r="C3" s="518" t="n"/>
-      <c r="D3" s="518" t="n"/>
-      <c r="E3" s="518" t="n"/>
-      <c r="F3" s="518" t="n"/>
-      <c r="G3" s="518" t="n"/>
-      <c r="H3" s="516" t="n"/>
-      <c r="I3" s="442" t="n"/>
-      <c r="J3" s="443" t="n"/>
-      <c r="K3" s="443" t="n"/>
-      <c r="L3" s="443" t="n"/>
-      <c r="M3" s="443" t="n"/>
-      <c r="N3" s="443" t="n"/>
-      <c r="O3" s="443" t="n"/>
-      <c r="P3" s="443" t="n"/>
-      <c r="Q3" s="443" t="n"/>
-      <c r="R3" s="443" t="n"/>
-      <c r="S3" s="443" t="n"/>
-      <c r="T3" s="443" t="n"/>
-      <c r="U3" s="443" t="n"/>
-      <c r="V3" s="443" t="n"/>
-      <c r="W3" s="443" t="n"/>
-      <c r="X3" s="443" t="n"/>
-      <c r="Y3" s="443" t="n"/>
-      <c r="Z3" s="443" t="n"/>
-      <c r="AA3" s="443" t="n"/>
-      <c r="AB3" s="443" t="n"/>
-      <c r="AC3" s="443" t="n"/>
-      <c r="AD3" s="444" t="n"/>
-      <c r="AE3" s="445" t="n"/>
-      <c r="AF3" s="446" t="n"/>
-      <c r="AG3" s="446" t="n"/>
-      <c r="AH3" s="447" t="n"/>
-      <c r="AI3" s="448" t="n"/>
-      <c r="AJ3" s="449" t="n"/>
-      <c r="AK3" s="449" t="n"/>
-      <c r="AL3" s="449" t="n"/>
-      <c r="AM3" s="449" t="n"/>
-      <c r="AN3" s="450" t="n"/>
-    </row>
-    <row r="4" ht="15" customHeight="1">
-      <c r="A4" s="519" t="inlineStr">
-        <is>
-          <t>Field</t>
-        </is>
-      </c>
-      <c r="B4" s="520" t="inlineStr">
-        <is>
-          <t>Value / Reference</t>
-        </is>
-      </c>
-      <c r="C4" s="520" t="inlineStr">
-        <is>
-          <t>Notes</t>
-        </is>
-      </c>
-      <c r="D4" s="518" t="n"/>
-      <c r="E4" s="518" t="n"/>
-      <c r="F4" s="518" t="n"/>
-      <c r="G4" s="518" t="n"/>
-      <c r="H4" s="516" t="n"/>
-      <c r="I4" s="451" t="n"/>
-      <c r="J4" s="452" t="n"/>
-      <c r="K4" s="452" t="n"/>
-      <c r="L4" s="452" t="n"/>
-      <c r="M4" s="452" t="n"/>
-      <c r="N4" s="452" t="n"/>
-      <c r="O4" s="452" t="n"/>
-      <c r="P4" s="452" t="n"/>
-      <c r="Q4" s="452" t="n"/>
-      <c r="R4" s="452" t="n"/>
-      <c r="S4" s="452" t="n"/>
-      <c r="T4" s="452" t="n"/>
-      <c r="U4" s="452" t="n"/>
-      <c r="V4" s="452" t="n"/>
-      <c r="W4" s="452" t="n"/>
-      <c r="X4" s="452" t="n"/>
-      <c r="Y4" s="452" t="n"/>
-      <c r="Z4" s="452" t="n"/>
-      <c r="AA4" s="452" t="n"/>
-      <c r="AB4" s="452" t="n"/>
-      <c r="AC4" s="452" t="n"/>
-      <c r="AD4" s="453" t="n"/>
-      <c r="AE4" s="445" t="n"/>
-      <c r="AF4" s="446" t="n"/>
-      <c r="AG4" s="446" t="n"/>
-      <c r="AH4" s="447" t="n"/>
-      <c r="AI4" s="448" t="n"/>
-      <c r="AJ4" s="449" t="n"/>
-      <c r="AK4" s="449" t="n"/>
-      <c r="AL4" s="449" t="n"/>
-      <c r="AM4" s="449" t="n"/>
-      <c r="AN4" s="450" t="n"/>
-    </row>
-    <row r="5" ht="15" customHeight="1">
-      <c r="A5" s="522" t="inlineStr">
-        <is>
-          <t>Source of Truth</t>
-        </is>
-      </c>
-      <c r="B5" s="523" t="inlineStr">
-        <is>
-          <t>M365 evidence / shared workbook</t>
-        </is>
-      </c>
-      <c r="C5" s="523" t="inlineStr">
-        <is>
-          <t>Do not duplicate ERP/M365/ANNEX master data.</t>
-        </is>
-      </c>
-      <c r="D5" s="541" t="n"/>
-      <c r="E5" s="541" t="n"/>
-      <c r="F5" s="541" t="n"/>
-      <c r="G5" s="541" t="n"/>
-      <c r="H5" s="542" t="n"/>
-      <c r="I5" s="457" t="n"/>
-      <c r="J5" s="458" t="n"/>
-      <c r="K5" s="458" t="n"/>
-      <c r="L5" s="458" t="n"/>
-      <c r="M5" s="458" t="n"/>
-      <c r="N5" s="458" t="n"/>
-      <c r="O5" s="458" t="n"/>
-      <c r="P5" s="458" t="n"/>
-      <c r="Q5" s="458" t="n"/>
-      <c r="R5" s="458" t="n"/>
-      <c r="S5" s="458" t="n"/>
-      <c r="T5" s="458" t="n"/>
-      <c r="U5" s="458" t="n"/>
-      <c r="V5" s="458" t="n"/>
-      <c r="W5" s="458" t="n"/>
-      <c r="X5" s="458" t="n"/>
-      <c r="Y5" s="458" t="n"/>
-      <c r="Z5" s="458" t="n"/>
-      <c r="AA5" s="458" t="n"/>
-      <c r="AB5" s="458" t="n"/>
-      <c r="AC5" s="458" t="n"/>
-      <c r="AD5" s="459" t="n"/>
-      <c r="AE5" s="460" t="n"/>
-      <c r="AF5" s="461" t="n"/>
-      <c r="AG5" s="461" t="n"/>
-      <c r="AH5" s="462" t="n"/>
-      <c r="AI5" s="463" t="n"/>
-      <c r="AJ5" s="464" t="n"/>
-      <c r="AK5" s="464" t="n"/>
-      <c r="AL5" s="464" t="n"/>
-      <c r="AM5" s="464" t="n"/>
-      <c r="AN5" s="465" t="n"/>
-    </row>
-    <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="525" t="inlineStr">
-        <is>
-          <t>Cross-Reference Boundary</t>
-        </is>
-      </c>
-      <c r="B6" s="526" t="inlineStr">
-        <is>
-          <t>This form does not replace SOP-702; it records the evidence, data or decision required by that SOP.
-Detailed task execution belongs in WI-716; this form captures results, checks, decisions or exceptions only.
-Rules, matrices, dictionaries, acceptance criteria and data definitions belong in ANNEX-QA-007 + ANNEX-WHS-001; do not copy ANNEX content into the live data-entry body.
-System-of-record / source-of-truth boundary: M365 evidence / shared workbook. If the master data already live there, reference or import them; do not re-key without need.</t>
-        </is>
-      </c>
-      <c r="C6" s="527" t="inlineStr">
-        <is>
-          <t>This form does not replace SOP-702; it records the evidence, data or decision required by that SOP.
-Detailed task execution belongs in WI-716; this form captures results, checks, decisions or exceptions only.
-Rules, matrices, dictionaries, acceptance criteria and data definitions belong in ANNEX-QA-007 + ANNEX-WHS-001; do not copy ANNEX content into the live data-entry body.
-System-of-record / source-of-truth boundary: M365 evidence / shared workbook. If the master data already live there, reference or import them; do not re-key without need.</t>
-        </is>
-      </c>
-      <c r="D6" s="471" t="n"/>
-      <c r="E6" s="471" t="n"/>
-      <c r="F6" s="471" t="n"/>
-      <c r="G6" s="471" t="n"/>
-      <c r="H6" s="471" t="n"/>
-      <c r="I6" s="471" t="n"/>
-      <c r="J6" s="471" t="n"/>
-      <c r="K6" s="471" t="n"/>
-      <c r="L6" s="471" t="n"/>
-      <c r="M6" s="471" t="n"/>
-      <c r="N6" s="471" t="n"/>
-      <c r="O6" s="471" t="n"/>
-      <c r="P6" s="471" t="n"/>
-      <c r="Q6" s="471" t="n"/>
-      <c r="R6" s="471" t="n"/>
-      <c r="S6" s="471" t="n"/>
-      <c r="T6" s="471" t="n"/>
-      <c r="U6" s="471" t="n"/>
-      <c r="V6" s="471" t="n"/>
-      <c r="W6" s="471" t="n"/>
-      <c r="X6" s="471" t="n"/>
-      <c r="Y6" s="471" t="n"/>
-      <c r="Z6" s="471" t="n"/>
-      <c r="AA6" s="471" t="n"/>
-      <c r="AB6" s="471" t="n"/>
-      <c r="AC6" s="471" t="n"/>
-      <c r="AD6" s="471" t="n"/>
-      <c r="AE6" s="471" t="n"/>
-      <c r="AF6" s="471" t="n"/>
-      <c r="AG6" s="471" t="n"/>
-      <c r="AH6" s="471" t="n"/>
-      <c r="AI6" s="471" t="n"/>
-      <c r="AJ6" s="471" t="n"/>
-      <c r="AK6" s="471" t="n"/>
-      <c r="AL6" s="471" t="n"/>
-      <c r="AM6" s="471" t="n"/>
-      <c r="AN6" s="503" t="n"/>
-    </row>
-    <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="528" t="inlineStr">
-        <is>
-          <t>SOP-702</t>
-        </is>
-      </c>
-      <c r="B7" s="529" t="inlineStr">
-        <is>
-          <t>SOP-702 — Kiểm soát nhiễm bẩn, xác nhận độ sạch và tuyến đóng gói sạch | HESEM QMS</t>
-        </is>
-      </c>
-      <c r="C7" s="530" t="inlineStr">
-        <is>
-          <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/01-SOPs/07-SOP-700/sop-702-contamination-control-and-cleanliness.html</t>
-        </is>
-      </c>
-      <c r="D7" s="344" t="n"/>
-      <c r="E7" s="344" t="n"/>
-      <c r="F7" s="344" t="n"/>
-      <c r="G7" s="344" t="n"/>
-      <c r="H7" s="344" t="n"/>
-      <c r="I7" s="344" t="n"/>
-      <c r="J7" s="344" t="n"/>
-      <c r="K7" s="344" t="n"/>
-      <c r="L7" s="344" t="n"/>
-      <c r="M7" s="344" t="n"/>
-      <c r="N7" s="344" t="n"/>
-      <c r="O7" s="344" t="n"/>
-      <c r="P7" s="344" t="n"/>
-      <c r="Q7" s="344" t="n"/>
-      <c r="R7" s="344" t="n"/>
-      <c r="S7" s="344" t="n"/>
-      <c r="T7" s="344" t="n"/>
-      <c r="U7" s="344" t="n"/>
-      <c r="V7" s="344" t="n"/>
-      <c r="W7" s="344" t="n"/>
-      <c r="X7" s="344" t="n"/>
-      <c r="Y7" s="344" t="n"/>
-      <c r="Z7" s="344" t="n"/>
-      <c r="AA7" s="344" t="n"/>
-      <c r="AB7" s="344" t="n"/>
-      <c r="AC7" s="344" t="n"/>
-      <c r="AD7" s="344" t="n"/>
-      <c r="AE7" s="344" t="n"/>
-      <c r="AF7" s="344" t="n"/>
-      <c r="AG7" s="344" t="n"/>
-      <c r="AH7" s="344" t="n"/>
-      <c r="AI7" s="344" t="n"/>
-      <c r="AJ7" s="344" t="n"/>
-      <c r="AK7" s="344" t="n"/>
-      <c r="AL7" s="344" t="n"/>
-      <c r="AM7" s="344" t="n"/>
-      <c r="AN7" s="531" t="n"/>
-    </row>
-    <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="532" t="inlineStr">
-        <is>
-          <t>WI-716</t>
-        </is>
-      </c>
-      <c r="B8" s="533" t="inlineStr">
-        <is>
-          <t>WI-716 — Lắp sạch, tương thích chân không, bagging và bảo quản cho Job đặc biệt</t>
-        </is>
-      </c>
-      <c r="C8" s="534" t="inlineStr">
-        <is>
-          <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/02-Work-Instructions/07-WI-700/wi-716-vacuum-compatible-clean-build-and-bagging.html</t>
-        </is>
-      </c>
-      <c r="D8" s="356" t="n"/>
-      <c r="E8" s="356" t="n"/>
-      <c r="F8" s="356" t="n"/>
-      <c r="G8" s="356" t="n"/>
-      <c r="H8" s="356" t="n"/>
-      <c r="I8" s="356" t="n"/>
-      <c r="J8" s="356" t="n"/>
-      <c r="K8" s="356" t="n"/>
-      <c r="L8" s="356" t="n"/>
-      <c r="M8" s="356" t="n"/>
-      <c r="N8" s="356" t="n"/>
-      <c r="O8" s="356" t="n"/>
-      <c r="P8" s="356" t="n"/>
-      <c r="Q8" s="356" t="n"/>
-      <c r="R8" s="356" t="n"/>
-      <c r="S8" s="356" t="n"/>
-      <c r="T8" s="356" t="n"/>
-      <c r="U8" s="356" t="n"/>
-      <c r="V8" s="356" t="n"/>
-      <c r="W8" s="356" t="n"/>
-      <c r="X8" s="356" t="n"/>
-      <c r="Y8" s="356" t="n"/>
-      <c r="Z8" s="356" t="n"/>
-      <c r="AA8" s="356" t="n"/>
-      <c r="AB8" s="356" t="n"/>
-      <c r="AC8" s="356" t="n"/>
-      <c r="AD8" s="356" t="n"/>
-      <c r="AE8" s="356" t="n"/>
-      <c r="AF8" s="356" t="n"/>
-      <c r="AG8" s="356" t="n"/>
-      <c r="AH8" s="356" t="n"/>
-      <c r="AI8" s="356" t="n"/>
-      <c r="AJ8" s="356" t="n"/>
-      <c r="AK8" s="356" t="n"/>
-      <c r="AL8" s="356" t="n"/>
-      <c r="AM8" s="356" t="n"/>
-      <c r="AN8" s="535" t="n"/>
-    </row>
-    <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="543" t="inlineStr">
-        <is>
-          <t>ANNEX-QA-007</t>
-        </is>
-      </c>
-      <c r="B9" s="544" t="inlineStr">
-        <is>
-          <t>ANNEX-QA-007 — Chuẩn bề mặt, độ sạch, tương thích chân không, rò rỉ và xử lý đặc biệt</t>
-        </is>
-      </c>
-      <c r="C9" s="356" t="inlineStr">
-        <is>
-          <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/03-Reference/02-ANNEX-Standards/annex-qa-007-surface-finish-vacuum-compatibility.html</t>
-        </is>
-      </c>
-      <c r="D9" s="356" t="n"/>
-      <c r="E9" s="356" t="n"/>
-      <c r="F9" s="356" t="n"/>
-      <c r="G9" s="356" t="n"/>
-      <c r="H9" s="356" t="n"/>
-      <c r="I9" s="356" t="n"/>
-      <c r="J9" s="356" t="n"/>
-      <c r="K9" s="356" t="n"/>
-      <c r="L9" s="356" t="n"/>
-      <c r="M9" s="356" t="n"/>
-      <c r="N9" s="356" t="n"/>
-      <c r="O9" s="356" t="n"/>
-      <c r="P9" s="356" t="n"/>
-      <c r="Q9" s="356" t="n"/>
-      <c r="R9" s="356" t="n"/>
-      <c r="S9" s="356" t="n"/>
-      <c r="T9" s="356" t="n"/>
-      <c r="U9" s="356" t="n"/>
-      <c r="V9" s="356" t="n"/>
-      <c r="W9" s="356" t="n"/>
-      <c r="X9" s="356" t="n"/>
-      <c r="Y9" s="356" t="n"/>
-      <c r="Z9" s="356" t="n"/>
-      <c r="AA9" s="356" t="n"/>
-      <c r="AB9" s="356" t="n"/>
-      <c r="AC9" s="356" t="n"/>
-      <c r="AD9" s="356" t="n"/>
-      <c r="AE9" s="356" t="n"/>
-      <c r="AF9" s="356" t="n"/>
-      <c r="AG9" s="356" t="n"/>
-      <c r="AH9" s="356" t="n"/>
-      <c r="AI9" s="356" t="n"/>
-      <c r="AJ9" s="356" t="n"/>
-      <c r="AK9" s="356" t="n"/>
-      <c r="AL9" s="356" t="n"/>
-      <c r="AM9" s="356" t="n"/>
-      <c r="AN9" s="535" t="n"/>
-    </row>
-    <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="543" t="inlineStr">
-        <is>
-          <t>ANNEX-WHS-001</t>
-        </is>
-      </c>
-      <c r="B10" s="544" t="inlineStr">
-        <is>
-          <t>ANNEX-WHS-001 — Quy cách đóng gói, nhãn, bảo quản và bằng chứng gói hàng</t>
-        </is>
-      </c>
-      <c r="C10" s="356" t="inlineStr">
-        <is>
-          <t>qms.hesem.com.vn/03-Tai-Lieu-Van-Hanh/03-Reference/02-ANNEX-Standards/annex-whs-001-packaging-labeling-spec.html</t>
-        </is>
-      </c>
-      <c r="D10" s="356" t="n"/>
-      <c r="E10" s="356" t="n"/>
-      <c r="F10" s="356" t="n"/>
-      <c r="G10" s="356" t="n"/>
-      <c r="H10" s="356" t="n"/>
-      <c r="I10" s="356" t="n"/>
-      <c r="J10" s="356" t="n"/>
-      <c r="K10" s="356" t="n"/>
-      <c r="L10" s="356" t="n"/>
-      <c r="M10" s="356" t="n"/>
-      <c r="N10" s="356" t="n"/>
-      <c r="O10" s="356" t="n"/>
-      <c r="P10" s="356" t="n"/>
-      <c r="Q10" s="356" t="n"/>
-      <c r="R10" s="356" t="n"/>
-      <c r="S10" s="356" t="n"/>
-      <c r="T10" s="356" t="n"/>
-      <c r="U10" s="356" t="n"/>
-      <c r="V10" s="356" t="n"/>
-      <c r="W10" s="356" t="n"/>
-      <c r="X10" s="356" t="n"/>
-      <c r="Y10" s="356" t="n"/>
-      <c r="Z10" s="356" t="n"/>
-      <c r="AA10" s="356" t="n"/>
-      <c r="AB10" s="356" t="n"/>
-      <c r="AC10" s="356" t="n"/>
-      <c r="AD10" s="356" t="n"/>
-      <c r="AE10" s="356" t="n"/>
-      <c r="AF10" s="356" t="n"/>
-      <c r="AG10" s="356" t="n"/>
-      <c r="AH10" s="356" t="n"/>
-      <c r="AI10" s="356" t="n"/>
-      <c r="AJ10" s="356" t="n"/>
-      <c r="AK10" s="356" t="n"/>
-      <c r="AL10" s="356" t="n"/>
-      <c r="AM10" s="356" t="n"/>
-      <c r="AN10" s="535" t="n"/>
-    </row>
-    <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="543" t="inlineStr">
-        <is>
-          <t>Open When</t>
-        </is>
-      </c>
-      <c r="B11" s="544" t="inlineStr">
-        <is>
-          <t>Open before the controlled activity starts or before the release decision is taken. Do not populate it retrospectively after execution has already moved forward.</t>
-        </is>
-      </c>
-      <c r="C11" s="356" t="inlineStr">
-        <is>
-          <t>Operational trigger</t>
-        </is>
-      </c>
-      <c r="D11" s="356" t="n"/>
-      <c r="E11" s="356" t="n"/>
-      <c r="F11" s="356" t="n"/>
-      <c r="G11" s="356" t="n"/>
-      <c r="H11" s="356" t="n"/>
-      <c r="I11" s="356" t="n"/>
-      <c r="J11" s="356" t="n"/>
-      <c r="K11" s="356" t="n"/>
-      <c r="L11" s="356" t="n"/>
-      <c r="M11" s="356" t="n"/>
-      <c r="N11" s="356" t="n"/>
-      <c r="O11" s="356" t="n"/>
-      <c r="P11" s="356" t="n"/>
-      <c r="Q11" s="356" t="n"/>
-      <c r="R11" s="356" t="n"/>
-      <c r="S11" s="356" t="n"/>
-      <c r="T11" s="356" t="n"/>
-      <c r="U11" s="356" t="n"/>
-      <c r="V11" s="356" t="n"/>
-      <c r="W11" s="356" t="n"/>
-      <c r="X11" s="356" t="n"/>
-      <c r="Y11" s="356" t="n"/>
-      <c r="Z11" s="356" t="n"/>
-      <c r="AA11" s="356" t="n"/>
-      <c r="AB11" s="356" t="n"/>
-      <c r="AC11" s="356" t="n"/>
-      <c r="AD11" s="356" t="n"/>
-      <c r="AE11" s="356" t="n"/>
-      <c r="AF11" s="356" t="n"/>
-      <c r="AG11" s="356" t="n"/>
-      <c r="AH11" s="356" t="n"/>
-      <c r="AI11" s="356" t="n"/>
-      <c r="AJ11" s="356" t="n"/>
-      <c r="AK11" s="356" t="n"/>
-      <c r="AL11" s="356" t="n"/>
-      <c r="AM11" s="356" t="n"/>
-      <c r="AN11" s="535" t="n"/>
-    </row>
-    <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="545" t="inlineStr">
-        <is>
-          <t>Close When</t>
-        </is>
-      </c>
-      <c r="B12" s="546" t="inlineStr">
-        <is>
-          <t>Close only after the final gate disposition, result or release status is recorded, all conditions are assigned to an owner, and the evidence package reference is complete.</t>
-        </is>
-      </c>
-      <c r="C12" s="539" t="inlineStr">
-        <is>
-          <t>Release / closure rule</t>
-        </is>
-      </c>
-      <c r="D12" s="539" t="n"/>
-      <c r="E12" s="539" t="n"/>
-      <c r="F12" s="539" t="n"/>
-      <c r="G12" s="539" t="n"/>
-      <c r="H12" s="539" t="n"/>
-      <c r="I12" s="539" t="n"/>
-      <c r="J12" s="539" t="n"/>
-      <c r="K12" s="539" t="n"/>
-      <c r="L12" s="539" t="n"/>
-      <c r="M12" s="539" t="n"/>
-      <c r="N12" s="539" t="n"/>
-      <c r="O12" s="539" t="n"/>
-      <c r="P12" s="539" t="n"/>
-      <c r="Q12" s="539" t="n"/>
-      <c r="R12" s="539" t="n"/>
-      <c r="S12" s="539" t="n"/>
-      <c r="T12" s="539" t="n"/>
-      <c r="U12" s="539" t="n"/>
-      <c r="V12" s="539" t="n"/>
-      <c r="W12" s="539" t="n"/>
-      <c r="X12" s="539" t="n"/>
-      <c r="Y12" s="539" t="n"/>
-      <c r="Z12" s="539" t="n"/>
-      <c r="AA12" s="539" t="n"/>
-      <c r="AB12" s="539" t="n"/>
-      <c r="AC12" s="539" t="n"/>
-      <c r="AD12" s="539" t="n"/>
-      <c r="AE12" s="539" t="n"/>
-      <c r="AF12" s="539" t="n"/>
-      <c r="AG12" s="539" t="n"/>
-      <c r="AH12" s="539" t="n"/>
-      <c r="AI12" s="539" t="n"/>
-      <c r="AJ12" s="539" t="n"/>
-      <c r="AK12" s="539" t="n"/>
-      <c r="AL12" s="539" t="n"/>
-      <c r="AM12" s="539" t="n"/>
-      <c r="AN12" s="540" t="n"/>
-    </row>
-    <row r="13" ht="20" customHeight="1"/>
-    <row r="14" ht="20" customHeight="1"/>
-    <row r="15" ht="20" customHeight="1"/>
-    <row r="16" ht="20" customHeight="1"/>
-    <row r="17" ht="20" customHeight="1"/>
-    <row r="18" ht="20" customHeight="1"/>
-    <row r="19" ht="20" customHeight="1"/>
-    <row r="20" ht="20" customHeight="1"/>
-    <row r="21" ht="20" customHeight="1"/>
-    <row r="22" ht="20" customHeight="1"/>
-    <row r="23" ht="20" customHeight="1"/>
-    <row r="24" ht="20" customHeight="1"/>
-    <row r="25" ht="20" customHeight="1"/>
-    <row r="26" ht="20" customHeight="1"/>
-    <row r="27" ht="20" customHeight="1"/>
-    <row r="28" ht="20" customHeight="1"/>
-    <row r="29" ht="20" customHeight="1"/>
-    <row r="30" ht="20" customHeight="1"/>
-  </sheetData>
-  <sheetProtection selectLockedCells="1" selectUnlockedCells="1" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="0" insertColumns="0" pivotTables="1" deleteRows="0" formatCells="0" formatRows="0" sort="1"/>
-  <autoFilter ref="A4:C8"/>
-  <mergeCells count="2">
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A1:G1"/>
-  </mergeCells>
-  <pageMargins left="0.197" right="0.197" top="0.197" bottom="0.197" header="0.1" footer="0.1"/>
-  <pageSetup paperSize="9" fitToHeight="0" fitToWidth="1"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-</worksheet>
 </file>
--- a/04-Bieu-Mau/07-FRM-700/FRM-715_Vacuum_Compatible_Clean_Build_and_Bagging_Record.xlsx
+++ b/04-Bieu-Mau/07-FRM-700/FRM-715_Vacuum_Compatible_Clean_Build_and_Bagging_Record.xlsx
@@ -18,261 +18,10 @@
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="82">
-  <si>
-    <t>  1. REFERENCE INFORMATION</t>
-  </si>
-  <si>
-    <t>  2. CLEAN BUILD / BAGGING VERIFICATION</t>
-  </si>
-  <si>
-    <t>  3. CONDITIONS / ACTIONS / RELEASE</t>
-  </si>
-  <si>
-    <t>  4. APPROVAL / SIGN-OFF</t>
-  </si>
-  <si>
-    <t>#</t>
-  </si>
-  <si>
-    <t>=ROW()-ROW($A$16)+1</t>
-  </si>
-  <si>
-    <t>=ROW()-ROW($A$9)+1</t>
-  </si>
-  <si>
-    <t>ACTION_STATUS</t>
-  </si>
-  <si>
-    <t>APPROVED</t>
-  </si>
-  <si>
-    <t>Approved by</t>
-  </si>
-  <si>
-    <t>Bagging / Seal Ref</t>
-  </si>
-  <si>
-    <t>Bagging Configuration</t>
-  </si>
-  <si>
-    <t>CLEAN</t>
-  </si>
-  <si>
-    <t>CLEAN_CLASS_LIST</t>
-  </si>
-  <si>
-    <t>CLOSED</t>
-  </si>
-  <si>
-    <t>CONDITIONAL</t>
-  </si>
-  <si>
-    <t>Cat.</t>
-  </si>
-  <si>
-    <t>Clean Build / Bagging Requirement</t>
-  </si>
-  <si>
-    <t>Clean Build Record ID</t>
-  </si>
-  <si>
-    <t>Clean Class</t>
-  </si>
-  <si>
-    <t>Condition / Exception</t>
-  </si>
-  <si>
-    <t>Conditional Action Required (YES/NO)</t>
-  </si>
-  <si>
-    <t>DISPOSITION_GATE</t>
-  </si>
-  <si>
-    <t>Due Date</t>
-  </si>
-  <si>
-    <t>ENG</t>
-  </si>
-  <si>
-    <t>Evidence / Method</t>
-  </si>
-  <si>
-    <t>Evidence Package Ref</t>
-  </si>
-  <si>
-    <t>FAIL</t>
-  </si>
-  <si>
-    <t>FRM-715</t>
-  </si>
-  <si>
-    <t>Final Release Decision</t>
-  </si>
-  <si>
-    <t>General Manager</t>
-  </si>
-  <si>
-    <t>HESEM Engineering · ISO 9001 / AS9100 · Semiconductor Equipment Parts</t>
-  </si>
-  <si>
-    <t>HIGH CLEAN</t>
-  </si>
-  <si>
-    <t>HOLD</t>
-  </si>
-  <si>
-    <t>HR</t>
-  </si>
-  <si>
-    <t>IN PROGRESS</t>
-  </si>
-  <si>
-    <t>INEFFECTIVE</t>
-  </si>
-  <si>
-    <t>IT</t>
-  </si>
-  <si>
-    <t>Job / Part / Package Class</t>
-  </si>
-  <si>
-    <t>Line Clearance / Gowning</t>
-  </si>
-  <si>
-    <t>MGT</t>
-  </si>
-  <si>
-    <t>MONITORING</t>
-  </si>
-  <si>
-    <t>NA</t>
-  </si>
-  <si>
-    <t>NO</t>
-  </si>
-  <si>
-    <t>NOTICE: Confirm cleanliness, approved materials, line clearance, bagging sequence and seal integrity before release. This is a controlled gap form.</t>
-  </si>
-  <si>
-    <t>Name / Signature / Date</t>
-  </si>
-  <si>
-    <t>OPEN</t>
-  </si>
-  <si>
-    <t>OVERDUE</t>
-  </si>
-  <si>
-    <t>OWNER_DEPT</t>
-  </si>
-  <si>
-    <t>Owner</t>
-  </si>
-  <si>
-    <t>PASS</t>
-  </si>
-  <si>
-    <t>PLANNING</t>
-  </si>
-  <si>
-    <t>PROD</t>
-  </si>
-  <si>
-    <t>PUR</t>
-  </si>
-  <si>
-    <t>Prepared by</t>
-  </si>
-  <si>
-    <t>Prepared by / Date-Time</t>
-  </si>
-  <si>
-    <t>QA</t>
-  </si>
-  <si>
-    <t>Quality Management System · Controlled Document</t>
-  </si>
-  <si>
-    <t>REJECT</t>
-  </si>
-  <si>
-    <t>RESULT</t>
-  </si>
-  <si>
-    <t>Record Status</t>
-  </si>
-  <si>
-    <t>Ref.</t>
-  </si>
-  <si>
-    <t>Release Status</t>
-  </si>
-  <si>
-    <t>Required Action</t>
-  </si>
-  <si>
-    <t>Result</t>
-  </si>
-  <si>
-    <t>Reviewed by</t>
-  </si>
-  <si>
-    <t>SALES</t>
-  </si>
-  <si>
-    <t>STANDARD</t>
-  </si>
-  <si>
-    <t>STATUS</t>
-  </si>
-  <si>
-    <t>Status</t>
-  </si>
-  <si>
-    <t>V0</t>
-  </si>
-  <si>
-    <t>VAC-BUILD CONDITIONS / ACTIONS</t>
-  </si>
-  <si>
-    <t>VACUUM-COMPATIBLE</t>
-  </si>
-  <si>
-    <t>VERIFIED</t>
-  </si>
-  <si>
-    <t>Vacuum-Compatible Clean Build and Bagging Record</t>
-  </si>
-  <si>
-    <t>Verified by</t>
-  </si>
-  <si>
-    <t>WHS</t>
-  </si>
-  <si>
-    <t>Warehouse + QA</t>
-  </si>
-  <si>
-    <t>Warehouse Owner</t>
-  </si>
-  <si>
-    <t>YES</t>
-  </si>
-  <si>
-    <t>YES_NO</t>
-  </si>
-  <si>
-    <t>YYYY-MM-DD</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="89">
+  <fonts count="90">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -773,6 +522,9 @@
       <color theme="1"/>
       <sz val="11"/>
     </font>
+    <font>
+      <name val="Segoe UI"/>
+    </font>
   </fonts>
   <fills count="54">
     <fill>
@@ -1042,7 +794,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="367">
+  <borders count="394">
     <border>
       <left/>
       <right/>
@@ -5023,11 +4775,341 @@
         <color rgb="002C9CD7"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00C5D9E8"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00C5D9E8"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00E2E8F0"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="000078D4"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00E2E8F0"/>
+      </left>
+      <right style="thin">
+        <color rgb="000078D4"/>
+      </right>
+      <top style="thin">
+        <color rgb="000078D4"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="000078D4"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00E2E8F0"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00E2E8F0"/>
+      </left>
+      <right style="thin">
+        <color rgb="000078D4"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="000078D4"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="000078D4"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00E2E8F0"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="000078D4"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00E2E8F0"/>
+      </left>
+      <right style="thin">
+        <color rgb="000078D4"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="000078D4"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00E2E8F0"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="000078D4"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="000078D4"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00E2E8F0"/>
+      </left>
+      <right style="thin">
+        <color rgb="000078D4"/>
+      </right>
+      <top style="thin">
+        <color rgb="000078D4"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="000078D4"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00E2E8F0"/>
+      </left>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="000078D4"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="000078D4"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="000078D4"/>
+      </left>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="000078D4"/>
+      </left>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="000078D4"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00E2E8F0"/>
+      </left>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="000078D4"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="000078D4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="000078D4"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="000078D4"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00E2E8F0"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00E2E8F0"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="000078D4"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="000078D4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00E2E8F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="000078D4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="79" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="674">
+  <cellXfs count="810">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -6713,6 +6795,363 @@
     <xf numFmtId="0" fontId="82" fillId="53" borderId="323" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="89" fillId="4" borderId="293" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="294" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="295" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="81" fillId="0" borderId="294" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="296" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="298" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="299" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="82" fillId="48" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="283" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="51" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="83" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="303" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="304" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="305" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="84" fillId="0" borderId="304" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="48" borderId="304" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="367" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="51" fillId="4" borderId="304" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="89" fillId="47" borderId="271" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="89" fillId="0" borderId="271" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="82" fillId="6" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="82" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="79" fillId="4" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="79" fillId="4" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="79" fillId="4" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="79" fillId="6" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="79" fillId="6" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="79" fillId="4" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="79" fillId="4" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="271" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="271" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="369" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="369" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="370" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="371" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="372" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="372" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="373" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="374" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="375" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="375" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="376" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="130" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="377" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="378" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="369" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="369" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="370" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="371" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="372" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="372" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="373" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="374" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="375" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="375" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="376" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="369" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="370" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="4" borderId="371" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="4" borderId="372" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="4" borderId="373" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="89" fillId="4" borderId="333" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="81" fillId="0" borderId="295" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="4" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="89" fillId="4" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="89" fillId="4" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="89" fillId="4" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="89" fillId="6" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="89" fillId="6" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="89" fillId="4" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="89" fillId="4" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="271" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="89" fillId="4" borderId="271" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="87" fillId="4" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="87" fillId="4" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="87" fillId="4" borderId="9" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="87" fillId="4" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="87" fillId="6" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="87" fillId="6" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="87" fillId="4" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="87" fillId="4" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="3" borderId="269" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="3" borderId="379" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="3" borderId="379" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="3" borderId="378" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="380" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="268" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="268" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="373" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="380" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="268" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="268" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="373" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="381" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="382" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="376" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="384" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="384" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="387" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="385" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="385" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="390" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="383" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="386" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="388" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="135" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="389" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="132" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="270" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="392" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="392" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="387" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="393" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="390" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -6798,7 +7237,7 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1792692" cy="517122"/>
+    <ext cx="1552575" cy="438150"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -6812,9 +7251,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -6831,7 +7267,7 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1303776" cy="376089"/>
+    <ext cx="1123950" cy="323850"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -6845,37 +7281,36 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
   </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>1</col>
+      <col>0</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="619125" cy="619125"/>
+    <ext cx="1552575" cy="438150"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId2"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -7267,7 +7702,7 @@
     <col width="2.33" customWidth="1" min="56" max="56"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1">
+    <row r="1" hidden="1">
       <c r="A1" s="547" t="n"/>
       <c r="B1" s="548" t="n"/>
       <c r="C1" s="548" t="n"/>
@@ -7334,596 +7769,706 @@
       <c r="BD1" s="549" t="n"/>
     </row>
     <row r="2" ht="15" customHeight="1">
-      <c r="A2" s="554" t="n"/>
-      <c r="K2" s="555" t="n"/>
-      <c r="L2" s="554" t="n"/>
-      <c r="AP2" s="555" t="n"/>
-      <c r="AQ2" s="556" t="n"/>
-      <c r="AR2" s="422" t="n"/>
-      <c r="AS2" s="422" t="n"/>
-      <c r="AT2" s="422" t="n"/>
-      <c r="AU2" s="422" t="n"/>
-      <c r="AV2" s="557" t="n"/>
-      <c r="AW2" s="558" t="inlineStr">
+      <c r="A2" s="1" t="n"/>
+      <c r="B2" s="694" t="n"/>
+      <c r="C2" s="694" t="n"/>
+      <c r="D2" s="694" t="n"/>
+      <c r="E2" s="694" t="n"/>
+      <c r="F2" s="694" t="n"/>
+      <c r="G2" s="694" t="n"/>
+      <c r="H2" s="694" t="n"/>
+      <c r="I2" s="694" t="n"/>
+      <c r="J2" s="694" t="n"/>
+      <c r="K2" s="695" t="n"/>
+      <c r="L2" s="694" t="n"/>
+      <c r="M2" s="694" t="n"/>
+      <c r="N2" s="694" t="n"/>
+      <c r="O2" s="694" t="n"/>
+      <c r="P2" s="694" t="n"/>
+      <c r="Q2" s="694" t="n"/>
+      <c r="R2" s="694" t="n"/>
+      <c r="S2" s="694" t="n"/>
+      <c r="T2" s="694" t="n"/>
+      <c r="U2" s="694" t="n"/>
+      <c r="V2" s="694" t="n"/>
+      <c r="W2" s="694" t="n"/>
+      <c r="X2" s="694" t="n"/>
+      <c r="Y2" s="694" t="n"/>
+      <c r="Z2" s="694" t="n"/>
+      <c r="AA2" s="694" t="n"/>
+      <c r="AB2" s="694" t="n"/>
+      <c r="AC2" s="694" t="n"/>
+      <c r="AD2" s="694" t="n"/>
+      <c r="AE2" s="694" t="n"/>
+      <c r="AF2" s="694" t="n"/>
+      <c r="AG2" s="694" t="n"/>
+      <c r="AH2" s="694" t="n"/>
+      <c r="AI2" s="694" t="n"/>
+      <c r="AJ2" s="694" t="n"/>
+      <c r="AK2" s="694" t="n"/>
+      <c r="AL2" s="694" t="n"/>
+      <c r="AM2" s="694" t="n"/>
+      <c r="AN2" s="694" t="n"/>
+      <c r="AO2" s="694" t="n"/>
+      <c r="AP2" s="695" t="n"/>
+      <c r="AQ2" s="696" t="n"/>
+      <c r="AR2" s="697" t="n"/>
+      <c r="AS2" s="697" t="n"/>
+      <c r="AT2" s="697" t="n"/>
+      <c r="AU2" s="697" t="n"/>
+      <c r="AV2" s="698" t="n"/>
+      <c r="AW2" s="7" t="inlineStr">
         <is>
           <t>V0</t>
         </is>
       </c>
-      <c r="AX2" s="422" t="n"/>
-      <c r="AY2" s="422" t="n"/>
-      <c r="AZ2" s="422" t="n"/>
-      <c r="BA2" s="422" t="n"/>
-      <c r="BB2" s="422" t="n"/>
-      <c r="BC2" s="422" t="n"/>
-      <c r="BD2" s="559" t="n"/>
+      <c r="AX2" s="699" t="n"/>
+      <c r="AY2" s="699" t="n"/>
+      <c r="AZ2" s="699" t="n"/>
+      <c r="BA2" s="699" t="n"/>
+      <c r="BB2" s="699" t="n"/>
+      <c r="BC2" s="699" t="n"/>
+      <c r="BD2" s="700" t="n"/>
     </row>
     <row r="3" ht="15" customHeight="1">
-      <c r="A3" s="554" t="n"/>
-      <c r="K3" s="555" t="n"/>
-      <c r="L3" s="554" t="n"/>
-      <c r="AP3" s="555" t="n"/>
-      <c r="AQ3" s="556" t="n"/>
-      <c r="AR3" s="422" t="n"/>
-      <c r="AS3" s="422" t="n"/>
-      <c r="AT3" s="422" t="n"/>
-      <c r="AU3" s="422" t="n"/>
-      <c r="AV3" s="557" t="n"/>
-      <c r="AW3" s="558" t="inlineStr">
+      <c r="A3" s="701" t="n"/>
+      <c r="B3" s="25" t="n"/>
+      <c r="C3" s="25" t="n"/>
+      <c r="D3" s="25" t="n"/>
+      <c r="E3" s="25" t="n"/>
+      <c r="F3" s="25" t="n"/>
+      <c r="G3" s="25" t="n"/>
+      <c r="H3" s="25" t="n"/>
+      <c r="I3" s="25" t="n"/>
+      <c r="J3" s="25" t="n"/>
+      <c r="K3" s="702" t="n"/>
+      <c r="L3" s="25" t="n"/>
+      <c r="M3" s="25" t="n"/>
+      <c r="N3" s="25" t="n"/>
+      <c r="O3" s="25" t="n"/>
+      <c r="P3" s="25" t="n"/>
+      <c r="Q3" s="25" t="n"/>
+      <c r="R3" s="25" t="n"/>
+      <c r="S3" s="25" t="n"/>
+      <c r="T3" s="25" t="n"/>
+      <c r="U3" s="25" t="n"/>
+      <c r="V3" s="25" t="n"/>
+      <c r="W3" s="25" t="n"/>
+      <c r="X3" s="25" t="n"/>
+      <c r="Y3" s="25" t="n"/>
+      <c r="Z3" s="25" t="n"/>
+      <c r="AA3" s="25" t="n"/>
+      <c r="AB3" s="25" t="n"/>
+      <c r="AC3" s="25" t="n"/>
+      <c r="AD3" s="25" t="n"/>
+      <c r="AE3" s="25" t="n"/>
+      <c r="AF3" s="25" t="n"/>
+      <c r="AG3" s="25" t="n"/>
+      <c r="AH3" s="25" t="n"/>
+      <c r="AI3" s="25" t="n"/>
+      <c r="AJ3" s="25" t="n"/>
+      <c r="AK3" s="25" t="n"/>
+      <c r="AL3" s="25" t="n"/>
+      <c r="AM3" s="25" t="n"/>
+      <c r="AN3" s="25" t="n"/>
+      <c r="AO3" s="25" t="n"/>
+      <c r="AP3" s="702" t="n"/>
+      <c r="AQ3" s="703" t="n"/>
+      <c r="AR3" s="704" t="n"/>
+      <c r="AS3" s="704" t="n"/>
+      <c r="AT3" s="704" t="n"/>
+      <c r="AU3" s="704" t="n"/>
+      <c r="AV3" s="705" t="n"/>
+      <c r="AW3" s="14" t="inlineStr">
         <is>
           <t>YYYY-MM-DD</t>
         </is>
       </c>
-      <c r="AX3" s="422" t="n"/>
-      <c r="AY3" s="422" t="n"/>
-      <c r="AZ3" s="422" t="n"/>
-      <c r="BA3" s="422" t="n"/>
-      <c r="BB3" s="422" t="n"/>
-      <c r="BC3" s="422" t="n"/>
-      <c r="BD3" s="559" t="n"/>
+      <c r="AX3" s="706" t="n"/>
+      <c r="AY3" s="706" t="n"/>
+      <c r="AZ3" s="706" t="n"/>
+      <c r="BA3" s="706" t="n"/>
+      <c r="BB3" s="706" t="n"/>
+      <c r="BC3" s="706" t="n"/>
+      <c r="BD3" s="707" t="n"/>
     </row>
     <row r="4" ht="15" customHeight="1">
-      <c r="A4" s="554" t="n"/>
-      <c r="K4" s="555" t="n"/>
-      <c r="L4" s="560" t="inlineStr">
+      <c r="A4" s="701" t="n"/>
+      <c r="B4" s="25" t="n"/>
+      <c r="C4" s="25" t="n"/>
+      <c r="D4" s="25" t="n"/>
+      <c r="E4" s="25" t="n"/>
+      <c r="F4" s="25" t="n"/>
+      <c r="G4" s="25" t="n"/>
+      <c r="H4" s="25" t="n"/>
+      <c r="I4" s="25" t="n"/>
+      <c r="J4" s="25" t="n"/>
+      <c r="K4" s="702" t="n"/>
+      <c r="L4" s="708" t="inlineStr">
         <is>
           <t>Quality Management System · Controlled Document</t>
         </is>
       </c>
-      <c r="AP4" s="555" t="n"/>
-      <c r="AQ4" s="556" t="n"/>
-      <c r="AR4" s="422" t="n"/>
-      <c r="AS4" s="422" t="n"/>
-      <c r="AT4" s="422" t="n"/>
-      <c r="AU4" s="422" t="n"/>
-      <c r="AV4" s="557" t="n"/>
-      <c r="AW4" s="558" t="inlineStr">
+      <c r="M4" s="25" t="n"/>
+      <c r="N4" s="25" t="n"/>
+      <c r="O4" s="25" t="n"/>
+      <c r="P4" s="25" t="n"/>
+      <c r="Q4" s="25" t="n"/>
+      <c r="R4" s="25" t="n"/>
+      <c r="S4" s="25" t="n"/>
+      <c r="T4" s="25" t="n"/>
+      <c r="U4" s="25" t="n"/>
+      <c r="V4" s="25" t="n"/>
+      <c r="W4" s="25" t="n"/>
+      <c r="X4" s="25" t="n"/>
+      <c r="Y4" s="25" t="n"/>
+      <c r="Z4" s="25" t="n"/>
+      <c r="AA4" s="25" t="n"/>
+      <c r="AB4" s="25" t="n"/>
+      <c r="AC4" s="25" t="n"/>
+      <c r="AD4" s="25" t="n"/>
+      <c r="AE4" s="25" t="n"/>
+      <c r="AF4" s="25" t="n"/>
+      <c r="AG4" s="25" t="n"/>
+      <c r="AH4" s="25" t="n"/>
+      <c r="AI4" s="25" t="n"/>
+      <c r="AJ4" s="25" t="n"/>
+      <c r="AK4" s="25" t="n"/>
+      <c r="AL4" s="25" t="n"/>
+      <c r="AM4" s="25" t="n"/>
+      <c r="AN4" s="25" t="n"/>
+      <c r="AO4" s="25" t="n"/>
+      <c r="AP4" s="702" t="n"/>
+      <c r="AQ4" s="703" t="n"/>
+      <c r="AR4" s="704" t="n"/>
+      <c r="AS4" s="704" t="n"/>
+      <c r="AT4" s="704" t="n"/>
+      <c r="AU4" s="704" t="n"/>
+      <c r="AV4" s="705" t="n"/>
+      <c r="AW4" s="14" t="inlineStr">
         <is>
           <t>Warehouse + QA</t>
         </is>
       </c>
-      <c r="AX4" s="422" t="n"/>
-      <c r="AY4" s="422" t="n"/>
-      <c r="AZ4" s="422" t="n"/>
-      <c r="BA4" s="422" t="n"/>
-      <c r="BB4" s="422" t="n"/>
-      <c r="BC4" s="422" t="n"/>
-      <c r="BD4" s="559" t="n"/>
+      <c r="AX4" s="706" t="n"/>
+      <c r="AY4" s="706" t="n"/>
+      <c r="AZ4" s="706" t="n"/>
+      <c r="BA4" s="706" t="n"/>
+      <c r="BB4" s="706" t="n"/>
+      <c r="BC4" s="706" t="n"/>
+      <c r="BD4" s="707" t="n"/>
     </row>
     <row r="5" ht="15" customHeight="1">
-      <c r="A5" s="561" t="n"/>
-      <c r="B5" s="562" t="n"/>
-      <c r="C5" s="562" t="n"/>
-      <c r="D5" s="562" t="n"/>
-      <c r="E5" s="562" t="n"/>
-      <c r="F5" s="562" t="n"/>
-      <c r="G5" s="562" t="n"/>
-      <c r="H5" s="562" t="n"/>
-      <c r="I5" s="562" t="n"/>
-      <c r="J5" s="562" t="n"/>
-      <c r="K5" s="563" t="n"/>
-      <c r="L5" s="564" t="inlineStr">
+      <c r="A5" s="701" t="n"/>
+      <c r="B5" s="25" t="n"/>
+      <c r="C5" s="25" t="n"/>
+      <c r="D5" s="25" t="n"/>
+      <c r="E5" s="25" t="n"/>
+      <c r="F5" s="25" t="n"/>
+      <c r="G5" s="25" t="n"/>
+      <c r="H5" s="25" t="n"/>
+      <c r="I5" s="25" t="n"/>
+      <c r="J5" s="25" t="n"/>
+      <c r="K5" s="702" t="n"/>
+      <c r="L5" s="709" t="inlineStr">
         <is>
           <t>HESEM Engineering · ISO 9001 / AS9100 · Semiconductor Equipment Parts</t>
         </is>
       </c>
-      <c r="M5" s="562" t="n"/>
-      <c r="N5" s="562" t="n"/>
-      <c r="O5" s="562" t="n"/>
-      <c r="P5" s="562" t="n"/>
-      <c r="Q5" s="562" t="n"/>
-      <c r="R5" s="562" t="n"/>
-      <c r="S5" s="562" t="n"/>
-      <c r="T5" s="562" t="n"/>
-      <c r="U5" s="562" t="n"/>
-      <c r="V5" s="562" t="n"/>
-      <c r="W5" s="562" t="n"/>
-      <c r="X5" s="562" t="n"/>
-      <c r="Y5" s="562" t="n"/>
-      <c r="Z5" s="562" t="n"/>
-      <c r="AA5" s="562" t="n"/>
-      <c r="AB5" s="562" t="n"/>
-      <c r="AC5" s="562" t="n"/>
-      <c r="AD5" s="562" t="n"/>
-      <c r="AE5" s="562" t="n"/>
-      <c r="AF5" s="562" t="n"/>
-      <c r="AG5" s="562" t="n"/>
-      <c r="AH5" s="562" t="n"/>
-      <c r="AI5" s="562" t="n"/>
-      <c r="AJ5" s="562" t="n"/>
-      <c r="AK5" s="562" t="n"/>
-      <c r="AL5" s="562" t="n"/>
-      <c r="AM5" s="562" t="n"/>
-      <c r="AN5" s="562" t="n"/>
-      <c r="AO5" s="562" t="n"/>
-      <c r="AP5" s="563" t="n"/>
-      <c r="AQ5" s="565" t="n"/>
-      <c r="AR5" s="566" t="n"/>
-      <c r="AS5" s="566" t="n"/>
-      <c r="AT5" s="566" t="n"/>
-      <c r="AU5" s="566" t="n"/>
-      <c r="AV5" s="567" t="n"/>
-      <c r="AW5" s="568" t="inlineStr">
+      <c r="M5" s="25" t="n"/>
+      <c r="N5" s="25" t="n"/>
+      <c r="O5" s="25" t="n"/>
+      <c r="P5" s="25" t="n"/>
+      <c r="Q5" s="25" t="n"/>
+      <c r="R5" s="25" t="n"/>
+      <c r="S5" s="25" t="n"/>
+      <c r="T5" s="25" t="n"/>
+      <c r="U5" s="25" t="n"/>
+      <c r="V5" s="25" t="n"/>
+      <c r="W5" s="25" t="n"/>
+      <c r="X5" s="25" t="n"/>
+      <c r="Y5" s="25" t="n"/>
+      <c r="Z5" s="25" t="n"/>
+      <c r="AA5" s="25" t="n"/>
+      <c r="AB5" s="25" t="n"/>
+      <c r="AC5" s="25" t="n"/>
+      <c r="AD5" s="25" t="n"/>
+      <c r="AE5" s="25" t="n"/>
+      <c r="AF5" s="25" t="n"/>
+      <c r="AG5" s="25" t="n"/>
+      <c r="AH5" s="25" t="n"/>
+      <c r="AI5" s="25" t="n"/>
+      <c r="AJ5" s="25" t="n"/>
+      <c r="AK5" s="25" t="n"/>
+      <c r="AL5" s="25" t="n"/>
+      <c r="AM5" s="25" t="n"/>
+      <c r="AN5" s="25" t="n"/>
+      <c r="AO5" s="25" t="n"/>
+      <c r="AP5" s="702" t="n"/>
+      <c r="AQ5" s="703" t="n"/>
+      <c r="AR5" s="704" t="n"/>
+      <c r="AS5" s="704" t="n"/>
+      <c r="AT5" s="704" t="n"/>
+      <c r="AU5" s="704" t="n"/>
+      <c r="AV5" s="705" t="n"/>
+      <c r="AW5" s="14" t="inlineStr">
         <is>
           <t>General Manager</t>
         </is>
       </c>
-      <c r="AX5" s="566" t="n"/>
-      <c r="AY5" s="566" t="n"/>
-      <c r="AZ5" s="566" t="n"/>
-      <c r="BA5" s="566" t="n"/>
-      <c r="BB5" s="566" t="n"/>
-      <c r="BC5" s="566" t="n"/>
-      <c r="BD5" s="569" t="n"/>
+      <c r="AX5" s="706" t="n"/>
+      <c r="AY5" s="706" t="n"/>
+      <c r="AZ5" s="706" t="n"/>
+      <c r="BA5" s="706" t="n"/>
+      <c r="BB5" s="706" t="n"/>
+      <c r="BC5" s="706" t="n"/>
+      <c r="BD5" s="707" t="n"/>
     </row>
-    <row r="6" ht="1.5" customHeight="1">
-      <c r="A6" s="466" t="n"/>
-      <c r="B6" s="466" t="n"/>
-      <c r="C6" s="466" t="n"/>
-      <c r="D6" s="466" t="n"/>
-      <c r="E6" s="466" t="n"/>
-      <c r="F6" s="466" t="n"/>
-      <c r="G6" s="466" t="n"/>
-      <c r="H6" s="466" t="n"/>
-      <c r="I6" s="466" t="n"/>
-      <c r="J6" s="466" t="n"/>
-      <c r="K6" s="466" t="n"/>
-      <c r="L6" s="466" t="n"/>
-      <c r="M6" s="466" t="n"/>
-      <c r="N6" s="466" t="n"/>
-      <c r="O6" s="466" t="n"/>
-      <c r="P6" s="466" t="n"/>
-      <c r="Q6" s="466" t="n"/>
-      <c r="R6" s="466" t="n"/>
-      <c r="S6" s="466" t="n"/>
-      <c r="T6" s="466" t="n"/>
-      <c r="U6" s="466" t="n"/>
-      <c r="V6" s="466" t="n"/>
-      <c r="W6" s="466" t="n"/>
-      <c r="X6" s="466" t="n"/>
-      <c r="Y6" s="466" t="n"/>
-      <c r="Z6" s="466" t="n"/>
-      <c r="AA6" s="466" t="n"/>
-      <c r="AB6" s="466" t="n"/>
-      <c r="AC6" s="466" t="n"/>
-      <c r="AD6" s="466" t="n"/>
-      <c r="AE6" s="466" t="n"/>
-      <c r="AF6" s="466" t="n"/>
-      <c r="AG6" s="466" t="n"/>
-      <c r="AH6" s="466" t="n"/>
-      <c r="AI6" s="466" t="n"/>
-      <c r="AJ6" s="466" t="n"/>
-      <c r="AK6" s="466" t="n"/>
-      <c r="AL6" s="466" t="n"/>
-      <c r="AM6" s="466" t="n"/>
-      <c r="AN6" s="466" t="n"/>
-      <c r="AO6" s="466" t="n"/>
-      <c r="AP6" s="466" t="n"/>
-      <c r="AQ6" s="466" t="n"/>
-      <c r="AR6" s="466" t="n"/>
-      <c r="AS6" s="466" t="n"/>
-      <c r="AT6" s="466" t="n"/>
-      <c r="AU6" s="466" t="n"/>
-      <c r="AV6" s="466" t="n"/>
-      <c r="AW6" s="466" t="n"/>
-      <c r="AX6" s="466" t="n"/>
-      <c r="AY6" s="466" t="n"/>
-      <c r="AZ6" s="466" t="n"/>
-      <c r="BA6" s="466" t="n"/>
-      <c r="BB6" s="466" t="n"/>
-      <c r="BC6" s="466" t="n"/>
-      <c r="BD6" s="466" t="n"/>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" s="710" t="n"/>
+      <c r="B6" s="711" t="n"/>
+      <c r="C6" s="711" t="n"/>
+      <c r="D6" s="711" t="n"/>
+      <c r="E6" s="711" t="n"/>
+      <c r="F6" s="711" t="n"/>
+      <c r="G6" s="711" t="n"/>
+      <c r="H6" s="711" t="n"/>
+      <c r="I6" s="711" t="n"/>
+      <c r="J6" s="711" t="n"/>
+      <c r="K6" s="712" t="n"/>
+      <c r="L6" s="711" t="n"/>
+      <c r="M6" s="711" t="n"/>
+      <c r="N6" s="711" t="n"/>
+      <c r="O6" s="711" t="n"/>
+      <c r="P6" s="711" t="n"/>
+      <c r="Q6" s="711" t="n"/>
+      <c r="R6" s="711" t="n"/>
+      <c r="S6" s="711" t="n"/>
+      <c r="T6" s="711" t="n"/>
+      <c r="U6" s="711" t="n"/>
+      <c r="V6" s="711" t="n"/>
+      <c r="W6" s="711" t="n"/>
+      <c r="X6" s="711" t="n"/>
+      <c r="Y6" s="711" t="n"/>
+      <c r="Z6" s="711" t="n"/>
+      <c r="AA6" s="711" t="n"/>
+      <c r="AB6" s="711" t="n"/>
+      <c r="AC6" s="711" t="n"/>
+      <c r="AD6" s="711" t="n"/>
+      <c r="AE6" s="711" t="n"/>
+      <c r="AF6" s="711" t="n"/>
+      <c r="AG6" s="711" t="n"/>
+      <c r="AH6" s="711" t="n"/>
+      <c r="AI6" s="711" t="n"/>
+      <c r="AJ6" s="711" t="n"/>
+      <c r="AK6" s="711" t="n"/>
+      <c r="AL6" s="711" t="n"/>
+      <c r="AM6" s="711" t="n"/>
+      <c r="AN6" s="711" t="n"/>
+      <c r="AO6" s="711" t="n"/>
+      <c r="AP6" s="712" t="n"/>
+      <c r="AQ6" s="713" t="n"/>
+      <c r="AR6" s="713" t="n"/>
+      <c r="AS6" s="713" t="n"/>
+      <c r="AT6" s="713" t="n"/>
+      <c r="AU6" s="713" t="n"/>
+      <c r="AV6" s="714" t="n"/>
+      <c r="AW6" s="715" t="n"/>
+      <c r="AX6" s="715" t="n"/>
+      <c r="AY6" s="715" t="n"/>
+      <c r="AZ6" s="715" t="n"/>
+      <c r="BA6" s="715" t="n"/>
+      <c r="BB6" s="715" t="n"/>
+      <c r="BC6" s="715" t="n"/>
+      <c r="BD6" s="716" t="n"/>
     </row>
-    <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="570" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  1. REFERENCE INFORMATION</t>
-        </is>
-      </c>
-      <c r="B7" s="571" t="n"/>
-      <c r="C7" s="571" t="n"/>
-      <c r="D7" s="571" t="n"/>
-      <c r="E7" s="571" t="n"/>
-      <c r="F7" s="571" t="n"/>
-      <c r="G7" s="571" t="n"/>
-      <c r="H7" s="571" t="n"/>
-      <c r="I7" s="571" t="n"/>
-      <c r="J7" s="571" t="n"/>
-      <c r="K7" s="571" t="n"/>
-      <c r="L7" s="571" t="n"/>
-      <c r="M7" s="571" t="n"/>
-      <c r="N7" s="571" t="n"/>
-      <c r="O7" s="571" t="n"/>
-      <c r="P7" s="571" t="n"/>
-      <c r="Q7" s="571" t="n"/>
-      <c r="R7" s="571" t="n"/>
-      <c r="S7" s="571" t="n"/>
-      <c r="T7" s="571" t="n"/>
-      <c r="U7" s="571" t="n"/>
-      <c r="V7" s="571" t="n"/>
-      <c r="W7" s="571" t="n"/>
-      <c r="X7" s="571" t="n"/>
-      <c r="Y7" s="571" t="n"/>
-      <c r="Z7" s="571" t="n"/>
-      <c r="AA7" s="571" t="n"/>
-      <c r="AB7" s="571" t="n"/>
-      <c r="AC7" s="571" t="n"/>
-      <c r="AD7" s="571" t="n"/>
-      <c r="AE7" s="571" t="n"/>
-      <c r="AF7" s="571" t="n"/>
-      <c r="AG7" s="571" t="n"/>
-      <c r="AH7" s="571" t="n"/>
-      <c r="AI7" s="571" t="n"/>
-      <c r="AJ7" s="571" t="n"/>
-      <c r="AK7" s="571" t="n"/>
-      <c r="AL7" s="571" t="n"/>
-      <c r="AM7" s="571" t="n"/>
-      <c r="AN7" s="571" t="n"/>
-      <c r="AO7" s="571" t="n"/>
-      <c r="AP7" s="571" t="n"/>
-      <c r="AQ7" s="571" t="n"/>
-      <c r="AR7" s="571" t="n"/>
-      <c r="AS7" s="571" t="n"/>
-      <c r="AT7" s="571" t="n"/>
-      <c r="AU7" s="571" t="n"/>
-      <c r="AV7" s="571" t="n"/>
-      <c r="AW7" s="571" t="n"/>
-      <c r="AX7" s="571" t="n"/>
-      <c r="AY7" s="571" t="n"/>
-      <c r="AZ7" s="571" t="n"/>
-      <c r="BA7" s="571" t="n"/>
-      <c r="BB7" s="571" t="n"/>
-      <c r="BC7" s="571" t="n"/>
-      <c r="BD7" s="572" t="n"/>
+    <row r="7" ht="4" customHeight="1">
+      <c r="A7" s="717" t="n"/>
+      <c r="B7" s="718" t="n"/>
+      <c r="C7" s="718" t="n"/>
+      <c r="D7" s="718" t="n"/>
+      <c r="E7" s="718" t="n"/>
+      <c r="F7" s="718" t="n"/>
+      <c r="G7" s="718" t="n"/>
+      <c r="H7" s="718" t="n"/>
+      <c r="I7" s="718" t="n"/>
+      <c r="J7" s="718" t="n"/>
+      <c r="K7" s="718" t="n"/>
+      <c r="L7" s="718" t="n"/>
+      <c r="M7" s="718" t="n"/>
+      <c r="N7" s="718" t="n"/>
+      <c r="O7" s="718" t="n"/>
+      <c r="P7" s="718" t="n"/>
+      <c r="Q7" s="718" t="n"/>
+      <c r="R7" s="718" t="n"/>
+      <c r="S7" s="718" t="n"/>
+      <c r="T7" s="718" t="n"/>
+      <c r="U7" s="718" t="n"/>
+      <c r="V7" s="718" t="n"/>
+      <c r="W7" s="718" t="n"/>
+      <c r="X7" s="718" t="n"/>
+      <c r="Y7" s="718" t="n"/>
+      <c r="Z7" s="718" t="n"/>
+      <c r="AA7" s="718" t="n"/>
+      <c r="AB7" s="718" t="n"/>
+      <c r="AC7" s="718" t="n"/>
+      <c r="AD7" s="718" t="n"/>
+      <c r="AE7" s="718" t="n"/>
+      <c r="AF7" s="718" t="n"/>
+      <c r="AG7" s="718" t="n"/>
+      <c r="AH7" s="718" t="n"/>
+      <c r="AI7" s="718" t="n"/>
+      <c r="AJ7" s="718" t="n"/>
+      <c r="AK7" s="718" t="n"/>
+      <c r="AL7" s="718" t="n"/>
+      <c r="AM7" s="718" t="n"/>
+      <c r="AN7" s="718" t="n"/>
+      <c r="AO7" s="718" t="n"/>
+      <c r="AP7" s="718" t="n"/>
+      <c r="AQ7" s="718" t="n"/>
+      <c r="AR7" s="718" t="n"/>
+      <c r="AS7" s="718" t="n"/>
+      <c r="AT7" s="718" t="n"/>
+      <c r="AU7" s="718" t="n"/>
+      <c r="AV7" s="718" t="n"/>
+      <c r="AW7" s="718" t="n"/>
+      <c r="AX7" s="718" t="n"/>
+      <c r="AY7" s="718" t="n"/>
+      <c r="AZ7" s="718" t="n"/>
+      <c r="BA7" s="718" t="n"/>
+      <c r="BB7" s="718" t="n"/>
+      <c r="BC7" s="718" t="n"/>
+      <c r="BD7" s="718" t="n"/>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="470" t="inlineStr">
+      <c r="A8" s="719" t="inlineStr">
         <is>
           <t>Clean Build Record ID</t>
         </is>
       </c>
-      <c r="B8" s="573" t="n"/>
-      <c r="C8" s="573" t="n"/>
-      <c r="D8" s="573" t="n"/>
-      <c r="E8" s="573" t="n"/>
-      <c r="F8" s="573" t="n"/>
-      <c r="G8" s="573" t="n"/>
-      <c r="H8" s="573" t="n"/>
-      <c r="I8" s="573" t="n"/>
-      <c r="J8" s="573" t="n"/>
-      <c r="K8" s="472" t="n"/>
-      <c r="L8" s="574" t="n"/>
-      <c r="M8" s="574" t="n"/>
-      <c r="N8" s="574" t="n"/>
-      <c r="O8" s="574" t="n"/>
-      <c r="P8" s="574" t="n"/>
-      <c r="Q8" s="574" t="n"/>
-      <c r="R8" s="574" t="n"/>
-      <c r="S8" s="574" t="n"/>
-      <c r="T8" s="574" t="n"/>
-      <c r="U8" s="574" t="n"/>
-      <c r="V8" s="574" t="n"/>
-      <c r="W8" s="574" t="n"/>
-      <c r="X8" s="574" t="n"/>
-      <c r="Y8" s="574" t="n"/>
-      <c r="Z8" s="574" t="n"/>
-      <c r="AA8" s="574" t="n"/>
-      <c r="AB8" s="574" t="n"/>
-      <c r="AC8" s="474" t="inlineStr">
+      <c r="B8" s="271" t="n"/>
+      <c r="C8" s="271" t="n"/>
+      <c r="D8" s="271" t="n"/>
+      <c r="E8" s="271" t="n"/>
+      <c r="F8" s="271" t="n"/>
+      <c r="G8" s="271" t="n"/>
+      <c r="H8" s="271" t="n"/>
+      <c r="I8" s="271" t="n"/>
+      <c r="J8" s="271" t="n"/>
+      <c r="K8" s="720" t="n"/>
+      <c r="L8" s="320" t="n"/>
+      <c r="M8" s="320" t="n"/>
+      <c r="N8" s="320" t="n"/>
+      <c r="O8" s="320" t="n"/>
+      <c r="P8" s="320" t="n"/>
+      <c r="Q8" s="320" t="n"/>
+      <c r="R8" s="320" t="n"/>
+      <c r="S8" s="320" t="n"/>
+      <c r="T8" s="320" t="n"/>
+      <c r="U8" s="320" t="n"/>
+      <c r="V8" s="320" t="n"/>
+      <c r="W8" s="320" t="n"/>
+      <c r="X8" s="320" t="n"/>
+      <c r="Y8" s="320" t="n"/>
+      <c r="Z8" s="320" t="n"/>
+      <c r="AA8" s="320" t="n"/>
+      <c r="AB8" s="320" t="n"/>
+      <c r="AC8" s="721" t="inlineStr">
         <is>
           <t>Release Status</t>
         </is>
       </c>
-      <c r="AD8" s="573" t="n"/>
-      <c r="AE8" s="573" t="n"/>
-      <c r="AF8" s="573" t="n"/>
-      <c r="AG8" s="573" t="n"/>
-      <c r="AH8" s="573" t="n"/>
-      <c r="AI8" s="573" t="n"/>
-      <c r="AJ8" s="573" t="n"/>
-      <c r="AK8" s="573" t="n"/>
-      <c r="AL8" s="573" t="n"/>
-      <c r="AM8" s="575" t="n"/>
-      <c r="AN8" s="574" t="n"/>
-      <c r="AO8" s="574" t="n"/>
-      <c r="AP8" s="574" t="n"/>
-      <c r="AQ8" s="574" t="n"/>
-      <c r="AR8" s="574" t="n"/>
-      <c r="AS8" s="574" t="n"/>
-      <c r="AT8" s="574" t="n"/>
-      <c r="AU8" s="574" t="n"/>
-      <c r="AV8" s="574" t="n"/>
-      <c r="AW8" s="574" t="n"/>
-      <c r="AX8" s="574" t="n"/>
-      <c r="AY8" s="574" t="n"/>
-      <c r="AZ8" s="574" t="n"/>
-      <c r="BA8" s="574" t="n"/>
-      <c r="BB8" s="574" t="n"/>
-      <c r="BC8" s="574" t="n"/>
-      <c r="BD8" s="576" t="n"/>
+      <c r="AD8" s="271" t="n"/>
+      <c r="AE8" s="271" t="n"/>
+      <c r="AF8" s="271" t="n"/>
+      <c r="AG8" s="271" t="n"/>
+      <c r="AH8" s="271" t="n"/>
+      <c r="AI8" s="271" t="n"/>
+      <c r="AJ8" s="271" t="n"/>
+      <c r="AK8" s="271" t="n"/>
+      <c r="AL8" s="271" t="n"/>
+      <c r="AM8" s="722" t="n"/>
+      <c r="AN8" s="320" t="n"/>
+      <c r="AO8" s="320" t="n"/>
+      <c r="AP8" s="320" t="n"/>
+      <c r="AQ8" s="320" t="n"/>
+      <c r="AR8" s="320" t="n"/>
+      <c r="AS8" s="320" t="n"/>
+      <c r="AT8" s="320" t="n"/>
+      <c r="AU8" s="320" t="n"/>
+      <c r="AV8" s="320" t="n"/>
+      <c r="AW8" s="320" t="n"/>
+      <c r="AX8" s="320" t="n"/>
+      <c r="AY8" s="320" t="n"/>
+      <c r="AZ8" s="320" t="n"/>
+      <c r="BA8" s="320" t="n"/>
+      <c r="BB8" s="320" t="n"/>
+      <c r="BC8" s="320" t="n"/>
+      <c r="BD8" s="322" t="n"/>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="476" t="inlineStr">
+      <c r="A9" s="723" t="inlineStr">
         <is>
           <t>Job / Part / Package Class</t>
         </is>
       </c>
-      <c r="B9" s="423" t="n"/>
-      <c r="C9" s="423" t="n"/>
-      <c r="D9" s="423" t="n"/>
-      <c r="E9" s="423" t="n"/>
-      <c r="F9" s="423" t="n"/>
-      <c r="G9" s="423" t="n"/>
-      <c r="H9" s="423" t="n"/>
-      <c r="I9" s="423" t="n"/>
-      <c r="J9" s="423" t="n"/>
-      <c r="K9" s="477" t="n"/>
-      <c r="L9" s="577" t="n"/>
-      <c r="M9" s="577" t="n"/>
-      <c r="N9" s="577" t="n"/>
-      <c r="O9" s="577" t="n"/>
-      <c r="P9" s="577" t="n"/>
-      <c r="Q9" s="577" t="n"/>
-      <c r="R9" s="577" t="n"/>
-      <c r="S9" s="577" t="n"/>
-      <c r="T9" s="577" t="n"/>
-      <c r="U9" s="577" t="n"/>
-      <c r="V9" s="577" t="n"/>
-      <c r="W9" s="577" t="n"/>
-      <c r="X9" s="577" t="n"/>
-      <c r="Y9" s="577" t="n"/>
-      <c r="Z9" s="577" t="n"/>
-      <c r="AA9" s="577" t="n"/>
-      <c r="AB9" s="577" t="n"/>
-      <c r="AC9" s="478" t="inlineStr">
+      <c r="B9" s="792" t="n"/>
+      <c r="C9" s="792" t="n"/>
+      <c r="D9" s="792" t="n"/>
+      <c r="E9" s="792" t="n"/>
+      <c r="F9" s="792" t="n"/>
+      <c r="G9" s="792" t="n"/>
+      <c r="H9" s="792" t="n"/>
+      <c r="I9" s="792" t="n"/>
+      <c r="J9" s="792" t="n"/>
+      <c r="K9" s="724" t="n"/>
+      <c r="L9" s="793" t="n"/>
+      <c r="M9" s="793" t="n"/>
+      <c r="N9" s="793" t="n"/>
+      <c r="O9" s="793" t="n"/>
+      <c r="P9" s="793" t="n"/>
+      <c r="Q9" s="793" t="n"/>
+      <c r="R9" s="793" t="n"/>
+      <c r="S9" s="793" t="n"/>
+      <c r="T9" s="793" t="n"/>
+      <c r="U9" s="793" t="n"/>
+      <c r="V9" s="793" t="n"/>
+      <c r="W9" s="793" t="n"/>
+      <c r="X9" s="793" t="n"/>
+      <c r="Y9" s="793" t="n"/>
+      <c r="Z9" s="793" t="n"/>
+      <c r="AA9" s="793" t="n"/>
+      <c r="AB9" s="793" t="n"/>
+      <c r="AC9" s="725" t="inlineStr">
         <is>
           <t>Clean Class</t>
         </is>
       </c>
-      <c r="AD9" s="423" t="n"/>
-      <c r="AE9" s="423" t="n"/>
-      <c r="AF9" s="423" t="n"/>
-      <c r="AG9" s="423" t="n"/>
-      <c r="AH9" s="423" t="n"/>
-      <c r="AI9" s="423" t="n"/>
-      <c r="AJ9" s="423" t="n"/>
-      <c r="AK9" s="423" t="n"/>
-      <c r="AL9" s="423" t="n"/>
-      <c r="AM9" s="578" t="n"/>
-      <c r="AN9" s="577" t="n"/>
-      <c r="AO9" s="577" t="n"/>
-      <c r="AP9" s="577" t="n"/>
-      <c r="AQ9" s="577" t="n"/>
-      <c r="AR9" s="577" t="n"/>
-      <c r="AS9" s="577" t="n"/>
-      <c r="AT9" s="577" t="n"/>
-      <c r="AU9" s="577" t="n"/>
-      <c r="AV9" s="577" t="n"/>
-      <c r="AW9" s="577" t="n"/>
-      <c r="AX9" s="577" t="n"/>
-      <c r="AY9" s="577" t="n"/>
-      <c r="AZ9" s="577" t="n"/>
-      <c r="BA9" s="577" t="n"/>
-      <c r="BB9" s="577" t="n"/>
-      <c r="BC9" s="577" t="n"/>
-      <c r="BD9" s="579" t="n"/>
+      <c r="AD9" s="792" t="n"/>
+      <c r="AE9" s="792" t="n"/>
+      <c r="AF9" s="792" t="n"/>
+      <c r="AG9" s="792" t="n"/>
+      <c r="AH9" s="792" t="n"/>
+      <c r="AI9" s="792" t="n"/>
+      <c r="AJ9" s="792" t="n"/>
+      <c r="AK9" s="792" t="n"/>
+      <c r="AL9" s="792" t="n"/>
+      <c r="AM9" s="726" t="n"/>
+      <c r="AN9" s="793" t="n"/>
+      <c r="AO9" s="793" t="n"/>
+      <c r="AP9" s="793" t="n"/>
+      <c r="AQ9" s="793" t="n"/>
+      <c r="AR9" s="793" t="n"/>
+      <c r="AS9" s="793" t="n"/>
+      <c r="AT9" s="793" t="n"/>
+      <c r="AU9" s="793" t="n"/>
+      <c r="AV9" s="793" t="n"/>
+      <c r="AW9" s="793" t="n"/>
+      <c r="AX9" s="793" t="n"/>
+      <c r="AY9" s="793" t="n"/>
+      <c r="AZ9" s="793" t="n"/>
+      <c r="BA9" s="793" t="n"/>
+      <c r="BB9" s="793" t="n"/>
+      <c r="BC9" s="793" t="n"/>
+      <c r="BD9" s="794" t="n"/>
     </row>
     <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="476" t="inlineStr">
+      <c r="A10" s="723" t="inlineStr">
         <is>
           <t>Bagging Configuration</t>
         </is>
       </c>
-      <c r="B10" s="423" t="n"/>
-      <c r="C10" s="423" t="n"/>
-      <c r="D10" s="423" t="n"/>
-      <c r="E10" s="423" t="n"/>
-      <c r="F10" s="423" t="n"/>
-      <c r="G10" s="423" t="n"/>
-      <c r="H10" s="423" t="n"/>
-      <c r="I10" s="423" t="n"/>
-      <c r="J10" s="423" t="n"/>
-      <c r="K10" s="477" t="n"/>
-      <c r="L10" s="577" t="n"/>
-      <c r="M10" s="577" t="n"/>
-      <c r="N10" s="577" t="n"/>
-      <c r="O10" s="577" t="n"/>
-      <c r="P10" s="577" t="n"/>
-      <c r="Q10" s="577" t="n"/>
-      <c r="R10" s="577" t="n"/>
-      <c r="S10" s="577" t="n"/>
-      <c r="T10" s="577" t="n"/>
-      <c r="U10" s="577" t="n"/>
-      <c r="V10" s="577" t="n"/>
-      <c r="W10" s="577" t="n"/>
-      <c r="X10" s="577" t="n"/>
-      <c r="Y10" s="577" t="n"/>
-      <c r="Z10" s="577" t="n"/>
-      <c r="AA10" s="577" t="n"/>
-      <c r="AB10" s="577" t="n"/>
-      <c r="AC10" s="478" t="inlineStr">
+      <c r="B10" s="792" t="n"/>
+      <c r="C10" s="792" t="n"/>
+      <c r="D10" s="792" t="n"/>
+      <c r="E10" s="792" t="n"/>
+      <c r="F10" s="792" t="n"/>
+      <c r="G10" s="792" t="n"/>
+      <c r="H10" s="792" t="n"/>
+      <c r="I10" s="792" t="n"/>
+      <c r="J10" s="792" t="n"/>
+      <c r="K10" s="724" t="n"/>
+      <c r="L10" s="793" t="n"/>
+      <c r="M10" s="793" t="n"/>
+      <c r="N10" s="793" t="n"/>
+      <c r="O10" s="793" t="n"/>
+      <c r="P10" s="793" t="n"/>
+      <c r="Q10" s="793" t="n"/>
+      <c r="R10" s="793" t="n"/>
+      <c r="S10" s="793" t="n"/>
+      <c r="T10" s="793" t="n"/>
+      <c r="U10" s="793" t="n"/>
+      <c r="V10" s="793" t="n"/>
+      <c r="W10" s="793" t="n"/>
+      <c r="X10" s="793" t="n"/>
+      <c r="Y10" s="793" t="n"/>
+      <c r="Z10" s="793" t="n"/>
+      <c r="AA10" s="793" t="n"/>
+      <c r="AB10" s="793" t="n"/>
+      <c r="AC10" s="725" t="inlineStr">
         <is>
           <t>Line Clearance / Gowning</t>
         </is>
       </c>
-      <c r="AD10" s="423" t="n"/>
-      <c r="AE10" s="423" t="n"/>
-      <c r="AF10" s="423" t="n"/>
-      <c r="AG10" s="423" t="n"/>
-      <c r="AH10" s="423" t="n"/>
-      <c r="AI10" s="423" t="n"/>
-      <c r="AJ10" s="423" t="n"/>
-      <c r="AK10" s="423" t="n"/>
-      <c r="AL10" s="423" t="n"/>
-      <c r="AM10" s="578" t="n"/>
-      <c r="AN10" s="577" t="n"/>
-      <c r="AO10" s="577" t="n"/>
-      <c r="AP10" s="577" t="n"/>
-      <c r="AQ10" s="577" t="n"/>
-      <c r="AR10" s="577" t="n"/>
-      <c r="AS10" s="577" t="n"/>
-      <c r="AT10" s="577" t="n"/>
-      <c r="AU10" s="577" t="n"/>
-      <c r="AV10" s="577" t="n"/>
-      <c r="AW10" s="577" t="n"/>
-      <c r="AX10" s="577" t="n"/>
-      <c r="AY10" s="577" t="n"/>
-      <c r="AZ10" s="577" t="n"/>
-      <c r="BA10" s="577" t="n"/>
-      <c r="BB10" s="577" t="n"/>
-      <c r="BC10" s="577" t="n"/>
-      <c r="BD10" s="579" t="n"/>
+      <c r="AD10" s="792" t="n"/>
+      <c r="AE10" s="792" t="n"/>
+      <c r="AF10" s="792" t="n"/>
+      <c r="AG10" s="792" t="n"/>
+      <c r="AH10" s="792" t="n"/>
+      <c r="AI10" s="792" t="n"/>
+      <c r="AJ10" s="792" t="n"/>
+      <c r="AK10" s="792" t="n"/>
+      <c r="AL10" s="792" t="n"/>
+      <c r="AM10" s="726" t="n"/>
+      <c r="AN10" s="793" t="n"/>
+      <c r="AO10" s="793" t="n"/>
+      <c r="AP10" s="793" t="n"/>
+      <c r="AQ10" s="793" t="n"/>
+      <c r="AR10" s="793" t="n"/>
+      <c r="AS10" s="793" t="n"/>
+      <c r="AT10" s="793" t="n"/>
+      <c r="AU10" s="793" t="n"/>
+      <c r="AV10" s="793" t="n"/>
+      <c r="AW10" s="793" t="n"/>
+      <c r="AX10" s="793" t="n"/>
+      <c r="AY10" s="793" t="n"/>
+      <c r="AZ10" s="793" t="n"/>
+      <c r="BA10" s="793" t="n"/>
+      <c r="BB10" s="793" t="n"/>
+      <c r="BC10" s="793" t="n"/>
+      <c r="BD10" s="794" t="n"/>
     </row>
     <row r="11" ht="26" customHeight="1">
-      <c r="A11" s="476" t="inlineStr">
+      <c r="A11" s="723" t="inlineStr">
         <is>
           <t>Prepared by / Date-Time</t>
         </is>
       </c>
-      <c r="B11" s="423" t="n"/>
-      <c r="C11" s="423" t="n"/>
-      <c r="D11" s="423" t="n"/>
-      <c r="E11" s="423" t="n"/>
-      <c r="F11" s="423" t="n"/>
-      <c r="G11" s="423" t="n"/>
-      <c r="H11" s="423" t="n"/>
-      <c r="I11" s="423" t="n"/>
-      <c r="J11" s="423" t="n"/>
-      <c r="K11" s="477" t="n"/>
-      <c r="L11" s="577" t="n"/>
-      <c r="M11" s="577" t="n"/>
-      <c r="N11" s="577" t="n"/>
-      <c r="O11" s="577" t="n"/>
-      <c r="P11" s="577" t="n"/>
-      <c r="Q11" s="577" t="n"/>
-      <c r="R11" s="577" t="n"/>
-      <c r="S11" s="577" t="n"/>
-      <c r="T11" s="577" t="n"/>
-      <c r="U11" s="577" t="n"/>
-      <c r="V11" s="577" t="n"/>
-      <c r="W11" s="577" t="n"/>
-      <c r="X11" s="577" t="n"/>
-      <c r="Y11" s="577" t="n"/>
-      <c r="Z11" s="577" t="n"/>
-      <c r="AA11" s="577" t="n"/>
-      <c r="AB11" s="577" t="n"/>
-      <c r="AC11" s="478" t="inlineStr">
+      <c r="B11" s="792" t="n"/>
+      <c r="C11" s="792" t="n"/>
+      <c r="D11" s="792" t="n"/>
+      <c r="E11" s="792" t="n"/>
+      <c r="F11" s="792" t="n"/>
+      <c r="G11" s="792" t="n"/>
+      <c r="H11" s="792" t="n"/>
+      <c r="I11" s="792" t="n"/>
+      <c r="J11" s="792" t="n"/>
+      <c r="K11" s="724" t="n"/>
+      <c r="L11" s="793" t="n"/>
+      <c r="M11" s="793" t="n"/>
+      <c r="N11" s="793" t="n"/>
+      <c r="O11" s="793" t="n"/>
+      <c r="P11" s="793" t="n"/>
+      <c r="Q11" s="793" t="n"/>
+      <c r="R11" s="793" t="n"/>
+      <c r="S11" s="793" t="n"/>
+      <c r="T11" s="793" t="n"/>
+      <c r="U11" s="793" t="n"/>
+      <c r="V11" s="793" t="n"/>
+      <c r="W11" s="793" t="n"/>
+      <c r="X11" s="793" t="n"/>
+      <c r="Y11" s="793" t="n"/>
+      <c r="Z11" s="793" t="n"/>
+      <c r="AA11" s="793" t="n"/>
+      <c r="AB11" s="793" t="n"/>
+      <c r="AC11" s="725" t="inlineStr">
         <is>
           <t>Warehouse Owner</t>
         </is>
       </c>
-      <c r="AD11" s="423" t="n"/>
-      <c r="AE11" s="423" t="n"/>
-      <c r="AF11" s="423" t="n"/>
-      <c r="AG11" s="423" t="n"/>
-      <c r="AH11" s="423" t="n"/>
-      <c r="AI11" s="423" t="n"/>
-      <c r="AJ11" s="423" t="n"/>
-      <c r="AK11" s="423" t="n"/>
-      <c r="AL11" s="423" t="n"/>
-      <c r="AM11" s="578" t="n"/>
-      <c r="AN11" s="577" t="n"/>
-      <c r="AO11" s="577" t="n"/>
-      <c r="AP11" s="577" t="n"/>
-      <c r="AQ11" s="577" t="n"/>
-      <c r="AR11" s="577" t="n"/>
-      <c r="AS11" s="577" t="n"/>
-      <c r="AT11" s="577" t="n"/>
-      <c r="AU11" s="577" t="n"/>
-      <c r="AV11" s="577" t="n"/>
-      <c r="AW11" s="577" t="n"/>
-      <c r="AX11" s="577" t="n"/>
-      <c r="AY11" s="577" t="n"/>
-      <c r="AZ11" s="577" t="n"/>
-      <c r="BA11" s="577" t="n"/>
-      <c r="BB11" s="577" t="n"/>
-      <c r="BC11" s="577" t="n"/>
-      <c r="BD11" s="579" t="n"/>
+      <c r="AD11" s="792" t="n"/>
+      <c r="AE11" s="792" t="n"/>
+      <c r="AF11" s="792" t="n"/>
+      <c r="AG11" s="792" t="n"/>
+      <c r="AH11" s="792" t="n"/>
+      <c r="AI11" s="792" t="n"/>
+      <c r="AJ11" s="792" t="n"/>
+      <c r="AK11" s="792" t="n"/>
+      <c r="AL11" s="792" t="n"/>
+      <c r="AM11" s="726" t="n"/>
+      <c r="AN11" s="793" t="n"/>
+      <c r="AO11" s="793" t="n"/>
+      <c r="AP11" s="793" t="n"/>
+      <c r="AQ11" s="793" t="n"/>
+      <c r="AR11" s="793" t="n"/>
+      <c r="AS11" s="793" t="n"/>
+      <c r="AT11" s="793" t="n"/>
+      <c r="AU11" s="793" t="n"/>
+      <c r="AV11" s="793" t="n"/>
+      <c r="AW11" s="793" t="n"/>
+      <c r="AX11" s="793" t="n"/>
+      <c r="AY11" s="793" t="n"/>
+      <c r="AZ11" s="793" t="n"/>
+      <c r="BA11" s="793" t="n"/>
+      <c r="BB11" s="793" t="n"/>
+      <c r="BC11" s="793" t="n"/>
+      <c r="BD11" s="794" t="n"/>
     </row>
     <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="480" t="inlineStr">
+      <c r="A12" s="727" t="inlineStr">
         <is>
           <t>Evidence Package Ref</t>
         </is>
       </c>
-      <c r="B12" s="566" t="n"/>
-      <c r="C12" s="566" t="n"/>
-      <c r="D12" s="566" t="n"/>
-      <c r="E12" s="566" t="n"/>
-      <c r="F12" s="566" t="n"/>
-      <c r="G12" s="566" t="n"/>
-      <c r="H12" s="566" t="n"/>
-      <c r="I12" s="566" t="n"/>
-      <c r="J12" s="566" t="n"/>
-      <c r="K12" s="482" t="n"/>
-      <c r="L12" s="580" t="n"/>
-      <c r="M12" s="580" t="n"/>
-      <c r="N12" s="580" t="n"/>
-      <c r="O12" s="580" t="n"/>
-      <c r="P12" s="580" t="n"/>
-      <c r="Q12" s="580" t="n"/>
-      <c r="R12" s="580" t="n"/>
-      <c r="S12" s="580" t="n"/>
-      <c r="T12" s="580" t="n"/>
-      <c r="U12" s="580" t="n"/>
-      <c r="V12" s="580" t="n"/>
-      <c r="W12" s="580" t="n"/>
-      <c r="X12" s="580" t="n"/>
-      <c r="Y12" s="580" t="n"/>
-      <c r="Z12" s="580" t="n"/>
-      <c r="AA12" s="580" t="n"/>
-      <c r="AB12" s="580" t="n"/>
-      <c r="AC12" s="484" t="inlineStr">
+      <c r="B12" s="795" t="n"/>
+      <c r="C12" s="795" t="n"/>
+      <c r="D12" s="795" t="n"/>
+      <c r="E12" s="795" t="n"/>
+      <c r="F12" s="795" t="n"/>
+      <c r="G12" s="795" t="n"/>
+      <c r="H12" s="795" t="n"/>
+      <c r="I12" s="795" t="n"/>
+      <c r="J12" s="795" t="n"/>
+      <c r="K12" s="728" t="n"/>
+      <c r="L12" s="796" t="n"/>
+      <c r="M12" s="796" t="n"/>
+      <c r="N12" s="796" t="n"/>
+      <c r="O12" s="796" t="n"/>
+      <c r="P12" s="796" t="n"/>
+      <c r="Q12" s="796" t="n"/>
+      <c r="R12" s="796" t="n"/>
+      <c r="S12" s="796" t="n"/>
+      <c r="T12" s="796" t="n"/>
+      <c r="U12" s="796" t="n"/>
+      <c r="V12" s="796" t="n"/>
+      <c r="W12" s="796" t="n"/>
+      <c r="X12" s="796" t="n"/>
+      <c r="Y12" s="796" t="n"/>
+      <c r="Z12" s="796" t="n"/>
+      <c r="AA12" s="796" t="n"/>
+      <c r="AB12" s="796" t="n"/>
+      <c r="AC12" s="729" t="inlineStr">
         <is>
           <t>Record Status</t>
         </is>
       </c>
-      <c r="AD12" s="566" t="n"/>
-      <c r="AE12" s="566" t="n"/>
-      <c r="AF12" s="566" t="n"/>
-      <c r="AG12" s="566" t="n"/>
-      <c r="AH12" s="566" t="n"/>
-      <c r="AI12" s="566" t="n"/>
-      <c r="AJ12" s="566" t="n"/>
-      <c r="AK12" s="566" t="n"/>
-      <c r="AL12" s="566" t="n"/>
-      <c r="AM12" s="581" t="n"/>
-      <c r="AN12" s="580" t="n"/>
-      <c r="AO12" s="580" t="n"/>
-      <c r="AP12" s="580" t="n"/>
-      <c r="AQ12" s="580" t="n"/>
-      <c r="AR12" s="580" t="n"/>
-      <c r="AS12" s="580" t="n"/>
-      <c r="AT12" s="580" t="n"/>
-      <c r="AU12" s="580" t="n"/>
-      <c r="AV12" s="580" t="n"/>
-      <c r="AW12" s="580" t="n"/>
-      <c r="AX12" s="580" t="n"/>
-      <c r="AY12" s="580" t="n"/>
-      <c r="AZ12" s="580" t="n"/>
-      <c r="BA12" s="580" t="n"/>
-      <c r="BB12" s="580" t="n"/>
-      <c r="BC12" s="580" t="n"/>
-      <c r="BD12" s="582" t="n"/>
+      <c r="AD12" s="795" t="n"/>
+      <c r="AE12" s="795" t="n"/>
+      <c r="AF12" s="795" t="n"/>
+      <c r="AG12" s="795" t="n"/>
+      <c r="AH12" s="795" t="n"/>
+      <c r="AI12" s="795" t="n"/>
+      <c r="AJ12" s="795" t="n"/>
+      <c r="AK12" s="795" t="n"/>
+      <c r="AL12" s="795" t="n"/>
+      <c r="AM12" s="730" t="n"/>
+      <c r="AN12" s="796" t="n"/>
+      <c r="AO12" s="796" t="n"/>
+      <c r="AP12" s="796" t="n"/>
+      <c r="AQ12" s="796" t="n"/>
+      <c r="AR12" s="796" t="n"/>
+      <c r="AS12" s="796" t="n"/>
+      <c r="AT12" s="796" t="n"/>
+      <c r="AU12" s="796" t="n"/>
+      <c r="AV12" s="796" t="n"/>
+      <c r="AW12" s="796" t="n"/>
+      <c r="AX12" s="796" t="n"/>
+      <c r="AY12" s="796" t="n"/>
+      <c r="AZ12" s="796" t="n"/>
+      <c r="BA12" s="796" t="n"/>
+      <c r="BB12" s="796" t="n"/>
+      <c r="BC12" s="796" t="n"/>
+      <c r="BD12" s="797" t="n"/>
     </row>
     <row r="13" ht="3" customHeight="1">
       <c r="A13" s="353" t="n"/>
@@ -7984,640 +8529,640 @@
       <c r="BD13" s="353" t="n"/>
     </row>
     <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="570" t="inlineStr">
+      <c r="A14" s="731" t="inlineStr">
         <is>
           <t xml:space="preserve">  2. CLEAN BUILD / BAGGING VERIFICATION</t>
         </is>
       </c>
-      <c r="B14" s="571" t="n"/>
-      <c r="C14" s="571" t="n"/>
-      <c r="D14" s="571" t="n"/>
-      <c r="E14" s="571" t="n"/>
-      <c r="F14" s="571" t="n"/>
-      <c r="G14" s="571" t="n"/>
-      <c r="H14" s="571" t="n"/>
-      <c r="I14" s="571" t="n"/>
-      <c r="J14" s="571" t="n"/>
-      <c r="K14" s="571" t="n"/>
-      <c r="L14" s="571" t="n"/>
-      <c r="M14" s="571" t="n"/>
-      <c r="N14" s="571" t="n"/>
-      <c r="O14" s="571" t="n"/>
-      <c r="P14" s="571" t="n"/>
-      <c r="Q14" s="571" t="n"/>
-      <c r="R14" s="571" t="n"/>
-      <c r="S14" s="571" t="n"/>
-      <c r="T14" s="571" t="n"/>
-      <c r="U14" s="571" t="n"/>
-      <c r="V14" s="571" t="n"/>
-      <c r="W14" s="571" t="n"/>
-      <c r="X14" s="571" t="n"/>
-      <c r="Y14" s="571" t="n"/>
-      <c r="Z14" s="571" t="n"/>
-      <c r="AA14" s="571" t="n"/>
-      <c r="AB14" s="571" t="n"/>
-      <c r="AC14" s="571" t="n"/>
-      <c r="AD14" s="571" t="n"/>
-      <c r="AE14" s="571" t="n"/>
-      <c r="AF14" s="571" t="n"/>
-      <c r="AG14" s="571" t="n"/>
-      <c r="AH14" s="571" t="n"/>
-      <c r="AI14" s="571" t="n"/>
-      <c r="AJ14" s="571" t="n"/>
-      <c r="AK14" s="571" t="n"/>
-      <c r="AL14" s="571" t="n"/>
-      <c r="AM14" s="571" t="n"/>
-      <c r="AN14" s="571" t="n"/>
-      <c r="AO14" s="571" t="n"/>
-      <c r="AP14" s="571" t="n"/>
-      <c r="AQ14" s="571" t="n"/>
-      <c r="AR14" s="571" t="n"/>
-      <c r="AS14" s="571" t="n"/>
-      <c r="AT14" s="571" t="n"/>
-      <c r="AU14" s="571" t="n"/>
-      <c r="AV14" s="571" t="n"/>
-      <c r="AW14" s="571" t="n"/>
-      <c r="AX14" s="571" t="n"/>
-      <c r="AY14" s="571" t="n"/>
-      <c r="AZ14" s="571" t="n"/>
-      <c r="BA14" s="571" t="n"/>
-      <c r="BB14" s="571" t="n"/>
-      <c r="BC14" s="571" t="n"/>
-      <c r="BD14" s="572" t="n"/>
+      <c r="B14" s="285" t="n"/>
+      <c r="C14" s="285" t="n"/>
+      <c r="D14" s="285" t="n"/>
+      <c r="E14" s="285" t="n"/>
+      <c r="F14" s="285" t="n"/>
+      <c r="G14" s="285" t="n"/>
+      <c r="H14" s="285" t="n"/>
+      <c r="I14" s="285" t="n"/>
+      <c r="J14" s="285" t="n"/>
+      <c r="K14" s="285" t="n"/>
+      <c r="L14" s="285" t="n"/>
+      <c r="M14" s="285" t="n"/>
+      <c r="N14" s="285" t="n"/>
+      <c r="O14" s="285" t="n"/>
+      <c r="P14" s="285" t="n"/>
+      <c r="Q14" s="285" t="n"/>
+      <c r="R14" s="285" t="n"/>
+      <c r="S14" s="285" t="n"/>
+      <c r="T14" s="285" t="n"/>
+      <c r="U14" s="285" t="n"/>
+      <c r="V14" s="285" t="n"/>
+      <c r="W14" s="285" t="n"/>
+      <c r="X14" s="285" t="n"/>
+      <c r="Y14" s="285" t="n"/>
+      <c r="Z14" s="285" t="n"/>
+      <c r="AA14" s="285" t="n"/>
+      <c r="AB14" s="285" t="n"/>
+      <c r="AC14" s="285" t="n"/>
+      <c r="AD14" s="285" t="n"/>
+      <c r="AE14" s="285" t="n"/>
+      <c r="AF14" s="285" t="n"/>
+      <c r="AG14" s="285" t="n"/>
+      <c r="AH14" s="285" t="n"/>
+      <c r="AI14" s="285" t="n"/>
+      <c r="AJ14" s="285" t="n"/>
+      <c r="AK14" s="285" t="n"/>
+      <c r="AL14" s="285" t="n"/>
+      <c r="AM14" s="285" t="n"/>
+      <c r="AN14" s="285" t="n"/>
+      <c r="AO14" s="285" t="n"/>
+      <c r="AP14" s="285" t="n"/>
+      <c r="AQ14" s="285" t="n"/>
+      <c r="AR14" s="285" t="n"/>
+      <c r="AS14" s="285" t="n"/>
+      <c r="AT14" s="285" t="n"/>
+      <c r="AU14" s="285" t="n"/>
+      <c r="AV14" s="285" t="n"/>
+      <c r="AW14" s="285" t="n"/>
+      <c r="AX14" s="285" t="n"/>
+      <c r="AY14" s="285" t="n"/>
+      <c r="AZ14" s="285" t="n"/>
+      <c r="BA14" s="285" t="n"/>
+      <c r="BB14" s="285" t="n"/>
+      <c r="BC14" s="285" t="n"/>
+      <c r="BD14" s="286" t="n"/>
     </row>
     <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="486" t="inlineStr">
+      <c r="A15" s="732" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B15" s="571" t="n"/>
-      <c r="C15" s="571" t="n"/>
-      <c r="D15" s="488" t="inlineStr">
+      <c r="B15" s="285" t="n"/>
+      <c r="C15" s="285" t="n"/>
+      <c r="D15" s="733" t="inlineStr">
         <is>
           <t>Cat.</t>
         </is>
       </c>
-      <c r="E15" s="571" t="n"/>
-      <c r="F15" s="571" t="n"/>
-      <c r="G15" s="571" t="n"/>
-      <c r="H15" s="488" t="inlineStr">
+      <c r="E15" s="285" t="n"/>
+      <c r="F15" s="285" t="n"/>
+      <c r="G15" s="285" t="n"/>
+      <c r="H15" s="733" t="inlineStr">
         <is>
           <t>Clean Build / Bagging Requirement</t>
         </is>
       </c>
-      <c r="I15" s="571" t="n"/>
-      <c r="J15" s="571" t="n"/>
-      <c r="K15" s="571" t="n"/>
-      <c r="L15" s="571" t="n"/>
-      <c r="M15" s="571" t="n"/>
-      <c r="N15" s="571" t="n"/>
-      <c r="O15" s="571" t="n"/>
-      <c r="P15" s="571" t="n"/>
-      <c r="Q15" s="571" t="n"/>
-      <c r="R15" s="571" t="n"/>
-      <c r="S15" s="571" t="n"/>
-      <c r="T15" s="571" t="n"/>
-      <c r="U15" s="571" t="n"/>
-      <c r="V15" s="571" t="n"/>
-      <c r="W15" s="571" t="n"/>
-      <c r="X15" s="571" t="n"/>
-      <c r="Y15" s="571" t="n"/>
-      <c r="Z15" s="571" t="n"/>
-      <c r="AA15" s="488" t="inlineStr">
+      <c r="I15" s="285" t="n"/>
+      <c r="J15" s="285" t="n"/>
+      <c r="K15" s="285" t="n"/>
+      <c r="L15" s="285" t="n"/>
+      <c r="M15" s="285" t="n"/>
+      <c r="N15" s="285" t="n"/>
+      <c r="O15" s="285" t="n"/>
+      <c r="P15" s="285" t="n"/>
+      <c r="Q15" s="285" t="n"/>
+      <c r="R15" s="285" t="n"/>
+      <c r="S15" s="285" t="n"/>
+      <c r="T15" s="285" t="n"/>
+      <c r="U15" s="285" t="n"/>
+      <c r="V15" s="285" t="n"/>
+      <c r="W15" s="285" t="n"/>
+      <c r="X15" s="285" t="n"/>
+      <c r="Y15" s="285" t="n"/>
+      <c r="Z15" s="285" t="n"/>
+      <c r="AA15" s="733" t="inlineStr">
         <is>
           <t>Evidence / Method</t>
         </is>
       </c>
-      <c r="AB15" s="571" t="n"/>
-      <c r="AC15" s="571" t="n"/>
-      <c r="AD15" s="571" t="n"/>
-      <c r="AE15" s="571" t="n"/>
-      <c r="AF15" s="571" t="n"/>
-      <c r="AG15" s="571" t="n"/>
-      <c r="AH15" s="571" t="n"/>
-      <c r="AI15" s="571" t="n"/>
-      <c r="AJ15" s="571" t="n"/>
-      <c r="AK15" s="571" t="n"/>
-      <c r="AL15" s="571" t="n"/>
-      <c r="AM15" s="571" t="n"/>
-      <c r="AN15" s="571" t="n"/>
-      <c r="AO15" s="571" t="n"/>
-      <c r="AP15" s="571" t="n"/>
-      <c r="AQ15" s="571" t="n"/>
-      <c r="AR15" s="488" t="inlineStr">
+      <c r="AB15" s="285" t="n"/>
+      <c r="AC15" s="285" t="n"/>
+      <c r="AD15" s="285" t="n"/>
+      <c r="AE15" s="285" t="n"/>
+      <c r="AF15" s="285" t="n"/>
+      <c r="AG15" s="285" t="n"/>
+      <c r="AH15" s="285" t="n"/>
+      <c r="AI15" s="285" t="n"/>
+      <c r="AJ15" s="285" t="n"/>
+      <c r="AK15" s="285" t="n"/>
+      <c r="AL15" s="285" t="n"/>
+      <c r="AM15" s="285" t="n"/>
+      <c r="AN15" s="285" t="n"/>
+      <c r="AO15" s="285" t="n"/>
+      <c r="AP15" s="285" t="n"/>
+      <c r="AQ15" s="285" t="n"/>
+      <c r="AR15" s="733" t="inlineStr">
         <is>
           <t>Result</t>
         </is>
       </c>
-      <c r="AS15" s="571" t="n"/>
-      <c r="AT15" s="571" t="n"/>
-      <c r="AU15" s="571" t="n"/>
-      <c r="AV15" s="571" t="n"/>
-      <c r="AW15" s="571" t="n"/>
-      <c r="AX15" s="488" t="inlineStr">
+      <c r="AS15" s="285" t="n"/>
+      <c r="AT15" s="285" t="n"/>
+      <c r="AU15" s="285" t="n"/>
+      <c r="AV15" s="285" t="n"/>
+      <c r="AW15" s="285" t="n"/>
+      <c r="AX15" s="733" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="AY15" s="571" t="n"/>
-      <c r="AZ15" s="571" t="n"/>
-      <c r="BA15" s="571" t="n"/>
-      <c r="BB15" s="583" t="inlineStr">
+      <c r="AY15" s="285" t="n"/>
+      <c r="AZ15" s="285" t="n"/>
+      <c r="BA15" s="285" t="n"/>
+      <c r="BB15" s="734" t="inlineStr">
         <is>
           <t>Ref.</t>
         </is>
       </c>
-      <c r="BC15" s="571" t="n"/>
-      <c r="BD15" s="572" t="n"/>
+      <c r="BC15" s="285" t="n"/>
+      <c r="BD15" s="286" t="n"/>
     </row>
     <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="490">
+      <c r="A16" s="735">
         <f>ROW()-ROW($A$16)+1</f>
         <v/>
       </c>
-      <c r="B16" s="573" t="n"/>
-      <c r="C16" s="573" t="n"/>
-      <c r="D16" s="491" t="n"/>
-      <c r="E16" s="574" t="n"/>
-      <c r="F16" s="574" t="n"/>
-      <c r="G16" s="574" t="n"/>
-      <c r="H16" s="472" t="n"/>
-      <c r="I16" s="574" t="n"/>
-      <c r="J16" s="574" t="n"/>
-      <c r="K16" s="574" t="n"/>
-      <c r="L16" s="574" t="n"/>
-      <c r="M16" s="574" t="n"/>
-      <c r="N16" s="574" t="n"/>
-      <c r="O16" s="574" t="n"/>
-      <c r="P16" s="574" t="n"/>
-      <c r="Q16" s="574" t="n"/>
-      <c r="R16" s="574" t="n"/>
-      <c r="S16" s="574" t="n"/>
-      <c r="T16" s="574" t="n"/>
-      <c r="U16" s="574" t="n"/>
-      <c r="V16" s="574" t="n"/>
-      <c r="W16" s="574" t="n"/>
-      <c r="X16" s="574" t="n"/>
-      <c r="Y16" s="574" t="n"/>
-      <c r="Z16" s="574" t="n"/>
-      <c r="AA16" s="492" t="n"/>
-      <c r="AB16" s="574" t="n"/>
-      <c r="AC16" s="574" t="n"/>
-      <c r="AD16" s="574" t="n"/>
-      <c r="AE16" s="574" t="n"/>
-      <c r="AF16" s="574" t="n"/>
-      <c r="AG16" s="574" t="n"/>
-      <c r="AH16" s="574" t="n"/>
-      <c r="AI16" s="574" t="n"/>
-      <c r="AJ16" s="574" t="n"/>
-      <c r="AK16" s="574" t="n"/>
-      <c r="AL16" s="574" t="n"/>
-      <c r="AM16" s="574" t="n"/>
-      <c r="AN16" s="574" t="n"/>
-      <c r="AO16" s="574" t="n"/>
-      <c r="AP16" s="574" t="n"/>
-      <c r="AQ16" s="574" t="n"/>
-      <c r="AR16" s="472" t="n"/>
-      <c r="AS16" s="574" t="n"/>
-      <c r="AT16" s="574" t="n"/>
-      <c r="AU16" s="574" t="n"/>
-      <c r="AV16" s="574" t="n"/>
-      <c r="AW16" s="574" t="n"/>
-      <c r="AX16" s="472" t="n"/>
-      <c r="AY16" s="574" t="n"/>
-      <c r="AZ16" s="574" t="n"/>
-      <c r="BA16" s="574" t="n"/>
-      <c r="BB16" s="584" t="n"/>
-      <c r="BC16" s="574" t="n"/>
-      <c r="BD16" s="576" t="n"/>
+      <c r="B16" s="271" t="n"/>
+      <c r="C16" s="271" t="n"/>
+      <c r="D16" s="736" t="n"/>
+      <c r="E16" s="320" t="n"/>
+      <c r="F16" s="320" t="n"/>
+      <c r="G16" s="320" t="n"/>
+      <c r="H16" s="720" t="n"/>
+      <c r="I16" s="320" t="n"/>
+      <c r="J16" s="320" t="n"/>
+      <c r="K16" s="320" t="n"/>
+      <c r="L16" s="320" t="n"/>
+      <c r="M16" s="320" t="n"/>
+      <c r="N16" s="320" t="n"/>
+      <c r="O16" s="320" t="n"/>
+      <c r="P16" s="320" t="n"/>
+      <c r="Q16" s="320" t="n"/>
+      <c r="R16" s="320" t="n"/>
+      <c r="S16" s="320" t="n"/>
+      <c r="T16" s="320" t="n"/>
+      <c r="U16" s="320" t="n"/>
+      <c r="V16" s="320" t="n"/>
+      <c r="W16" s="320" t="n"/>
+      <c r="X16" s="320" t="n"/>
+      <c r="Y16" s="320" t="n"/>
+      <c r="Z16" s="320" t="n"/>
+      <c r="AA16" s="737" t="n"/>
+      <c r="AB16" s="320" t="n"/>
+      <c r="AC16" s="320" t="n"/>
+      <c r="AD16" s="320" t="n"/>
+      <c r="AE16" s="320" t="n"/>
+      <c r="AF16" s="320" t="n"/>
+      <c r="AG16" s="320" t="n"/>
+      <c r="AH16" s="320" t="n"/>
+      <c r="AI16" s="320" t="n"/>
+      <c r="AJ16" s="320" t="n"/>
+      <c r="AK16" s="320" t="n"/>
+      <c r="AL16" s="320" t="n"/>
+      <c r="AM16" s="320" t="n"/>
+      <c r="AN16" s="320" t="n"/>
+      <c r="AO16" s="320" t="n"/>
+      <c r="AP16" s="320" t="n"/>
+      <c r="AQ16" s="320" t="n"/>
+      <c r="AR16" s="720" t="n"/>
+      <c r="AS16" s="320" t="n"/>
+      <c r="AT16" s="320" t="n"/>
+      <c r="AU16" s="320" t="n"/>
+      <c r="AV16" s="320" t="n"/>
+      <c r="AW16" s="320" t="n"/>
+      <c r="AX16" s="720" t="n"/>
+      <c r="AY16" s="320" t="n"/>
+      <c r="AZ16" s="320" t="n"/>
+      <c r="BA16" s="320" t="n"/>
+      <c r="BB16" s="738" t="n"/>
+      <c r="BC16" s="320" t="n"/>
+      <c r="BD16" s="322" t="n"/>
     </row>
     <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="494">
+      <c r="A17" s="739">
         <f>ROW()-ROW($A$16)+1</f>
         <v/>
       </c>
-      <c r="B17" s="423" t="n"/>
-      <c r="C17" s="423" t="n"/>
-      <c r="D17" s="495" t="n"/>
-      <c r="E17" s="577" t="n"/>
-      <c r="F17" s="577" t="n"/>
-      <c r="G17" s="577" t="n"/>
-      <c r="H17" s="477" t="n"/>
-      <c r="I17" s="577" t="n"/>
-      <c r="J17" s="577" t="n"/>
-      <c r="K17" s="577" t="n"/>
-      <c r="L17" s="577" t="n"/>
-      <c r="M17" s="577" t="n"/>
-      <c r="N17" s="577" t="n"/>
-      <c r="O17" s="577" t="n"/>
-      <c r="P17" s="577" t="n"/>
-      <c r="Q17" s="577" t="n"/>
-      <c r="R17" s="577" t="n"/>
-      <c r="S17" s="577" t="n"/>
-      <c r="T17" s="577" t="n"/>
-      <c r="U17" s="577" t="n"/>
-      <c r="V17" s="577" t="n"/>
-      <c r="W17" s="577" t="n"/>
-      <c r="X17" s="577" t="n"/>
-      <c r="Y17" s="577" t="n"/>
-      <c r="Z17" s="577" t="n"/>
-      <c r="AA17" s="496" t="n"/>
-      <c r="AB17" s="577" t="n"/>
-      <c r="AC17" s="577" t="n"/>
-      <c r="AD17" s="577" t="n"/>
-      <c r="AE17" s="577" t="n"/>
-      <c r="AF17" s="577" t="n"/>
-      <c r="AG17" s="577" t="n"/>
-      <c r="AH17" s="577" t="n"/>
-      <c r="AI17" s="577" t="n"/>
-      <c r="AJ17" s="577" t="n"/>
-      <c r="AK17" s="577" t="n"/>
-      <c r="AL17" s="577" t="n"/>
-      <c r="AM17" s="577" t="n"/>
-      <c r="AN17" s="577" t="n"/>
-      <c r="AO17" s="577" t="n"/>
-      <c r="AP17" s="577" t="n"/>
-      <c r="AQ17" s="577" t="n"/>
-      <c r="AR17" s="477" t="n"/>
-      <c r="AS17" s="577" t="n"/>
-      <c r="AT17" s="577" t="n"/>
-      <c r="AU17" s="577" t="n"/>
-      <c r="AV17" s="577" t="n"/>
-      <c r="AW17" s="577" t="n"/>
-      <c r="AX17" s="477" t="n"/>
-      <c r="AY17" s="577" t="n"/>
-      <c r="AZ17" s="577" t="n"/>
-      <c r="BA17" s="577" t="n"/>
-      <c r="BB17" s="585" t="n"/>
-      <c r="BC17" s="577" t="n"/>
-      <c r="BD17" s="579" t="n"/>
+      <c r="B17" s="792" t="n"/>
+      <c r="C17" s="792" t="n"/>
+      <c r="D17" s="740" t="n"/>
+      <c r="E17" s="793" t="n"/>
+      <c r="F17" s="793" t="n"/>
+      <c r="G17" s="793" t="n"/>
+      <c r="H17" s="724" t="n"/>
+      <c r="I17" s="793" t="n"/>
+      <c r="J17" s="793" t="n"/>
+      <c r="K17" s="793" t="n"/>
+      <c r="L17" s="793" t="n"/>
+      <c r="M17" s="793" t="n"/>
+      <c r="N17" s="793" t="n"/>
+      <c r="O17" s="793" t="n"/>
+      <c r="P17" s="793" t="n"/>
+      <c r="Q17" s="793" t="n"/>
+      <c r="R17" s="793" t="n"/>
+      <c r="S17" s="793" t="n"/>
+      <c r="T17" s="793" t="n"/>
+      <c r="U17" s="793" t="n"/>
+      <c r="V17" s="793" t="n"/>
+      <c r="W17" s="793" t="n"/>
+      <c r="X17" s="793" t="n"/>
+      <c r="Y17" s="793" t="n"/>
+      <c r="Z17" s="793" t="n"/>
+      <c r="AA17" s="741" t="n"/>
+      <c r="AB17" s="793" t="n"/>
+      <c r="AC17" s="793" t="n"/>
+      <c r="AD17" s="793" t="n"/>
+      <c r="AE17" s="793" t="n"/>
+      <c r="AF17" s="793" t="n"/>
+      <c r="AG17" s="793" t="n"/>
+      <c r="AH17" s="793" t="n"/>
+      <c r="AI17" s="793" t="n"/>
+      <c r="AJ17" s="793" t="n"/>
+      <c r="AK17" s="793" t="n"/>
+      <c r="AL17" s="793" t="n"/>
+      <c r="AM17" s="793" t="n"/>
+      <c r="AN17" s="793" t="n"/>
+      <c r="AO17" s="793" t="n"/>
+      <c r="AP17" s="793" t="n"/>
+      <c r="AQ17" s="793" t="n"/>
+      <c r="AR17" s="724" t="n"/>
+      <c r="AS17" s="793" t="n"/>
+      <c r="AT17" s="793" t="n"/>
+      <c r="AU17" s="793" t="n"/>
+      <c r="AV17" s="793" t="n"/>
+      <c r="AW17" s="793" t="n"/>
+      <c r="AX17" s="724" t="n"/>
+      <c r="AY17" s="793" t="n"/>
+      <c r="AZ17" s="793" t="n"/>
+      <c r="BA17" s="793" t="n"/>
+      <c r="BB17" s="742" t="n"/>
+      <c r="BC17" s="793" t="n"/>
+      <c r="BD17" s="794" t="n"/>
     </row>
     <row r="18" ht="20" customHeight="1">
-      <c r="A18" s="494">
+      <c r="A18" s="739">
         <f>ROW()-ROW($A$16)+1</f>
         <v/>
       </c>
-      <c r="B18" s="423" t="n"/>
-      <c r="C18" s="423" t="n"/>
-      <c r="D18" s="495" t="n"/>
-      <c r="E18" s="577" t="n"/>
-      <c r="F18" s="577" t="n"/>
-      <c r="G18" s="577" t="n"/>
-      <c r="H18" s="477" t="n"/>
-      <c r="I18" s="577" t="n"/>
-      <c r="J18" s="577" t="n"/>
-      <c r="K18" s="577" t="n"/>
-      <c r="L18" s="577" t="n"/>
-      <c r="M18" s="577" t="n"/>
-      <c r="N18" s="577" t="n"/>
-      <c r="O18" s="577" t="n"/>
-      <c r="P18" s="577" t="n"/>
-      <c r="Q18" s="577" t="n"/>
-      <c r="R18" s="577" t="n"/>
-      <c r="S18" s="577" t="n"/>
-      <c r="T18" s="577" t="n"/>
-      <c r="U18" s="577" t="n"/>
-      <c r="V18" s="577" t="n"/>
-      <c r="W18" s="577" t="n"/>
-      <c r="X18" s="577" t="n"/>
-      <c r="Y18" s="577" t="n"/>
-      <c r="Z18" s="577" t="n"/>
-      <c r="AA18" s="496" t="n"/>
-      <c r="AB18" s="577" t="n"/>
-      <c r="AC18" s="577" t="n"/>
-      <c r="AD18" s="577" t="n"/>
-      <c r="AE18" s="577" t="n"/>
-      <c r="AF18" s="577" t="n"/>
-      <c r="AG18" s="577" t="n"/>
-      <c r="AH18" s="577" t="n"/>
-      <c r="AI18" s="577" t="n"/>
-      <c r="AJ18" s="577" t="n"/>
-      <c r="AK18" s="577" t="n"/>
-      <c r="AL18" s="577" t="n"/>
-      <c r="AM18" s="577" t="n"/>
-      <c r="AN18" s="577" t="n"/>
-      <c r="AO18" s="577" t="n"/>
-      <c r="AP18" s="577" t="n"/>
-      <c r="AQ18" s="577" t="n"/>
-      <c r="AR18" s="477" t="n"/>
-      <c r="AS18" s="577" t="n"/>
-      <c r="AT18" s="577" t="n"/>
-      <c r="AU18" s="577" t="n"/>
-      <c r="AV18" s="577" t="n"/>
-      <c r="AW18" s="577" t="n"/>
-      <c r="AX18" s="477" t="n"/>
-      <c r="AY18" s="577" t="n"/>
-      <c r="AZ18" s="577" t="n"/>
-      <c r="BA18" s="577" t="n"/>
-      <c r="BB18" s="585" t="n"/>
-      <c r="BC18" s="577" t="n"/>
-      <c r="BD18" s="579" t="n"/>
+      <c r="B18" s="792" t="n"/>
+      <c r="C18" s="792" t="n"/>
+      <c r="D18" s="740" t="n"/>
+      <c r="E18" s="793" t="n"/>
+      <c r="F18" s="793" t="n"/>
+      <c r="G18" s="793" t="n"/>
+      <c r="H18" s="724" t="n"/>
+      <c r="I18" s="793" t="n"/>
+      <c r="J18" s="793" t="n"/>
+      <c r="K18" s="793" t="n"/>
+      <c r="L18" s="793" t="n"/>
+      <c r="M18" s="793" t="n"/>
+      <c r="N18" s="793" t="n"/>
+      <c r="O18" s="793" t="n"/>
+      <c r="P18" s="793" t="n"/>
+      <c r="Q18" s="793" t="n"/>
+      <c r="R18" s="793" t="n"/>
+      <c r="S18" s="793" t="n"/>
+      <c r="T18" s="793" t="n"/>
+      <c r="U18" s="793" t="n"/>
+      <c r="V18" s="793" t="n"/>
+      <c r="W18" s="793" t="n"/>
+      <c r="X18" s="793" t="n"/>
+      <c r="Y18" s="793" t="n"/>
+      <c r="Z18" s="793" t="n"/>
+      <c r="AA18" s="741" t="n"/>
+      <c r="AB18" s="793" t="n"/>
+      <c r="AC18" s="793" t="n"/>
+      <c r="AD18" s="793" t="n"/>
+      <c r="AE18" s="793" t="n"/>
+      <c r="AF18" s="793" t="n"/>
+      <c r="AG18" s="793" t="n"/>
+      <c r="AH18" s="793" t="n"/>
+      <c r="AI18" s="793" t="n"/>
+      <c r="AJ18" s="793" t="n"/>
+      <c r="AK18" s="793" t="n"/>
+      <c r="AL18" s="793" t="n"/>
+      <c r="AM18" s="793" t="n"/>
+      <c r="AN18" s="793" t="n"/>
+      <c r="AO18" s="793" t="n"/>
+      <c r="AP18" s="793" t="n"/>
+      <c r="AQ18" s="793" t="n"/>
+      <c r="AR18" s="724" t="n"/>
+      <c r="AS18" s="793" t="n"/>
+      <c r="AT18" s="793" t="n"/>
+      <c r="AU18" s="793" t="n"/>
+      <c r="AV18" s="793" t="n"/>
+      <c r="AW18" s="793" t="n"/>
+      <c r="AX18" s="724" t="n"/>
+      <c r="AY18" s="793" t="n"/>
+      <c r="AZ18" s="793" t="n"/>
+      <c r="BA18" s="793" t="n"/>
+      <c r="BB18" s="742" t="n"/>
+      <c r="BC18" s="793" t="n"/>
+      <c r="BD18" s="794" t="n"/>
     </row>
     <row r="19" ht="20" customHeight="1">
-      <c r="A19" s="494">
+      <c r="A19" s="739">
         <f>ROW()-ROW($A$16)+1</f>
         <v/>
       </c>
-      <c r="B19" s="423" t="n"/>
-      <c r="C19" s="423" t="n"/>
-      <c r="D19" s="495" t="n"/>
-      <c r="E19" s="577" t="n"/>
-      <c r="F19" s="577" t="n"/>
-      <c r="G19" s="577" t="n"/>
-      <c r="H19" s="477" t="n"/>
-      <c r="I19" s="577" t="n"/>
-      <c r="J19" s="577" t="n"/>
-      <c r="K19" s="577" t="n"/>
-      <c r="L19" s="577" t="n"/>
-      <c r="M19" s="577" t="n"/>
-      <c r="N19" s="577" t="n"/>
-      <c r="O19" s="577" t="n"/>
-      <c r="P19" s="577" t="n"/>
-      <c r="Q19" s="577" t="n"/>
-      <c r="R19" s="577" t="n"/>
-      <c r="S19" s="577" t="n"/>
-      <c r="T19" s="577" t="n"/>
-      <c r="U19" s="577" t="n"/>
-      <c r="V19" s="577" t="n"/>
-      <c r="W19" s="577" t="n"/>
-      <c r="X19" s="577" t="n"/>
-      <c r="Y19" s="577" t="n"/>
-      <c r="Z19" s="577" t="n"/>
-      <c r="AA19" s="496" t="n"/>
-      <c r="AB19" s="577" t="n"/>
-      <c r="AC19" s="577" t="n"/>
-      <c r="AD19" s="577" t="n"/>
-      <c r="AE19" s="577" t="n"/>
-      <c r="AF19" s="577" t="n"/>
-      <c r="AG19" s="577" t="n"/>
-      <c r="AH19" s="577" t="n"/>
-      <c r="AI19" s="577" t="n"/>
-      <c r="AJ19" s="577" t="n"/>
-      <c r="AK19" s="577" t="n"/>
-      <c r="AL19" s="577" t="n"/>
-      <c r="AM19" s="577" t="n"/>
-      <c r="AN19" s="577" t="n"/>
-      <c r="AO19" s="577" t="n"/>
-      <c r="AP19" s="577" t="n"/>
-      <c r="AQ19" s="577" t="n"/>
-      <c r="AR19" s="477" t="n"/>
-      <c r="AS19" s="577" t="n"/>
-      <c r="AT19" s="577" t="n"/>
-      <c r="AU19" s="577" t="n"/>
-      <c r="AV19" s="577" t="n"/>
-      <c r="AW19" s="577" t="n"/>
-      <c r="AX19" s="477" t="n"/>
-      <c r="AY19" s="577" t="n"/>
-      <c r="AZ19" s="577" t="n"/>
-      <c r="BA19" s="577" t="n"/>
-      <c r="BB19" s="585" t="n"/>
-      <c r="BC19" s="577" t="n"/>
-      <c r="BD19" s="579" t="n"/>
+      <c r="B19" s="792" t="n"/>
+      <c r="C19" s="792" t="n"/>
+      <c r="D19" s="740" t="n"/>
+      <c r="E19" s="793" t="n"/>
+      <c r="F19" s="793" t="n"/>
+      <c r="G19" s="793" t="n"/>
+      <c r="H19" s="724" t="n"/>
+      <c r="I19" s="793" t="n"/>
+      <c r="J19" s="793" t="n"/>
+      <c r="K19" s="793" t="n"/>
+      <c r="L19" s="793" t="n"/>
+      <c r="M19" s="793" t="n"/>
+      <c r="N19" s="793" t="n"/>
+      <c r="O19" s="793" t="n"/>
+      <c r="P19" s="793" t="n"/>
+      <c r="Q19" s="793" t="n"/>
+      <c r="R19" s="793" t="n"/>
+      <c r="S19" s="793" t="n"/>
+      <c r="T19" s="793" t="n"/>
+      <c r="U19" s="793" t="n"/>
+      <c r="V19" s="793" t="n"/>
+      <c r="W19" s="793" t="n"/>
+      <c r="X19" s="793" t="n"/>
+      <c r="Y19" s="793" t="n"/>
+      <c r="Z19" s="793" t="n"/>
+      <c r="AA19" s="741" t="n"/>
+      <c r="AB19" s="793" t="n"/>
+      <c r="AC19" s="793" t="n"/>
+      <c r="AD19" s="793" t="n"/>
+      <c r="AE19" s="793" t="n"/>
+      <c r="AF19" s="793" t="n"/>
+      <c r="AG19" s="793" t="n"/>
+      <c r="AH19" s="793" t="n"/>
+      <c r="AI19" s="793" t="n"/>
+      <c r="AJ19" s="793" t="n"/>
+      <c r="AK19" s="793" t="n"/>
+      <c r="AL19" s="793" t="n"/>
+      <c r="AM19" s="793" t="n"/>
+      <c r="AN19" s="793" t="n"/>
+      <c r="AO19" s="793" t="n"/>
+      <c r="AP19" s="793" t="n"/>
+      <c r="AQ19" s="793" t="n"/>
+      <c r="AR19" s="724" t="n"/>
+      <c r="AS19" s="793" t="n"/>
+      <c r="AT19" s="793" t="n"/>
+      <c r="AU19" s="793" t="n"/>
+      <c r="AV19" s="793" t="n"/>
+      <c r="AW19" s="793" t="n"/>
+      <c r="AX19" s="724" t="n"/>
+      <c r="AY19" s="793" t="n"/>
+      <c r="AZ19" s="793" t="n"/>
+      <c r="BA19" s="793" t="n"/>
+      <c r="BB19" s="742" t="n"/>
+      <c r="BC19" s="793" t="n"/>
+      <c r="BD19" s="794" t="n"/>
     </row>
     <row r="20" ht="20" customHeight="1">
-      <c r="A20" s="494">
+      <c r="A20" s="739">
         <f>ROW()-ROW($A$16)+1</f>
         <v/>
       </c>
-      <c r="B20" s="423" t="n"/>
-      <c r="C20" s="423" t="n"/>
-      <c r="D20" s="495" t="n"/>
-      <c r="E20" s="577" t="n"/>
-      <c r="F20" s="577" t="n"/>
-      <c r="G20" s="577" t="n"/>
-      <c r="H20" s="477" t="n"/>
-      <c r="I20" s="577" t="n"/>
-      <c r="J20" s="577" t="n"/>
-      <c r="K20" s="577" t="n"/>
-      <c r="L20" s="577" t="n"/>
-      <c r="M20" s="577" t="n"/>
-      <c r="N20" s="577" t="n"/>
-      <c r="O20" s="577" t="n"/>
-      <c r="P20" s="577" t="n"/>
-      <c r="Q20" s="577" t="n"/>
-      <c r="R20" s="577" t="n"/>
-      <c r="S20" s="577" t="n"/>
-      <c r="T20" s="577" t="n"/>
-      <c r="U20" s="577" t="n"/>
-      <c r="V20" s="577" t="n"/>
-      <c r="W20" s="577" t="n"/>
-      <c r="X20" s="577" t="n"/>
-      <c r="Y20" s="577" t="n"/>
-      <c r="Z20" s="577" t="n"/>
-      <c r="AA20" s="496" t="n"/>
-      <c r="AB20" s="577" t="n"/>
-      <c r="AC20" s="577" t="n"/>
-      <c r="AD20" s="577" t="n"/>
-      <c r="AE20" s="577" t="n"/>
-      <c r="AF20" s="577" t="n"/>
-      <c r="AG20" s="577" t="n"/>
-      <c r="AH20" s="577" t="n"/>
-      <c r="AI20" s="577" t="n"/>
-      <c r="AJ20" s="577" t="n"/>
-      <c r="AK20" s="577" t="n"/>
-      <c r="AL20" s="577" t="n"/>
-      <c r="AM20" s="577" t="n"/>
-      <c r="AN20" s="577" t="n"/>
-      <c r="AO20" s="577" t="n"/>
-      <c r="AP20" s="577" t="n"/>
-      <c r="AQ20" s="577" t="n"/>
-      <c r="AR20" s="477" t="n"/>
-      <c r="AS20" s="577" t="n"/>
-      <c r="AT20" s="577" t="n"/>
-      <c r="AU20" s="577" t="n"/>
-      <c r="AV20" s="577" t="n"/>
-      <c r="AW20" s="577" t="n"/>
-      <c r="AX20" s="477" t="n"/>
-      <c r="AY20" s="577" t="n"/>
-      <c r="AZ20" s="577" t="n"/>
-      <c r="BA20" s="577" t="n"/>
-      <c r="BB20" s="585" t="n"/>
-      <c r="BC20" s="577" t="n"/>
-      <c r="BD20" s="579" t="n"/>
+      <c r="B20" s="792" t="n"/>
+      <c r="C20" s="792" t="n"/>
+      <c r="D20" s="740" t="n"/>
+      <c r="E20" s="793" t="n"/>
+      <c r="F20" s="793" t="n"/>
+      <c r="G20" s="793" t="n"/>
+      <c r="H20" s="724" t="n"/>
+      <c r="I20" s="793" t="n"/>
+      <c r="J20" s="793" t="n"/>
+      <c r="K20" s="793" t="n"/>
+      <c r="L20" s="793" t="n"/>
+      <c r="M20" s="793" t="n"/>
+      <c r="N20" s="793" t="n"/>
+      <c r="O20" s="793" t="n"/>
+      <c r="P20" s="793" t="n"/>
+      <c r="Q20" s="793" t="n"/>
+      <c r="R20" s="793" t="n"/>
+      <c r="S20" s="793" t="n"/>
+      <c r="T20" s="793" t="n"/>
+      <c r="U20" s="793" t="n"/>
+      <c r="V20" s="793" t="n"/>
+      <c r="W20" s="793" t="n"/>
+      <c r="X20" s="793" t="n"/>
+      <c r="Y20" s="793" t="n"/>
+      <c r="Z20" s="793" t="n"/>
+      <c r="AA20" s="741" t="n"/>
+      <c r="AB20" s="793" t="n"/>
+      <c r="AC20" s="793" t="n"/>
+      <c r="AD20" s="793" t="n"/>
+      <c r="AE20" s="793" t="n"/>
+      <c r="AF20" s="793" t="n"/>
+      <c r="AG20" s="793" t="n"/>
+      <c r="AH20" s="793" t="n"/>
+      <c r="AI20" s="793" t="n"/>
+      <c r="AJ20" s="793" t="n"/>
+      <c r="AK20" s="793" t="n"/>
+      <c r="AL20" s="793" t="n"/>
+      <c r="AM20" s="793" t="n"/>
+      <c r="AN20" s="793" t="n"/>
+      <c r="AO20" s="793" t="n"/>
+      <c r="AP20" s="793" t="n"/>
+      <c r="AQ20" s="793" t="n"/>
+      <c r="AR20" s="724" t="n"/>
+      <c r="AS20" s="793" t="n"/>
+      <c r="AT20" s="793" t="n"/>
+      <c r="AU20" s="793" t="n"/>
+      <c r="AV20" s="793" t="n"/>
+      <c r="AW20" s="793" t="n"/>
+      <c r="AX20" s="724" t="n"/>
+      <c r="AY20" s="793" t="n"/>
+      <c r="AZ20" s="793" t="n"/>
+      <c r="BA20" s="793" t="n"/>
+      <c r="BB20" s="742" t="n"/>
+      <c r="BC20" s="793" t="n"/>
+      <c r="BD20" s="794" t="n"/>
     </row>
     <row r="21" ht="20" customHeight="1">
-      <c r="A21" s="494">
+      <c r="A21" s="739">
         <f>ROW()-ROW($A$16)+1</f>
         <v/>
       </c>
-      <c r="B21" s="423" t="n"/>
-      <c r="C21" s="423" t="n"/>
-      <c r="D21" s="495" t="n"/>
-      <c r="E21" s="577" t="n"/>
-      <c r="F21" s="577" t="n"/>
-      <c r="G21" s="577" t="n"/>
-      <c r="H21" s="477" t="n"/>
-      <c r="I21" s="577" t="n"/>
-      <c r="J21" s="577" t="n"/>
-      <c r="K21" s="577" t="n"/>
-      <c r="L21" s="577" t="n"/>
-      <c r="M21" s="577" t="n"/>
-      <c r="N21" s="577" t="n"/>
-      <c r="O21" s="577" t="n"/>
-      <c r="P21" s="577" t="n"/>
-      <c r="Q21" s="577" t="n"/>
-      <c r="R21" s="577" t="n"/>
-      <c r="S21" s="577" t="n"/>
-      <c r="T21" s="577" t="n"/>
-      <c r="U21" s="577" t="n"/>
-      <c r="V21" s="577" t="n"/>
-      <c r="W21" s="577" t="n"/>
-      <c r="X21" s="577" t="n"/>
-      <c r="Y21" s="577" t="n"/>
-      <c r="Z21" s="577" t="n"/>
-      <c r="AA21" s="496" t="n"/>
-      <c r="AB21" s="577" t="n"/>
-      <c r="AC21" s="577" t="n"/>
-      <c r="AD21" s="577" t="n"/>
-      <c r="AE21" s="577" t="n"/>
-      <c r="AF21" s="577" t="n"/>
-      <c r="AG21" s="577" t="n"/>
-      <c r="AH21" s="577" t="n"/>
-      <c r="AI21" s="577" t="n"/>
-      <c r="AJ21" s="577" t="n"/>
-      <c r="AK21" s="577" t="n"/>
-      <c r="AL21" s="577" t="n"/>
-      <c r="AM21" s="577" t="n"/>
-      <c r="AN21" s="577" t="n"/>
-      <c r="AO21" s="577" t="n"/>
-      <c r="AP21" s="577" t="n"/>
-      <c r="AQ21" s="577" t="n"/>
-      <c r="AR21" s="477" t="n"/>
-      <c r="AS21" s="577" t="n"/>
-      <c r="AT21" s="577" t="n"/>
-      <c r="AU21" s="577" t="n"/>
-      <c r="AV21" s="577" t="n"/>
-      <c r="AW21" s="577" t="n"/>
-      <c r="AX21" s="477" t="n"/>
-      <c r="AY21" s="577" t="n"/>
-      <c r="AZ21" s="577" t="n"/>
-      <c r="BA21" s="577" t="n"/>
-      <c r="BB21" s="585" t="n"/>
-      <c r="BC21" s="577" t="n"/>
-      <c r="BD21" s="579" t="n"/>
+      <c r="B21" s="792" t="n"/>
+      <c r="C21" s="792" t="n"/>
+      <c r="D21" s="740" t="n"/>
+      <c r="E21" s="793" t="n"/>
+      <c r="F21" s="793" t="n"/>
+      <c r="G21" s="793" t="n"/>
+      <c r="H21" s="724" t="n"/>
+      <c r="I21" s="793" t="n"/>
+      <c r="J21" s="793" t="n"/>
+      <c r="K21" s="793" t="n"/>
+      <c r="L21" s="793" t="n"/>
+      <c r="M21" s="793" t="n"/>
+      <c r="N21" s="793" t="n"/>
+      <c r="O21" s="793" t="n"/>
+      <c r="P21" s="793" t="n"/>
+      <c r="Q21" s="793" t="n"/>
+      <c r="R21" s="793" t="n"/>
+      <c r="S21" s="793" t="n"/>
+      <c r="T21" s="793" t="n"/>
+      <c r="U21" s="793" t="n"/>
+      <c r="V21" s="793" t="n"/>
+      <c r="W21" s="793" t="n"/>
+      <c r="X21" s="793" t="n"/>
+      <c r="Y21" s="793" t="n"/>
+      <c r="Z21" s="793" t="n"/>
+      <c r="AA21" s="741" t="n"/>
+      <c r="AB21" s="793" t="n"/>
+      <c r="AC21" s="793" t="n"/>
+      <c r="AD21" s="793" t="n"/>
+      <c r="AE21" s="793" t="n"/>
+      <c r="AF21" s="793" t="n"/>
+      <c r="AG21" s="793" t="n"/>
+      <c r="AH21" s="793" t="n"/>
+      <c r="AI21" s="793" t="n"/>
+      <c r="AJ21" s="793" t="n"/>
+      <c r="AK21" s="793" t="n"/>
+      <c r="AL21" s="793" t="n"/>
+      <c r="AM21" s="793" t="n"/>
+      <c r="AN21" s="793" t="n"/>
+      <c r="AO21" s="793" t="n"/>
+      <c r="AP21" s="793" t="n"/>
+      <c r="AQ21" s="793" t="n"/>
+      <c r="AR21" s="724" t="n"/>
+      <c r="AS21" s="793" t="n"/>
+      <c r="AT21" s="793" t="n"/>
+      <c r="AU21" s="793" t="n"/>
+      <c r="AV21" s="793" t="n"/>
+      <c r="AW21" s="793" t="n"/>
+      <c r="AX21" s="724" t="n"/>
+      <c r="AY21" s="793" t="n"/>
+      <c r="AZ21" s="793" t="n"/>
+      <c r="BA21" s="793" t="n"/>
+      <c r="BB21" s="742" t="n"/>
+      <c r="BC21" s="793" t="n"/>
+      <c r="BD21" s="794" t="n"/>
     </row>
     <row r="22" ht="20" customHeight="1">
-      <c r="A22" s="494">
+      <c r="A22" s="739">
         <f>ROW()-ROW($A$16)+1</f>
         <v/>
       </c>
-      <c r="B22" s="423" t="n"/>
-      <c r="C22" s="423" t="n"/>
-      <c r="D22" s="495" t="n"/>
-      <c r="E22" s="577" t="n"/>
-      <c r="F22" s="577" t="n"/>
-      <c r="G22" s="577" t="n"/>
-      <c r="H22" s="477" t="n"/>
-      <c r="I22" s="577" t="n"/>
-      <c r="J22" s="577" t="n"/>
-      <c r="K22" s="577" t="n"/>
-      <c r="L22" s="577" t="n"/>
-      <c r="M22" s="577" t="n"/>
-      <c r="N22" s="577" t="n"/>
-      <c r="O22" s="577" t="n"/>
-      <c r="P22" s="577" t="n"/>
-      <c r="Q22" s="577" t="n"/>
-      <c r="R22" s="577" t="n"/>
-      <c r="S22" s="577" t="n"/>
-      <c r="T22" s="577" t="n"/>
-      <c r="U22" s="577" t="n"/>
-      <c r="V22" s="577" t="n"/>
-      <c r="W22" s="577" t="n"/>
-      <c r="X22" s="577" t="n"/>
-      <c r="Y22" s="577" t="n"/>
-      <c r="Z22" s="577" t="n"/>
-      <c r="AA22" s="496" t="n"/>
-      <c r="AB22" s="577" t="n"/>
-      <c r="AC22" s="577" t="n"/>
-      <c r="AD22" s="577" t="n"/>
-      <c r="AE22" s="577" t="n"/>
-      <c r="AF22" s="577" t="n"/>
-      <c r="AG22" s="577" t="n"/>
-      <c r="AH22" s="577" t="n"/>
-      <c r="AI22" s="577" t="n"/>
-      <c r="AJ22" s="577" t="n"/>
-      <c r="AK22" s="577" t="n"/>
-      <c r="AL22" s="577" t="n"/>
-      <c r="AM22" s="577" t="n"/>
-      <c r="AN22" s="577" t="n"/>
-      <c r="AO22" s="577" t="n"/>
-      <c r="AP22" s="577" t="n"/>
-      <c r="AQ22" s="577" t="n"/>
-      <c r="AR22" s="477" t="n"/>
-      <c r="AS22" s="577" t="n"/>
-      <c r="AT22" s="577" t="n"/>
-      <c r="AU22" s="577" t="n"/>
-      <c r="AV22" s="577" t="n"/>
-      <c r="AW22" s="577" t="n"/>
-      <c r="AX22" s="477" t="n"/>
-      <c r="AY22" s="577" t="n"/>
-      <c r="AZ22" s="577" t="n"/>
-      <c r="BA22" s="577" t="n"/>
-      <c r="BB22" s="585" t="n"/>
-      <c r="BC22" s="577" t="n"/>
-      <c r="BD22" s="579" t="n"/>
+      <c r="B22" s="792" t="n"/>
+      <c r="C22" s="792" t="n"/>
+      <c r="D22" s="740" t="n"/>
+      <c r="E22" s="793" t="n"/>
+      <c r="F22" s="793" t="n"/>
+      <c r="G22" s="793" t="n"/>
+      <c r="H22" s="724" t="n"/>
+      <c r="I22" s="793" t="n"/>
+      <c r="J22" s="793" t="n"/>
+      <c r="K22" s="793" t="n"/>
+      <c r="L22" s="793" t="n"/>
+      <c r="M22" s="793" t="n"/>
+      <c r="N22" s="793" t="n"/>
+      <c r="O22" s="793" t="n"/>
+      <c r="P22" s="793" t="n"/>
+      <c r="Q22" s="793" t="n"/>
+      <c r="R22" s="793" t="n"/>
+      <c r="S22" s="793" t="n"/>
+      <c r="T22" s="793" t="n"/>
+      <c r="U22" s="793" t="n"/>
+      <c r="V22" s="793" t="n"/>
+      <c r="W22" s="793" t="n"/>
+      <c r="X22" s="793" t="n"/>
+      <c r="Y22" s="793" t="n"/>
+      <c r="Z22" s="793" t="n"/>
+      <c r="AA22" s="741" t="n"/>
+      <c r="AB22" s="793" t="n"/>
+      <c r="AC22" s="793" t="n"/>
+      <c r="AD22" s="793" t="n"/>
+      <c r="AE22" s="793" t="n"/>
+      <c r="AF22" s="793" t="n"/>
+      <c r="AG22" s="793" t="n"/>
+      <c r="AH22" s="793" t="n"/>
+      <c r="AI22" s="793" t="n"/>
+      <c r="AJ22" s="793" t="n"/>
+      <c r="AK22" s="793" t="n"/>
+      <c r="AL22" s="793" t="n"/>
+      <c r="AM22" s="793" t="n"/>
+      <c r="AN22" s="793" t="n"/>
+      <c r="AO22" s="793" t="n"/>
+      <c r="AP22" s="793" t="n"/>
+      <c r="AQ22" s="793" t="n"/>
+      <c r="AR22" s="724" t="n"/>
+      <c r="AS22" s="793" t="n"/>
+      <c r="AT22" s="793" t="n"/>
+      <c r="AU22" s="793" t="n"/>
+      <c r="AV22" s="793" t="n"/>
+      <c r="AW22" s="793" t="n"/>
+      <c r="AX22" s="724" t="n"/>
+      <c r="AY22" s="793" t="n"/>
+      <c r="AZ22" s="793" t="n"/>
+      <c r="BA22" s="793" t="n"/>
+      <c r="BB22" s="742" t="n"/>
+      <c r="BC22" s="793" t="n"/>
+      <c r="BD22" s="794" t="n"/>
     </row>
     <row r="23" ht="20" customHeight="1">
-      <c r="A23" s="498">
+      <c r="A23" s="743">
         <f>ROW()-ROW($A$16)+1</f>
         <v/>
       </c>
-      <c r="B23" s="566" t="n"/>
-      <c r="C23" s="566" t="n"/>
-      <c r="D23" s="499" t="n"/>
-      <c r="E23" s="580" t="n"/>
-      <c r="F23" s="580" t="n"/>
-      <c r="G23" s="580" t="n"/>
-      <c r="H23" s="482" t="n"/>
-      <c r="I23" s="580" t="n"/>
-      <c r="J23" s="580" t="n"/>
-      <c r="K23" s="580" t="n"/>
-      <c r="L23" s="580" t="n"/>
-      <c r="M23" s="580" t="n"/>
-      <c r="N23" s="580" t="n"/>
-      <c r="O23" s="580" t="n"/>
-      <c r="P23" s="580" t="n"/>
-      <c r="Q23" s="580" t="n"/>
-      <c r="R23" s="580" t="n"/>
-      <c r="S23" s="580" t="n"/>
-      <c r="T23" s="580" t="n"/>
-      <c r="U23" s="580" t="n"/>
-      <c r="V23" s="580" t="n"/>
-      <c r="W23" s="580" t="n"/>
-      <c r="X23" s="580" t="n"/>
-      <c r="Y23" s="580" t="n"/>
-      <c r="Z23" s="580" t="n"/>
-      <c r="AA23" s="500" t="n"/>
-      <c r="AB23" s="580" t="n"/>
-      <c r="AC23" s="580" t="n"/>
-      <c r="AD23" s="580" t="n"/>
-      <c r="AE23" s="580" t="n"/>
-      <c r="AF23" s="580" t="n"/>
-      <c r="AG23" s="580" t="n"/>
-      <c r="AH23" s="580" t="n"/>
-      <c r="AI23" s="580" t="n"/>
-      <c r="AJ23" s="580" t="n"/>
-      <c r="AK23" s="580" t="n"/>
-      <c r="AL23" s="580" t="n"/>
-      <c r="AM23" s="580" t="n"/>
-      <c r="AN23" s="580" t="n"/>
-      <c r="AO23" s="580" t="n"/>
-      <c r="AP23" s="580" t="n"/>
-      <c r="AQ23" s="580" t="n"/>
-      <c r="AR23" s="482" t="n"/>
-      <c r="AS23" s="580" t="n"/>
-      <c r="AT23" s="580" t="n"/>
-      <c r="AU23" s="580" t="n"/>
-      <c r="AV23" s="580" t="n"/>
-      <c r="AW23" s="580" t="n"/>
-      <c r="AX23" s="482" t="n"/>
-      <c r="AY23" s="580" t="n"/>
-      <c r="AZ23" s="580" t="n"/>
-      <c r="BA23" s="580" t="n"/>
-      <c r="BB23" s="586" t="n"/>
-      <c r="BC23" s="580" t="n"/>
-      <c r="BD23" s="582" t="n"/>
+      <c r="B23" s="795" t="n"/>
+      <c r="C23" s="795" t="n"/>
+      <c r="D23" s="744" t="n"/>
+      <c r="E23" s="796" t="n"/>
+      <c r="F23" s="796" t="n"/>
+      <c r="G23" s="796" t="n"/>
+      <c r="H23" s="728" t="n"/>
+      <c r="I23" s="796" t="n"/>
+      <c r="J23" s="796" t="n"/>
+      <c r="K23" s="796" t="n"/>
+      <c r="L23" s="796" t="n"/>
+      <c r="M23" s="796" t="n"/>
+      <c r="N23" s="796" t="n"/>
+      <c r="O23" s="796" t="n"/>
+      <c r="P23" s="796" t="n"/>
+      <c r="Q23" s="796" t="n"/>
+      <c r="R23" s="796" t="n"/>
+      <c r="S23" s="796" t="n"/>
+      <c r="T23" s="796" t="n"/>
+      <c r="U23" s="796" t="n"/>
+      <c r="V23" s="796" t="n"/>
+      <c r="W23" s="796" t="n"/>
+      <c r="X23" s="796" t="n"/>
+      <c r="Y23" s="796" t="n"/>
+      <c r="Z23" s="796" t="n"/>
+      <c r="AA23" s="745" t="n"/>
+      <c r="AB23" s="796" t="n"/>
+      <c r="AC23" s="796" t="n"/>
+      <c r="AD23" s="796" t="n"/>
+      <c r="AE23" s="796" t="n"/>
+      <c r="AF23" s="796" t="n"/>
+      <c r="AG23" s="796" t="n"/>
+      <c r="AH23" s="796" t="n"/>
+      <c r="AI23" s="796" t="n"/>
+      <c r="AJ23" s="796" t="n"/>
+      <c r="AK23" s="796" t="n"/>
+      <c r="AL23" s="796" t="n"/>
+      <c r="AM23" s="796" t="n"/>
+      <c r="AN23" s="796" t="n"/>
+      <c r="AO23" s="796" t="n"/>
+      <c r="AP23" s="796" t="n"/>
+      <c r="AQ23" s="796" t="n"/>
+      <c r="AR23" s="728" t="n"/>
+      <c r="AS23" s="796" t="n"/>
+      <c r="AT23" s="796" t="n"/>
+      <c r="AU23" s="796" t="n"/>
+      <c r="AV23" s="796" t="n"/>
+      <c r="AW23" s="796" t="n"/>
+      <c r="AX23" s="728" t="n"/>
+      <c r="AY23" s="796" t="n"/>
+      <c r="AZ23" s="796" t="n"/>
+      <c r="BA23" s="796" t="n"/>
+      <c r="BB23" s="746" t="n"/>
+      <c r="BC23" s="796" t="n"/>
+      <c r="BD23" s="797" t="n"/>
     </row>
     <row r="24" ht="3" customHeight="1">
       <c r="A24" s="375" t="n"/>
@@ -8678,198 +9223,198 @@
       <c r="BD24" s="353" t="n"/>
     </row>
     <row r="25" ht="18" customHeight="1">
-      <c r="A25" s="570" t="inlineStr">
+      <c r="A25" s="731" t="inlineStr">
         <is>
           <t xml:space="preserve">  3. CONDITIONS / ACTIONS / RELEASE</t>
         </is>
       </c>
-      <c r="B25" s="571" t="n"/>
-      <c r="C25" s="571" t="n"/>
-      <c r="D25" s="571" t="n"/>
-      <c r="E25" s="571" t="n"/>
-      <c r="F25" s="571" t="n"/>
-      <c r="G25" s="571" t="n"/>
-      <c r="H25" s="571" t="n"/>
-      <c r="I25" s="571" t="n"/>
-      <c r="J25" s="571" t="n"/>
-      <c r="K25" s="571" t="n"/>
-      <c r="L25" s="571" t="n"/>
-      <c r="M25" s="571" t="n"/>
-      <c r="N25" s="571" t="n"/>
-      <c r="O25" s="571" t="n"/>
-      <c r="P25" s="571" t="n"/>
-      <c r="Q25" s="571" t="n"/>
-      <c r="R25" s="571" t="n"/>
-      <c r="S25" s="571" t="n"/>
-      <c r="T25" s="571" t="n"/>
-      <c r="U25" s="571" t="n"/>
-      <c r="V25" s="571" t="n"/>
-      <c r="W25" s="571" t="n"/>
-      <c r="X25" s="571" t="n"/>
-      <c r="Y25" s="571" t="n"/>
-      <c r="Z25" s="571" t="n"/>
-      <c r="AA25" s="571" t="n"/>
-      <c r="AB25" s="571" t="n"/>
-      <c r="AC25" s="571" t="n"/>
-      <c r="AD25" s="571" t="n"/>
-      <c r="AE25" s="571" t="n"/>
-      <c r="AF25" s="571" t="n"/>
-      <c r="AG25" s="571" t="n"/>
-      <c r="AH25" s="571" t="n"/>
-      <c r="AI25" s="571" t="n"/>
-      <c r="AJ25" s="571" t="n"/>
-      <c r="AK25" s="571" t="n"/>
-      <c r="AL25" s="571" t="n"/>
-      <c r="AM25" s="571" t="n"/>
-      <c r="AN25" s="571" t="n"/>
-      <c r="AO25" s="571" t="n"/>
-      <c r="AP25" s="571" t="n"/>
-      <c r="AQ25" s="571" t="n"/>
-      <c r="AR25" s="571" t="n"/>
-      <c r="AS25" s="571" t="n"/>
-      <c r="AT25" s="571" t="n"/>
-      <c r="AU25" s="571" t="n"/>
-      <c r="AV25" s="571" t="n"/>
-      <c r="AW25" s="571" t="n"/>
-      <c r="AX25" s="571" t="n"/>
-      <c r="AY25" s="571" t="n"/>
-      <c r="AZ25" s="571" t="n"/>
-      <c r="BA25" s="571" t="n"/>
-      <c r="BB25" s="571" t="n"/>
-      <c r="BC25" s="571" t="n"/>
-      <c r="BD25" s="572" t="n"/>
+      <c r="B25" s="285" t="n"/>
+      <c r="C25" s="285" t="n"/>
+      <c r="D25" s="285" t="n"/>
+      <c r="E25" s="285" t="n"/>
+      <c r="F25" s="285" t="n"/>
+      <c r="G25" s="285" t="n"/>
+      <c r="H25" s="285" t="n"/>
+      <c r="I25" s="285" t="n"/>
+      <c r="J25" s="285" t="n"/>
+      <c r="K25" s="285" t="n"/>
+      <c r="L25" s="285" t="n"/>
+      <c r="M25" s="285" t="n"/>
+      <c r="N25" s="285" t="n"/>
+      <c r="O25" s="285" t="n"/>
+      <c r="P25" s="285" t="n"/>
+      <c r="Q25" s="285" t="n"/>
+      <c r="R25" s="285" t="n"/>
+      <c r="S25" s="285" t="n"/>
+      <c r="T25" s="285" t="n"/>
+      <c r="U25" s="285" t="n"/>
+      <c r="V25" s="285" t="n"/>
+      <c r="W25" s="285" t="n"/>
+      <c r="X25" s="285" t="n"/>
+      <c r="Y25" s="285" t="n"/>
+      <c r="Z25" s="285" t="n"/>
+      <c r="AA25" s="285" t="n"/>
+      <c r="AB25" s="285" t="n"/>
+      <c r="AC25" s="285" t="n"/>
+      <c r="AD25" s="285" t="n"/>
+      <c r="AE25" s="285" t="n"/>
+      <c r="AF25" s="285" t="n"/>
+      <c r="AG25" s="285" t="n"/>
+      <c r="AH25" s="285" t="n"/>
+      <c r="AI25" s="285" t="n"/>
+      <c r="AJ25" s="285" t="n"/>
+      <c r="AK25" s="285" t="n"/>
+      <c r="AL25" s="285" t="n"/>
+      <c r="AM25" s="285" t="n"/>
+      <c r="AN25" s="285" t="n"/>
+      <c r="AO25" s="285" t="n"/>
+      <c r="AP25" s="285" t="n"/>
+      <c r="AQ25" s="285" t="n"/>
+      <c r="AR25" s="285" t="n"/>
+      <c r="AS25" s="285" t="n"/>
+      <c r="AT25" s="285" t="n"/>
+      <c r="AU25" s="285" t="n"/>
+      <c r="AV25" s="285" t="n"/>
+      <c r="AW25" s="285" t="n"/>
+      <c r="AX25" s="285" t="n"/>
+      <c r="AY25" s="285" t="n"/>
+      <c r="AZ25" s="285" t="n"/>
+      <c r="BA25" s="285" t="n"/>
+      <c r="BB25" s="285" t="n"/>
+      <c r="BC25" s="285" t="n"/>
+      <c r="BD25" s="286" t="n"/>
     </row>
     <row r="26" ht="20" customHeight="1">
-      <c r="A26" s="470" t="inlineStr">
+      <c r="A26" s="719" t="inlineStr">
         <is>
           <t>Conditional Action Required (YES/NO)</t>
         </is>
       </c>
-      <c r="B26" s="573" t="n"/>
-      <c r="C26" s="573" t="n"/>
-      <c r="D26" s="573" t="n"/>
-      <c r="E26" s="573" t="n"/>
-      <c r="F26" s="573" t="n"/>
-      <c r="G26" s="573" t="n"/>
-      <c r="H26" s="573" t="n"/>
-      <c r="I26" s="573" t="n"/>
-      <c r="J26" s="573" t="n"/>
-      <c r="K26" s="472" t="n"/>
-      <c r="L26" s="574" t="n"/>
-      <c r="M26" s="574" t="n"/>
-      <c r="N26" s="574" t="n"/>
-      <c r="O26" s="574" t="n"/>
-      <c r="P26" s="574" t="n"/>
-      <c r="Q26" s="574" t="n"/>
-      <c r="R26" s="574" t="n"/>
-      <c r="S26" s="574" t="n"/>
-      <c r="T26" s="574" t="n"/>
-      <c r="U26" s="574" t="n"/>
-      <c r="V26" s="574" t="n"/>
-      <c r="W26" s="574" t="n"/>
-      <c r="X26" s="574" t="n"/>
-      <c r="Y26" s="574" t="n"/>
-      <c r="Z26" s="574" t="n"/>
-      <c r="AA26" s="574" t="n"/>
-      <c r="AB26" s="574" t="n"/>
-      <c r="AC26" s="474" t="inlineStr">
+      <c r="B26" s="271" t="n"/>
+      <c r="C26" s="271" t="n"/>
+      <c r="D26" s="271" t="n"/>
+      <c r="E26" s="271" t="n"/>
+      <c r="F26" s="271" t="n"/>
+      <c r="G26" s="271" t="n"/>
+      <c r="H26" s="271" t="n"/>
+      <c r="I26" s="271" t="n"/>
+      <c r="J26" s="271" t="n"/>
+      <c r="K26" s="720" t="n"/>
+      <c r="L26" s="320" t="n"/>
+      <c r="M26" s="320" t="n"/>
+      <c r="N26" s="320" t="n"/>
+      <c r="O26" s="320" t="n"/>
+      <c r="P26" s="320" t="n"/>
+      <c r="Q26" s="320" t="n"/>
+      <c r="R26" s="320" t="n"/>
+      <c r="S26" s="320" t="n"/>
+      <c r="T26" s="320" t="n"/>
+      <c r="U26" s="320" t="n"/>
+      <c r="V26" s="320" t="n"/>
+      <c r="W26" s="320" t="n"/>
+      <c r="X26" s="320" t="n"/>
+      <c r="Y26" s="320" t="n"/>
+      <c r="Z26" s="320" t="n"/>
+      <c r="AA26" s="320" t="n"/>
+      <c r="AB26" s="320" t="n"/>
+      <c r="AC26" s="721" t="inlineStr">
         <is>
           <t>Bagging / Seal Ref</t>
         </is>
       </c>
-      <c r="AD26" s="573" t="n"/>
-      <c r="AE26" s="573" t="n"/>
-      <c r="AF26" s="573" t="n"/>
-      <c r="AG26" s="573" t="n"/>
-      <c r="AH26" s="573" t="n"/>
-      <c r="AI26" s="573" t="n"/>
-      <c r="AJ26" s="573" t="n"/>
-      <c r="AK26" s="573" t="n"/>
-      <c r="AL26" s="573" t="n"/>
-      <c r="AM26" s="575" t="n"/>
-      <c r="AN26" s="574" t="n"/>
-      <c r="AO26" s="574" t="n"/>
-      <c r="AP26" s="574" t="n"/>
-      <c r="AQ26" s="574" t="n"/>
-      <c r="AR26" s="574" t="n"/>
-      <c r="AS26" s="574" t="n"/>
-      <c r="AT26" s="574" t="n"/>
-      <c r="AU26" s="574" t="n"/>
-      <c r="AV26" s="574" t="n"/>
-      <c r="AW26" s="574" t="n"/>
-      <c r="AX26" s="574" t="n"/>
-      <c r="AY26" s="574" t="n"/>
-      <c r="AZ26" s="574" t="n"/>
-      <c r="BA26" s="574" t="n"/>
-      <c r="BB26" s="574" t="n"/>
-      <c r="BC26" s="574" t="n"/>
-      <c r="BD26" s="576" t="n"/>
+      <c r="AD26" s="271" t="n"/>
+      <c r="AE26" s="271" t="n"/>
+      <c r="AF26" s="271" t="n"/>
+      <c r="AG26" s="271" t="n"/>
+      <c r="AH26" s="271" t="n"/>
+      <c r="AI26" s="271" t="n"/>
+      <c r="AJ26" s="271" t="n"/>
+      <c r="AK26" s="271" t="n"/>
+      <c r="AL26" s="271" t="n"/>
+      <c r="AM26" s="722" t="n"/>
+      <c r="AN26" s="320" t="n"/>
+      <c r="AO26" s="320" t="n"/>
+      <c r="AP26" s="320" t="n"/>
+      <c r="AQ26" s="320" t="n"/>
+      <c r="AR26" s="320" t="n"/>
+      <c r="AS26" s="320" t="n"/>
+      <c r="AT26" s="320" t="n"/>
+      <c r="AU26" s="320" t="n"/>
+      <c r="AV26" s="320" t="n"/>
+      <c r="AW26" s="320" t="n"/>
+      <c r="AX26" s="320" t="n"/>
+      <c r="AY26" s="320" t="n"/>
+      <c r="AZ26" s="320" t="n"/>
+      <c r="BA26" s="320" t="n"/>
+      <c r="BB26" s="320" t="n"/>
+      <c r="BC26" s="320" t="n"/>
+      <c r="BD26" s="322" t="n"/>
     </row>
     <row r="27" ht="20" customHeight="1">
-      <c r="A27" s="480" t="inlineStr">
+      <c r="A27" s="727" t="inlineStr">
         <is>
           <t>Final Release Decision</t>
         </is>
       </c>
-      <c r="B27" s="566" t="n"/>
-      <c r="C27" s="566" t="n"/>
-      <c r="D27" s="566" t="n"/>
-      <c r="E27" s="566" t="n"/>
-      <c r="F27" s="566" t="n"/>
-      <c r="G27" s="566" t="n"/>
-      <c r="H27" s="566" t="n"/>
-      <c r="I27" s="566" t="n"/>
-      <c r="J27" s="566" t="n"/>
-      <c r="K27" s="482" t="n"/>
-      <c r="L27" s="580" t="n"/>
-      <c r="M27" s="580" t="n"/>
-      <c r="N27" s="580" t="n"/>
-      <c r="O27" s="580" t="n"/>
-      <c r="P27" s="580" t="n"/>
-      <c r="Q27" s="580" t="n"/>
-      <c r="R27" s="580" t="n"/>
-      <c r="S27" s="580" t="n"/>
-      <c r="T27" s="580" t="n"/>
-      <c r="U27" s="580" t="n"/>
-      <c r="V27" s="580" t="n"/>
-      <c r="W27" s="580" t="n"/>
-      <c r="X27" s="580" t="n"/>
-      <c r="Y27" s="580" t="n"/>
-      <c r="Z27" s="580" t="n"/>
-      <c r="AA27" s="580" t="n"/>
-      <c r="AB27" s="580" t="n"/>
-      <c r="AC27" s="484" t="inlineStr">
+      <c r="B27" s="795" t="n"/>
+      <c r="C27" s="795" t="n"/>
+      <c r="D27" s="795" t="n"/>
+      <c r="E27" s="795" t="n"/>
+      <c r="F27" s="795" t="n"/>
+      <c r="G27" s="795" t="n"/>
+      <c r="H27" s="795" t="n"/>
+      <c r="I27" s="795" t="n"/>
+      <c r="J27" s="795" t="n"/>
+      <c r="K27" s="728" t="n"/>
+      <c r="L27" s="796" t="n"/>
+      <c r="M27" s="796" t="n"/>
+      <c r="N27" s="796" t="n"/>
+      <c r="O27" s="796" t="n"/>
+      <c r="P27" s="796" t="n"/>
+      <c r="Q27" s="796" t="n"/>
+      <c r="R27" s="796" t="n"/>
+      <c r="S27" s="796" t="n"/>
+      <c r="T27" s="796" t="n"/>
+      <c r="U27" s="796" t="n"/>
+      <c r="V27" s="796" t="n"/>
+      <c r="W27" s="796" t="n"/>
+      <c r="X27" s="796" t="n"/>
+      <c r="Y27" s="796" t="n"/>
+      <c r="Z27" s="796" t="n"/>
+      <c r="AA27" s="796" t="n"/>
+      <c r="AB27" s="796" t="n"/>
+      <c r="AC27" s="729" t="inlineStr">
         <is>
           <t>Approved by</t>
         </is>
       </c>
-      <c r="AD27" s="566" t="n"/>
-      <c r="AE27" s="566" t="n"/>
-      <c r="AF27" s="566" t="n"/>
-      <c r="AG27" s="566" t="n"/>
-      <c r="AH27" s="566" t="n"/>
-      <c r="AI27" s="566" t="n"/>
-      <c r="AJ27" s="566" t="n"/>
-      <c r="AK27" s="566" t="n"/>
-      <c r="AL27" s="566" t="n"/>
-      <c r="AM27" s="581" t="n"/>
-      <c r="AN27" s="580" t="n"/>
-      <c r="AO27" s="580" t="n"/>
-      <c r="AP27" s="580" t="n"/>
-      <c r="AQ27" s="580" t="n"/>
-      <c r="AR27" s="580" t="n"/>
-      <c r="AS27" s="580" t="n"/>
-      <c r="AT27" s="580" t="n"/>
-      <c r="AU27" s="580" t="n"/>
-      <c r="AV27" s="580" t="n"/>
-      <c r="AW27" s="580" t="n"/>
-      <c r="AX27" s="580" t="n"/>
-      <c r="AY27" s="580" t="n"/>
-      <c r="AZ27" s="580" t="n"/>
-      <c r="BA27" s="580" t="n"/>
-      <c r="BB27" s="580" t="n"/>
-      <c r="BC27" s="580" t="n"/>
-      <c r="BD27" s="582" t="n"/>
+      <c r="AD27" s="795" t="n"/>
+      <c r="AE27" s="795" t="n"/>
+      <c r="AF27" s="795" t="n"/>
+      <c r="AG27" s="795" t="n"/>
+      <c r="AH27" s="795" t="n"/>
+      <c r="AI27" s="795" t="n"/>
+      <c r="AJ27" s="795" t="n"/>
+      <c r="AK27" s="795" t="n"/>
+      <c r="AL27" s="795" t="n"/>
+      <c r="AM27" s="730" t="n"/>
+      <c r="AN27" s="796" t="n"/>
+      <c r="AO27" s="796" t="n"/>
+      <c r="AP27" s="796" t="n"/>
+      <c r="AQ27" s="796" t="n"/>
+      <c r="AR27" s="796" t="n"/>
+      <c r="AS27" s="796" t="n"/>
+      <c r="AT27" s="796" t="n"/>
+      <c r="AU27" s="796" t="n"/>
+      <c r="AV27" s="796" t="n"/>
+      <c r="AW27" s="796" t="n"/>
+      <c r="AX27" s="796" t="n"/>
+      <c r="AY27" s="796" t="n"/>
+      <c r="AZ27" s="796" t="n"/>
+      <c r="BA27" s="796" t="n"/>
+      <c r="BB27" s="796" t="n"/>
+      <c r="BC27" s="796" t="n"/>
+      <c r="BD27" s="797" t="n"/>
     </row>
     <row r="28" ht="3" customHeight="1">
       <c r="A28" s="375" t="n"/>
@@ -8930,209 +9475,209 @@
       <c r="BD28" s="353" t="n"/>
     </row>
     <row r="29" ht="18" customHeight="1">
-      <c r="A29" s="570" t="inlineStr">
+      <c r="A29" s="731" t="inlineStr">
         <is>
           <t xml:space="preserve">  4. APPROVAL / SIGN-OFF</t>
         </is>
       </c>
-      <c r="B29" s="571" t="n"/>
-      <c r="C29" s="571" t="n"/>
-      <c r="D29" s="571" t="n"/>
-      <c r="E29" s="571" t="n"/>
-      <c r="F29" s="571" t="n"/>
-      <c r="G29" s="571" t="n"/>
-      <c r="H29" s="571" t="n"/>
-      <c r="I29" s="571" t="n"/>
-      <c r="J29" s="571" t="n"/>
-      <c r="K29" s="571" t="n"/>
-      <c r="L29" s="571" t="n"/>
-      <c r="M29" s="571" t="n"/>
-      <c r="N29" s="571" t="n"/>
-      <c r="O29" s="571" t="n"/>
-      <c r="P29" s="571" t="n"/>
-      <c r="Q29" s="571" t="n"/>
-      <c r="R29" s="571" t="n"/>
-      <c r="S29" s="571" t="n"/>
-      <c r="T29" s="571" t="n"/>
-      <c r="U29" s="571" t="n"/>
-      <c r="V29" s="571" t="n"/>
-      <c r="W29" s="571" t="n"/>
-      <c r="X29" s="571" t="n"/>
-      <c r="Y29" s="571" t="n"/>
-      <c r="Z29" s="571" t="n"/>
-      <c r="AA29" s="571" t="n"/>
-      <c r="AB29" s="571" t="n"/>
-      <c r="AC29" s="571" t="n"/>
-      <c r="AD29" s="571" t="n"/>
-      <c r="AE29" s="571" t="n"/>
-      <c r="AF29" s="571" t="n"/>
-      <c r="AG29" s="571" t="n"/>
-      <c r="AH29" s="571" t="n"/>
-      <c r="AI29" s="571" t="n"/>
-      <c r="AJ29" s="571" t="n"/>
-      <c r="AK29" s="571" t="n"/>
-      <c r="AL29" s="571" t="n"/>
-      <c r="AM29" s="571" t="n"/>
-      <c r="AN29" s="571" t="n"/>
-      <c r="AO29" s="571" t="n"/>
-      <c r="AP29" s="571" t="n"/>
-      <c r="AQ29" s="571" t="n"/>
-      <c r="AR29" s="571" t="n"/>
-      <c r="AS29" s="571" t="n"/>
-      <c r="AT29" s="571" t="n"/>
-      <c r="AU29" s="571" t="n"/>
-      <c r="AV29" s="571" t="n"/>
-      <c r="AW29" s="571" t="n"/>
-      <c r="AX29" s="571" t="n"/>
-      <c r="AY29" s="571" t="n"/>
-      <c r="AZ29" s="571" t="n"/>
-      <c r="BA29" s="571" t="n"/>
-      <c r="BB29" s="571" t="n"/>
-      <c r="BC29" s="571" t="n"/>
-      <c r="BD29" s="572" t="n"/>
+      <c r="B29" s="285" t="n"/>
+      <c r="C29" s="285" t="n"/>
+      <c r="D29" s="285" t="n"/>
+      <c r="E29" s="285" t="n"/>
+      <c r="F29" s="285" t="n"/>
+      <c r="G29" s="285" t="n"/>
+      <c r="H29" s="285" t="n"/>
+      <c r="I29" s="285" t="n"/>
+      <c r="J29" s="285" t="n"/>
+      <c r="K29" s="285" t="n"/>
+      <c r="L29" s="285" t="n"/>
+      <c r="M29" s="285" t="n"/>
+      <c r="N29" s="285" t="n"/>
+      <c r="O29" s="285" t="n"/>
+      <c r="P29" s="285" t="n"/>
+      <c r="Q29" s="285" t="n"/>
+      <c r="R29" s="285" t="n"/>
+      <c r="S29" s="285" t="n"/>
+      <c r="T29" s="285" t="n"/>
+      <c r="U29" s="285" t="n"/>
+      <c r="V29" s="285" t="n"/>
+      <c r="W29" s="285" t="n"/>
+      <c r="X29" s="285" t="n"/>
+      <c r="Y29" s="285" t="n"/>
+      <c r="Z29" s="285" t="n"/>
+      <c r="AA29" s="285" t="n"/>
+      <c r="AB29" s="285" t="n"/>
+      <c r="AC29" s="285" t="n"/>
+      <c r="AD29" s="285" t="n"/>
+      <c r="AE29" s="285" t="n"/>
+      <c r="AF29" s="285" t="n"/>
+      <c r="AG29" s="285" t="n"/>
+      <c r="AH29" s="285" t="n"/>
+      <c r="AI29" s="285" t="n"/>
+      <c r="AJ29" s="285" t="n"/>
+      <c r="AK29" s="285" t="n"/>
+      <c r="AL29" s="285" t="n"/>
+      <c r="AM29" s="285" t="n"/>
+      <c r="AN29" s="285" t="n"/>
+      <c r="AO29" s="285" t="n"/>
+      <c r="AP29" s="285" t="n"/>
+      <c r="AQ29" s="285" t="n"/>
+      <c r="AR29" s="285" t="n"/>
+      <c r="AS29" s="285" t="n"/>
+      <c r="AT29" s="285" t="n"/>
+      <c r="AU29" s="285" t="n"/>
+      <c r="AV29" s="285" t="n"/>
+      <c r="AW29" s="285" t="n"/>
+      <c r="AX29" s="285" t="n"/>
+      <c r="AY29" s="285" t="n"/>
+      <c r="AZ29" s="285" t="n"/>
+      <c r="BA29" s="285" t="n"/>
+      <c r="BB29" s="285" t="n"/>
+      <c r="BC29" s="285" t="n"/>
+      <c r="BD29" s="286" t="n"/>
     </row>
     <row r="30" ht="26" customHeight="1">
-      <c r="A30" s="490" t="inlineStr">
+      <c r="A30" s="735" t="inlineStr">
         <is>
           <t>Prepared by</t>
         </is>
       </c>
-      <c r="B30" s="573" t="n"/>
-      <c r="C30" s="573" t="n"/>
-      <c r="D30" s="573" t="n"/>
-      <c r="E30" s="573" t="n"/>
-      <c r="F30" s="573" t="n"/>
-      <c r="G30" s="573" t="n"/>
-      <c r="H30" s="573" t="n"/>
-      <c r="I30" s="573" t="n"/>
-      <c r="J30" s="573" t="n"/>
-      <c r="K30" s="573" t="n"/>
-      <c r="L30" s="573" t="n"/>
-      <c r="M30" s="573" t="n"/>
-      <c r="N30" s="573" t="n"/>
-      <c r="O30" s="573" t="n"/>
-      <c r="P30" s="573" t="n"/>
-      <c r="Q30" s="573" t="n"/>
-      <c r="R30" s="573" t="n"/>
-      <c r="S30" s="502" t="inlineStr">
+      <c r="B30" s="271" t="n"/>
+      <c r="C30" s="271" t="n"/>
+      <c r="D30" s="271" t="n"/>
+      <c r="E30" s="271" t="n"/>
+      <c r="F30" s="271" t="n"/>
+      <c r="G30" s="271" t="n"/>
+      <c r="H30" s="271" t="n"/>
+      <c r="I30" s="271" t="n"/>
+      <c r="J30" s="271" t="n"/>
+      <c r="K30" s="271" t="n"/>
+      <c r="L30" s="271" t="n"/>
+      <c r="M30" s="271" t="n"/>
+      <c r="N30" s="271" t="n"/>
+      <c r="O30" s="271" t="n"/>
+      <c r="P30" s="271" t="n"/>
+      <c r="Q30" s="271" t="n"/>
+      <c r="R30" s="271" t="n"/>
+      <c r="S30" s="747" t="inlineStr">
         <is>
           <t>Reviewed by</t>
         </is>
       </c>
-      <c r="T30" s="573" t="n"/>
-      <c r="U30" s="573" t="n"/>
-      <c r="V30" s="573" t="n"/>
-      <c r="W30" s="573" t="n"/>
-      <c r="X30" s="573" t="n"/>
-      <c r="Y30" s="573" t="n"/>
-      <c r="Z30" s="573" t="n"/>
-      <c r="AA30" s="573" t="n"/>
-      <c r="AB30" s="573" t="n"/>
-      <c r="AC30" s="573" t="n"/>
-      <c r="AD30" s="573" t="n"/>
-      <c r="AE30" s="573" t="n"/>
-      <c r="AF30" s="573" t="n"/>
-      <c r="AG30" s="573" t="n"/>
-      <c r="AH30" s="573" t="n"/>
-      <c r="AI30" s="573" t="n"/>
-      <c r="AJ30" s="573" t="n"/>
-      <c r="AK30" s="587" t="inlineStr">
+      <c r="T30" s="271" t="n"/>
+      <c r="U30" s="271" t="n"/>
+      <c r="V30" s="271" t="n"/>
+      <c r="W30" s="271" t="n"/>
+      <c r="X30" s="271" t="n"/>
+      <c r="Y30" s="271" t="n"/>
+      <c r="Z30" s="271" t="n"/>
+      <c r="AA30" s="271" t="n"/>
+      <c r="AB30" s="271" t="n"/>
+      <c r="AC30" s="271" t="n"/>
+      <c r="AD30" s="271" t="n"/>
+      <c r="AE30" s="271" t="n"/>
+      <c r="AF30" s="271" t="n"/>
+      <c r="AG30" s="271" t="n"/>
+      <c r="AH30" s="271" t="n"/>
+      <c r="AI30" s="271" t="n"/>
+      <c r="AJ30" s="271" t="n"/>
+      <c r="AK30" s="748" t="inlineStr">
         <is>
           <t>Approved by</t>
         </is>
       </c>
-      <c r="AL30" s="573" t="n"/>
-      <c r="AM30" s="573" t="n"/>
-      <c r="AN30" s="573" t="n"/>
-      <c r="AO30" s="573" t="n"/>
-      <c r="AP30" s="573" t="n"/>
-      <c r="AQ30" s="573" t="n"/>
-      <c r="AR30" s="573" t="n"/>
-      <c r="AS30" s="573" t="n"/>
-      <c r="AT30" s="573" t="n"/>
-      <c r="AU30" s="573" t="n"/>
-      <c r="AV30" s="573" t="n"/>
-      <c r="AW30" s="573" t="n"/>
-      <c r="AX30" s="573" t="n"/>
-      <c r="AY30" s="573" t="n"/>
-      <c r="AZ30" s="573" t="n"/>
-      <c r="BA30" s="573" t="n"/>
-      <c r="BB30" s="573" t="n"/>
-      <c r="BC30" s="573" t="n"/>
-      <c r="BD30" s="588" t="n"/>
+      <c r="AL30" s="271" t="n"/>
+      <c r="AM30" s="271" t="n"/>
+      <c r="AN30" s="271" t="n"/>
+      <c r="AO30" s="271" t="n"/>
+      <c r="AP30" s="271" t="n"/>
+      <c r="AQ30" s="271" t="n"/>
+      <c r="AR30" s="271" t="n"/>
+      <c r="AS30" s="271" t="n"/>
+      <c r="AT30" s="271" t="n"/>
+      <c r="AU30" s="271" t="n"/>
+      <c r="AV30" s="271" t="n"/>
+      <c r="AW30" s="271" t="n"/>
+      <c r="AX30" s="271" t="n"/>
+      <c r="AY30" s="271" t="n"/>
+      <c r="AZ30" s="271" t="n"/>
+      <c r="BA30" s="271" t="n"/>
+      <c r="BB30" s="271" t="n"/>
+      <c r="BC30" s="271" t="n"/>
+      <c r="BD30" s="274" t="n"/>
     </row>
     <row r="31" ht="26" customHeight="1">
-      <c r="A31" s="504" t="inlineStr">
+      <c r="A31" s="749" t="inlineStr">
         <is>
           <t>Name / Signature / Date</t>
         </is>
       </c>
-      <c r="B31" s="589" t="n"/>
-      <c r="C31" s="589" t="n"/>
-      <c r="D31" s="589" t="n"/>
-      <c r="E31" s="589" t="n"/>
-      <c r="F31" s="589" t="n"/>
-      <c r="G31" s="589" t="n"/>
-      <c r="H31" s="589" t="n"/>
-      <c r="I31" s="589" t="n"/>
-      <c r="J31" s="589" t="n"/>
-      <c r="K31" s="589" t="n"/>
-      <c r="L31" s="589" t="n"/>
-      <c r="M31" s="589" t="n"/>
-      <c r="N31" s="589" t="n"/>
-      <c r="O31" s="589" t="n"/>
-      <c r="P31" s="589" t="n"/>
-      <c r="Q31" s="589" t="n"/>
-      <c r="R31" s="589" t="n"/>
-      <c r="S31" s="505" t="inlineStr">
+      <c r="B31" s="798" t="n"/>
+      <c r="C31" s="798" t="n"/>
+      <c r="D31" s="798" t="n"/>
+      <c r="E31" s="798" t="n"/>
+      <c r="F31" s="798" t="n"/>
+      <c r="G31" s="798" t="n"/>
+      <c r="H31" s="798" t="n"/>
+      <c r="I31" s="798" t="n"/>
+      <c r="J31" s="798" t="n"/>
+      <c r="K31" s="798" t="n"/>
+      <c r="L31" s="798" t="n"/>
+      <c r="M31" s="798" t="n"/>
+      <c r="N31" s="798" t="n"/>
+      <c r="O31" s="798" t="n"/>
+      <c r="P31" s="798" t="n"/>
+      <c r="Q31" s="798" t="n"/>
+      <c r="R31" s="798" t="n"/>
+      <c r="S31" s="750" t="inlineStr">
         <is>
           <t>Name / Signature / Date</t>
         </is>
       </c>
-      <c r="T31" s="589" t="n"/>
-      <c r="U31" s="589" t="n"/>
-      <c r="V31" s="589" t="n"/>
-      <c r="W31" s="589" t="n"/>
-      <c r="X31" s="589" t="n"/>
-      <c r="Y31" s="589" t="n"/>
-      <c r="Z31" s="589" t="n"/>
-      <c r="AA31" s="589" t="n"/>
-      <c r="AB31" s="589" t="n"/>
-      <c r="AC31" s="589" t="n"/>
-      <c r="AD31" s="589" t="n"/>
-      <c r="AE31" s="589" t="n"/>
-      <c r="AF31" s="589" t="n"/>
-      <c r="AG31" s="589" t="n"/>
-      <c r="AH31" s="589" t="n"/>
-      <c r="AI31" s="589" t="n"/>
-      <c r="AJ31" s="589" t="n"/>
-      <c r="AK31" s="590" t="inlineStr">
+      <c r="T31" s="798" t="n"/>
+      <c r="U31" s="798" t="n"/>
+      <c r="V31" s="798" t="n"/>
+      <c r="W31" s="798" t="n"/>
+      <c r="X31" s="798" t="n"/>
+      <c r="Y31" s="798" t="n"/>
+      <c r="Z31" s="798" t="n"/>
+      <c r="AA31" s="798" t="n"/>
+      <c r="AB31" s="798" t="n"/>
+      <c r="AC31" s="798" t="n"/>
+      <c r="AD31" s="798" t="n"/>
+      <c r="AE31" s="798" t="n"/>
+      <c r="AF31" s="798" t="n"/>
+      <c r="AG31" s="798" t="n"/>
+      <c r="AH31" s="798" t="n"/>
+      <c r="AI31" s="798" t="n"/>
+      <c r="AJ31" s="798" t="n"/>
+      <c r="AK31" s="751" t="inlineStr">
         <is>
           <t>Name / Signature / Date</t>
         </is>
       </c>
-      <c r="AL31" s="589" t="n"/>
-      <c r="AM31" s="589" t="n"/>
-      <c r="AN31" s="589" t="n"/>
-      <c r="AO31" s="589" t="n"/>
-      <c r="AP31" s="589" t="n"/>
-      <c r="AQ31" s="589" t="n"/>
-      <c r="AR31" s="589" t="n"/>
-      <c r="AS31" s="589" t="n"/>
-      <c r="AT31" s="589" t="n"/>
-      <c r="AU31" s="589" t="n"/>
-      <c r="AV31" s="589" t="n"/>
-      <c r="AW31" s="589" t="n"/>
-      <c r="AX31" s="589" t="n"/>
-      <c r="AY31" s="589" t="n"/>
-      <c r="AZ31" s="589" t="n"/>
-      <c r="BA31" s="589" t="n"/>
-      <c r="BB31" s="589" t="n"/>
-      <c r="BC31" s="589" t="n"/>
-      <c r="BD31" s="591" t="n"/>
+      <c r="AL31" s="798" t="n"/>
+      <c r="AM31" s="798" t="n"/>
+      <c r="AN31" s="798" t="n"/>
+      <c r="AO31" s="798" t="n"/>
+      <c r="AP31" s="798" t="n"/>
+      <c r="AQ31" s="798" t="n"/>
+      <c r="AR31" s="798" t="n"/>
+      <c r="AS31" s="798" t="n"/>
+      <c r="AT31" s="798" t="n"/>
+      <c r="AU31" s="798" t="n"/>
+      <c r="AV31" s="798" t="n"/>
+      <c r="AW31" s="798" t="n"/>
+      <c r="AX31" s="798" t="n"/>
+      <c r="AY31" s="798" t="n"/>
+      <c r="AZ31" s="798" t="n"/>
+      <c r="BA31" s="798" t="n"/>
+      <c r="BB31" s="798" t="n"/>
+      <c r="BC31" s="798" t="n"/>
+      <c r="BD31" s="799" t="n"/>
     </row>
     <row r="32" ht="20" customHeight="1">
-      <c r="A32" s="592" t="n"/>
+      <c r="A32" s="330" t="n"/>
       <c r="B32" s="331" t="n"/>
       <c r="C32" s="331" t="n"/>
       <c r="D32" s="331" t="n"/>
@@ -9150,7 +9695,7 @@
       <c r="P32" s="331" t="n"/>
       <c r="Q32" s="331" t="n"/>
       <c r="R32" s="331" t="n"/>
-      <c r="S32" s="593" t="n"/>
+      <c r="S32" s="800" t="n"/>
       <c r="T32" s="331" t="n"/>
       <c r="U32" s="331" t="n"/>
       <c r="V32" s="331" t="n"/>
@@ -9168,7 +9713,7 @@
       <c r="AH32" s="331" t="n"/>
       <c r="AI32" s="331" t="n"/>
       <c r="AJ32" s="331" t="n"/>
-      <c r="AK32" s="593" t="n"/>
+      <c r="AK32" s="800" t="n"/>
       <c r="AL32" s="331" t="n"/>
       <c r="AM32" s="331" t="n"/>
       <c r="AN32" s="331" t="n"/>
@@ -9187,65 +9732,65 @@
       <c r="BA32" s="331" t="n"/>
       <c r="BB32" s="331" t="n"/>
       <c r="BC32" s="331" t="n"/>
-      <c r="BD32" s="594" t="n"/>
+      <c r="BD32" s="332" t="n"/>
     </row>
     <row r="33" ht="20" customHeight="1">
-      <c r="A33" s="595" t="n"/>
-      <c r="B33" s="596" t="n"/>
-      <c r="C33" s="596" t="n"/>
-      <c r="D33" s="596" t="n"/>
-      <c r="E33" s="596" t="n"/>
-      <c r="F33" s="596" t="n"/>
-      <c r="G33" s="596" t="n"/>
-      <c r="H33" s="596" t="n"/>
-      <c r="I33" s="596" t="n"/>
-      <c r="J33" s="596" t="n"/>
-      <c r="K33" s="596" t="n"/>
-      <c r="L33" s="596" t="n"/>
-      <c r="M33" s="596" t="n"/>
-      <c r="N33" s="596" t="n"/>
-      <c r="O33" s="596" t="n"/>
-      <c r="P33" s="596" t="n"/>
-      <c r="Q33" s="596" t="n"/>
-      <c r="R33" s="596" t="n"/>
-      <c r="S33" s="597" t="n"/>
-      <c r="T33" s="596" t="n"/>
-      <c r="U33" s="596" t="n"/>
-      <c r="V33" s="596" t="n"/>
-      <c r="W33" s="596" t="n"/>
-      <c r="X33" s="596" t="n"/>
-      <c r="Y33" s="596" t="n"/>
-      <c r="Z33" s="596" t="n"/>
-      <c r="AA33" s="596" t="n"/>
-      <c r="AB33" s="596" t="n"/>
-      <c r="AC33" s="596" t="n"/>
-      <c r="AD33" s="596" t="n"/>
-      <c r="AE33" s="596" t="n"/>
-      <c r="AF33" s="596" t="n"/>
-      <c r="AG33" s="596" t="n"/>
-      <c r="AH33" s="596" t="n"/>
-      <c r="AI33" s="596" t="n"/>
-      <c r="AJ33" s="596" t="n"/>
-      <c r="AK33" s="597" t="n"/>
-      <c r="AL33" s="596" t="n"/>
-      <c r="AM33" s="596" t="n"/>
-      <c r="AN33" s="596" t="n"/>
-      <c r="AO33" s="596" t="n"/>
-      <c r="AP33" s="596" t="n"/>
-      <c r="AQ33" s="596" t="n"/>
-      <c r="AR33" s="596" t="n"/>
-      <c r="AS33" s="596" t="n"/>
-      <c r="AT33" s="596" t="n"/>
-      <c r="AU33" s="596" t="n"/>
-      <c r="AV33" s="596" t="n"/>
-      <c r="AW33" s="596" t="n"/>
-      <c r="AX33" s="596" t="n"/>
-      <c r="AY33" s="596" t="n"/>
-      <c r="AZ33" s="596" t="n"/>
-      <c r="BA33" s="596" t="n"/>
-      <c r="BB33" s="596" t="n"/>
-      <c r="BC33" s="596" t="n"/>
-      <c r="BD33" s="598" t="n"/>
+      <c r="A33" s="801" t="n"/>
+      <c r="B33" s="323" t="n"/>
+      <c r="C33" s="323" t="n"/>
+      <c r="D33" s="323" t="n"/>
+      <c r="E33" s="323" t="n"/>
+      <c r="F33" s="323" t="n"/>
+      <c r="G33" s="323" t="n"/>
+      <c r="H33" s="323" t="n"/>
+      <c r="I33" s="323" t="n"/>
+      <c r="J33" s="323" t="n"/>
+      <c r="K33" s="323" t="n"/>
+      <c r="L33" s="323" t="n"/>
+      <c r="M33" s="323" t="n"/>
+      <c r="N33" s="323" t="n"/>
+      <c r="O33" s="323" t="n"/>
+      <c r="P33" s="323" t="n"/>
+      <c r="Q33" s="323" t="n"/>
+      <c r="R33" s="323" t="n"/>
+      <c r="S33" s="802" t="n"/>
+      <c r="T33" s="323" t="n"/>
+      <c r="U33" s="323" t="n"/>
+      <c r="V33" s="323" t="n"/>
+      <c r="W33" s="323" t="n"/>
+      <c r="X33" s="323" t="n"/>
+      <c r="Y33" s="323" t="n"/>
+      <c r="Z33" s="323" t="n"/>
+      <c r="AA33" s="323" t="n"/>
+      <c r="AB33" s="323" t="n"/>
+      <c r="AC33" s="323" t="n"/>
+      <c r="AD33" s="323" t="n"/>
+      <c r="AE33" s="323" t="n"/>
+      <c r="AF33" s="323" t="n"/>
+      <c r="AG33" s="323" t="n"/>
+      <c r="AH33" s="323" t="n"/>
+      <c r="AI33" s="323" t="n"/>
+      <c r="AJ33" s="323" t="n"/>
+      <c r="AK33" s="802" t="n"/>
+      <c r="AL33" s="323" t="n"/>
+      <c r="AM33" s="323" t="n"/>
+      <c r="AN33" s="323" t="n"/>
+      <c r="AO33" s="323" t="n"/>
+      <c r="AP33" s="323" t="n"/>
+      <c r="AQ33" s="323" t="n"/>
+      <c r="AR33" s="323" t="n"/>
+      <c r="AS33" s="323" t="n"/>
+      <c r="AT33" s="323" t="n"/>
+      <c r="AU33" s="323" t="n"/>
+      <c r="AV33" s="323" t="n"/>
+      <c r="AW33" s="323" t="n"/>
+      <c r="AX33" s="323" t="n"/>
+      <c r="AY33" s="323" t="n"/>
+      <c r="AZ33" s="323" t="n"/>
+      <c r="BA33" s="323" t="n"/>
+      <c r="BB33" s="323" t="n"/>
+      <c r="BC33" s="323" t="n"/>
+      <c r="BD33" s="325" t="n"/>
     </row>
     <row r="34" ht="3" customHeight="1">
       <c r="A34" s="391" t="n"/>
@@ -9306,66 +9851,66 @@
       <c r="BD34" s="353" t="n"/>
     </row>
     <row r="35" ht="26" customHeight="1">
-      <c r="A35" s="600" t="inlineStr">
+      <c r="A35" s="55" t="inlineStr">
         <is>
           <t>NOTICE: Confirm cleanliness, approved materials, line clearance, bagging sequence and seal integrity before release. This is a controlled gap form.</t>
         </is>
       </c>
-      <c r="B35" s="601" t="n"/>
-      <c r="C35" s="601" t="n"/>
-      <c r="D35" s="601" t="n"/>
-      <c r="E35" s="601" t="n"/>
-      <c r="F35" s="601" t="n"/>
-      <c r="G35" s="601" t="n"/>
-      <c r="H35" s="601" t="n"/>
-      <c r="I35" s="601" t="n"/>
-      <c r="J35" s="601" t="n"/>
-      <c r="K35" s="601" t="n"/>
-      <c r="L35" s="601" t="n"/>
-      <c r="M35" s="601" t="n"/>
-      <c r="N35" s="601" t="n"/>
-      <c r="O35" s="601" t="n"/>
-      <c r="P35" s="601" t="n"/>
-      <c r="Q35" s="601" t="n"/>
-      <c r="R35" s="601" t="n"/>
-      <c r="S35" s="601" t="n"/>
-      <c r="T35" s="601" t="n"/>
-      <c r="U35" s="601" t="n"/>
-      <c r="V35" s="601" t="n"/>
-      <c r="W35" s="601" t="n"/>
-      <c r="X35" s="601" t="n"/>
-      <c r="Y35" s="601" t="n"/>
-      <c r="Z35" s="601" t="n"/>
-      <c r="AA35" s="601" t="n"/>
-      <c r="AB35" s="601" t="n"/>
-      <c r="AC35" s="601" t="n"/>
-      <c r="AD35" s="601" t="n"/>
-      <c r="AE35" s="601" t="n"/>
-      <c r="AF35" s="601" t="n"/>
-      <c r="AG35" s="601" t="n"/>
-      <c r="AH35" s="601" t="n"/>
-      <c r="AI35" s="601" t="n"/>
-      <c r="AJ35" s="601" t="n"/>
-      <c r="AK35" s="601" t="n"/>
-      <c r="AL35" s="601" t="n"/>
-      <c r="AM35" s="601" t="n"/>
-      <c r="AN35" s="601" t="n"/>
-      <c r="AO35" s="601" t="n"/>
-      <c r="AP35" s="601" t="n"/>
-      <c r="AQ35" s="601" t="n"/>
-      <c r="AR35" s="601" t="n"/>
-      <c r="AS35" s="601" t="n"/>
-      <c r="AT35" s="601" t="n"/>
-      <c r="AU35" s="601" t="n"/>
-      <c r="AV35" s="601" t="n"/>
-      <c r="AW35" s="601" t="n"/>
-      <c r="AX35" s="601" t="n"/>
-      <c r="AY35" s="601" t="n"/>
-      <c r="AZ35" s="601" t="n"/>
-      <c r="BA35" s="601" t="n"/>
-      <c r="BB35" s="601" t="n"/>
-      <c r="BC35" s="601" t="n"/>
-      <c r="BD35" s="602" t="n"/>
+      <c r="B35" s="752" t="n"/>
+      <c r="C35" s="752" t="n"/>
+      <c r="D35" s="752" t="n"/>
+      <c r="E35" s="752" t="n"/>
+      <c r="F35" s="752" t="n"/>
+      <c r="G35" s="752" t="n"/>
+      <c r="H35" s="752" t="n"/>
+      <c r="I35" s="752" t="n"/>
+      <c r="J35" s="752" t="n"/>
+      <c r="K35" s="752" t="n"/>
+      <c r="L35" s="752" t="n"/>
+      <c r="M35" s="752" t="n"/>
+      <c r="N35" s="752" t="n"/>
+      <c r="O35" s="752" t="n"/>
+      <c r="P35" s="752" t="n"/>
+      <c r="Q35" s="752" t="n"/>
+      <c r="R35" s="752" t="n"/>
+      <c r="S35" s="752" t="n"/>
+      <c r="T35" s="752" t="n"/>
+      <c r="U35" s="752" t="n"/>
+      <c r="V35" s="752" t="n"/>
+      <c r="W35" s="752" t="n"/>
+      <c r="X35" s="752" t="n"/>
+      <c r="Y35" s="752" t="n"/>
+      <c r="Z35" s="752" t="n"/>
+      <c r="AA35" s="752" t="n"/>
+      <c r="AB35" s="752" t="n"/>
+      <c r="AC35" s="752" t="n"/>
+      <c r="AD35" s="752" t="n"/>
+      <c r="AE35" s="752" t="n"/>
+      <c r="AF35" s="752" t="n"/>
+      <c r="AG35" s="752" t="n"/>
+      <c r="AH35" s="752" t="n"/>
+      <c r="AI35" s="752" t="n"/>
+      <c r="AJ35" s="752" t="n"/>
+      <c r="AK35" s="752" t="n"/>
+      <c r="AL35" s="752" t="n"/>
+      <c r="AM35" s="752" t="n"/>
+      <c r="AN35" s="752" t="n"/>
+      <c r="AO35" s="752" t="n"/>
+      <c r="AP35" s="752" t="n"/>
+      <c r="AQ35" s="752" t="n"/>
+      <c r="AR35" s="752" t="n"/>
+      <c r="AS35" s="752" t="n"/>
+      <c r="AT35" s="752" t="n"/>
+      <c r="AU35" s="752" t="n"/>
+      <c r="AV35" s="752" t="n"/>
+      <c r="AW35" s="752" t="n"/>
+      <c r="AX35" s="752" t="n"/>
+      <c r="AY35" s="752" t="n"/>
+      <c r="AZ35" s="752" t="n"/>
+      <c r="BA35" s="752" t="n"/>
+      <c r="BB35" s="752" t="n"/>
+      <c r="BC35" s="752" t="n"/>
+      <c r="BD35" s="753" t="n"/>
     </row>
     <row r="36" ht="20" customHeight="1"/>
     <row r="37" ht="20" customHeight="1"/>
@@ -9527,254 +10072,1083 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:AN20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="2.33" customWidth="1" min="1" max="1"/>
+    <col width="2.33" customWidth="1" min="2" max="2"/>
+    <col width="2.33" customWidth="1" min="3" max="3"/>
+    <col width="2.33" customWidth="1" min="4" max="4"/>
+    <col width="2.33" customWidth="1" min="5" max="5"/>
+    <col width="2.33" customWidth="1" min="6" max="6"/>
+    <col width="2.33" customWidth="1" min="7" max="7"/>
+    <col width="2.33" customWidth="1" min="8" max="8"/>
+    <col width="2.33" customWidth="1" min="9" max="9"/>
+    <col width="2.33" customWidth="1" min="10" max="10"/>
+    <col width="2.33" customWidth="1" min="11" max="11"/>
+    <col width="2.33" customWidth="1" min="12" max="12"/>
+    <col width="2.33" customWidth="1" min="13" max="13"/>
+    <col width="2.33" customWidth="1" min="14" max="14"/>
+    <col width="2.33" customWidth="1" min="15" max="15"/>
+    <col width="2.33" customWidth="1" min="16" max="16"/>
+    <col width="2.33" customWidth="1" min="17" max="17"/>
+    <col width="2.33" customWidth="1" min="18" max="18"/>
+    <col width="2.33" customWidth="1" min="19" max="19"/>
+    <col width="2.33" customWidth="1" min="20" max="20"/>
+    <col width="2.33" customWidth="1" min="21" max="21"/>
+    <col width="2.33" customWidth="1" min="22" max="22"/>
+    <col width="2.33" customWidth="1" min="23" max="23"/>
+    <col width="2.33" customWidth="1" min="24" max="24"/>
+    <col width="2.33" customWidth="1" min="25" max="25"/>
+    <col width="2.33" customWidth="1" min="26" max="26"/>
+    <col width="2.33" customWidth="1" min="27" max="27"/>
+    <col width="2.33" customWidth="1" min="28" max="28"/>
+    <col width="2.33" customWidth="1" min="29" max="29"/>
+    <col width="2.33" customWidth="1" min="30" max="30"/>
+    <col width="2.33" customWidth="1" min="31" max="31"/>
+    <col width="2.33" customWidth="1" min="32" max="32"/>
+    <col width="2.33" customWidth="1" min="33" max="33"/>
+    <col width="2.33" customWidth="1" min="34" max="34"/>
+    <col width="2.33" customWidth="1" min="35" max="35"/>
+    <col width="2.33" customWidth="1" min="36" max="36"/>
+    <col width="2.33" customWidth="1" min="37" max="37"/>
+    <col width="2.33" customWidth="1" min="38" max="38"/>
+    <col width="2.33" customWidth="1" min="39" max="39"/>
+    <col width="2.33" customWidth="1" min="40" max="40"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="265" t="inlineStr">
+    <row r="1" hidden="1">
+      <c r="A1" s="754" t="n"/>
+      <c r="B1" s="548" t="n"/>
+      <c r="C1" s="548" t="n"/>
+      <c r="D1" s="548" t="n"/>
+      <c r="E1" s="548" t="n"/>
+      <c r="F1" s="548" t="n"/>
+      <c r="G1" s="548" t="n"/>
+      <c r="H1" s="549" t="n"/>
+      <c r="I1" s="755" t="inlineStr">
         <is>
-          <t>RESULT</t>
+          <t>Vacuum-Compatible Clean Build and Bagging Record</t>
         </is>
       </c>
-      <c r="B1" s="265" t="inlineStr">
+      <c r="J1" s="548" t="n"/>
+      <c r="K1" s="548" t="n"/>
+      <c r="L1" s="548" t="n"/>
+      <c r="M1" s="548" t="n"/>
+      <c r="N1" s="548" t="n"/>
+      <c r="O1" s="548" t="n"/>
+      <c r="P1" s="548" t="n"/>
+      <c r="Q1" s="548" t="n"/>
+      <c r="R1" s="548" t="n"/>
+      <c r="S1" s="548" t="n"/>
+      <c r="T1" s="548" t="n"/>
+      <c r="U1" s="548" t="n"/>
+      <c r="V1" s="548" t="n"/>
+      <c r="W1" s="548" t="n"/>
+      <c r="X1" s="548" t="n"/>
+      <c r="Y1" s="548" t="n"/>
+      <c r="Z1" s="548" t="n"/>
+      <c r="AA1" s="548" t="n"/>
+      <c r="AB1" s="548" t="n"/>
+      <c r="AC1" s="548" t="n"/>
+      <c r="AD1" s="549" t="n"/>
+      <c r="AE1" s="436" t="inlineStr">
         <is>
-          <t>DISPOSITION_GATE</t>
+          <t>Form Code</t>
         </is>
       </c>
-      <c r="C1" s="265" t="inlineStr">
+      <c r="AF1" s="548" t="n"/>
+      <c r="AG1" s="548" t="n"/>
+      <c r="AH1" s="552" t="n"/>
+      <c r="AI1" s="439" t="n"/>
+      <c r="AJ1" s="548" t="n"/>
+      <c r="AK1" s="548" t="n"/>
+      <c r="AL1" s="548" t="n"/>
+      <c r="AM1" s="548" t="n"/>
+      <c r="AN1" s="549" t="n"/>
+    </row>
+    <row r="2" ht="15" customHeight="1">
+      <c r="A2" s="1" t="n"/>
+      <c r="B2" s="694" t="n"/>
+      <c r="C2" s="694" t="n"/>
+      <c r="D2" s="694" t="n"/>
+      <c r="E2" s="694" t="n"/>
+      <c r="F2" s="694" t="n"/>
+      <c r="G2" s="694" t="n"/>
+      <c r="H2" s="695" t="n"/>
+      <c r="I2" s="694" t="n"/>
+      <c r="J2" s="694" t="n"/>
+      <c r="K2" s="694" t="n"/>
+      <c r="L2" s="694" t="n"/>
+      <c r="M2" s="694" t="n"/>
+      <c r="N2" s="694" t="n"/>
+      <c r="O2" s="694" t="n"/>
+      <c r="P2" s="694" t="n"/>
+      <c r="Q2" s="694" t="n"/>
+      <c r="R2" s="694" t="n"/>
+      <c r="S2" s="694" t="n"/>
+      <c r="T2" s="694" t="n"/>
+      <c r="U2" s="694" t="n"/>
+      <c r="V2" s="694" t="n"/>
+      <c r="W2" s="694" t="n"/>
+      <c r="X2" s="694" t="n"/>
+      <c r="Y2" s="694" t="n"/>
+      <c r="Z2" s="694" t="n"/>
+      <c r="AA2" s="694" t="n"/>
+      <c r="AB2" s="694" t="n"/>
+      <c r="AC2" s="694" t="n"/>
+      <c r="AD2" s="695" t="n"/>
+      <c r="AE2" s="756" t="inlineStr">
         <is>
-          <t>CLEAN_CLASS_LIST</t>
+          <t>Revision</t>
         </is>
       </c>
-      <c r="D1" s="265" t="inlineStr">
+      <c r="AF2" s="697" t="n"/>
+      <c r="AG2" s="697" t="n"/>
+      <c r="AH2" s="698" t="n"/>
+      <c r="AI2" s="757" t="n"/>
+      <c r="AJ2" s="699" t="n"/>
+      <c r="AK2" s="699" t="n"/>
+      <c r="AL2" s="699" t="n"/>
+      <c r="AM2" s="699" t="n"/>
+      <c r="AN2" s="700" t="n"/>
+    </row>
+    <row r="3" ht="15" customHeight="1">
+      <c r="A3" s="701" t="n"/>
+      <c r="B3" s="25" t="n"/>
+      <c r="C3" s="25" t="n"/>
+      <c r="D3" s="25" t="n"/>
+      <c r="E3" s="25" t="n"/>
+      <c r="F3" s="25" t="n"/>
+      <c r="G3" s="25" t="n"/>
+      <c r="H3" s="702" t="n"/>
+      <c r="I3" s="25" t="n"/>
+      <c r="J3" s="25" t="n"/>
+      <c r="K3" s="25" t="n"/>
+      <c r="L3" s="25" t="n"/>
+      <c r="M3" s="25" t="n"/>
+      <c r="N3" s="25" t="n"/>
+      <c r="O3" s="25" t="n"/>
+      <c r="P3" s="25" t="n"/>
+      <c r="Q3" s="25" t="n"/>
+      <c r="R3" s="25" t="n"/>
+      <c r="S3" s="25" t="n"/>
+      <c r="T3" s="25" t="n"/>
+      <c r="U3" s="25" t="n"/>
+      <c r="V3" s="25" t="n"/>
+      <c r="W3" s="25" t="n"/>
+      <c r="X3" s="25" t="n"/>
+      <c r="Y3" s="25" t="n"/>
+      <c r="Z3" s="25" t="n"/>
+      <c r="AA3" s="25" t="n"/>
+      <c r="AB3" s="25" t="n"/>
+      <c r="AC3" s="25" t="n"/>
+      <c r="AD3" s="702" t="n"/>
+      <c r="AE3" s="758" t="inlineStr">
         <is>
-          <t>YES_NO</t>
+          <t>Eff. Date</t>
         </is>
       </c>
-      <c r="E1" s="265" t="inlineStr">
+      <c r="AF3" s="704" t="n"/>
+      <c r="AG3" s="704" t="n"/>
+      <c r="AH3" s="705" t="n"/>
+      <c r="AI3" s="759" t="n"/>
+      <c r="AJ3" s="706" t="n"/>
+      <c r="AK3" s="706" t="n"/>
+      <c r="AL3" s="706" t="n"/>
+      <c r="AM3" s="706" t="n"/>
+      <c r="AN3" s="707" t="n"/>
+    </row>
+    <row r="4" ht="15" customHeight="1">
+      <c r="A4" s="701" t="n"/>
+      <c r="B4" s="25" t="n"/>
+      <c r="C4" s="25" t="n"/>
+      <c r="D4" s="25" t="n"/>
+      <c r="E4" s="25" t="n"/>
+      <c r="F4" s="25" t="n"/>
+      <c r="G4" s="25" t="n"/>
+      <c r="H4" s="702" t="n"/>
+      <c r="I4" s="708" t="inlineStr">
         <is>
-          <t>ACTION_STATUS</t>
+          <t>Quality Management System · Controlled Document</t>
         </is>
       </c>
-      <c r="F1" s="265" t="inlineStr">
+      <c r="J4" s="25" t="n"/>
+      <c r="K4" s="25" t="n"/>
+      <c r="L4" s="25" t="n"/>
+      <c r="M4" s="25" t="n"/>
+      <c r="N4" s="25" t="n"/>
+      <c r="O4" s="25" t="n"/>
+      <c r="P4" s="25" t="n"/>
+      <c r="Q4" s="25" t="n"/>
+      <c r="R4" s="25" t="n"/>
+      <c r="S4" s="25" t="n"/>
+      <c r="T4" s="25" t="n"/>
+      <c r="U4" s="25" t="n"/>
+      <c r="V4" s="25" t="n"/>
+      <c r="W4" s="25" t="n"/>
+      <c r="X4" s="25" t="n"/>
+      <c r="Y4" s="25" t="n"/>
+      <c r="Z4" s="25" t="n"/>
+      <c r="AA4" s="25" t="n"/>
+      <c r="AB4" s="25" t="n"/>
+      <c r="AC4" s="25" t="n"/>
+      <c r="AD4" s="702" t="n"/>
+      <c r="AE4" s="758" t="inlineStr">
         <is>
-          <t>OWNER_DEPT</t>
+          <t>Owner</t>
         </is>
       </c>
-      <c r="G1" s="265" t="inlineStr">
+      <c r="AF4" s="704" t="n"/>
+      <c r="AG4" s="704" t="n"/>
+      <c r="AH4" s="705" t="n"/>
+      <c r="AI4" s="759" t="n"/>
+      <c r="AJ4" s="706" t="n"/>
+      <c r="AK4" s="706" t="n"/>
+      <c r="AL4" s="706" t="n"/>
+      <c r="AM4" s="706" t="n"/>
+      <c r="AN4" s="707" t="n"/>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" s="701" t="n"/>
+      <c r="B5" s="25" t="n"/>
+      <c r="C5" s="25" t="n"/>
+      <c r="D5" s="25" t="n"/>
+      <c r="E5" s="25" t="n"/>
+      <c r="F5" s="25" t="n"/>
+      <c r="G5" s="25" t="n"/>
+      <c r="H5" s="702" t="n"/>
+      <c r="I5" s="709" t="inlineStr">
         <is>
-          <t>STATUS</t>
+          <t>General Manager</t>
         </is>
       </c>
+      <c r="J5" s="25" t="n"/>
+      <c r="K5" s="25" t="n"/>
+      <c r="L5" s="25" t="n"/>
+      <c r="M5" s="25" t="n"/>
+      <c r="N5" s="25" t="n"/>
+      <c r="O5" s="25" t="n"/>
+      <c r="P5" s="25" t="n"/>
+      <c r="Q5" s="25" t="n"/>
+      <c r="R5" s="25" t="n"/>
+      <c r="S5" s="25" t="n"/>
+      <c r="T5" s="25" t="n"/>
+      <c r="U5" s="25" t="n"/>
+      <c r="V5" s="25" t="n"/>
+      <c r="W5" s="25" t="n"/>
+      <c r="X5" s="25" t="n"/>
+      <c r="Y5" s="25" t="n"/>
+      <c r="Z5" s="25" t="n"/>
+      <c r="AA5" s="25" t="n"/>
+      <c r="AB5" s="25" t="n"/>
+      <c r="AC5" s="25" t="n"/>
+      <c r="AD5" s="702" t="n"/>
+      <c r="AE5" s="758" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="AF5" s="704" t="n"/>
+      <c r="AG5" s="704" t="n"/>
+      <c r="AH5" s="705" t="n"/>
+      <c r="AI5" s="759" t="n"/>
+      <c r="AJ5" s="706" t="n"/>
+      <c r="AK5" s="706" t="n"/>
+      <c r="AL5" s="706" t="n"/>
+      <c r="AM5" s="706" t="n"/>
+      <c r="AN5" s="707" t="n"/>
     </row>
-    <row r="2">
-      <c r="A2" s="266" t="inlineStr">
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" s="760" t="n"/>
+      <c r="B6" s="761" t="n"/>
+      <c r="C6" s="761" t="n"/>
+      <c r="D6" s="761" t="n"/>
+      <c r="E6" s="761" t="n"/>
+      <c r="F6" s="761" t="n"/>
+      <c r="G6" s="761" t="n"/>
+      <c r="H6" s="762" t="n"/>
+      <c r="I6" s="761" t="n"/>
+      <c r="J6" s="761" t="n"/>
+      <c r="K6" s="761" t="n"/>
+      <c r="L6" s="761" t="n"/>
+      <c r="M6" s="761" t="n"/>
+      <c r="N6" s="761" t="n"/>
+      <c r="O6" s="761" t="n"/>
+      <c r="P6" s="761" t="n"/>
+      <c r="Q6" s="761" t="n"/>
+      <c r="R6" s="761" t="n"/>
+      <c r="S6" s="761" t="n"/>
+      <c r="T6" s="761" t="n"/>
+      <c r="U6" s="761" t="n"/>
+      <c r="V6" s="761" t="n"/>
+      <c r="W6" s="761" t="n"/>
+      <c r="X6" s="761" t="n"/>
+      <c r="Y6" s="761" t="n"/>
+      <c r="Z6" s="761" t="n"/>
+      <c r="AA6" s="761" t="n"/>
+      <c r="AB6" s="761" t="n"/>
+      <c r="AC6" s="761" t="n"/>
+      <c r="AD6" s="762" t="n"/>
+      <c r="AE6" s="763" t="n"/>
+      <c r="AF6" s="763" t="n"/>
+      <c r="AG6" s="763" t="n"/>
+      <c r="AH6" s="764" t="n"/>
+      <c r="AI6" s="765" t="n"/>
+      <c r="AJ6" s="765" t="n"/>
+      <c r="AK6" s="765" t="n"/>
+      <c r="AL6" s="765" t="n"/>
+      <c r="AM6" s="765" t="n"/>
+      <c r="AN6" s="766" t="n"/>
+    </row>
+    <row r="7" ht="4" customHeight="1">
+      <c r="A7" s="767" t="n"/>
+      <c r="B7" s="767" t="n"/>
+      <c r="C7" s="767" t="n"/>
+      <c r="D7" s="767" t="n"/>
+      <c r="E7" s="767" t="n"/>
+      <c r="F7" s="767" t="n"/>
+      <c r="G7" s="767" t="n"/>
+      <c r="H7" s="768" t="n"/>
+      <c r="I7" s="768" t="n"/>
+      <c r="J7" s="768" t="n"/>
+      <c r="K7" s="768" t="n"/>
+      <c r="L7" s="768" t="n"/>
+      <c r="M7" s="768" t="n"/>
+      <c r="N7" s="768" t="n"/>
+      <c r="O7" s="768" t="n"/>
+      <c r="P7" s="768" t="n"/>
+      <c r="Q7" s="768" t="n"/>
+      <c r="R7" s="768" t="n"/>
+      <c r="S7" s="768" t="n"/>
+      <c r="T7" s="768" t="n"/>
+      <c r="U7" s="768" t="n"/>
+      <c r="V7" s="768" t="n"/>
+      <c r="W7" s="768" t="n"/>
+      <c r="X7" s="768" t="n"/>
+      <c r="Y7" s="768" t="n"/>
+      <c r="Z7" s="768" t="n"/>
+      <c r="AA7" s="768" t="n"/>
+      <c r="AB7" s="768" t="n"/>
+      <c r="AC7" s="768" t="n"/>
+      <c r="AD7" s="768" t="n"/>
+      <c r="AE7" s="768" t="n"/>
+      <c r="AF7" s="768" t="n"/>
+      <c r="AG7" s="768" t="n"/>
+      <c r="AH7" s="768" t="n"/>
+      <c r="AI7" s="768" t="n"/>
+      <c r="AJ7" s="768" t="n"/>
+      <c r="AK7" s="768" t="n"/>
+      <c r="AL7" s="768" t="n"/>
+      <c r="AM7" s="768" t="n"/>
+      <c r="AN7" s="768" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="266" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
-      <c r="B2" s="266" t="inlineStr">
+      <c r="B8" s="266" t="inlineStr">
         <is>
           <t>APPROVED</t>
         </is>
       </c>
-      <c r="C2" s="266" t="inlineStr">
+      <c r="C8" s="266" t="inlineStr">
         <is>
           <t>STANDARD</t>
         </is>
       </c>
-      <c r="D2" s="266" t="inlineStr">
+      <c r="D8" s="266" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="E2" s="266" t="inlineStr">
+      <c r="E8" s="266" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
       </c>
-      <c r="F2" s="266" t="inlineStr">
+      <c r="F8" s="266" t="inlineStr">
         <is>
           <t>SALES</t>
         </is>
       </c>
-      <c r="G2" s="266" t="inlineStr">
+      <c r="G8" s="266" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
       </c>
+      <c r="H8" s="693" t="n"/>
+      <c r="I8" s="693" t="n"/>
+      <c r="J8" s="693" t="n"/>
+      <c r="K8" s="693" t="n"/>
+      <c r="L8" s="693" t="n"/>
+      <c r="M8" s="693" t="n"/>
+      <c r="N8" s="693" t="n"/>
+      <c r="O8" s="693" t="n"/>
+      <c r="P8" s="693" t="n"/>
+      <c r="Q8" s="693" t="n"/>
+      <c r="R8" s="693" t="n"/>
+      <c r="S8" s="693" t="n"/>
+      <c r="T8" s="693" t="n"/>
+      <c r="U8" s="693" t="n"/>
+      <c r="V8" s="693" t="n"/>
+      <c r="W8" s="693" t="n"/>
+      <c r="X8" s="693" t="n"/>
+      <c r="Y8" s="693" t="n"/>
+      <c r="Z8" s="693" t="n"/>
+      <c r="AA8" s="693" t="n"/>
+      <c r="AB8" s="693" t="n"/>
+      <c r="AC8" s="693" t="n"/>
+      <c r="AD8" s="693" t="n"/>
+      <c r="AE8" s="693" t="n"/>
+      <c r="AF8" s="693" t="n"/>
+      <c r="AG8" s="693" t="n"/>
+      <c r="AH8" s="693" t="n"/>
+      <c r="AI8" s="693" t="n"/>
+      <c r="AJ8" s="693" t="n"/>
+      <c r="AK8" s="693" t="n"/>
+      <c r="AL8" s="693" t="n"/>
+      <c r="AM8" s="693" t="n"/>
+      <c r="AN8" s="693" t="n"/>
     </row>
-    <row r="3">
-      <c r="A3" s="266" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="266" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="B3" s="266" t="inlineStr">
+      <c r="B9" s="266" t="inlineStr">
         <is>
           <t>CONDITIONAL</t>
         </is>
       </c>
-      <c r="C3" s="266" t="inlineStr">
+      <c r="C9" s="266" t="inlineStr">
         <is>
           <t>CLEAN</t>
         </is>
       </c>
-      <c r="D3" s="266" t="inlineStr">
+      <c r="D9" s="266" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="E3" s="266" t="inlineStr">
+      <c r="E9" s="266" t="inlineStr">
         <is>
           <t>IN PROGRESS</t>
         </is>
       </c>
-      <c r="F3" s="266" t="inlineStr">
+      <c r="F9" s="266" t="inlineStr">
         <is>
           <t>ENG</t>
         </is>
       </c>
-      <c r="G3" s="266" t="inlineStr">
+      <c r="G9" s="266" t="inlineStr">
         <is>
           <t>IN PROGRESS</t>
         </is>
       </c>
+      <c r="H9" s="693" t="n"/>
+      <c r="I9" s="693" t="n"/>
+      <c r="J9" s="693" t="n"/>
+      <c r="K9" s="693" t="n"/>
+      <c r="L9" s="693" t="n"/>
+      <c r="M9" s="693" t="n"/>
+      <c r="N9" s="693" t="n"/>
+      <c r="O9" s="693" t="n"/>
+      <c r="P9" s="693" t="n"/>
+      <c r="Q9" s="693" t="n"/>
+      <c r="R9" s="693" t="n"/>
+      <c r="S9" s="693" t="n"/>
+      <c r="T9" s="693" t="n"/>
+      <c r="U9" s="693" t="n"/>
+      <c r="V9" s="693" t="n"/>
+      <c r="W9" s="693" t="n"/>
+      <c r="X9" s="693" t="n"/>
+      <c r="Y9" s="693" t="n"/>
+      <c r="Z9" s="693" t="n"/>
+      <c r="AA9" s="693" t="n"/>
+      <c r="AB9" s="693" t="n"/>
+      <c r="AC9" s="693" t="n"/>
+      <c r="AD9" s="693" t="n"/>
+      <c r="AE9" s="693" t="n"/>
+      <c r="AF9" s="693" t="n"/>
+      <c r="AG9" s="693" t="n"/>
+      <c r="AH9" s="693" t="n"/>
+      <c r="AI9" s="693" t="n"/>
+      <c r="AJ9" s="693" t="n"/>
+      <c r="AK9" s="693" t="n"/>
+      <c r="AL9" s="693" t="n"/>
+      <c r="AM9" s="693" t="n"/>
+      <c r="AN9" s="693" t="n"/>
     </row>
-    <row r="4">
-      <c r="A4" s="266" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="266" t="inlineStr">
         <is>
           <t>FAIL</t>
         </is>
       </c>
-      <c r="B4" s="266" t="inlineStr">
+      <c r="B10" s="266" t="inlineStr">
         <is>
           <t>HOLD</t>
         </is>
       </c>
-      <c r="C4" s="266" t="inlineStr">
+      <c r="C10" s="266" t="inlineStr">
         <is>
           <t>HIGH CLEAN</t>
         </is>
       </c>
-      <c r="D4" s="266" t="inlineStr">
+      <c r="D10" s="266" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="E4" s="266" t="inlineStr">
+      <c r="E10" s="266" t="inlineStr">
         <is>
           <t>OVERDUE</t>
         </is>
       </c>
-      <c r="F4" s="266" t="inlineStr">
+      <c r="F10" s="266" t="inlineStr">
         <is>
           <t>PLANNING</t>
         </is>
       </c>
-      <c r="G4" s="266" t="inlineStr">
+      <c r="G10" s="266" t="inlineStr">
         <is>
           <t>CLOSED</t>
         </is>
       </c>
+      <c r="H10" s="693" t="n"/>
+      <c r="I10" s="693" t="n"/>
+      <c r="J10" s="693" t="n"/>
+      <c r="K10" s="693" t="n"/>
+      <c r="L10" s="693" t="n"/>
+      <c r="M10" s="693" t="n"/>
+      <c r="N10" s="693" t="n"/>
+      <c r="O10" s="693" t="n"/>
+      <c r="P10" s="693" t="n"/>
+      <c r="Q10" s="693" t="n"/>
+      <c r="R10" s="693" t="n"/>
+      <c r="S10" s="693" t="n"/>
+      <c r="T10" s="693" t="n"/>
+      <c r="U10" s="693" t="n"/>
+      <c r="V10" s="693" t="n"/>
+      <c r="W10" s="693" t="n"/>
+      <c r="X10" s="693" t="n"/>
+      <c r="Y10" s="693" t="n"/>
+      <c r="Z10" s="693" t="n"/>
+      <c r="AA10" s="693" t="n"/>
+      <c r="AB10" s="693" t="n"/>
+      <c r="AC10" s="693" t="n"/>
+      <c r="AD10" s="693" t="n"/>
+      <c r="AE10" s="693" t="n"/>
+      <c r="AF10" s="693" t="n"/>
+      <c r="AG10" s="693" t="n"/>
+      <c r="AH10" s="693" t="n"/>
+      <c r="AI10" s="693" t="n"/>
+      <c r="AJ10" s="693" t="n"/>
+      <c r="AK10" s="693" t="n"/>
+      <c r="AL10" s="693" t="n"/>
+      <c r="AM10" s="693" t="n"/>
+      <c r="AN10" s="693" t="n"/>
     </row>
-    <row r="5">
-      <c r="A5" s="266" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="266" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="B5" s="266" t="inlineStr">
+      <c r="B11" s="266" t="inlineStr">
         <is>
           <t>REJECT</t>
         </is>
       </c>
-      <c r="C5" s="266" t="inlineStr">
+      <c r="C11" s="266" t="inlineStr">
         <is>
           <t>VACUUM-COMPATIBLE</t>
         </is>
       </c>
-      <c r="D5" s="266" t="n"/>
-      <c r="E5" s="348" t="inlineStr">
+      <c r="D11" s="693" t="n"/>
+      <c r="E11" s="348" t="inlineStr">
         <is>
           <t>VERIFIED</t>
         </is>
       </c>
-      <c r="F5" s="266" t="inlineStr">
+      <c r="F11" s="266" t="inlineStr">
         <is>
           <t>PROD</t>
         </is>
       </c>
-      <c r="G5" s="266" t="inlineStr">
+      <c r="G11" s="266" t="inlineStr">
         <is>
           <t>MONITORING</t>
         </is>
       </c>
+      <c r="H11" s="693" t="n"/>
+      <c r="I11" s="693" t="n"/>
+      <c r="J11" s="693" t="n"/>
+      <c r="K11" s="693" t="n"/>
+      <c r="L11" s="693" t="n"/>
+      <c r="M11" s="693" t="n"/>
+      <c r="N11" s="693" t="n"/>
+      <c r="O11" s="693" t="n"/>
+      <c r="P11" s="693" t="n"/>
+      <c r="Q11" s="693" t="n"/>
+      <c r="R11" s="693" t="n"/>
+      <c r="S11" s="693" t="n"/>
+      <c r="T11" s="693" t="n"/>
+      <c r="U11" s="693" t="n"/>
+      <c r="V11" s="693" t="n"/>
+      <c r="W11" s="693" t="n"/>
+      <c r="X11" s="693" t="n"/>
+      <c r="Y11" s="693" t="n"/>
+      <c r="Z11" s="693" t="n"/>
+      <c r="AA11" s="693" t="n"/>
+      <c r="AB11" s="693" t="n"/>
+      <c r="AC11" s="693" t="n"/>
+      <c r="AD11" s="693" t="n"/>
+      <c r="AE11" s="693" t="n"/>
+      <c r="AF11" s="693" t="n"/>
+      <c r="AG11" s="693" t="n"/>
+      <c r="AH11" s="693" t="n"/>
+      <c r="AI11" s="693" t="n"/>
+      <c r="AJ11" s="693" t="n"/>
+      <c r="AK11" s="693" t="n"/>
+      <c r="AL11" s="693" t="n"/>
+      <c r="AM11" s="693" t="n"/>
+      <c r="AN11" s="693" t="n"/>
     </row>
-    <row r="6">
-      <c r="E6" s="348" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="693" t="n"/>
+      <c r="B12" s="693" t="n"/>
+      <c r="C12" s="693" t="n"/>
+      <c r="D12" s="693" t="n"/>
+      <c r="E12" s="348" t="inlineStr">
         <is>
           <t>INEFFECTIVE</t>
         </is>
       </c>
-      <c r="F6" s="266" t="inlineStr">
+      <c r="F12" s="266" t="inlineStr">
         <is>
           <t>QA</t>
         </is>
       </c>
-      <c r="G6" s="266" t="n"/>
+      <c r="G12" s="693" t="n"/>
+      <c r="H12" s="693" t="n"/>
+      <c r="I12" s="693" t="n"/>
+      <c r="J12" s="693" t="n"/>
+      <c r="K12" s="693" t="n"/>
+      <c r="L12" s="693" t="n"/>
+      <c r="M12" s="693" t="n"/>
+      <c r="N12" s="693" t="n"/>
+      <c r="O12" s="693" t="n"/>
+      <c r="P12" s="693" t="n"/>
+      <c r="Q12" s="693" t="n"/>
+      <c r="R12" s="693" t="n"/>
+      <c r="S12" s="693" t="n"/>
+      <c r="T12" s="693" t="n"/>
+      <c r="U12" s="693" t="n"/>
+      <c r="V12" s="693" t="n"/>
+      <c r="W12" s="693" t="n"/>
+      <c r="X12" s="693" t="n"/>
+      <c r="Y12" s="693" t="n"/>
+      <c r="Z12" s="693" t="n"/>
+      <c r="AA12" s="693" t="n"/>
+      <c r="AB12" s="693" t="n"/>
+      <c r="AC12" s="693" t="n"/>
+      <c r="AD12" s="693" t="n"/>
+      <c r="AE12" s="693" t="n"/>
+      <c r="AF12" s="693" t="n"/>
+      <c r="AG12" s="693" t="n"/>
+      <c r="AH12" s="693" t="n"/>
+      <c r="AI12" s="693" t="n"/>
+      <c r="AJ12" s="693" t="n"/>
+      <c r="AK12" s="693" t="n"/>
+      <c r="AL12" s="693" t="n"/>
+      <c r="AM12" s="693" t="n"/>
+      <c r="AN12" s="693" t="n"/>
     </row>
-    <row r="7">
-      <c r="E7" s="348" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="693" t="n"/>
+      <c r="B13" s="693" t="n"/>
+      <c r="C13" s="693" t="n"/>
+      <c r="D13" s="693" t="n"/>
+      <c r="E13" s="348" t="inlineStr">
         <is>
           <t>CLOSED</t>
         </is>
       </c>
-      <c r="F7" s="266" t="inlineStr">
+      <c r="F13" s="266" t="inlineStr">
         <is>
           <t>PUR</t>
         </is>
       </c>
+      <c r="G13" s="693" t="n"/>
+      <c r="H13" s="693" t="n"/>
+      <c r="I13" s="693" t="n"/>
+      <c r="J13" s="693" t="n"/>
+      <c r="K13" s="693" t="n"/>
+      <c r="L13" s="693" t="n"/>
+      <c r="M13" s="693" t="n"/>
+      <c r="N13" s="693" t="n"/>
+      <c r="O13" s="693" t="n"/>
+      <c r="P13" s="693" t="n"/>
+      <c r="Q13" s="693" t="n"/>
+      <c r="R13" s="693" t="n"/>
+      <c r="S13" s="693" t="n"/>
+      <c r="T13" s="693" t="n"/>
+      <c r="U13" s="693" t="n"/>
+      <c r="V13" s="693" t="n"/>
+      <c r="W13" s="693" t="n"/>
+      <c r="X13" s="693" t="n"/>
+      <c r="Y13" s="693" t="n"/>
+      <c r="Z13" s="693" t="n"/>
+      <c r="AA13" s="693" t="n"/>
+      <c r="AB13" s="693" t="n"/>
+      <c r="AC13" s="693" t="n"/>
+      <c r="AD13" s="693" t="n"/>
+      <c r="AE13" s="693" t="n"/>
+      <c r="AF13" s="693" t="n"/>
+      <c r="AG13" s="693" t="n"/>
+      <c r="AH13" s="693" t="n"/>
+      <c r="AI13" s="693" t="n"/>
+      <c r="AJ13" s="693" t="n"/>
+      <c r="AK13" s="693" t="n"/>
+      <c r="AL13" s="693" t="n"/>
+      <c r="AM13" s="693" t="n"/>
+      <c r="AN13" s="693" t="n"/>
     </row>
-    <row r="8">
-      <c r="F8" s="266" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="693" t="n"/>
+      <c r="B14" s="693" t="n"/>
+      <c r="C14" s="693" t="n"/>
+      <c r="D14" s="693" t="n"/>
+      <c r="E14" s="693" t="n"/>
+      <c r="F14" s="266" t="inlineStr">
         <is>
           <t>WHS</t>
         </is>
       </c>
+      <c r="G14" s="693" t="n"/>
+      <c r="H14" s="693" t="n"/>
+      <c r="I14" s="693" t="n"/>
+      <c r="J14" s="693" t="n"/>
+      <c r="K14" s="693" t="n"/>
+      <c r="L14" s="693" t="n"/>
+      <c r="M14" s="693" t="n"/>
+      <c r="N14" s="693" t="n"/>
+      <c r="O14" s="693" t="n"/>
+      <c r="P14" s="693" t="n"/>
+      <c r="Q14" s="693" t="n"/>
+      <c r="R14" s="693" t="n"/>
+      <c r="S14" s="693" t="n"/>
+      <c r="T14" s="693" t="n"/>
+      <c r="U14" s="693" t="n"/>
+      <c r="V14" s="693" t="n"/>
+      <c r="W14" s="693" t="n"/>
+      <c r="X14" s="693" t="n"/>
+      <c r="Y14" s="693" t="n"/>
+      <c r="Z14" s="693" t="n"/>
+      <c r="AA14" s="693" t="n"/>
+      <c r="AB14" s="693" t="n"/>
+      <c r="AC14" s="693" t="n"/>
+      <c r="AD14" s="693" t="n"/>
+      <c r="AE14" s="693" t="n"/>
+      <c r="AF14" s="693" t="n"/>
+      <c r="AG14" s="693" t="n"/>
+      <c r="AH14" s="693" t="n"/>
+      <c r="AI14" s="693" t="n"/>
+      <c r="AJ14" s="693" t="n"/>
+      <c r="AK14" s="693" t="n"/>
+      <c r="AL14" s="693" t="n"/>
+      <c r="AM14" s="693" t="n"/>
+      <c r="AN14" s="693" t="n"/>
     </row>
-    <row r="9">
-      <c r="F9" s="266" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="693" t="n"/>
+      <c r="B15" s="693" t="n"/>
+      <c r="C15" s="693" t="n"/>
+      <c r="D15" s="693" t="n"/>
+      <c r="E15" s="693" t="n"/>
+      <c r="F15" s="266" t="inlineStr">
         <is>
           <t>IT</t>
         </is>
       </c>
+      <c r="G15" s="693" t="n"/>
+      <c r="H15" s="693" t="n"/>
+      <c r="I15" s="693" t="n"/>
+      <c r="J15" s="693" t="n"/>
+      <c r="K15" s="693" t="n"/>
+      <c r="L15" s="693" t="n"/>
+      <c r="M15" s="693" t="n"/>
+      <c r="N15" s="693" t="n"/>
+      <c r="O15" s="693" t="n"/>
+      <c r="P15" s="693" t="n"/>
+      <c r="Q15" s="693" t="n"/>
+      <c r="R15" s="693" t="n"/>
+      <c r="S15" s="693" t="n"/>
+      <c r="T15" s="693" t="n"/>
+      <c r="U15" s="693" t="n"/>
+      <c r="V15" s="693" t="n"/>
+      <c r="W15" s="693" t="n"/>
+      <c r="X15" s="693" t="n"/>
+      <c r="Y15" s="693" t="n"/>
+      <c r="Z15" s="693" t="n"/>
+      <c r="AA15" s="693" t="n"/>
+      <c r="AB15" s="693" t="n"/>
+      <c r="AC15" s="693" t="n"/>
+      <c r="AD15" s="693" t="n"/>
+      <c r="AE15" s="693" t="n"/>
+      <c r="AF15" s="693" t="n"/>
+      <c r="AG15" s="693" t="n"/>
+      <c r="AH15" s="693" t="n"/>
+      <c r="AI15" s="693" t="n"/>
+      <c r="AJ15" s="693" t="n"/>
+      <c r="AK15" s="693" t="n"/>
+      <c r="AL15" s="693" t="n"/>
+      <c r="AM15" s="693" t="n"/>
+      <c r="AN15" s="693" t="n"/>
     </row>
-    <row r="10">
-      <c r="F10" s="266" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="693" t="n"/>
+      <c r="B16" s="693" t="n"/>
+      <c r="C16" s="693" t="n"/>
+      <c r="D16" s="693" t="n"/>
+      <c r="E16" s="693" t="n"/>
+      <c r="F16" s="266" t="inlineStr">
         <is>
           <t>HR</t>
         </is>
       </c>
+      <c r="G16" s="693" t="n"/>
+      <c r="H16" s="693" t="n"/>
+      <c r="I16" s="693" t="n"/>
+      <c r="J16" s="693" t="n"/>
+      <c r="K16" s="693" t="n"/>
+      <c r="L16" s="693" t="n"/>
+      <c r="M16" s="693" t="n"/>
+      <c r="N16" s="693" t="n"/>
+      <c r="O16" s="693" t="n"/>
+      <c r="P16" s="693" t="n"/>
+      <c r="Q16" s="693" t="n"/>
+      <c r="R16" s="693" t="n"/>
+      <c r="S16" s="693" t="n"/>
+      <c r="T16" s="693" t="n"/>
+      <c r="U16" s="693" t="n"/>
+      <c r="V16" s="693" t="n"/>
+      <c r="W16" s="693" t="n"/>
+      <c r="X16" s="693" t="n"/>
+      <c r="Y16" s="693" t="n"/>
+      <c r="Z16" s="693" t="n"/>
+      <c r="AA16" s="693" t="n"/>
+      <c r="AB16" s="693" t="n"/>
+      <c r="AC16" s="693" t="n"/>
+      <c r="AD16" s="693" t="n"/>
+      <c r="AE16" s="693" t="n"/>
+      <c r="AF16" s="693" t="n"/>
+      <c r="AG16" s="693" t="n"/>
+      <c r="AH16" s="693" t="n"/>
+      <c r="AI16" s="693" t="n"/>
+      <c r="AJ16" s="693" t="n"/>
+      <c r="AK16" s="693" t="n"/>
+      <c r="AL16" s="693" t="n"/>
+      <c r="AM16" s="693" t="n"/>
+      <c r="AN16" s="693" t="n"/>
     </row>
-    <row r="11">
-      <c r="F11" s="266" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="693" t="n"/>
+      <c r="B17" s="693" t="n"/>
+      <c r="C17" s="693" t="n"/>
+      <c r="D17" s="693" t="n"/>
+      <c r="E17" s="693" t="n"/>
+      <c r="F17" s="266" t="inlineStr">
         <is>
           <t>MGT</t>
         </is>
       </c>
+      <c r="G17" s="693" t="n"/>
+      <c r="H17" s="693" t="n"/>
+      <c r="I17" s="693" t="n"/>
+      <c r="J17" s="693" t="n"/>
+      <c r="K17" s="693" t="n"/>
+      <c r="L17" s="693" t="n"/>
+      <c r="M17" s="693" t="n"/>
+      <c r="N17" s="693" t="n"/>
+      <c r="O17" s="693" t="n"/>
+      <c r="P17" s="693" t="n"/>
+      <c r="Q17" s="693" t="n"/>
+      <c r="R17" s="693" t="n"/>
+      <c r="S17" s="693" t="n"/>
+      <c r="T17" s="693" t="n"/>
+      <c r="U17" s="693" t="n"/>
+      <c r="V17" s="693" t="n"/>
+      <c r="W17" s="693" t="n"/>
+      <c r="X17" s="693" t="n"/>
+      <c r="Y17" s="693" t="n"/>
+      <c r="Z17" s="693" t="n"/>
+      <c r="AA17" s="693" t="n"/>
+      <c r="AB17" s="693" t="n"/>
+      <c r="AC17" s="693" t="n"/>
+      <c r="AD17" s="693" t="n"/>
+      <c r="AE17" s="693" t="n"/>
+      <c r="AF17" s="693" t="n"/>
+      <c r="AG17" s="693" t="n"/>
+      <c r="AH17" s="693" t="n"/>
+      <c r="AI17" s="693" t="n"/>
+      <c r="AJ17" s="693" t="n"/>
+      <c r="AK17" s="693" t="n"/>
+      <c r="AL17" s="693" t="n"/>
+      <c r="AM17" s="693" t="n"/>
+      <c r="AN17" s="693" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="693" t="n"/>
+      <c r="B18" s="693" t="n"/>
+      <c r="C18" s="693" t="n"/>
+      <c r="D18" s="693" t="n"/>
+      <c r="E18" s="693" t="n"/>
+      <c r="F18" s="693" t="n"/>
+      <c r="G18" s="693" t="n"/>
+      <c r="H18" s="693" t="n"/>
+      <c r="I18" s="693" t="n"/>
+      <c r="J18" s="693" t="n"/>
+      <c r="K18" s="693" t="n"/>
+      <c r="L18" s="693" t="n"/>
+      <c r="M18" s="693" t="n"/>
+      <c r="N18" s="693" t="n"/>
+      <c r="O18" s="693" t="n"/>
+      <c r="P18" s="693" t="n"/>
+      <c r="Q18" s="693" t="n"/>
+      <c r="R18" s="693" t="n"/>
+      <c r="S18" s="693" t="n"/>
+      <c r="T18" s="693" t="n"/>
+      <c r="U18" s="693" t="n"/>
+      <c r="V18" s="693" t="n"/>
+      <c r="W18" s="693" t="n"/>
+      <c r="X18" s="693" t="n"/>
+      <c r="Y18" s="693" t="n"/>
+      <c r="Z18" s="693" t="n"/>
+      <c r="AA18" s="693" t="n"/>
+      <c r="AB18" s="693" t="n"/>
+      <c r="AC18" s="693" t="n"/>
+      <c r="AD18" s="693" t="n"/>
+      <c r="AE18" s="693" t="n"/>
+      <c r="AF18" s="693" t="n"/>
+      <c r="AG18" s="693" t="n"/>
+      <c r="AH18" s="693" t="n"/>
+      <c r="AI18" s="693" t="n"/>
+      <c r="AJ18" s="693" t="n"/>
+      <c r="AK18" s="693" t="n"/>
+      <c r="AL18" s="693" t="n"/>
+      <c r="AM18" s="693" t="n"/>
+      <c r="AN18" s="693" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="693" t="n"/>
+      <c r="B19" s="693" t="n"/>
+      <c r="C19" s="693" t="n"/>
+      <c r="D19" s="693" t="n"/>
+      <c r="E19" s="693" t="n"/>
+      <c r="F19" s="693" t="n"/>
+      <c r="G19" s="693" t="n"/>
+      <c r="H19" s="693" t="n"/>
+      <c r="I19" s="693" t="n"/>
+      <c r="J19" s="693" t="n"/>
+      <c r="K19" s="693" t="n"/>
+      <c r="L19" s="693" t="n"/>
+      <c r="M19" s="693" t="n"/>
+      <c r="N19" s="693" t="n"/>
+      <c r="O19" s="693" t="n"/>
+      <c r="P19" s="693" t="n"/>
+      <c r="Q19" s="693" t="n"/>
+      <c r="R19" s="693" t="n"/>
+      <c r="S19" s="693" t="n"/>
+      <c r="T19" s="693" t="n"/>
+      <c r="U19" s="693" t="n"/>
+      <c r="V19" s="693" t="n"/>
+      <c r="W19" s="693" t="n"/>
+      <c r="X19" s="693" t="n"/>
+      <c r="Y19" s="693" t="n"/>
+      <c r="Z19" s="693" t="n"/>
+      <c r="AA19" s="693" t="n"/>
+      <c r="AB19" s="693" t="n"/>
+      <c r="AC19" s="693" t="n"/>
+      <c r="AD19" s="693" t="n"/>
+      <c r="AE19" s="693" t="n"/>
+      <c r="AF19" s="693" t="n"/>
+      <c r="AG19" s="693" t="n"/>
+      <c r="AH19" s="693" t="n"/>
+      <c r="AI19" s="693" t="n"/>
+      <c r="AJ19" s="693" t="n"/>
+      <c r="AK19" s="693" t="n"/>
+      <c r="AL19" s="693" t="n"/>
+      <c r="AM19" s="693" t="n"/>
+      <c r="AN19" s="693" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="693" t="n"/>
+      <c r="B20" s="693" t="n"/>
+      <c r="C20" s="693" t="n"/>
+      <c r="D20" s="693" t="n"/>
+      <c r="E20" s="693" t="n"/>
+      <c r="F20" s="693" t="n"/>
+      <c r="G20" s="693" t="n"/>
+      <c r="H20" s="693" t="n"/>
+      <c r="I20" s="693" t="n"/>
+      <c r="J20" s="693" t="n"/>
+      <c r="K20" s="693" t="n"/>
+      <c r="L20" s="693" t="n"/>
+      <c r="M20" s="693" t="n"/>
+      <c r="N20" s="693" t="n"/>
+      <c r="O20" s="693" t="n"/>
+      <c r="P20" s="693" t="n"/>
+      <c r="Q20" s="693" t="n"/>
+      <c r="R20" s="693" t="n"/>
+      <c r="S20" s="693" t="n"/>
+      <c r="T20" s="693" t="n"/>
+      <c r="U20" s="693" t="n"/>
+      <c r="V20" s="693" t="n"/>
+      <c r="W20" s="693" t="n"/>
+      <c r="X20" s="693" t="n"/>
+      <c r="Y20" s="693" t="n"/>
+      <c r="Z20" s="693" t="n"/>
+      <c r="AA20" s="693" t="n"/>
+      <c r="AB20" s="693" t="n"/>
+      <c r="AC20" s="693" t="n"/>
+      <c r="AD20" s="693" t="n"/>
+      <c r="AE20" s="693" t="n"/>
+      <c r="AF20" s="693" t="n"/>
+      <c r="AG20" s="693" t="n"/>
+      <c r="AH20" s="693" t="n"/>
+      <c r="AI20" s="693" t="n"/>
+      <c r="AJ20" s="693" t="n"/>
+      <c r="AK20" s="693" t="n"/>
+      <c r="AL20" s="693" t="n"/>
+      <c r="AM20" s="693" t="n"/>
+      <c r="AN20" s="693" t="n"/>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <mergeCells count="14">
+    <mergeCell ref="AI2:AN2"/>
+    <mergeCell ref="I1:AD3"/>
+    <mergeCell ref="AE4:AH4"/>
+    <mergeCell ref="AI1:AN1"/>
+    <mergeCell ref="I5:AD5"/>
+    <mergeCell ref="AE3:AH3"/>
+    <mergeCell ref="AI5:AN5"/>
+    <mergeCell ref="A1:H5"/>
+    <mergeCell ref="AI4:AN4"/>
+    <mergeCell ref="AE2:AH2"/>
+    <mergeCell ref="I4:AD4"/>
+    <mergeCell ref="AI3:AN3"/>
+    <mergeCell ref="AE1:AH1"/>
+    <mergeCell ref="AE5:AH5"/>
+  </mergeCells>
+  <pageMargins left="0.197" right="0.197" top="0.197" bottom="0.197" header="0.1" footer="0.1"/>
+  <pageSetup paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -9845,7 +11219,7 @@
     <col width="2.33" customWidth="1" min="56" max="56"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1">
+    <row r="1" hidden="1">
       <c r="A1" s="547" t="n"/>
       <c r="B1" s="548" t="n"/>
       <c r="C1" s="548" t="n"/>
@@ -9912,840 +11286,950 @@
       <c r="BD1" s="549" t="n"/>
     </row>
     <row r="2" ht="15" customHeight="1">
-      <c r="A2" s="554" t="n"/>
-      <c r="K2" s="555" t="n"/>
-      <c r="L2" s="554" t="n"/>
-      <c r="AP2" s="555" t="n"/>
-      <c r="AQ2" s="556" t="n"/>
-      <c r="AR2" s="422" t="n"/>
-      <c r="AS2" s="422" t="n"/>
-      <c r="AT2" s="422" t="n"/>
-      <c r="AU2" s="422" t="n"/>
-      <c r="AV2" s="557" t="n"/>
-      <c r="AW2" s="558" t="inlineStr">
+      <c r="A2" s="1" t="n"/>
+      <c r="B2" s="694" t="n"/>
+      <c r="C2" s="694" t="n"/>
+      <c r="D2" s="694" t="n"/>
+      <c r="E2" s="694" t="n"/>
+      <c r="F2" s="694" t="n"/>
+      <c r="G2" s="694" t="n"/>
+      <c r="H2" s="694" t="n"/>
+      <c r="I2" s="694" t="n"/>
+      <c r="J2" s="694" t="n"/>
+      <c r="K2" s="695" t="n"/>
+      <c r="L2" s="694" t="n"/>
+      <c r="M2" s="694" t="n"/>
+      <c r="N2" s="694" t="n"/>
+      <c r="O2" s="694" t="n"/>
+      <c r="P2" s="694" t="n"/>
+      <c r="Q2" s="694" t="n"/>
+      <c r="R2" s="694" t="n"/>
+      <c r="S2" s="694" t="n"/>
+      <c r="T2" s="694" t="n"/>
+      <c r="U2" s="694" t="n"/>
+      <c r="V2" s="694" t="n"/>
+      <c r="W2" s="694" t="n"/>
+      <c r="X2" s="694" t="n"/>
+      <c r="Y2" s="694" t="n"/>
+      <c r="Z2" s="694" t="n"/>
+      <c r="AA2" s="694" t="n"/>
+      <c r="AB2" s="694" t="n"/>
+      <c r="AC2" s="694" t="n"/>
+      <c r="AD2" s="694" t="n"/>
+      <c r="AE2" s="694" t="n"/>
+      <c r="AF2" s="694" t="n"/>
+      <c r="AG2" s="694" t="n"/>
+      <c r="AH2" s="694" t="n"/>
+      <c r="AI2" s="694" t="n"/>
+      <c r="AJ2" s="694" t="n"/>
+      <c r="AK2" s="694" t="n"/>
+      <c r="AL2" s="694" t="n"/>
+      <c r="AM2" s="694" t="n"/>
+      <c r="AN2" s="694" t="n"/>
+      <c r="AO2" s="694" t="n"/>
+      <c r="AP2" s="695" t="n"/>
+      <c r="AQ2" s="696" t="n"/>
+      <c r="AR2" s="697" t="n"/>
+      <c r="AS2" s="697" t="n"/>
+      <c r="AT2" s="697" t="n"/>
+      <c r="AU2" s="697" t="n"/>
+      <c r="AV2" s="698" t="n"/>
+      <c r="AW2" s="7" t="inlineStr">
         <is>
           <t>V0</t>
         </is>
       </c>
-      <c r="AX2" s="422" t="n"/>
-      <c r="AY2" s="422" t="n"/>
-      <c r="AZ2" s="422" t="n"/>
-      <c r="BA2" s="422" t="n"/>
-      <c r="BB2" s="422" t="n"/>
-      <c r="BC2" s="422" t="n"/>
-      <c r="BD2" s="559" t="n"/>
+      <c r="AX2" s="699" t="n"/>
+      <c r="AY2" s="699" t="n"/>
+      <c r="AZ2" s="699" t="n"/>
+      <c r="BA2" s="699" t="n"/>
+      <c r="BB2" s="699" t="n"/>
+      <c r="BC2" s="699" t="n"/>
+      <c r="BD2" s="700" t="n"/>
     </row>
     <row r="3" ht="15" customHeight="1">
-      <c r="A3" s="554" t="n"/>
-      <c r="K3" s="555" t="n"/>
-      <c r="L3" s="554" t="n"/>
-      <c r="AP3" s="555" t="n"/>
-      <c r="AQ3" s="556" t="n"/>
-      <c r="AR3" s="422" t="n"/>
-      <c r="AS3" s="422" t="n"/>
-      <c r="AT3" s="422" t="n"/>
-      <c r="AU3" s="422" t="n"/>
-      <c r="AV3" s="557" t="n"/>
-      <c r="AW3" s="558" t="inlineStr">
+      <c r="A3" s="701" t="n"/>
+      <c r="B3" s="25" t="n"/>
+      <c r="C3" s="25" t="n"/>
+      <c r="D3" s="25" t="n"/>
+      <c r="E3" s="25" t="n"/>
+      <c r="F3" s="25" t="n"/>
+      <c r="G3" s="25" t="n"/>
+      <c r="H3" s="25" t="n"/>
+      <c r="I3" s="25" t="n"/>
+      <c r="J3" s="25" t="n"/>
+      <c r="K3" s="702" t="n"/>
+      <c r="L3" s="25" t="n"/>
+      <c r="M3" s="25" t="n"/>
+      <c r="N3" s="25" t="n"/>
+      <c r="O3" s="25" t="n"/>
+      <c r="P3" s="25" t="n"/>
+      <c r="Q3" s="25" t="n"/>
+      <c r="R3" s="25" t="n"/>
+      <c r="S3" s="25" t="n"/>
+      <c r="T3" s="25" t="n"/>
+      <c r="U3" s="25" t="n"/>
+      <c r="V3" s="25" t="n"/>
+      <c r="W3" s="25" t="n"/>
+      <c r="X3" s="25" t="n"/>
+      <c r="Y3" s="25" t="n"/>
+      <c r="Z3" s="25" t="n"/>
+      <c r="AA3" s="25" t="n"/>
+      <c r="AB3" s="25" t="n"/>
+      <c r="AC3" s="25" t="n"/>
+      <c r="AD3" s="25" t="n"/>
+      <c r="AE3" s="25" t="n"/>
+      <c r="AF3" s="25" t="n"/>
+      <c r="AG3" s="25" t="n"/>
+      <c r="AH3" s="25" t="n"/>
+      <c r="AI3" s="25" t="n"/>
+      <c r="AJ3" s="25" t="n"/>
+      <c r="AK3" s="25" t="n"/>
+      <c r="AL3" s="25" t="n"/>
+      <c r="AM3" s="25" t="n"/>
+      <c r="AN3" s="25" t="n"/>
+      <c r="AO3" s="25" t="n"/>
+      <c r="AP3" s="702" t="n"/>
+      <c r="AQ3" s="703" t="n"/>
+      <c r="AR3" s="704" t="n"/>
+      <c r="AS3" s="704" t="n"/>
+      <c r="AT3" s="704" t="n"/>
+      <c r="AU3" s="704" t="n"/>
+      <c r="AV3" s="705" t="n"/>
+      <c r="AW3" s="14" t="inlineStr">
         <is>
           <t>YYYY-MM-DD</t>
         </is>
       </c>
-      <c r="AX3" s="422" t="n"/>
-      <c r="AY3" s="422" t="n"/>
-      <c r="AZ3" s="422" t="n"/>
-      <c r="BA3" s="422" t="n"/>
-      <c r="BB3" s="422" t="n"/>
-      <c r="BC3" s="422" t="n"/>
-      <c r="BD3" s="559" t="n"/>
+      <c r="AX3" s="706" t="n"/>
+      <c r="AY3" s="706" t="n"/>
+      <c r="AZ3" s="706" t="n"/>
+      <c r="BA3" s="706" t="n"/>
+      <c r="BB3" s="706" t="n"/>
+      <c r="BC3" s="706" t="n"/>
+      <c r="BD3" s="707" t="n"/>
     </row>
     <row r="4" ht="15" customHeight="1">
-      <c r="A4" s="554" t="n"/>
-      <c r="K4" s="555" t="n"/>
-      <c r="L4" s="560" t="inlineStr">
+      <c r="A4" s="701" t="n"/>
+      <c r="B4" s="25" t="n"/>
+      <c r="C4" s="25" t="n"/>
+      <c r="D4" s="25" t="n"/>
+      <c r="E4" s="25" t="n"/>
+      <c r="F4" s="25" t="n"/>
+      <c r="G4" s="25" t="n"/>
+      <c r="H4" s="25" t="n"/>
+      <c r="I4" s="25" t="n"/>
+      <c r="J4" s="25" t="n"/>
+      <c r="K4" s="702" t="n"/>
+      <c r="L4" s="708" t="inlineStr">
         <is>
           <t>Quality Management System · Controlled Document</t>
         </is>
       </c>
-      <c r="AP4" s="555" t="n"/>
-      <c r="AQ4" s="556" t="n"/>
-      <c r="AR4" s="422" t="n"/>
-      <c r="AS4" s="422" t="n"/>
-      <c r="AT4" s="422" t="n"/>
-      <c r="AU4" s="422" t="n"/>
-      <c r="AV4" s="557" t="n"/>
-      <c r="AW4" s="558" t="inlineStr">
+      <c r="M4" s="25" t="n"/>
+      <c r="N4" s="25" t="n"/>
+      <c r="O4" s="25" t="n"/>
+      <c r="P4" s="25" t="n"/>
+      <c r="Q4" s="25" t="n"/>
+      <c r="R4" s="25" t="n"/>
+      <c r="S4" s="25" t="n"/>
+      <c r="T4" s="25" t="n"/>
+      <c r="U4" s="25" t="n"/>
+      <c r="V4" s="25" t="n"/>
+      <c r="W4" s="25" t="n"/>
+      <c r="X4" s="25" t="n"/>
+      <c r="Y4" s="25" t="n"/>
+      <c r="Z4" s="25" t="n"/>
+      <c r="AA4" s="25" t="n"/>
+      <c r="AB4" s="25" t="n"/>
+      <c r="AC4" s="25" t="n"/>
+      <c r="AD4" s="25" t="n"/>
+      <c r="AE4" s="25" t="n"/>
+      <c r="AF4" s="25" t="n"/>
+      <c r="AG4" s="25" t="n"/>
+      <c r="AH4" s="25" t="n"/>
+      <c r="AI4" s="25" t="n"/>
+      <c r="AJ4" s="25" t="n"/>
+      <c r="AK4" s="25" t="n"/>
+      <c r="AL4" s="25" t="n"/>
+      <c r="AM4" s="25" t="n"/>
+      <c r="AN4" s="25" t="n"/>
+      <c r="AO4" s="25" t="n"/>
+      <c r="AP4" s="702" t="n"/>
+      <c r="AQ4" s="703" t="n"/>
+      <c r="AR4" s="704" t="n"/>
+      <c r="AS4" s="704" t="n"/>
+      <c r="AT4" s="704" t="n"/>
+      <c r="AU4" s="704" t="n"/>
+      <c r="AV4" s="705" t="n"/>
+      <c r="AW4" s="14" t="inlineStr">
         <is>
           <t>Warehouse + QA</t>
         </is>
       </c>
-      <c r="AX4" s="422" t="n"/>
-      <c r="AY4" s="422" t="n"/>
-      <c r="AZ4" s="422" t="n"/>
-      <c r="BA4" s="422" t="n"/>
-      <c r="BB4" s="422" t="n"/>
-      <c r="BC4" s="422" t="n"/>
-      <c r="BD4" s="559" t="n"/>
+      <c r="AX4" s="706" t="n"/>
+      <c r="AY4" s="706" t="n"/>
+      <c r="AZ4" s="706" t="n"/>
+      <c r="BA4" s="706" t="n"/>
+      <c r="BB4" s="706" t="n"/>
+      <c r="BC4" s="706" t="n"/>
+      <c r="BD4" s="707" t="n"/>
     </row>
     <row r="5" ht="15" customHeight="1">
-      <c r="A5" s="561" t="n"/>
-      <c r="B5" s="562" t="n"/>
-      <c r="C5" s="562" t="n"/>
-      <c r="D5" s="562" t="n"/>
-      <c r="E5" s="562" t="n"/>
-      <c r="F5" s="562" t="n"/>
-      <c r="G5" s="562" t="n"/>
-      <c r="H5" s="562" t="n"/>
-      <c r="I5" s="562" t="n"/>
-      <c r="J5" s="562" t="n"/>
-      <c r="K5" s="563" t="n"/>
-      <c r="L5" s="564" t="inlineStr">
+      <c r="A5" s="701" t="n"/>
+      <c r="B5" s="25" t="n"/>
+      <c r="C5" s="25" t="n"/>
+      <c r="D5" s="25" t="n"/>
+      <c r="E5" s="25" t="n"/>
+      <c r="F5" s="25" t="n"/>
+      <c r="G5" s="25" t="n"/>
+      <c r="H5" s="25" t="n"/>
+      <c r="I5" s="25" t="n"/>
+      <c r="J5" s="25" t="n"/>
+      <c r="K5" s="702" t="n"/>
+      <c r="L5" s="709" t="inlineStr">
         <is>
           <t>HESEM Engineering · ISO 9001 / AS9100 · Semiconductor Equipment Parts</t>
         </is>
       </c>
-      <c r="M5" s="562" t="n"/>
-      <c r="N5" s="562" t="n"/>
-      <c r="O5" s="562" t="n"/>
-      <c r="P5" s="562" t="n"/>
-      <c r="Q5" s="562" t="n"/>
-      <c r="R5" s="562" t="n"/>
-      <c r="S5" s="562" t="n"/>
-      <c r="T5" s="562" t="n"/>
-      <c r="U5" s="562" t="n"/>
-      <c r="V5" s="562" t="n"/>
-      <c r="W5" s="562" t="n"/>
-      <c r="X5" s="562" t="n"/>
-      <c r="Y5" s="562" t="n"/>
-      <c r="Z5" s="562" t="n"/>
-      <c r="AA5" s="562" t="n"/>
-      <c r="AB5" s="562" t="n"/>
-      <c r="AC5" s="562" t="n"/>
-      <c r="AD5" s="562" t="n"/>
-      <c r="AE5" s="562" t="n"/>
-      <c r="AF5" s="562" t="n"/>
-      <c r="AG5" s="562" t="n"/>
-      <c r="AH5" s="562" t="n"/>
-      <c r="AI5" s="562" t="n"/>
-      <c r="AJ5" s="562" t="n"/>
-      <c r="AK5" s="562" t="n"/>
-      <c r="AL5" s="562" t="n"/>
-      <c r="AM5" s="562" t="n"/>
-      <c r="AN5" s="562" t="n"/>
-      <c r="AO5" s="562" t="n"/>
-      <c r="AP5" s="563" t="n"/>
-      <c r="AQ5" s="565" t="n"/>
-      <c r="AR5" s="566" t="n"/>
-      <c r="AS5" s="566" t="n"/>
-      <c r="AT5" s="566" t="n"/>
-      <c r="AU5" s="566" t="n"/>
-      <c r="AV5" s="567" t="n"/>
-      <c r="AW5" s="568" t="inlineStr">
+      <c r="M5" s="25" t="n"/>
+      <c r="N5" s="25" t="n"/>
+      <c r="O5" s="25" t="n"/>
+      <c r="P5" s="25" t="n"/>
+      <c r="Q5" s="25" t="n"/>
+      <c r="R5" s="25" t="n"/>
+      <c r="S5" s="25" t="n"/>
+      <c r="T5" s="25" t="n"/>
+      <c r="U5" s="25" t="n"/>
+      <c r="V5" s="25" t="n"/>
+      <c r="W5" s="25" t="n"/>
+      <c r="X5" s="25" t="n"/>
+      <c r="Y5" s="25" t="n"/>
+      <c r="Z5" s="25" t="n"/>
+      <c r="AA5" s="25" t="n"/>
+      <c r="AB5" s="25" t="n"/>
+      <c r="AC5" s="25" t="n"/>
+      <c r="AD5" s="25" t="n"/>
+      <c r="AE5" s="25" t="n"/>
+      <c r="AF5" s="25" t="n"/>
+      <c r="AG5" s="25" t="n"/>
+      <c r="AH5" s="25" t="n"/>
+      <c r="AI5" s="25" t="n"/>
+      <c r="AJ5" s="25" t="n"/>
+      <c r="AK5" s="25" t="n"/>
+      <c r="AL5" s="25" t="n"/>
+      <c r="AM5" s="25" t="n"/>
+      <c r="AN5" s="25" t="n"/>
+      <c r="AO5" s="25" t="n"/>
+      <c r="AP5" s="702" t="n"/>
+      <c r="AQ5" s="703" t="n"/>
+      <c r="AR5" s="704" t="n"/>
+      <c r="AS5" s="704" t="n"/>
+      <c r="AT5" s="704" t="n"/>
+      <c r="AU5" s="704" t="n"/>
+      <c r="AV5" s="705" t="n"/>
+      <c r="AW5" s="14" t="inlineStr">
         <is>
           <t>General Manager</t>
         </is>
       </c>
-      <c r="AX5" s="566" t="n"/>
-      <c r="AY5" s="566" t="n"/>
-      <c r="AZ5" s="566" t="n"/>
-      <c r="BA5" s="566" t="n"/>
-      <c r="BB5" s="566" t="n"/>
-      <c r="BC5" s="566" t="n"/>
-      <c r="BD5" s="569" t="n"/>
+      <c r="AX5" s="706" t="n"/>
+      <c r="AY5" s="706" t="n"/>
+      <c r="AZ5" s="706" t="n"/>
+      <c r="BA5" s="706" t="n"/>
+      <c r="BB5" s="706" t="n"/>
+      <c r="BC5" s="706" t="n"/>
+      <c r="BD5" s="707" t="n"/>
     </row>
-    <row r="6" ht="1.5" customHeight="1">
-      <c r="A6" s="659" t="n"/>
-      <c r="B6" s="659" t="n"/>
-      <c r="C6" s="660" t="n"/>
-      <c r="D6" s="659" t="n"/>
-      <c r="E6" s="659" t="n"/>
-      <c r="F6" s="659" t="n"/>
-      <c r="G6" s="659" t="n"/>
-      <c r="H6" s="659" t="n"/>
-      <c r="I6" s="659" t="n"/>
-      <c r="J6" s="659" t="n"/>
-      <c r="K6" s="659" t="n"/>
-      <c r="L6" s="659" t="n"/>
-      <c r="M6" s="659" t="n"/>
-      <c r="N6" s="659" t="n"/>
-      <c r="O6" s="659" t="n"/>
-      <c r="P6" s="659" t="n"/>
-      <c r="Q6" s="659" t="n"/>
-      <c r="R6" s="659" t="n"/>
-      <c r="S6" s="659" t="n"/>
-      <c r="T6" s="659" t="n"/>
-      <c r="U6" s="659" t="n"/>
-      <c r="V6" s="659" t="n"/>
-      <c r="W6" s="659" t="n"/>
-      <c r="X6" s="659" t="n"/>
-      <c r="Y6" s="659" t="n"/>
-      <c r="Z6" s="659" t="n"/>
-      <c r="AA6" s="659" t="n"/>
-      <c r="AB6" s="659" t="n"/>
-      <c r="AC6" s="659" t="n"/>
-      <c r="AD6" s="659" t="n"/>
-      <c r="AE6" s="659" t="n"/>
-      <c r="AF6" s="659" t="n"/>
-      <c r="AG6" s="659" t="n"/>
-      <c r="AH6" s="659" t="n"/>
-      <c r="AI6" s="659" t="n"/>
-      <c r="AJ6" s="659" t="n"/>
-      <c r="AK6" s="659" t="n"/>
-      <c r="AL6" s="659" t="n"/>
-      <c r="AM6" s="659" t="n"/>
-      <c r="AN6" s="659" t="n"/>
-      <c r="AO6" s="659" t="n"/>
-      <c r="AP6" s="659" t="n"/>
-      <c r="AQ6" s="659" t="n"/>
-      <c r="AR6" s="659" t="n"/>
-      <c r="AS6" s="659" t="n"/>
-      <c r="AT6" s="659" t="n"/>
-      <c r="AU6" s="659" t="n"/>
-      <c r="AV6" s="659" t="n"/>
-      <c r="AW6" s="659" t="n"/>
-      <c r="AX6" s="659" t="n"/>
-      <c r="AY6" s="659" t="n"/>
-      <c r="AZ6" s="659" t="n"/>
-      <c r="BA6" s="659" t="n"/>
-      <c r="BB6" s="659" t="n"/>
-      <c r="BC6" s="659" t="n"/>
-      <c r="BD6" s="659" t="n"/>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" s="769" t="n"/>
+      <c r="B6" s="770" t="n"/>
+      <c r="C6" s="771" t="n"/>
+      <c r="D6" s="770" t="n"/>
+      <c r="E6" s="770" t="n"/>
+      <c r="F6" s="770" t="n"/>
+      <c r="G6" s="770" t="n"/>
+      <c r="H6" s="770" t="n"/>
+      <c r="I6" s="770" t="n"/>
+      <c r="J6" s="770" t="n"/>
+      <c r="K6" s="772" t="n"/>
+      <c r="L6" s="770" t="n"/>
+      <c r="M6" s="770" t="n"/>
+      <c r="N6" s="770" t="n"/>
+      <c r="O6" s="770" t="n"/>
+      <c r="P6" s="770" t="n"/>
+      <c r="Q6" s="770" t="n"/>
+      <c r="R6" s="770" t="n"/>
+      <c r="S6" s="770" t="n"/>
+      <c r="T6" s="770" t="n"/>
+      <c r="U6" s="770" t="n"/>
+      <c r="V6" s="770" t="n"/>
+      <c r="W6" s="770" t="n"/>
+      <c r="X6" s="770" t="n"/>
+      <c r="Y6" s="770" t="n"/>
+      <c r="Z6" s="770" t="n"/>
+      <c r="AA6" s="770" t="n"/>
+      <c r="AB6" s="770" t="n"/>
+      <c r="AC6" s="770" t="n"/>
+      <c r="AD6" s="770" t="n"/>
+      <c r="AE6" s="770" t="n"/>
+      <c r="AF6" s="770" t="n"/>
+      <c r="AG6" s="770" t="n"/>
+      <c r="AH6" s="770" t="n"/>
+      <c r="AI6" s="770" t="n"/>
+      <c r="AJ6" s="770" t="n"/>
+      <c r="AK6" s="770" t="n"/>
+      <c r="AL6" s="770" t="n"/>
+      <c r="AM6" s="770" t="n"/>
+      <c r="AN6" s="770" t="n"/>
+      <c r="AO6" s="770" t="n"/>
+      <c r="AP6" s="772" t="n"/>
+      <c r="AQ6" s="773" t="n"/>
+      <c r="AR6" s="773" t="n"/>
+      <c r="AS6" s="773" t="n"/>
+      <c r="AT6" s="773" t="n"/>
+      <c r="AU6" s="773" t="n"/>
+      <c r="AV6" s="774" t="n"/>
+      <c r="AW6" s="775" t="n"/>
+      <c r="AX6" s="775" t="n"/>
+      <c r="AY6" s="775" t="n"/>
+      <c r="AZ6" s="775" t="n"/>
+      <c r="BA6" s="775" t="n"/>
+      <c r="BB6" s="775" t="n"/>
+      <c r="BC6" s="775" t="n"/>
+      <c r="BD6" s="776" t="n"/>
     </row>
-    <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="570" t="inlineStr">
-        <is>
-          <t>VAC-BUILD CONDITIONS / ACTIONS</t>
-        </is>
-      </c>
-      <c r="B7" s="571" t="n"/>
-      <c r="C7" s="571" t="n"/>
-      <c r="D7" s="571" t="n"/>
-      <c r="E7" s="571" t="n"/>
-      <c r="F7" s="571" t="n"/>
-      <c r="G7" s="571" t="n"/>
-      <c r="H7" s="571" t="n"/>
-      <c r="I7" s="571" t="n"/>
-      <c r="J7" s="571" t="n"/>
-      <c r="K7" s="571" t="n"/>
-      <c r="L7" s="571" t="n"/>
-      <c r="M7" s="571" t="n"/>
-      <c r="N7" s="571" t="n"/>
-      <c r="O7" s="571" t="n"/>
-      <c r="P7" s="571" t="n"/>
-      <c r="Q7" s="571" t="n"/>
-      <c r="R7" s="571" t="n"/>
-      <c r="S7" s="571" t="n"/>
-      <c r="T7" s="571" t="n"/>
-      <c r="U7" s="571" t="n"/>
-      <c r="V7" s="571" t="n"/>
-      <c r="W7" s="571" t="n"/>
-      <c r="X7" s="571" t="n"/>
-      <c r="Y7" s="571" t="n"/>
-      <c r="Z7" s="571" t="n"/>
-      <c r="AA7" s="571" t="n"/>
-      <c r="AB7" s="571" t="n"/>
-      <c r="AC7" s="571" t="n"/>
-      <c r="AD7" s="571" t="n"/>
-      <c r="AE7" s="571" t="n"/>
-      <c r="AF7" s="571" t="n"/>
-      <c r="AG7" s="571" t="n"/>
-      <c r="AH7" s="571" t="n"/>
-      <c r="AI7" s="571" t="n"/>
-      <c r="AJ7" s="571" t="n"/>
-      <c r="AK7" s="571" t="n"/>
-      <c r="AL7" s="571" t="n"/>
-      <c r="AM7" s="571" t="n"/>
-      <c r="AN7" s="571" t="n"/>
-      <c r="AO7" s="571" t="n"/>
-      <c r="AP7" s="571" t="n"/>
-      <c r="AQ7" s="571" t="n"/>
-      <c r="AR7" s="571" t="n"/>
-      <c r="AS7" s="571" t="n"/>
-      <c r="AT7" s="571" t="n"/>
-      <c r="AU7" s="571" t="n"/>
-      <c r="AV7" s="571" t="n"/>
-      <c r="AW7" s="571" t="n"/>
-      <c r="AX7" s="571" t="n"/>
-      <c r="AY7" s="571" t="n"/>
-      <c r="AZ7" s="571" t="n"/>
-      <c r="BA7" s="571" t="n"/>
-      <c r="BB7" s="571" t="n"/>
-      <c r="BC7" s="571" t="n"/>
-      <c r="BD7" s="572" t="n"/>
+    <row r="7" ht="4" customHeight="1">
+      <c r="A7" s="717" t="n"/>
+      <c r="B7" s="718" t="n"/>
+      <c r="C7" s="718" t="n"/>
+      <c r="D7" s="718" t="n"/>
+      <c r="E7" s="718" t="n"/>
+      <c r="F7" s="718" t="n"/>
+      <c r="G7" s="718" t="n"/>
+      <c r="H7" s="718" t="n"/>
+      <c r="I7" s="718" t="n"/>
+      <c r="J7" s="718" t="n"/>
+      <c r="K7" s="718" t="n"/>
+      <c r="L7" s="718" t="n"/>
+      <c r="M7" s="718" t="n"/>
+      <c r="N7" s="718" t="n"/>
+      <c r="O7" s="718" t="n"/>
+      <c r="P7" s="718" t="n"/>
+      <c r="Q7" s="718" t="n"/>
+      <c r="R7" s="718" t="n"/>
+      <c r="S7" s="718" t="n"/>
+      <c r="T7" s="718" t="n"/>
+      <c r="U7" s="718" t="n"/>
+      <c r="V7" s="718" t="n"/>
+      <c r="W7" s="718" t="n"/>
+      <c r="X7" s="718" t="n"/>
+      <c r="Y7" s="718" t="n"/>
+      <c r="Z7" s="718" t="n"/>
+      <c r="AA7" s="718" t="n"/>
+      <c r="AB7" s="718" t="n"/>
+      <c r="AC7" s="718" t="n"/>
+      <c r="AD7" s="718" t="n"/>
+      <c r="AE7" s="718" t="n"/>
+      <c r="AF7" s="718" t="n"/>
+      <c r="AG7" s="718" t="n"/>
+      <c r="AH7" s="718" t="n"/>
+      <c r="AI7" s="718" t="n"/>
+      <c r="AJ7" s="718" t="n"/>
+      <c r="AK7" s="718" t="n"/>
+      <c r="AL7" s="718" t="n"/>
+      <c r="AM7" s="718" t="n"/>
+      <c r="AN7" s="718" t="n"/>
+      <c r="AO7" s="718" t="n"/>
+      <c r="AP7" s="718" t="n"/>
+      <c r="AQ7" s="718" t="n"/>
+      <c r="AR7" s="718" t="n"/>
+      <c r="AS7" s="718" t="n"/>
+      <c r="AT7" s="718" t="n"/>
+      <c r="AU7" s="718" t="n"/>
+      <c r="AV7" s="718" t="n"/>
+      <c r="AW7" s="718" t="n"/>
+      <c r="AX7" s="718" t="n"/>
+      <c r="AY7" s="718" t="n"/>
+      <c r="AZ7" s="718" t="n"/>
+      <c r="BA7" s="718" t="n"/>
+      <c r="BB7" s="718" t="n"/>
+      <c r="BC7" s="718" t="n"/>
+      <c r="BD7" s="718" t="n"/>
     </row>
     <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="640" t="inlineStr">
+      <c r="A8" s="777" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B8" s="641" t="n"/>
-      <c r="C8" s="668" t="inlineStr">
+      <c r="B8" s="327" t="n"/>
+      <c r="C8" s="778" t="inlineStr">
         <is>
           <t>Condition / Exception</t>
         </is>
       </c>
-      <c r="D8" s="669" t="n"/>
-      <c r="E8" s="669" t="n"/>
-      <c r="F8" s="669" t="n"/>
-      <c r="G8" s="669" t="n"/>
-      <c r="H8" s="669" t="n"/>
-      <c r="I8" s="669" t="n"/>
-      <c r="J8" s="669" t="n"/>
-      <c r="K8" s="669" t="n"/>
-      <c r="L8" s="669" t="n"/>
-      <c r="M8" s="669" t="n"/>
-      <c r="N8" s="669" t="n"/>
-      <c r="O8" s="669" t="n"/>
-      <c r="P8" s="670" t="n"/>
-      <c r="Q8" s="642" t="inlineStr">
+      <c r="D8" s="803" t="n"/>
+      <c r="E8" s="803" t="n"/>
+      <c r="F8" s="803" t="n"/>
+      <c r="G8" s="803" t="n"/>
+      <c r="H8" s="803" t="n"/>
+      <c r="I8" s="803" t="n"/>
+      <c r="J8" s="803" t="n"/>
+      <c r="K8" s="803" t="n"/>
+      <c r="L8" s="803" t="n"/>
+      <c r="M8" s="803" t="n"/>
+      <c r="N8" s="803" t="n"/>
+      <c r="O8" s="803" t="n"/>
+      <c r="P8" s="804" t="n"/>
+      <c r="Q8" s="779" t="inlineStr">
         <is>
           <t>Required Action</t>
         </is>
       </c>
-      <c r="R8" s="571" t="n"/>
-      <c r="S8" s="571" t="n"/>
-      <c r="T8" s="571" t="n"/>
-      <c r="U8" s="571" t="n"/>
-      <c r="V8" s="571" t="n"/>
-      <c r="W8" s="571" t="n"/>
-      <c r="X8" s="571" t="n"/>
-      <c r="Y8" s="571" t="n"/>
-      <c r="Z8" s="571" t="n"/>
-      <c r="AA8" s="571" t="n"/>
-      <c r="AB8" s="571" t="n"/>
-      <c r="AC8" s="571" t="n"/>
-      <c r="AD8" s="571" t="n"/>
-      <c r="AE8" s="571" t="n"/>
-      <c r="AF8" s="571" t="n"/>
-      <c r="AG8" s="641" t="n"/>
-      <c r="AH8" s="642" t="inlineStr">
+      <c r="R8" s="285" t="n"/>
+      <c r="S8" s="285" t="n"/>
+      <c r="T8" s="285" t="n"/>
+      <c r="U8" s="285" t="n"/>
+      <c r="V8" s="285" t="n"/>
+      <c r="W8" s="285" t="n"/>
+      <c r="X8" s="285" t="n"/>
+      <c r="Y8" s="285" t="n"/>
+      <c r="Z8" s="285" t="n"/>
+      <c r="AA8" s="285" t="n"/>
+      <c r="AB8" s="285" t="n"/>
+      <c r="AC8" s="285" t="n"/>
+      <c r="AD8" s="285" t="n"/>
+      <c r="AE8" s="285" t="n"/>
+      <c r="AF8" s="285" t="n"/>
+      <c r="AG8" s="327" t="n"/>
+      <c r="AH8" s="779" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="AI8" s="571" t="n"/>
-      <c r="AJ8" s="571" t="n"/>
-      <c r="AK8" s="571" t="n"/>
-      <c r="AL8" s="571" t="n"/>
-      <c r="AM8" s="571" t="n"/>
-      <c r="AN8" s="641" t="n"/>
-      <c r="AO8" s="642" t="inlineStr">
+      <c r="AI8" s="285" t="n"/>
+      <c r="AJ8" s="285" t="n"/>
+      <c r="AK8" s="285" t="n"/>
+      <c r="AL8" s="285" t="n"/>
+      <c r="AM8" s="285" t="n"/>
+      <c r="AN8" s="327" t="n"/>
+      <c r="AO8" s="779" t="inlineStr">
         <is>
           <t>Due Date</t>
         </is>
       </c>
-      <c r="AP8" s="571" t="n"/>
-      <c r="AQ8" s="571" t="n"/>
-      <c r="AR8" s="571" t="n"/>
-      <c r="AS8" s="571" t="n"/>
-      <c r="AT8" s="571" t="n"/>
-      <c r="AU8" s="641" t="n"/>
-      <c r="AV8" s="642" t="inlineStr">
+      <c r="AP8" s="285" t="n"/>
+      <c r="AQ8" s="285" t="n"/>
+      <c r="AR8" s="285" t="n"/>
+      <c r="AS8" s="285" t="n"/>
+      <c r="AT8" s="285" t="n"/>
+      <c r="AU8" s="327" t="n"/>
+      <c r="AV8" s="779" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="AW8" s="571" t="n"/>
-      <c r="AX8" s="571" t="n"/>
-      <c r="AY8" s="641" t="n"/>
-      <c r="AZ8" s="643" t="inlineStr">
+      <c r="AW8" s="285" t="n"/>
+      <c r="AX8" s="285" t="n"/>
+      <c r="AY8" s="327" t="n"/>
+      <c r="AZ8" s="780" t="inlineStr">
         <is>
           <t>Verified by</t>
         </is>
       </c>
-      <c r="BA8" s="571" t="n"/>
-      <c r="BB8" s="571" t="n"/>
-      <c r="BC8" s="571" t="n"/>
-      <c r="BD8" s="572" t="n"/>
+      <c r="BA8" s="285" t="n"/>
+      <c r="BB8" s="285" t="n"/>
+      <c r="BC8" s="285" t="n"/>
+      <c r="BD8" s="286" t="n"/>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="671">
+      <c r="A9" s="781">
         <f>ROW()-ROW($A$9)+1</f>
         <v/>
       </c>
-      <c r="B9" s="424" t="n"/>
-      <c r="C9" s="645" t="n"/>
-      <c r="D9" s="577" t="n"/>
-      <c r="E9" s="577" t="n"/>
-      <c r="F9" s="577" t="n"/>
-      <c r="G9" s="577" t="n"/>
-      <c r="H9" s="577" t="n"/>
-      <c r="I9" s="577" t="n"/>
-      <c r="J9" s="577" t="n"/>
-      <c r="K9" s="577" t="n"/>
-      <c r="L9" s="577" t="n"/>
-      <c r="M9" s="577" t="n"/>
-      <c r="N9" s="577" t="n"/>
-      <c r="O9" s="577" t="n"/>
-      <c r="P9" s="646" t="n"/>
-      <c r="Q9" s="647" t="n"/>
-      <c r="R9" s="423" t="n"/>
-      <c r="S9" s="423" t="n"/>
-      <c r="T9" s="423" t="n"/>
-      <c r="U9" s="423" t="n"/>
-      <c r="V9" s="423" t="n"/>
-      <c r="W9" s="423" t="n"/>
-      <c r="X9" s="423" t="n"/>
-      <c r="Y9" s="423" t="n"/>
-      <c r="Z9" s="423" t="n"/>
-      <c r="AA9" s="423" t="n"/>
-      <c r="AB9" s="423" t="n"/>
-      <c r="AC9" s="423" t="n"/>
-      <c r="AD9" s="423" t="n"/>
-      <c r="AE9" s="423" t="n"/>
-      <c r="AF9" s="423" t="n"/>
-      <c r="AG9" s="424" t="n"/>
-      <c r="AH9" s="647" t="n"/>
-      <c r="AI9" s="423" t="n"/>
-      <c r="AJ9" s="423" t="n"/>
-      <c r="AK9" s="423" t="n"/>
-      <c r="AL9" s="423" t="n"/>
-      <c r="AM9" s="423" t="n"/>
-      <c r="AN9" s="424" t="n"/>
-      <c r="AO9" s="647" t="n"/>
-      <c r="AP9" s="423" t="n"/>
-      <c r="AQ9" s="423" t="n"/>
-      <c r="AR9" s="423" t="n"/>
-      <c r="AS9" s="423" t="n"/>
-      <c r="AT9" s="423" t="n"/>
-      <c r="AU9" s="424" t="n"/>
-      <c r="AV9" s="647" t="n"/>
-      <c r="AW9" s="423" t="n"/>
-      <c r="AX9" s="423" t="n"/>
-      <c r="AY9" s="424" t="n"/>
-      <c r="AZ9" s="648" t="n"/>
-      <c r="BA9" s="423" t="n"/>
-      <c r="BB9" s="423" t="n"/>
-      <c r="BC9" s="423" t="n"/>
-      <c r="BD9" s="649" t="n"/>
+      <c r="B9" s="805" t="n"/>
+      <c r="C9" s="782" t="n"/>
+      <c r="D9" s="793" t="n"/>
+      <c r="E9" s="793" t="n"/>
+      <c r="F9" s="793" t="n"/>
+      <c r="G9" s="793" t="n"/>
+      <c r="H9" s="793" t="n"/>
+      <c r="I9" s="793" t="n"/>
+      <c r="J9" s="793" t="n"/>
+      <c r="K9" s="793" t="n"/>
+      <c r="L9" s="793" t="n"/>
+      <c r="M9" s="793" t="n"/>
+      <c r="N9" s="793" t="n"/>
+      <c r="O9" s="793" t="n"/>
+      <c r="P9" s="806" t="n"/>
+      <c r="Q9" s="783" t="n"/>
+      <c r="R9" s="792" t="n"/>
+      <c r="S9" s="792" t="n"/>
+      <c r="T9" s="792" t="n"/>
+      <c r="U9" s="792" t="n"/>
+      <c r="V9" s="792" t="n"/>
+      <c r="W9" s="792" t="n"/>
+      <c r="X9" s="792" t="n"/>
+      <c r="Y9" s="792" t="n"/>
+      <c r="Z9" s="792" t="n"/>
+      <c r="AA9" s="792" t="n"/>
+      <c r="AB9" s="792" t="n"/>
+      <c r="AC9" s="792" t="n"/>
+      <c r="AD9" s="792" t="n"/>
+      <c r="AE9" s="792" t="n"/>
+      <c r="AF9" s="792" t="n"/>
+      <c r="AG9" s="805" t="n"/>
+      <c r="AH9" s="783" t="n"/>
+      <c r="AI9" s="792" t="n"/>
+      <c r="AJ9" s="792" t="n"/>
+      <c r="AK9" s="792" t="n"/>
+      <c r="AL9" s="792" t="n"/>
+      <c r="AM9" s="792" t="n"/>
+      <c r="AN9" s="805" t="n"/>
+      <c r="AO9" s="783" t="n"/>
+      <c r="AP9" s="792" t="n"/>
+      <c r="AQ9" s="792" t="n"/>
+      <c r="AR9" s="792" t="n"/>
+      <c r="AS9" s="792" t="n"/>
+      <c r="AT9" s="792" t="n"/>
+      <c r="AU9" s="805" t="n"/>
+      <c r="AV9" s="783" t="n"/>
+      <c r="AW9" s="792" t="n"/>
+      <c r="AX9" s="792" t="n"/>
+      <c r="AY9" s="805" t="n"/>
+      <c r="AZ9" s="784" t="n"/>
+      <c r="BA9" s="792" t="n"/>
+      <c r="BB9" s="792" t="n"/>
+      <c r="BC9" s="792" t="n"/>
+      <c r="BD9" s="807" t="n"/>
     </row>
     <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="672">
+      <c r="A10" s="785">
         <f>ROW()-ROW($A$9)+1</f>
         <v/>
       </c>
-      <c r="B10" s="424" t="n"/>
-      <c r="C10" s="651" t="n"/>
-      <c r="D10" s="577" t="n"/>
-      <c r="E10" s="577" t="n"/>
-      <c r="F10" s="577" t="n"/>
-      <c r="G10" s="577" t="n"/>
-      <c r="H10" s="577" t="n"/>
-      <c r="I10" s="577" t="n"/>
-      <c r="J10" s="577" t="n"/>
-      <c r="K10" s="577" t="n"/>
-      <c r="L10" s="577" t="n"/>
-      <c r="M10" s="577" t="n"/>
-      <c r="N10" s="577" t="n"/>
-      <c r="O10" s="577" t="n"/>
-      <c r="P10" s="646" t="n"/>
-      <c r="Q10" s="652" t="n"/>
-      <c r="R10" s="423" t="n"/>
-      <c r="S10" s="423" t="n"/>
-      <c r="T10" s="423" t="n"/>
-      <c r="U10" s="423" t="n"/>
-      <c r="V10" s="423" t="n"/>
-      <c r="W10" s="423" t="n"/>
-      <c r="X10" s="423" t="n"/>
-      <c r="Y10" s="423" t="n"/>
-      <c r="Z10" s="423" t="n"/>
-      <c r="AA10" s="423" t="n"/>
-      <c r="AB10" s="423" t="n"/>
-      <c r="AC10" s="423" t="n"/>
-      <c r="AD10" s="423" t="n"/>
-      <c r="AE10" s="423" t="n"/>
-      <c r="AF10" s="423" t="n"/>
-      <c r="AG10" s="424" t="n"/>
-      <c r="AH10" s="652" t="n"/>
-      <c r="AI10" s="423" t="n"/>
-      <c r="AJ10" s="423" t="n"/>
-      <c r="AK10" s="423" t="n"/>
-      <c r="AL10" s="423" t="n"/>
-      <c r="AM10" s="423" t="n"/>
-      <c r="AN10" s="424" t="n"/>
-      <c r="AO10" s="652" t="n"/>
-      <c r="AP10" s="423" t="n"/>
-      <c r="AQ10" s="423" t="n"/>
-      <c r="AR10" s="423" t="n"/>
-      <c r="AS10" s="423" t="n"/>
-      <c r="AT10" s="423" t="n"/>
-      <c r="AU10" s="424" t="n"/>
-      <c r="AV10" s="652" t="n"/>
-      <c r="AW10" s="423" t="n"/>
-      <c r="AX10" s="423" t="n"/>
-      <c r="AY10" s="424" t="n"/>
-      <c r="AZ10" s="653" t="n"/>
-      <c r="BA10" s="423" t="n"/>
-      <c r="BB10" s="423" t="n"/>
-      <c r="BC10" s="423" t="n"/>
-      <c r="BD10" s="649" t="n"/>
+      <c r="B10" s="805" t="n"/>
+      <c r="C10" s="786" t="n"/>
+      <c r="D10" s="793" t="n"/>
+      <c r="E10" s="793" t="n"/>
+      <c r="F10" s="793" t="n"/>
+      <c r="G10" s="793" t="n"/>
+      <c r="H10" s="793" t="n"/>
+      <c r="I10" s="793" t="n"/>
+      <c r="J10" s="793" t="n"/>
+      <c r="K10" s="793" t="n"/>
+      <c r="L10" s="793" t="n"/>
+      <c r="M10" s="793" t="n"/>
+      <c r="N10" s="793" t="n"/>
+      <c r="O10" s="793" t="n"/>
+      <c r="P10" s="806" t="n"/>
+      <c r="Q10" s="787" t="n"/>
+      <c r="R10" s="792" t="n"/>
+      <c r="S10" s="792" t="n"/>
+      <c r="T10" s="792" t="n"/>
+      <c r="U10" s="792" t="n"/>
+      <c r="V10" s="792" t="n"/>
+      <c r="W10" s="792" t="n"/>
+      <c r="X10" s="792" t="n"/>
+      <c r="Y10" s="792" t="n"/>
+      <c r="Z10" s="792" t="n"/>
+      <c r="AA10" s="792" t="n"/>
+      <c r="AB10" s="792" t="n"/>
+      <c r="AC10" s="792" t="n"/>
+      <c r="AD10" s="792" t="n"/>
+      <c r="AE10" s="792" t="n"/>
+      <c r="AF10" s="792" t="n"/>
+      <c r="AG10" s="805" t="n"/>
+      <c r="AH10" s="787" t="n"/>
+      <c r="AI10" s="792" t="n"/>
+      <c r="AJ10" s="792" t="n"/>
+      <c r="AK10" s="792" t="n"/>
+      <c r="AL10" s="792" t="n"/>
+      <c r="AM10" s="792" t="n"/>
+      <c r="AN10" s="805" t="n"/>
+      <c r="AO10" s="787" t="n"/>
+      <c r="AP10" s="792" t="n"/>
+      <c r="AQ10" s="792" t="n"/>
+      <c r="AR10" s="792" t="n"/>
+      <c r="AS10" s="792" t="n"/>
+      <c r="AT10" s="792" t="n"/>
+      <c r="AU10" s="805" t="n"/>
+      <c r="AV10" s="787" t="n"/>
+      <c r="AW10" s="792" t="n"/>
+      <c r="AX10" s="792" t="n"/>
+      <c r="AY10" s="805" t="n"/>
+      <c r="AZ10" s="788" t="n"/>
+      <c r="BA10" s="792" t="n"/>
+      <c r="BB10" s="792" t="n"/>
+      <c r="BC10" s="792" t="n"/>
+      <c r="BD10" s="807" t="n"/>
     </row>
     <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="671">
+      <c r="A11" s="781">
         <f>ROW()-ROW($A$9)+1</f>
         <v/>
       </c>
-      <c r="B11" s="424" t="n"/>
-      <c r="C11" s="645" t="n"/>
-      <c r="D11" s="577" t="n"/>
-      <c r="E11" s="577" t="n"/>
-      <c r="F11" s="577" t="n"/>
-      <c r="G11" s="577" t="n"/>
-      <c r="H11" s="577" t="n"/>
-      <c r="I11" s="577" t="n"/>
-      <c r="J11" s="577" t="n"/>
-      <c r="K11" s="577" t="n"/>
-      <c r="L11" s="577" t="n"/>
-      <c r="M11" s="577" t="n"/>
-      <c r="N11" s="577" t="n"/>
-      <c r="O11" s="577" t="n"/>
-      <c r="P11" s="646" t="n"/>
-      <c r="Q11" s="647" t="n"/>
-      <c r="R11" s="423" t="n"/>
-      <c r="S11" s="423" t="n"/>
-      <c r="T11" s="423" t="n"/>
-      <c r="U11" s="423" t="n"/>
-      <c r="V11" s="423" t="n"/>
-      <c r="W11" s="423" t="n"/>
-      <c r="X11" s="423" t="n"/>
-      <c r="Y11" s="423" t="n"/>
-      <c r="Z11" s="423" t="n"/>
-      <c r="AA11" s="423" t="n"/>
-      <c r="AB11" s="423" t="n"/>
-      <c r="AC11" s="423" t="n"/>
-      <c r="AD11" s="423" t="n"/>
-      <c r="AE11" s="423" t="n"/>
-      <c r="AF11" s="423" t="n"/>
-      <c r="AG11" s="424" t="n"/>
-      <c r="AH11" s="647" t="n"/>
-      <c r="AI11" s="423" t="n"/>
-      <c r="AJ11" s="423" t="n"/>
-      <c r="AK11" s="423" t="n"/>
-      <c r="AL11" s="423" t="n"/>
-      <c r="AM11" s="423" t="n"/>
-      <c r="AN11" s="424" t="n"/>
-      <c r="AO11" s="647" t="n"/>
-      <c r="AP11" s="423" t="n"/>
-      <c r="AQ11" s="423" t="n"/>
-      <c r="AR11" s="423" t="n"/>
-      <c r="AS11" s="423" t="n"/>
-      <c r="AT11" s="423" t="n"/>
-      <c r="AU11" s="424" t="n"/>
-      <c r="AV11" s="647" t="n"/>
-      <c r="AW11" s="423" t="n"/>
-      <c r="AX11" s="423" t="n"/>
-      <c r="AY11" s="424" t="n"/>
-      <c r="AZ11" s="648" t="n"/>
-      <c r="BA11" s="423" t="n"/>
-      <c r="BB11" s="423" t="n"/>
-      <c r="BC11" s="423" t="n"/>
-      <c r="BD11" s="649" t="n"/>
+      <c r="B11" s="805" t="n"/>
+      <c r="C11" s="782" t="n"/>
+      <c r="D11" s="793" t="n"/>
+      <c r="E11" s="793" t="n"/>
+      <c r="F11" s="793" t="n"/>
+      <c r="G11" s="793" t="n"/>
+      <c r="H11" s="793" t="n"/>
+      <c r="I11" s="793" t="n"/>
+      <c r="J11" s="793" t="n"/>
+      <c r="K11" s="793" t="n"/>
+      <c r="L11" s="793" t="n"/>
+      <c r="M11" s="793" t="n"/>
+      <c r="N11" s="793" t="n"/>
+      <c r="O11" s="793" t="n"/>
+      <c r="P11" s="806" t="n"/>
+      <c r="Q11" s="783" t="n"/>
+      <c r="R11" s="792" t="n"/>
+      <c r="S11" s="792" t="n"/>
+      <c r="T11" s="792" t="n"/>
+      <c r="U11" s="792" t="n"/>
+      <c r="V11" s="792" t="n"/>
+      <c r="W11" s="792" t="n"/>
+      <c r="X11" s="792" t="n"/>
+      <c r="Y11" s="792" t="n"/>
+      <c r="Z11" s="792" t="n"/>
+      <c r="AA11" s="792" t="n"/>
+      <c r="AB11" s="792" t="n"/>
+      <c r="AC11" s="792" t="n"/>
+      <c r="AD11" s="792" t="n"/>
+      <c r="AE11" s="792" t="n"/>
+      <c r="AF11" s="792" t="n"/>
+      <c r="AG11" s="805" t="n"/>
+      <c r="AH11" s="783" t="n"/>
+      <c r="AI11" s="792" t="n"/>
+      <c r="AJ11" s="792" t="n"/>
+      <c r="AK11" s="792" t="n"/>
+      <c r="AL11" s="792" t="n"/>
+      <c r="AM11" s="792" t="n"/>
+      <c r="AN11" s="805" t="n"/>
+      <c r="AO11" s="783" t="n"/>
+      <c r="AP11" s="792" t="n"/>
+      <c r="AQ11" s="792" t="n"/>
+      <c r="AR11" s="792" t="n"/>
+      <c r="AS11" s="792" t="n"/>
+      <c r="AT11" s="792" t="n"/>
+      <c r="AU11" s="805" t="n"/>
+      <c r="AV11" s="783" t="n"/>
+      <c r="AW11" s="792" t="n"/>
+      <c r="AX11" s="792" t="n"/>
+      <c r="AY11" s="805" t="n"/>
+      <c r="AZ11" s="784" t="n"/>
+      <c r="BA11" s="792" t="n"/>
+      <c r="BB11" s="792" t="n"/>
+      <c r="BC11" s="792" t="n"/>
+      <c r="BD11" s="807" t="n"/>
     </row>
     <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="672">
+      <c r="A12" s="785">
         <f>ROW()-ROW($A$9)+1</f>
         <v/>
       </c>
-      <c r="B12" s="424" t="n"/>
-      <c r="C12" s="651" t="n"/>
-      <c r="D12" s="577" t="n"/>
-      <c r="E12" s="577" t="n"/>
-      <c r="F12" s="577" t="n"/>
-      <c r="G12" s="577" t="n"/>
-      <c r="H12" s="577" t="n"/>
-      <c r="I12" s="577" t="n"/>
-      <c r="J12" s="577" t="n"/>
-      <c r="K12" s="577" t="n"/>
-      <c r="L12" s="577" t="n"/>
-      <c r="M12" s="577" t="n"/>
-      <c r="N12" s="577" t="n"/>
-      <c r="O12" s="577" t="n"/>
-      <c r="P12" s="646" t="n"/>
-      <c r="Q12" s="652" t="n"/>
-      <c r="R12" s="423" t="n"/>
-      <c r="S12" s="423" t="n"/>
-      <c r="T12" s="423" t="n"/>
-      <c r="U12" s="423" t="n"/>
-      <c r="V12" s="423" t="n"/>
-      <c r="W12" s="423" t="n"/>
-      <c r="X12" s="423" t="n"/>
-      <c r="Y12" s="423" t="n"/>
-      <c r="Z12" s="423" t="n"/>
-      <c r="AA12" s="423" t="n"/>
-      <c r="AB12" s="423" t="n"/>
-      <c r="AC12" s="423" t="n"/>
-      <c r="AD12" s="423" t="n"/>
-      <c r="AE12" s="423" t="n"/>
-      <c r="AF12" s="423" t="n"/>
-      <c r="AG12" s="424" t="n"/>
-      <c r="AH12" s="652" t="n"/>
-      <c r="AI12" s="423" t="n"/>
-      <c r="AJ12" s="423" t="n"/>
-      <c r="AK12" s="423" t="n"/>
-      <c r="AL12" s="423" t="n"/>
-      <c r="AM12" s="423" t="n"/>
-      <c r="AN12" s="424" t="n"/>
-      <c r="AO12" s="652" t="n"/>
-      <c r="AP12" s="423" t="n"/>
-      <c r="AQ12" s="423" t="n"/>
-      <c r="AR12" s="423" t="n"/>
-      <c r="AS12" s="423" t="n"/>
-      <c r="AT12" s="423" t="n"/>
-      <c r="AU12" s="424" t="n"/>
-      <c r="AV12" s="652" t="n"/>
-      <c r="AW12" s="423" t="n"/>
-      <c r="AX12" s="423" t="n"/>
-      <c r="AY12" s="424" t="n"/>
-      <c r="AZ12" s="653" t="n"/>
-      <c r="BA12" s="423" t="n"/>
-      <c r="BB12" s="423" t="n"/>
-      <c r="BC12" s="423" t="n"/>
-      <c r="BD12" s="649" t="n"/>
+      <c r="B12" s="805" t="n"/>
+      <c r="C12" s="786" t="n"/>
+      <c r="D12" s="793" t="n"/>
+      <c r="E12" s="793" t="n"/>
+      <c r="F12" s="793" t="n"/>
+      <c r="G12" s="793" t="n"/>
+      <c r="H12" s="793" t="n"/>
+      <c r="I12" s="793" t="n"/>
+      <c r="J12" s="793" t="n"/>
+      <c r="K12" s="793" t="n"/>
+      <c r="L12" s="793" t="n"/>
+      <c r="M12" s="793" t="n"/>
+      <c r="N12" s="793" t="n"/>
+      <c r="O12" s="793" t="n"/>
+      <c r="P12" s="806" t="n"/>
+      <c r="Q12" s="787" t="n"/>
+      <c r="R12" s="792" t="n"/>
+      <c r="S12" s="792" t="n"/>
+      <c r="T12" s="792" t="n"/>
+      <c r="U12" s="792" t="n"/>
+      <c r="V12" s="792" t="n"/>
+      <c r="W12" s="792" t="n"/>
+      <c r="X12" s="792" t="n"/>
+      <c r="Y12" s="792" t="n"/>
+      <c r="Z12" s="792" t="n"/>
+      <c r="AA12" s="792" t="n"/>
+      <c r="AB12" s="792" t="n"/>
+      <c r="AC12" s="792" t="n"/>
+      <c r="AD12" s="792" t="n"/>
+      <c r="AE12" s="792" t="n"/>
+      <c r="AF12" s="792" t="n"/>
+      <c r="AG12" s="805" t="n"/>
+      <c r="AH12" s="787" t="n"/>
+      <c r="AI12" s="792" t="n"/>
+      <c r="AJ12" s="792" t="n"/>
+      <c r="AK12" s="792" t="n"/>
+      <c r="AL12" s="792" t="n"/>
+      <c r="AM12" s="792" t="n"/>
+      <c r="AN12" s="805" t="n"/>
+      <c r="AO12" s="787" t="n"/>
+      <c r="AP12" s="792" t="n"/>
+      <c r="AQ12" s="792" t="n"/>
+      <c r="AR12" s="792" t="n"/>
+      <c r="AS12" s="792" t="n"/>
+      <c r="AT12" s="792" t="n"/>
+      <c r="AU12" s="805" t="n"/>
+      <c r="AV12" s="787" t="n"/>
+      <c r="AW12" s="792" t="n"/>
+      <c r="AX12" s="792" t="n"/>
+      <c r="AY12" s="805" t="n"/>
+      <c r="AZ12" s="788" t="n"/>
+      <c r="BA12" s="792" t="n"/>
+      <c r="BB12" s="792" t="n"/>
+      <c r="BC12" s="792" t="n"/>
+      <c r="BD12" s="807" t="n"/>
     </row>
     <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="671">
+      <c r="A13" s="781">
         <f>ROW()-ROW($A$9)+1</f>
         <v/>
       </c>
-      <c r="B13" s="424" t="n"/>
-      <c r="C13" s="645" t="n"/>
-      <c r="D13" s="577" t="n"/>
-      <c r="E13" s="577" t="n"/>
-      <c r="F13" s="577" t="n"/>
-      <c r="G13" s="577" t="n"/>
-      <c r="H13" s="577" t="n"/>
-      <c r="I13" s="577" t="n"/>
-      <c r="J13" s="577" t="n"/>
-      <c r="K13" s="577" t="n"/>
-      <c r="L13" s="577" t="n"/>
-      <c r="M13" s="577" t="n"/>
-      <c r="N13" s="577" t="n"/>
-      <c r="O13" s="577" t="n"/>
-      <c r="P13" s="646" t="n"/>
-      <c r="Q13" s="647" t="n"/>
-      <c r="R13" s="423" t="n"/>
-      <c r="S13" s="423" t="n"/>
-      <c r="T13" s="423" t="n"/>
-      <c r="U13" s="423" t="n"/>
-      <c r="V13" s="423" t="n"/>
-      <c r="W13" s="423" t="n"/>
-      <c r="X13" s="423" t="n"/>
-      <c r="Y13" s="423" t="n"/>
-      <c r="Z13" s="423" t="n"/>
-      <c r="AA13" s="423" t="n"/>
-      <c r="AB13" s="423" t="n"/>
-      <c r="AC13" s="423" t="n"/>
-      <c r="AD13" s="423" t="n"/>
-      <c r="AE13" s="423" t="n"/>
-      <c r="AF13" s="423" t="n"/>
-      <c r="AG13" s="424" t="n"/>
-      <c r="AH13" s="647" t="n"/>
-      <c r="AI13" s="423" t="n"/>
-      <c r="AJ13" s="423" t="n"/>
-      <c r="AK13" s="423" t="n"/>
-      <c r="AL13" s="423" t="n"/>
-      <c r="AM13" s="423" t="n"/>
-      <c r="AN13" s="424" t="n"/>
-      <c r="AO13" s="647" t="n"/>
-      <c r="AP13" s="423" t="n"/>
-      <c r="AQ13" s="423" t="n"/>
-      <c r="AR13" s="423" t="n"/>
-      <c r="AS13" s="423" t="n"/>
-      <c r="AT13" s="423" t="n"/>
-      <c r="AU13" s="424" t="n"/>
-      <c r="AV13" s="647" t="n"/>
-      <c r="AW13" s="423" t="n"/>
-      <c r="AX13" s="423" t="n"/>
-      <c r="AY13" s="424" t="n"/>
-      <c r="AZ13" s="648" t="n"/>
-      <c r="BA13" s="423" t="n"/>
-      <c r="BB13" s="423" t="n"/>
-      <c r="BC13" s="423" t="n"/>
-      <c r="BD13" s="649" t="n"/>
+      <c r="B13" s="805" t="n"/>
+      <c r="C13" s="782" t="n"/>
+      <c r="D13" s="793" t="n"/>
+      <c r="E13" s="793" t="n"/>
+      <c r="F13" s="793" t="n"/>
+      <c r="G13" s="793" t="n"/>
+      <c r="H13" s="793" t="n"/>
+      <c r="I13" s="793" t="n"/>
+      <c r="J13" s="793" t="n"/>
+      <c r="K13" s="793" t="n"/>
+      <c r="L13" s="793" t="n"/>
+      <c r="M13" s="793" t="n"/>
+      <c r="N13" s="793" t="n"/>
+      <c r="O13" s="793" t="n"/>
+      <c r="P13" s="806" t="n"/>
+      <c r="Q13" s="783" t="n"/>
+      <c r="R13" s="792" t="n"/>
+      <c r="S13" s="792" t="n"/>
+      <c r="T13" s="792" t="n"/>
+      <c r="U13" s="792" t="n"/>
+      <c r="V13" s="792" t="n"/>
+      <c r="W13" s="792" t="n"/>
+      <c r="X13" s="792" t="n"/>
+      <c r="Y13" s="792" t="n"/>
+      <c r="Z13" s="792" t="n"/>
+      <c r="AA13" s="792" t="n"/>
+      <c r="AB13" s="792" t="n"/>
+      <c r="AC13" s="792" t="n"/>
+      <c r="AD13" s="792" t="n"/>
+      <c r="AE13" s="792" t="n"/>
+      <c r="AF13" s="792" t="n"/>
+      <c r="AG13" s="805" t="n"/>
+      <c r="AH13" s="783" t="n"/>
+      <c r="AI13" s="792" t="n"/>
+      <c r="AJ13" s="792" t="n"/>
+      <c r="AK13" s="792" t="n"/>
+      <c r="AL13" s="792" t="n"/>
+      <c r="AM13" s="792" t="n"/>
+      <c r="AN13" s="805" t="n"/>
+      <c r="AO13" s="783" t="n"/>
+      <c r="AP13" s="792" t="n"/>
+      <c r="AQ13" s="792" t="n"/>
+      <c r="AR13" s="792" t="n"/>
+      <c r="AS13" s="792" t="n"/>
+      <c r="AT13" s="792" t="n"/>
+      <c r="AU13" s="805" t="n"/>
+      <c r="AV13" s="783" t="n"/>
+      <c r="AW13" s="792" t="n"/>
+      <c r="AX13" s="792" t="n"/>
+      <c r="AY13" s="805" t="n"/>
+      <c r="AZ13" s="784" t="n"/>
+      <c r="BA13" s="792" t="n"/>
+      <c r="BB13" s="792" t="n"/>
+      <c r="BC13" s="792" t="n"/>
+      <c r="BD13" s="807" t="n"/>
     </row>
     <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="672">
+      <c r="A14" s="785">
         <f>ROW()-ROW($A$9)+1</f>
         <v/>
       </c>
-      <c r="B14" s="424" t="n"/>
-      <c r="C14" s="651" t="n"/>
-      <c r="D14" s="577" t="n"/>
-      <c r="E14" s="577" t="n"/>
-      <c r="F14" s="577" t="n"/>
-      <c r="G14" s="577" t="n"/>
-      <c r="H14" s="577" t="n"/>
-      <c r="I14" s="577" t="n"/>
-      <c r="J14" s="577" t="n"/>
-      <c r="K14" s="577" t="n"/>
-      <c r="L14" s="577" t="n"/>
-      <c r="M14" s="577" t="n"/>
-      <c r="N14" s="577" t="n"/>
-      <c r="O14" s="577" t="n"/>
-      <c r="P14" s="646" t="n"/>
-      <c r="Q14" s="652" t="n"/>
-      <c r="R14" s="423" t="n"/>
-      <c r="S14" s="423" t="n"/>
-      <c r="T14" s="423" t="n"/>
-      <c r="U14" s="423" t="n"/>
-      <c r="V14" s="423" t="n"/>
-      <c r="W14" s="423" t="n"/>
-      <c r="X14" s="423" t="n"/>
-      <c r="Y14" s="423" t="n"/>
-      <c r="Z14" s="423" t="n"/>
-      <c r="AA14" s="423" t="n"/>
-      <c r="AB14" s="423" t="n"/>
-      <c r="AC14" s="423" t="n"/>
-      <c r="AD14" s="423" t="n"/>
-      <c r="AE14" s="423" t="n"/>
-      <c r="AF14" s="423" t="n"/>
-      <c r="AG14" s="424" t="n"/>
-      <c r="AH14" s="652" t="n"/>
-      <c r="AI14" s="423" t="n"/>
-      <c r="AJ14" s="423" t="n"/>
-      <c r="AK14" s="423" t="n"/>
-      <c r="AL14" s="423" t="n"/>
-      <c r="AM14" s="423" t="n"/>
-      <c r="AN14" s="424" t="n"/>
-      <c r="AO14" s="652" t="n"/>
-      <c r="AP14" s="423" t="n"/>
-      <c r="AQ14" s="423" t="n"/>
-      <c r="AR14" s="423" t="n"/>
-      <c r="AS14" s="423" t="n"/>
-      <c r="AT14" s="423" t="n"/>
-      <c r="AU14" s="424" t="n"/>
-      <c r="AV14" s="652" t="n"/>
-      <c r="AW14" s="423" t="n"/>
-      <c r="AX14" s="423" t="n"/>
-      <c r="AY14" s="424" t="n"/>
-      <c r="AZ14" s="653" t="n"/>
-      <c r="BA14" s="423" t="n"/>
-      <c r="BB14" s="423" t="n"/>
-      <c r="BC14" s="423" t="n"/>
-      <c r="BD14" s="649" t="n"/>
+      <c r="B14" s="805" t="n"/>
+      <c r="C14" s="786" t="n"/>
+      <c r="D14" s="793" t="n"/>
+      <c r="E14" s="793" t="n"/>
+      <c r="F14" s="793" t="n"/>
+      <c r="G14" s="793" t="n"/>
+      <c r="H14" s="793" t="n"/>
+      <c r="I14" s="793" t="n"/>
+      <c r="J14" s="793" t="n"/>
+      <c r="K14" s="793" t="n"/>
+      <c r="L14" s="793" t="n"/>
+      <c r="M14" s="793" t="n"/>
+      <c r="N14" s="793" t="n"/>
+      <c r="O14" s="793" t="n"/>
+      <c r="P14" s="806" t="n"/>
+      <c r="Q14" s="787" t="n"/>
+      <c r="R14" s="792" t="n"/>
+      <c r="S14" s="792" t="n"/>
+      <c r="T14" s="792" t="n"/>
+      <c r="U14" s="792" t="n"/>
+      <c r="V14" s="792" t="n"/>
+      <c r="W14" s="792" t="n"/>
+      <c r="X14" s="792" t="n"/>
+      <c r="Y14" s="792" t="n"/>
+      <c r="Z14" s="792" t="n"/>
+      <c r="AA14" s="792" t="n"/>
+      <c r="AB14" s="792" t="n"/>
+      <c r="AC14" s="792" t="n"/>
+      <c r="AD14" s="792" t="n"/>
+      <c r="AE14" s="792" t="n"/>
+      <c r="AF14" s="792" t="n"/>
+      <c r="AG14" s="805" t="n"/>
+      <c r="AH14" s="787" t="n"/>
+      <c r="AI14" s="792" t="n"/>
+      <c r="AJ14" s="792" t="n"/>
+      <c r="AK14" s="792" t="n"/>
+      <c r="AL14" s="792" t="n"/>
+      <c r="AM14" s="792" t="n"/>
+      <c r="AN14" s="805" t="n"/>
+      <c r="AO14" s="787" t="n"/>
+      <c r="AP14" s="792" t="n"/>
+      <c r="AQ14" s="792" t="n"/>
+      <c r="AR14" s="792" t="n"/>
+      <c r="AS14" s="792" t="n"/>
+      <c r="AT14" s="792" t="n"/>
+      <c r="AU14" s="805" t="n"/>
+      <c r="AV14" s="787" t="n"/>
+      <c r="AW14" s="792" t="n"/>
+      <c r="AX14" s="792" t="n"/>
+      <c r="AY14" s="805" t="n"/>
+      <c r="AZ14" s="788" t="n"/>
+      <c r="BA14" s="792" t="n"/>
+      <c r="BB14" s="792" t="n"/>
+      <c r="BC14" s="792" t="n"/>
+      <c r="BD14" s="807" t="n"/>
     </row>
     <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="671">
+      <c r="A15" s="781">
         <f>ROW()-ROW($A$9)+1</f>
         <v/>
       </c>
-      <c r="B15" s="424" t="n"/>
-      <c r="C15" s="647" t="n"/>
-      <c r="D15" s="423" t="n"/>
-      <c r="E15" s="423" t="n"/>
-      <c r="F15" s="423" t="n"/>
-      <c r="G15" s="423" t="n"/>
-      <c r="H15" s="423" t="n"/>
-      <c r="I15" s="423" t="n"/>
-      <c r="J15" s="423" t="n"/>
-      <c r="K15" s="423" t="n"/>
-      <c r="L15" s="423" t="n"/>
-      <c r="M15" s="423" t="n"/>
-      <c r="N15" s="423" t="n"/>
-      <c r="O15" s="423" t="n"/>
-      <c r="P15" s="424" t="n"/>
-      <c r="Q15" s="647" t="n"/>
-      <c r="R15" s="423" t="n"/>
-      <c r="S15" s="423" t="n"/>
-      <c r="T15" s="423" t="n"/>
-      <c r="U15" s="423" t="n"/>
-      <c r="V15" s="423" t="n"/>
-      <c r="W15" s="423" t="n"/>
-      <c r="X15" s="423" t="n"/>
-      <c r="Y15" s="423" t="n"/>
-      <c r="Z15" s="423" t="n"/>
-      <c r="AA15" s="423" t="n"/>
-      <c r="AB15" s="423" t="n"/>
-      <c r="AC15" s="423" t="n"/>
-      <c r="AD15" s="423" t="n"/>
-      <c r="AE15" s="423" t="n"/>
-      <c r="AF15" s="423" t="n"/>
-      <c r="AG15" s="424" t="n"/>
-      <c r="AH15" s="647" t="n"/>
-      <c r="AI15" s="423" t="n"/>
-      <c r="AJ15" s="423" t="n"/>
-      <c r="AK15" s="423" t="n"/>
-      <c r="AL15" s="423" t="n"/>
-      <c r="AM15" s="423" t="n"/>
-      <c r="AN15" s="424" t="n"/>
-      <c r="AO15" s="647" t="n"/>
-      <c r="AP15" s="423" t="n"/>
-      <c r="AQ15" s="423" t="n"/>
-      <c r="AR15" s="423" t="n"/>
-      <c r="AS15" s="423" t="n"/>
-      <c r="AT15" s="423" t="n"/>
-      <c r="AU15" s="424" t="n"/>
-      <c r="AV15" s="647" t="n"/>
-      <c r="AW15" s="423" t="n"/>
-      <c r="AX15" s="423" t="n"/>
-      <c r="AY15" s="424" t="n"/>
-      <c r="AZ15" s="648" t="n"/>
-      <c r="BA15" s="423" t="n"/>
-      <c r="BB15" s="423" t="n"/>
-      <c r="BC15" s="423" t="n"/>
-      <c r="BD15" s="649" t="n"/>
+      <c r="B15" s="805" t="n"/>
+      <c r="C15" s="783" t="n"/>
+      <c r="D15" s="792" t="n"/>
+      <c r="E15" s="792" t="n"/>
+      <c r="F15" s="792" t="n"/>
+      <c r="G15" s="792" t="n"/>
+      <c r="H15" s="792" t="n"/>
+      <c r="I15" s="792" t="n"/>
+      <c r="J15" s="792" t="n"/>
+      <c r="K15" s="792" t="n"/>
+      <c r="L15" s="792" t="n"/>
+      <c r="M15" s="792" t="n"/>
+      <c r="N15" s="792" t="n"/>
+      <c r="O15" s="792" t="n"/>
+      <c r="P15" s="805" t="n"/>
+      <c r="Q15" s="783" t="n"/>
+      <c r="R15" s="792" t="n"/>
+      <c r="S15" s="792" t="n"/>
+      <c r="T15" s="792" t="n"/>
+      <c r="U15" s="792" t="n"/>
+      <c r="V15" s="792" t="n"/>
+      <c r="W15" s="792" t="n"/>
+      <c r="X15" s="792" t="n"/>
+      <c r="Y15" s="792" t="n"/>
+      <c r="Z15" s="792" t="n"/>
+      <c r="AA15" s="792" t="n"/>
+      <c r="AB15" s="792" t="n"/>
+      <c r="AC15" s="792" t="n"/>
+      <c r="AD15" s="792" t="n"/>
+      <c r="AE15" s="792" t="n"/>
+      <c r="AF15" s="792" t="n"/>
+      <c r="AG15" s="805" t="n"/>
+      <c r="AH15" s="783" t="n"/>
+      <c r="AI15" s="792" t="n"/>
+      <c r="AJ15" s="792" t="n"/>
+      <c r="AK15" s="792" t="n"/>
+      <c r="AL15" s="792" t="n"/>
+      <c r="AM15" s="792" t="n"/>
+      <c r="AN15" s="805" t="n"/>
+      <c r="AO15" s="783" t="n"/>
+      <c r="AP15" s="792" t="n"/>
+      <c r="AQ15" s="792" t="n"/>
+      <c r="AR15" s="792" t="n"/>
+      <c r="AS15" s="792" t="n"/>
+      <c r="AT15" s="792" t="n"/>
+      <c r="AU15" s="805" t="n"/>
+      <c r="AV15" s="783" t="n"/>
+      <c r="AW15" s="792" t="n"/>
+      <c r="AX15" s="792" t="n"/>
+      <c r="AY15" s="805" t="n"/>
+      <c r="AZ15" s="784" t="n"/>
+      <c r="BA15" s="792" t="n"/>
+      <c r="BB15" s="792" t="n"/>
+      <c r="BC15" s="792" t="n"/>
+      <c r="BD15" s="807" t="n"/>
     </row>
     <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="673">
+      <c r="A16" s="789">
         <f>ROW()-ROW($A$9)+1</f>
         <v/>
       </c>
-      <c r="B16" s="567" t="n"/>
-      <c r="C16" s="657" t="n"/>
-      <c r="D16" s="566" t="n"/>
-      <c r="E16" s="566" t="n"/>
-      <c r="F16" s="566" t="n"/>
-      <c r="G16" s="566" t="n"/>
-      <c r="H16" s="566" t="n"/>
-      <c r="I16" s="566" t="n"/>
-      <c r="J16" s="566" t="n"/>
-      <c r="K16" s="566" t="n"/>
-      <c r="L16" s="566" t="n"/>
-      <c r="M16" s="566" t="n"/>
-      <c r="N16" s="566" t="n"/>
-      <c r="O16" s="566" t="n"/>
-      <c r="P16" s="567" t="n"/>
-      <c r="Q16" s="657" t="n"/>
-      <c r="R16" s="566" t="n"/>
-      <c r="S16" s="566" t="n"/>
-      <c r="T16" s="566" t="n"/>
-      <c r="U16" s="566" t="n"/>
-      <c r="V16" s="566" t="n"/>
-      <c r="W16" s="566" t="n"/>
-      <c r="X16" s="566" t="n"/>
-      <c r="Y16" s="566" t="n"/>
-      <c r="Z16" s="566" t="n"/>
-      <c r="AA16" s="566" t="n"/>
-      <c r="AB16" s="566" t="n"/>
-      <c r="AC16" s="566" t="n"/>
-      <c r="AD16" s="566" t="n"/>
-      <c r="AE16" s="566" t="n"/>
-      <c r="AF16" s="566" t="n"/>
-      <c r="AG16" s="567" t="n"/>
-      <c r="AH16" s="657" t="n"/>
-      <c r="AI16" s="566" t="n"/>
-      <c r="AJ16" s="566" t="n"/>
-      <c r="AK16" s="566" t="n"/>
-      <c r="AL16" s="566" t="n"/>
-      <c r="AM16" s="566" t="n"/>
-      <c r="AN16" s="567" t="n"/>
-      <c r="AO16" s="657" t="n"/>
-      <c r="AP16" s="566" t="n"/>
-      <c r="AQ16" s="566" t="n"/>
-      <c r="AR16" s="566" t="n"/>
-      <c r="AS16" s="566" t="n"/>
-      <c r="AT16" s="566" t="n"/>
-      <c r="AU16" s="567" t="n"/>
-      <c r="AV16" s="657" t="n"/>
-      <c r="AW16" s="566" t="n"/>
-      <c r="AX16" s="566" t="n"/>
-      <c r="AY16" s="567" t="n"/>
-      <c r="AZ16" s="658" t="n"/>
-      <c r="BA16" s="566" t="n"/>
-      <c r="BB16" s="566" t="n"/>
-      <c r="BC16" s="566" t="n"/>
-      <c r="BD16" s="569" t="n"/>
+      <c r="B16" s="808" t="n"/>
+      <c r="C16" s="790" t="n"/>
+      <c r="D16" s="795" t="n"/>
+      <c r="E16" s="795" t="n"/>
+      <c r="F16" s="795" t="n"/>
+      <c r="G16" s="795" t="n"/>
+      <c r="H16" s="795" t="n"/>
+      <c r="I16" s="795" t="n"/>
+      <c r="J16" s="795" t="n"/>
+      <c r="K16" s="795" t="n"/>
+      <c r="L16" s="795" t="n"/>
+      <c r="M16" s="795" t="n"/>
+      <c r="N16" s="795" t="n"/>
+      <c r="O16" s="795" t="n"/>
+      <c r="P16" s="808" t="n"/>
+      <c r="Q16" s="790" t="n"/>
+      <c r="R16" s="795" t="n"/>
+      <c r="S16" s="795" t="n"/>
+      <c r="T16" s="795" t="n"/>
+      <c r="U16" s="795" t="n"/>
+      <c r="V16" s="795" t="n"/>
+      <c r="W16" s="795" t="n"/>
+      <c r="X16" s="795" t="n"/>
+      <c r="Y16" s="795" t="n"/>
+      <c r="Z16" s="795" t="n"/>
+      <c r="AA16" s="795" t="n"/>
+      <c r="AB16" s="795" t="n"/>
+      <c r="AC16" s="795" t="n"/>
+      <c r="AD16" s="795" t="n"/>
+      <c r="AE16" s="795" t="n"/>
+      <c r="AF16" s="795" t="n"/>
+      <c r="AG16" s="808" t="n"/>
+      <c r="AH16" s="790" t="n"/>
+      <c r="AI16" s="795" t="n"/>
+      <c r="AJ16" s="795" t="n"/>
+      <c r="AK16" s="795" t="n"/>
+      <c r="AL16" s="795" t="n"/>
+      <c r="AM16" s="795" t="n"/>
+      <c r="AN16" s="808" t="n"/>
+      <c r="AO16" s="790" t="n"/>
+      <c r="AP16" s="795" t="n"/>
+      <c r="AQ16" s="795" t="n"/>
+      <c r="AR16" s="795" t="n"/>
+      <c r="AS16" s="795" t="n"/>
+      <c r="AT16" s="795" t="n"/>
+      <c r="AU16" s="808" t="n"/>
+      <c r="AV16" s="790" t="n"/>
+      <c r="AW16" s="795" t="n"/>
+      <c r="AX16" s="795" t="n"/>
+      <c r="AY16" s="808" t="n"/>
+      <c r="AZ16" s="791" t="n"/>
+      <c r="BA16" s="795" t="n"/>
+      <c r="BB16" s="795" t="n"/>
+      <c r="BC16" s="795" t="n"/>
+      <c r="BD16" s="809" t="n"/>
     </row>
     <row r="17" ht="20" customHeight="1">
       <c r="A17" s="667" t="n"/>

--- a/04-Bieu-Mau/07-FRM-700/FRM-715_Vacuum_Compatible_Clean_Build_and_Bagging_Record.xlsx
+++ b/04-Bieu-Mau/07-FRM-700/FRM-715_Vacuum_Compatible_Clean_Build_and_Bagging_Record.xlsx
@@ -4547,6 +4547,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -4577,6 +4580,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -4607,6 +4613,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -6878,7 +6887,6 @@
     <row r="46" ht="4" customHeight="1"/>
     <row r="47" ht="24" customHeight="1"/>
   </sheetData>
-  <sheetProtection selectLockedCells="1" selectUnlockedCells="1" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="0" insertColumns="0" pivotTables="1" deleteRows="0" formatCells="0" formatRows="0" sort="1"/>
   <mergeCells count="117">
     <mergeCell ref="D18:G18"/>
     <mergeCell ref="AX18:BA18"/>
@@ -7516,7 +7524,6 @@
     <row r="39" ht="20" customHeight="1"/>
     <row r="40" ht="20" customHeight="1"/>
   </sheetData>
-  <sheetProtection selectLockedCells="1" selectUnlockedCells="1" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="0" insertColumns="0" pivotTables="1" deleteRows="0" formatCells="0" formatRows="0" sort="1"/>
   <mergeCells count="2">
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>
@@ -7766,7 +7773,6 @@
     <row r="29" ht="20" customHeight="1"/>
     <row r="30" ht="20" customHeight="1"/>
   </sheetData>
-  <sheetProtection selectLockedCells="1" selectUnlockedCells="1" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="0" insertColumns="0" pivotTables="1" deleteRows="0" formatCells="0" formatRows="0" sort="1"/>
   <autoFilter ref="A4:C14"/>
   <mergeCells count="2">
     <mergeCell ref="A2:G2"/>
@@ -7994,7 +8000,6 @@
     <row r="29" ht="20" customHeight="1"/>
     <row r="30" ht="20" customHeight="1"/>
   </sheetData>
-  <sheetProtection selectLockedCells="1" selectUnlockedCells="1" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="0" insertColumns="0" pivotTables="1" deleteRows="0" formatCells="0" formatRows="0" sort="1"/>
   <autoFilter ref="A4:C8"/>
   <mergeCells count="2">
     <mergeCell ref="A2:G2"/>

--- a/04-Bieu-Mau/07-FRM-700/FRM-715_Vacuum_Compatible_Clean_Build_and_Bagging_Record.xlsx
+++ b/04-Bieu-Mau/07-FRM-700/FRM-715_Vacuum_Compatible_Clean_Build_and_Bagging_Record.xlsx
@@ -8,10 +8,10 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VAC_BAG_GATE" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LISTS" sheetId="2" state="hidden" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CONDITIONS_ACTIONS" sheetId="3" state="hidden" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="REF_IMPORT" sheetId="4" state="hidden" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EVIDENCE_REF" sheetId="5" state="hidden" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LISTS" sheetId="2" state="veryHidden" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CONDITIONS_ACTIONS" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="REF_IMPORT" sheetId="4" state="veryHidden" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EVIDENCE_REF" sheetId="5" state="veryHidden" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'VAC_BAG_GATE'!$A$1:$BD$35</definedName>

--- a/04-Bieu-Mau/07-FRM-700/FRM-715_Vacuum_Compatible_Clean_Build_and_Bagging_Record.xlsx
+++ b/04-Bieu-Mau/07-FRM-700/FRM-715_Vacuum_Compatible_Clean_Build_and_Bagging_Record.xlsx
@@ -15,8 +15,6 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'VAC_BAG_GATE'!$A$1:$BD$35</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'REF_IMPORT'!$A$4:$C$14</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'EVIDENCE_REF'!$A$4:$C$8</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -7773,7 +7771,6 @@
     <row r="29" ht="20" customHeight="1"/>
     <row r="30" ht="20" customHeight="1"/>
   </sheetData>
-  <autoFilter ref="A4:C14"/>
   <mergeCells count="2">
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>
@@ -8000,7 +7997,6 @@
     <row r="29" ht="20" customHeight="1"/>
     <row r="30" ht="20" customHeight="1"/>
   </sheetData>
-  <autoFilter ref="A4:C8"/>
   <mergeCells count="2">
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>

--- a/04-Bieu-Mau/07-FRM-700/FRM-715_Vacuum_Compatible_Clean_Build_and_Bagging_Record.xlsx
+++ b/04-Bieu-Mau/07-FRM-700/FRM-715_Vacuum_Compatible_Clean_Build_and_Bagging_Record.xlsx
@@ -8,13 +8,16 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VAC_BAG_GATE" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LISTS" sheetId="2" state="veryHidden" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CONDITIONS_ACTIONS" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="REF_IMPORT" sheetId="4" state="veryHidden" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EVIDENCE_REF" sheetId="5" state="veryHidden" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LISTS" sheetId="2" state="hidden" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CONDITIONS_ACTIONS" sheetId="3" state="hidden" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="REF_IMPORT" sheetId="4" state="hidden" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EVIDENCE_REF" sheetId="5" state="hidden" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="REV_HISTORY" sheetId="6" state="hidden" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'VAC_BAG_GATE'!$A$1:$BD$35</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'REF_IMPORT'!$A$4:$C$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'EVIDENCE_REF'!$A$4:$C$8</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -4522,105 +4525,6 @@
 </wsDr>
 </file>
 
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>161925</colOff>
-      <row>0</row>
-      <rowOff>314325</rowOff>
-    </from>
-    <ext cx="1123950" cy="323850"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="1" name="Image 1" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-</wsDr>
-</file>
-
-<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>161925</colOff>
-      <row>0</row>
-      <rowOff>314325</rowOff>
-    </from>
-    <ext cx="1123950" cy="323850"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="1" name="Image 1" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-</wsDr>
-</file>
-
-<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>161925</colOff>
-      <row>0</row>
-      <rowOff>314325</rowOff>
-    </from>
-    <ext cx="1123950" cy="323850"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="1" name="Image 1" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-</wsDr>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="FRM_707_COND" displayName="FRM_715_COND" ref="A4:H14" headerRowCount="1">
   <autoFilter ref="A4:H14"/>
@@ -5569,7 +5473,7 @@
     <row r="12" ht="20" customHeight="1">
       <c r="A12" s="287" t="inlineStr">
         <is>
-          <t>Evidence Package Ref</t>
+          <t>Linked FRM-711 / FRM-712</t>
         </is>
       </c>
       <c r="B12" s="271" t="n"/>
@@ -5601,7 +5505,7 @@
       <c r="AB12" s="321" t="n"/>
       <c r="AC12" s="289" t="inlineStr">
         <is>
-          <t>Record Status</t>
+          <t>Ref: SOP-701</t>
         </is>
       </c>
       <c r="AD12" s="271" t="n"/>
@@ -5613,7 +5517,11 @@
       <c r="AJ12" s="271" t="n"/>
       <c r="AK12" s="271" t="n"/>
       <c r="AL12" s="272" t="n"/>
-      <c r="AM12" s="290" t="n"/>
+      <c r="AM12" s="290" t="inlineStr">
+        <is>
+          <t>Retain: 10 years per QMS schedule</t>
+        </is>
+      </c>
       <c r="AN12" s="320" t="n"/>
       <c r="AO12" s="320" t="n"/>
       <c r="AP12" s="320" t="n"/>
@@ -6885,6 +6793,7 @@
     <row r="46" ht="4" customHeight="1"/>
     <row r="47" ht="24" customHeight="1"/>
   </sheetData>
+  <sheetProtection selectLockedCells="1" selectUnlockedCells="1" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="0" insertColumns="0" pivotTables="1" deleteRows="0" formatCells="0" formatRows="0" sort="1"/>
   <mergeCells count="117">
     <mergeCell ref="D18:G18"/>
     <mergeCell ref="AX18:BA18"/>
@@ -7522,6 +7431,7 @@
     <row r="39" ht="20" customHeight="1"/>
     <row r="40" ht="20" customHeight="1"/>
   </sheetData>
+  <sheetProtection selectLockedCells="1" selectUnlockedCells="1" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="0" insertColumns="0" pivotTables="1" deleteRows="0" formatCells="0" formatRows="0" sort="1"/>
   <mergeCells count="2">
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>
@@ -7538,10 +7448,9 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   <tableParts count="2">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
   </tableParts>
 </worksheet>
 </file>
@@ -7771,12 +7680,13 @@
     <row r="29" ht="20" customHeight="1"/>
     <row r="30" ht="20" customHeight="1"/>
   </sheetData>
+  <sheetProtection selectLockedCells="1" selectUnlockedCells="1" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="0" insertColumns="0" pivotTables="1" deleteRows="0" formatCells="0" formatRows="0" sort="1"/>
+  <autoFilter ref="A4:C14"/>
   <mergeCells count="2">
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -7997,11 +7907,92 @@
     <row r="29" ht="20" customHeight="1"/>
     <row r="30" ht="20" customHeight="1"/>
   </sheetData>
+  <sheetProtection selectLockedCells="1" selectUnlockedCells="1" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="0" insertColumns="0" pivotTables="1" deleteRows="0" formatCells="0" formatRows="0" sort="1"/>
+  <autoFilter ref="A4:C8"/>
   <mergeCells count="2">
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Rev</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Author</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>V0</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Initial release</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>QMS Team</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>V1</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Cross-ref: FRM-711, FRM-712; Parent ref: SOP-701</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>QMS Upgrade</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/04-Bieu-Mau/07-FRM-700/FRM-715_Vacuum_Compatible_Clean_Build_and_Bagging_Record.xlsx
+++ b/04-Bieu-Mau/07-FRM-700/FRM-715_Vacuum_Compatible_Clean_Build_and_Bagging_Record.xlsx
@@ -4953,6 +4953,88 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>QMS</author>
+  </authors>
+  <commentList>
+    <comment ref="A9" authorId="0" shapeId="0">
+      <text>
+        <t xml:space="preserve">Số Job
+</t>
+      </text>
+    </comment>
+    <comment ref="U9" authorId="0" shapeId="0">
+      <text>
+        <t xml:space="preserve">Mã chi tiết
+</t>
+      </text>
+    </comment>
+    <comment ref="A10" authorId="0" shapeId="0">
+      <text>
+        <t xml:space="preserve">Ngày
+</t>
+      </text>
+    </comment>
+    <comment ref="U10" authorId="0" shapeId="0">
+      <text>
+        <t xml:space="preserve">Kỹ thuật viên
+</t>
+      </text>
+    </comment>
+    <comment ref="F14" authorId="0" shapeId="0">
+      <text>
+        <t>Sạch
+FRM-711 đã PASS.</t>
+      </text>
+    </comment>
+    <comment ref="F15" authorId="0" shapeId="0">
+      <text>
+        <t>Găng tay
+Lint-free, powder-free, cleanroom grade.</t>
+      </text>
+    </comment>
+    <comment ref="F16" authorId="0" shapeId="0">
+      <text>
+        <t>Khu vực sạch
+Laminar flow bench hoặc cleanroom.</t>
+      </text>
+    </comment>
+    <comment ref="F17" authorId="0" shapeId="0">
+      <text>
+        <t>Vật liệu
+Vacuum-grade PE/Nylon bag.</t>
+      </text>
+    </comment>
+    <comment ref="F18" authorId="0" shapeId="0">
+      <text>
+        <t>Seal chân không
+Kiểm tra seal kín, không rò.</t>
+      </text>
+    </comment>
+    <comment ref="F19" authorId="0" shapeId="0">
+      <text>
+        <t>Nhãn
+Clean label, không gây ô nhiễm.</t>
+      </text>
+    </comment>
+    <comment ref="F20" authorId="0" shapeId="0">
+      <text>
+        <t>Leak check
+Nếu yêu cầu → kiểm tra seal bằng vacuum.</t>
+      </text>
+    </comment>
+    <comment ref="F21" authorId="0" shapeId="0">
+      <text>
+        <t>Release
+Phê duyệt cuối cùng.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5862,8 +5944,9 @@
       <c r="AN13" s="479" t="n"/>
     </row>
     <row r="14" ht="20" customHeight="1" s="264">
-      <c r="A14" s="490" t="n">
-        <v>1</v>
+      <c r="A14" s="490">
+        <f>ROW()-ROW($A$14)+1</f>
+        <v/>
       </c>
       <c r="B14" s="491" t="n"/>
       <c r="C14" s="492" t="inlineStr">
@@ -5875,7 +5958,7 @@
       <c r="E14" s="491" t="n"/>
       <c r="F14" s="494" t="inlineStr">
         <is>
-          <t>Cleanliness verification passed (FRM-711).</t>
+          <t>Cleanliness verified (FRM-711).</t>
         </is>
       </c>
       <c r="G14" s="493" t="n"/>
@@ -5918,8 +6001,9 @@
       <c r="AN14" s="498" t="n"/>
     </row>
     <row r="15" ht="20" customHeight="1" s="264">
-      <c r="A15" s="490" t="n">
-        <v>2</v>
+      <c r="A15" s="490">
+        <f>ROW()-ROW($A$14)+1</f>
+        <v/>
       </c>
       <c r="B15" s="491" t="n"/>
       <c r="C15" s="492" t="inlineStr">
@@ -5931,7 +6015,7 @@
       <c r="E15" s="491" t="n"/>
       <c r="F15" s="499" t="inlineStr">
         <is>
-          <t>Glove protocol followed (lint-free, powder-free).</t>
+          <t>Glove protocol followed.</t>
         </is>
       </c>
       <c r="G15" s="493" t="n"/>
@@ -5951,7 +6035,7 @@
       <c r="U15" s="491" t="n"/>
       <c r="V15" s="495" t="inlineStr">
         <is>
-          <t>Correct glove type used.</t>
+          <t>Lint-free, powder-free.</t>
         </is>
       </c>
       <c r="W15" s="493" t="n"/>
@@ -5974,8 +6058,9 @@
       <c r="AN15" s="498" t="n"/>
     </row>
     <row r="16" ht="20" customHeight="1" s="264">
-      <c r="A16" s="490" t="n">
-        <v>3</v>
+      <c r="A16" s="490">
+        <f>ROW()-ROW($A$14)+1</f>
+        <v/>
       </c>
       <c r="B16" s="491" t="n"/>
       <c r="C16" s="492" t="inlineStr">
@@ -5987,7 +6072,7 @@
       <c r="E16" s="491" t="n"/>
       <c r="F16" s="494" t="inlineStr">
         <is>
-          <t>Assembly in clean area / laminar flow bench.</t>
+          <t>Assembly in clean area / laminar flow.</t>
         </is>
       </c>
       <c r="G16" s="493" t="n"/>
@@ -6030,8 +6115,9 @@
       <c r="AN16" s="498" t="n"/>
     </row>
     <row r="17" ht="20" customHeight="1" s="264">
-      <c r="A17" s="490" t="n">
-        <v>4</v>
+      <c r="A17" s="490">
+        <f>ROW()-ROW($A$14)+1</f>
+        <v/>
       </c>
       <c r="B17" s="491" t="n"/>
       <c r="C17" s="492" t="inlineStr">
@@ -6043,7 +6129,7 @@
       <c r="E17" s="491" t="n"/>
       <c r="F17" s="499" t="inlineStr">
         <is>
-          <t>Vacuum-compatible bagging material used.</t>
+          <t>Vacuum-compatible bagging material.</t>
         </is>
       </c>
       <c r="G17" s="493" t="n"/>
@@ -6086,8 +6172,9 @@
       <c r="AN17" s="498" t="n"/>
     </row>
     <row r="18" ht="20" customHeight="1" s="264">
-      <c r="A18" s="490" t="n">
-        <v>5</v>
+      <c r="A18" s="490">
+        <f>ROW()-ROW($A$14)+1</f>
+        <v/>
       </c>
       <c r="B18" s="491" t="n"/>
       <c r="C18" s="492" t="inlineStr">
@@ -6142,8 +6229,9 @@
       <c r="AN18" s="498" t="n"/>
     </row>
     <row r="19" ht="20" customHeight="1" s="264">
-      <c r="A19" s="490" t="n">
-        <v>6</v>
+      <c r="A19" s="490">
+        <f>ROW()-ROW($A$14)+1</f>
+        <v/>
       </c>
       <c r="B19" s="491" t="n"/>
       <c r="C19" s="492" t="inlineStr">
@@ -6155,7 +6243,7 @@
       <c r="E19" s="491" t="n"/>
       <c r="F19" s="499" t="inlineStr">
         <is>
-          <t>Identification label applied (clean method).</t>
+          <t>Identification label applied.</t>
         </is>
       </c>
       <c r="G19" s="493" t="n"/>
@@ -6198,8 +6286,9 @@
       <c r="AN19" s="498" t="n"/>
     </row>
     <row r="20" ht="20" customHeight="1" s="264">
-      <c r="A20" s="490" t="n">
-        <v>7</v>
+      <c r="A20" s="490">
+        <f>ROW()-ROW($A$14)+1</f>
+        <v/>
       </c>
       <c r="B20" s="491" t="n"/>
       <c r="C20" s="492" t="inlineStr">
@@ -6254,8 +6343,9 @@
       <c r="AN20" s="498" t="n"/>
     </row>
     <row r="21" ht="20" customHeight="1" s="264">
-      <c r="A21" s="490" t="n">
-        <v>8</v>
+      <c r="A21" s="490">
+        <f>ROW()-ROW($A$14)+1</f>
+        <v/>
       </c>
       <c r="B21" s="491" t="n"/>
       <c r="C21" s="492" t="inlineStr">
@@ -6310,8 +6400,9 @@
       <c r="AN21" s="498" t="n"/>
     </row>
     <row r="22" ht="20" customHeight="1" s="264">
-      <c r="A22" s="490" t="n">
-        <v>9</v>
+      <c r="A22" s="490">
+        <f>ROW()-ROW($A$14)+1</f>
+        <v/>
       </c>
       <c r="B22" s="491" t="n"/>
       <c r="C22" s="500" t="n"/>
@@ -6354,8 +6445,9 @@
       <c r="AN22" s="498" t="n"/>
     </row>
     <row r="23" ht="20" customHeight="1" s="264">
-      <c r="A23" s="502" t="n">
-        <v>10</v>
+      <c r="A23" s="502">
+        <f>ROW()-ROW($A$14)+1</f>
+        <v/>
       </c>
       <c r="B23" s="482" t="n"/>
       <c r="C23" s="503" t="n"/>
@@ -6678,7 +6770,7 @@
     <row r="31" ht="24" customHeight="1" s="264">
       <c r="A31" s="514" t="inlineStr">
         <is>
-          <t>NOTICE — Vacuum-compatible parts only. Ref: SOP-701. Retain: 10 years.</t>
+          <t>NOTICE — Vacuum-compatible parts. Ref: SOP-701. Retain: 10 years.</t>
         </is>
       </c>
       <c r="B31" s="471" t="n"/>
@@ -6843,6 +6935,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
